--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kp_generator\templates_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CE47DE-2732-4DA9-AC33-7D9E7C0B67A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716BADE0-C532-4B0D-92A6-DA2756812951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="294" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
   <si>
     <t>По номенклатуре:</t>
   </si>
@@ -59,69 +59,6 @@
   </si>
   <si>
     <t>Наименование поставщика / Склад резервирования</t>
-  </si>
-  <si>
-    <t>По потребителю:</t>
-  </si>
-  <si>
-    <t>Фактически оплачено по спецификации</t>
-  </si>
-  <si>
-    <t>Процент оплаты</t>
-  </si>
-  <si>
-    <t>Итого по спецификации</t>
-  </si>
-  <si>
-    <t>№</t>
-  </si>
-  <si>
-    <t>Итого по бюджету сделки</t>
-  </si>
-  <si>
-    <t>Прогноз выручки по контракту</t>
-  </si>
-  <si>
-    <t>Сумма НДС (начислено)</t>
-  </si>
-  <si>
-    <t>Менеджер:</t>
-  </si>
-  <si>
-    <t>Выручка по контракту (без НДС)</t>
-  </si>
-  <si>
-    <t>Всего прямых затрат, в т.ч. (без НДС)</t>
-  </si>
-  <si>
-    <t>- стоимость контракта</t>
-  </si>
-  <si>
-    <t>- таможенная пошлина (плановая)</t>
-  </si>
-  <si>
-    <t>- транспортные до границы РФ</t>
-  </si>
-  <si>
-    <t>- транспортные по РФ</t>
-  </si>
-  <si>
-    <t>Бондарева В. В.</t>
-  </si>
-  <si>
-    <t>Маржинальный доход (вклад на покрытие), руб</t>
-  </si>
-  <si>
-    <t>Скидка, %</t>
-  </si>
-  <si>
-    <t>Маржинальный доход , %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Договор поставки: </t>
-  </si>
-  <si>
-    <t>Коммерческий директор:</t>
   </si>
   <si>
     <t>Вес, кг</t>
@@ -199,29 +136,8 @@
     <t>шт.</t>
   </si>
   <si>
-    <t>КРЕДИТ</t>
-  </si>
-  <si>
-    <t>БАНКОВСКАЯ ГАРАНТИЯ</t>
-  </si>
-  <si>
-    <t>ДА</t>
-  </si>
-  <si>
-    <t>НЕТ</t>
-  </si>
-  <si>
-    <t>Длина сделки</t>
-  </si>
-  <si>
-    <t>Ген. директор</t>
-  </si>
-  <si>
     <t>Бюджет сделки по документу Спецификация ___ от  _____ 2024 г.
  на момент последнего движения</t>
-  </si>
-  <si>
-    <t>Тунегов Я.Ю.</t>
   </si>
   <si>
     <t>ТД РИНАКО</t>
@@ -231,15 +147,6 @@
   </si>
   <si>
     <t>№ п/п</t>
-  </si>
-  <si>
-    <t>РФ</t>
-  </si>
-  <si>
-    <t>КНР</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - сертификация</t>
   </si>
   <si>
     <t>Номер тендера:</t>
@@ -260,45 +167,117 @@
     <t>¥/кг покупка</t>
   </si>
   <si>
-    <t>Итого без ндс</t>
+    <t xml:space="preserve">KONTRAGENT
+</t>
   </si>
   <si>
-    <t>Итого с ндс</t>
+    <t>%</t>
   </si>
   <si>
-    <t>ПНР</t>
+    <t>Сумма в рублях</t>
   </si>
   <si>
-    <t xml:space="preserve"> - шеф-монтаж</t>
+    <t>По потребителю:</t>
   </si>
   <si>
-    <t xml:space="preserve">KONTRAGENT
-</t>
+    <t xml:space="preserve">Договор поставки: </t>
+  </si>
+  <si>
+    <t>Условия Поставки: 140-150 календарных дней с даты подписания спецификации последней стороной.</t>
   </si>
   <si>
     <t xml:space="preserve">Условия оплаты:  100% в течение 30 календарных дней от даты поставки
 </t>
   </si>
   <si>
-    <t>Условия Поставки: 140-150 календарных дней с даты подписания спецификации последней стороной.</t>
+    <t>Длина сделки</t>
   </si>
   <si>
-    <t>%</t>
+    <t>Итого без ндс</t>
   </si>
   <si>
-    <t>Власов М.Д.</t>
+    <t>Фактически оплачено по спецификации</t>
   </si>
   <si>
-    <t>КНР-</t>
+    <t>Итого с ндс</t>
   </si>
   <si>
-    <t>Сумма в рублях</t>
+    <t>Процент оплаты</t>
+  </si>
+  <si>
+    <t>Итого по спецификации</t>
+  </si>
+  <si>
+    <t>Итого по бюджету сделки</t>
+  </si>
+  <si>
+    <t>Прогноз выручки по контракту</t>
+  </si>
+  <si>
+    <t>Сумма НДС (начислено)</t>
+  </si>
+  <si>
+    <t>Выручка по контракту (без НДС)</t>
+  </si>
+  <si>
+    <t>Всего прямых затрат, в т.ч. (без НДС)</t>
+  </si>
+  <si>
+    <t>- стоимость контракта</t>
   </si>
   <si>
     <t xml:space="preserve"> - стоимость конвертации (3,2%)</t>
   </si>
   <si>
+    <t>КНР</t>
+  </si>
+  <si>
+    <t>- таможенная пошлина (плановая)</t>
+  </si>
+  <si>
+    <t>- транспортные до границы РФ</t>
+  </si>
+  <si>
+    <t>- транспортные по РФ</t>
+  </si>
+  <si>
+    <t>ДА</t>
+  </si>
+  <si>
+    <t>НЕТ</t>
+  </si>
+  <si>
+    <t>РФ</t>
+  </si>
+  <si>
+    <t>КРЕДИТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - сертификация</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - шеф-монтаж</t>
+  </si>
+  <si>
+    <t>БАНКОВСКАЯ ГАРАНТИЯ</t>
+  </si>
+  <si>
+    <t>- ПНР</t>
+  </si>
+  <si>
+    <t>Маржинальный доход (вклад на покрытие), руб</t>
+  </si>
+  <si>
+    <t>Скидка, %</t>
+  </si>
+  <si>
+    <t>Маржинальный доход , %</t>
+  </si>
+  <si>
     <t>{{ company }}</t>
+  </si>
+  <si>
+    <t>{{ product }} ч.{{ drawing_number }}</t>
   </si>
   <si>
     <t>{{ quantity }}</t>
@@ -313,7 +292,7 @@
     <t>{{ logistics }}</t>
   </si>
   <si>
-    <t>{{ product }} ч.{{ drawing_number }}</t>
+    <t>КНР-</t>
   </si>
 </sst>
 </file>
@@ -345,7 +324,7 @@
     <numFmt numFmtId="184" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="185" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -623,6 +602,13 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -645,12 +631,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -658,6 +638,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,26 +675,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -790,54 +756,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -892,6 +810,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1662">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3125,7 +3111,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3133,10 +3119,10 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3145,26 +3131,26 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3191,481 +3177,433 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="1655" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="38" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="37" fillId="3" borderId="14" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="39" fillId="0" borderId="13" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="39" fillId="0" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="32" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="0" borderId="14" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="3" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="39" fillId="0" borderId="10" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="32" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="0" borderId="3" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="2" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="180" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="32" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="179" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="37" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="37" fillId="4" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="1655" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="38" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="38" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="38" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="37" fillId="3" borderId="20" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="3" borderId="20" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="32" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="32" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="32" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="39" fillId="0" borderId="19" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="39" fillId="0" borderId="18" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="32" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="0" borderId="20" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="3" borderId="11" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="32" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="39" fillId="0" borderId="16" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="32" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="0" borderId="3" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="32" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="32" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="32" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="5" borderId="6" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="0" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="2" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1662">
@@ -5676,24 +5614,25 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AG44"/>
+  <dimension ref="A1:AZ522"/>
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="11.45" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="0.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="54.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.1640625" style="1" customWidth="1"/>
-    <col min="9" max="11" width="20.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="149" customWidth="1"/>
+    <col min="10" max="11" width="20.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="16.1640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.1640625" style="104" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" style="104" customWidth="1"/>
+    <col min="16" max="16" width="11.1640625" style="97" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" style="97" customWidth="1"/>
     <col min="18" max="18" width="16.6640625" style="8" customWidth="1"/>
     <col min="19" max="19" width="15.6640625" style="8" customWidth="1"/>
     <col min="20" max="20" width="16.1640625" style="8" customWidth="1"/>
@@ -5709,53 +5648,67 @@
     <col min="32" max="16384" width="10.1640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="165" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
-      <c r="L1" s="165"/>
-      <c r="M1" s="165"/>
-      <c r="N1" s="165"/>
-      <c r="O1" s="165"/>
-    </row>
-    <row r="2" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1">
+    <row r="1" spans="1:52" s="1" customFormat="1" ht="32.1" customHeight="1">
+      <c r="B1" s="166" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="167"/>
+      <c r="N1" s="167"/>
+      <c r="O1" s="168"/>
+      <c r="AD1" s="172"/>
+      <c r="AU1"/>
+      <c r="AV1"/>
+      <c r="AW1"/>
+      <c r="AX1"/>
+      <c r="AY1"/>
+      <c r="AZ1"/>
+    </row>
+    <row r="2" spans="1:52" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="2"/>
+      <c r="I2" s="142"/>
       <c r="J2" s="6"/>
-      <c r="V2" s="172"/>
-      <c r="W2" s="172"/>
-      <c r="X2" s="172"/>
-      <c r="Y2" s="172"/>
-      <c r="Z2" s="172"/>
-    </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1">
+      <c r="V2" s="135"/>
+      <c r="W2" s="135"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="135"/>
+      <c r="Z2" s="135"/>
+      <c r="AD2" s="172"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+    </row>
+    <row r="3" spans="1:52" ht="15" customHeight="1">
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="2"/>
+      <c r="I3" s="142"/>
       <c r="J3" s="5"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5764,53 +5717,67 @@
       <c r="O3" s="5"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="172"/>
-    </row>
-    <row r="4" spans="1:30" ht="39.75" customHeight="1">
+      <c r="V3" s="135"/>
+      <c r="W3" s="135"/>
+      <c r="X3" s="135"/>
+      <c r="Y3" s="135"/>
+      <c r="Z3" s="135"/>
+      <c r="AD3" s="172"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3"/>
+      <c r="AZ3"/>
+    </row>
+    <row r="4" spans="1:52" ht="39.75" customHeight="1">
       <c r="B4" s="9"/>
       <c r="C4" s="10" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="142"/>
       <c r="J4" s="5"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="174"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="172"/>
-      <c r="W4" s="172"/>
-      <c r="X4" s="172"/>
-      <c r="Y4" s="172"/>
-      <c r="Z4" s="172"/>
-    </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1">
+      <c r="P4" s="169"/>
+      <c r="Q4" s="170"/>
+      <c r="R4" s="170"/>
+      <c r="S4" s="170"/>
+      <c r="T4" s="170"/>
+      <c r="U4" s="171"/>
+      <c r="V4" s="135"/>
+      <c r="W4" s="135"/>
+      <c r="X4" s="135"/>
+      <c r="Y4" s="135"/>
+      <c r="Z4" s="135"/>
+      <c r="AD4" s="172"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4"/>
+      <c r="AZ4"/>
+    </row>
+    <row r="5" spans="1:52" ht="15" customHeight="1">
       <c r="B5" s="12"/>
       <c r="C5" s="13" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="15"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
+      <c r="I5" s="143"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -5823,81 +5790,102 @@
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
-      <c r="V5" s="172"/>
-      <c r="W5" s="172"/>
-      <c r="X5" s="172"/>
-      <c r="Y5" s="172"/>
-      <c r="Z5" s="172"/>
-    </row>
-    <row r="6" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="135"/>
+      <c r="Z5" s="135"/>
+      <c r="AD5" s="172"/>
+      <c r="AU5"/>
+      <c r="AV5"/>
+      <c r="AW5"/>
+      <c r="AX5"/>
+      <c r="AY5"/>
+      <c r="AZ5"/>
+    </row>
+    <row r="6" spans="1:52" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="180" t="s">
+      <c r="B6" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="180"/>
+      <c r="C6" s="138"/>
       <c r="D6" s="18"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
+      <c r="I6" s="144"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
-      <c r="V6" s="173"/>
-      <c r="W6" s="173"/>
-      <c r="X6" s="173"/>
-      <c r="Y6" s="173"/>
-      <c r="Z6" s="173"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1">
+      <c r="V6" s="136"/>
+      <c r="W6" s="136"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AD6" s="172"/>
+      <c r="AU6"/>
+      <c r="AV6"/>
+      <c r="AW6"/>
+      <c r="AX6"/>
+      <c r="AY6"/>
+      <c r="AZ6"/>
+    </row>
+    <row r="7" spans="1:52" ht="15" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="183" t="s">
+      <c r="B7" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="166"/>
-      <c r="D7" s="166"/>
-      <c r="E7" s="166"/>
-      <c r="F7" s="166"/>
-      <c r="G7" s="166"/>
-      <c r="H7" s="166"/>
-      <c r="I7" s="166"/>
-      <c r="J7" s="167"/>
-      <c r="K7" s="166" t="s">
+      <c r="C7" s="133"/>
+      <c r="D7" s="133"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="145"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="166"/>
-      <c r="M7" s="166"/>
-      <c r="N7" s="166"/>
-      <c r="O7" s="166"/>
-      <c r="P7" s="166"/>
-      <c r="Q7" s="166"/>
-      <c r="R7" s="166"/>
-      <c r="S7" s="166"/>
-      <c r="T7" s="166"/>
-      <c r="U7" s="166"/>
-      <c r="V7" s="166"/>
-      <c r="W7" s="166"/>
-      <c r="X7" s="166"/>
-      <c r="Y7" s="166"/>
-      <c r="Z7" s="167"/>
-    </row>
-    <row r="8" spans="1:30" s="22" customFormat="1" ht="54.75" customHeight="1">
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="133"/>
+      <c r="X7" s="133"/>
+      <c r="Y7" s="133"/>
+      <c r="Z7" s="134"/>
+      <c r="AD7" s="172"/>
+      <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+    </row>
+    <row r="8" spans="1:52" s="22" customFormat="1" ht="54.75" customHeight="1">
       <c r="A8" s="21"/>
       <c r="B8" s="22" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>4</v>
@@ -5906,13 +5894,13 @@
         <v>5</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="I8" s="146" t="s">
+        <v>26</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K8" s="25" t="s">
         <v>6</v>
@@ -5921,1298 +5909,5749 @@
         <v>5</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="P8" s="25" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="S8" s="28" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T8" s="27" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="V8" s="25" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="W8" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="X8" s="181" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y8" s="182"/>
+        <v>41</v>
+      </c>
+      <c r="X8" s="139" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y8" s="140"/>
       <c r="Z8" s="25" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
       <c r="AC8" s="30"/>
-      <c r="AD8" s="21"/>
-    </row>
-    <row r="9" spans="1:30" s="42" customFormat="1" ht="19.5" customHeight="1">
+      <c r="AD8" s="172"/>
+      <c r="AU8"/>
+      <c r="AV8"/>
+      <c r="AW8"/>
+      <c r="AX8"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+    </row>
+    <row r="9" spans="1:52" s="40" customFormat="1" ht="19.5" customHeight="1">
       <c r="A9" s="31"/>
-      <c r="B9" s="179">
+      <c r="B9" s="137">
         <v>1</v>
       </c>
-      <c r="C9" s="179"/>
+      <c r="C9" s="137"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33">
+      <c r="E9" s="126"/>
+      <c r="F9" s="126">
         <v>2</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="126">
         <v>3</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="33">
         <v>4</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="147">
         <v>5</v>
       </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="34">
+      <c r="J9" s="34"/>
+      <c r="K9" s="33">
         <v>6</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="35">
         <v>7</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="33">
         <v>8</v>
       </c>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34">
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>9</v>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="33">
         <v>10</v>
       </c>
-      <c r="Q9" s="37">
+      <c r="Q9" s="36">
         <v>11</v>
       </c>
-      <c r="R9" s="37">
+      <c r="R9" s="36">
         <v>12</v>
       </c>
-      <c r="S9" s="37">
+      <c r="S9" s="36">
         <v>13</v>
       </c>
-      <c r="T9" s="37">
+      <c r="T9" s="36">
         <v>14</v>
       </c>
-      <c r="U9" s="38">
+      <c r="U9" s="37">
         <v>15</v>
       </c>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38">
+      <c r="V9" s="37"/>
+      <c r="W9" s="37">
         <v>16</v>
       </c>
-      <c r="X9" s="38">
+      <c r="X9" s="37">
         <v>17</v>
       </c>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38">
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37">
         <v>19</v>
       </c>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="41"/>
-    </row>
-    <row r="10" spans="1:30" s="65" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A10" s="43"/>
-      <c r="B10" s="44">
+      <c r="AA9" s="38"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="172"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+      <c r="AY9"/>
+      <c r="AZ9"/>
+    </row>
+    <row r="10" spans="1:52" s="61" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A10" s="41"/>
+      <c r="B10" s="42">
         <v>1</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="184" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49" t="e">
+      <c r="C10" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="44"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="162" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="47"/>
+      <c r="I10" s="148" t="e">
         <f>G10*H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="50" t="e">
+      <c r="J10" s="48" t="e">
         <f>I10*14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K10" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="52" t="str">
+      <c r="K10" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="50" t="str">
         <f>G10</f>
         <v>{{ quantity }}</v>
       </c>
-      <c r="M10" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="N10" s="54" t="e">
+      <c r="M10" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="N10" s="52" t="e">
         <f>M10/P10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O10" s="55" t="e">
+      <c r="O10" s="53" t="e">
         <f>M10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P10" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="57" t="e">
+      <c r="P10" s="163" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q10" s="54" t="e">
         <f>P10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R10" s="58" t="e">
-        <f>$U$14/Q11*P10/12*0.3</f>
+      <c r="R10" s="104" t="e">
+        <f>$U$14/$Q$11*P10/12*0.3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S10" s="58" t="e">
+      <c r="S10" s="55" t="e">
         <f>R10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="T10" s="58" t="e">
-        <f>$U$14/Q11*P10/12*0.7</f>
+      <c r="T10" s="55" t="e">
+        <f>$U$14/$Q$11*P10/12*0.7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U10" s="58" t="e">
+      <c r="U10" s="55" t="e">
         <f>T10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V10" s="59" t="e">
+      <c r="V10" s="56" t="e">
         <f>H10/P10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W10" s="54" t="e">
+      <c r="W10" s="52" t="e">
         <f>N10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X10" s="60" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y10" s="61" t="e">
+      <c r="X10" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y10" s="58" t="e">
         <f>L10*(M10+R10)*X10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z10" s="62" t="e">
+      <c r="Z10" s="59" t="e">
         <f>(I10-O10-S10-U10-Y10-AA10-AC10-AB10)/I10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA10" s="63"/>
-      <c r="AB10" s="63"/>
-      <c r="AC10" s="63"/>
-      <c r="AD10" s="64"/>
-    </row>
-    <row r="11" spans="1:30" s="65" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="43"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="49" t="e">
+      <c r="AA10" s="60"/>
+      <c r="AB10" s="60"/>
+      <c r="AC10" s="60"/>
+      <c r="AD10" s="172"/>
+      <c r="AU10"/>
+      <c r="AV10"/>
+      <c r="AW10"/>
+      <c r="AX10"/>
+      <c r="AY10"/>
+      <c r="AZ10"/>
+    </row>
+    <row r="11" spans="1:52" s="61" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="41"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="148" t="e">
         <f>SUM(I10:I10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="73"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="49" t="e">
+      <c r="J11" s="66"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="47" t="e">
         <f>SUM(O10:O10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="77" t="e">
+      <c r="P11" s="71"/>
+      <c r="Q11" s="72" t="e">
         <f>SUM(Q10:Q10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R11" s="78"/>
-      <c r="S11" s="49" t="e">
+      <c r="R11" s="73"/>
+      <c r="S11" s="47" t="e">
         <f>SUM(S10:S10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="T11" s="79"/>
-      <c r="U11" s="79" t="e">
+      <c r="T11" s="74"/>
+      <c r="U11" s="74" t="e">
         <f>SUM(U10:U10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V11" s="80"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="82" t="e">
+      <c r="V11" s="75"/>
+      <c r="W11" s="76"/>
+      <c r="X11" s="77" t="e">
         <f>AVERAGE(X10:X10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y11" s="49" t="e">
+      <c r="Y11" s="47" t="e">
         <f>SUM(Y10:Y10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z11" s="83" t="e">
+      <c r="Z11" s="78" t="e">
         <f>(I11-O11-S11-U11-Y11-AA11-AC11-AB11)/I11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="63"/>
-      <c r="AC11" s="63"/>
-      <c r="AD11" s="8"/>
-    </row>
-    <row r="12" spans="1:30" s="65" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="43"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="49" t="e">
+      <c r="AA11" s="60"/>
+      <c r="AB11" s="60"/>
+      <c r="AC11" s="60"/>
+      <c r="AD11" s="172"/>
+      <c r="AU11"/>
+      <c r="AV11"/>
+      <c r="AW11"/>
+      <c r="AX11"/>
+      <c r="AY11"/>
+      <c r="AZ11"/>
+    </row>
+    <row r="12" spans="1:52" s="61" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="41"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="148" t="e">
         <f>I11*1.2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="88"/>
+      <c r="J12" s="82"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="89"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="90"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="94"/>
-      <c r="S12" s="95"/>
-      <c r="T12" s="96"/>
-      <c r="U12" s="97"/>
-      <c r="V12" s="80"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="99"/>
-      <c r="Z12" s="100"/>
-      <c r="AC12" s="101"/>
-      <c r="AD12" s="64"/>
-    </row>
-    <row r="13" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A13" s="102" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="175" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="176"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="177"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="R13" s="105"/>
-      <c r="AD13" s="15"/>
-    </row>
-    <row r="14" spans="1:30" ht="14.1" customHeight="1">
-      <c r="A14" s="102" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="168" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="169"/>
-      <c r="D14" s="169"/>
-      <c r="E14" s="169"/>
-      <c r="F14" s="169"/>
-      <c r="G14" s="169"/>
-      <c r="H14" s="169"/>
-      <c r="I14" s="178"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="85"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="88"/>
+      <c r="S12" s="89"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="91"/>
+      <c r="V12" s="75"/>
+      <c r="W12" s="76"/>
+      <c r="X12" s="92"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="94"/>
+      <c r="AC12" s="95"/>
+      <c r="AD12" s="172"/>
+      <c r="AU12"/>
+      <c r="AV12"/>
+      <c r="AW12"/>
+      <c r="AX12"/>
+      <c r="AY12"/>
+      <c r="AZ12"/>
+    </row>
+    <row r="13" spans="1:52" s="1" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A13" s="129" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="127" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="128"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="149"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13"/>
+      <c r="AA13"/>
+      <c r="AD13" s="172"/>
+      <c r="AU13"/>
+      <c r="AV13"/>
+      <c r="AW13"/>
+      <c r="AX13"/>
+      <c r="AY13"/>
+      <c r="AZ13"/>
+    </row>
+    <row r="14" spans="1:52" ht="14.1" customHeight="1">
+      <c r="A14" s="129" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="106"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="107"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="109" t="s">
+      <c r="O14" s="109"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14" s="165" t="s">
+        <v>83</v>
+      </c>
+      <c r="U14" s="164" t="s">
         <v>82</v>
       </c>
-      <c r="U14" s="110" t="s">
-        <v>89</v>
-      </c>
-      <c r="V14" s="111"/>
-      <c r="W14" s="109"/>
-    </row>
-    <row r="15" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A15" s="102" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="168" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="169"/>
-      <c r="D15" s="169"/>
-      <c r="E15" s="169"/>
-      <c r="F15" s="169"/>
-      <c r="G15" s="169"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="112">
-        <v>140</v>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+      <c r="AD14" s="172"/>
+      <c r="AU14"/>
+      <c r="AV14"/>
+      <c r="AW14"/>
+      <c r="AX14"/>
+      <c r="AY14"/>
+      <c r="AZ14"/>
+    </row>
+    <row r="15" spans="1:52" s="1" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A15" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="105" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="106"/>
+      <c r="D15" s="106"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="151">
+        <v>150</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="104">
+        <v>49</v>
+      </c>
+      <c r="K15" s="97">
         <f>I15+I16</f>
-        <v>170</v>
-      </c>
-      <c r="L15" s="104"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="108"/>
-      <c r="U15" s="113"/>
-    </row>
-    <row r="16" spans="1:30" s="42" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A16" s="102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="170" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="171"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="171"/>
-      <c r="F16" s="171"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="114">
+        <v>180</v>
+      </c>
+      <c r="L15" s="97"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AD15" s="172"/>
+      <c r="AU15"/>
+      <c r="AV15"/>
+      <c r="AW15"/>
+      <c r="AX15"/>
+      <c r="AY15"/>
+      <c r="AZ15"/>
+    </row>
+    <row r="16" spans="1:52" s="40" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A16" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="107" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="152">
         <v>30</v>
       </c>
-      <c r="J16" s="115"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
       <c r="N16" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O16" s="116" t="e">
+        <v>50</v>
+      </c>
+      <c r="O16" s="111" t="e">
         <f>I11*14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="107"/>
-      <c r="S16" s="108"/>
-      <c r="U16" s="118"/>
-    </row>
-    <row r="17" spans="1:32" ht="14.1" customHeight="1">
-      <c r="A17" s="102" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="152" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="153"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AD16" s="172"/>
+      <c r="AU16"/>
+      <c r="AV16"/>
+      <c r="AW16"/>
+      <c r="AX16"/>
+      <c r="AY16"/>
+      <c r="AZ16"/>
+    </row>
+    <row r="17" spans="1:52" ht="14.1" customHeight="1">
+      <c r="A17" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="115" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
       <c r="N17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="O17" s="116" t="e">
+        <v>52</v>
+      </c>
+      <c r="O17" s="111" t="e">
         <f>I12*14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="8"/>
-      <c r="U17" s="121"/>
-    </row>
-    <row r="18" spans="1:32" ht="14.1" customHeight="1">
-      <c r="A18" s="102" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="152" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="153"/>
-      <c r="D18" s="153"/>
-      <c r="E18" s="153"/>
-      <c r="F18" s="153"/>
-      <c r="G18" s="153"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="8"/>
-    </row>
-    <row r="19" spans="1:32" ht="14.1" customHeight="1">
-      <c r="A19" s="102" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="152" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="153"/>
-      <c r="D19" s="153"/>
-      <c r="E19" s="153"/>
-      <c r="F19" s="153"/>
-      <c r="G19" s="153"/>
-      <c r="H19" s="154"/>
-      <c r="I19" s="124" t="e">
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17"/>
+      <c r="Z17"/>
+      <c r="AA17"/>
+      <c r="AD17" s="172"/>
+      <c r="AU17"/>
+      <c r="AV17"/>
+      <c r="AW17"/>
+      <c r="AX17"/>
+      <c r="AY17"/>
+      <c r="AZ17"/>
+    </row>
+    <row r="18" spans="1:52" ht="14.1" customHeight="1">
+      <c r="A18" s="96" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="115" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="154"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AD18" s="172"/>
+      <c r="AU18"/>
+      <c r="AV18"/>
+      <c r="AW18"/>
+      <c r="AX18"/>
+      <c r="AY18"/>
+      <c r="AZ18"/>
+    </row>
+    <row r="19" spans="1:52" ht="18.75" customHeight="1">
+      <c r="A19" s="96" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="115" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="155" t="e">
         <f>I11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="125"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="104"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
       <c r="M19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-    </row>
-    <row r="20" spans="1:32" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A20" s="102" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="127"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="R20" s="128"/>
-      <c r="U20" s="42"/>
-    </row>
-    <row r="21" spans="1:32" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A21" s="102" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="126"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="R21" s="129"/>
-    </row>
-    <row r="22" spans="1:32" s="1" customFormat="1" ht="11.1" customHeight="1">
-      <c r="A22" s="102" t="s">
-        <v>37</v>
-      </c>
-      <c r="J22" s="127"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="R22" s="128"/>
-    </row>
-    <row r="23" spans="1:32" s="135" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="130" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="131" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="156"/>
-      <c r="H23" s="156"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="132"/>
-      <c r="K23" s="133"/>
-      <c r="L23" s="133"/>
-      <c r="M23" s="133"/>
-      <c r="N23" s="133"/>
-      <c r="O23" s="133"/>
-      <c r="P23" s="104"/>
-      <c r="Q23" s="134"/>
-      <c r="R23" s="134"/>
-    </row>
-    <row r="24" spans="1:32" s="133" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="136"/>
-      <c r="B24" s="66">
-        <v>1</v>
-      </c>
-      <c r="C24" s="158" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="159"/>
-      <c r="H24" s="160"/>
-      <c r="I24" s="137" t="e">
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AD19" s="172"/>
+      <c r="AU19"/>
+      <c r="AV19"/>
+      <c r="AW19"/>
+      <c r="AX19"/>
+      <c r="AY19"/>
+      <c r="AZ19"/>
+    </row>
+    <row r="20" spans="1:52" s="1" customFormat="1" ht="12" customHeight="1">
+      <c r="A20" s="96" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="115"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="155"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20"/>
+      <c r="Z20"/>
+      <c r="AA20"/>
+      <c r="AD20" s="172"/>
+      <c r="AU20"/>
+      <c r="AV20"/>
+      <c r="AW20"/>
+      <c r="AX20"/>
+      <c r="AY20"/>
+      <c r="AZ20"/>
+    </row>
+    <row r="21" spans="1:52" s="1" customFormat="1" ht="12" customHeight="1">
+      <c r="A21" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="115"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="155"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21"/>
+      <c r="AA21"/>
+      <c r="AD21" s="172"/>
+      <c r="AU21"/>
+      <c r="AV21"/>
+      <c r="AW21"/>
+      <c r="AX21"/>
+      <c r="AY21"/>
+      <c r="AZ21"/>
+    </row>
+    <row r="22" spans="1:52" s="1" customFormat="1" ht="11.1" customHeight="1">
+      <c r="A22" s="96" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="155"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AD22" s="172"/>
+      <c r="AU22"/>
+      <c r="AV22"/>
+      <c r="AW22"/>
+      <c r="AX22"/>
+      <c r="AY22"/>
+      <c r="AZ22"/>
+    </row>
+    <row r="23" spans="1:52" s="101" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="118"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="156"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AD23" s="172"/>
+      <c r="AU23"/>
+      <c r="AV23"/>
+      <c r="AW23"/>
+      <c r="AX23"/>
+      <c r="AY23"/>
+      <c r="AZ23"/>
+    </row>
+    <row r="24" spans="1:52" s="99" customFormat="1" ht="15" customHeight="1">
+      <c r="A24" s="102"/>
+      <c r="B24" s="115" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="157" t="e">
         <f>I12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J24" s="138"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="65"/>
-      <c r="P24" s="104"/>
-      <c r="Q24" s="134"/>
-      <c r="R24" s="134"/>
-      <c r="S24" s="134"/>
-    </row>
-    <row r="25" spans="1:32" s="65" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="43"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="158" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="160"/>
-      <c r="I25" s="139" t="e">
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24"/>
+      <c r="Z24"/>
+      <c r="AA24"/>
+      <c r="AD24" s="172"/>
+      <c r="AU24"/>
+      <c r="AV24"/>
+      <c r="AW24"/>
+      <c r="AX24"/>
+      <c r="AY24"/>
+      <c r="AZ24"/>
+    </row>
+    <row r="25" spans="1:52" s="61" customFormat="1" ht="15" customHeight="1">
+      <c r="A25" s="41"/>
+      <c r="B25" s="115" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="158" t="e">
         <f>I24/120*20</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J25" s="138" t="e">
-        <f>I25*15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K25" s="140"/>
-      <c r="P25" s="104"/>
-      <c r="Q25" s="134"/>
-      <c r="R25" s="134"/>
-      <c r="S25" s="134"/>
-    </row>
-    <row r="26" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="141"/>
-      <c r="B26" s="66">
-        <v>2</v>
-      </c>
-      <c r="C26" s="158" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="160"/>
-      <c r="I26" s="139" t="e">
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25"/>
+      <c r="Z25"/>
+      <c r="AA25"/>
+      <c r="AD25" s="172"/>
+      <c r="AU25"/>
+      <c r="AV25"/>
+      <c r="AW25"/>
+      <c r="AX25"/>
+      <c r="AY25"/>
+      <c r="AZ25"/>
+    </row>
+    <row r="26" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="103"/>
+      <c r="B26" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="158" t="e">
         <f>I24-I25</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J26" s="138"/>
-      <c r="K26" s="135"/>
-      <c r="L26" s="135"/>
-      <c r="M26" s="142" t="s">
-        <v>15</v>
-      </c>
-      <c r="N26" s="143" t="s">
-        <v>81</v>
-      </c>
-      <c r="P26" s="134"/>
-      <c r="Q26" s="134"/>
-      <c r="R26" s="134"/>
-      <c r="S26" s="134"/>
-      <c r="T26" s="134"/>
-      <c r="U26" s="134"/>
-      <c r="V26" s="134"/>
-      <c r="W26" s="134"/>
-      <c r="X26" s="134"/>
-    </row>
-    <row r="27" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="141"/>
-      <c r="B27" s="66">
-        <v>3</v>
-      </c>
-      <c r="C27" s="158" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="159"/>
-      <c r="E27" s="159"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="159"/>
-      <c r="H27" s="160"/>
-      <c r="I27" s="139" t="e">
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26"/>
+      <c r="Z26"/>
+      <c r="AA26"/>
+      <c r="AD26" s="172"/>
+      <c r="AU26"/>
+      <c r="AV26"/>
+      <c r="AW26"/>
+      <c r="AX26"/>
+      <c r="AY26"/>
+      <c r="AZ26"/>
+    </row>
+    <row r="27" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="103"/>
+      <c r="B27" s="115" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="158" t="e">
         <f>SUM(I28:I37)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J27" s="138"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="135"/>
-      <c r="M27" s="135"/>
-      <c r="N27" s="135"/>
-      <c r="P27" s="134"/>
-      <c r="Q27" s="134"/>
-      <c r="R27" s="134"/>
-      <c r="S27" s="134"/>
-      <c r="T27" s="134"/>
-      <c r="U27" s="134"/>
-      <c r="V27" s="134"/>
-      <c r="W27" s="134"/>
-      <c r="X27" s="134"/>
-    </row>
-    <row r="28" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="141"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="158" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="159"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="159"/>
-      <c r="G28" s="159"/>
-      <c r="H28" s="160"/>
-      <c r="I28" s="139" t="e">
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27"/>
+      <c r="AA27"/>
+      <c r="AD27" s="172"/>
+      <c r="AU27"/>
+      <c r="AV27"/>
+      <c r="AW27"/>
+      <c r="AX27"/>
+      <c r="AY27"/>
+      <c r="AZ27"/>
+    </row>
+    <row r="28" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="103"/>
+      <c r="B28" s="115" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="158" t="e">
         <f>O11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J28" s="144"/>
-      <c r="K28" s="135"/>
-      <c r="L28" s="135"/>
-      <c r="M28" s="142" t="s">
-        <v>27</v>
-      </c>
-      <c r="N28" s="143" t="s">
-        <v>60</v>
-      </c>
-      <c r="P28" s="134"/>
-      <c r="Q28" s="134"/>
-      <c r="R28" s="134"/>
-      <c r="S28" s="134"/>
-      <c r="T28" s="134"/>
-      <c r="U28" s="134"/>
-      <c r="V28" s="134"/>
-      <c r="W28" s="134"/>
-      <c r="X28" s="134"/>
-    </row>
-    <row r="29" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A29" s="141"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="161" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="162"/>
-      <c r="E29" s="162"/>
-      <c r="F29" s="162"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="145" t="s">
-        <v>65</v>
-      </c>
-      <c r="I29" s="146" t="e">
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28"/>
+      <c r="Z28"/>
+      <c r="AA28"/>
+      <c r="AD28" s="172"/>
+      <c r="AU28"/>
+      <c r="AV28"/>
+      <c r="AW28"/>
+      <c r="AX28"/>
+      <c r="AY28"/>
+      <c r="AZ28"/>
+    </row>
+    <row r="29" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="103"/>
+      <c r="B29" s="123" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="124"/>
+      <c r="D29" s="124"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="124"/>
+      <c r="G29" s="121"/>
+      <c r="H29" s="120" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" s="159" t="e">
         <f>IF(H29=D43,I28*3.2%,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="144"/>
-      <c r="K29" s="135"/>
-      <c r="L29" s="135"/>
-      <c r="M29" s="135"/>
-      <c r="N29" s="135"/>
-      <c r="P29" s="134"/>
-      <c r="Q29" s="134"/>
-      <c r="R29" s="134"/>
-      <c r="S29" s="134"/>
-      <c r="T29" s="134"/>
-      <c r="U29" s="134"/>
-      <c r="V29" s="134"/>
-      <c r="W29" s="134"/>
-      <c r="X29" s="134"/>
-    </row>
-    <row r="30" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="141"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="159"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="159"/>
-      <c r="H30" s="160"/>
-      <c r="I30" s="139" t="e">
-        <f>Y11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J30" s="144"/>
-      <c r="K30" s="135"/>
-      <c r="L30" s="135"/>
-      <c r="M30" s="142" t="s">
-        <v>58</v>
-      </c>
-      <c r="N30" s="143" t="s">
-        <v>22</v>
-      </c>
-      <c r="P30" s="134"/>
-      <c r="Q30" s="134"/>
-      <c r="R30" s="134"/>
-      <c r="S30" s="134"/>
-      <c r="T30" s="134"/>
-      <c r="U30" s="134"/>
-      <c r="V30" s="134"/>
-      <c r="W30" s="134"/>
-      <c r="X30" s="134"/>
-    </row>
-    <row r="31" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="141"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="158" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="159"/>
-      <c r="E31" s="159"/>
-      <c r="F31" s="159"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="160"/>
-      <c r="I31" s="139" t="e">
-        <f>S11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J31" s="144"/>
-      <c r="K31" s="135"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="Q31" s="134"/>
-      <c r="R31" s="134"/>
-      <c r="S31" s="134"/>
-      <c r="T31" s="134"/>
-      <c r="U31" s="134"/>
-      <c r="V31" s="134"/>
-      <c r="W31" s="134"/>
-      <c r="X31" s="134"/>
-      <c r="Y31" s="134"/>
-      <c r="Z31" s="134"/>
-      <c r="AA31" s="134"/>
-      <c r="AB31" s="134"/>
-      <c r="AC31" s="134"/>
-      <c r="AD31" s="134"/>
-      <c r="AE31" s="134"/>
-      <c r="AF31" s="134"/>
-    </row>
-    <row r="32" spans="1:32" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A32" s="141"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="158" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="159"/>
-      <c r="E32" s="159"/>
-      <c r="F32" s="159"/>
-      <c r="G32" s="159"/>
-      <c r="H32" s="160"/>
-      <c r="I32" s="139" t="e">
-        <f>U11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J32" s="144"/>
-      <c r="K32" s="135"/>
-      <c r="L32" s="135"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="Q32" s="134"/>
-      <c r="R32" s="134"/>
-      <c r="S32" s="134"/>
-      <c r="T32" s="134"/>
-      <c r="U32" s="134"/>
-      <c r="V32" s="134"/>
-      <c r="W32" s="134"/>
-      <c r="X32" s="134"/>
-      <c r="Y32" s="134"/>
-      <c r="Z32" s="134"/>
-      <c r="AA32" s="134"/>
-      <c r="AB32" s="134"/>
-      <c r="AC32" s="134"/>
-      <c r="AD32" s="134"/>
-      <c r="AE32" s="134"/>
-      <c r="AF32" s="134"/>
-    </row>
-    <row r="33" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A33" s="141"/>
-      <c r="B33" s="161" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="162"/>
-      <c r="D33" s="162"/>
-      <c r="E33" s="162"/>
-      <c r="F33" s="162"/>
-      <c r="G33" s="162"/>
-      <c r="H33" s="145" t="s">
-        <v>55</v>
-      </c>
-      <c r="I33" s="147" t="e">
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29"/>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29"/>
+      <c r="AA29"/>
+      <c r="AD29" s="172"/>
+      <c r="AU29"/>
+      <c r="AV29"/>
+      <c r="AW29"/>
+      <c r="AX29"/>
+      <c r="AY29"/>
+      <c r="AZ29"/>
+    </row>
+    <row r="30" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="103"/>
+      <c r="B30" s="115" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="116"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="116"/>
+      <c r="G30" s="116"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="158">
+        <f>AA11</f>
+        <v>0</v>
+      </c>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AD30" s="172"/>
+      <c r="AU30"/>
+      <c r="AV30"/>
+      <c r="AW30"/>
+      <c r="AX30"/>
+      <c r="AY30"/>
+      <c r="AZ30"/>
+    </row>
+    <row r="31" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="103"/>
+      <c r="B31" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="116"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="158">
+        <f>AB11</f>
+        <v>0</v>
+      </c>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31"/>
+      <c r="AB31" s="100"/>
+      <c r="AC31" s="100"/>
+      <c r="AD31" s="172"/>
+      <c r="AE31" s="100"/>
+      <c r="AF31" s="100"/>
+      <c r="AU31"/>
+      <c r="AV31"/>
+      <c r="AW31"/>
+      <c r="AX31"/>
+      <c r="AY31"/>
+      <c r="AZ31"/>
+    </row>
+    <row r="32" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="103"/>
+      <c r="B32" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="116"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="116"/>
+      <c r="G32" s="116"/>
+      <c r="H32" s="117"/>
+      <c r="I32" s="158">
+        <f>AC11</f>
+        <v>0</v>
+      </c>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+      <c r="S32"/>
+      <c r="T32"/>
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+      <c r="Y32"/>
+      <c r="Z32"/>
+      <c r="AA32"/>
+      <c r="AB32" s="100"/>
+      <c r="AC32" s="100"/>
+      <c r="AD32" s="172"/>
+      <c r="AE32" s="100"/>
+      <c r="AF32" s="100"/>
+      <c r="AU32"/>
+      <c r="AV32"/>
+      <c r="AW32"/>
+      <c r="AX32"/>
+      <c r="AY32"/>
+      <c r="AZ32"/>
+    </row>
+    <row r="33" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="103"/>
+      <c r="B33" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="124"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="124"/>
+      <c r="G33" s="121"/>
+      <c r="H33" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="159" t="e">
         <f>IF(H33="ДА",I28*16%/365*Длина_сделки,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J33" s="138"/>
-      <c r="K33" s="135"/>
-      <c r="L33" s="135"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="Q33" s="134"/>
-      <c r="R33" s="134"/>
-      <c r="S33" s="134"/>
-      <c r="T33" s="134"/>
-      <c r="U33" s="134"/>
-      <c r="V33" s="134"/>
-      <c r="W33" s="134"/>
-      <c r="X33" s="134"/>
-      <c r="Y33" s="134"/>
-      <c r="Z33" s="134"/>
-      <c r="AA33" s="134"/>
-      <c r="AB33" s="134"/>
-      <c r="AC33" s="134"/>
-      <c r="AD33" s="134"/>
-      <c r="AE33" s="134"/>
-      <c r="AF33" s="134"/>
-    </row>
-    <row r="34" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A34" s="141"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="163" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="164"/>
-      <c r="E34" s="159"/>
-      <c r="F34" s="159"/>
-      <c r="G34" s="159"/>
-      <c r="H34" s="160"/>
-      <c r="I34" s="139">
-        <f>AD11</f>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+      <c r="S33"/>
+      <c r="T33"/>
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+      <c r="Y33"/>
+      <c r="Z33"/>
+      <c r="AA33"/>
+      <c r="AB33" s="100"/>
+      <c r="AC33" s="100"/>
+      <c r="AD33" s="172"/>
+      <c r="AE33" s="100"/>
+      <c r="AF33" s="100"/>
+      <c r="AU33"/>
+      <c r="AV33"/>
+      <c r="AW33"/>
+      <c r="AX33"/>
+      <c r="AY33"/>
+      <c r="AZ33"/>
+    </row>
+    <row r="34" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A34" s="103"/>
+      <c r="B34" s="122" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="116"/>
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="116"/>
+      <c r="G34" s="116"/>
+      <c r="H34" s="117"/>
+      <c r="I34" s="158">
+        <f>AA11</f>
         <v>0</v>
       </c>
-      <c r="J34" s="148"/>
-      <c r="K34" s="135"/>
-      <c r="L34" s="135"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="R34" s="134"/>
-      <c r="S34" s="134"/>
-      <c r="T34" s="134"/>
-      <c r="U34" s="134"/>
-      <c r="V34" s="134"/>
-      <c r="W34" s="134"/>
-      <c r="X34" s="134"/>
-      <c r="Y34" s="134"/>
-      <c r="Z34" s="134"/>
-      <c r="AA34" s="134"/>
-      <c r="AB34" s="134"/>
-      <c r="AC34" s="134"/>
-      <c r="AD34" s="134"/>
-      <c r="AE34" s="134"/>
-      <c r="AF34" s="134"/>
-      <c r="AG34" s="134"/>
-    </row>
-    <row r="35" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="141"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="158" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="159"/>
-      <c r="G35" s="159"/>
-      <c r="H35" s="160"/>
-      <c r="I35" s="139">
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+      <c r="Y34"/>
+      <c r="Z34"/>
+      <c r="AA34"/>
+      <c r="AB34" s="100"/>
+      <c r="AC34" s="100"/>
+      <c r="AD34" s="172"/>
+      <c r="AE34" s="100"/>
+      <c r="AF34" s="100"/>
+      <c r="AG34" s="100"/>
+      <c r="AU34"/>
+      <c r="AV34"/>
+      <c r="AW34"/>
+      <c r="AX34"/>
+      <c r="AY34"/>
+      <c r="AZ34"/>
+    </row>
+    <row r="35" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A35" s="103"/>
+      <c r="B35" s="122" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="116"/>
+      <c r="D35" s="116"/>
+      <c r="E35" s="116"/>
+      <c r="F35" s="116"/>
+      <c r="G35" s="116"/>
+      <c r="H35" s="117"/>
+      <c r="I35" s="158">
         <f>AB11</f>
         <v>0</v>
       </c>
-      <c r="J35" s="148"/>
-      <c r="K35" s="135"/>
-      <c r="L35" s="135"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="R35" s="134"/>
-      <c r="S35" s="134"/>
-      <c r="T35" s="134"/>
-      <c r="U35" s="134"/>
-      <c r="V35" s="134"/>
-      <c r="W35" s="134"/>
-      <c r="X35" s="134"/>
-      <c r="Y35" s="134"/>
-      <c r="Z35" s="134"/>
-      <c r="AA35" s="134"/>
-      <c r="AB35" s="134"/>
-      <c r="AC35" s="134"/>
-      <c r="AD35" s="134"/>
-      <c r="AE35" s="134"/>
-      <c r="AF35" s="134"/>
-      <c r="AG35" s="134"/>
-    </row>
-    <row r="36" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A36" s="141"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="158" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="159"/>
-      <c r="E36" s="159"/>
-      <c r="F36" s="159"/>
-      <c r="G36" s="159"/>
-      <c r="H36" s="160"/>
-      <c r="I36" s="139">
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+      <c r="S35"/>
+      <c r="T35"/>
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+      <c r="Y35"/>
+      <c r="Z35"/>
+      <c r="AA35"/>
+      <c r="AB35" s="100"/>
+      <c r="AC35" s="100"/>
+      <c r="AD35" s="172"/>
+      <c r="AE35" s="100"/>
+      <c r="AF35" s="100"/>
+      <c r="AG35" s="100"/>
+      <c r="AU35"/>
+      <c r="AV35"/>
+      <c r="AW35"/>
+      <c r="AX35"/>
+      <c r="AY35"/>
+      <c r="AZ35"/>
+    </row>
+    <row r="36" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A36" s="103"/>
+      <c r="B36" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="116"/>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="116"/>
+      <c r="G36" s="116"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="158">
         <f>AC11</f>
         <v>0</v>
       </c>
-      <c r="J36" s="148"/>
-      <c r="K36" s="135"/>
-      <c r="L36" s="135"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="R36" s="134"/>
-      <c r="S36" s="134"/>
-      <c r="T36" s="134"/>
-      <c r="U36" s="134"/>
-      <c r="V36" s="134"/>
-      <c r="W36" s="134"/>
-      <c r="X36" s="134"/>
-      <c r="Y36" s="134"/>
-      <c r="Z36" s="134"/>
-      <c r="AA36" s="134"/>
-      <c r="AB36" s="134"/>
-      <c r="AC36" s="134"/>
-      <c r="AD36" s="134"/>
-      <c r="AE36" s="134"/>
-      <c r="AF36" s="134"/>
-      <c r="AG36" s="134"/>
-    </row>
-    <row r="37" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A37" s="141"/>
-      <c r="B37" s="161" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="162"/>
-      <c r="D37" s="162"/>
-      <c r="E37" s="162"/>
-      <c r="F37" s="162"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="145" t="s">
-        <v>56</v>
-      </c>
-      <c r="I37" s="146">
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+      <c r="S36"/>
+      <c r="T36"/>
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+      <c r="Y36"/>
+      <c r="Z36"/>
+      <c r="AA36"/>
+      <c r="AB36" s="100"/>
+      <c r="AC36" s="100"/>
+      <c r="AD36" s="172"/>
+      <c r="AE36" s="100"/>
+      <c r="AF36" s="100"/>
+      <c r="AG36" s="100"/>
+      <c r="AU36"/>
+      <c r="AV36"/>
+      <c r="AW36"/>
+      <c r="AX36"/>
+      <c r="AY36"/>
+      <c r="AZ36"/>
+    </row>
+    <row r="37" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A37" s="103"/>
+      <c r="B37" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="124"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="124"/>
+      <c r="G37" s="121"/>
+      <c r="H37" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="I37" s="159">
         <f>IF(H37="ДА",I24*3%/365*(I15+I16),0)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="138"/>
-      <c r="K37" s="135"/>
-      <c r="L37" s="135"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="R37" s="134"/>
-      <c r="S37" s="134"/>
-      <c r="T37" s="134"/>
-      <c r="U37" s="134"/>
-      <c r="V37" s="134"/>
-      <c r="W37" s="134"/>
-      <c r="X37" s="134"/>
-      <c r="Y37" s="134"/>
-      <c r="Z37" s="134"/>
-      <c r="AA37" s="134"/>
-      <c r="AB37" s="134"/>
-      <c r="AC37" s="134"/>
-      <c r="AD37" s="134"/>
-      <c r="AE37" s="134"/>
-      <c r="AF37" s="134"/>
-      <c r="AG37" s="134"/>
-    </row>
-    <row r="38" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A38" s="141"/>
-      <c r="B38" s="66">
-        <v>4</v>
-      </c>
-      <c r="C38" s="158" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="159"/>
-      <c r="E38" s="159"/>
-      <c r="F38" s="159"/>
-      <c r="G38" s="159"/>
-      <c r="H38" s="160"/>
-      <c r="I38" s="139" t="e">
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37"/>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37" s="100"/>
+      <c r="AC37" s="100"/>
+      <c r="AD37" s="172"/>
+      <c r="AE37" s="100"/>
+      <c r="AF37" s="100"/>
+      <c r="AG37" s="100"/>
+      <c r="AU37"/>
+      <c r="AV37"/>
+      <c r="AW37"/>
+      <c r="AX37"/>
+      <c r="AY37"/>
+      <c r="AZ37"/>
+    </row>
+    <row r="38" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A38" s="103"/>
+      <c r="B38" s="122" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="116"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="116"/>
+      <c r="F38" s="116"/>
+      <c r="G38" s="116"/>
+      <c r="H38" s="117"/>
+      <c r="I38" s="158" t="e">
         <f>I26-I27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J38" s="138" t="e">
-        <f>I38*15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K38" s="149"/>
-      <c r="L38" s="135"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="R38" s="134"/>
-      <c r="S38" s="134"/>
-      <c r="T38" s="134"/>
-      <c r="U38" s="134"/>
-      <c r="V38" s="134"/>
-      <c r="W38" s="134"/>
-      <c r="X38" s="134"/>
-      <c r="Y38" s="134"/>
-      <c r="Z38" s="134"/>
-      <c r="AA38" s="134"/>
-      <c r="AB38" s="134"/>
-      <c r="AC38" s="134"/>
-      <c r="AD38" s="134"/>
-      <c r="AE38" s="134"/>
-      <c r="AF38" s="134"/>
-      <c r="AG38" s="134"/>
-    </row>
-    <row r="39" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A39" s="141"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="158" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="159"/>
-      <c r="E39" s="159"/>
-      <c r="F39" s="159"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="160"/>
-      <c r="I39" s="139"/>
-      <c r="J39" s="148"/>
-      <c r="K39" s="135"/>
-      <c r="L39" s="135"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="R39" s="134"/>
-      <c r="S39" s="134"/>
-      <c r="T39" s="134"/>
-      <c r="U39" s="134"/>
-      <c r="V39" s="134"/>
-      <c r="W39" s="134"/>
-      <c r="X39" s="134"/>
-      <c r="Y39" s="134"/>
-      <c r="Z39" s="134"/>
-      <c r="AA39" s="134"/>
-      <c r="AB39" s="134"/>
-      <c r="AC39" s="134"/>
-      <c r="AD39" s="134"/>
-      <c r="AE39" s="134"/>
-      <c r="AF39" s="134"/>
-      <c r="AG39" s="134"/>
-    </row>
-    <row r="40" spans="1:33" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="141"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="158" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="159"/>
-      <c r="E40" s="159"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="159"/>
-      <c r="H40" s="160"/>
-      <c r="I40" s="150" t="e">
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38"/>
+      <c r="T38"/>
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+      <c r="Y38"/>
+      <c r="Z38"/>
+      <c r="AA38"/>
+      <c r="AB38" s="100"/>
+      <c r="AC38" s="100"/>
+      <c r="AD38" s="172"/>
+      <c r="AE38" s="100"/>
+      <c r="AF38" s="100"/>
+      <c r="AG38" s="100"/>
+      <c r="AU38"/>
+      <c r="AV38"/>
+      <c r="AW38"/>
+      <c r="AX38"/>
+      <c r="AY38"/>
+      <c r="AZ38"/>
+    </row>
+    <row r="39" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A39" s="103"/>
+      <c r="B39" s="122" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="116"/>
+      <c r="D39" s="116"/>
+      <c r="E39" s="116"/>
+      <c r="F39" s="116"/>
+      <c r="G39" s="116"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="158"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39"/>
+      <c r="Z39"/>
+      <c r="AA39"/>
+      <c r="AB39" s="100"/>
+      <c r="AC39" s="100"/>
+      <c r="AD39" s="172"/>
+      <c r="AE39" s="100"/>
+      <c r="AF39" s="100"/>
+      <c r="AG39" s="100"/>
+      <c r="AU39"/>
+      <c r="AV39"/>
+      <c r="AW39"/>
+      <c r="AX39"/>
+      <c r="AY39"/>
+      <c r="AZ39"/>
+    </row>
+    <row r="40" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
+      <c r="A40" s="103"/>
+      <c r="B40" s="122" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="116"/>
+      <c r="E40" s="116"/>
+      <c r="F40" s="116"/>
+      <c r="G40" s="116"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="160" t="e">
         <f>I38/I26</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J40" s="151"/>
-      <c r="K40" s="135"/>
-      <c r="L40" s="135"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="R40" s="134"/>
-      <c r="S40" s="134"/>
-      <c r="T40" s="134"/>
-      <c r="U40" s="134"/>
-      <c r="V40" s="134"/>
-      <c r="W40" s="134"/>
-      <c r="X40" s="134"/>
-      <c r="Y40" s="134"/>
-      <c r="Z40" s="134"/>
-      <c r="AA40" s="134"/>
-      <c r="AB40" s="134"/>
-      <c r="AC40" s="134"/>
-      <c r="AD40" s="134"/>
-      <c r="AE40" s="134"/>
-      <c r="AF40" s="134"/>
-      <c r="AG40" s="134"/>
-    </row>
-    <row r="41" spans="1:33" s="104" customFormat="1" ht="12" customHeight="1">
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40"/>
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+      <c r="Y40"/>
+      <c r="Z40"/>
+      <c r="AA40"/>
+      <c r="AB40" s="100"/>
+      <c r="AC40" s="100"/>
+      <c r="AD40" s="172"/>
+      <c r="AE40" s="100"/>
+      <c r="AF40" s="100"/>
+      <c r="AG40" s="100"/>
+      <c r="AU40"/>
+      <c r="AV40"/>
+      <c r="AW40"/>
+      <c r="AX40"/>
+      <c r="AY40"/>
+      <c r="AZ40"/>
+    </row>
+    <row r="41" spans="1:52" s="97" customFormat="1" ht="12" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="127"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="R41" s="8"/>
-      <c r="S41" s="8"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="8"/>
-      <c r="W41" s="8"/>
-      <c r="X41" s="8"/>
-      <c r="Y41" s="8"/>
-      <c r="Z41" s="8"/>
-      <c r="AA41" s="8"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41" s="161"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41"/>
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41"/>
+      <c r="Z41"/>
+      <c r="AA41"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-      <c r="AD41" s="8"/>
+      <c r="AD41" s="172"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
-    </row>
-    <row r="42" spans="1:33" s="1" customFormat="1" ht="11.25" customHeight="1">
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="J42" s="127"/>
-      <c r="P42" s="104"/>
-      <c r="Q42" s="104"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="8"/>
-      <c r="W42" s="8"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="8"/>
-      <c r="Z42" s="8"/>
-      <c r="AA42" s="8"/>
+      <c r="AU41"/>
+      <c r="AV41"/>
+      <c r="AW41"/>
+      <c r="AX41"/>
+      <c r="AY41"/>
+      <c r="AZ41"/>
+    </row>
+    <row r="42" spans="1:52" s="1" customFormat="1" ht="11.25" customHeight="1">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42" s="161"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42"/>
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+      <c r="Y42"/>
+      <c r="Z42"/>
+      <c r="AA42"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
+      <c r="AD42" s="172"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
-    </row>
-    <row r="43" spans="1:33" s="1" customFormat="1" ht="11.45" customHeight="1">
+      <c r="AU42"/>
+      <c r="AV42"/>
+      <c r="AW42"/>
+      <c r="AX42"/>
+      <c r="AY42"/>
+      <c r="AZ42"/>
+    </row>
+    <row r="43" spans="1:52" s="1" customFormat="1" ht="11.45" customHeight="1">
       <c r="C43" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J43" s="127"/>
-      <c r="P43" s="104"/>
-      <c r="Q43" s="104"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="8"/>
-      <c r="W43" s="8"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="8"/>
-      <c r="Z43" s="8"/>
-      <c r="AA43" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43" s="161"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+      <c r="S43"/>
+      <c r="T43"/>
+      <c r="U43"/>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+      <c r="Y43"/>
+      <c r="Z43"/>
+      <c r="AA43"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
+      <c r="AD43" s="172"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
-    </row>
-    <row r="44" spans="1:33" ht="11.45" customHeight="1">
+      <c r="AU43"/>
+      <c r="AV43"/>
+      <c r="AW43"/>
+      <c r="AX43"/>
+      <c r="AY43"/>
+      <c r="AZ43"/>
+    </row>
+    <row r="44" spans="1:52" ht="11.45" customHeight="1">
       <c r="C44" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J44" s="127"/>
+        <v>68</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44" s="161"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+      <c r="S44"/>
+      <c r="T44"/>
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+      <c r="Y44"/>
+      <c r="Z44"/>
+      <c r="AA44"/>
+      <c r="AD44" s="172"/>
+      <c r="AU44"/>
+      <c r="AV44"/>
+      <c r="AW44"/>
+      <c r="AX44"/>
+      <c r="AY44"/>
+      <c r="AZ44"/>
+    </row>
+    <row r="45" spans="1:52" ht="11.45" customHeight="1">
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45" s="161"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+      <c r="S45"/>
+      <c r="T45"/>
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+      <c r="Y45"/>
+      <c r="Z45"/>
+      <c r="AA45"/>
+      <c r="AD45" s="172"/>
+      <c r="AU45"/>
+      <c r="AV45"/>
+      <c r="AW45"/>
+      <c r="AX45"/>
+      <c r="AY45"/>
+      <c r="AZ45"/>
+    </row>
+    <row r="46" spans="1:52" ht="11.45" customHeight="1">
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46" s="161"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AD46" s="172"/>
+      <c r="AU46"/>
+      <c r="AV46"/>
+      <c r="AW46"/>
+      <c r="AX46"/>
+      <c r="AY46"/>
+      <c r="AZ46"/>
+    </row>
+    <row r="47" spans="1:52" ht="11.45" customHeight="1">
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47" s="161"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AD47" s="172"/>
+      <c r="AU47"/>
+      <c r="AV47"/>
+      <c r="AW47"/>
+      <c r="AX47"/>
+      <c r="AY47"/>
+      <c r="AZ47"/>
+    </row>
+    <row r="48" spans="1:52" ht="11.45" customHeight="1">
+      <c r="AD48" s="172"/>
+      <c r="AU48"/>
+      <c r="AV48"/>
+      <c r="AW48"/>
+      <c r="AX48"/>
+      <c r="AY48"/>
+      <c r="AZ48"/>
+    </row>
+    <row r="49" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD49" s="172"/>
+      <c r="AU49"/>
+      <c r="AV49"/>
+      <c r="AW49"/>
+      <c r="AX49"/>
+      <c r="AY49"/>
+      <c r="AZ49"/>
+    </row>
+    <row r="50" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD50" s="172"/>
+      <c r="AU50"/>
+      <c r="AV50"/>
+      <c r="AW50"/>
+      <c r="AX50"/>
+      <c r="AY50"/>
+      <c r="AZ50"/>
+    </row>
+    <row r="51" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD51" s="172"/>
+      <c r="AU51"/>
+      <c r="AV51"/>
+      <c r="AW51"/>
+      <c r="AX51"/>
+      <c r="AY51"/>
+      <c r="AZ51"/>
+    </row>
+    <row r="52" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD52" s="172"/>
+      <c r="AU52"/>
+      <c r="AV52"/>
+      <c r="AW52"/>
+      <c r="AX52"/>
+      <c r="AY52"/>
+      <c r="AZ52"/>
+    </row>
+    <row r="53" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD53" s="172"/>
+      <c r="AU53"/>
+      <c r="AV53"/>
+      <c r="AW53"/>
+      <c r="AX53"/>
+      <c r="AY53"/>
+      <c r="AZ53"/>
+    </row>
+    <row r="54" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD54" s="172"/>
+      <c r="AU54"/>
+      <c r="AV54"/>
+      <c r="AW54"/>
+      <c r="AX54"/>
+      <c r="AY54"/>
+      <c r="AZ54"/>
+    </row>
+    <row r="55" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD55" s="172"/>
+      <c r="AU55"/>
+      <c r="AV55"/>
+      <c r="AW55"/>
+      <c r="AX55"/>
+      <c r="AY55"/>
+      <c r="AZ55"/>
+    </row>
+    <row r="56" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD56" s="172"/>
+      <c r="AU56"/>
+      <c r="AV56"/>
+      <c r="AW56"/>
+      <c r="AX56"/>
+      <c r="AY56"/>
+      <c r="AZ56"/>
+    </row>
+    <row r="57" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD57" s="172"/>
+      <c r="AU57"/>
+      <c r="AV57"/>
+      <c r="AW57"/>
+      <c r="AX57"/>
+      <c r="AY57"/>
+      <c r="AZ57"/>
+    </row>
+    <row r="58" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD58" s="172"/>
+      <c r="AU58"/>
+      <c r="AV58"/>
+      <c r="AW58"/>
+      <c r="AX58"/>
+      <c r="AY58"/>
+      <c r="AZ58"/>
+    </row>
+    <row r="59" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD59" s="172"/>
+      <c r="AU59"/>
+      <c r="AV59"/>
+      <c r="AW59"/>
+      <c r="AX59"/>
+      <c r="AY59"/>
+      <c r="AZ59"/>
+    </row>
+    <row r="60" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD60" s="172"/>
+      <c r="AU60"/>
+      <c r="AV60"/>
+      <c r="AW60"/>
+      <c r="AX60"/>
+      <c r="AY60"/>
+      <c r="AZ60"/>
+    </row>
+    <row r="61" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD61" s="172"/>
+      <c r="AU61"/>
+      <c r="AV61"/>
+      <c r="AW61"/>
+      <c r="AX61"/>
+      <c r="AY61"/>
+      <c r="AZ61"/>
+    </row>
+    <row r="62" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD62" s="172"/>
+      <c r="AU62"/>
+      <c r="AV62"/>
+      <c r="AW62"/>
+      <c r="AX62"/>
+      <c r="AY62"/>
+      <c r="AZ62"/>
+    </row>
+    <row r="63" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD63" s="172"/>
+      <c r="AU63"/>
+      <c r="AV63"/>
+      <c r="AW63"/>
+      <c r="AX63"/>
+      <c r="AY63"/>
+      <c r="AZ63"/>
+    </row>
+    <row r="64" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD64" s="172"/>
+      <c r="AU64"/>
+      <c r="AV64"/>
+      <c r="AW64"/>
+      <c r="AX64"/>
+      <c r="AY64"/>
+      <c r="AZ64"/>
+    </row>
+    <row r="65" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD65" s="172"/>
+      <c r="AU65"/>
+      <c r="AV65"/>
+      <c r="AW65"/>
+      <c r="AX65"/>
+      <c r="AY65"/>
+      <c r="AZ65"/>
+    </row>
+    <row r="66" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD66" s="172"/>
+      <c r="AU66"/>
+      <c r="AV66"/>
+      <c r="AW66"/>
+      <c r="AX66"/>
+      <c r="AY66"/>
+      <c r="AZ66"/>
+    </row>
+    <row r="67" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD67" s="172"/>
+      <c r="AU67"/>
+      <c r="AV67"/>
+      <c r="AW67"/>
+      <c r="AX67"/>
+      <c r="AY67"/>
+      <c r="AZ67"/>
+    </row>
+    <row r="68" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD68" s="172"/>
+      <c r="AU68"/>
+      <c r="AV68"/>
+      <c r="AW68"/>
+      <c r="AX68"/>
+      <c r="AY68"/>
+      <c r="AZ68"/>
+    </row>
+    <row r="69" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD69" s="172"/>
+      <c r="AU69"/>
+      <c r="AV69"/>
+      <c r="AW69"/>
+      <c r="AX69"/>
+      <c r="AY69"/>
+      <c r="AZ69"/>
+    </row>
+    <row r="70" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD70" s="172"/>
+      <c r="AU70"/>
+      <c r="AV70"/>
+      <c r="AW70"/>
+      <c r="AX70"/>
+      <c r="AY70"/>
+      <c r="AZ70"/>
+    </row>
+    <row r="71" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD71" s="172"/>
+      <c r="AU71"/>
+      <c r="AV71"/>
+      <c r="AW71"/>
+      <c r="AX71"/>
+      <c r="AY71"/>
+      <c r="AZ71"/>
+    </row>
+    <row r="72" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD72" s="172"/>
+      <c r="AU72"/>
+      <c r="AV72"/>
+      <c r="AW72"/>
+      <c r="AX72"/>
+      <c r="AY72"/>
+      <c r="AZ72"/>
+    </row>
+    <row r="73" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD73" s="172"/>
+      <c r="AU73"/>
+      <c r="AV73"/>
+      <c r="AW73"/>
+      <c r="AX73"/>
+      <c r="AY73"/>
+      <c r="AZ73"/>
+    </row>
+    <row r="74" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD74" s="172"/>
+      <c r="AU74"/>
+      <c r="AV74"/>
+      <c r="AW74"/>
+      <c r="AX74"/>
+      <c r="AY74"/>
+      <c r="AZ74"/>
+    </row>
+    <row r="75" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD75" s="172"/>
+      <c r="AU75"/>
+      <c r="AV75"/>
+      <c r="AW75"/>
+      <c r="AX75"/>
+      <c r="AY75"/>
+      <c r="AZ75"/>
+    </row>
+    <row r="76" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD76" s="172"/>
+      <c r="AU76"/>
+      <c r="AV76"/>
+      <c r="AW76"/>
+      <c r="AX76"/>
+      <c r="AY76"/>
+      <c r="AZ76"/>
+    </row>
+    <row r="77" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD77" s="172"/>
+      <c r="AU77"/>
+      <c r="AV77"/>
+      <c r="AW77"/>
+      <c r="AX77"/>
+      <c r="AY77"/>
+      <c r="AZ77"/>
+    </row>
+    <row r="78" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD78" s="172"/>
+      <c r="AU78"/>
+      <c r="AV78"/>
+      <c r="AW78"/>
+      <c r="AX78"/>
+      <c r="AY78"/>
+      <c r="AZ78"/>
+    </row>
+    <row r="79" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD79" s="172"/>
+      <c r="AU79"/>
+      <c r="AV79"/>
+      <c r="AW79"/>
+      <c r="AX79"/>
+      <c r="AY79"/>
+      <c r="AZ79"/>
+    </row>
+    <row r="80" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD80" s="172"/>
+      <c r="AU80"/>
+      <c r="AV80"/>
+      <c r="AW80"/>
+      <c r="AX80"/>
+      <c r="AY80"/>
+      <c r="AZ80"/>
+    </row>
+    <row r="81" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD81" s="172"/>
+      <c r="AU81"/>
+      <c r="AV81"/>
+      <c r="AW81"/>
+      <c r="AX81"/>
+      <c r="AY81"/>
+      <c r="AZ81"/>
+    </row>
+    <row r="82" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD82" s="172"/>
+      <c r="AU82"/>
+      <c r="AV82"/>
+      <c r="AW82"/>
+      <c r="AX82"/>
+      <c r="AY82"/>
+      <c r="AZ82"/>
+    </row>
+    <row r="83" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD83" s="172"/>
+      <c r="AU83"/>
+      <c r="AV83"/>
+      <c r="AW83"/>
+      <c r="AX83"/>
+      <c r="AY83"/>
+      <c r="AZ83"/>
+    </row>
+    <row r="84" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD84" s="172"/>
+      <c r="AU84"/>
+      <c r="AV84"/>
+      <c r="AW84"/>
+      <c r="AX84"/>
+      <c r="AY84"/>
+      <c r="AZ84"/>
+    </row>
+    <row r="85" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD85" s="172"/>
+      <c r="AU85"/>
+      <c r="AV85"/>
+      <c r="AW85"/>
+      <c r="AX85"/>
+      <c r="AY85"/>
+      <c r="AZ85"/>
+    </row>
+    <row r="86" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD86" s="172"/>
+      <c r="AU86"/>
+      <c r="AV86"/>
+      <c r="AW86"/>
+      <c r="AX86"/>
+      <c r="AY86"/>
+      <c r="AZ86"/>
+    </row>
+    <row r="87" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD87" s="172"/>
+      <c r="AU87"/>
+      <c r="AV87"/>
+      <c r="AW87"/>
+      <c r="AX87"/>
+      <c r="AY87"/>
+      <c r="AZ87"/>
+    </row>
+    <row r="88" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD88" s="172"/>
+      <c r="AU88"/>
+      <c r="AV88"/>
+      <c r="AW88"/>
+      <c r="AX88"/>
+      <c r="AY88"/>
+      <c r="AZ88"/>
+    </row>
+    <row r="89" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD89" s="172"/>
+      <c r="AU89"/>
+      <c r="AV89"/>
+      <c r="AW89"/>
+      <c r="AX89"/>
+      <c r="AY89"/>
+      <c r="AZ89"/>
+    </row>
+    <row r="90" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD90" s="172"/>
+      <c r="AU90"/>
+      <c r="AV90"/>
+      <c r="AW90"/>
+      <c r="AX90"/>
+      <c r="AY90"/>
+      <c r="AZ90"/>
+    </row>
+    <row r="91" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD91" s="172"/>
+      <c r="AU91"/>
+      <c r="AV91"/>
+      <c r="AW91"/>
+      <c r="AX91"/>
+      <c r="AY91"/>
+      <c r="AZ91"/>
+    </row>
+    <row r="92" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD92" s="172"/>
+      <c r="AU92"/>
+      <c r="AV92"/>
+      <c r="AW92"/>
+      <c r="AX92"/>
+      <c r="AY92"/>
+      <c r="AZ92"/>
+    </row>
+    <row r="93" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD93" s="172"/>
+      <c r="AU93"/>
+      <c r="AV93"/>
+      <c r="AW93"/>
+      <c r="AX93"/>
+      <c r="AY93"/>
+      <c r="AZ93"/>
+    </row>
+    <row r="94" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD94" s="172"/>
+      <c r="AU94"/>
+      <c r="AV94"/>
+      <c r="AW94"/>
+      <c r="AX94"/>
+      <c r="AY94"/>
+      <c r="AZ94"/>
+    </row>
+    <row r="95" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD95" s="172"/>
+      <c r="AU95"/>
+      <c r="AV95"/>
+      <c r="AW95"/>
+      <c r="AX95"/>
+      <c r="AY95"/>
+      <c r="AZ95"/>
+    </row>
+    <row r="96" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD96" s="172"/>
+      <c r="AU96"/>
+      <c r="AV96"/>
+      <c r="AW96"/>
+      <c r="AX96"/>
+      <c r="AY96"/>
+      <c r="AZ96"/>
+    </row>
+    <row r="97" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD97" s="172"/>
+      <c r="AU97"/>
+      <c r="AV97"/>
+      <c r="AW97"/>
+      <c r="AX97"/>
+      <c r="AY97"/>
+      <c r="AZ97"/>
+    </row>
+    <row r="98" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD98" s="172"/>
+      <c r="AU98"/>
+      <c r="AV98"/>
+      <c r="AW98"/>
+      <c r="AX98"/>
+      <c r="AY98"/>
+      <c r="AZ98"/>
+    </row>
+    <row r="99" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD99" s="172"/>
+      <c r="AU99"/>
+      <c r="AV99"/>
+      <c r="AW99"/>
+      <c r="AX99"/>
+      <c r="AY99"/>
+      <c r="AZ99"/>
+    </row>
+    <row r="100" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD100" s="172"/>
+      <c r="AU100"/>
+      <c r="AV100"/>
+      <c r="AW100"/>
+      <c r="AX100"/>
+      <c r="AY100"/>
+      <c r="AZ100"/>
+    </row>
+    <row r="101" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD101" s="172"/>
+      <c r="AU101"/>
+      <c r="AV101"/>
+      <c r="AW101"/>
+      <c r="AX101"/>
+      <c r="AY101"/>
+      <c r="AZ101"/>
+    </row>
+    <row r="102" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD102" s="172"/>
+      <c r="AU102"/>
+      <c r="AV102"/>
+      <c r="AW102"/>
+      <c r="AX102"/>
+      <c r="AY102"/>
+      <c r="AZ102"/>
+    </row>
+    <row r="103" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD103" s="172"/>
+      <c r="AU103"/>
+      <c r="AV103"/>
+      <c r="AW103"/>
+      <c r="AX103"/>
+      <c r="AY103"/>
+      <c r="AZ103"/>
+    </row>
+    <row r="104" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD104" s="172"/>
+      <c r="AU104"/>
+      <c r="AV104"/>
+      <c r="AW104"/>
+      <c r="AX104"/>
+      <c r="AY104"/>
+      <c r="AZ104"/>
+    </row>
+    <row r="105" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD105" s="172"/>
+      <c r="AU105"/>
+      <c r="AV105"/>
+      <c r="AW105"/>
+      <c r="AX105"/>
+      <c r="AY105"/>
+      <c r="AZ105"/>
+    </row>
+    <row r="106" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD106" s="172"/>
+      <c r="AU106"/>
+      <c r="AV106"/>
+      <c r="AW106"/>
+      <c r="AX106"/>
+      <c r="AY106"/>
+      <c r="AZ106"/>
+    </row>
+    <row r="107" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD107" s="172"/>
+      <c r="AU107"/>
+      <c r="AV107"/>
+      <c r="AW107"/>
+      <c r="AX107"/>
+      <c r="AY107"/>
+      <c r="AZ107"/>
+    </row>
+    <row r="108" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD108" s="172"/>
+      <c r="AU108"/>
+      <c r="AV108"/>
+      <c r="AW108"/>
+      <c r="AX108"/>
+      <c r="AY108"/>
+      <c r="AZ108"/>
+    </row>
+    <row r="109" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD109" s="172"/>
+      <c r="AU109"/>
+      <c r="AV109"/>
+      <c r="AW109"/>
+      <c r="AX109"/>
+      <c r="AY109"/>
+      <c r="AZ109"/>
+    </row>
+    <row r="110" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD110" s="172"/>
+      <c r="AU110"/>
+      <c r="AV110"/>
+      <c r="AW110"/>
+      <c r="AX110"/>
+      <c r="AY110"/>
+      <c r="AZ110"/>
+    </row>
+    <row r="111" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD111" s="172"/>
+      <c r="AU111"/>
+      <c r="AV111"/>
+      <c r="AW111"/>
+      <c r="AX111"/>
+      <c r="AY111"/>
+      <c r="AZ111"/>
+    </row>
+    <row r="112" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD112" s="172"/>
+      <c r="AU112"/>
+      <c r="AV112"/>
+      <c r="AW112"/>
+      <c r="AX112"/>
+      <c r="AY112"/>
+      <c r="AZ112"/>
+    </row>
+    <row r="113" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD113" s="172"/>
+      <c r="AU113"/>
+      <c r="AV113"/>
+      <c r="AW113"/>
+      <c r="AX113"/>
+      <c r="AY113"/>
+      <c r="AZ113"/>
+    </row>
+    <row r="114" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD114" s="172"/>
+      <c r="AU114"/>
+      <c r="AV114"/>
+      <c r="AW114"/>
+      <c r="AX114"/>
+      <c r="AY114"/>
+      <c r="AZ114"/>
+    </row>
+    <row r="115" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD115" s="172"/>
+      <c r="AU115"/>
+      <c r="AV115"/>
+      <c r="AW115"/>
+      <c r="AX115"/>
+      <c r="AY115"/>
+      <c r="AZ115"/>
+    </row>
+    <row r="116" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD116" s="172"/>
+      <c r="AU116"/>
+      <c r="AV116"/>
+      <c r="AW116"/>
+      <c r="AX116"/>
+      <c r="AY116"/>
+      <c r="AZ116"/>
+    </row>
+    <row r="117" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD117" s="172"/>
+      <c r="AU117"/>
+      <c r="AV117"/>
+      <c r="AW117"/>
+      <c r="AX117"/>
+      <c r="AY117"/>
+      <c r="AZ117"/>
+    </row>
+    <row r="118" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD118" s="172"/>
+      <c r="AU118"/>
+      <c r="AV118"/>
+      <c r="AW118"/>
+      <c r="AX118"/>
+      <c r="AY118"/>
+      <c r="AZ118"/>
+    </row>
+    <row r="119" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD119" s="172"/>
+      <c r="AU119"/>
+      <c r="AV119"/>
+      <c r="AW119"/>
+      <c r="AX119"/>
+      <c r="AY119"/>
+      <c r="AZ119"/>
+    </row>
+    <row r="120" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD120" s="172"/>
+      <c r="AU120"/>
+      <c r="AV120"/>
+      <c r="AW120"/>
+      <c r="AX120"/>
+      <c r="AY120"/>
+      <c r="AZ120"/>
+    </row>
+    <row r="121" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD121" s="172"/>
+      <c r="AU121"/>
+      <c r="AV121"/>
+      <c r="AW121"/>
+      <c r="AX121"/>
+      <c r="AY121"/>
+      <c r="AZ121"/>
+    </row>
+    <row r="122" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD122" s="172"/>
+      <c r="AU122"/>
+      <c r="AV122"/>
+      <c r="AW122"/>
+      <c r="AX122"/>
+      <c r="AY122"/>
+      <c r="AZ122"/>
+    </row>
+    <row r="123" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD123" s="172"/>
+      <c r="AU123"/>
+      <c r="AV123"/>
+      <c r="AW123"/>
+      <c r="AX123"/>
+      <c r="AY123"/>
+      <c r="AZ123"/>
+    </row>
+    <row r="124" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD124" s="172"/>
+      <c r="AU124"/>
+      <c r="AV124"/>
+      <c r="AW124"/>
+      <c r="AX124"/>
+      <c r="AY124"/>
+      <c r="AZ124"/>
+    </row>
+    <row r="125" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD125" s="172"/>
+      <c r="AU125"/>
+      <c r="AV125"/>
+      <c r="AW125"/>
+      <c r="AX125"/>
+      <c r="AY125"/>
+      <c r="AZ125"/>
+    </row>
+    <row r="126" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD126" s="172"/>
+      <c r="AU126"/>
+      <c r="AV126"/>
+      <c r="AW126"/>
+      <c r="AX126"/>
+      <c r="AY126"/>
+      <c r="AZ126"/>
+    </row>
+    <row r="127" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD127" s="172"/>
+      <c r="AU127"/>
+      <c r="AV127"/>
+      <c r="AW127"/>
+      <c r="AX127"/>
+      <c r="AY127"/>
+      <c r="AZ127"/>
+    </row>
+    <row r="128" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD128" s="172"/>
+      <c r="AU128"/>
+      <c r="AV128"/>
+      <c r="AW128"/>
+      <c r="AX128"/>
+      <c r="AY128"/>
+      <c r="AZ128"/>
+    </row>
+    <row r="129" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD129" s="172"/>
+      <c r="AU129"/>
+      <c r="AV129"/>
+      <c r="AW129"/>
+      <c r="AX129"/>
+      <c r="AY129"/>
+      <c r="AZ129"/>
+    </row>
+    <row r="130" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD130" s="172"/>
+      <c r="AU130"/>
+      <c r="AV130"/>
+      <c r="AW130"/>
+      <c r="AX130"/>
+      <c r="AY130"/>
+      <c r="AZ130"/>
+    </row>
+    <row r="131" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD131" s="172"/>
+      <c r="AU131"/>
+      <c r="AV131"/>
+      <c r="AW131"/>
+      <c r="AX131"/>
+      <c r="AY131"/>
+      <c r="AZ131"/>
+    </row>
+    <row r="132" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD132" s="172"/>
+      <c r="AU132"/>
+      <c r="AV132"/>
+      <c r="AW132"/>
+      <c r="AX132"/>
+      <c r="AY132"/>
+      <c r="AZ132"/>
+    </row>
+    <row r="133" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD133" s="172"/>
+      <c r="AU133"/>
+      <c r="AV133"/>
+      <c r="AW133"/>
+      <c r="AX133"/>
+      <c r="AY133"/>
+      <c r="AZ133"/>
+    </row>
+    <row r="134" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD134" s="172"/>
+      <c r="AU134"/>
+      <c r="AV134"/>
+      <c r="AW134"/>
+      <c r="AX134"/>
+      <c r="AY134"/>
+      <c r="AZ134"/>
+    </row>
+    <row r="135" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD135" s="172"/>
+      <c r="AU135"/>
+      <c r="AV135"/>
+      <c r="AW135"/>
+      <c r="AX135"/>
+      <c r="AY135"/>
+      <c r="AZ135"/>
+    </row>
+    <row r="136" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD136" s="172"/>
+      <c r="AU136"/>
+      <c r="AV136"/>
+      <c r="AW136"/>
+      <c r="AX136"/>
+      <c r="AY136"/>
+      <c r="AZ136"/>
+    </row>
+    <row r="137" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD137" s="172"/>
+      <c r="AU137"/>
+      <c r="AV137"/>
+      <c r="AW137"/>
+      <c r="AX137"/>
+      <c r="AY137"/>
+      <c r="AZ137"/>
+    </row>
+    <row r="138" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD138" s="172"/>
+      <c r="AU138"/>
+      <c r="AV138"/>
+      <c r="AW138"/>
+      <c r="AX138"/>
+      <c r="AY138"/>
+      <c r="AZ138"/>
+    </row>
+    <row r="139" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD139" s="172"/>
+      <c r="AU139"/>
+      <c r="AV139"/>
+      <c r="AW139"/>
+      <c r="AX139"/>
+      <c r="AY139"/>
+      <c r="AZ139"/>
+    </row>
+    <row r="140" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD140" s="172"/>
+      <c r="AU140"/>
+      <c r="AV140"/>
+      <c r="AW140"/>
+      <c r="AX140"/>
+      <c r="AY140"/>
+      <c r="AZ140"/>
+    </row>
+    <row r="141" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD141" s="172"/>
+      <c r="AU141"/>
+      <c r="AV141"/>
+      <c r="AW141"/>
+      <c r="AX141"/>
+      <c r="AY141"/>
+      <c r="AZ141"/>
+    </row>
+    <row r="142" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD142" s="172"/>
+      <c r="AU142"/>
+      <c r="AV142"/>
+      <c r="AW142"/>
+      <c r="AX142"/>
+      <c r="AY142"/>
+      <c r="AZ142"/>
+    </row>
+    <row r="143" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD143" s="172"/>
+      <c r="AU143"/>
+      <c r="AV143"/>
+      <c r="AW143"/>
+      <c r="AX143"/>
+      <c r="AY143"/>
+      <c r="AZ143"/>
+    </row>
+    <row r="144" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD144" s="172"/>
+      <c r="AU144"/>
+      <c r="AV144"/>
+      <c r="AW144"/>
+      <c r="AX144"/>
+      <c r="AY144"/>
+      <c r="AZ144"/>
+    </row>
+    <row r="145" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD145" s="172"/>
+      <c r="AU145"/>
+      <c r="AV145"/>
+      <c r="AW145"/>
+      <c r="AX145"/>
+      <c r="AY145"/>
+      <c r="AZ145"/>
+    </row>
+    <row r="146" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD146" s="172"/>
+      <c r="AU146"/>
+      <c r="AV146"/>
+      <c r="AW146"/>
+      <c r="AX146"/>
+      <c r="AY146"/>
+      <c r="AZ146"/>
+    </row>
+    <row r="147" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD147" s="172"/>
+      <c r="AU147"/>
+      <c r="AV147"/>
+      <c r="AW147"/>
+      <c r="AX147"/>
+      <c r="AY147"/>
+      <c r="AZ147"/>
+    </row>
+    <row r="148" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD148" s="172"/>
+      <c r="AU148"/>
+      <c r="AV148"/>
+      <c r="AW148"/>
+      <c r="AX148"/>
+      <c r="AY148"/>
+      <c r="AZ148"/>
+    </row>
+    <row r="149" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD149" s="172"/>
+      <c r="AU149"/>
+      <c r="AV149"/>
+      <c r="AW149"/>
+      <c r="AX149"/>
+      <c r="AY149"/>
+      <c r="AZ149"/>
+    </row>
+    <row r="150" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD150" s="172"/>
+      <c r="AU150"/>
+      <c r="AV150"/>
+      <c r="AW150"/>
+      <c r="AX150"/>
+      <c r="AY150"/>
+      <c r="AZ150"/>
+    </row>
+    <row r="151" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD151" s="172"/>
+      <c r="AU151"/>
+      <c r="AV151"/>
+      <c r="AW151"/>
+      <c r="AX151"/>
+      <c r="AY151"/>
+      <c r="AZ151"/>
+    </row>
+    <row r="152" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD152" s="172"/>
+      <c r="AU152"/>
+      <c r="AV152"/>
+      <c r="AW152"/>
+      <c r="AX152"/>
+      <c r="AY152"/>
+      <c r="AZ152"/>
+    </row>
+    <row r="153" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD153" s="172"/>
+      <c r="AU153"/>
+      <c r="AV153"/>
+      <c r="AW153"/>
+      <c r="AX153"/>
+      <c r="AY153"/>
+      <c r="AZ153"/>
+    </row>
+    <row r="154" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD154" s="172"/>
+      <c r="AU154"/>
+      <c r="AV154"/>
+      <c r="AW154"/>
+      <c r="AX154"/>
+      <c r="AY154"/>
+      <c r="AZ154"/>
+    </row>
+    <row r="155" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD155" s="172"/>
+      <c r="AU155"/>
+      <c r="AV155"/>
+      <c r="AW155"/>
+      <c r="AX155"/>
+      <c r="AY155"/>
+      <c r="AZ155"/>
+    </row>
+    <row r="156" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD156" s="172"/>
+      <c r="AU156"/>
+      <c r="AV156"/>
+      <c r="AW156"/>
+      <c r="AX156"/>
+      <c r="AY156"/>
+      <c r="AZ156"/>
+    </row>
+    <row r="157" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD157" s="172"/>
+      <c r="AU157"/>
+      <c r="AV157"/>
+      <c r="AW157"/>
+      <c r="AX157"/>
+      <c r="AY157"/>
+      <c r="AZ157"/>
+    </row>
+    <row r="158" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD158" s="172"/>
+      <c r="AU158"/>
+      <c r="AV158"/>
+      <c r="AW158"/>
+      <c r="AX158"/>
+      <c r="AY158"/>
+      <c r="AZ158"/>
+    </row>
+    <row r="159" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD159" s="172"/>
+      <c r="AU159"/>
+      <c r="AV159"/>
+      <c r="AW159"/>
+      <c r="AX159"/>
+      <c r="AY159"/>
+      <c r="AZ159"/>
+    </row>
+    <row r="160" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD160" s="172"/>
+      <c r="AU160"/>
+      <c r="AV160"/>
+      <c r="AW160"/>
+      <c r="AX160"/>
+      <c r="AY160"/>
+      <c r="AZ160"/>
+    </row>
+    <row r="161" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD161" s="172"/>
+      <c r="AU161"/>
+      <c r="AV161"/>
+      <c r="AW161"/>
+      <c r="AX161"/>
+      <c r="AY161"/>
+      <c r="AZ161"/>
+    </row>
+    <row r="162" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD162" s="172"/>
+      <c r="AU162"/>
+      <c r="AV162"/>
+      <c r="AW162"/>
+      <c r="AX162"/>
+      <c r="AY162"/>
+      <c r="AZ162"/>
+    </row>
+    <row r="163" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD163" s="172"/>
+      <c r="AU163"/>
+      <c r="AV163"/>
+      <c r="AW163"/>
+      <c r="AX163"/>
+      <c r="AY163"/>
+      <c r="AZ163"/>
+    </row>
+    <row r="164" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD164" s="172"/>
+      <c r="AU164"/>
+      <c r="AV164"/>
+      <c r="AW164"/>
+      <c r="AX164"/>
+      <c r="AY164"/>
+      <c r="AZ164"/>
+    </row>
+    <row r="165" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD165" s="172"/>
+      <c r="AU165"/>
+      <c r="AV165"/>
+      <c r="AW165"/>
+      <c r="AX165"/>
+      <c r="AY165"/>
+      <c r="AZ165"/>
+    </row>
+    <row r="166" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD166" s="172"/>
+      <c r="AU166"/>
+      <c r="AV166"/>
+      <c r="AW166"/>
+      <c r="AX166"/>
+      <c r="AY166"/>
+      <c r="AZ166"/>
+    </row>
+    <row r="167" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD167" s="172"/>
+      <c r="AU167"/>
+      <c r="AV167"/>
+      <c r="AW167"/>
+      <c r="AX167"/>
+      <c r="AY167"/>
+      <c r="AZ167"/>
+    </row>
+    <row r="168" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD168" s="172"/>
+      <c r="AU168"/>
+      <c r="AV168"/>
+      <c r="AW168"/>
+      <c r="AX168"/>
+      <c r="AY168"/>
+      <c r="AZ168"/>
+    </row>
+    <row r="169" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD169" s="172"/>
+      <c r="AU169"/>
+      <c r="AV169"/>
+      <c r="AW169"/>
+      <c r="AX169"/>
+      <c r="AY169"/>
+      <c r="AZ169"/>
+    </row>
+    <row r="170" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD170" s="172"/>
+      <c r="AU170"/>
+      <c r="AV170"/>
+      <c r="AW170"/>
+      <c r="AX170"/>
+      <c r="AY170"/>
+      <c r="AZ170"/>
+    </row>
+    <row r="171" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD171" s="172"/>
+      <c r="AU171"/>
+      <c r="AV171"/>
+      <c r="AW171"/>
+      <c r="AX171"/>
+      <c r="AY171"/>
+      <c r="AZ171"/>
+    </row>
+    <row r="172" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD172" s="172"/>
+      <c r="AU172"/>
+      <c r="AV172"/>
+      <c r="AW172"/>
+      <c r="AX172"/>
+      <c r="AY172"/>
+      <c r="AZ172"/>
+    </row>
+    <row r="173" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD173" s="172"/>
+      <c r="AU173"/>
+      <c r="AV173"/>
+      <c r="AW173"/>
+      <c r="AX173"/>
+      <c r="AY173"/>
+      <c r="AZ173"/>
+    </row>
+    <row r="174" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD174" s="172"/>
+      <c r="AU174"/>
+      <c r="AV174"/>
+      <c r="AW174"/>
+      <c r="AX174"/>
+      <c r="AY174"/>
+      <c r="AZ174"/>
+    </row>
+    <row r="175" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD175" s="172"/>
+      <c r="AU175"/>
+      <c r="AV175"/>
+      <c r="AW175"/>
+      <c r="AX175"/>
+      <c r="AY175"/>
+      <c r="AZ175"/>
+    </row>
+    <row r="176" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD176" s="172"/>
+      <c r="AU176"/>
+      <c r="AV176"/>
+      <c r="AW176"/>
+      <c r="AX176"/>
+      <c r="AY176"/>
+      <c r="AZ176"/>
+    </row>
+    <row r="177" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD177" s="172"/>
+      <c r="AU177"/>
+      <c r="AV177"/>
+      <c r="AW177"/>
+      <c r="AX177"/>
+      <c r="AY177"/>
+      <c r="AZ177"/>
+    </row>
+    <row r="178" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD178" s="172"/>
+      <c r="AU178"/>
+      <c r="AV178"/>
+      <c r="AW178"/>
+      <c r="AX178"/>
+      <c r="AY178"/>
+      <c r="AZ178"/>
+    </row>
+    <row r="179" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD179" s="172"/>
+      <c r="AU179"/>
+      <c r="AV179"/>
+      <c r="AW179"/>
+      <c r="AX179"/>
+      <c r="AY179"/>
+      <c r="AZ179"/>
+    </row>
+    <row r="180" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD180" s="172"/>
+      <c r="AU180"/>
+      <c r="AV180"/>
+      <c r="AW180"/>
+      <c r="AX180"/>
+      <c r="AY180"/>
+      <c r="AZ180"/>
+    </row>
+    <row r="181" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD181" s="172"/>
+      <c r="AU181"/>
+      <c r="AV181"/>
+      <c r="AW181"/>
+      <c r="AX181"/>
+      <c r="AY181"/>
+      <c r="AZ181"/>
+    </row>
+    <row r="182" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD182" s="172"/>
+      <c r="AU182"/>
+      <c r="AV182"/>
+      <c r="AW182"/>
+      <c r="AX182"/>
+      <c r="AY182"/>
+      <c r="AZ182"/>
+    </row>
+    <row r="183" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD183" s="172"/>
+      <c r="AU183"/>
+      <c r="AV183"/>
+      <c r="AW183"/>
+      <c r="AX183"/>
+      <c r="AY183"/>
+      <c r="AZ183"/>
+    </row>
+    <row r="184" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD184" s="172"/>
+      <c r="AU184"/>
+      <c r="AV184"/>
+      <c r="AW184"/>
+      <c r="AX184"/>
+      <c r="AY184"/>
+      <c r="AZ184"/>
+    </row>
+    <row r="185" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD185" s="172"/>
+      <c r="AU185"/>
+      <c r="AV185"/>
+      <c r="AW185"/>
+      <c r="AX185"/>
+      <c r="AY185"/>
+      <c r="AZ185"/>
+    </row>
+    <row r="186" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD186" s="172"/>
+      <c r="AU186"/>
+      <c r="AV186"/>
+      <c r="AW186"/>
+      <c r="AX186"/>
+      <c r="AY186"/>
+      <c r="AZ186"/>
+    </row>
+    <row r="187" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD187" s="172"/>
+      <c r="AU187"/>
+      <c r="AV187"/>
+      <c r="AW187"/>
+      <c r="AX187"/>
+      <c r="AY187"/>
+      <c r="AZ187"/>
+    </row>
+    <row r="188" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD188" s="172"/>
+      <c r="AU188"/>
+      <c r="AV188"/>
+      <c r="AW188"/>
+      <c r="AX188"/>
+      <c r="AY188"/>
+      <c r="AZ188"/>
+    </row>
+    <row r="189" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD189" s="172"/>
+      <c r="AU189"/>
+      <c r="AV189"/>
+      <c r="AW189"/>
+      <c r="AX189"/>
+      <c r="AY189"/>
+      <c r="AZ189"/>
+    </row>
+    <row r="190" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD190" s="172"/>
+      <c r="AU190"/>
+      <c r="AV190"/>
+      <c r="AW190"/>
+      <c r="AX190"/>
+      <c r="AY190"/>
+      <c r="AZ190"/>
+    </row>
+    <row r="191" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD191" s="172"/>
+      <c r="AU191"/>
+      <c r="AV191"/>
+      <c r="AW191"/>
+      <c r="AX191"/>
+      <c r="AY191"/>
+      <c r="AZ191"/>
+    </row>
+    <row r="192" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD192" s="172"/>
+      <c r="AU192"/>
+      <c r="AV192"/>
+      <c r="AW192"/>
+      <c r="AX192"/>
+      <c r="AY192"/>
+      <c r="AZ192"/>
+    </row>
+    <row r="193" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD193" s="172"/>
+      <c r="AU193"/>
+      <c r="AV193"/>
+      <c r="AW193"/>
+      <c r="AX193"/>
+      <c r="AY193"/>
+      <c r="AZ193"/>
+    </row>
+    <row r="194" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD194" s="172"/>
+      <c r="AU194"/>
+      <c r="AV194"/>
+      <c r="AW194"/>
+      <c r="AX194"/>
+      <c r="AY194"/>
+      <c r="AZ194"/>
+    </row>
+    <row r="195" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD195" s="172"/>
+      <c r="AU195"/>
+      <c r="AV195"/>
+      <c r="AW195"/>
+      <c r="AX195"/>
+      <c r="AY195"/>
+      <c r="AZ195"/>
+    </row>
+    <row r="196" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD196" s="172"/>
+      <c r="AU196"/>
+      <c r="AV196"/>
+      <c r="AW196"/>
+      <c r="AX196"/>
+      <c r="AY196"/>
+      <c r="AZ196"/>
+    </row>
+    <row r="197" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD197" s="172"/>
+      <c r="AU197"/>
+      <c r="AV197"/>
+      <c r="AW197"/>
+      <c r="AX197"/>
+      <c r="AY197"/>
+      <c r="AZ197"/>
+    </row>
+    <row r="198" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD198" s="172"/>
+      <c r="AU198"/>
+      <c r="AV198"/>
+      <c r="AW198"/>
+      <c r="AX198"/>
+      <c r="AY198"/>
+      <c r="AZ198"/>
+    </row>
+    <row r="199" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD199" s="172"/>
+      <c r="AU199"/>
+      <c r="AV199"/>
+      <c r="AW199"/>
+      <c r="AX199"/>
+      <c r="AY199"/>
+      <c r="AZ199"/>
+    </row>
+    <row r="200" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AD200" s="172"/>
+      <c r="AU200"/>
+      <c r="AV200"/>
+      <c r="AW200"/>
+      <c r="AX200"/>
+      <c r="AY200"/>
+      <c r="AZ200"/>
+    </row>
+    <row r="201" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU201"/>
+      <c r="AV201"/>
+      <c r="AW201"/>
+      <c r="AX201"/>
+      <c r="AY201"/>
+      <c r="AZ201"/>
+    </row>
+    <row r="202" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU202"/>
+      <c r="AV202"/>
+      <c r="AW202"/>
+      <c r="AX202"/>
+      <c r="AY202"/>
+      <c r="AZ202"/>
+    </row>
+    <row r="203" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU203"/>
+      <c r="AV203"/>
+      <c r="AW203"/>
+      <c r="AX203"/>
+      <c r="AY203"/>
+      <c r="AZ203"/>
+    </row>
+    <row r="204" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU204"/>
+      <c r="AV204"/>
+      <c r="AW204"/>
+      <c r="AX204"/>
+      <c r="AY204"/>
+      <c r="AZ204"/>
+    </row>
+    <row r="205" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU205"/>
+      <c r="AV205"/>
+      <c r="AW205"/>
+      <c r="AX205"/>
+      <c r="AY205"/>
+      <c r="AZ205"/>
+    </row>
+    <row r="206" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU206"/>
+      <c r="AV206"/>
+      <c r="AW206"/>
+      <c r="AX206"/>
+      <c r="AY206"/>
+      <c r="AZ206"/>
+    </row>
+    <row r="207" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU207"/>
+      <c r="AV207"/>
+      <c r="AW207"/>
+      <c r="AX207"/>
+      <c r="AY207"/>
+      <c r="AZ207"/>
+    </row>
+    <row r="208" spans="30:52" ht="11.45" customHeight="1">
+      <c r="AU208"/>
+      <c r="AV208"/>
+      <c r="AW208"/>
+      <c r="AX208"/>
+      <c r="AY208"/>
+      <c r="AZ208"/>
+    </row>
+    <row r="209" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU209"/>
+      <c r="AV209"/>
+      <c r="AW209"/>
+      <c r="AX209"/>
+      <c r="AY209"/>
+      <c r="AZ209"/>
+    </row>
+    <row r="210" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU210"/>
+      <c r="AV210"/>
+      <c r="AW210"/>
+      <c r="AX210"/>
+      <c r="AY210"/>
+      <c r="AZ210"/>
+    </row>
+    <row r="211" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU211"/>
+      <c r="AV211"/>
+      <c r="AW211"/>
+      <c r="AX211"/>
+      <c r="AY211"/>
+      <c r="AZ211"/>
+    </row>
+    <row r="212" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU212"/>
+      <c r="AV212"/>
+      <c r="AW212"/>
+      <c r="AX212"/>
+      <c r="AY212"/>
+      <c r="AZ212"/>
+    </row>
+    <row r="213" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU213"/>
+      <c r="AV213"/>
+      <c r="AW213"/>
+      <c r="AX213"/>
+      <c r="AY213"/>
+      <c r="AZ213"/>
+    </row>
+    <row r="214" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU214"/>
+      <c r="AV214"/>
+      <c r="AW214"/>
+      <c r="AX214"/>
+      <c r="AY214"/>
+      <c r="AZ214"/>
+    </row>
+    <row r="215" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU215"/>
+      <c r="AV215"/>
+      <c r="AW215"/>
+      <c r="AX215"/>
+      <c r="AY215"/>
+      <c r="AZ215"/>
+    </row>
+    <row r="216" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU216"/>
+      <c r="AV216"/>
+      <c r="AW216"/>
+      <c r="AX216"/>
+      <c r="AY216"/>
+      <c r="AZ216"/>
+    </row>
+    <row r="217" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU217"/>
+      <c r="AV217"/>
+      <c r="AW217"/>
+      <c r="AX217"/>
+      <c r="AY217"/>
+      <c r="AZ217"/>
+    </row>
+    <row r="218" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU218"/>
+      <c r="AV218"/>
+      <c r="AW218"/>
+      <c r="AX218"/>
+      <c r="AY218"/>
+      <c r="AZ218"/>
+    </row>
+    <row r="219" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU219"/>
+      <c r="AV219"/>
+      <c r="AW219"/>
+      <c r="AX219"/>
+      <c r="AY219"/>
+      <c r="AZ219"/>
+    </row>
+    <row r="220" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU220"/>
+      <c r="AV220"/>
+      <c r="AW220"/>
+      <c r="AX220"/>
+      <c r="AY220"/>
+      <c r="AZ220"/>
+    </row>
+    <row r="221" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU221"/>
+      <c r="AV221"/>
+      <c r="AW221"/>
+      <c r="AX221"/>
+      <c r="AY221"/>
+      <c r="AZ221"/>
+    </row>
+    <row r="222" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU222"/>
+      <c r="AV222"/>
+      <c r="AW222"/>
+      <c r="AX222"/>
+      <c r="AY222"/>
+      <c r="AZ222"/>
+    </row>
+    <row r="223" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU223"/>
+      <c r="AV223"/>
+      <c r="AW223"/>
+      <c r="AX223"/>
+      <c r="AY223"/>
+      <c r="AZ223"/>
+    </row>
+    <row r="224" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU224"/>
+      <c r="AV224"/>
+      <c r="AW224"/>
+      <c r="AX224"/>
+      <c r="AY224"/>
+      <c r="AZ224"/>
+    </row>
+    <row r="225" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU225"/>
+      <c r="AV225"/>
+      <c r="AW225"/>
+      <c r="AX225"/>
+      <c r="AY225"/>
+      <c r="AZ225"/>
+    </row>
+    <row r="226" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU226"/>
+      <c r="AV226"/>
+      <c r="AW226"/>
+      <c r="AX226"/>
+      <c r="AY226"/>
+      <c r="AZ226"/>
+    </row>
+    <row r="227" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU227"/>
+      <c r="AV227"/>
+      <c r="AW227"/>
+      <c r="AX227"/>
+      <c r="AY227"/>
+      <c r="AZ227"/>
+    </row>
+    <row r="228" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU228"/>
+      <c r="AV228"/>
+      <c r="AW228"/>
+      <c r="AX228"/>
+      <c r="AY228"/>
+      <c r="AZ228"/>
+    </row>
+    <row r="229" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU229"/>
+      <c r="AV229"/>
+      <c r="AW229"/>
+      <c r="AX229"/>
+      <c r="AY229"/>
+      <c r="AZ229"/>
+    </row>
+    <row r="230" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU230"/>
+      <c r="AV230"/>
+      <c r="AW230"/>
+      <c r="AX230"/>
+      <c r="AY230"/>
+      <c r="AZ230"/>
+    </row>
+    <row r="231" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU231"/>
+      <c r="AV231"/>
+      <c r="AW231"/>
+      <c r="AX231"/>
+      <c r="AY231"/>
+      <c r="AZ231"/>
+    </row>
+    <row r="232" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU232"/>
+      <c r="AV232"/>
+      <c r="AW232"/>
+      <c r="AX232"/>
+      <c r="AY232"/>
+      <c r="AZ232"/>
+    </row>
+    <row r="233" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU233"/>
+      <c r="AV233"/>
+      <c r="AW233"/>
+      <c r="AX233"/>
+      <c r="AY233"/>
+      <c r="AZ233"/>
+    </row>
+    <row r="234" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU234"/>
+      <c r="AV234"/>
+      <c r="AW234"/>
+      <c r="AX234"/>
+      <c r="AY234"/>
+      <c r="AZ234"/>
+    </row>
+    <row r="235" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU235"/>
+      <c r="AV235"/>
+      <c r="AW235"/>
+      <c r="AX235"/>
+      <c r="AY235"/>
+      <c r="AZ235"/>
+    </row>
+    <row r="236" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU236"/>
+      <c r="AV236"/>
+      <c r="AW236"/>
+      <c r="AX236"/>
+      <c r="AY236"/>
+      <c r="AZ236"/>
+    </row>
+    <row r="237" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU237"/>
+      <c r="AV237"/>
+      <c r="AW237"/>
+      <c r="AX237"/>
+      <c r="AY237"/>
+      <c r="AZ237"/>
+    </row>
+    <row r="238" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU238"/>
+      <c r="AV238"/>
+      <c r="AW238"/>
+      <c r="AX238"/>
+      <c r="AY238"/>
+      <c r="AZ238"/>
+    </row>
+    <row r="239" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU239"/>
+      <c r="AV239"/>
+      <c r="AW239"/>
+      <c r="AX239"/>
+      <c r="AY239"/>
+      <c r="AZ239"/>
+    </row>
+    <row r="240" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU240"/>
+      <c r="AV240"/>
+      <c r="AW240"/>
+      <c r="AX240"/>
+      <c r="AY240"/>
+      <c r="AZ240"/>
+    </row>
+    <row r="241" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU241"/>
+      <c r="AV241"/>
+      <c r="AW241"/>
+      <c r="AX241"/>
+      <c r="AY241"/>
+      <c r="AZ241"/>
+    </row>
+    <row r="242" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU242"/>
+      <c r="AV242"/>
+      <c r="AW242"/>
+      <c r="AX242"/>
+      <c r="AY242"/>
+      <c r="AZ242"/>
+    </row>
+    <row r="243" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU243"/>
+      <c r="AV243"/>
+      <c r="AW243"/>
+      <c r="AX243"/>
+      <c r="AY243"/>
+      <c r="AZ243"/>
+    </row>
+    <row r="244" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU244"/>
+      <c r="AV244"/>
+      <c r="AW244"/>
+      <c r="AX244"/>
+      <c r="AY244"/>
+      <c r="AZ244"/>
+    </row>
+    <row r="245" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU245"/>
+      <c r="AV245"/>
+      <c r="AW245"/>
+      <c r="AX245"/>
+      <c r="AY245"/>
+      <c r="AZ245"/>
+    </row>
+    <row r="246" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU246"/>
+      <c r="AV246"/>
+      <c r="AW246"/>
+      <c r="AX246"/>
+      <c r="AY246"/>
+      <c r="AZ246"/>
+    </row>
+    <row r="247" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU247"/>
+      <c r="AV247"/>
+      <c r="AW247"/>
+      <c r="AX247"/>
+      <c r="AY247"/>
+      <c r="AZ247"/>
+    </row>
+    <row r="248" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU248"/>
+      <c r="AV248"/>
+      <c r="AW248"/>
+      <c r="AX248"/>
+      <c r="AY248"/>
+      <c r="AZ248"/>
+    </row>
+    <row r="249" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU249"/>
+      <c r="AV249"/>
+      <c r="AW249"/>
+      <c r="AX249"/>
+      <c r="AY249"/>
+      <c r="AZ249"/>
+    </row>
+    <row r="250" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU250"/>
+      <c r="AV250"/>
+      <c r="AW250"/>
+      <c r="AX250"/>
+      <c r="AY250"/>
+      <c r="AZ250"/>
+    </row>
+    <row r="251" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU251"/>
+      <c r="AV251"/>
+      <c r="AW251"/>
+      <c r="AX251"/>
+      <c r="AY251"/>
+      <c r="AZ251"/>
+    </row>
+    <row r="252" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU252"/>
+      <c r="AV252"/>
+      <c r="AW252"/>
+      <c r="AX252"/>
+      <c r="AY252"/>
+      <c r="AZ252"/>
+    </row>
+    <row r="253" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU253"/>
+      <c r="AV253"/>
+      <c r="AW253"/>
+      <c r="AX253"/>
+      <c r="AY253"/>
+      <c r="AZ253"/>
+    </row>
+    <row r="254" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU254"/>
+      <c r="AV254"/>
+      <c r="AW254"/>
+      <c r="AX254"/>
+      <c r="AY254"/>
+      <c r="AZ254"/>
+    </row>
+    <row r="255" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU255"/>
+      <c r="AV255"/>
+      <c r="AW255"/>
+      <c r="AX255"/>
+      <c r="AY255"/>
+      <c r="AZ255"/>
+    </row>
+    <row r="256" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU256"/>
+      <c r="AV256"/>
+      <c r="AW256"/>
+      <c r="AX256"/>
+      <c r="AY256"/>
+      <c r="AZ256"/>
+    </row>
+    <row r="257" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU257"/>
+      <c r="AV257"/>
+      <c r="AW257"/>
+      <c r="AX257"/>
+      <c r="AY257"/>
+      <c r="AZ257"/>
+    </row>
+    <row r="258" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU258"/>
+      <c r="AV258"/>
+      <c r="AW258"/>
+      <c r="AX258"/>
+      <c r="AY258"/>
+      <c r="AZ258"/>
+    </row>
+    <row r="259" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU259"/>
+      <c r="AV259"/>
+      <c r="AW259"/>
+      <c r="AX259"/>
+      <c r="AY259"/>
+      <c r="AZ259"/>
+    </row>
+    <row r="260" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU260"/>
+      <c r="AV260"/>
+      <c r="AW260"/>
+      <c r="AX260"/>
+      <c r="AY260"/>
+      <c r="AZ260"/>
+    </row>
+    <row r="261" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU261"/>
+      <c r="AV261"/>
+      <c r="AW261"/>
+      <c r="AX261"/>
+      <c r="AY261"/>
+      <c r="AZ261"/>
+    </row>
+    <row r="262" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU262"/>
+      <c r="AV262"/>
+      <c r="AW262"/>
+      <c r="AX262"/>
+      <c r="AY262"/>
+      <c r="AZ262"/>
+    </row>
+    <row r="263" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU263"/>
+      <c r="AV263"/>
+      <c r="AW263"/>
+      <c r="AX263"/>
+      <c r="AY263"/>
+      <c r="AZ263"/>
+    </row>
+    <row r="264" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU264"/>
+      <c r="AV264"/>
+      <c r="AW264"/>
+      <c r="AX264"/>
+      <c r="AY264"/>
+      <c r="AZ264"/>
+    </row>
+    <row r="265" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU265"/>
+      <c r="AV265"/>
+      <c r="AW265"/>
+      <c r="AX265"/>
+      <c r="AY265"/>
+      <c r="AZ265"/>
+    </row>
+    <row r="266" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU266"/>
+      <c r="AV266"/>
+      <c r="AW266"/>
+      <c r="AX266"/>
+      <c r="AY266"/>
+      <c r="AZ266"/>
+    </row>
+    <row r="267" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU267"/>
+      <c r="AV267"/>
+      <c r="AW267"/>
+      <c r="AX267"/>
+      <c r="AY267"/>
+      <c r="AZ267"/>
+    </row>
+    <row r="268" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU268"/>
+      <c r="AV268"/>
+      <c r="AW268"/>
+      <c r="AX268"/>
+      <c r="AY268"/>
+      <c r="AZ268"/>
+    </row>
+    <row r="269" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU269"/>
+      <c r="AV269"/>
+      <c r="AW269"/>
+      <c r="AX269"/>
+      <c r="AY269"/>
+      <c r="AZ269"/>
+    </row>
+    <row r="270" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU270"/>
+      <c r="AV270"/>
+      <c r="AW270"/>
+      <c r="AX270"/>
+      <c r="AY270"/>
+      <c r="AZ270"/>
+    </row>
+    <row r="271" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU271"/>
+      <c r="AV271"/>
+      <c r="AW271"/>
+      <c r="AX271"/>
+      <c r="AY271"/>
+      <c r="AZ271"/>
+    </row>
+    <row r="272" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU272"/>
+      <c r="AV272"/>
+      <c r="AW272"/>
+      <c r="AX272"/>
+      <c r="AY272"/>
+      <c r="AZ272"/>
+    </row>
+    <row r="273" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU273"/>
+      <c r="AV273"/>
+      <c r="AW273"/>
+      <c r="AX273"/>
+      <c r="AY273"/>
+      <c r="AZ273"/>
+    </row>
+    <row r="274" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU274"/>
+      <c r="AV274"/>
+      <c r="AW274"/>
+      <c r="AX274"/>
+      <c r="AY274"/>
+      <c r="AZ274"/>
+    </row>
+    <row r="275" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU275"/>
+      <c r="AV275"/>
+      <c r="AW275"/>
+      <c r="AX275"/>
+      <c r="AY275"/>
+      <c r="AZ275"/>
+    </row>
+    <row r="276" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU276"/>
+      <c r="AV276"/>
+      <c r="AW276"/>
+      <c r="AX276"/>
+      <c r="AY276"/>
+      <c r="AZ276"/>
+    </row>
+    <row r="277" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU277"/>
+      <c r="AV277"/>
+      <c r="AW277"/>
+      <c r="AX277"/>
+      <c r="AY277"/>
+      <c r="AZ277"/>
+    </row>
+    <row r="278" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU278"/>
+      <c r="AV278"/>
+      <c r="AW278"/>
+      <c r="AX278"/>
+      <c r="AY278"/>
+      <c r="AZ278"/>
+    </row>
+    <row r="279" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU279"/>
+      <c r="AV279"/>
+      <c r="AW279"/>
+      <c r="AX279"/>
+      <c r="AY279"/>
+      <c r="AZ279"/>
+    </row>
+    <row r="280" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU280"/>
+      <c r="AV280"/>
+      <c r="AW280"/>
+      <c r="AX280"/>
+      <c r="AY280"/>
+      <c r="AZ280"/>
+    </row>
+    <row r="281" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU281"/>
+      <c r="AV281"/>
+      <c r="AW281"/>
+      <c r="AX281"/>
+      <c r="AY281"/>
+      <c r="AZ281"/>
+    </row>
+    <row r="282" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU282"/>
+      <c r="AV282"/>
+      <c r="AW282"/>
+      <c r="AX282"/>
+      <c r="AY282"/>
+      <c r="AZ282"/>
+    </row>
+    <row r="283" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU283"/>
+      <c r="AV283"/>
+      <c r="AW283"/>
+      <c r="AX283"/>
+      <c r="AY283"/>
+      <c r="AZ283"/>
+    </row>
+    <row r="284" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU284"/>
+      <c r="AV284"/>
+      <c r="AW284"/>
+      <c r="AX284"/>
+      <c r="AY284"/>
+      <c r="AZ284"/>
+    </row>
+    <row r="285" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU285"/>
+      <c r="AV285"/>
+      <c r="AW285"/>
+      <c r="AX285"/>
+      <c r="AY285"/>
+      <c r="AZ285"/>
+    </row>
+    <row r="286" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU286"/>
+      <c r="AV286"/>
+      <c r="AW286"/>
+      <c r="AX286"/>
+      <c r="AY286"/>
+      <c r="AZ286"/>
+    </row>
+    <row r="287" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU287"/>
+      <c r="AV287"/>
+      <c r="AW287"/>
+      <c r="AX287"/>
+      <c r="AY287"/>
+      <c r="AZ287"/>
+    </row>
+    <row r="288" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU288"/>
+      <c r="AV288"/>
+      <c r="AW288"/>
+      <c r="AX288"/>
+      <c r="AY288"/>
+      <c r="AZ288"/>
+    </row>
+    <row r="289" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU289"/>
+      <c r="AV289"/>
+      <c r="AW289"/>
+      <c r="AX289"/>
+      <c r="AY289"/>
+      <c r="AZ289"/>
+    </row>
+    <row r="290" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU290"/>
+      <c r="AV290"/>
+      <c r="AW290"/>
+      <c r="AX290"/>
+      <c r="AY290"/>
+      <c r="AZ290"/>
+    </row>
+    <row r="291" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU291"/>
+      <c r="AV291"/>
+      <c r="AW291"/>
+      <c r="AX291"/>
+      <c r="AY291"/>
+      <c r="AZ291"/>
+    </row>
+    <row r="292" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU292"/>
+      <c r="AV292"/>
+      <c r="AW292"/>
+      <c r="AX292"/>
+      <c r="AY292"/>
+      <c r="AZ292"/>
+    </row>
+    <row r="293" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU293"/>
+      <c r="AV293"/>
+      <c r="AW293"/>
+      <c r="AX293"/>
+      <c r="AY293"/>
+      <c r="AZ293"/>
+    </row>
+    <row r="294" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU294"/>
+      <c r="AV294"/>
+      <c r="AW294"/>
+      <c r="AX294"/>
+      <c r="AY294"/>
+      <c r="AZ294"/>
+    </row>
+    <row r="295" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU295"/>
+      <c r="AV295"/>
+      <c r="AW295"/>
+      <c r="AX295"/>
+      <c r="AY295"/>
+      <c r="AZ295"/>
+    </row>
+    <row r="296" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU296"/>
+      <c r="AV296"/>
+      <c r="AW296"/>
+      <c r="AX296"/>
+      <c r="AY296"/>
+      <c r="AZ296"/>
+    </row>
+    <row r="297" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU297"/>
+      <c r="AV297"/>
+      <c r="AW297"/>
+      <c r="AX297"/>
+      <c r="AY297"/>
+      <c r="AZ297"/>
+    </row>
+    <row r="298" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU298"/>
+      <c r="AV298"/>
+      <c r="AW298"/>
+      <c r="AX298"/>
+      <c r="AY298"/>
+      <c r="AZ298"/>
+    </row>
+    <row r="299" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU299"/>
+      <c r="AV299"/>
+      <c r="AW299"/>
+      <c r="AX299"/>
+      <c r="AY299"/>
+      <c r="AZ299"/>
+    </row>
+    <row r="300" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU300"/>
+      <c r="AV300"/>
+      <c r="AW300"/>
+      <c r="AX300"/>
+      <c r="AY300"/>
+      <c r="AZ300"/>
+    </row>
+    <row r="301" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU301"/>
+      <c r="AV301"/>
+      <c r="AW301"/>
+      <c r="AX301"/>
+      <c r="AY301"/>
+      <c r="AZ301"/>
+    </row>
+    <row r="302" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU302"/>
+      <c r="AV302"/>
+      <c r="AW302"/>
+      <c r="AX302"/>
+      <c r="AY302"/>
+      <c r="AZ302"/>
+    </row>
+    <row r="303" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU303"/>
+      <c r="AV303"/>
+      <c r="AW303"/>
+      <c r="AX303"/>
+      <c r="AY303"/>
+      <c r="AZ303"/>
+    </row>
+    <row r="304" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU304"/>
+      <c r="AV304"/>
+      <c r="AW304"/>
+      <c r="AX304"/>
+      <c r="AY304"/>
+      <c r="AZ304"/>
+    </row>
+    <row r="305" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU305"/>
+      <c r="AV305"/>
+      <c r="AW305"/>
+      <c r="AX305"/>
+      <c r="AY305"/>
+      <c r="AZ305"/>
+    </row>
+    <row r="306" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU306"/>
+      <c r="AV306"/>
+      <c r="AW306"/>
+      <c r="AX306"/>
+      <c r="AY306"/>
+      <c r="AZ306"/>
+    </row>
+    <row r="307" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU307"/>
+      <c r="AV307"/>
+      <c r="AW307"/>
+      <c r="AX307"/>
+      <c r="AY307"/>
+      <c r="AZ307"/>
+    </row>
+    <row r="308" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU308"/>
+      <c r="AV308"/>
+      <c r="AW308"/>
+      <c r="AX308"/>
+      <c r="AY308"/>
+      <c r="AZ308"/>
+    </row>
+    <row r="309" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU309"/>
+      <c r="AV309"/>
+      <c r="AW309"/>
+      <c r="AX309"/>
+      <c r="AY309"/>
+      <c r="AZ309"/>
+    </row>
+    <row r="310" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU310"/>
+      <c r="AV310"/>
+      <c r="AW310"/>
+      <c r="AX310"/>
+      <c r="AY310"/>
+      <c r="AZ310"/>
+    </row>
+    <row r="311" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU311"/>
+      <c r="AV311"/>
+      <c r="AW311"/>
+      <c r="AX311"/>
+      <c r="AY311"/>
+      <c r="AZ311"/>
+    </row>
+    <row r="312" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU312"/>
+      <c r="AV312"/>
+      <c r="AW312"/>
+      <c r="AX312"/>
+      <c r="AY312"/>
+      <c r="AZ312"/>
+    </row>
+    <row r="313" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU313"/>
+      <c r="AV313"/>
+      <c r="AW313"/>
+      <c r="AX313"/>
+      <c r="AY313"/>
+      <c r="AZ313"/>
+    </row>
+    <row r="314" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU314"/>
+      <c r="AV314"/>
+      <c r="AW314"/>
+      <c r="AX314"/>
+      <c r="AY314"/>
+      <c r="AZ314"/>
+    </row>
+    <row r="315" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU315"/>
+      <c r="AV315"/>
+      <c r="AW315"/>
+      <c r="AX315"/>
+      <c r="AY315"/>
+      <c r="AZ315"/>
+    </row>
+    <row r="316" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU316"/>
+      <c r="AV316"/>
+      <c r="AW316"/>
+      <c r="AX316"/>
+      <c r="AY316"/>
+      <c r="AZ316"/>
+    </row>
+    <row r="317" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU317"/>
+      <c r="AV317"/>
+      <c r="AW317"/>
+      <c r="AX317"/>
+      <c r="AY317"/>
+      <c r="AZ317"/>
+    </row>
+    <row r="318" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU318"/>
+      <c r="AV318"/>
+      <c r="AW318"/>
+      <c r="AX318"/>
+      <c r="AY318"/>
+      <c r="AZ318"/>
+    </row>
+    <row r="319" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU319"/>
+      <c r="AV319"/>
+      <c r="AW319"/>
+      <c r="AX319"/>
+      <c r="AY319"/>
+      <c r="AZ319"/>
+    </row>
+    <row r="320" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU320"/>
+      <c r="AV320"/>
+      <c r="AW320"/>
+      <c r="AX320"/>
+      <c r="AY320"/>
+      <c r="AZ320"/>
+    </row>
+    <row r="321" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU321"/>
+      <c r="AV321"/>
+      <c r="AW321"/>
+      <c r="AX321"/>
+      <c r="AY321"/>
+      <c r="AZ321"/>
+    </row>
+    <row r="322" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU322"/>
+      <c r="AV322"/>
+      <c r="AW322"/>
+      <c r="AX322"/>
+      <c r="AY322"/>
+      <c r="AZ322"/>
+    </row>
+    <row r="323" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU323"/>
+      <c r="AV323"/>
+      <c r="AW323"/>
+      <c r="AX323"/>
+      <c r="AY323"/>
+      <c r="AZ323"/>
+    </row>
+    <row r="324" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU324"/>
+      <c r="AV324"/>
+      <c r="AW324"/>
+      <c r="AX324"/>
+      <c r="AY324"/>
+      <c r="AZ324"/>
+    </row>
+    <row r="325" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU325"/>
+      <c r="AV325"/>
+      <c r="AW325"/>
+      <c r="AX325"/>
+      <c r="AY325"/>
+      <c r="AZ325"/>
+    </row>
+    <row r="326" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU326"/>
+      <c r="AV326"/>
+      <c r="AW326"/>
+      <c r="AX326"/>
+      <c r="AY326"/>
+      <c r="AZ326"/>
+    </row>
+    <row r="327" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU327"/>
+      <c r="AV327"/>
+      <c r="AW327"/>
+      <c r="AX327"/>
+      <c r="AY327"/>
+      <c r="AZ327"/>
+    </row>
+    <row r="328" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU328"/>
+      <c r="AV328"/>
+      <c r="AW328"/>
+      <c r="AX328"/>
+      <c r="AY328"/>
+      <c r="AZ328"/>
+    </row>
+    <row r="329" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU329"/>
+      <c r="AV329"/>
+      <c r="AW329"/>
+      <c r="AX329"/>
+      <c r="AY329"/>
+      <c r="AZ329"/>
+    </row>
+    <row r="330" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU330"/>
+      <c r="AV330"/>
+      <c r="AW330"/>
+      <c r="AX330"/>
+      <c r="AY330"/>
+      <c r="AZ330"/>
+    </row>
+    <row r="331" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU331"/>
+      <c r="AV331"/>
+      <c r="AW331"/>
+      <c r="AX331"/>
+      <c r="AY331"/>
+      <c r="AZ331"/>
+    </row>
+    <row r="332" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU332"/>
+      <c r="AV332"/>
+      <c r="AW332"/>
+      <c r="AX332"/>
+      <c r="AY332"/>
+      <c r="AZ332"/>
+    </row>
+    <row r="333" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU333"/>
+      <c r="AV333"/>
+      <c r="AW333"/>
+      <c r="AX333"/>
+      <c r="AY333"/>
+      <c r="AZ333"/>
+    </row>
+    <row r="334" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU334"/>
+      <c r="AV334"/>
+      <c r="AW334"/>
+      <c r="AX334"/>
+      <c r="AY334"/>
+      <c r="AZ334"/>
+    </row>
+    <row r="335" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU335"/>
+      <c r="AV335"/>
+      <c r="AW335"/>
+      <c r="AX335"/>
+      <c r="AY335"/>
+      <c r="AZ335"/>
+    </row>
+    <row r="336" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU336"/>
+      <c r="AV336"/>
+      <c r="AW336"/>
+      <c r="AX336"/>
+      <c r="AY336"/>
+      <c r="AZ336"/>
+    </row>
+    <row r="337" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU337"/>
+      <c r="AV337"/>
+      <c r="AW337"/>
+      <c r="AX337"/>
+      <c r="AY337"/>
+      <c r="AZ337"/>
+    </row>
+    <row r="338" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU338"/>
+      <c r="AV338"/>
+      <c r="AW338"/>
+      <c r="AX338"/>
+      <c r="AY338"/>
+      <c r="AZ338"/>
+    </row>
+    <row r="339" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU339"/>
+      <c r="AV339"/>
+      <c r="AW339"/>
+      <c r="AX339"/>
+      <c r="AY339"/>
+      <c r="AZ339"/>
+    </row>
+    <row r="340" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU340"/>
+      <c r="AV340"/>
+      <c r="AW340"/>
+      <c r="AX340"/>
+      <c r="AY340"/>
+      <c r="AZ340"/>
+    </row>
+    <row r="341" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU341"/>
+      <c r="AV341"/>
+      <c r="AW341"/>
+      <c r="AX341"/>
+      <c r="AY341"/>
+      <c r="AZ341"/>
+    </row>
+    <row r="342" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU342"/>
+      <c r="AV342"/>
+      <c r="AW342"/>
+      <c r="AX342"/>
+      <c r="AY342"/>
+      <c r="AZ342"/>
+    </row>
+    <row r="343" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU343"/>
+      <c r="AV343"/>
+      <c r="AW343"/>
+      <c r="AX343"/>
+      <c r="AY343"/>
+      <c r="AZ343"/>
+    </row>
+    <row r="344" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU344"/>
+      <c r="AV344"/>
+      <c r="AW344"/>
+      <c r="AX344"/>
+      <c r="AY344"/>
+      <c r="AZ344"/>
+    </row>
+    <row r="345" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU345"/>
+      <c r="AV345"/>
+      <c r="AW345"/>
+      <c r="AX345"/>
+      <c r="AY345"/>
+      <c r="AZ345"/>
+    </row>
+    <row r="346" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU346"/>
+      <c r="AV346"/>
+      <c r="AW346"/>
+      <c r="AX346"/>
+      <c r="AY346"/>
+      <c r="AZ346"/>
+    </row>
+    <row r="347" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU347"/>
+      <c r="AV347"/>
+      <c r="AW347"/>
+      <c r="AX347"/>
+      <c r="AY347"/>
+      <c r="AZ347"/>
+    </row>
+    <row r="348" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU348"/>
+      <c r="AV348"/>
+      <c r="AW348"/>
+      <c r="AX348"/>
+      <c r="AY348"/>
+      <c r="AZ348"/>
+    </row>
+    <row r="349" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU349"/>
+      <c r="AV349"/>
+      <c r="AW349"/>
+      <c r="AX349"/>
+      <c r="AY349"/>
+      <c r="AZ349"/>
+    </row>
+    <row r="350" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU350"/>
+      <c r="AV350"/>
+      <c r="AW350"/>
+      <c r="AX350"/>
+      <c r="AY350"/>
+      <c r="AZ350"/>
+    </row>
+    <row r="351" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU351"/>
+      <c r="AV351"/>
+      <c r="AW351"/>
+      <c r="AX351"/>
+      <c r="AY351"/>
+      <c r="AZ351"/>
+    </row>
+    <row r="352" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU352"/>
+      <c r="AV352"/>
+      <c r="AW352"/>
+      <c r="AX352"/>
+      <c r="AY352"/>
+      <c r="AZ352"/>
+    </row>
+    <row r="353" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU353"/>
+      <c r="AV353"/>
+      <c r="AW353"/>
+      <c r="AX353"/>
+      <c r="AY353"/>
+      <c r="AZ353"/>
+    </row>
+    <row r="354" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU354"/>
+      <c r="AV354"/>
+      <c r="AW354"/>
+      <c r="AX354"/>
+      <c r="AY354"/>
+      <c r="AZ354"/>
+    </row>
+    <row r="355" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU355"/>
+      <c r="AV355"/>
+      <c r="AW355"/>
+      <c r="AX355"/>
+      <c r="AY355"/>
+      <c r="AZ355"/>
+    </row>
+    <row r="356" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU356"/>
+      <c r="AV356"/>
+      <c r="AW356"/>
+      <c r="AX356"/>
+      <c r="AY356"/>
+      <c r="AZ356"/>
+    </row>
+    <row r="357" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU357"/>
+      <c r="AV357"/>
+      <c r="AW357"/>
+      <c r="AX357"/>
+      <c r="AY357"/>
+      <c r="AZ357"/>
+    </row>
+    <row r="358" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU358"/>
+      <c r="AV358"/>
+      <c r="AW358"/>
+      <c r="AX358"/>
+      <c r="AY358"/>
+      <c r="AZ358"/>
+    </row>
+    <row r="359" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU359"/>
+      <c r="AV359"/>
+      <c r="AW359"/>
+      <c r="AX359"/>
+      <c r="AY359"/>
+      <c r="AZ359"/>
+    </row>
+    <row r="360" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU360"/>
+      <c r="AV360"/>
+      <c r="AW360"/>
+      <c r="AX360"/>
+      <c r="AY360"/>
+      <c r="AZ360"/>
+    </row>
+    <row r="361" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU361"/>
+      <c r="AV361"/>
+      <c r="AW361"/>
+      <c r="AX361"/>
+      <c r="AY361"/>
+      <c r="AZ361"/>
+    </row>
+    <row r="362" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU362"/>
+      <c r="AV362"/>
+      <c r="AW362"/>
+      <c r="AX362"/>
+      <c r="AY362"/>
+      <c r="AZ362"/>
+    </row>
+    <row r="363" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU363"/>
+      <c r="AV363"/>
+      <c r="AW363"/>
+      <c r="AX363"/>
+      <c r="AY363"/>
+      <c r="AZ363"/>
+    </row>
+    <row r="364" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU364"/>
+      <c r="AV364"/>
+      <c r="AW364"/>
+      <c r="AX364"/>
+      <c r="AY364"/>
+      <c r="AZ364"/>
+    </row>
+    <row r="365" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU365"/>
+      <c r="AV365"/>
+      <c r="AW365"/>
+      <c r="AX365"/>
+      <c r="AY365"/>
+      <c r="AZ365"/>
+    </row>
+    <row r="366" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU366"/>
+      <c r="AV366"/>
+      <c r="AW366"/>
+      <c r="AX366"/>
+      <c r="AY366"/>
+      <c r="AZ366"/>
+    </row>
+    <row r="367" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU367"/>
+      <c r="AV367"/>
+      <c r="AW367"/>
+      <c r="AX367"/>
+      <c r="AY367"/>
+      <c r="AZ367"/>
+    </row>
+    <row r="368" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU368"/>
+      <c r="AV368"/>
+      <c r="AW368"/>
+      <c r="AX368"/>
+      <c r="AY368"/>
+      <c r="AZ368"/>
+    </row>
+    <row r="369" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU369"/>
+      <c r="AV369"/>
+      <c r="AW369"/>
+      <c r="AX369"/>
+      <c r="AY369"/>
+      <c r="AZ369"/>
+    </row>
+    <row r="370" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU370"/>
+      <c r="AV370"/>
+      <c r="AW370"/>
+      <c r="AX370"/>
+      <c r="AY370"/>
+      <c r="AZ370"/>
+    </row>
+    <row r="371" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU371"/>
+      <c r="AV371"/>
+      <c r="AW371"/>
+      <c r="AX371"/>
+      <c r="AY371"/>
+      <c r="AZ371"/>
+    </row>
+    <row r="372" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU372"/>
+      <c r="AV372"/>
+      <c r="AW372"/>
+      <c r="AX372"/>
+      <c r="AY372"/>
+      <c r="AZ372"/>
+    </row>
+    <row r="373" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU373"/>
+      <c r="AV373"/>
+      <c r="AW373"/>
+      <c r="AX373"/>
+      <c r="AY373"/>
+      <c r="AZ373"/>
+    </row>
+    <row r="374" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU374"/>
+      <c r="AV374"/>
+      <c r="AW374"/>
+      <c r="AX374"/>
+      <c r="AY374"/>
+      <c r="AZ374"/>
+    </row>
+    <row r="375" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU375"/>
+      <c r="AV375"/>
+      <c r="AW375"/>
+      <c r="AX375"/>
+      <c r="AY375"/>
+      <c r="AZ375"/>
+    </row>
+    <row r="376" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU376"/>
+      <c r="AV376"/>
+      <c r="AW376"/>
+      <c r="AX376"/>
+      <c r="AY376"/>
+      <c r="AZ376"/>
+    </row>
+    <row r="377" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU377"/>
+      <c r="AV377"/>
+      <c r="AW377"/>
+      <c r="AX377"/>
+      <c r="AY377"/>
+      <c r="AZ377"/>
+    </row>
+    <row r="378" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU378"/>
+      <c r="AV378"/>
+      <c r="AW378"/>
+      <c r="AX378"/>
+      <c r="AY378"/>
+      <c r="AZ378"/>
+    </row>
+    <row r="379" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU379"/>
+      <c r="AV379"/>
+      <c r="AW379"/>
+      <c r="AX379"/>
+      <c r="AY379"/>
+      <c r="AZ379"/>
+    </row>
+    <row r="380" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU380"/>
+      <c r="AV380"/>
+      <c r="AW380"/>
+      <c r="AX380"/>
+      <c r="AY380"/>
+      <c r="AZ380"/>
+    </row>
+    <row r="381" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU381"/>
+      <c r="AV381"/>
+      <c r="AW381"/>
+      <c r="AX381"/>
+      <c r="AY381"/>
+      <c r="AZ381"/>
+    </row>
+    <row r="382" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU382"/>
+      <c r="AV382"/>
+      <c r="AW382"/>
+      <c r="AX382"/>
+      <c r="AY382"/>
+      <c r="AZ382"/>
+    </row>
+    <row r="383" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU383"/>
+      <c r="AV383"/>
+      <c r="AW383"/>
+      <c r="AX383"/>
+      <c r="AY383"/>
+      <c r="AZ383"/>
+    </row>
+    <row r="384" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU384"/>
+      <c r="AV384"/>
+      <c r="AW384"/>
+      <c r="AX384"/>
+      <c r="AY384"/>
+      <c r="AZ384"/>
+    </row>
+    <row r="385" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU385"/>
+      <c r="AV385"/>
+      <c r="AW385"/>
+      <c r="AX385"/>
+      <c r="AY385"/>
+      <c r="AZ385"/>
+    </row>
+    <row r="386" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU386"/>
+      <c r="AV386"/>
+      <c r="AW386"/>
+      <c r="AX386"/>
+      <c r="AY386"/>
+      <c r="AZ386"/>
+    </row>
+    <row r="387" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU387"/>
+      <c r="AV387"/>
+      <c r="AW387"/>
+      <c r="AX387"/>
+      <c r="AY387"/>
+      <c r="AZ387"/>
+    </row>
+    <row r="388" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU388"/>
+      <c r="AV388"/>
+      <c r="AW388"/>
+      <c r="AX388"/>
+      <c r="AY388"/>
+      <c r="AZ388"/>
+    </row>
+    <row r="389" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU389"/>
+      <c r="AV389"/>
+      <c r="AW389"/>
+      <c r="AX389"/>
+      <c r="AY389"/>
+      <c r="AZ389"/>
+    </row>
+    <row r="390" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU390"/>
+      <c r="AV390"/>
+      <c r="AW390"/>
+      <c r="AX390"/>
+      <c r="AY390"/>
+      <c r="AZ390"/>
+    </row>
+    <row r="391" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU391"/>
+      <c r="AV391"/>
+      <c r="AW391"/>
+      <c r="AX391"/>
+      <c r="AY391"/>
+      <c r="AZ391"/>
+    </row>
+    <row r="392" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU392"/>
+      <c r="AV392"/>
+      <c r="AW392"/>
+      <c r="AX392"/>
+      <c r="AY392"/>
+      <c r="AZ392"/>
+    </row>
+    <row r="393" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU393"/>
+      <c r="AV393"/>
+      <c r="AW393"/>
+      <c r="AX393"/>
+      <c r="AY393"/>
+      <c r="AZ393"/>
+    </row>
+    <row r="394" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU394"/>
+      <c r="AV394"/>
+      <c r="AW394"/>
+      <c r="AX394"/>
+      <c r="AY394"/>
+      <c r="AZ394"/>
+    </row>
+    <row r="395" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU395"/>
+      <c r="AV395"/>
+      <c r="AW395"/>
+      <c r="AX395"/>
+      <c r="AY395"/>
+      <c r="AZ395"/>
+    </row>
+    <row r="396" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU396"/>
+      <c r="AV396"/>
+      <c r="AW396"/>
+      <c r="AX396"/>
+      <c r="AY396"/>
+      <c r="AZ396"/>
+    </row>
+    <row r="397" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU397"/>
+      <c r="AV397"/>
+      <c r="AW397"/>
+      <c r="AX397"/>
+      <c r="AY397"/>
+      <c r="AZ397"/>
+    </row>
+    <row r="398" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU398"/>
+      <c r="AV398"/>
+      <c r="AW398"/>
+      <c r="AX398"/>
+      <c r="AY398"/>
+      <c r="AZ398"/>
+    </row>
+    <row r="399" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU399"/>
+      <c r="AV399"/>
+      <c r="AW399"/>
+      <c r="AX399"/>
+      <c r="AY399"/>
+      <c r="AZ399"/>
+    </row>
+    <row r="400" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU400"/>
+      <c r="AV400"/>
+      <c r="AW400"/>
+      <c r="AX400"/>
+      <c r="AY400"/>
+      <c r="AZ400"/>
+    </row>
+    <row r="401" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU401"/>
+      <c r="AV401"/>
+      <c r="AW401"/>
+      <c r="AX401"/>
+      <c r="AY401"/>
+      <c r="AZ401"/>
+    </row>
+    <row r="402" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU402"/>
+      <c r="AV402"/>
+      <c r="AW402"/>
+      <c r="AX402"/>
+      <c r="AY402"/>
+      <c r="AZ402"/>
+    </row>
+    <row r="403" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU403"/>
+      <c r="AV403"/>
+      <c r="AW403"/>
+      <c r="AX403"/>
+      <c r="AY403"/>
+      <c r="AZ403"/>
+    </row>
+    <row r="404" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU404"/>
+      <c r="AV404"/>
+      <c r="AW404"/>
+      <c r="AX404"/>
+      <c r="AY404"/>
+      <c r="AZ404"/>
+    </row>
+    <row r="405" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU405"/>
+      <c r="AV405"/>
+      <c r="AW405"/>
+      <c r="AX405"/>
+      <c r="AY405"/>
+      <c r="AZ405"/>
+    </row>
+    <row r="406" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU406"/>
+      <c r="AV406"/>
+      <c r="AW406"/>
+      <c r="AX406"/>
+      <c r="AY406"/>
+      <c r="AZ406"/>
+    </row>
+    <row r="407" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU407"/>
+      <c r="AV407"/>
+      <c r="AW407"/>
+      <c r="AX407"/>
+      <c r="AY407"/>
+      <c r="AZ407"/>
+    </row>
+    <row r="408" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU408"/>
+      <c r="AV408"/>
+      <c r="AW408"/>
+      <c r="AX408"/>
+      <c r="AY408"/>
+      <c r="AZ408"/>
+    </row>
+    <row r="409" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU409"/>
+      <c r="AV409"/>
+      <c r="AW409"/>
+      <c r="AX409"/>
+      <c r="AY409"/>
+      <c r="AZ409"/>
+    </row>
+    <row r="410" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU410"/>
+      <c r="AV410"/>
+      <c r="AW410"/>
+      <c r="AX410"/>
+      <c r="AY410"/>
+      <c r="AZ410"/>
+    </row>
+    <row r="411" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU411"/>
+      <c r="AV411"/>
+      <c r="AW411"/>
+      <c r="AX411"/>
+      <c r="AY411"/>
+      <c r="AZ411"/>
+    </row>
+    <row r="412" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU412"/>
+      <c r="AV412"/>
+      <c r="AW412"/>
+      <c r="AX412"/>
+      <c r="AY412"/>
+      <c r="AZ412"/>
+    </row>
+    <row r="413" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU413"/>
+      <c r="AV413"/>
+      <c r="AW413"/>
+      <c r="AX413"/>
+      <c r="AY413"/>
+      <c r="AZ413"/>
+    </row>
+    <row r="414" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU414"/>
+      <c r="AV414"/>
+      <c r="AW414"/>
+      <c r="AX414"/>
+      <c r="AY414"/>
+      <c r="AZ414"/>
+    </row>
+    <row r="415" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU415"/>
+      <c r="AV415"/>
+      <c r="AW415"/>
+      <c r="AX415"/>
+      <c r="AY415"/>
+      <c r="AZ415"/>
+    </row>
+    <row r="416" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU416"/>
+      <c r="AV416"/>
+      <c r="AW416"/>
+      <c r="AX416"/>
+      <c r="AY416"/>
+      <c r="AZ416"/>
+    </row>
+    <row r="417" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU417"/>
+      <c r="AV417"/>
+      <c r="AW417"/>
+      <c r="AX417"/>
+      <c r="AY417"/>
+      <c r="AZ417"/>
+    </row>
+    <row r="418" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU418"/>
+      <c r="AV418"/>
+      <c r="AW418"/>
+      <c r="AX418"/>
+      <c r="AY418"/>
+      <c r="AZ418"/>
+    </row>
+    <row r="419" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU419"/>
+      <c r="AV419"/>
+      <c r="AW419"/>
+      <c r="AX419"/>
+      <c r="AY419"/>
+      <c r="AZ419"/>
+    </row>
+    <row r="420" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU420"/>
+      <c r="AV420"/>
+      <c r="AW420"/>
+      <c r="AX420"/>
+      <c r="AY420"/>
+      <c r="AZ420"/>
+    </row>
+    <row r="421" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU421"/>
+      <c r="AV421"/>
+      <c r="AW421"/>
+      <c r="AX421"/>
+      <c r="AY421"/>
+      <c r="AZ421"/>
+    </row>
+    <row r="422" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU422"/>
+      <c r="AV422"/>
+      <c r="AW422"/>
+      <c r="AX422"/>
+      <c r="AY422"/>
+      <c r="AZ422"/>
+    </row>
+    <row r="423" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU423"/>
+      <c r="AV423"/>
+      <c r="AW423"/>
+      <c r="AX423"/>
+      <c r="AY423"/>
+      <c r="AZ423"/>
+    </row>
+    <row r="424" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU424"/>
+      <c r="AV424"/>
+      <c r="AW424"/>
+      <c r="AX424"/>
+      <c r="AY424"/>
+      <c r="AZ424"/>
+    </row>
+    <row r="425" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU425"/>
+      <c r="AV425"/>
+      <c r="AW425"/>
+      <c r="AX425"/>
+      <c r="AY425"/>
+      <c r="AZ425"/>
+    </row>
+    <row r="426" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU426"/>
+      <c r="AV426"/>
+      <c r="AW426"/>
+      <c r="AX426"/>
+      <c r="AY426"/>
+      <c r="AZ426"/>
+    </row>
+    <row r="427" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU427"/>
+      <c r="AV427"/>
+      <c r="AW427"/>
+      <c r="AX427"/>
+      <c r="AY427"/>
+      <c r="AZ427"/>
+    </row>
+    <row r="428" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU428"/>
+      <c r="AV428"/>
+      <c r="AW428"/>
+      <c r="AX428"/>
+      <c r="AY428"/>
+      <c r="AZ428"/>
+    </row>
+    <row r="429" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU429"/>
+      <c r="AV429"/>
+      <c r="AW429"/>
+      <c r="AX429"/>
+      <c r="AY429"/>
+      <c r="AZ429"/>
+    </row>
+    <row r="430" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU430"/>
+      <c r="AV430"/>
+      <c r="AW430"/>
+      <c r="AX430"/>
+      <c r="AY430"/>
+      <c r="AZ430"/>
+    </row>
+    <row r="431" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU431"/>
+      <c r="AV431"/>
+      <c r="AW431"/>
+      <c r="AX431"/>
+      <c r="AY431"/>
+      <c r="AZ431"/>
+    </row>
+    <row r="432" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU432"/>
+      <c r="AV432"/>
+      <c r="AW432"/>
+      <c r="AX432"/>
+      <c r="AY432"/>
+      <c r="AZ432"/>
+    </row>
+    <row r="433" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU433"/>
+      <c r="AV433"/>
+      <c r="AW433"/>
+      <c r="AX433"/>
+      <c r="AY433"/>
+      <c r="AZ433"/>
+    </row>
+    <row r="434" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU434"/>
+      <c r="AV434"/>
+      <c r="AW434"/>
+      <c r="AX434"/>
+      <c r="AY434"/>
+      <c r="AZ434"/>
+    </row>
+    <row r="435" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU435"/>
+      <c r="AV435"/>
+      <c r="AW435"/>
+      <c r="AX435"/>
+      <c r="AY435"/>
+      <c r="AZ435"/>
+    </row>
+    <row r="436" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU436"/>
+      <c r="AV436"/>
+      <c r="AW436"/>
+      <c r="AX436"/>
+      <c r="AY436"/>
+      <c r="AZ436"/>
+    </row>
+    <row r="437" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU437"/>
+      <c r="AV437"/>
+      <c r="AW437"/>
+      <c r="AX437"/>
+      <c r="AY437"/>
+      <c r="AZ437"/>
+    </row>
+    <row r="438" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU438"/>
+      <c r="AV438"/>
+      <c r="AW438"/>
+      <c r="AX438"/>
+      <c r="AY438"/>
+      <c r="AZ438"/>
+    </row>
+    <row r="439" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU439"/>
+      <c r="AV439"/>
+      <c r="AW439"/>
+      <c r="AX439"/>
+      <c r="AY439"/>
+      <c r="AZ439"/>
+    </row>
+    <row r="440" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU440"/>
+      <c r="AV440"/>
+      <c r="AW440"/>
+      <c r="AX440"/>
+      <c r="AY440"/>
+      <c r="AZ440"/>
+    </row>
+    <row r="441" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU441"/>
+      <c r="AV441"/>
+      <c r="AW441"/>
+      <c r="AX441"/>
+      <c r="AY441"/>
+      <c r="AZ441"/>
+    </row>
+    <row r="442" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU442"/>
+      <c r="AV442"/>
+      <c r="AW442"/>
+      <c r="AX442"/>
+      <c r="AY442"/>
+      <c r="AZ442"/>
+    </row>
+    <row r="443" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU443"/>
+      <c r="AV443"/>
+      <c r="AW443"/>
+      <c r="AX443"/>
+      <c r="AY443"/>
+      <c r="AZ443"/>
+    </row>
+    <row r="444" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU444"/>
+      <c r="AV444"/>
+      <c r="AW444"/>
+      <c r="AX444"/>
+      <c r="AY444"/>
+      <c r="AZ444"/>
+    </row>
+    <row r="445" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU445"/>
+      <c r="AV445"/>
+      <c r="AW445"/>
+      <c r="AX445"/>
+      <c r="AY445"/>
+      <c r="AZ445"/>
+    </row>
+    <row r="446" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU446"/>
+      <c r="AV446"/>
+      <c r="AW446"/>
+      <c r="AX446"/>
+      <c r="AY446"/>
+      <c r="AZ446"/>
+    </row>
+    <row r="447" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU447"/>
+      <c r="AV447"/>
+      <c r="AW447"/>
+      <c r="AX447"/>
+      <c r="AY447"/>
+      <c r="AZ447"/>
+    </row>
+    <row r="448" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU448"/>
+      <c r="AV448"/>
+      <c r="AW448"/>
+      <c r="AX448"/>
+      <c r="AY448"/>
+      <c r="AZ448"/>
+    </row>
+    <row r="449" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU449"/>
+      <c r="AV449"/>
+      <c r="AW449"/>
+      <c r="AX449"/>
+      <c r="AY449"/>
+      <c r="AZ449"/>
+    </row>
+    <row r="450" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU450"/>
+      <c r="AV450"/>
+      <c r="AW450"/>
+      <c r="AX450"/>
+      <c r="AY450"/>
+      <c r="AZ450"/>
+    </row>
+    <row r="451" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU451"/>
+      <c r="AV451"/>
+      <c r="AW451"/>
+      <c r="AX451"/>
+      <c r="AY451"/>
+      <c r="AZ451"/>
+    </row>
+    <row r="452" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU452"/>
+      <c r="AV452"/>
+      <c r="AW452"/>
+      <c r="AX452"/>
+      <c r="AY452"/>
+      <c r="AZ452"/>
+    </row>
+    <row r="453" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU453"/>
+      <c r="AV453"/>
+      <c r="AW453"/>
+      <c r="AX453"/>
+      <c r="AY453"/>
+      <c r="AZ453"/>
+    </row>
+    <row r="454" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU454"/>
+      <c r="AV454"/>
+      <c r="AW454"/>
+      <c r="AX454"/>
+      <c r="AY454"/>
+      <c r="AZ454"/>
+    </row>
+    <row r="455" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU455"/>
+      <c r="AV455"/>
+      <c r="AW455"/>
+      <c r="AX455"/>
+      <c r="AY455"/>
+      <c r="AZ455"/>
+    </row>
+    <row r="456" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU456"/>
+      <c r="AV456"/>
+      <c r="AW456"/>
+      <c r="AX456"/>
+      <c r="AY456"/>
+      <c r="AZ456"/>
+    </row>
+    <row r="457" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU457"/>
+      <c r="AV457"/>
+      <c r="AW457"/>
+      <c r="AX457"/>
+      <c r="AY457"/>
+      <c r="AZ457"/>
+    </row>
+    <row r="458" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU458"/>
+      <c r="AV458"/>
+      <c r="AW458"/>
+      <c r="AX458"/>
+      <c r="AY458"/>
+      <c r="AZ458"/>
+    </row>
+    <row r="459" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU459"/>
+      <c r="AV459"/>
+      <c r="AW459"/>
+      <c r="AX459"/>
+      <c r="AY459"/>
+      <c r="AZ459"/>
+    </row>
+    <row r="460" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU460"/>
+      <c r="AV460"/>
+      <c r="AW460"/>
+      <c r="AX460"/>
+      <c r="AY460"/>
+      <c r="AZ460"/>
+    </row>
+    <row r="461" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU461"/>
+      <c r="AV461"/>
+      <c r="AW461"/>
+      <c r="AX461"/>
+      <c r="AY461"/>
+      <c r="AZ461"/>
+    </row>
+    <row r="462" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU462"/>
+      <c r="AV462"/>
+      <c r="AW462"/>
+      <c r="AX462"/>
+      <c r="AY462"/>
+      <c r="AZ462"/>
+    </row>
+    <row r="463" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU463"/>
+      <c r="AV463"/>
+      <c r="AW463"/>
+      <c r="AX463"/>
+      <c r="AY463"/>
+      <c r="AZ463"/>
+    </row>
+    <row r="464" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU464"/>
+      <c r="AV464"/>
+      <c r="AW464"/>
+      <c r="AX464"/>
+      <c r="AY464"/>
+      <c r="AZ464"/>
+    </row>
+    <row r="465" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU465"/>
+      <c r="AV465"/>
+      <c r="AW465"/>
+      <c r="AX465"/>
+      <c r="AY465"/>
+      <c r="AZ465"/>
+    </row>
+    <row r="466" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU466"/>
+      <c r="AV466"/>
+      <c r="AW466"/>
+      <c r="AX466"/>
+      <c r="AY466"/>
+      <c r="AZ466"/>
+    </row>
+    <row r="467" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU467"/>
+      <c r="AV467"/>
+      <c r="AW467"/>
+      <c r="AX467"/>
+      <c r="AY467"/>
+      <c r="AZ467"/>
+    </row>
+    <row r="468" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU468"/>
+      <c r="AV468"/>
+      <c r="AW468"/>
+      <c r="AX468"/>
+      <c r="AY468"/>
+      <c r="AZ468"/>
+    </row>
+    <row r="469" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU469"/>
+      <c r="AV469"/>
+      <c r="AW469"/>
+      <c r="AX469"/>
+      <c r="AY469"/>
+      <c r="AZ469"/>
+    </row>
+    <row r="470" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU470"/>
+      <c r="AV470"/>
+      <c r="AW470"/>
+      <c r="AX470"/>
+      <c r="AY470"/>
+      <c r="AZ470"/>
+    </row>
+    <row r="471" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU471"/>
+      <c r="AV471"/>
+      <c r="AW471"/>
+      <c r="AX471"/>
+      <c r="AY471"/>
+      <c r="AZ471"/>
+    </row>
+    <row r="472" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU472"/>
+      <c r="AV472"/>
+      <c r="AW472"/>
+      <c r="AX472"/>
+      <c r="AY472"/>
+      <c r="AZ472"/>
+    </row>
+    <row r="473" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU473"/>
+      <c r="AV473"/>
+      <c r="AW473"/>
+      <c r="AX473"/>
+      <c r="AY473"/>
+      <c r="AZ473"/>
+    </row>
+    <row r="474" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU474"/>
+      <c r="AV474"/>
+      <c r="AW474"/>
+      <c r="AX474"/>
+      <c r="AY474"/>
+      <c r="AZ474"/>
+    </row>
+    <row r="475" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU475"/>
+      <c r="AV475"/>
+      <c r="AW475"/>
+      <c r="AX475"/>
+      <c r="AY475"/>
+      <c r="AZ475"/>
+    </row>
+    <row r="476" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU476"/>
+      <c r="AV476"/>
+      <c r="AW476"/>
+      <c r="AX476"/>
+      <c r="AY476"/>
+      <c r="AZ476"/>
+    </row>
+    <row r="477" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU477"/>
+      <c r="AV477"/>
+      <c r="AW477"/>
+      <c r="AX477"/>
+      <c r="AY477"/>
+      <c r="AZ477"/>
+    </row>
+    <row r="478" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU478"/>
+      <c r="AV478"/>
+      <c r="AW478"/>
+      <c r="AX478"/>
+      <c r="AY478"/>
+      <c r="AZ478"/>
+    </row>
+    <row r="479" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU479"/>
+      <c r="AV479"/>
+      <c r="AW479"/>
+      <c r="AX479"/>
+      <c r="AY479"/>
+      <c r="AZ479"/>
+    </row>
+    <row r="480" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU480"/>
+      <c r="AV480"/>
+      <c r="AW480"/>
+      <c r="AX480"/>
+      <c r="AY480"/>
+      <c r="AZ480"/>
+    </row>
+    <row r="481" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU481"/>
+      <c r="AV481"/>
+      <c r="AW481"/>
+      <c r="AX481"/>
+      <c r="AY481"/>
+      <c r="AZ481"/>
+    </row>
+    <row r="482" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU482"/>
+      <c r="AV482"/>
+      <c r="AW482"/>
+      <c r="AX482"/>
+      <c r="AY482"/>
+      <c r="AZ482"/>
+    </row>
+    <row r="483" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU483"/>
+      <c r="AV483"/>
+      <c r="AW483"/>
+      <c r="AX483"/>
+      <c r="AY483"/>
+      <c r="AZ483"/>
+    </row>
+    <row r="484" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU484"/>
+      <c r="AV484"/>
+      <c r="AW484"/>
+      <c r="AX484"/>
+      <c r="AY484"/>
+      <c r="AZ484"/>
+    </row>
+    <row r="485" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU485"/>
+      <c r="AV485"/>
+      <c r="AW485"/>
+      <c r="AX485"/>
+      <c r="AY485"/>
+      <c r="AZ485"/>
+    </row>
+    <row r="486" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU486"/>
+      <c r="AV486"/>
+      <c r="AW486"/>
+      <c r="AX486"/>
+      <c r="AY486"/>
+      <c r="AZ486"/>
+    </row>
+    <row r="487" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU487"/>
+      <c r="AV487"/>
+      <c r="AW487"/>
+      <c r="AX487"/>
+      <c r="AY487"/>
+      <c r="AZ487"/>
+    </row>
+    <row r="488" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU488"/>
+      <c r="AV488"/>
+      <c r="AW488"/>
+      <c r="AX488"/>
+      <c r="AY488"/>
+      <c r="AZ488"/>
+    </row>
+    <row r="489" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU489"/>
+      <c r="AV489"/>
+      <c r="AW489"/>
+      <c r="AX489"/>
+      <c r="AY489"/>
+      <c r="AZ489"/>
+    </row>
+    <row r="490" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU490"/>
+      <c r="AV490"/>
+      <c r="AW490"/>
+      <c r="AX490"/>
+      <c r="AY490"/>
+      <c r="AZ490"/>
+    </row>
+    <row r="491" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU491"/>
+      <c r="AV491"/>
+      <c r="AW491"/>
+      <c r="AX491"/>
+      <c r="AY491"/>
+      <c r="AZ491"/>
+    </row>
+    <row r="492" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU492"/>
+      <c r="AV492"/>
+      <c r="AW492"/>
+      <c r="AX492"/>
+      <c r="AY492"/>
+      <c r="AZ492"/>
+    </row>
+    <row r="493" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU493"/>
+      <c r="AV493"/>
+      <c r="AW493"/>
+      <c r="AX493"/>
+      <c r="AY493"/>
+      <c r="AZ493"/>
+    </row>
+    <row r="494" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU494"/>
+      <c r="AV494"/>
+      <c r="AW494"/>
+      <c r="AX494"/>
+      <c r="AY494"/>
+      <c r="AZ494"/>
+    </row>
+    <row r="495" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU495"/>
+      <c r="AV495"/>
+      <c r="AW495"/>
+      <c r="AX495"/>
+      <c r="AY495"/>
+      <c r="AZ495"/>
+    </row>
+    <row r="496" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU496"/>
+      <c r="AV496"/>
+      <c r="AW496"/>
+      <c r="AX496"/>
+      <c r="AY496"/>
+      <c r="AZ496"/>
+    </row>
+    <row r="497" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU497"/>
+      <c r="AV497"/>
+      <c r="AW497"/>
+      <c r="AX497"/>
+      <c r="AY497"/>
+      <c r="AZ497"/>
+    </row>
+    <row r="498" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU498"/>
+      <c r="AV498"/>
+      <c r="AW498"/>
+      <c r="AX498"/>
+      <c r="AY498"/>
+      <c r="AZ498"/>
+    </row>
+    <row r="499" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU499"/>
+      <c r="AV499"/>
+      <c r="AW499"/>
+      <c r="AX499"/>
+      <c r="AY499"/>
+      <c r="AZ499"/>
+    </row>
+    <row r="500" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU500"/>
+      <c r="AV500"/>
+      <c r="AW500"/>
+      <c r="AX500"/>
+      <c r="AY500"/>
+      <c r="AZ500"/>
+    </row>
+    <row r="501" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU501"/>
+      <c r="AV501"/>
+      <c r="AW501"/>
+      <c r="AX501"/>
+      <c r="AY501"/>
+      <c r="AZ501"/>
+    </row>
+    <row r="502" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU502"/>
+      <c r="AV502"/>
+      <c r="AW502"/>
+      <c r="AX502"/>
+      <c r="AY502"/>
+      <c r="AZ502"/>
+    </row>
+    <row r="503" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU503"/>
+      <c r="AV503"/>
+      <c r="AW503"/>
+      <c r="AX503"/>
+      <c r="AY503"/>
+      <c r="AZ503"/>
+    </row>
+    <row r="504" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU504"/>
+      <c r="AV504"/>
+      <c r="AW504"/>
+      <c r="AX504"/>
+      <c r="AY504"/>
+      <c r="AZ504"/>
+    </row>
+    <row r="505" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU505"/>
+      <c r="AV505"/>
+      <c r="AW505"/>
+      <c r="AX505"/>
+      <c r="AY505"/>
+      <c r="AZ505"/>
+    </row>
+    <row r="506" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU506"/>
+      <c r="AV506"/>
+      <c r="AW506"/>
+      <c r="AX506"/>
+      <c r="AY506"/>
+      <c r="AZ506"/>
+    </row>
+    <row r="507" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU507"/>
+      <c r="AV507"/>
+      <c r="AW507"/>
+      <c r="AX507"/>
+      <c r="AY507"/>
+      <c r="AZ507"/>
+    </row>
+    <row r="508" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU508"/>
+      <c r="AV508"/>
+      <c r="AW508"/>
+      <c r="AX508"/>
+      <c r="AY508"/>
+      <c r="AZ508"/>
+    </row>
+    <row r="509" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU509"/>
+      <c r="AV509"/>
+      <c r="AW509"/>
+      <c r="AX509"/>
+      <c r="AY509"/>
+      <c r="AZ509"/>
+    </row>
+    <row r="510" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU510"/>
+      <c r="AV510"/>
+      <c r="AW510"/>
+      <c r="AX510"/>
+      <c r="AY510"/>
+      <c r="AZ510"/>
+    </row>
+    <row r="511" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU511"/>
+      <c r="AV511"/>
+      <c r="AW511"/>
+      <c r="AX511"/>
+      <c r="AY511"/>
+      <c r="AZ511"/>
+    </row>
+    <row r="512" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU512"/>
+      <c r="AV512"/>
+      <c r="AW512"/>
+      <c r="AX512"/>
+      <c r="AY512"/>
+      <c r="AZ512"/>
+    </row>
+    <row r="513" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU513"/>
+      <c r="AV513"/>
+      <c r="AW513"/>
+      <c r="AX513"/>
+      <c r="AY513"/>
+      <c r="AZ513"/>
+    </row>
+    <row r="514" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU514"/>
+      <c r="AV514"/>
+      <c r="AW514"/>
+      <c r="AX514"/>
+      <c r="AY514"/>
+      <c r="AZ514"/>
+    </row>
+    <row r="515" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU515"/>
+      <c r="AV515"/>
+      <c r="AW515"/>
+      <c r="AX515"/>
+      <c r="AY515"/>
+      <c r="AZ515"/>
+    </row>
+    <row r="516" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU516"/>
+      <c r="AV516"/>
+      <c r="AW516"/>
+      <c r="AX516"/>
+      <c r="AY516"/>
+      <c r="AZ516"/>
+    </row>
+    <row r="517" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU517"/>
+      <c r="AV517"/>
+      <c r="AW517"/>
+      <c r="AX517"/>
+      <c r="AY517"/>
+      <c r="AZ517"/>
+    </row>
+    <row r="518" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU518"/>
+      <c r="AV518"/>
+      <c r="AW518"/>
+      <c r="AX518"/>
+      <c r="AY518"/>
+      <c r="AZ518"/>
+    </row>
+    <row r="519" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU519"/>
+      <c r="AV519"/>
+      <c r="AW519"/>
+      <c r="AX519"/>
+      <c r="AY519"/>
+      <c r="AZ519"/>
+    </row>
+    <row r="520" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU520"/>
+      <c r="AV520"/>
+      <c r="AW520"/>
+      <c r="AX520"/>
+      <c r="AY520"/>
+      <c r="AZ520"/>
+    </row>
+    <row r="521" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU521"/>
+      <c r="AV521"/>
+      <c r="AW521"/>
+      <c r="AX521"/>
+      <c r="AY521"/>
+      <c r="AZ521"/>
+    </row>
+    <row r="522" spans="47:52" ht="11.45" customHeight="1">
+      <c r="AU522"/>
+      <c r="AV522"/>
+      <c r="AW522"/>
+      <c r="AX522"/>
+      <c r="AY522"/>
+      <c r="AZ522"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:AC15">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:AC10">
     <sortCondition ref="B9"/>
   </sortState>
-  <mergeCells count="34">
+  <mergeCells count="3">
     <mergeCell ref="B1:O1"/>
-    <mergeCell ref="K7:Z7"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="V2:Z6"/>
     <mergeCell ref="P4:U4"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="AD1:AD200"/>
   </mergeCells>
   <conditionalFormatting sqref="I40">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -7220,11 +11659,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29" xr:uid="{7DB9EFD9-E784-464D-B93C-ABBEF7F1E8CE}">
+      <formula1>$D$43:$D$44</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37" xr:uid="{9801D4AE-E571-4CBA-A92E-D326A24D3A44}">
       <formula1>$C$43:$C$44</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>$D$43:$D$44</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.15748031496062992" right="0.19685039370078741" top="0.15748031496062992" bottom="0.15748031496062992" header="0.23622047244094491" footer="0.15748031496062992"/>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_exel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kp_generator\templates_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716BADE0-C532-4B0D-92A6-DA2756812951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568254F2-30BD-4714-8229-07CDB0582DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="294" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="85">
   <si>
     <t>По номенклатуре:</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>КНР-</t>
+  </si>
+  <si>
+    <t>{{ tender_number }}</t>
   </si>
 </sst>
 </file>
@@ -5772,7 +5775,9 @@
       <c r="C5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="14" t="s">
+        <v>84</v>
+      </c>
       <c r="E5" s="15"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kp_generator\templates_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\kp_generator\templates_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568254F2-30BD-4714-8229-07CDB0582DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="294" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="294"/>
   </bookViews>
   <sheets>
     <sheet name="расчет" sheetId="4" r:id="rId1"/>
@@ -19,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$36</definedName>
     <definedName name="Длина_сделки">расчет!$K$15</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullPrecision="0"/>
+  <calcPr calcId="162913" fullPrecision="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -301,31 +300,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="23">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-415]General"/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="[$$-409]#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* &quot;-&quot;??[$€-1]_-"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="[$¥-478]#,##0.00"/>
-    <numFmt numFmtId="176" formatCode="_ [$¥-478]* #,##0_ ;_ [$¥-478]* \-#,##0_ ;_ [$¥-478]* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="[$¥-478]#,##0"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="179" formatCode="[$¥-804]#,##0.00"/>
-    <numFmt numFmtId="180" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
-    <numFmt numFmtId="181" formatCode="[$¥-478]#,##0.0"/>
-    <numFmt numFmtId="182" formatCode="#,##0.00\ &quot;₽&quot;;[Red]#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="183" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
-    <numFmt numFmtId="184" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="185" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="[$-415]General"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="[$$-409]#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* &quot;-&quot;??[$€-1]_-"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="[$¥-478]#,##0.00"/>
+    <numFmt numFmtId="175" formatCode="_ [$¥-478]* #,##0_ ;_ [$¥-478]* \-#,##0_ ;_ [$¥-478]* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$¥-478]#,##0"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="178" formatCode="[$¥-804]#,##0.00"/>
+    <numFmt numFmtId="179" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="[$¥-478]#,##0.0"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00\ &quot;₽&quot;;[Red]#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="182" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
+    <numFmt numFmtId="183" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="184" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -888,24 +887,24 @@
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3">
@@ -923,17 +922,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -944,10 +943,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -959,23 +958,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -993,7 +992,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1100,21 +1099,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1140,7 +1139,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1155,7 +1154,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -1181,23 +1180,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
@@ -1211,7 +1210,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -1219,12 +1218,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
@@ -1240,7 +1239,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1251,49 +1250,49 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1439,11 +1438,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1451,22 +1450,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -1489,17 +1488,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1534,201 +1533,201 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
@@ -1736,12 +1735,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1768,77 +1767,77 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1873,69 +1872,69 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1945,13 +1944,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -1969,7 +1968,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -1986,7 +1985,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2003,7 +2002,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2048,7 +2047,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -2059,119 +2058,119 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
@@ -2332,15 +2331,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
@@ -2474,7 +2473,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
@@ -2489,7 +2488,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2519,7 +2518,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2576,39 +2575,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2634,11 +2633,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2667,407 +2666,407 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3">
@@ -3088,7 +3087,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="3">
@@ -3114,7 +3113,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3228,7 +3227,7 @@
     <xf numFmtId="0" fontId="32" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3253,10 +3252,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="180" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3265,34 +3264,34 @@
     <xf numFmtId="0" fontId="38" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="38" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="38" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="3" borderId="14" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="3" borderId="14" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3305,10 +3304,10 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="32" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3317,28 +3316,28 @@
     <xf numFmtId="3" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="39" fillId="0" borderId="13" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="39" fillId="0" borderId="13" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="39" fillId="0" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="39" fillId="0" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="32" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="32" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="14" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3358,13 +3357,13 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="32" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="39" fillId="0" borderId="10" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="10" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="32" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3373,31 +3372,31 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="32" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="3" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3423,9 +3422,6 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3541,7 +3537,7 @@
     <xf numFmtId="1" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3560,19 +3556,19 @@
     <xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="37" fillId="4" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3585,7 +3581,7 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3610,1668 +3606,1668 @@
     </xf>
   </cellXfs>
   <cellStyles count="1662">
-    <cellStyle name="Excel Built-in Normal" xfId="78" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Excel Built-in Normal 2" xfId="95" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Excel Built-in Normal 2 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Excel Built-in Normal 3" xfId="96" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Excel Built-in Normal 4" xfId="97" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Excel Built-in Normal 4 2" xfId="81" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Excel Built-in Normal 5" xfId="76" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Excel Built-in Normal 5 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Гиперссылка 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Гиперссылка 2 10" xfId="94" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Гиперссылка 2 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2" xfId="99" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2" xfId="84" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2" xfId="104" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 4" xfId="108" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 5" xfId="113" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 3" xfId="114" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 5" xfId="118" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 6" xfId="120" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3" xfId="121" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 2" xfId="122" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 3" xfId="123" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 4" xfId="125" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 5" xfId="127" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 4" xfId="128" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 5" xfId="130" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 6" xfId="132" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 7" xfId="134" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3" xfId="136" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2" xfId="138" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 2" xfId="143" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 3" xfId="145" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 4" xfId="147" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 5" xfId="149" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 3" xfId="151" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 4" xfId="158" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 5" xfId="163" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 6" xfId="166" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4" xfId="168" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 2" xfId="172" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 3" xfId="176" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 4" xfId="177" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 5" xfId="178" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="Гиперссылка 2 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="Гиперссылка 2 2 6" xfId="183" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="Гиперссылка 2 2 7" xfId="185" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="Гиперссылка 2 2 8" xfId="186" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Гиперссылка 2 3" xfId="189" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2" xfId="190" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2" xfId="193" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 3" xfId="196" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 4" xfId="199" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 5" xfId="201" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 3" xfId="203" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 4" xfId="205" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 5" xfId="206" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 6" xfId="207" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3" xfId="209" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 2" xfId="210" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 3" xfId="211" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 4" xfId="213" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 5" xfId="215" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="Гиперссылка 2 3 4" xfId="217" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="Гиперссылка 2 3 5" xfId="52" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="Гиперссылка 2 3 6" xfId="219" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="Гиперссылка 2 3 7" xfId="220" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="Гиперссылка 2 4" xfId="222" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2" xfId="224" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 3" xfId="226" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 4" xfId="228" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 5" xfId="231" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Гиперссылка 2 4 3" xfId="54" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Гиперссылка 2 4 4" xfId="232" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="Гиперссылка 2 4 5" xfId="233" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="Гиперссылка 2 4 6" xfId="235" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="Гиперссылка 2 5" xfId="237" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2" xfId="242" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 2" xfId="244" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 3" xfId="246" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 4" xfId="248" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 5" xfId="250" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="Гиперссылка 2 5 3" xfId="252" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="Гиперссылка 2 5 4" xfId="254" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="Гиперссылка 2 5 5" xfId="256" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="Гиперссылка 2 5 6" xfId="259" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="Гиперссылка 2 6" xfId="261" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="Гиперссылка 2 6 2" xfId="264" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="Гиперссылка 2 6 3" xfId="266" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="Гиперссылка 2 6 4" xfId="268" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="Гиперссылка 2 6 5" xfId="270" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="Гиперссылка 2 7" xfId="273" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="Гиперссылка 2 8" xfId="275" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="Гиперссылка 2 9" xfId="277" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="78"/>
+    <cellStyle name="Excel Built-in Normal 2" xfId="95"/>
+    <cellStyle name="Excel Built-in Normal 2 2" xfId="89"/>
+    <cellStyle name="Excel Built-in Normal 3" xfId="96"/>
+    <cellStyle name="Excel Built-in Normal 4" xfId="97"/>
+    <cellStyle name="Excel Built-in Normal 4 2" xfId="81"/>
+    <cellStyle name="Excel Built-in Normal 5" xfId="76"/>
+    <cellStyle name="Excel Built-in Normal 5 2" xfId="77"/>
+    <cellStyle name="Гиперссылка 2" xfId="48"/>
+    <cellStyle name="Гиперссылка 2 10" xfId="94"/>
+    <cellStyle name="Гиперссылка 2 2" xfId="98"/>
+    <cellStyle name="Гиперссылка 2 2 2" xfId="99"/>
+    <cellStyle name="Гиперссылка 2 2 2 2" xfId="84"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2" xfId="104"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 2" xfId="83"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 3" xfId="88"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 4" xfId="108"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 5" xfId="113"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 3" xfId="114"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 4" xfId="116"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 5" xfId="118"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 6" xfId="120"/>
+    <cellStyle name="Гиперссылка 2 2 2 3" xfId="121"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 2" xfId="122"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 3" xfId="123"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 4" xfId="125"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 5" xfId="127"/>
+    <cellStyle name="Гиперссылка 2 2 2 4" xfId="128"/>
+    <cellStyle name="Гиперссылка 2 2 2 5" xfId="130"/>
+    <cellStyle name="Гиперссылка 2 2 2 6" xfId="132"/>
+    <cellStyle name="Гиперссылка 2 2 2 7" xfId="134"/>
+    <cellStyle name="Гиперссылка 2 2 3" xfId="136"/>
+    <cellStyle name="Гиперссылка 2 2 3 2" xfId="138"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 2" xfId="143"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 3" xfId="145"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 4" xfId="147"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 5" xfId="149"/>
+    <cellStyle name="Гиперссылка 2 2 3 3" xfId="151"/>
+    <cellStyle name="Гиперссылка 2 2 3 4" xfId="158"/>
+    <cellStyle name="Гиперссылка 2 2 3 5" xfId="163"/>
+    <cellStyle name="Гиперссылка 2 2 3 6" xfId="166"/>
+    <cellStyle name="Гиперссылка 2 2 4" xfId="168"/>
+    <cellStyle name="Гиперссылка 2 2 4 2" xfId="172"/>
+    <cellStyle name="Гиперссылка 2 2 4 3" xfId="176"/>
+    <cellStyle name="Гиперссылка 2 2 4 4" xfId="177"/>
+    <cellStyle name="Гиперссылка 2 2 4 5" xfId="178"/>
+    <cellStyle name="Гиперссылка 2 2 5" xfId="180"/>
+    <cellStyle name="Гиперссылка 2 2 6" xfId="183"/>
+    <cellStyle name="Гиперссылка 2 2 7" xfId="185"/>
+    <cellStyle name="Гиперссылка 2 2 8" xfId="186"/>
+    <cellStyle name="Гиперссылка 2 3" xfId="189"/>
+    <cellStyle name="Гиперссылка 2 3 2" xfId="190"/>
+    <cellStyle name="Гиперссылка 2 3 2 2" xfId="193"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 2" xfId="36"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 3" xfId="196"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 4" xfId="199"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 5" xfId="201"/>
+    <cellStyle name="Гиперссылка 2 3 2 3" xfId="203"/>
+    <cellStyle name="Гиперссылка 2 3 2 4" xfId="205"/>
+    <cellStyle name="Гиперссылка 2 3 2 5" xfId="206"/>
+    <cellStyle name="Гиперссылка 2 3 2 6" xfId="207"/>
+    <cellStyle name="Гиперссылка 2 3 3" xfId="209"/>
+    <cellStyle name="Гиперссылка 2 3 3 2" xfId="210"/>
+    <cellStyle name="Гиперссылка 2 3 3 3" xfId="211"/>
+    <cellStyle name="Гиперссылка 2 3 3 4" xfId="213"/>
+    <cellStyle name="Гиперссылка 2 3 3 5" xfId="215"/>
+    <cellStyle name="Гиперссылка 2 3 4" xfId="217"/>
+    <cellStyle name="Гиперссылка 2 3 5" xfId="52"/>
+    <cellStyle name="Гиперссылка 2 3 6" xfId="219"/>
+    <cellStyle name="Гиперссылка 2 3 7" xfId="220"/>
+    <cellStyle name="Гиперссылка 2 4" xfId="222"/>
+    <cellStyle name="Гиперссылка 2 4 2" xfId="224"/>
+    <cellStyle name="Гиперссылка 2 4 2 2" xfId="38"/>
+    <cellStyle name="Гиперссылка 2 4 2 3" xfId="226"/>
+    <cellStyle name="Гиперссылка 2 4 2 4" xfId="228"/>
+    <cellStyle name="Гиперссылка 2 4 2 5" xfId="231"/>
+    <cellStyle name="Гиперссылка 2 4 3" xfId="54"/>
+    <cellStyle name="Гиперссылка 2 4 4" xfId="232"/>
+    <cellStyle name="Гиперссылка 2 4 5" xfId="233"/>
+    <cellStyle name="Гиперссылка 2 4 6" xfId="235"/>
+    <cellStyle name="Гиперссылка 2 5" xfId="237"/>
+    <cellStyle name="Гиперссылка 2 5 2" xfId="242"/>
+    <cellStyle name="Гиперссылка 2 5 2 2" xfId="244"/>
+    <cellStyle name="Гиперссылка 2 5 2 3" xfId="246"/>
+    <cellStyle name="Гиперссылка 2 5 2 4" xfId="248"/>
+    <cellStyle name="Гиперссылка 2 5 2 5" xfId="250"/>
+    <cellStyle name="Гиперссылка 2 5 3" xfId="252"/>
+    <cellStyle name="Гиперссылка 2 5 4" xfId="254"/>
+    <cellStyle name="Гиперссылка 2 5 5" xfId="256"/>
+    <cellStyle name="Гиперссылка 2 5 6" xfId="259"/>
+    <cellStyle name="Гиперссылка 2 6" xfId="261"/>
+    <cellStyle name="Гиперссылка 2 6 2" xfId="264"/>
+    <cellStyle name="Гиперссылка 2 6 3" xfId="266"/>
+    <cellStyle name="Гиперссылка 2 6 4" xfId="268"/>
+    <cellStyle name="Гиперссылка 2 6 5" xfId="270"/>
+    <cellStyle name="Гиперссылка 2 7" xfId="273"/>
+    <cellStyle name="Гиперссылка 2 8" xfId="275"/>
+    <cellStyle name="Гиперссылка 2 9" xfId="277"/>
     <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Денежный 2" xfId="112" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="Денежный 2 2" xfId="278" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="Денежный 2 2 2" xfId="157" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Денежный 2" xfId="112"/>
+    <cellStyle name="Денежный 2 2" xfId="278"/>
+    <cellStyle name="Денежный 2 2 2" xfId="157"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="279" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="Обычный 10 2" xfId="281" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="Обычный 11" xfId="282" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="Обычный 11 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="Обычный 12" xfId="287" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="Обычный 12 2" xfId="291" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="Обычный 13" xfId="293" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="Обычный 13 2" xfId="69" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="Обычный 14" xfId="295" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="Обычный 14 2" xfId="131" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="Обычный 15" xfId="298" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="Обычный 15 2" xfId="165" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="Обычный 16" xfId="301" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="Обычный 16 2" xfId="302" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="Обычный 17" xfId="303" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="Обычный 17 2" xfId="305" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="Обычный 18" xfId="306" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="Обычный 18 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="Обычный 19" xfId="19" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="Обычный 2" xfId="4" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="Обычный 2 10" xfId="310" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="Обычный 2 10 2" xfId="182" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="Обычный 2 11" xfId="311" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="Обычный 2 12" xfId="37" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="Обычный 2 12 2" xfId="234" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="Обычный 2 12 3" xfId="312" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="Обычный 2 13" xfId="225" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="Обычный 2 13 2" xfId="258" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="Обычный 2 14" xfId="227" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="Обычный 2 14 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="Обычный 2 15" xfId="229" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="Обычный 2 15 2" xfId="317" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="Обычный 2 16" xfId="319" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="Обычный 2 16 2" xfId="322" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="Обычный 2 17" xfId="325" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="Обычный 2 17 2" xfId="329" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="Обычный 2 18" xfId="333" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="Обычный 2 18 2" xfId="57" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="Обычный 2 19" xfId="338" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="Обычный 2 19 2" xfId="342" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="Обычный 2 19 3" xfId="346" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="Обычный 2 2" xfId="348" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="Обычный 2 2 10" xfId="353" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="Обычный 2 2 10 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="Обычный 2 2 10 3" xfId="359" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="Обычный 2 2 10 4" xfId="362" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="Обычный 2 2 11" xfId="93" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="Обычный 2 2 2" xfId="365" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="Обычный 2 2 2 2" xfId="366" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2" xfId="367" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2" xfId="369" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 2" xfId="292" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 3" xfId="294" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 4" xfId="297" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 5" xfId="300" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 3" xfId="371" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 4" xfId="372" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 5" xfId="373" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 6" xfId="374" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3" xfId="75" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 2" xfId="376" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 3" xfId="191" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 4" xfId="202" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 5" xfId="204" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 4" xfId="377" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 5" xfId="378" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 6" xfId="379" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 7" xfId="380" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3" xfId="82" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2" xfId="42" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 2" xfId="381" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 3" xfId="382" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 4" xfId="383" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 5" xfId="384" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 3" xfId="385" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 4" xfId="386" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 5" xfId="387" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 6" xfId="388" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4" xfId="87" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 2" xfId="390" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 3" xfId="392" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 4" xfId="394" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 5" xfId="102" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 5" xfId="107" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 6" xfId="111" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 7" xfId="398" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 8" xfId="402" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="Обычный 2 2 2 3" xfId="403" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="Обычный 2 2 2 3 2" xfId="404" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="Обычный 2 2 3" xfId="407" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="Обычный 2 2 3 2" xfId="408" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="Обычный 2 2 4" xfId="241" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="Обычный 2 2 4 2" xfId="243" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2" xfId="409" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 2" xfId="137" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 3" xfId="150" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 4" xfId="154" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 5" xfId="162" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 3" xfId="167" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 4" xfId="179" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 6" xfId="184" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3" xfId="410" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 2" xfId="208" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 3" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 4" xfId="51" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 5" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 4" xfId="412" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 5" xfId="308" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 6" xfId="414" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 7" xfId="352" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="Обычный 2 2 4 3" xfId="245" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2" xfId="415" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 4" xfId="423" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 5" xfId="425" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 3" xfId="426" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 4" xfId="427" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 5" xfId="60" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 6" xfId="49" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="Обычный 2 2 4 4" xfId="247" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 3" xfId="431" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 4" xfId="434" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 5" xfId="437" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="Обычный 2 2 4 5" xfId="249" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="Обычный 2 2 4 6" xfId="438" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="Обычный 2 2 4 7" xfId="223" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="Обычный 2 2 4 8" xfId="53" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="Обычный 2 2 5" xfId="251" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="Обычный 2 2 5 2" xfId="440" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2" xfId="442" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 2" xfId="444" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 3" xfId="446" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 5" xfId="174" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 3" xfId="448" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 4" xfId="450" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 5" xfId="452" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 6" xfId="454" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="Обычный 2 2 5 3" xfId="456" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 2" xfId="458" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 3" xfId="460" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 4" xfId="461" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 5" xfId="462" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="Обычный 2 2 5 4" xfId="464" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="Обычный 2 2 5 5" xfId="364" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="Обычный 2 2 5 6" xfId="406" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="Обычный 2 2 5 7" xfId="240" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="Обычный 2 2 6" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="Обычный 2 2 6 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 2" xfId="389" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 3" xfId="391" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 4" xfId="393" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 5" xfId="100" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="Обычный 2 2 6 3" xfId="106" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="Обычный 2 2 6 4" xfId="110" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="Обычный 2 2 6 5" xfId="396" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="Обычный 2 2 6 6" xfId="400" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="Обычный 2 2 7" xfId="255" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="Обычный 2 2 7 2" xfId="465" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 2" xfId="468" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 3" xfId="285" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 4" xfId="473" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 5" xfId="141" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="Обычный 2 2 7 3" xfId="474" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="Обычный 2 2 7 4" xfId="280" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="Обычный 2 2 7 5" xfId="476" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="Обычный 2 2 7 6" xfId="478" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="Обычный 2 2 8" xfId="257" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="Обычный 2 2 8 2" xfId="479" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 2" xfId="482" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 3" xfId="485" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 4" xfId="488" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 5" xfId="491" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="Обычный 2 2 8 3" xfId="466" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="Обычный 2 2 8 4" xfId="283" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="Обычный 2 2 8 5" xfId="469" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="Обычный 2 2 8 6" xfId="140" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="Обычный 2 2 9" xfId="492" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="Обычный 2 2 9 2" xfId="493" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="Обычный 2 2 9 3" xfId="79" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="Обычный 2 2 9 4" xfId="288" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="Обычный 2 2 9 5" xfId="496" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="Обычный 2 20" xfId="230" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="Обычный 2 20 2" xfId="318" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="Обычный 2 21" xfId="320" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="Обычный 2 21 2" xfId="323" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="Обычный 2 22" xfId="326" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="Обычный 2 22 2" xfId="330" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="Обычный 2 23" xfId="334" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="Обычный 2 24" xfId="339" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="Обычный 2 25" xfId="500" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="Обычный 2 26" xfId="504" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="Обычный 2 27" xfId="506" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="Обычный 2 28" xfId="508" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="Обычный 2 29" xfId="156" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="Обычный 2 3" xfId="509" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="Обычный 2 3 10" xfId="324" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="Обычный 2 3 10 2" xfId="328" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="Обычный 2 3 11" xfId="332" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="Обычный 2 3 11 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="Обычный 2 3 12" xfId="336" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="Обычный 2 3 12 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="Обычный 2 3 13" xfId="498" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="Обычный 2 3 13 2" xfId="514" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="Обычный 2 3 14" xfId="502" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="Обычный 2 3 14 2" xfId="188" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Обычный 2 3 2" xfId="395" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="Обычный 2 3 2 2" xfId="515" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="Обычный 2 3 2 2 2" xfId="212" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="Обычный 2 3 3" xfId="399" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="Обычный 2 3 3 2" xfId="516" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="Обычный 2 3 4" xfId="262" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="Обычный 2 3 5" xfId="265" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="Обычный 2 3 5 2" xfId="517" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="Обычный 2 3 5 3" xfId="518" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="Обычный 2 3 6" xfId="267" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="Обычный 2 3 6 2" xfId="519" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="Обычный 2 3 7" xfId="269" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="Обычный 2 3 7 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="Обычный 2 3 8" xfId="313" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Обычный 2 3 9" xfId="521" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="Обычный 2 3 9 2" xfId="271" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="Обычный 2 30" xfId="1655" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="Обычный 2 4" xfId="1" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="Обычный 2 4 2" xfId="475" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="Обычный 2 4 2 2" xfId="129" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Обычный 2 4 3" xfId="477" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="Обычный 2 4 4" xfId="522" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="Обычный 2 5" xfId="523" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="Обычный 2 5 2" xfId="472" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="Обычный 2 5 3" xfId="139" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="Обычный 2 5 3 2" xfId="214" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="Обычный 2 5 4" xfId="144" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="Обычный 2 6" xfId="524" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="Обычный 2 6 2" xfId="495" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="Обычный 2 6 3" xfId="525" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="Обычный 2 6 3 2" xfId="526" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="Обычный 2 7" xfId="55" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="Обычный 2 7 2" xfId="73" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="Обычный 2 7 3" xfId="347" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="Обычный 2 8" xfId="527" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="Обычный 2 8 2" xfId="133" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="Обычный 2 9" xfId="528" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="Обычный 2 9 2" xfId="529" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="Обычный 20" xfId="18" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="Обычный 21" xfId="1641" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="Обычный 22" xfId="1650" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="Обычный 23" xfId="1660" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="Обычный 24" xfId="1661" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="Обычный 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="Обычный 3 2" xfId="531" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="Обычный 3 2 2" xfId="532" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="Обычный 3 2 2 2" xfId="484" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="Обычный 3 2 2 3" xfId="487" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
-    <cellStyle name="Обычный 3 2 2 4" xfId="489" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
-    <cellStyle name="Обычный 3 2 2 5" xfId="533" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
-    <cellStyle name="Обычный 3 2 3" xfId="534" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
-    <cellStyle name="Обычный 3 2 4" xfId="535" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
-    <cellStyle name="Обычный 3 2 5" xfId="536" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
-    <cellStyle name="Обычный 3 2 6" xfId="537" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
-    <cellStyle name="Обычный 3 3" xfId="538" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
-    <cellStyle name="Обычный 3 3 2" xfId="539" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
-    <cellStyle name="Обычный 3 4" xfId="540" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
-    <cellStyle name="Обычный 3 4 2" xfId="542" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
-    <cellStyle name="Обычный 3 5" xfId="543" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
-    <cellStyle name="Обычный 3 5 2" xfId="486" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
-    <cellStyle name="Обычный 3 6" xfId="160" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
-    <cellStyle name="Обычный 3 7" xfId="1645" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
-    <cellStyle name="Обычный 3 8" xfId="1656" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
-    <cellStyle name="Обычный 4" xfId="164" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
-    <cellStyle name="Обычный 4 10" xfId="1657" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
-    <cellStyle name="Обычный 4 2" xfId="545" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
-    <cellStyle name="Обычный 4 2 10" xfId="546" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
-    <cellStyle name="Обычный 4 2 2" xfId="548" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
-    <cellStyle name="Обычный 4 2 3" xfId="551" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
-    <cellStyle name="Обычный 4 2 3 2" xfId="115" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2" xfId="553" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 2" xfId="554" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 3" xfId="555" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 4" xfId="541" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 5" xfId="557" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 3" xfId="480" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 4" xfId="467" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 5" xfId="284" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 6" xfId="470" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
-    <cellStyle name="Обычный 4 2 3 3" xfId="117" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 2" xfId="558" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 3" xfId="494" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 4" xfId="80" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 5" xfId="289" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
-    <cellStyle name="Обычный 4 2 3 4" xfId="119" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
-    <cellStyle name="Обычный 4 2 3 5" xfId="559" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
-    <cellStyle name="Обычный 4 2 3 6" xfId="560" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
-    <cellStyle name="Обычный 4 2 3 7" xfId="561" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
-    <cellStyle name="Обычный 4 2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
-    <cellStyle name="Обычный 4 2 4 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 2" xfId="562" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 3" xfId="563" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 4" xfId="481" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 5" xfId="483" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
-    <cellStyle name="Обычный 4 2 4 3" xfId="126" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
-    <cellStyle name="Обычный 4 2 4 4" xfId="564" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
-    <cellStyle name="Обычный 4 2 4 5" xfId="565" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
-    <cellStyle name="Обычный 4 2 4 6" xfId="566" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
-    <cellStyle name="Обычный 4 2 5" xfId="195" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
-    <cellStyle name="Обычный 4 2 5 2" xfId="568" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 2" xfId="430" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 3" xfId="433" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 4" xfId="436" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 5" xfId="570" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
-    <cellStyle name="Обычный 4 2 5 3" xfId="26" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
-    <cellStyle name="Обычный 4 2 5 4" xfId="572" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
-    <cellStyle name="Обычный 4 2 5 5" xfId="574" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
-    <cellStyle name="Обычный 4 2 5 6" xfId="576" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
-    <cellStyle name="Обычный 4 2 6" xfId="198" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
-    <cellStyle name="Обычный 4 2 6 2" xfId="578" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
-    <cellStyle name="Обычный 4 2 6 3" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
-    <cellStyle name="Обычный 4 2 6 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
-    <cellStyle name="Обычный 4 2 6 5" xfId="424" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
-    <cellStyle name="Обычный 4 2 7" xfId="200" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
-    <cellStyle name="Обычный 4 2 8" xfId="368" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
-    <cellStyle name="Обычный 4 2 9" xfId="370" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
-    <cellStyle name="Обычный 4 3" xfId="580" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
-    <cellStyle name="Обычный 4 3 2" xfId="350" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
-    <cellStyle name="Обычный 4 3 2 2" xfId="355" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2" xfId="581" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 2" xfId="331" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 3" xfId="335" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 4" xfId="497" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 5" xfId="501" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 3" xfId="304" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 4" xfId="582" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 5" xfId="549" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 6" xfId="552" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
-    <cellStyle name="Обычный 4 3 2 3" xfId="358" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 2" xfId="411" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 3" xfId="307" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 4" xfId="413" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 5" xfId="351" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
-    <cellStyle name="Обычный 4 3 2 4" xfId="361" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
-    <cellStyle name="Обычный 4 3 2 5" xfId="316" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
-    <cellStyle name="Обычный 4 3 2 6" xfId="583" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
-    <cellStyle name="Обычный 4 3 2 7" xfId="32" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
-    <cellStyle name="Обычный 4 3 3" xfId="91" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
-    <cellStyle name="Обычный 4 3 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 3" xfId="65" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 4" xfId="58" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 5" xfId="45" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
-    <cellStyle name="Обычный 4 3 3 3" xfId="148" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
-    <cellStyle name="Обычный 4 3 3 4" xfId="584" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
-    <cellStyle name="Обычный 4 3 3 5" xfId="321" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
-    <cellStyle name="Обычный 4 3 3 6" xfId="585" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
-    <cellStyle name="Обычный 4 3 4" xfId="587" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
-    <cellStyle name="Обычный 4 3 4 2" xfId="588" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
-    <cellStyle name="Обычный 4 3 4 3" xfId="589" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
-    <cellStyle name="Обычный 4 3 4 4" xfId="590" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
-    <cellStyle name="Обычный 4 3 4 5" xfId="327" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
-    <cellStyle name="Обычный 4 3 5" xfId="592" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
-    <cellStyle name="Обычный 4 3 6" xfId="594" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
-    <cellStyle name="Обычный 4 3 7" xfId="595" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
-    <cellStyle name="Обычный 4 3 8" xfId="375" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
-    <cellStyle name="Обычный 4 4" xfId="29" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
-    <cellStyle name="Обычный 4 5" xfId="597" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
-    <cellStyle name="Обычный 4 6" xfId="599" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
-    <cellStyle name="Обычный 4 7" xfId="511" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
-    <cellStyle name="Обычный 4 8" xfId="600" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
-    <cellStyle name="Обычный 4 9" xfId="1646" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
-    <cellStyle name="Обычный 4_Капекс_НВ_ 12.09.11" xfId="344" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
-    <cellStyle name="Обычный 5" xfId="530" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
-    <cellStyle name="Обычный 5 2" xfId="602" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
-    <cellStyle name="Обычный 5 2 10" xfId="603" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
-    <cellStyle name="Обычный 5 2 2" xfId="44" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
-    <cellStyle name="Обычный 5 2 2 2" xfId="606" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2" xfId="607" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2" xfId="608" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 2" xfId="101" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 3" xfId="609" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 4" xfId="610" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 5" xfId="611" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 3" xfId="612" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 4" xfId="613" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 5" xfId="614" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 6" xfId="615" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3" xfId="616" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 2" xfId="617" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 3" xfId="618" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 4" xfId="155" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 5" xfId="159" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 4" xfId="619" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 5" xfId="620" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 6" xfId="621" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 7" xfId="622" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
-    <cellStyle name="Обычный 5 2 2 3" xfId="625" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2" xfId="627" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 2" xfId="628" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 3" xfId="629" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 4" xfId="630" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 5" xfId="631" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 3" xfId="633" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 4" xfId="635" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 5" xfId="637" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 6" xfId="639" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
-    <cellStyle name="Обычный 5 2 2 4" xfId="642" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
-    <cellStyle name="Обычный 5 2 2 4 2" xfId="643" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
-    <cellStyle name="Обычный 5 2 2 4 3" xfId="644" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
-    <cellStyle name="Обычный 5 2 2 4 4" xfId="646" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
-    <cellStyle name="Обычный 5 2 2 4 5" xfId="648" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
-    <cellStyle name="Обычный 5 2 2 5" xfId="650" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
-    <cellStyle name="Обычный 5 2 2 6" xfId="652" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
-    <cellStyle name="Обычный 5 2 2 7" xfId="653" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
-    <cellStyle name="Обычный 5 2 2 8" xfId="654" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
-    <cellStyle name="Обычный 5 2 3" xfId="656" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
-    <cellStyle name="Обычный 5 2 3 2" xfId="658" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2" xfId="659" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 2" xfId="660" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 3" xfId="661" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 4" xfId="662" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 5" xfId="663" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 3" xfId="664" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 4" xfId="665" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 5" xfId="666" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 6" xfId="667" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
-    <cellStyle name="Обычный 5 2 3 3" xfId="669" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 2" xfId="670" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 3" xfId="671" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 4" xfId="672" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 5" xfId="673" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
-    <cellStyle name="Обычный 5 2 3 4" xfId="675" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
-    <cellStyle name="Обычный 5 2 3 5" xfId="677" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
-    <cellStyle name="Обычный 5 2 3 6" xfId="678" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
-    <cellStyle name="Обычный 5 2 3 7" xfId="679" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
-    <cellStyle name="Обычный 5 2 4" xfId="681" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="Обычный 5 2 4 2" xfId="683" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 2" xfId="684" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 3" xfId="685" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 4" xfId="686" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 5" xfId="687" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Обычный 5 2 4 3" xfId="689" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Обычный 5 2 4 4" xfId="691" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Обычный 5 2 4 5" xfId="692" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Обычный 5 2 4 6" xfId="694" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Обычный 5 2 5" xfId="696" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Обычный 5 2 5 2" xfId="697" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 4" xfId="700" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 5" xfId="701" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Обычный 5 2 5 3" xfId="702" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Обычный 5 2 5 4" xfId="703" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Обычный 5 2 5 5" xfId="704" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Обычный 5 2 5 6" xfId="705" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Обычный 5 2 6" xfId="706" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Обычный 5 2 6 2" xfId="707" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Обычный 5 2 6 3" xfId="708" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Обычный 5 2 6 4" xfId="709" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Обычный 5 2 6 5" xfId="710" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Обычный 5 2 7" xfId="711" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Обычный 5 2 8" xfId="712" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Обычный 5 2 9" xfId="713" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Обычный 5 3" xfId="715" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Обычный 5 3 2" xfId="716" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Обычный 5 4" xfId="718" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="Обычный 5 4 2" xfId="719" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="Обычный 5 5" xfId="721" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="Обычный 5 5 2" xfId="722" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Обычный 5 6" xfId="725" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Обычный 5 6 2" xfId="726" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="Обычный 5 7" xfId="728" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="Обычный 5 7 2" xfId="729" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="Обычный 6 10" xfId="731" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Обычный 6 11" xfId="732" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Обычный 6 12" xfId="730" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="Обычный 6 2" xfId="735" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Обычный 6 2 2" xfId="737" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="Обычный 6 2 2 2" xfId="739" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2" xfId="740" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 3" xfId="742" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 4" xfId="743" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 5" xfId="744" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 3" xfId="746" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 4" xfId="747" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 5" xfId="748" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 6" xfId="749" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Обычный 6 2 2 3" xfId="751" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 2" xfId="752" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 3" xfId="754" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 4" xfId="755" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 5" xfId="756" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Обычный 6 2 2 4" xfId="757" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Обычный 6 2 2 5" xfId="758" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Обычный 6 2 2 6" xfId="759" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Обычный 6 2 2 7" xfId="760" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Обычный 6 2 3" xfId="762" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Обычный 6 2 3 2" xfId="764" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 2" xfId="765" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 3" xfId="766" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 4" xfId="767" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 5" xfId="768" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Обычный 6 2 3 3" xfId="769" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="Обычный 6 2 3 4" xfId="770" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="Обычный 6 2 3 5" xfId="771" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Обычный 6 2 3 6" xfId="772" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Обычный 6 2 4" xfId="775" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Обычный 6 2 4 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Обычный 6 2 4 3" xfId="777" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Обычный 6 2 4 4" xfId="778" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="Обычный 6 2 4 5" xfId="779" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="Обычный 6 2 5" xfId="782" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="Обычный 6 2 6" xfId="784" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="Обычный 6 2 7" xfId="786" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="Обычный 6 2 8" xfId="787" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Обычный 6 3" xfId="790" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Обычный 6 3 2" xfId="791" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="Обычный 6 3 2 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 2" xfId="793" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 3" xfId="794" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 4" xfId="795" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 5" xfId="796" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="Обычный 6 3 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="Обычный 6 3 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="Обычный 6 3 2 5" xfId="799" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Обычный 6 3 2 6" xfId="471" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Обычный 6 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="Обычный 6 3 3 2" xfId="801" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="Обычный 6 3 3 3" xfId="802" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="Обычный 6 3 3 4" xfId="803" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Обычный 6 3 3 5" xfId="804" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Обычный 6 3 4" xfId="805" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="Обычный 6 3 5" xfId="806" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="Обычный 6 3 6" xfId="807" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="Обычный 6 3 7" xfId="808" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="Обычный 6 4" xfId="811" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="Обычный 6 4 2" xfId="812" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="Обычный 6 4 2 2" xfId="813" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="Обычный 6 4 2 3" xfId="814" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="Обычный 6 4 2 4" xfId="815" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="Обычный 6 4 2 5" xfId="816" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="Обычный 6 4 3" xfId="817" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="Обычный 6 4 4" xfId="818" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
-    <cellStyle name="Обычный 6 4 5" xfId="819" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
-    <cellStyle name="Обычный 6 4 6" xfId="820" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
-    <cellStyle name="Обычный 6 5" xfId="822" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
-    <cellStyle name="Обычный 6 5 2" xfId="825" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
-    <cellStyle name="Обычный 6 5 2 2" xfId="828" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
-    <cellStyle name="Обычный 6 5 2 3" xfId="830" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
-    <cellStyle name="Обычный 6 5 2 4" xfId="832" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
-    <cellStyle name="Обычный 6 5 2 5" xfId="834" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
-    <cellStyle name="Обычный 6 5 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
-    <cellStyle name="Обычный 6 5 4" xfId="837" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
-    <cellStyle name="Обычный 6 5 5" xfId="840" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
-    <cellStyle name="Обычный 6 5 6" xfId="843" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
-    <cellStyle name="Обычный 6 6" xfId="845" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
-    <cellStyle name="Обычный 6 6 2" xfId="846" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
-    <cellStyle name="Обычный 6 6 2 2" xfId="847" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
-    <cellStyle name="Обычный 6 6 2 3" xfId="848" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
-    <cellStyle name="Обычный 6 6 2 4" xfId="849" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
-    <cellStyle name="Обычный 6 6 2 5" xfId="850" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
-    <cellStyle name="Обычный 6 6 3" xfId="851" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
-    <cellStyle name="Обычный 6 6 4" xfId="852" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
-    <cellStyle name="Обычный 6 6 5" xfId="853" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
-    <cellStyle name="Обычный 6 6 6" xfId="854" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
-    <cellStyle name="Обычный 6 7" xfId="855" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
-    <cellStyle name="Обычный 6 7 2" xfId="856" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
-    <cellStyle name="Обычный 6 7 3" xfId="857" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
-    <cellStyle name="Обычный 6 7 4" xfId="858" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
-    <cellStyle name="Обычный 6 7 5" xfId="859" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
-    <cellStyle name="Обычный 6 8" xfId="860" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
-    <cellStyle name="Обычный 6 9" xfId="861" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
-    <cellStyle name="Обычный 7" xfId="862" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
-    <cellStyle name="Обычный 7 10" xfId="863" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
-    <cellStyle name="Обычный 7 11" xfId="864" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
-    <cellStyle name="Обычный 7 2" xfId="866" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
-    <cellStyle name="Обычный 7 2 2" xfId="868" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
-    <cellStyle name="Обычный 7 2 2 2" xfId="869" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2" xfId="870" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 2" xfId="873" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 3" xfId="876" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 4" xfId="878" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 5" xfId="879" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 3" xfId="880" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 4" xfId="881" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 5" xfId="882" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 6" xfId="883" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
-    <cellStyle name="Обычный 7 2 2 3" xfId="885" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 2" xfId="887" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 3" xfId="889" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 4" xfId="891" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 5" xfId="893" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
-    <cellStyle name="Обычный 7 2 2 4" xfId="895" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
-    <cellStyle name="Обычный 7 2 2 5" xfId="734" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
-    <cellStyle name="Обычный 7 2 2 6" xfId="789" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
-    <cellStyle name="Обычный 7 2 2 7" xfId="810" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
-    <cellStyle name="Обычный 7 2 3" xfId="896" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
-    <cellStyle name="Обычный 7 2 3 2" xfId="898" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 2" xfId="899" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 3" xfId="901" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 4" xfId="903" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 5" xfId="905" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
-    <cellStyle name="Обычный 7 2 3 3" xfId="908" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
-    <cellStyle name="Обычный 7 2 3 4" xfId="910" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
-    <cellStyle name="Обычный 7 2 3 5" xfId="865" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
-    <cellStyle name="Обычный 7 2 3 6" xfId="912" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
-    <cellStyle name="Обычный 7 2 4" xfId="913" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
-    <cellStyle name="Обычный 7 2 4 2" xfId="915" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
-    <cellStyle name="Обычный 7 2 4 3" xfId="918" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
-    <cellStyle name="Обычный 7 2 4 4" xfId="919" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
-    <cellStyle name="Обычный 7 2 4 5" xfId="921" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
-    <cellStyle name="Обычный 7 2 5" xfId="922" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
-    <cellStyle name="Обычный 7 2 6" xfId="923" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
-    <cellStyle name="Обычный 7 2 7" xfId="924" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
-    <cellStyle name="Обычный 7 2 8" xfId="925" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
-    <cellStyle name="Обычный 7 3" xfId="911" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
-    <cellStyle name="Обычный 7 3 2" xfId="926" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
-    <cellStyle name="Обычный 7 3 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 2" xfId="928" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 3" xfId="872" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 4" xfId="875" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 5" xfId="877" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
-    <cellStyle name="Обычный 7 3 2 3" xfId="66" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
-    <cellStyle name="Обычный 7 3 2 4" xfId="59" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
-    <cellStyle name="Обычный 7 3 2 5" xfId="47" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
-    <cellStyle name="Обычный 7 3 2 6" xfId="930" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
-    <cellStyle name="Обычный 7 3 3" xfId="931" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
-    <cellStyle name="Обычный 7 3 3 2" xfId="933" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
-    <cellStyle name="Обычный 7 3 3 3" xfId="935" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
-    <cellStyle name="Обычный 7 3 3 4" xfId="937" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
-    <cellStyle name="Обычный 7 3 3 5" xfId="939" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
-    <cellStyle name="Обычный 7 3 4" xfId="940" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
-    <cellStyle name="Обычный 7 3 5" xfId="941" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
-    <cellStyle name="Обычный 7 3 6" xfId="942" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
-    <cellStyle name="Обычный 7 3 7" xfId="943" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
-    <cellStyle name="Обычный 7 4" xfId="944" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
-    <cellStyle name="Обычный 7 4 2" xfId="945" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
-    <cellStyle name="Обычный 7 4 2 2" xfId="946" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
-    <cellStyle name="Обычный 7 4 2 3" xfId="947" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
-    <cellStyle name="Обычный 7 4 2 4" xfId="948" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
-    <cellStyle name="Обычный 7 4 2 5" xfId="949" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
-    <cellStyle name="Обычный 7 4 3" xfId="950" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
-    <cellStyle name="Обычный 7 4 4" xfId="951" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
-    <cellStyle name="Обычный 7 4 5" xfId="952" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
-    <cellStyle name="Обычный 7 4 6" xfId="953" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
-    <cellStyle name="Обычный 7 5" xfId="954" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
-    <cellStyle name="Обычный 7 5 2" xfId="955" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
-    <cellStyle name="Обычный 7 5 2 2" xfId="956" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
-    <cellStyle name="Обычный 7 5 2 3" xfId="957" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
-    <cellStyle name="Обычный 7 5 2 4" xfId="958" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
-    <cellStyle name="Обычный 7 5 2 5" xfId="959" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
-    <cellStyle name="Обычный 7 5 3" xfId="960" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
-    <cellStyle name="Обычный 7 5 4" xfId="961" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
-    <cellStyle name="Обычный 7 5 5" xfId="962" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
-    <cellStyle name="Обычный 7 5 6" xfId="963" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
-    <cellStyle name="Обычный 7 6" xfId="964" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
-    <cellStyle name="Обычный 7 6 2" xfId="965" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
-    <cellStyle name="Обычный 7 6 2 2" xfId="966" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
-    <cellStyle name="Обычный 7 6 2 3" xfId="968" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
-    <cellStyle name="Обычный 7 6 2 4" xfId="970" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
-    <cellStyle name="Обычный 7 6 2 5" xfId="971" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
-    <cellStyle name="Обычный 7 6 3" xfId="972" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
-    <cellStyle name="Обычный 7 6 4" xfId="973" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
-    <cellStyle name="Обычный 7 6 5" xfId="974" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
-    <cellStyle name="Обычный 7 6 6" xfId="343" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
-    <cellStyle name="Обычный 7 7" xfId="975" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
-    <cellStyle name="Обычный 7 7 2" xfId="976" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
-    <cellStyle name="Обычный 7 7 3" xfId="977" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
-    <cellStyle name="Обычный 7 7 4" xfId="978" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
-    <cellStyle name="Обычный 7 7 5" xfId="979" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
-    <cellStyle name="Обычный 7 8" xfId="980" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
-    <cellStyle name="Обычный 7 9" xfId="192" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
-    <cellStyle name="Обычный 8" xfId="981" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
-    <cellStyle name="Обычный 8 2" xfId="920" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
-    <cellStyle name="Обычный 9" xfId="982" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
-    <cellStyle name="Обычный 9 2" xfId="984" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
+    <cellStyle name="Обычный 10" xfId="279"/>
+    <cellStyle name="Обычный 10 2" xfId="281"/>
+    <cellStyle name="Обычный 11" xfId="282"/>
+    <cellStyle name="Обычный 11 2" xfId="286"/>
+    <cellStyle name="Обычный 12" xfId="287"/>
+    <cellStyle name="Обычный 12 2" xfId="291"/>
+    <cellStyle name="Обычный 13" xfId="293"/>
+    <cellStyle name="Обычный 13 2" xfId="69"/>
+    <cellStyle name="Обычный 14" xfId="295"/>
+    <cellStyle name="Обычный 14 2" xfId="131"/>
+    <cellStyle name="Обычный 15" xfId="298"/>
+    <cellStyle name="Обычный 15 2" xfId="165"/>
+    <cellStyle name="Обычный 16" xfId="301"/>
+    <cellStyle name="Обычный 16 2" xfId="302"/>
+    <cellStyle name="Обычный 17" xfId="303"/>
+    <cellStyle name="Обычный 17 2" xfId="305"/>
+    <cellStyle name="Обычный 18" xfId="306"/>
+    <cellStyle name="Обычный 18 2" xfId="309"/>
+    <cellStyle name="Обычный 19" xfId="19"/>
+    <cellStyle name="Обычный 2" xfId="4"/>
+    <cellStyle name="Обычный 2 10" xfId="310"/>
+    <cellStyle name="Обычный 2 10 2" xfId="182"/>
+    <cellStyle name="Обычный 2 11" xfId="311"/>
+    <cellStyle name="Обычный 2 12" xfId="37"/>
+    <cellStyle name="Обычный 2 12 2" xfId="234"/>
+    <cellStyle name="Обычный 2 12 3" xfId="312"/>
+    <cellStyle name="Обычный 2 13" xfId="225"/>
+    <cellStyle name="Обычный 2 13 2" xfId="258"/>
+    <cellStyle name="Обычный 2 14" xfId="227"/>
+    <cellStyle name="Обычный 2 14 2" xfId="314"/>
+    <cellStyle name="Обычный 2 15" xfId="229"/>
+    <cellStyle name="Обычный 2 15 2" xfId="317"/>
+    <cellStyle name="Обычный 2 16" xfId="319"/>
+    <cellStyle name="Обычный 2 16 2" xfId="322"/>
+    <cellStyle name="Обычный 2 17" xfId="325"/>
+    <cellStyle name="Обычный 2 17 2" xfId="329"/>
+    <cellStyle name="Обычный 2 18" xfId="333"/>
+    <cellStyle name="Обычный 2 18 2" xfId="57"/>
+    <cellStyle name="Обычный 2 19" xfId="338"/>
+    <cellStyle name="Обычный 2 19 2" xfId="342"/>
+    <cellStyle name="Обычный 2 19 3" xfId="346"/>
+    <cellStyle name="Обычный 2 2" xfId="348"/>
+    <cellStyle name="Обычный 2 2 10" xfId="353"/>
+    <cellStyle name="Обычный 2 2 10 2" xfId="356"/>
+    <cellStyle name="Обычный 2 2 10 3" xfId="359"/>
+    <cellStyle name="Обычный 2 2 10 4" xfId="362"/>
+    <cellStyle name="Обычный 2 2 11" xfId="93"/>
+    <cellStyle name="Обычный 2 2 2" xfId="365"/>
+    <cellStyle name="Обычный 2 2 2 2" xfId="366"/>
+    <cellStyle name="Обычный 2 2 2 2 2" xfId="367"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2" xfId="71"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2" xfId="369"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 2" xfId="292"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 3" xfId="294"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 4" xfId="297"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 5" xfId="300"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 3" xfId="371"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 4" xfId="372"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 5" xfId="373"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 6" xfId="374"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3" xfId="75"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 2" xfId="376"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 3" xfId="191"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 4" xfId="202"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 5" xfId="204"/>
+    <cellStyle name="Обычный 2 2 2 2 2 4" xfId="377"/>
+    <cellStyle name="Обычный 2 2 2 2 2 5" xfId="378"/>
+    <cellStyle name="Обычный 2 2 2 2 2 6" xfId="379"/>
+    <cellStyle name="Обычный 2 2 2 2 2 7" xfId="380"/>
+    <cellStyle name="Обычный 2 2 2 2 3" xfId="82"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2" xfId="42"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 2" xfId="381"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 3" xfId="382"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 4" xfId="383"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 5" xfId="384"/>
+    <cellStyle name="Обычный 2 2 2 2 3 3" xfId="385"/>
+    <cellStyle name="Обычный 2 2 2 2 3 4" xfId="386"/>
+    <cellStyle name="Обычный 2 2 2 2 3 5" xfId="387"/>
+    <cellStyle name="Обычный 2 2 2 2 3 6" xfId="388"/>
+    <cellStyle name="Обычный 2 2 2 2 4" xfId="87"/>
+    <cellStyle name="Обычный 2 2 2 2 4 2" xfId="390"/>
+    <cellStyle name="Обычный 2 2 2 2 4 3" xfId="392"/>
+    <cellStyle name="Обычный 2 2 2 2 4 4" xfId="394"/>
+    <cellStyle name="Обычный 2 2 2 2 4 5" xfId="102"/>
+    <cellStyle name="Обычный 2 2 2 2 5" xfId="107"/>
+    <cellStyle name="Обычный 2 2 2 2 6" xfId="111"/>
+    <cellStyle name="Обычный 2 2 2 2 7" xfId="398"/>
+    <cellStyle name="Обычный 2 2 2 2 8" xfId="402"/>
+    <cellStyle name="Обычный 2 2 2 3" xfId="403"/>
+    <cellStyle name="Обычный 2 2 2 3 2" xfId="404"/>
+    <cellStyle name="Обычный 2 2 3" xfId="407"/>
+    <cellStyle name="Обычный 2 2 3 2" xfId="408"/>
+    <cellStyle name="Обычный 2 2 4" xfId="241"/>
+    <cellStyle name="Обычный 2 2 4 2" xfId="243"/>
+    <cellStyle name="Обычный 2 2 4 2 2" xfId="409"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2" xfId="135"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 2" xfId="137"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 3" xfId="150"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 4" xfId="154"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 5" xfId="162"/>
+    <cellStyle name="Обычный 2 2 4 2 2 3" xfId="167"/>
+    <cellStyle name="Обычный 2 2 4 2 2 4" xfId="179"/>
+    <cellStyle name="Обычный 2 2 4 2 2 5" xfId="181"/>
+    <cellStyle name="Обычный 2 2 4 2 2 6" xfId="184"/>
+    <cellStyle name="Обычный 2 2 4 2 3" xfId="410"/>
+    <cellStyle name="Обычный 2 2 4 2 3 2" xfId="208"/>
+    <cellStyle name="Обычный 2 2 4 2 3 3" xfId="216"/>
+    <cellStyle name="Обычный 2 2 4 2 3 4" xfId="51"/>
+    <cellStyle name="Обычный 2 2 4 2 3 5" xfId="218"/>
+    <cellStyle name="Обычный 2 2 4 2 4" xfId="412"/>
+    <cellStyle name="Обычный 2 2 4 2 5" xfId="308"/>
+    <cellStyle name="Обычный 2 2 4 2 6" xfId="414"/>
+    <cellStyle name="Обычный 2 2 4 2 7" xfId="352"/>
+    <cellStyle name="Обычный 2 2 4 3" xfId="245"/>
+    <cellStyle name="Обычный 2 2 4 3 2" xfId="415"/>
+    <cellStyle name="Обычный 2 2 4 3 2 2" xfId="417"/>
+    <cellStyle name="Обычный 2 2 4 3 2 3" xfId="420"/>
+    <cellStyle name="Обычный 2 2 4 3 2 4" xfId="423"/>
+    <cellStyle name="Обычный 2 2 4 3 2 5" xfId="425"/>
+    <cellStyle name="Обычный 2 2 4 3 3" xfId="426"/>
+    <cellStyle name="Обычный 2 2 4 3 4" xfId="427"/>
+    <cellStyle name="Обычный 2 2 4 3 5" xfId="60"/>
+    <cellStyle name="Обычный 2 2 4 3 6" xfId="49"/>
+    <cellStyle name="Обычный 2 2 4 4" xfId="247"/>
+    <cellStyle name="Обычный 2 2 4 4 2" xfId="27"/>
+    <cellStyle name="Обычный 2 2 4 4 3" xfId="431"/>
+    <cellStyle name="Обычный 2 2 4 4 4" xfId="434"/>
+    <cellStyle name="Обычный 2 2 4 4 5" xfId="437"/>
+    <cellStyle name="Обычный 2 2 4 5" xfId="249"/>
+    <cellStyle name="Обычный 2 2 4 6" xfId="438"/>
+    <cellStyle name="Обычный 2 2 4 7" xfId="223"/>
+    <cellStyle name="Обычный 2 2 4 8" xfId="53"/>
+    <cellStyle name="Обычный 2 2 5" xfId="251"/>
+    <cellStyle name="Обычный 2 2 5 2" xfId="440"/>
+    <cellStyle name="Обычный 2 2 5 2 2" xfId="442"/>
+    <cellStyle name="Обычный 2 2 5 2 2 2" xfId="444"/>
+    <cellStyle name="Обычный 2 2 5 2 2 3" xfId="446"/>
+    <cellStyle name="Обычный 2 2 5 2 2 4" xfId="170"/>
+    <cellStyle name="Обычный 2 2 5 2 2 5" xfId="174"/>
+    <cellStyle name="Обычный 2 2 5 2 3" xfId="448"/>
+    <cellStyle name="Обычный 2 2 5 2 4" xfId="450"/>
+    <cellStyle name="Обычный 2 2 5 2 5" xfId="452"/>
+    <cellStyle name="Обычный 2 2 5 2 6" xfId="454"/>
+    <cellStyle name="Обычный 2 2 5 3" xfId="456"/>
+    <cellStyle name="Обычный 2 2 5 3 2" xfId="458"/>
+    <cellStyle name="Обычный 2 2 5 3 3" xfId="460"/>
+    <cellStyle name="Обычный 2 2 5 3 4" xfId="461"/>
+    <cellStyle name="Обычный 2 2 5 3 5" xfId="462"/>
+    <cellStyle name="Обычный 2 2 5 4" xfId="464"/>
+    <cellStyle name="Обычный 2 2 5 5" xfId="364"/>
+    <cellStyle name="Обычный 2 2 5 6" xfId="406"/>
+    <cellStyle name="Обычный 2 2 5 7" xfId="240"/>
+    <cellStyle name="Обычный 2 2 6" xfId="253"/>
+    <cellStyle name="Обычный 2 2 6 2" xfId="86"/>
+    <cellStyle name="Обычный 2 2 6 2 2" xfId="389"/>
+    <cellStyle name="Обычный 2 2 6 2 3" xfId="391"/>
+    <cellStyle name="Обычный 2 2 6 2 4" xfId="393"/>
+    <cellStyle name="Обычный 2 2 6 2 5" xfId="100"/>
+    <cellStyle name="Обычный 2 2 6 3" xfId="106"/>
+    <cellStyle name="Обычный 2 2 6 4" xfId="110"/>
+    <cellStyle name="Обычный 2 2 6 5" xfId="396"/>
+    <cellStyle name="Обычный 2 2 6 6" xfId="400"/>
+    <cellStyle name="Обычный 2 2 7" xfId="255"/>
+    <cellStyle name="Обычный 2 2 7 2" xfId="465"/>
+    <cellStyle name="Обычный 2 2 7 2 2" xfId="468"/>
+    <cellStyle name="Обычный 2 2 7 2 3" xfId="285"/>
+    <cellStyle name="Обычный 2 2 7 2 4" xfId="473"/>
+    <cellStyle name="Обычный 2 2 7 2 5" xfId="141"/>
+    <cellStyle name="Обычный 2 2 7 3" xfId="474"/>
+    <cellStyle name="Обычный 2 2 7 4" xfId="280"/>
+    <cellStyle name="Обычный 2 2 7 5" xfId="476"/>
+    <cellStyle name="Обычный 2 2 7 6" xfId="478"/>
+    <cellStyle name="Обычный 2 2 8" xfId="257"/>
+    <cellStyle name="Обычный 2 2 8 2" xfId="479"/>
+    <cellStyle name="Обычный 2 2 8 2 2" xfId="482"/>
+    <cellStyle name="Обычный 2 2 8 2 3" xfId="485"/>
+    <cellStyle name="Обычный 2 2 8 2 4" xfId="488"/>
+    <cellStyle name="Обычный 2 2 8 2 5" xfId="491"/>
+    <cellStyle name="Обычный 2 2 8 3" xfId="466"/>
+    <cellStyle name="Обычный 2 2 8 4" xfId="283"/>
+    <cellStyle name="Обычный 2 2 8 5" xfId="469"/>
+    <cellStyle name="Обычный 2 2 8 6" xfId="140"/>
+    <cellStyle name="Обычный 2 2 9" xfId="492"/>
+    <cellStyle name="Обычный 2 2 9 2" xfId="493"/>
+    <cellStyle name="Обычный 2 2 9 3" xfId="79"/>
+    <cellStyle name="Обычный 2 2 9 4" xfId="288"/>
+    <cellStyle name="Обычный 2 2 9 5" xfId="496"/>
+    <cellStyle name="Обычный 2 20" xfId="230"/>
+    <cellStyle name="Обычный 2 20 2" xfId="318"/>
+    <cellStyle name="Обычный 2 21" xfId="320"/>
+    <cellStyle name="Обычный 2 21 2" xfId="323"/>
+    <cellStyle name="Обычный 2 22" xfId="326"/>
+    <cellStyle name="Обычный 2 22 2" xfId="330"/>
+    <cellStyle name="Обычный 2 23" xfId="334"/>
+    <cellStyle name="Обычный 2 24" xfId="339"/>
+    <cellStyle name="Обычный 2 25" xfId="500"/>
+    <cellStyle name="Обычный 2 26" xfId="504"/>
+    <cellStyle name="Обычный 2 27" xfId="506"/>
+    <cellStyle name="Обычный 2 28" xfId="508"/>
+    <cellStyle name="Обычный 2 29" xfId="156"/>
+    <cellStyle name="Обычный 2 3" xfId="509"/>
+    <cellStyle name="Обычный 2 3 10" xfId="324"/>
+    <cellStyle name="Обычный 2 3 10 2" xfId="328"/>
+    <cellStyle name="Обычный 2 3 11" xfId="332"/>
+    <cellStyle name="Обычный 2 3 11 2" xfId="56"/>
+    <cellStyle name="Обычный 2 3 12" xfId="336"/>
+    <cellStyle name="Обычный 2 3 12 2" xfId="340"/>
+    <cellStyle name="Обычный 2 3 13" xfId="498"/>
+    <cellStyle name="Обычный 2 3 13 2" xfId="514"/>
+    <cellStyle name="Обычный 2 3 14" xfId="502"/>
+    <cellStyle name="Обычный 2 3 14 2" xfId="188"/>
+    <cellStyle name="Обычный 2 3 2" xfId="395"/>
+    <cellStyle name="Обычный 2 3 2 2" xfId="515"/>
+    <cellStyle name="Обычный 2 3 2 2 2" xfId="212"/>
+    <cellStyle name="Обычный 2 3 3" xfId="399"/>
+    <cellStyle name="Обычный 2 3 3 2" xfId="516"/>
+    <cellStyle name="Обычный 2 3 4" xfId="262"/>
+    <cellStyle name="Обычный 2 3 5" xfId="265"/>
+    <cellStyle name="Обычный 2 3 5 2" xfId="517"/>
+    <cellStyle name="Обычный 2 3 5 3" xfId="518"/>
+    <cellStyle name="Обычный 2 3 6" xfId="267"/>
+    <cellStyle name="Обычный 2 3 6 2" xfId="519"/>
+    <cellStyle name="Обычный 2 3 7" xfId="269"/>
+    <cellStyle name="Обычный 2 3 7 2" xfId="520"/>
+    <cellStyle name="Обычный 2 3 8" xfId="313"/>
+    <cellStyle name="Обычный 2 3 9" xfId="521"/>
+    <cellStyle name="Обычный 2 3 9 2" xfId="271"/>
+    <cellStyle name="Обычный 2 30" xfId="1655"/>
+    <cellStyle name="Обычный 2 4" xfId="1"/>
+    <cellStyle name="Обычный 2 4 2" xfId="475"/>
+    <cellStyle name="Обычный 2 4 2 2" xfId="129"/>
+    <cellStyle name="Обычный 2 4 3" xfId="477"/>
+    <cellStyle name="Обычный 2 4 4" xfId="522"/>
+    <cellStyle name="Обычный 2 5" xfId="523"/>
+    <cellStyle name="Обычный 2 5 2" xfId="472"/>
+    <cellStyle name="Обычный 2 5 3" xfId="139"/>
+    <cellStyle name="Обычный 2 5 3 2" xfId="214"/>
+    <cellStyle name="Обычный 2 5 4" xfId="144"/>
+    <cellStyle name="Обычный 2 6" xfId="524"/>
+    <cellStyle name="Обычный 2 6 2" xfId="495"/>
+    <cellStyle name="Обычный 2 6 3" xfId="525"/>
+    <cellStyle name="Обычный 2 6 3 2" xfId="526"/>
+    <cellStyle name="Обычный 2 7" xfId="55"/>
+    <cellStyle name="Обычный 2 7 2" xfId="73"/>
+    <cellStyle name="Обычный 2 7 3" xfId="347"/>
+    <cellStyle name="Обычный 2 8" xfId="527"/>
+    <cellStyle name="Обычный 2 8 2" xfId="133"/>
+    <cellStyle name="Обычный 2 9" xfId="528"/>
+    <cellStyle name="Обычный 2 9 2" xfId="529"/>
+    <cellStyle name="Обычный 20" xfId="18"/>
+    <cellStyle name="Обычный 21" xfId="1641"/>
+    <cellStyle name="Обычный 22" xfId="1650"/>
+    <cellStyle name="Обычный 23" xfId="1660"/>
+    <cellStyle name="Обычный 24" xfId="1661"/>
+    <cellStyle name="Обычный 3" xfId="17"/>
+    <cellStyle name="Обычный 3 2" xfId="531"/>
+    <cellStyle name="Обычный 3 2 2" xfId="532"/>
+    <cellStyle name="Обычный 3 2 2 2" xfId="484"/>
+    <cellStyle name="Обычный 3 2 2 3" xfId="487"/>
+    <cellStyle name="Обычный 3 2 2 4" xfId="489"/>
+    <cellStyle name="Обычный 3 2 2 5" xfId="533"/>
+    <cellStyle name="Обычный 3 2 3" xfId="534"/>
+    <cellStyle name="Обычный 3 2 4" xfId="535"/>
+    <cellStyle name="Обычный 3 2 5" xfId="536"/>
+    <cellStyle name="Обычный 3 2 6" xfId="537"/>
+    <cellStyle name="Обычный 3 3" xfId="538"/>
+    <cellStyle name="Обычный 3 3 2" xfId="539"/>
+    <cellStyle name="Обычный 3 4" xfId="540"/>
+    <cellStyle name="Обычный 3 4 2" xfId="542"/>
+    <cellStyle name="Обычный 3 5" xfId="543"/>
+    <cellStyle name="Обычный 3 5 2" xfId="486"/>
+    <cellStyle name="Обычный 3 6" xfId="160"/>
+    <cellStyle name="Обычный 3 7" xfId="1645"/>
+    <cellStyle name="Обычный 3 8" xfId="1656"/>
+    <cellStyle name="Обычный 4" xfId="164"/>
+    <cellStyle name="Обычный 4 10" xfId="1657"/>
+    <cellStyle name="Обычный 4 2" xfId="545"/>
+    <cellStyle name="Обычный 4 2 10" xfId="546"/>
+    <cellStyle name="Обычный 4 2 2" xfId="548"/>
+    <cellStyle name="Обычный 4 2 3" xfId="551"/>
+    <cellStyle name="Обычный 4 2 3 2" xfId="115"/>
+    <cellStyle name="Обычный 4 2 3 2 2" xfId="553"/>
+    <cellStyle name="Обычный 4 2 3 2 2 2" xfId="554"/>
+    <cellStyle name="Обычный 4 2 3 2 2 3" xfId="555"/>
+    <cellStyle name="Обычный 4 2 3 2 2 4" xfId="541"/>
+    <cellStyle name="Обычный 4 2 3 2 2 5" xfId="557"/>
+    <cellStyle name="Обычный 4 2 3 2 3" xfId="480"/>
+    <cellStyle name="Обычный 4 2 3 2 4" xfId="467"/>
+    <cellStyle name="Обычный 4 2 3 2 5" xfId="284"/>
+    <cellStyle name="Обычный 4 2 3 2 6" xfId="470"/>
+    <cellStyle name="Обычный 4 2 3 3" xfId="117"/>
+    <cellStyle name="Обычный 4 2 3 3 2" xfId="558"/>
+    <cellStyle name="Обычный 4 2 3 3 3" xfId="494"/>
+    <cellStyle name="Обычный 4 2 3 3 4" xfId="80"/>
+    <cellStyle name="Обычный 4 2 3 3 5" xfId="289"/>
+    <cellStyle name="Обычный 4 2 3 4" xfId="119"/>
+    <cellStyle name="Обычный 4 2 3 5" xfId="559"/>
+    <cellStyle name="Обычный 4 2 3 6" xfId="560"/>
+    <cellStyle name="Обычный 4 2 3 7" xfId="561"/>
+    <cellStyle name="Обычный 4 2 4" xfId="35"/>
+    <cellStyle name="Обычный 4 2 4 2" xfId="124"/>
+    <cellStyle name="Обычный 4 2 4 2 2" xfId="562"/>
+    <cellStyle name="Обычный 4 2 4 2 3" xfId="563"/>
+    <cellStyle name="Обычный 4 2 4 2 4" xfId="481"/>
+    <cellStyle name="Обычный 4 2 4 2 5" xfId="483"/>
+    <cellStyle name="Обычный 4 2 4 3" xfId="126"/>
+    <cellStyle name="Обычный 4 2 4 4" xfId="564"/>
+    <cellStyle name="Обычный 4 2 4 5" xfId="565"/>
+    <cellStyle name="Обычный 4 2 4 6" xfId="566"/>
+    <cellStyle name="Обычный 4 2 5" xfId="195"/>
+    <cellStyle name="Обычный 4 2 5 2" xfId="568"/>
+    <cellStyle name="Обычный 4 2 5 2 2" xfId="430"/>
+    <cellStyle name="Обычный 4 2 5 2 3" xfId="433"/>
+    <cellStyle name="Обычный 4 2 5 2 4" xfId="436"/>
+    <cellStyle name="Обычный 4 2 5 2 5" xfId="570"/>
+    <cellStyle name="Обычный 4 2 5 3" xfId="26"/>
+    <cellStyle name="Обычный 4 2 5 4" xfId="572"/>
+    <cellStyle name="Обычный 4 2 5 5" xfId="574"/>
+    <cellStyle name="Обычный 4 2 5 6" xfId="576"/>
+    <cellStyle name="Обычный 4 2 6" xfId="198"/>
+    <cellStyle name="Обычный 4 2 6 2" xfId="578"/>
+    <cellStyle name="Обычный 4 2 6 3" xfId="418"/>
+    <cellStyle name="Обычный 4 2 6 4" xfId="421"/>
+    <cellStyle name="Обычный 4 2 6 5" xfId="424"/>
+    <cellStyle name="Обычный 4 2 7" xfId="200"/>
+    <cellStyle name="Обычный 4 2 8" xfId="368"/>
+    <cellStyle name="Обычный 4 2 9" xfId="370"/>
+    <cellStyle name="Обычный 4 3" xfId="580"/>
+    <cellStyle name="Обычный 4 3 2" xfId="350"/>
+    <cellStyle name="Обычный 4 3 2 2" xfId="355"/>
+    <cellStyle name="Обычный 4 3 2 2 2" xfId="581"/>
+    <cellStyle name="Обычный 4 3 2 2 2 2" xfId="331"/>
+    <cellStyle name="Обычный 4 3 2 2 2 3" xfId="335"/>
+    <cellStyle name="Обычный 4 3 2 2 2 4" xfId="497"/>
+    <cellStyle name="Обычный 4 3 2 2 2 5" xfId="501"/>
+    <cellStyle name="Обычный 4 3 2 2 3" xfId="304"/>
+    <cellStyle name="Обычный 4 3 2 2 4" xfId="582"/>
+    <cellStyle name="Обычный 4 3 2 2 5" xfId="549"/>
+    <cellStyle name="Обычный 4 3 2 2 6" xfId="552"/>
+    <cellStyle name="Обычный 4 3 2 3" xfId="358"/>
+    <cellStyle name="Обычный 4 3 2 3 2" xfId="411"/>
+    <cellStyle name="Обычный 4 3 2 3 3" xfId="307"/>
+    <cellStyle name="Обычный 4 3 2 3 4" xfId="413"/>
+    <cellStyle name="Обычный 4 3 2 3 5" xfId="351"/>
+    <cellStyle name="Обычный 4 3 2 4" xfId="361"/>
+    <cellStyle name="Обычный 4 3 2 5" xfId="316"/>
+    <cellStyle name="Обычный 4 3 2 6" xfId="583"/>
+    <cellStyle name="Обычный 4 3 2 7" xfId="32"/>
+    <cellStyle name="Обычный 4 3 3" xfId="91"/>
+    <cellStyle name="Обычный 4 3 3 2" xfId="146"/>
+    <cellStyle name="Обычный 4 3 3 2 2" xfId="21"/>
+    <cellStyle name="Обычный 4 3 3 2 3" xfId="65"/>
+    <cellStyle name="Обычный 4 3 3 2 4" xfId="58"/>
+    <cellStyle name="Обычный 4 3 3 2 5" xfId="45"/>
+    <cellStyle name="Обычный 4 3 3 3" xfId="148"/>
+    <cellStyle name="Обычный 4 3 3 4" xfId="584"/>
+    <cellStyle name="Обычный 4 3 3 5" xfId="321"/>
+    <cellStyle name="Обычный 4 3 3 6" xfId="585"/>
+    <cellStyle name="Обычный 4 3 4" xfId="587"/>
+    <cellStyle name="Обычный 4 3 4 2" xfId="588"/>
+    <cellStyle name="Обычный 4 3 4 3" xfId="589"/>
+    <cellStyle name="Обычный 4 3 4 4" xfId="590"/>
+    <cellStyle name="Обычный 4 3 4 5" xfId="327"/>
+    <cellStyle name="Обычный 4 3 5" xfId="592"/>
+    <cellStyle name="Обычный 4 3 6" xfId="594"/>
+    <cellStyle name="Обычный 4 3 7" xfId="595"/>
+    <cellStyle name="Обычный 4 3 8" xfId="375"/>
+    <cellStyle name="Обычный 4 4" xfId="29"/>
+    <cellStyle name="Обычный 4 5" xfId="597"/>
+    <cellStyle name="Обычный 4 6" xfId="599"/>
+    <cellStyle name="Обычный 4 7" xfId="511"/>
+    <cellStyle name="Обычный 4 8" xfId="600"/>
+    <cellStyle name="Обычный 4 9" xfId="1646"/>
+    <cellStyle name="Обычный 4_Капекс_НВ_ 12.09.11" xfId="344"/>
+    <cellStyle name="Обычный 5" xfId="530"/>
+    <cellStyle name="Обычный 5 2" xfId="602"/>
+    <cellStyle name="Обычный 5 2 10" xfId="603"/>
+    <cellStyle name="Обычный 5 2 2" xfId="44"/>
+    <cellStyle name="Обычный 5 2 2 2" xfId="606"/>
+    <cellStyle name="Обычный 5 2 2 2 2" xfId="607"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2" xfId="608"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 2" xfId="101"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 3" xfId="609"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 4" xfId="610"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 5" xfId="611"/>
+    <cellStyle name="Обычный 5 2 2 2 2 3" xfId="612"/>
+    <cellStyle name="Обычный 5 2 2 2 2 4" xfId="613"/>
+    <cellStyle name="Обычный 5 2 2 2 2 5" xfId="614"/>
+    <cellStyle name="Обычный 5 2 2 2 2 6" xfId="615"/>
+    <cellStyle name="Обычный 5 2 2 2 3" xfId="616"/>
+    <cellStyle name="Обычный 5 2 2 2 3 2" xfId="617"/>
+    <cellStyle name="Обычный 5 2 2 2 3 3" xfId="618"/>
+    <cellStyle name="Обычный 5 2 2 2 3 4" xfId="155"/>
+    <cellStyle name="Обычный 5 2 2 2 3 5" xfId="159"/>
+    <cellStyle name="Обычный 5 2 2 2 4" xfId="619"/>
+    <cellStyle name="Обычный 5 2 2 2 5" xfId="620"/>
+    <cellStyle name="Обычный 5 2 2 2 6" xfId="621"/>
+    <cellStyle name="Обычный 5 2 2 2 7" xfId="622"/>
+    <cellStyle name="Обычный 5 2 2 3" xfId="625"/>
+    <cellStyle name="Обычный 5 2 2 3 2" xfId="627"/>
+    <cellStyle name="Обычный 5 2 2 3 2 2" xfId="628"/>
+    <cellStyle name="Обычный 5 2 2 3 2 3" xfId="629"/>
+    <cellStyle name="Обычный 5 2 2 3 2 4" xfId="630"/>
+    <cellStyle name="Обычный 5 2 2 3 2 5" xfId="631"/>
+    <cellStyle name="Обычный 5 2 2 3 3" xfId="633"/>
+    <cellStyle name="Обычный 5 2 2 3 4" xfId="635"/>
+    <cellStyle name="Обычный 5 2 2 3 5" xfId="637"/>
+    <cellStyle name="Обычный 5 2 2 3 6" xfId="639"/>
+    <cellStyle name="Обычный 5 2 2 4" xfId="642"/>
+    <cellStyle name="Обычный 5 2 2 4 2" xfId="643"/>
+    <cellStyle name="Обычный 5 2 2 4 3" xfId="644"/>
+    <cellStyle name="Обычный 5 2 2 4 4" xfId="646"/>
+    <cellStyle name="Обычный 5 2 2 4 5" xfId="648"/>
+    <cellStyle name="Обычный 5 2 2 5" xfId="650"/>
+    <cellStyle name="Обычный 5 2 2 6" xfId="652"/>
+    <cellStyle name="Обычный 5 2 2 7" xfId="653"/>
+    <cellStyle name="Обычный 5 2 2 8" xfId="654"/>
+    <cellStyle name="Обычный 5 2 3" xfId="656"/>
+    <cellStyle name="Обычный 5 2 3 2" xfId="658"/>
+    <cellStyle name="Обычный 5 2 3 2 2" xfId="659"/>
+    <cellStyle name="Обычный 5 2 3 2 2 2" xfId="660"/>
+    <cellStyle name="Обычный 5 2 3 2 2 3" xfId="661"/>
+    <cellStyle name="Обычный 5 2 3 2 2 4" xfId="662"/>
+    <cellStyle name="Обычный 5 2 3 2 2 5" xfId="663"/>
+    <cellStyle name="Обычный 5 2 3 2 3" xfId="664"/>
+    <cellStyle name="Обычный 5 2 3 2 4" xfId="665"/>
+    <cellStyle name="Обычный 5 2 3 2 5" xfId="666"/>
+    <cellStyle name="Обычный 5 2 3 2 6" xfId="667"/>
+    <cellStyle name="Обычный 5 2 3 3" xfId="669"/>
+    <cellStyle name="Обычный 5 2 3 3 2" xfId="670"/>
+    <cellStyle name="Обычный 5 2 3 3 3" xfId="671"/>
+    <cellStyle name="Обычный 5 2 3 3 4" xfId="672"/>
+    <cellStyle name="Обычный 5 2 3 3 5" xfId="673"/>
+    <cellStyle name="Обычный 5 2 3 4" xfId="675"/>
+    <cellStyle name="Обычный 5 2 3 5" xfId="677"/>
+    <cellStyle name="Обычный 5 2 3 6" xfId="678"/>
+    <cellStyle name="Обычный 5 2 3 7" xfId="679"/>
+    <cellStyle name="Обычный 5 2 4" xfId="681"/>
+    <cellStyle name="Обычный 5 2 4 2" xfId="683"/>
+    <cellStyle name="Обычный 5 2 4 2 2" xfId="684"/>
+    <cellStyle name="Обычный 5 2 4 2 3" xfId="685"/>
+    <cellStyle name="Обычный 5 2 4 2 4" xfId="686"/>
+    <cellStyle name="Обычный 5 2 4 2 5" xfId="687"/>
+    <cellStyle name="Обычный 5 2 4 3" xfId="689"/>
+    <cellStyle name="Обычный 5 2 4 4" xfId="691"/>
+    <cellStyle name="Обычный 5 2 4 5" xfId="692"/>
+    <cellStyle name="Обычный 5 2 4 6" xfId="694"/>
+    <cellStyle name="Обычный 5 2 5" xfId="696"/>
+    <cellStyle name="Обычный 5 2 5 2" xfId="697"/>
+    <cellStyle name="Обычный 5 2 5 2 2" xfId="698"/>
+    <cellStyle name="Обычный 5 2 5 2 3" xfId="699"/>
+    <cellStyle name="Обычный 5 2 5 2 4" xfId="700"/>
+    <cellStyle name="Обычный 5 2 5 2 5" xfId="701"/>
+    <cellStyle name="Обычный 5 2 5 3" xfId="702"/>
+    <cellStyle name="Обычный 5 2 5 4" xfId="703"/>
+    <cellStyle name="Обычный 5 2 5 5" xfId="704"/>
+    <cellStyle name="Обычный 5 2 5 6" xfId="705"/>
+    <cellStyle name="Обычный 5 2 6" xfId="706"/>
+    <cellStyle name="Обычный 5 2 6 2" xfId="707"/>
+    <cellStyle name="Обычный 5 2 6 3" xfId="708"/>
+    <cellStyle name="Обычный 5 2 6 4" xfId="709"/>
+    <cellStyle name="Обычный 5 2 6 5" xfId="710"/>
+    <cellStyle name="Обычный 5 2 7" xfId="711"/>
+    <cellStyle name="Обычный 5 2 8" xfId="712"/>
+    <cellStyle name="Обычный 5 2 9" xfId="713"/>
+    <cellStyle name="Обычный 5 3" xfId="715"/>
+    <cellStyle name="Обычный 5 3 2" xfId="716"/>
+    <cellStyle name="Обычный 5 4" xfId="718"/>
+    <cellStyle name="Обычный 5 4 2" xfId="719"/>
+    <cellStyle name="Обычный 5 5" xfId="721"/>
+    <cellStyle name="Обычный 5 5 2" xfId="722"/>
+    <cellStyle name="Обычный 5 6" xfId="725"/>
+    <cellStyle name="Обычный 5 6 2" xfId="726"/>
+    <cellStyle name="Обычный 5 7" xfId="728"/>
+    <cellStyle name="Обычный 5 7 2" xfId="729"/>
+    <cellStyle name="Обычный 6" xfId="3"/>
+    <cellStyle name="Обычный 6 10" xfId="731"/>
+    <cellStyle name="Обычный 6 11" xfId="732"/>
+    <cellStyle name="Обычный 6 12" xfId="730"/>
+    <cellStyle name="Обычный 6 2" xfId="735"/>
+    <cellStyle name="Обычный 6 2 2" xfId="737"/>
+    <cellStyle name="Обычный 6 2 2 2" xfId="739"/>
+    <cellStyle name="Обычный 6 2 2 2 2" xfId="740"/>
+    <cellStyle name="Обычный 6 2 2 2 2 2" xfId="741"/>
+    <cellStyle name="Обычный 6 2 2 2 2 3" xfId="742"/>
+    <cellStyle name="Обычный 6 2 2 2 2 4" xfId="743"/>
+    <cellStyle name="Обычный 6 2 2 2 2 5" xfId="744"/>
+    <cellStyle name="Обычный 6 2 2 2 3" xfId="746"/>
+    <cellStyle name="Обычный 6 2 2 2 4" xfId="747"/>
+    <cellStyle name="Обычный 6 2 2 2 5" xfId="748"/>
+    <cellStyle name="Обычный 6 2 2 2 6" xfId="749"/>
+    <cellStyle name="Обычный 6 2 2 3" xfId="751"/>
+    <cellStyle name="Обычный 6 2 2 3 2" xfId="752"/>
+    <cellStyle name="Обычный 6 2 2 3 3" xfId="754"/>
+    <cellStyle name="Обычный 6 2 2 3 4" xfId="755"/>
+    <cellStyle name="Обычный 6 2 2 3 5" xfId="756"/>
+    <cellStyle name="Обычный 6 2 2 4" xfId="757"/>
+    <cellStyle name="Обычный 6 2 2 5" xfId="758"/>
+    <cellStyle name="Обычный 6 2 2 6" xfId="759"/>
+    <cellStyle name="Обычный 6 2 2 7" xfId="760"/>
+    <cellStyle name="Обычный 6 2 3" xfId="762"/>
+    <cellStyle name="Обычный 6 2 3 2" xfId="764"/>
+    <cellStyle name="Обычный 6 2 3 2 2" xfId="765"/>
+    <cellStyle name="Обычный 6 2 3 2 3" xfId="766"/>
+    <cellStyle name="Обычный 6 2 3 2 4" xfId="767"/>
+    <cellStyle name="Обычный 6 2 3 2 5" xfId="768"/>
+    <cellStyle name="Обычный 6 2 3 3" xfId="769"/>
+    <cellStyle name="Обычный 6 2 3 4" xfId="770"/>
+    <cellStyle name="Обычный 6 2 3 5" xfId="771"/>
+    <cellStyle name="Обычный 6 2 3 6" xfId="772"/>
+    <cellStyle name="Обычный 6 2 4" xfId="775"/>
+    <cellStyle name="Обычный 6 2 4 2" xfId="776"/>
+    <cellStyle name="Обычный 6 2 4 3" xfId="777"/>
+    <cellStyle name="Обычный 6 2 4 4" xfId="778"/>
+    <cellStyle name="Обычный 6 2 4 5" xfId="779"/>
+    <cellStyle name="Обычный 6 2 5" xfId="782"/>
+    <cellStyle name="Обычный 6 2 6" xfId="784"/>
+    <cellStyle name="Обычный 6 2 7" xfId="786"/>
+    <cellStyle name="Обычный 6 2 8" xfId="787"/>
+    <cellStyle name="Обычный 6 3" xfId="790"/>
+    <cellStyle name="Обычный 6 3 2" xfId="791"/>
+    <cellStyle name="Обычный 6 3 2 2" xfId="792"/>
+    <cellStyle name="Обычный 6 3 2 2 2" xfId="793"/>
+    <cellStyle name="Обычный 6 3 2 2 3" xfId="794"/>
+    <cellStyle name="Обычный 6 3 2 2 4" xfId="795"/>
+    <cellStyle name="Обычный 6 3 2 2 5" xfId="796"/>
+    <cellStyle name="Обычный 6 3 2 3" xfId="797"/>
+    <cellStyle name="Обычный 6 3 2 4" xfId="798"/>
+    <cellStyle name="Обычный 6 3 2 5" xfId="799"/>
+    <cellStyle name="Обычный 6 3 2 6" xfId="471"/>
+    <cellStyle name="Обычный 6 3 3" xfId="800"/>
+    <cellStyle name="Обычный 6 3 3 2" xfId="801"/>
+    <cellStyle name="Обычный 6 3 3 3" xfId="802"/>
+    <cellStyle name="Обычный 6 3 3 4" xfId="803"/>
+    <cellStyle name="Обычный 6 3 3 5" xfId="804"/>
+    <cellStyle name="Обычный 6 3 4" xfId="805"/>
+    <cellStyle name="Обычный 6 3 5" xfId="806"/>
+    <cellStyle name="Обычный 6 3 6" xfId="807"/>
+    <cellStyle name="Обычный 6 3 7" xfId="808"/>
+    <cellStyle name="Обычный 6 4" xfId="811"/>
+    <cellStyle name="Обычный 6 4 2" xfId="812"/>
+    <cellStyle name="Обычный 6 4 2 2" xfId="813"/>
+    <cellStyle name="Обычный 6 4 2 3" xfId="814"/>
+    <cellStyle name="Обычный 6 4 2 4" xfId="815"/>
+    <cellStyle name="Обычный 6 4 2 5" xfId="816"/>
+    <cellStyle name="Обычный 6 4 3" xfId="817"/>
+    <cellStyle name="Обычный 6 4 4" xfId="818"/>
+    <cellStyle name="Обычный 6 4 5" xfId="819"/>
+    <cellStyle name="Обычный 6 4 6" xfId="820"/>
+    <cellStyle name="Обычный 6 5" xfId="822"/>
+    <cellStyle name="Обычный 6 5 2" xfId="825"/>
+    <cellStyle name="Обычный 6 5 2 2" xfId="828"/>
+    <cellStyle name="Обычный 6 5 2 3" xfId="830"/>
+    <cellStyle name="Обычный 6 5 2 4" xfId="832"/>
+    <cellStyle name="Обычный 6 5 2 5" xfId="834"/>
+    <cellStyle name="Обычный 6 5 3" xfId="24"/>
+    <cellStyle name="Обычный 6 5 4" xfId="837"/>
+    <cellStyle name="Обычный 6 5 5" xfId="840"/>
+    <cellStyle name="Обычный 6 5 6" xfId="843"/>
+    <cellStyle name="Обычный 6 6" xfId="845"/>
+    <cellStyle name="Обычный 6 6 2" xfId="846"/>
+    <cellStyle name="Обычный 6 6 2 2" xfId="847"/>
+    <cellStyle name="Обычный 6 6 2 3" xfId="848"/>
+    <cellStyle name="Обычный 6 6 2 4" xfId="849"/>
+    <cellStyle name="Обычный 6 6 2 5" xfId="850"/>
+    <cellStyle name="Обычный 6 6 3" xfId="851"/>
+    <cellStyle name="Обычный 6 6 4" xfId="852"/>
+    <cellStyle name="Обычный 6 6 5" xfId="853"/>
+    <cellStyle name="Обычный 6 6 6" xfId="854"/>
+    <cellStyle name="Обычный 6 7" xfId="855"/>
+    <cellStyle name="Обычный 6 7 2" xfId="856"/>
+    <cellStyle name="Обычный 6 7 3" xfId="857"/>
+    <cellStyle name="Обычный 6 7 4" xfId="858"/>
+    <cellStyle name="Обычный 6 7 5" xfId="859"/>
+    <cellStyle name="Обычный 6 8" xfId="860"/>
+    <cellStyle name="Обычный 6 9" xfId="861"/>
+    <cellStyle name="Обычный 7" xfId="862"/>
+    <cellStyle name="Обычный 7 10" xfId="863"/>
+    <cellStyle name="Обычный 7 11" xfId="864"/>
+    <cellStyle name="Обычный 7 2" xfId="866"/>
+    <cellStyle name="Обычный 7 2 2" xfId="868"/>
+    <cellStyle name="Обычный 7 2 2 2" xfId="869"/>
+    <cellStyle name="Обычный 7 2 2 2 2" xfId="870"/>
+    <cellStyle name="Обычный 7 2 2 2 2 2" xfId="873"/>
+    <cellStyle name="Обычный 7 2 2 2 2 3" xfId="876"/>
+    <cellStyle name="Обычный 7 2 2 2 2 4" xfId="878"/>
+    <cellStyle name="Обычный 7 2 2 2 2 5" xfId="879"/>
+    <cellStyle name="Обычный 7 2 2 2 3" xfId="880"/>
+    <cellStyle name="Обычный 7 2 2 2 4" xfId="881"/>
+    <cellStyle name="Обычный 7 2 2 2 5" xfId="882"/>
+    <cellStyle name="Обычный 7 2 2 2 6" xfId="883"/>
+    <cellStyle name="Обычный 7 2 2 3" xfId="885"/>
+    <cellStyle name="Обычный 7 2 2 3 2" xfId="887"/>
+    <cellStyle name="Обычный 7 2 2 3 3" xfId="889"/>
+    <cellStyle name="Обычный 7 2 2 3 4" xfId="891"/>
+    <cellStyle name="Обычный 7 2 2 3 5" xfId="893"/>
+    <cellStyle name="Обычный 7 2 2 4" xfId="895"/>
+    <cellStyle name="Обычный 7 2 2 5" xfId="734"/>
+    <cellStyle name="Обычный 7 2 2 6" xfId="789"/>
+    <cellStyle name="Обычный 7 2 2 7" xfId="810"/>
+    <cellStyle name="Обычный 7 2 3" xfId="896"/>
+    <cellStyle name="Обычный 7 2 3 2" xfId="898"/>
+    <cellStyle name="Обычный 7 2 3 2 2" xfId="899"/>
+    <cellStyle name="Обычный 7 2 3 2 3" xfId="901"/>
+    <cellStyle name="Обычный 7 2 3 2 4" xfId="903"/>
+    <cellStyle name="Обычный 7 2 3 2 5" xfId="905"/>
+    <cellStyle name="Обычный 7 2 3 3" xfId="908"/>
+    <cellStyle name="Обычный 7 2 3 4" xfId="910"/>
+    <cellStyle name="Обычный 7 2 3 5" xfId="865"/>
+    <cellStyle name="Обычный 7 2 3 6" xfId="912"/>
+    <cellStyle name="Обычный 7 2 4" xfId="913"/>
+    <cellStyle name="Обычный 7 2 4 2" xfId="915"/>
+    <cellStyle name="Обычный 7 2 4 3" xfId="918"/>
+    <cellStyle name="Обычный 7 2 4 4" xfId="919"/>
+    <cellStyle name="Обычный 7 2 4 5" xfId="921"/>
+    <cellStyle name="Обычный 7 2 5" xfId="922"/>
+    <cellStyle name="Обычный 7 2 6" xfId="923"/>
+    <cellStyle name="Обычный 7 2 7" xfId="924"/>
+    <cellStyle name="Обычный 7 2 8" xfId="925"/>
+    <cellStyle name="Обычный 7 3" xfId="911"/>
+    <cellStyle name="Обычный 7 3 2" xfId="926"/>
+    <cellStyle name="Обычный 7 3 2 2" xfId="20"/>
+    <cellStyle name="Обычный 7 3 2 2 2" xfId="928"/>
+    <cellStyle name="Обычный 7 3 2 2 3" xfId="872"/>
+    <cellStyle name="Обычный 7 3 2 2 4" xfId="875"/>
+    <cellStyle name="Обычный 7 3 2 2 5" xfId="877"/>
+    <cellStyle name="Обычный 7 3 2 3" xfId="66"/>
+    <cellStyle name="Обычный 7 3 2 4" xfId="59"/>
+    <cellStyle name="Обычный 7 3 2 5" xfId="47"/>
+    <cellStyle name="Обычный 7 3 2 6" xfId="930"/>
+    <cellStyle name="Обычный 7 3 3" xfId="931"/>
+    <cellStyle name="Обычный 7 3 3 2" xfId="933"/>
+    <cellStyle name="Обычный 7 3 3 3" xfId="935"/>
+    <cellStyle name="Обычный 7 3 3 4" xfId="937"/>
+    <cellStyle name="Обычный 7 3 3 5" xfId="939"/>
+    <cellStyle name="Обычный 7 3 4" xfId="940"/>
+    <cellStyle name="Обычный 7 3 5" xfId="941"/>
+    <cellStyle name="Обычный 7 3 6" xfId="942"/>
+    <cellStyle name="Обычный 7 3 7" xfId="943"/>
+    <cellStyle name="Обычный 7 4" xfId="944"/>
+    <cellStyle name="Обычный 7 4 2" xfId="945"/>
+    <cellStyle name="Обычный 7 4 2 2" xfId="946"/>
+    <cellStyle name="Обычный 7 4 2 3" xfId="947"/>
+    <cellStyle name="Обычный 7 4 2 4" xfId="948"/>
+    <cellStyle name="Обычный 7 4 2 5" xfId="949"/>
+    <cellStyle name="Обычный 7 4 3" xfId="950"/>
+    <cellStyle name="Обычный 7 4 4" xfId="951"/>
+    <cellStyle name="Обычный 7 4 5" xfId="952"/>
+    <cellStyle name="Обычный 7 4 6" xfId="953"/>
+    <cellStyle name="Обычный 7 5" xfId="954"/>
+    <cellStyle name="Обычный 7 5 2" xfId="955"/>
+    <cellStyle name="Обычный 7 5 2 2" xfId="956"/>
+    <cellStyle name="Обычный 7 5 2 3" xfId="957"/>
+    <cellStyle name="Обычный 7 5 2 4" xfId="958"/>
+    <cellStyle name="Обычный 7 5 2 5" xfId="959"/>
+    <cellStyle name="Обычный 7 5 3" xfId="960"/>
+    <cellStyle name="Обычный 7 5 4" xfId="961"/>
+    <cellStyle name="Обычный 7 5 5" xfId="962"/>
+    <cellStyle name="Обычный 7 5 6" xfId="963"/>
+    <cellStyle name="Обычный 7 6" xfId="964"/>
+    <cellStyle name="Обычный 7 6 2" xfId="965"/>
+    <cellStyle name="Обычный 7 6 2 2" xfId="966"/>
+    <cellStyle name="Обычный 7 6 2 3" xfId="968"/>
+    <cellStyle name="Обычный 7 6 2 4" xfId="970"/>
+    <cellStyle name="Обычный 7 6 2 5" xfId="971"/>
+    <cellStyle name="Обычный 7 6 3" xfId="972"/>
+    <cellStyle name="Обычный 7 6 4" xfId="973"/>
+    <cellStyle name="Обычный 7 6 5" xfId="974"/>
+    <cellStyle name="Обычный 7 6 6" xfId="343"/>
+    <cellStyle name="Обычный 7 7" xfId="975"/>
+    <cellStyle name="Обычный 7 7 2" xfId="976"/>
+    <cellStyle name="Обычный 7 7 3" xfId="977"/>
+    <cellStyle name="Обычный 7 7 4" xfId="978"/>
+    <cellStyle name="Обычный 7 7 5" xfId="979"/>
+    <cellStyle name="Обычный 7 8" xfId="980"/>
+    <cellStyle name="Обычный 7 9" xfId="192"/>
+    <cellStyle name="Обычный 8" xfId="981"/>
+    <cellStyle name="Обычный 8 2" xfId="920"/>
+    <cellStyle name="Обычный 9" xfId="982"/>
+    <cellStyle name="Обычный 9 2" xfId="984"/>
     <cellStyle name="Процентный" xfId="13" builtinId="5"/>
-    <cellStyle name="Стиль 1" xfId="693" xr:uid="{00000000-0005-0000-0000-000010030000}"/>
-    <cellStyle name="Стиль 1 2" xfId="985" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
-    <cellStyle name="Стиль 1 2 2" xfId="986" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
-    <cellStyle name="Стиль 1 3" xfId="987" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
-    <cellStyle name="Стиль 1 3 2" xfId="988" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
-    <cellStyle name="Стиль 1 4" xfId="989" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
-    <cellStyle name="Стиль 1 4 2" xfId="990" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
-    <cellStyle name="Стиль 1 5" xfId="991" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
-    <cellStyle name="Стиль 1 5 2" xfId="993" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
-    <cellStyle name="Финансовый 2" xfId="994" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
-    <cellStyle name="Финансовый 2 10" xfId="995" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
-    <cellStyle name="Финансовый 2 10 2" xfId="997" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
-    <cellStyle name="Финансовый 2 2" xfId="221" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
-    <cellStyle name="Финансовый 2 3" xfId="236" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
-    <cellStyle name="Финансовый 2 4" xfId="260" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
-    <cellStyle name="Финансовый 2 4 2" xfId="263" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
-    <cellStyle name="Финансовый 2 5" xfId="272" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
-    <cellStyle name="Финансовый 2 5 2" xfId="998" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
-    <cellStyle name="Финансовый 2 6" xfId="274" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
-    <cellStyle name="Финансовый 2 6 2" xfId="999" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
-    <cellStyle name="Финансовый 2 7" xfId="276" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
-    <cellStyle name="Финансовый 2 7 2" xfId="1001" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
-    <cellStyle name="Финансовый 2 8" xfId="1003" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
-    <cellStyle name="Финансовый 2 8 2" xfId="1005" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
-    <cellStyle name="Финансовый 2 9" xfId="1007" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
-    <cellStyle name="Финансовый 2 9 2" xfId="1009" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
-    <cellStyle name="Финансовый 3" xfId="33" xr:uid="{00000000-0005-0000-0000-00002A030000}"/>
-    <cellStyle name="Финансовый 4" xfId="1642" xr:uid="{00000000-0005-0000-0000-00002B030000}"/>
-    <cellStyle name="Финансовый 5" xfId="1651" xr:uid="{00000000-0005-0000-0000-00002C030000}"/>
-    <cellStyle name="千位分隔 10" xfId="1464" xr:uid="{00000000-0005-0000-0000-00002D030000}"/>
-    <cellStyle name="千位分隔 10 2" xfId="1465" xr:uid="{00000000-0005-0000-0000-00002E030000}"/>
-    <cellStyle name="千位分隔 10 2 2" xfId="1466" xr:uid="{00000000-0005-0000-0000-00002F030000}"/>
-    <cellStyle name="千位分隔 10 2 3" xfId="1467" xr:uid="{00000000-0005-0000-0000-000030030000}"/>
-    <cellStyle name="千位分隔 10 2 4" xfId="1468" xr:uid="{00000000-0005-0000-0000-000031030000}"/>
-    <cellStyle name="千位分隔 10 2 5" xfId="1469" xr:uid="{00000000-0005-0000-0000-000032030000}"/>
-    <cellStyle name="千位分隔 10 3" xfId="1470" xr:uid="{00000000-0005-0000-0000-000033030000}"/>
-    <cellStyle name="千位分隔 10 4" xfId="1471" xr:uid="{00000000-0005-0000-0000-000034030000}"/>
-    <cellStyle name="千位分隔 10 5" xfId="1472" xr:uid="{00000000-0005-0000-0000-000035030000}"/>
-    <cellStyle name="千位分隔 10 6" xfId="1473" xr:uid="{00000000-0005-0000-0000-000036030000}"/>
-    <cellStyle name="千位分隔 11" xfId="1474" xr:uid="{00000000-0005-0000-0000-000037030000}"/>
-    <cellStyle name="千位分隔 11 2" xfId="1475" xr:uid="{00000000-0005-0000-0000-000038030000}"/>
-    <cellStyle name="千位分隔 12" xfId="1476" xr:uid="{00000000-0005-0000-0000-000039030000}"/>
-    <cellStyle name="千位分隔 12 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00003A030000}"/>
-    <cellStyle name="千位分隔 12 2 2" xfId="1328" xr:uid="{00000000-0005-0000-0000-00003B030000}"/>
-    <cellStyle name="千位分隔 12 2 3" xfId="1477" xr:uid="{00000000-0005-0000-0000-00003C030000}"/>
-    <cellStyle name="千位分隔 12 2 4" xfId="1478" xr:uid="{00000000-0005-0000-0000-00003D030000}"/>
-    <cellStyle name="千位分隔 12 2 5" xfId="1479" xr:uid="{00000000-0005-0000-0000-00003E030000}"/>
-    <cellStyle name="千位分隔 12 3" xfId="929" xr:uid="{00000000-0005-0000-0000-00003F030000}"/>
-    <cellStyle name="千位分隔 12 4" xfId="1480" xr:uid="{00000000-0005-0000-0000-000040030000}"/>
-    <cellStyle name="千位分隔 12 5" xfId="1481" xr:uid="{00000000-0005-0000-0000-000041030000}"/>
-    <cellStyle name="千位分隔 12 6" xfId="1482" xr:uid="{00000000-0005-0000-0000-000042030000}"/>
-    <cellStyle name="千位分隔 13" xfId="14" xr:uid="{00000000-0005-0000-0000-000043030000}"/>
-    <cellStyle name="千位分隔 13 2" xfId="938" xr:uid="{00000000-0005-0000-0000-000044030000}"/>
-    <cellStyle name="千位分隔 13 2 2" xfId="1383" xr:uid="{00000000-0005-0000-0000-000045030000}"/>
-    <cellStyle name="千位分隔 13 2 3" xfId="1484" xr:uid="{00000000-0005-0000-0000-000046030000}"/>
-    <cellStyle name="千位分隔 13 2 4" xfId="1485" xr:uid="{00000000-0005-0000-0000-000047030000}"/>
-    <cellStyle name="千位分隔 13 2 5" xfId="1486" xr:uid="{00000000-0005-0000-0000-000048030000}"/>
-    <cellStyle name="千位分隔 13 3" xfId="1487" xr:uid="{00000000-0005-0000-0000-000049030000}"/>
-    <cellStyle name="千位分隔 13 4" xfId="1488" xr:uid="{00000000-0005-0000-0000-00004A030000}"/>
-    <cellStyle name="千位分隔 13 5" xfId="1489" xr:uid="{00000000-0005-0000-0000-00004B030000}"/>
-    <cellStyle name="千位分隔 13 6" xfId="1490" xr:uid="{00000000-0005-0000-0000-00004C030000}"/>
-    <cellStyle name="千位分隔 13 7" xfId="1483" xr:uid="{00000000-0005-0000-0000-00004D030000}"/>
-    <cellStyle name="千位分隔 14" xfId="1491" xr:uid="{00000000-0005-0000-0000-00004E030000}"/>
-    <cellStyle name="千位分隔 14 2" xfId="1492" xr:uid="{00000000-0005-0000-0000-00004F030000}"/>
-    <cellStyle name="千位分隔 14 2 2" xfId="1493" xr:uid="{00000000-0005-0000-0000-000050030000}"/>
-    <cellStyle name="千位分隔 14 2 3" xfId="1494" xr:uid="{00000000-0005-0000-0000-000051030000}"/>
-    <cellStyle name="千位分隔 14 2 4" xfId="1495" xr:uid="{00000000-0005-0000-0000-000052030000}"/>
-    <cellStyle name="千位分隔 14 2 5" xfId="1496" xr:uid="{00000000-0005-0000-0000-000053030000}"/>
-    <cellStyle name="千位分隔 14 3" xfId="1497" xr:uid="{00000000-0005-0000-0000-000054030000}"/>
-    <cellStyle name="千位分隔 14 4" xfId="1498" xr:uid="{00000000-0005-0000-0000-000055030000}"/>
-    <cellStyle name="千位分隔 14 5" xfId="1499" xr:uid="{00000000-0005-0000-0000-000056030000}"/>
-    <cellStyle name="千位分隔 14 6" xfId="1500" xr:uid="{00000000-0005-0000-0000-000057030000}"/>
-    <cellStyle name="千位分隔 15" xfId="9" xr:uid="{00000000-0005-0000-0000-000058030000}"/>
-    <cellStyle name="千位分隔 15 2" xfId="1503" xr:uid="{00000000-0005-0000-0000-000059030000}"/>
-    <cellStyle name="千位分隔 15 3" xfId="1504" xr:uid="{00000000-0005-0000-0000-00005A030000}"/>
-    <cellStyle name="千位分隔 15 4" xfId="1505" xr:uid="{00000000-0005-0000-0000-00005B030000}"/>
-    <cellStyle name="千位分隔 15 5" xfId="1506" xr:uid="{00000000-0005-0000-0000-00005C030000}"/>
-    <cellStyle name="千位分隔 15 6" xfId="1502" xr:uid="{00000000-0005-0000-0000-00005D030000}"/>
-    <cellStyle name="千位分隔 16" xfId="605" xr:uid="{00000000-0005-0000-0000-00005E030000}"/>
-    <cellStyle name="千位分隔 17" xfId="624" xr:uid="{00000000-0005-0000-0000-00005F030000}"/>
-    <cellStyle name="千位分隔 17 2" xfId="626" xr:uid="{00000000-0005-0000-0000-000060030000}"/>
-    <cellStyle name="千位分隔 17 3" xfId="632" xr:uid="{00000000-0005-0000-0000-000061030000}"/>
-    <cellStyle name="千位分隔 18" xfId="11" xr:uid="{00000000-0005-0000-0000-000062030000}"/>
-    <cellStyle name="千位分隔 18 2" xfId="641" xr:uid="{00000000-0005-0000-0000-000063030000}"/>
-    <cellStyle name="千位分隔 19" xfId="16" xr:uid="{00000000-0005-0000-0000-000064030000}"/>
-    <cellStyle name="千位分隔 2" xfId="296" xr:uid="{00000000-0005-0000-0000-000065030000}"/>
-    <cellStyle name="千位分隔 2 10" xfId="1507" xr:uid="{00000000-0005-0000-0000-000066030000}"/>
-    <cellStyle name="千位分隔 2 11" xfId="1508" xr:uid="{00000000-0005-0000-0000-000067030000}"/>
-    <cellStyle name="千位分隔 2 12" xfId="290" xr:uid="{00000000-0005-0000-0000-000068030000}"/>
-    <cellStyle name="千位分隔 2 2" xfId="1509" xr:uid="{00000000-0005-0000-0000-000069030000}"/>
-    <cellStyle name="千位分隔 2 2 2" xfId="1287" xr:uid="{00000000-0005-0000-0000-00006A030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2" xfId="1510" xr:uid="{00000000-0005-0000-0000-00006B030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2" xfId="1511" xr:uid="{00000000-0005-0000-0000-00006C030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 2" xfId="1512" xr:uid="{00000000-0005-0000-0000-00006D030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 3" xfId="1513" xr:uid="{00000000-0005-0000-0000-00006E030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 4" xfId="1514" xr:uid="{00000000-0005-0000-0000-00006F030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 5" xfId="1515" xr:uid="{00000000-0005-0000-0000-000070030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 3" xfId="1516" xr:uid="{00000000-0005-0000-0000-000071030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 4" xfId="1517" xr:uid="{00000000-0005-0000-0000-000072030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 5" xfId="1518" xr:uid="{00000000-0005-0000-0000-000073030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 6" xfId="1089" xr:uid="{00000000-0005-0000-0000-000074030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3" xfId="1519" xr:uid="{00000000-0005-0000-0000-000075030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 2" xfId="1520" xr:uid="{00000000-0005-0000-0000-000076030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 3" xfId="1521" xr:uid="{00000000-0005-0000-0000-000077030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 4" xfId="1522" xr:uid="{00000000-0005-0000-0000-000078030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 5" xfId="1523" xr:uid="{00000000-0005-0000-0000-000079030000}"/>
-    <cellStyle name="千位分隔 2 2 2 4" xfId="1524" xr:uid="{00000000-0005-0000-0000-00007A030000}"/>
-    <cellStyle name="千位分隔 2 2 2 5" xfId="1525" xr:uid="{00000000-0005-0000-0000-00007B030000}"/>
-    <cellStyle name="千位分隔 2 2 2 6" xfId="1526" xr:uid="{00000000-0005-0000-0000-00007C030000}"/>
-    <cellStyle name="千位分隔 2 2 2 7" xfId="1527" xr:uid="{00000000-0005-0000-0000-00007D030000}"/>
-    <cellStyle name="千位分隔 2 2 3" xfId="1528" xr:uid="{00000000-0005-0000-0000-00007E030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2" xfId="1529" xr:uid="{00000000-0005-0000-0000-00007F030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 2" xfId="1530" xr:uid="{00000000-0005-0000-0000-000080030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 3" xfId="1531" xr:uid="{00000000-0005-0000-0000-000081030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 4" xfId="1532" xr:uid="{00000000-0005-0000-0000-000082030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 5" xfId="1533" xr:uid="{00000000-0005-0000-0000-000083030000}"/>
-    <cellStyle name="千位分隔 2 2 3 3" xfId="1534" xr:uid="{00000000-0005-0000-0000-000084030000}"/>
-    <cellStyle name="千位分隔 2 2 3 4" xfId="1535" xr:uid="{00000000-0005-0000-0000-000085030000}"/>
-    <cellStyle name="千位分隔 2 2 3 5" xfId="1536" xr:uid="{00000000-0005-0000-0000-000086030000}"/>
-    <cellStyle name="千位分隔 2 2 3 6" xfId="1537" xr:uid="{00000000-0005-0000-0000-000087030000}"/>
-    <cellStyle name="千位分隔 2 2 4" xfId="992" xr:uid="{00000000-0005-0000-0000-000088030000}"/>
-    <cellStyle name="千位分隔 2 2 4 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000089030000}"/>
-    <cellStyle name="千位分隔 2 2 4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00008A030000}"/>
-    <cellStyle name="千位分隔 2 2 4 4" xfId="68" xr:uid="{00000000-0005-0000-0000-00008B030000}"/>
-    <cellStyle name="千位分隔 2 2 4 5" xfId="72" xr:uid="{00000000-0005-0000-0000-00008C030000}"/>
-    <cellStyle name="千位分隔 2 2 5" xfId="1203" xr:uid="{00000000-0005-0000-0000-00008D030000}"/>
-    <cellStyle name="千位分隔 2 2 6" xfId="1205" xr:uid="{00000000-0005-0000-0000-00008E030000}"/>
-    <cellStyle name="千位分隔 2 2 7" xfId="512" xr:uid="{00000000-0005-0000-0000-00008F030000}"/>
-    <cellStyle name="千位分隔 2 2 8" xfId="1207" xr:uid="{00000000-0005-0000-0000-000090030000}"/>
-    <cellStyle name="千位分隔 2 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000091030000}"/>
-    <cellStyle name="千位分隔 2 3 2" xfId="1300" xr:uid="{00000000-0005-0000-0000-000092030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2" xfId="1539" xr:uid="{00000000-0005-0000-0000-000093030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 2" xfId="724" xr:uid="{00000000-0005-0000-0000-000094030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 3" xfId="727" xr:uid="{00000000-0005-0000-0000-000095030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 4" xfId="1540" xr:uid="{00000000-0005-0000-0000-000096030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 5" xfId="1541" xr:uid="{00000000-0005-0000-0000-000097030000}"/>
-    <cellStyle name="千位分隔 2 3 2 3" xfId="1542" xr:uid="{00000000-0005-0000-0000-000098030000}"/>
-    <cellStyle name="千位分隔 2 3 2 4" xfId="1543" xr:uid="{00000000-0005-0000-0000-000099030000}"/>
-    <cellStyle name="千位分隔 2 3 2 5" xfId="1544" xr:uid="{00000000-0005-0000-0000-00009A030000}"/>
-    <cellStyle name="千位分隔 2 3 2 6" xfId="1545" xr:uid="{00000000-0005-0000-0000-00009B030000}"/>
-    <cellStyle name="千位分隔 2 3 3" xfId="1546" xr:uid="{00000000-0005-0000-0000-00009C030000}"/>
-    <cellStyle name="千位分隔 2 3 3 2" xfId="1547" xr:uid="{00000000-0005-0000-0000-00009D030000}"/>
-    <cellStyle name="千位分隔 2 3 3 3" xfId="1548" xr:uid="{00000000-0005-0000-0000-00009E030000}"/>
-    <cellStyle name="千位分隔 2 3 3 4" xfId="1549" xr:uid="{00000000-0005-0000-0000-00009F030000}"/>
-    <cellStyle name="千位分隔 2 3 3 5" xfId="1550" xr:uid="{00000000-0005-0000-0000-0000A0030000}"/>
-    <cellStyle name="千位分隔 2 3 4" xfId="1551" xr:uid="{00000000-0005-0000-0000-0000A1030000}"/>
-    <cellStyle name="千位分隔 2 3 5" xfId="1552" xr:uid="{00000000-0005-0000-0000-0000A2030000}"/>
-    <cellStyle name="千位分隔 2 3 6" xfId="1553" xr:uid="{00000000-0005-0000-0000-0000A3030000}"/>
-    <cellStyle name="千位分隔 2 3 7" xfId="187" xr:uid="{00000000-0005-0000-0000-0000A4030000}"/>
-    <cellStyle name="千位分隔 2 3 8" xfId="1538" xr:uid="{00000000-0005-0000-0000-0000A5030000}"/>
-    <cellStyle name="千位分隔 2 4" xfId="544" xr:uid="{00000000-0005-0000-0000-0000A6030000}"/>
-    <cellStyle name="千位分隔 2 4 2" xfId="547" xr:uid="{00000000-0005-0000-0000-0000A7030000}"/>
-    <cellStyle name="千位分隔 2 4 2 2" xfId="1554" xr:uid="{00000000-0005-0000-0000-0000A8030000}"/>
-    <cellStyle name="千位分隔 2 4 2 3" xfId="1555" xr:uid="{00000000-0005-0000-0000-0000A9030000}"/>
-    <cellStyle name="千位分隔 2 4 2 4" xfId="1556" xr:uid="{00000000-0005-0000-0000-0000AA030000}"/>
-    <cellStyle name="千位分隔 2 4 2 5" xfId="1557" xr:uid="{00000000-0005-0000-0000-0000AB030000}"/>
-    <cellStyle name="千位分隔 2 4 3" xfId="550" xr:uid="{00000000-0005-0000-0000-0000AC030000}"/>
-    <cellStyle name="千位分隔 2 4 4" xfId="34" xr:uid="{00000000-0005-0000-0000-0000AD030000}"/>
-    <cellStyle name="千位分隔 2 4 5" xfId="194" xr:uid="{00000000-0005-0000-0000-0000AE030000}"/>
-    <cellStyle name="千位分隔 2 4 6" xfId="197" xr:uid="{00000000-0005-0000-0000-0000AF030000}"/>
-    <cellStyle name="千位分隔 2 5" xfId="579" xr:uid="{00000000-0005-0000-0000-0000B0030000}"/>
-    <cellStyle name="千位分隔 2 5 2" xfId="349" xr:uid="{00000000-0005-0000-0000-0000B1030000}"/>
-    <cellStyle name="千位分隔 2 5 2 2" xfId="354" xr:uid="{00000000-0005-0000-0000-0000B2030000}"/>
-    <cellStyle name="千位分隔 2 5 2 3" xfId="357" xr:uid="{00000000-0005-0000-0000-0000B3030000}"/>
-    <cellStyle name="千位分隔 2 5 2 4" xfId="360" xr:uid="{00000000-0005-0000-0000-0000B4030000}"/>
-    <cellStyle name="千位分隔 2 5 2 5" xfId="315" xr:uid="{00000000-0005-0000-0000-0000B5030000}"/>
-    <cellStyle name="千位分隔 2 5 3" xfId="90" xr:uid="{00000000-0005-0000-0000-0000B6030000}"/>
-    <cellStyle name="千位分隔 2 5 4" xfId="586" xr:uid="{00000000-0005-0000-0000-0000B7030000}"/>
-    <cellStyle name="千位分隔 2 5 5" xfId="591" xr:uid="{00000000-0005-0000-0000-0000B8030000}"/>
-    <cellStyle name="千位分隔 2 5 6" xfId="593" xr:uid="{00000000-0005-0000-0000-0000B9030000}"/>
-    <cellStyle name="千位分隔 2 6" xfId="28" xr:uid="{00000000-0005-0000-0000-0000BA030000}"/>
-    <cellStyle name="千位分隔 2 6 2" xfId="1558" xr:uid="{00000000-0005-0000-0000-0000BB030000}"/>
-    <cellStyle name="千位分隔 2 6 2 2" xfId="1559" xr:uid="{00000000-0005-0000-0000-0000BC030000}"/>
-    <cellStyle name="千位分隔 2 6 2 3" xfId="1560" xr:uid="{00000000-0005-0000-0000-0000BD030000}"/>
-    <cellStyle name="千位分隔 2 6 2 4" xfId="1561" xr:uid="{00000000-0005-0000-0000-0000BE030000}"/>
-    <cellStyle name="千位分隔 2 6 2 5" xfId="1562" xr:uid="{00000000-0005-0000-0000-0000BF030000}"/>
-    <cellStyle name="千位分隔 2 6 3" xfId="1563" xr:uid="{00000000-0005-0000-0000-0000C0030000}"/>
-    <cellStyle name="千位分隔 2 6 4" xfId="1564" xr:uid="{00000000-0005-0000-0000-0000C1030000}"/>
-    <cellStyle name="千位分隔 2 6 5" xfId="1565" xr:uid="{00000000-0005-0000-0000-0000C2030000}"/>
-    <cellStyle name="千位分隔 2 6 6" xfId="1566" xr:uid="{00000000-0005-0000-0000-0000C3030000}"/>
-    <cellStyle name="千位分隔 2 7" xfId="596" xr:uid="{00000000-0005-0000-0000-0000C4030000}"/>
-    <cellStyle name="千位分隔 2 7 2" xfId="1567" xr:uid="{00000000-0005-0000-0000-0000C5030000}"/>
-    <cellStyle name="千位分隔 2 7 3" xfId="1568" xr:uid="{00000000-0005-0000-0000-0000C6030000}"/>
-    <cellStyle name="千位分隔 2 7 4" xfId="1569" xr:uid="{00000000-0005-0000-0000-0000C7030000}"/>
-    <cellStyle name="千位分隔 2 7 5" xfId="1570" xr:uid="{00000000-0005-0000-0000-0000C8030000}"/>
-    <cellStyle name="千位分隔 2 8" xfId="598" xr:uid="{00000000-0005-0000-0000-0000C9030000}"/>
-    <cellStyle name="千位分隔 2 8 2" xfId="1571" xr:uid="{00000000-0005-0000-0000-0000CA030000}"/>
-    <cellStyle name="千位分隔 2 8 3" xfId="1572" xr:uid="{00000000-0005-0000-0000-0000CB030000}"/>
-    <cellStyle name="千位分隔 2 8 4" xfId="996" xr:uid="{00000000-0005-0000-0000-0000CC030000}"/>
-    <cellStyle name="千位分隔 2 8 5" xfId="1573" xr:uid="{00000000-0005-0000-0000-0000CD030000}"/>
-    <cellStyle name="千位分隔 2 9" xfId="510" xr:uid="{00000000-0005-0000-0000-0000CE030000}"/>
-    <cellStyle name="千位分隔 2 9 2" xfId="1574" xr:uid="{00000000-0005-0000-0000-0000CF030000}"/>
-    <cellStyle name="千位分隔 2 9 3" xfId="1575" xr:uid="{00000000-0005-0000-0000-0000D0030000}"/>
-    <cellStyle name="千位分隔 2 9 4" xfId="1576" xr:uid="{00000000-0005-0000-0000-0000D1030000}"/>
-    <cellStyle name="千位分隔 20" xfId="15" xr:uid="{00000000-0005-0000-0000-0000D2030000}"/>
-    <cellStyle name="千位分隔 20 2" xfId="1501" xr:uid="{00000000-0005-0000-0000-0000D3030000}"/>
-    <cellStyle name="千位分隔 21" xfId="604" xr:uid="{00000000-0005-0000-0000-0000D4030000}"/>
-    <cellStyle name="千位分隔 22" xfId="623" xr:uid="{00000000-0005-0000-0000-0000D5030000}"/>
-    <cellStyle name="千位分隔 23" xfId="640" xr:uid="{00000000-0005-0000-0000-0000D6030000}"/>
-    <cellStyle name="千位分隔 24" xfId="649" xr:uid="{00000000-0005-0000-0000-0000D7030000}"/>
-    <cellStyle name="千位分隔 25" xfId="651" xr:uid="{00000000-0005-0000-0000-0000D8030000}"/>
-    <cellStyle name="千位分隔 3" xfId="299" xr:uid="{00000000-0005-0000-0000-0000D9030000}"/>
-    <cellStyle name="千位分隔 3 2" xfId="1577" xr:uid="{00000000-0005-0000-0000-0000DA030000}"/>
-    <cellStyle name="千位分隔 3 2 2" xfId="1578" xr:uid="{00000000-0005-0000-0000-0000DB030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2" xfId="900" xr:uid="{00000000-0005-0000-0000-0000DC030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 2" xfId="1579" xr:uid="{00000000-0005-0000-0000-0000DD030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 3" xfId="1580" xr:uid="{00000000-0005-0000-0000-0000DE030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 4" xfId="1581" xr:uid="{00000000-0005-0000-0000-0000DF030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 5" xfId="1582" xr:uid="{00000000-0005-0000-0000-0000E0030000}"/>
-    <cellStyle name="千位分隔 3 2 2 3" xfId="902" xr:uid="{00000000-0005-0000-0000-0000E1030000}"/>
-    <cellStyle name="千位分隔 3 2 2 4" xfId="904" xr:uid="{00000000-0005-0000-0000-0000E2030000}"/>
-    <cellStyle name="千位分隔 3 2 2 5" xfId="1583" xr:uid="{00000000-0005-0000-0000-0000E3030000}"/>
-    <cellStyle name="千位分隔 3 2 2 6" xfId="1584" xr:uid="{00000000-0005-0000-0000-0000E4030000}"/>
-    <cellStyle name="千位分隔 3 2 3" xfId="1585" xr:uid="{00000000-0005-0000-0000-0000E5030000}"/>
-    <cellStyle name="千位分隔 3 2 3 2" xfId="1586" xr:uid="{00000000-0005-0000-0000-0000E6030000}"/>
-    <cellStyle name="千位分隔 3 2 3 3" xfId="1587" xr:uid="{00000000-0005-0000-0000-0000E7030000}"/>
-    <cellStyle name="千位分隔 3 2 3 4" xfId="1588" xr:uid="{00000000-0005-0000-0000-0000E8030000}"/>
-    <cellStyle name="千位分隔 3 2 3 5" xfId="1589" xr:uid="{00000000-0005-0000-0000-0000E9030000}"/>
-    <cellStyle name="千位分隔 3 2 4" xfId="1590" xr:uid="{00000000-0005-0000-0000-0000EA030000}"/>
-    <cellStyle name="千位分隔 3 2 5" xfId="1591" xr:uid="{00000000-0005-0000-0000-0000EB030000}"/>
-    <cellStyle name="千位分隔 3 2 6" xfId="1592" xr:uid="{00000000-0005-0000-0000-0000EC030000}"/>
-    <cellStyle name="千位分隔 3 2 7" xfId="1593" xr:uid="{00000000-0005-0000-0000-0000ED030000}"/>
-    <cellStyle name="千位分隔 3 3" xfId="1594" xr:uid="{00000000-0005-0000-0000-0000EE030000}"/>
-    <cellStyle name="千位分隔 3 3 2" xfId="1595" xr:uid="{00000000-0005-0000-0000-0000EF030000}"/>
-    <cellStyle name="千位分隔 3 3 2 2" xfId="1596" xr:uid="{00000000-0005-0000-0000-0000F0030000}"/>
-    <cellStyle name="千位分隔 3 3 2 3" xfId="1597" xr:uid="{00000000-0005-0000-0000-0000F1030000}"/>
-    <cellStyle name="千位分隔 3 3 2 4" xfId="1598" xr:uid="{00000000-0005-0000-0000-0000F2030000}"/>
-    <cellStyle name="千位分隔 3 3 2 5" xfId="1599" xr:uid="{00000000-0005-0000-0000-0000F3030000}"/>
-    <cellStyle name="千位分隔 3 3 3" xfId="1600" xr:uid="{00000000-0005-0000-0000-0000F4030000}"/>
-    <cellStyle name="千位分隔 3 3 4" xfId="1601" xr:uid="{00000000-0005-0000-0000-0000F5030000}"/>
-    <cellStyle name="千位分隔 3 3 5" xfId="1602" xr:uid="{00000000-0005-0000-0000-0000F6030000}"/>
-    <cellStyle name="千位分隔 3 3 6" xfId="1603" xr:uid="{00000000-0005-0000-0000-0000F7030000}"/>
-    <cellStyle name="千位分隔 3 4" xfId="601" xr:uid="{00000000-0005-0000-0000-0000F8030000}"/>
-    <cellStyle name="千位分隔 3 4 2" xfId="43" xr:uid="{00000000-0005-0000-0000-0000F9030000}"/>
-    <cellStyle name="千位分隔 3 4 3" xfId="655" xr:uid="{00000000-0005-0000-0000-0000FA030000}"/>
-    <cellStyle name="千位分隔 3 4 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000FB030000}"/>
-    <cellStyle name="千位分隔 3 4 5" xfId="695" xr:uid="{00000000-0005-0000-0000-0000FC030000}"/>
-    <cellStyle name="千位分隔 3 5" xfId="714" xr:uid="{00000000-0005-0000-0000-0000FD030000}"/>
-    <cellStyle name="千位分隔 3 6" xfId="717" xr:uid="{00000000-0005-0000-0000-0000FE030000}"/>
-    <cellStyle name="千位分隔 3 7" xfId="720" xr:uid="{00000000-0005-0000-0000-0000FF030000}"/>
-    <cellStyle name="千位分隔 3 8" xfId="723" xr:uid="{00000000-0005-0000-0000-000000040000}"/>
-    <cellStyle name="千位分隔 4" xfId="1604" xr:uid="{00000000-0005-0000-0000-000001040000}"/>
-    <cellStyle name="千位分隔 4 2" xfId="884" xr:uid="{00000000-0005-0000-0000-000002040000}"/>
-    <cellStyle name="千位分隔 4 2 2" xfId="886" xr:uid="{00000000-0005-0000-0000-000003040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2" xfId="1389" xr:uid="{00000000-0005-0000-0000-000004040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 2" xfId="1605" xr:uid="{00000000-0005-0000-0000-000005040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 3" xfId="1606" xr:uid="{00000000-0005-0000-0000-000006040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 4" xfId="1607" xr:uid="{00000000-0005-0000-0000-000007040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 5" xfId="1608" xr:uid="{00000000-0005-0000-0000-000008040000}"/>
-    <cellStyle name="千位分隔 4 2 2 3" xfId="1392" xr:uid="{00000000-0005-0000-0000-000009040000}"/>
-    <cellStyle name="千位分隔 4 2 2 4" xfId="1609" xr:uid="{00000000-0005-0000-0000-00000A040000}"/>
-    <cellStyle name="千位分隔 4 2 2 5" xfId="1610" xr:uid="{00000000-0005-0000-0000-00000B040000}"/>
-    <cellStyle name="千位分隔 4 2 2 6" xfId="1611" xr:uid="{00000000-0005-0000-0000-00000C040000}"/>
-    <cellStyle name="千位分隔 4 2 3" xfId="888" xr:uid="{00000000-0005-0000-0000-00000D040000}"/>
-    <cellStyle name="千位分隔 4 2 3 2" xfId="1411" xr:uid="{00000000-0005-0000-0000-00000E040000}"/>
-    <cellStyle name="千位分隔 4 2 3 3" xfId="1612" xr:uid="{00000000-0005-0000-0000-00000F040000}"/>
-    <cellStyle name="千位分隔 4 2 3 4" xfId="1613" xr:uid="{00000000-0005-0000-0000-000010040000}"/>
-    <cellStyle name="千位分隔 4 2 3 5" xfId="1614" xr:uid="{00000000-0005-0000-0000-000011040000}"/>
-    <cellStyle name="千位分隔 4 2 4" xfId="890" xr:uid="{00000000-0005-0000-0000-000012040000}"/>
-    <cellStyle name="千位分隔 4 2 5" xfId="892" xr:uid="{00000000-0005-0000-0000-000013040000}"/>
-    <cellStyle name="千位分隔 4 2 6" xfId="1615" xr:uid="{00000000-0005-0000-0000-000014040000}"/>
-    <cellStyle name="千位分隔 4 2 7" xfId="1616" xr:uid="{00000000-0005-0000-0000-000015040000}"/>
-    <cellStyle name="千位分隔 4 3" xfId="894" xr:uid="{00000000-0005-0000-0000-000016040000}"/>
-    <cellStyle name="千位分隔 4 3 2" xfId="1617" xr:uid="{00000000-0005-0000-0000-000017040000}"/>
-    <cellStyle name="千位分隔 4 3 2 2" xfId="1435" xr:uid="{00000000-0005-0000-0000-000018040000}"/>
-    <cellStyle name="千位分隔 4 3 2 3" xfId="1437" xr:uid="{00000000-0005-0000-0000-000019040000}"/>
-    <cellStyle name="千位分隔 4 3 2 4" xfId="1618" xr:uid="{00000000-0005-0000-0000-00001A040000}"/>
-    <cellStyle name="千位分隔 4 3 2 5" xfId="1619" xr:uid="{00000000-0005-0000-0000-00001B040000}"/>
-    <cellStyle name="千位分隔 4 3 3" xfId="1620" xr:uid="{00000000-0005-0000-0000-00001C040000}"/>
-    <cellStyle name="千位分隔 4 3 4" xfId="1621" xr:uid="{00000000-0005-0000-0000-00001D040000}"/>
-    <cellStyle name="千位分隔 4 3 5" xfId="1622" xr:uid="{00000000-0005-0000-0000-00001E040000}"/>
-    <cellStyle name="千位分隔 4 3 6" xfId="1623" xr:uid="{00000000-0005-0000-0000-00001F040000}"/>
-    <cellStyle name="千位分隔 4 4" xfId="733" xr:uid="{00000000-0005-0000-0000-000020040000}"/>
-    <cellStyle name="千位分隔 4 4 2" xfId="736" xr:uid="{00000000-0005-0000-0000-000021040000}"/>
-    <cellStyle name="千位分隔 4 4 3" xfId="761" xr:uid="{00000000-0005-0000-0000-000022040000}"/>
-    <cellStyle name="千位分隔 4 4 4" xfId="773" xr:uid="{00000000-0005-0000-0000-000023040000}"/>
-    <cellStyle name="千位分隔 4 4 5" xfId="780" xr:uid="{00000000-0005-0000-0000-000024040000}"/>
-    <cellStyle name="千位分隔 4 5" xfId="788" xr:uid="{00000000-0005-0000-0000-000025040000}"/>
-    <cellStyle name="千位分隔 4 6" xfId="809" xr:uid="{00000000-0005-0000-0000-000026040000}"/>
-    <cellStyle name="千位分隔 4 7" xfId="821" xr:uid="{00000000-0005-0000-0000-000027040000}"/>
-    <cellStyle name="千位分隔 4 8" xfId="844" xr:uid="{00000000-0005-0000-0000-000028040000}"/>
-    <cellStyle name="千位分隔 5" xfId="1624" xr:uid="{00000000-0005-0000-0000-000029040000}"/>
-    <cellStyle name="千位分隔 5 2" xfId="906" xr:uid="{00000000-0005-0000-0000-00002A040000}"/>
-    <cellStyle name="千位分隔 6" xfId="1102" xr:uid="{00000000-0005-0000-0000-00002B040000}"/>
-    <cellStyle name="千位分隔 6 2" xfId="916" xr:uid="{00000000-0005-0000-0000-00002C040000}"/>
-    <cellStyle name="千位分隔 7" xfId="1625" xr:uid="{00000000-0005-0000-0000-00002D040000}"/>
-    <cellStyle name="千位分隔 7 2" xfId="1626" xr:uid="{00000000-0005-0000-0000-00002E040000}"/>
-    <cellStyle name="千位分隔 7 2 2" xfId="1627" xr:uid="{00000000-0005-0000-0000-00002F040000}"/>
-    <cellStyle name="千位分隔 7 2 2 2" xfId="1628" xr:uid="{00000000-0005-0000-0000-000030040000}"/>
-    <cellStyle name="千位分隔 7 2 2 3" xfId="1629" xr:uid="{00000000-0005-0000-0000-000031040000}"/>
-    <cellStyle name="千位分隔 7 2 2 4" xfId="1630" xr:uid="{00000000-0005-0000-0000-000032040000}"/>
-    <cellStyle name="千位分隔 7 2 2 5" xfId="1631" xr:uid="{00000000-0005-0000-0000-000033040000}"/>
-    <cellStyle name="千位分隔 7 2 3" xfId="657" xr:uid="{00000000-0005-0000-0000-000034040000}"/>
-    <cellStyle name="千位分隔 7 2 4" xfId="668" xr:uid="{00000000-0005-0000-0000-000035040000}"/>
-    <cellStyle name="千位分隔 7 2 5" xfId="674" xr:uid="{00000000-0005-0000-0000-000036040000}"/>
-    <cellStyle name="千位分隔 7 2 6" xfId="676" xr:uid="{00000000-0005-0000-0000-000037040000}"/>
-    <cellStyle name="千位分隔 7 3" xfId="1632" xr:uid="{00000000-0005-0000-0000-000038040000}"/>
-    <cellStyle name="千位分隔 7 3 2" xfId="1633" xr:uid="{00000000-0005-0000-0000-000039040000}"/>
-    <cellStyle name="千位分隔 7 3 3" xfId="682" xr:uid="{00000000-0005-0000-0000-00003A040000}"/>
-    <cellStyle name="千位分隔 7 3 4" xfId="688" xr:uid="{00000000-0005-0000-0000-00003B040000}"/>
-    <cellStyle name="千位分隔 7 3 5" xfId="690" xr:uid="{00000000-0005-0000-0000-00003C040000}"/>
-    <cellStyle name="千位分隔 7 4" xfId="983" xr:uid="{00000000-0005-0000-0000-00003D040000}"/>
-    <cellStyle name="千位分隔 7 5" xfId="1634" xr:uid="{00000000-0005-0000-0000-00003E040000}"/>
-    <cellStyle name="千位分隔 7 6" xfId="1635" xr:uid="{00000000-0005-0000-0000-00003F040000}"/>
-    <cellStyle name="千位分隔 7 7" xfId="1636" xr:uid="{00000000-0005-0000-0000-000040040000}"/>
-    <cellStyle name="千位分隔 8" xfId="1637" xr:uid="{00000000-0005-0000-0000-000041040000}"/>
-    <cellStyle name="千位分隔 8 2" xfId="1638" xr:uid="{00000000-0005-0000-0000-000042040000}"/>
-    <cellStyle name="千位分隔 8 3" xfId="1639" xr:uid="{00000000-0005-0000-0000-000043040000}"/>
-    <cellStyle name="千位分隔 9" xfId="1640" xr:uid="{00000000-0005-0000-0000-000044040000}"/>
-    <cellStyle name="常规 10" xfId="439" xr:uid="{00000000-0005-0000-0000-000045040000}"/>
-    <cellStyle name="常规 10 10" xfId="1010" xr:uid="{00000000-0005-0000-0000-000046040000}"/>
-    <cellStyle name="常规 10 11" xfId="1011" xr:uid="{00000000-0005-0000-0000-000047040000}"/>
-    <cellStyle name="常规 10 12" xfId="1654" xr:uid="{00000000-0005-0000-0000-000048040000}"/>
-    <cellStyle name="常规 10 2" xfId="441" xr:uid="{00000000-0005-0000-0000-000049040000}"/>
-    <cellStyle name="常规 10 2 2" xfId="443" xr:uid="{00000000-0005-0000-0000-00004A040000}"/>
-    <cellStyle name="常规 10 2 2 2" xfId="1012" xr:uid="{00000000-0005-0000-0000-00004B040000}"/>
-    <cellStyle name="常规 10 2 2 2 2" xfId="1013" xr:uid="{00000000-0005-0000-0000-00004C040000}"/>
-    <cellStyle name="常规 10 2 2 2 2 2" xfId="1014" xr:uid="{00000000-0005-0000-0000-00004D040000}"/>
-    <cellStyle name="常规 10 2 2 2 3" xfId="1015" xr:uid="{00000000-0005-0000-0000-00004E040000}"/>
-    <cellStyle name="常规 10 2 2 2 4" xfId="1016" xr:uid="{00000000-0005-0000-0000-00004F040000}"/>
-    <cellStyle name="常规 10 2 2 2 5" xfId="1017" xr:uid="{00000000-0005-0000-0000-000050040000}"/>
-    <cellStyle name="常规 10 2 2 2 6" xfId="1018" xr:uid="{00000000-0005-0000-0000-000051040000}"/>
-    <cellStyle name="常规 10 2 2 3" xfId="1019" xr:uid="{00000000-0005-0000-0000-000052040000}"/>
-    <cellStyle name="常规 10 2 2 3 2" xfId="1020" xr:uid="{00000000-0005-0000-0000-000053040000}"/>
-    <cellStyle name="常规 10 2 2 4" xfId="1021" xr:uid="{00000000-0005-0000-0000-000054040000}"/>
-    <cellStyle name="常规 10 2 2 5" xfId="1022" xr:uid="{00000000-0005-0000-0000-000055040000}"/>
-    <cellStyle name="常规 10 2 2 6" xfId="1023" xr:uid="{00000000-0005-0000-0000-000056040000}"/>
-    <cellStyle name="常规 10 2 3" xfId="445" xr:uid="{00000000-0005-0000-0000-000057040000}"/>
-    <cellStyle name="常规 10 2 3 2" xfId="556" xr:uid="{00000000-0005-0000-0000-000058040000}"/>
-    <cellStyle name="常规 10 2 3 2 2" xfId="1024" xr:uid="{00000000-0005-0000-0000-000059040000}"/>
-    <cellStyle name="常规 10 2 3 2 2 2" xfId="1025" xr:uid="{00000000-0005-0000-0000-00005A040000}"/>
-    <cellStyle name="常规 10 2 3 2 3" xfId="1026" xr:uid="{00000000-0005-0000-0000-00005B040000}"/>
-    <cellStyle name="常规 10 2 3 2 4" xfId="1027" xr:uid="{00000000-0005-0000-0000-00005C040000}"/>
-    <cellStyle name="常规 10 2 3 2 5" xfId="1028" xr:uid="{00000000-0005-0000-0000-00005D040000}"/>
-    <cellStyle name="常规 10 2 3 2 6" xfId="1029" xr:uid="{00000000-0005-0000-0000-00005E040000}"/>
-    <cellStyle name="常规 10 2 3 3" xfId="1030" xr:uid="{00000000-0005-0000-0000-00005F040000}"/>
-    <cellStyle name="常规 10 2 3 3 2" xfId="1031" xr:uid="{00000000-0005-0000-0000-000060040000}"/>
-    <cellStyle name="常规 10 2 3 4" xfId="1032" xr:uid="{00000000-0005-0000-0000-000061040000}"/>
-    <cellStyle name="常规 10 2 3 5" xfId="1033" xr:uid="{00000000-0005-0000-0000-000062040000}"/>
-    <cellStyle name="常规 10 2 3 6" xfId="1034" xr:uid="{00000000-0005-0000-0000-000063040000}"/>
-    <cellStyle name="常规 10 2 4" xfId="169" xr:uid="{00000000-0005-0000-0000-000064040000}"/>
-    <cellStyle name="常规 10 2 4 2" xfId="490" xr:uid="{00000000-0005-0000-0000-000065040000}"/>
-    <cellStyle name="常规 10 2 4 2 2" xfId="1035" xr:uid="{00000000-0005-0000-0000-000066040000}"/>
-    <cellStyle name="常规 10 2 4 2 2 2" xfId="459" xr:uid="{00000000-0005-0000-0000-000067040000}"/>
-    <cellStyle name="常规 10 2 4 2 3" xfId="1036" xr:uid="{00000000-0005-0000-0000-000068040000}"/>
-    <cellStyle name="常规 10 2 4 2 4" xfId="1037" xr:uid="{00000000-0005-0000-0000-000069040000}"/>
-    <cellStyle name="常规 10 2 4 2 5" xfId="1038" xr:uid="{00000000-0005-0000-0000-00006A040000}"/>
-    <cellStyle name="常规 10 2 4 3" xfId="1039" xr:uid="{00000000-0005-0000-0000-00006B040000}"/>
-    <cellStyle name="常规 10 2 4 3 2" xfId="1040" xr:uid="{00000000-0005-0000-0000-00006C040000}"/>
-    <cellStyle name="常规 10 2 4 3 2 2" xfId="1041" xr:uid="{00000000-0005-0000-0000-00006D040000}"/>
-    <cellStyle name="常规 10 2 4 3 3" xfId="1042" xr:uid="{00000000-0005-0000-0000-00006E040000}"/>
-    <cellStyle name="常规 10 2 4 3 4" xfId="1043" xr:uid="{00000000-0005-0000-0000-00006F040000}"/>
-    <cellStyle name="常规 10 2 4 3 5" xfId="1044" xr:uid="{00000000-0005-0000-0000-000070040000}"/>
-    <cellStyle name="常规 10 2 4 3 6" xfId="1046" xr:uid="{00000000-0005-0000-0000-000071040000}"/>
-    <cellStyle name="常规 10 2 4 4" xfId="1047" xr:uid="{00000000-0005-0000-0000-000072040000}"/>
-    <cellStyle name="常规 10 2 4 4 2" xfId="1048" xr:uid="{00000000-0005-0000-0000-000073040000}"/>
-    <cellStyle name="常规 10 2 4 5" xfId="1049" xr:uid="{00000000-0005-0000-0000-000074040000}"/>
-    <cellStyle name="常规 10 2 4 6" xfId="1050" xr:uid="{00000000-0005-0000-0000-000075040000}"/>
-    <cellStyle name="常规 10 2 4 7" xfId="1051" xr:uid="{00000000-0005-0000-0000-000076040000}"/>
-    <cellStyle name="常规 10 2 5" xfId="173" xr:uid="{00000000-0005-0000-0000-000077040000}"/>
-    <cellStyle name="常规 10 2 5 2" xfId="1052" xr:uid="{00000000-0005-0000-0000-000078040000}"/>
-    <cellStyle name="常规 10 2 5 2 2" xfId="1053" xr:uid="{00000000-0005-0000-0000-000079040000}"/>
-    <cellStyle name="常规 10 2 5 3" xfId="1054" xr:uid="{00000000-0005-0000-0000-00007A040000}"/>
-    <cellStyle name="常规 10 2 5 4" xfId="1055" xr:uid="{00000000-0005-0000-0000-00007B040000}"/>
-    <cellStyle name="常规 10 2 5 5" xfId="1056" xr:uid="{00000000-0005-0000-0000-00007C040000}"/>
-    <cellStyle name="常规 10 2 5 6" xfId="1057" xr:uid="{00000000-0005-0000-0000-00007D040000}"/>
-    <cellStyle name="常规 10 2 6" xfId="1058" xr:uid="{00000000-0005-0000-0000-00007E040000}"/>
-    <cellStyle name="常规 10 2 6 2" xfId="1059" xr:uid="{00000000-0005-0000-0000-00007F040000}"/>
-    <cellStyle name="常规 10 2 7" xfId="1060" xr:uid="{00000000-0005-0000-0000-000080040000}"/>
-    <cellStyle name="常规 10 2 8" xfId="1061" xr:uid="{00000000-0005-0000-0000-000081040000}"/>
-    <cellStyle name="常规 10 2 9" xfId="1062" xr:uid="{00000000-0005-0000-0000-000082040000}"/>
-    <cellStyle name="常规 10 3" xfId="447" xr:uid="{00000000-0005-0000-0000-000083040000}"/>
-    <cellStyle name="常规 10 3 2" xfId="1063" xr:uid="{00000000-0005-0000-0000-000084040000}"/>
-    <cellStyle name="常规 10 3 2 2" xfId="1064" xr:uid="{00000000-0005-0000-0000-000085040000}"/>
-    <cellStyle name="常规 10 3 2 2 2" xfId="1065" xr:uid="{00000000-0005-0000-0000-000086040000}"/>
-    <cellStyle name="常规 10 3 2 3" xfId="1066" xr:uid="{00000000-0005-0000-0000-000087040000}"/>
-    <cellStyle name="常规 10 3 2 4" xfId="1067" xr:uid="{00000000-0005-0000-0000-000088040000}"/>
-    <cellStyle name="常规 10 3 2 5" xfId="1068" xr:uid="{00000000-0005-0000-0000-000089040000}"/>
-    <cellStyle name="常规 10 3 3" xfId="1069" xr:uid="{00000000-0005-0000-0000-00008A040000}"/>
-    <cellStyle name="常规 10 3 3 2" xfId="1070" xr:uid="{00000000-0005-0000-0000-00008B040000}"/>
-    <cellStyle name="常规 10 3 3 2 2" xfId="1071" xr:uid="{00000000-0005-0000-0000-00008C040000}"/>
-    <cellStyle name="常规 10 3 3 3" xfId="1072" xr:uid="{00000000-0005-0000-0000-00008D040000}"/>
-    <cellStyle name="常规 10 3 3 4" xfId="1073" xr:uid="{00000000-0005-0000-0000-00008E040000}"/>
-    <cellStyle name="常规 10 3 3 5" xfId="1074" xr:uid="{00000000-0005-0000-0000-00008F040000}"/>
-    <cellStyle name="常规 10 3 3 6" xfId="1075" xr:uid="{00000000-0005-0000-0000-000090040000}"/>
-    <cellStyle name="常规 10 3 4" xfId="1076" xr:uid="{00000000-0005-0000-0000-000091040000}"/>
-    <cellStyle name="常规 10 3 4 2" xfId="1077" xr:uid="{00000000-0005-0000-0000-000092040000}"/>
-    <cellStyle name="常规 10 3 5" xfId="1078" xr:uid="{00000000-0005-0000-0000-000093040000}"/>
-    <cellStyle name="常规 10 3 6" xfId="1079" xr:uid="{00000000-0005-0000-0000-000094040000}"/>
-    <cellStyle name="常规 10 3 7" xfId="1080" xr:uid="{00000000-0005-0000-0000-000095040000}"/>
-    <cellStyle name="常规 10 4" xfId="449" xr:uid="{00000000-0005-0000-0000-000096040000}"/>
-    <cellStyle name="常规 10 4 2" xfId="1081" xr:uid="{00000000-0005-0000-0000-000097040000}"/>
-    <cellStyle name="常规 10 4 2 2" xfId="1082" xr:uid="{00000000-0005-0000-0000-000098040000}"/>
-    <cellStyle name="常规 10 4 2 2 2" xfId="1083" xr:uid="{00000000-0005-0000-0000-000099040000}"/>
-    <cellStyle name="常规 10 4 2 3" xfId="1084" xr:uid="{00000000-0005-0000-0000-00009A040000}"/>
-    <cellStyle name="常规 10 4 2 4" xfId="1085" xr:uid="{00000000-0005-0000-0000-00009B040000}"/>
-    <cellStyle name="常规 10 4 2 5" xfId="1086" xr:uid="{00000000-0005-0000-0000-00009C040000}"/>
-    <cellStyle name="常规 10 4 3" xfId="1087" xr:uid="{00000000-0005-0000-0000-00009D040000}"/>
-    <cellStyle name="常规 10 4 3 2" xfId="1088" xr:uid="{00000000-0005-0000-0000-00009E040000}"/>
-    <cellStyle name="常规 10 4 3 2 2" xfId="1090" xr:uid="{00000000-0005-0000-0000-00009F040000}"/>
-    <cellStyle name="常规 10 4 3 3" xfId="1091" xr:uid="{00000000-0005-0000-0000-0000A0040000}"/>
-    <cellStyle name="常规 10 4 3 4" xfId="1092" xr:uid="{00000000-0005-0000-0000-0000A1040000}"/>
-    <cellStyle name="常规 10 4 3 5" xfId="1093" xr:uid="{00000000-0005-0000-0000-0000A2040000}"/>
-    <cellStyle name="常规 10 4 3 6" xfId="1094" xr:uid="{00000000-0005-0000-0000-0000A3040000}"/>
-    <cellStyle name="常规 10 4 4" xfId="1095" xr:uid="{00000000-0005-0000-0000-0000A4040000}"/>
-    <cellStyle name="常规 10 4 4 2" xfId="1096" xr:uid="{00000000-0005-0000-0000-0000A5040000}"/>
-    <cellStyle name="常规 10 4 5" xfId="1097" xr:uid="{00000000-0005-0000-0000-0000A6040000}"/>
-    <cellStyle name="常规 10 4 6" xfId="1098" xr:uid="{00000000-0005-0000-0000-0000A7040000}"/>
-    <cellStyle name="常规 10 4 7" xfId="1099" xr:uid="{00000000-0005-0000-0000-0000A8040000}"/>
-    <cellStyle name="常规 10 5" xfId="451" xr:uid="{00000000-0005-0000-0000-0000A9040000}"/>
-    <cellStyle name="常规 10 5 2" xfId="1100" xr:uid="{00000000-0005-0000-0000-0000AA040000}"/>
-    <cellStyle name="常规 10 5 2 2" xfId="1101" xr:uid="{00000000-0005-0000-0000-0000AB040000}"/>
-    <cellStyle name="常规 10 5 2 2 2" xfId="1103" xr:uid="{00000000-0005-0000-0000-0000AC040000}"/>
-    <cellStyle name="常规 10 5 2 3" xfId="1104" xr:uid="{00000000-0005-0000-0000-0000AD040000}"/>
-    <cellStyle name="常规 10 5 2 4" xfId="1105" xr:uid="{00000000-0005-0000-0000-0000AE040000}"/>
-    <cellStyle name="常规 10 5 2 5" xfId="1106" xr:uid="{00000000-0005-0000-0000-0000AF040000}"/>
-    <cellStyle name="常规 10 5 3" xfId="1107" xr:uid="{00000000-0005-0000-0000-0000B0040000}"/>
-    <cellStyle name="常规 10 5 3 2" xfId="1108" xr:uid="{00000000-0005-0000-0000-0000B1040000}"/>
-    <cellStyle name="常规 10 5 3 2 2" xfId="1109" xr:uid="{00000000-0005-0000-0000-0000B2040000}"/>
-    <cellStyle name="常规 10 5 3 3" xfId="1110" xr:uid="{00000000-0005-0000-0000-0000B3040000}"/>
-    <cellStyle name="常规 10 5 3 4" xfId="1111" xr:uid="{00000000-0005-0000-0000-0000B4040000}"/>
-    <cellStyle name="常规 10 5 3 5" xfId="1112" xr:uid="{00000000-0005-0000-0000-0000B5040000}"/>
-    <cellStyle name="常规 10 5 3 6" xfId="1113" xr:uid="{00000000-0005-0000-0000-0000B6040000}"/>
-    <cellStyle name="常规 10 5 4" xfId="1114" xr:uid="{00000000-0005-0000-0000-0000B7040000}"/>
-    <cellStyle name="常规 10 5 4 2" xfId="1115" xr:uid="{00000000-0005-0000-0000-0000B8040000}"/>
-    <cellStyle name="常规 10 5 5" xfId="1116" xr:uid="{00000000-0005-0000-0000-0000B9040000}"/>
-    <cellStyle name="常规 10 5 6" xfId="1118" xr:uid="{00000000-0005-0000-0000-0000BA040000}"/>
-    <cellStyle name="常规 10 5 7" xfId="1120" xr:uid="{00000000-0005-0000-0000-0000BB040000}"/>
-    <cellStyle name="常规 10 6" xfId="453" xr:uid="{00000000-0005-0000-0000-0000BC040000}"/>
-    <cellStyle name="常规 10 6 2" xfId="1121" xr:uid="{00000000-0005-0000-0000-0000BD040000}"/>
-    <cellStyle name="常规 10 6 2 2" xfId="1122" xr:uid="{00000000-0005-0000-0000-0000BE040000}"/>
-    <cellStyle name="常规 10 6 3" xfId="1123" xr:uid="{00000000-0005-0000-0000-0000BF040000}"/>
-    <cellStyle name="常规 10 6 4" xfId="1124" xr:uid="{00000000-0005-0000-0000-0000C0040000}"/>
-    <cellStyle name="常规 10 6 5" xfId="1125" xr:uid="{00000000-0005-0000-0000-0000C1040000}"/>
-    <cellStyle name="常规 10 6 6" xfId="429" xr:uid="{00000000-0005-0000-0000-0000C2040000}"/>
-    <cellStyle name="常规 10 7" xfId="1126" xr:uid="{00000000-0005-0000-0000-0000C3040000}"/>
-    <cellStyle name="常规 10 7 2" xfId="1127" xr:uid="{00000000-0005-0000-0000-0000C4040000}"/>
-    <cellStyle name="常规 10 7 2 2" xfId="1128" xr:uid="{00000000-0005-0000-0000-0000C5040000}"/>
-    <cellStyle name="常规 10 7 3" xfId="1129" xr:uid="{00000000-0005-0000-0000-0000C6040000}"/>
-    <cellStyle name="常规 10 7 4" xfId="1130" xr:uid="{00000000-0005-0000-0000-0000C7040000}"/>
-    <cellStyle name="常规 10 7 5" xfId="1131" xr:uid="{00000000-0005-0000-0000-0000C8040000}"/>
-    <cellStyle name="常规 10 7 6" xfId="1133" xr:uid="{00000000-0005-0000-0000-0000C9040000}"/>
-    <cellStyle name="常规 10 8" xfId="1134" xr:uid="{00000000-0005-0000-0000-0000CA040000}"/>
-    <cellStyle name="常规 10 8 2" xfId="1135" xr:uid="{00000000-0005-0000-0000-0000CB040000}"/>
-    <cellStyle name="常规 10 8 3" xfId="1136" xr:uid="{00000000-0005-0000-0000-0000CC040000}"/>
-    <cellStyle name="常规 10 8 4" xfId="1137" xr:uid="{00000000-0005-0000-0000-0000CD040000}"/>
-    <cellStyle name="常规 10 8 5" xfId="1138" xr:uid="{00000000-0005-0000-0000-0000CE040000}"/>
-    <cellStyle name="常规 10 9" xfId="1139" xr:uid="{00000000-0005-0000-0000-0000CF040000}"/>
-    <cellStyle name="常规 11" xfId="455" xr:uid="{00000000-0005-0000-0000-0000D0040000}"/>
-    <cellStyle name="常规 11 2" xfId="457" xr:uid="{00000000-0005-0000-0000-0000D1040000}"/>
-    <cellStyle name="常规 11 3" xfId="1647" xr:uid="{00000000-0005-0000-0000-0000D2040000}"/>
-    <cellStyle name="常规 12" xfId="463" xr:uid="{00000000-0005-0000-0000-0000D3040000}"/>
-    <cellStyle name="常规 12 2" xfId="745" xr:uid="{00000000-0005-0000-0000-0000D4040000}"/>
-    <cellStyle name="常规 13" xfId="363" xr:uid="{00000000-0005-0000-0000-0000D5040000}"/>
-    <cellStyle name="常规 13 2" xfId="753" xr:uid="{00000000-0005-0000-0000-0000D6040000}"/>
-    <cellStyle name="常规 14" xfId="405" xr:uid="{00000000-0005-0000-0000-0000D7040000}"/>
-    <cellStyle name="常规 14 2" xfId="1140" xr:uid="{00000000-0005-0000-0000-0000D8040000}"/>
-    <cellStyle name="常规 15" xfId="5" xr:uid="{00000000-0005-0000-0000-0000D9040000}"/>
-    <cellStyle name="常规 15 2" xfId="1142" xr:uid="{00000000-0005-0000-0000-0000DA040000}"/>
-    <cellStyle name="常规 15 2 2" xfId="1143" xr:uid="{00000000-0005-0000-0000-0000DB040000}"/>
-    <cellStyle name="常规 15 2 2 2" xfId="1144" xr:uid="{00000000-0005-0000-0000-0000DC040000}"/>
-    <cellStyle name="常规 15 2 2 3" xfId="1145" xr:uid="{00000000-0005-0000-0000-0000DD040000}"/>
-    <cellStyle name="常规 15 2 2 4" xfId="1146" xr:uid="{00000000-0005-0000-0000-0000DE040000}"/>
-    <cellStyle name="常规 15 2 2 5" xfId="1147" xr:uid="{00000000-0005-0000-0000-0000DF040000}"/>
-    <cellStyle name="常规 15 2 3" xfId="1148" xr:uid="{00000000-0005-0000-0000-0000E0040000}"/>
-    <cellStyle name="常规 15 2 4" xfId="897" xr:uid="{00000000-0005-0000-0000-0000E1040000}"/>
-    <cellStyle name="常规 15 2 5" xfId="907" xr:uid="{00000000-0005-0000-0000-0000E2040000}"/>
-    <cellStyle name="常规 15 2 6" xfId="909" xr:uid="{00000000-0005-0000-0000-0000E3040000}"/>
-    <cellStyle name="常规 15 3" xfId="1151" xr:uid="{00000000-0005-0000-0000-0000E4040000}"/>
-    <cellStyle name="常规 15 3 2" xfId="1152" xr:uid="{00000000-0005-0000-0000-0000E5040000}"/>
-    <cellStyle name="常规 15 3 3" xfId="1153" xr:uid="{00000000-0005-0000-0000-0000E6040000}"/>
-    <cellStyle name="常规 15 3 4" xfId="914" xr:uid="{00000000-0005-0000-0000-0000E7040000}"/>
-    <cellStyle name="常规 15 3 5" xfId="917" xr:uid="{00000000-0005-0000-0000-0000E8040000}"/>
-    <cellStyle name="常规 15 4" xfId="1155" xr:uid="{00000000-0005-0000-0000-0000E9040000}"/>
-    <cellStyle name="常规 15 5" xfId="1157" xr:uid="{00000000-0005-0000-0000-0000EA040000}"/>
-    <cellStyle name="常规 15 6" xfId="1159" xr:uid="{00000000-0005-0000-0000-0000EB040000}"/>
-    <cellStyle name="常规 15 7" xfId="1160" xr:uid="{00000000-0005-0000-0000-0000EC040000}"/>
-    <cellStyle name="常规 15 8" xfId="239" xr:uid="{00000000-0005-0000-0000-0000ED040000}"/>
-    <cellStyle name="常规 16" xfId="1162" xr:uid="{00000000-0005-0000-0000-0000EE040000}"/>
-    <cellStyle name="常规 16 2" xfId="1164" xr:uid="{00000000-0005-0000-0000-0000EF040000}"/>
-    <cellStyle name="常规 16 2 2" xfId="1165" xr:uid="{00000000-0005-0000-0000-0000F0040000}"/>
-    <cellStyle name="常规 16 2 2 2" xfId="1167" xr:uid="{00000000-0005-0000-0000-0000F1040000}"/>
-    <cellStyle name="常规 16 2 2 3" xfId="1169" xr:uid="{00000000-0005-0000-0000-0000F2040000}"/>
-    <cellStyle name="常规 16 2 2 4" xfId="171" xr:uid="{00000000-0005-0000-0000-0000F3040000}"/>
-    <cellStyle name="常规 16 2 2 5" xfId="175" xr:uid="{00000000-0005-0000-0000-0000F4040000}"/>
-    <cellStyle name="常规 16 2 3" xfId="1170" xr:uid="{00000000-0005-0000-0000-0000F5040000}"/>
-    <cellStyle name="常规 16 2 4" xfId="932" xr:uid="{00000000-0005-0000-0000-0000F6040000}"/>
-    <cellStyle name="常规 16 2 5" xfId="934" xr:uid="{00000000-0005-0000-0000-0000F7040000}"/>
-    <cellStyle name="常规 16 2 6" xfId="936" xr:uid="{00000000-0005-0000-0000-0000F8040000}"/>
-    <cellStyle name="常规 16 3" xfId="1171" xr:uid="{00000000-0005-0000-0000-0000F9040000}"/>
-    <cellStyle name="常规 16 3 2" xfId="1172" xr:uid="{00000000-0005-0000-0000-0000FA040000}"/>
-    <cellStyle name="常规 16 3 3" xfId="1173" xr:uid="{00000000-0005-0000-0000-0000FB040000}"/>
-    <cellStyle name="常规 16 3 4" xfId="1174" xr:uid="{00000000-0005-0000-0000-0000FC040000}"/>
-    <cellStyle name="常规 16 3 5" xfId="1175" xr:uid="{00000000-0005-0000-0000-0000FD040000}"/>
-    <cellStyle name="常规 16 4" xfId="1176" xr:uid="{00000000-0005-0000-0000-0000FE040000}"/>
-    <cellStyle name="常规 16 5" xfId="1177" xr:uid="{00000000-0005-0000-0000-0000FF040000}"/>
-    <cellStyle name="常规 16 6" xfId="1178" xr:uid="{00000000-0005-0000-0000-000000050000}"/>
-    <cellStyle name="常规 16 7" xfId="1179" xr:uid="{00000000-0005-0000-0000-000001050000}"/>
-    <cellStyle name="常规 17" xfId="1181" xr:uid="{00000000-0005-0000-0000-000002050000}"/>
-    <cellStyle name="常规 17 2" xfId="1183" xr:uid="{00000000-0005-0000-0000-000003050000}"/>
-    <cellStyle name="常规 17 3" xfId="1185" xr:uid="{00000000-0005-0000-0000-000004050000}"/>
-    <cellStyle name="常规 18" xfId="1187" xr:uid="{00000000-0005-0000-0000-000005050000}"/>
-    <cellStyle name="常规 18 2" xfId="1189" xr:uid="{00000000-0005-0000-0000-000006050000}"/>
-    <cellStyle name="常规 18 3" xfId="1191" xr:uid="{00000000-0005-0000-0000-000007050000}"/>
-    <cellStyle name="常规 19" xfId="1193" xr:uid="{00000000-0005-0000-0000-000008050000}"/>
-    <cellStyle name="常规 19 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000009050000}"/>
-    <cellStyle name="常规 19 3" xfId="1195" xr:uid="{00000000-0005-0000-0000-00000A050000}"/>
-    <cellStyle name="常规 2" xfId="1196" xr:uid="{00000000-0005-0000-0000-00000B050000}"/>
-    <cellStyle name="常规 2 10" xfId="1658" xr:uid="{00000000-0005-0000-0000-00000C050000}"/>
-    <cellStyle name="常规 2 2" xfId="1197" xr:uid="{00000000-0005-0000-0000-00000D050000}"/>
-    <cellStyle name="常规 2 2 2" xfId="1198" xr:uid="{00000000-0005-0000-0000-00000E050000}"/>
-    <cellStyle name="常规 2 2 2 2" xfId="1117" xr:uid="{00000000-0005-0000-0000-00000F050000}"/>
-    <cellStyle name="常规 2 2 2 2 2" xfId="1199" xr:uid="{00000000-0005-0000-0000-000010050000}"/>
-    <cellStyle name="常规 2 2 2 2 3" xfId="1200" xr:uid="{00000000-0005-0000-0000-000011050000}"/>
-    <cellStyle name="常规 2 2 2 2 4" xfId="1201" xr:uid="{00000000-0005-0000-0000-000012050000}"/>
-    <cellStyle name="常规 2 2 2 2 5" xfId="1202" xr:uid="{00000000-0005-0000-0000-000013050000}"/>
-    <cellStyle name="常规 2 2 2 3" xfId="1119" xr:uid="{00000000-0005-0000-0000-000014050000}"/>
-    <cellStyle name="常规 2 2 2 4" xfId="61" xr:uid="{00000000-0005-0000-0000-000015050000}"/>
-    <cellStyle name="常规 2 2 2 5" xfId="50" xr:uid="{00000000-0005-0000-0000-000016050000}"/>
-    <cellStyle name="常规 2 2 2 6" xfId="63" xr:uid="{00000000-0005-0000-0000-000017050000}"/>
-    <cellStyle name="常规 2 2 3" xfId="567" xr:uid="{00000000-0005-0000-0000-000018050000}"/>
-    <cellStyle name="常规 2 2 3 2" xfId="428" xr:uid="{00000000-0005-0000-0000-000019050000}"/>
-    <cellStyle name="常规 2 2 3 2 2" xfId="1204" xr:uid="{00000000-0005-0000-0000-00001A050000}"/>
-    <cellStyle name="常规 2 2 3 2 3" xfId="1206" xr:uid="{00000000-0005-0000-0000-00001B050000}"/>
-    <cellStyle name="常规 2 2 3 2 4" xfId="513" xr:uid="{00000000-0005-0000-0000-00001C050000}"/>
-    <cellStyle name="常规 2 2 3 2 5" xfId="1208" xr:uid="{00000000-0005-0000-0000-00001D050000}"/>
-    <cellStyle name="常规 2 2 3 3" xfId="432" xr:uid="{00000000-0005-0000-0000-00001E050000}"/>
-    <cellStyle name="常规 2 2 3 4" xfId="435" xr:uid="{00000000-0005-0000-0000-00001F050000}"/>
-    <cellStyle name="常规 2 2 3 5" xfId="569" xr:uid="{00000000-0005-0000-0000-000020050000}"/>
-    <cellStyle name="常规 2 2 3 6" xfId="1209" xr:uid="{00000000-0005-0000-0000-000021050000}"/>
-    <cellStyle name="常规 2 2 4" xfId="25" xr:uid="{00000000-0005-0000-0000-000022050000}"/>
-    <cellStyle name="常规 2 2 4 2" xfId="1132" xr:uid="{00000000-0005-0000-0000-000023050000}"/>
-    <cellStyle name="常规 2 2 4 3" xfId="1210" xr:uid="{00000000-0005-0000-0000-000024050000}"/>
-    <cellStyle name="常规 2 2 4 4" xfId="1211" xr:uid="{00000000-0005-0000-0000-000025050000}"/>
-    <cellStyle name="常规 2 2 4 5" xfId="1212" xr:uid="{00000000-0005-0000-0000-000026050000}"/>
-    <cellStyle name="常规 2 2 5" xfId="571" xr:uid="{00000000-0005-0000-0000-000027050000}"/>
-    <cellStyle name="常规 2 2 6" xfId="573" xr:uid="{00000000-0005-0000-0000-000028050000}"/>
-    <cellStyle name="常规 2 2 7" xfId="575" xr:uid="{00000000-0005-0000-0000-000029050000}"/>
-    <cellStyle name="常规 2 2 8" xfId="1213" xr:uid="{00000000-0005-0000-0000-00002A050000}"/>
-    <cellStyle name="常规 2 3" xfId="1214" xr:uid="{00000000-0005-0000-0000-00002B050000}"/>
-    <cellStyle name="常规 2 3 2" xfId="1215" xr:uid="{00000000-0005-0000-0000-00002C050000}"/>
-    <cellStyle name="常规 2 3 2 2" xfId="1216" xr:uid="{00000000-0005-0000-0000-00002D050000}"/>
-    <cellStyle name="常规 2 3 2 3" xfId="1217" xr:uid="{00000000-0005-0000-0000-00002E050000}"/>
-    <cellStyle name="常规 2 3 2 4" xfId="1218" xr:uid="{00000000-0005-0000-0000-00002F050000}"/>
-    <cellStyle name="常规 2 3 2 5" xfId="1219" xr:uid="{00000000-0005-0000-0000-000030050000}"/>
-    <cellStyle name="常规 2 3 3" xfId="577" xr:uid="{00000000-0005-0000-0000-000031050000}"/>
-    <cellStyle name="常规 2 3 4" xfId="416" xr:uid="{00000000-0005-0000-0000-000032050000}"/>
-    <cellStyle name="常规 2 3 5" xfId="419" xr:uid="{00000000-0005-0000-0000-000033050000}"/>
-    <cellStyle name="常规 2 3 6" xfId="422" xr:uid="{00000000-0005-0000-0000-000034050000}"/>
-    <cellStyle name="常规 2 4" xfId="1220" xr:uid="{00000000-0005-0000-0000-000035050000}"/>
-    <cellStyle name="常规 2 4 2" xfId="1221" xr:uid="{00000000-0005-0000-0000-000036050000}"/>
-    <cellStyle name="常规 2 4 2 2" xfId="1222" xr:uid="{00000000-0005-0000-0000-000037050000}"/>
-    <cellStyle name="常规 2 4 2 3" xfId="1223" xr:uid="{00000000-0005-0000-0000-000038050000}"/>
-    <cellStyle name="常规 2 4 2 4" xfId="1224" xr:uid="{00000000-0005-0000-0000-000039050000}"/>
-    <cellStyle name="常规 2 4 2 5" xfId="1225" xr:uid="{00000000-0005-0000-0000-00003A050000}"/>
-    <cellStyle name="常规 2 4 3" xfId="1226" xr:uid="{00000000-0005-0000-0000-00003B050000}"/>
-    <cellStyle name="常规 2 4 4" xfId="1227" xr:uid="{00000000-0005-0000-0000-00003C050000}"/>
-    <cellStyle name="常规 2 4 5" xfId="1228" xr:uid="{00000000-0005-0000-0000-00003D050000}"/>
-    <cellStyle name="常规 2 4 6" xfId="1229" xr:uid="{00000000-0005-0000-0000-00003E050000}"/>
-    <cellStyle name="常规 2 5" xfId="1230" xr:uid="{00000000-0005-0000-0000-00003F050000}"/>
-    <cellStyle name="常规 2 5 2" xfId="1231" xr:uid="{00000000-0005-0000-0000-000040050000}"/>
-    <cellStyle name="常规 2 5 2 2" xfId="1232" xr:uid="{00000000-0005-0000-0000-000041050000}"/>
-    <cellStyle name="常规 2 5 2 3" xfId="1233" xr:uid="{00000000-0005-0000-0000-000042050000}"/>
-    <cellStyle name="常规 2 5 2 4" xfId="1234" xr:uid="{00000000-0005-0000-0000-000043050000}"/>
-    <cellStyle name="常规 2 5 2 5" xfId="1000" xr:uid="{00000000-0005-0000-0000-000044050000}"/>
-    <cellStyle name="常规 2 5 3" xfId="1235" xr:uid="{00000000-0005-0000-0000-000045050000}"/>
-    <cellStyle name="常规 2 5 4" xfId="1236" xr:uid="{00000000-0005-0000-0000-000046050000}"/>
-    <cellStyle name="常规 2 5 5" xfId="1237" xr:uid="{00000000-0005-0000-0000-000047050000}"/>
-    <cellStyle name="常规 2 5 6" xfId="1238" xr:uid="{00000000-0005-0000-0000-000048050000}"/>
-    <cellStyle name="常规 2 6" xfId="1239" xr:uid="{00000000-0005-0000-0000-000049050000}"/>
-    <cellStyle name="常规 2 6 2" xfId="1240" xr:uid="{00000000-0005-0000-0000-00004A050000}"/>
-    <cellStyle name="常规 2 6 3" xfId="1241" xr:uid="{00000000-0005-0000-0000-00004B050000}"/>
-    <cellStyle name="常规 2 6 4" xfId="1242" xr:uid="{00000000-0005-0000-0000-00004C050000}"/>
-    <cellStyle name="常规 2 6 5" xfId="1243" xr:uid="{00000000-0005-0000-0000-00004D050000}"/>
-    <cellStyle name="常规 2 7" xfId="1166" xr:uid="{00000000-0005-0000-0000-00004E050000}"/>
-    <cellStyle name="常规 2 7 2" xfId="1244" xr:uid="{00000000-0005-0000-0000-00004F050000}"/>
-    <cellStyle name="常规 2 7 3" xfId="1245" xr:uid="{00000000-0005-0000-0000-000050050000}"/>
-    <cellStyle name="常规 2 7 4" xfId="1246" xr:uid="{00000000-0005-0000-0000-000051050000}"/>
-    <cellStyle name="常规 2 8" xfId="1168" xr:uid="{00000000-0005-0000-0000-000052050000}"/>
-    <cellStyle name="常规 2 8 2" xfId="967" xr:uid="{00000000-0005-0000-0000-000053050000}"/>
-    <cellStyle name="常规 2 8 3" xfId="969" xr:uid="{00000000-0005-0000-0000-000054050000}"/>
-    <cellStyle name="常规 2 9" xfId="1648" xr:uid="{00000000-0005-0000-0000-000055050000}"/>
-    <cellStyle name="常规 20" xfId="238" xr:uid="{00000000-0005-0000-0000-000056050000}"/>
-    <cellStyle name="常规 20 2" xfId="1141" xr:uid="{00000000-0005-0000-0000-000057050000}"/>
-    <cellStyle name="常规 20 3" xfId="1150" xr:uid="{00000000-0005-0000-0000-000058050000}"/>
-    <cellStyle name="常规 21" xfId="1161" xr:uid="{00000000-0005-0000-0000-000059050000}"/>
-    <cellStyle name="常规 21 2" xfId="1163" xr:uid="{00000000-0005-0000-0000-00005A050000}"/>
-    <cellStyle name="常规 22" xfId="1180" xr:uid="{00000000-0005-0000-0000-00005B050000}"/>
-    <cellStyle name="常规 22 2" xfId="1182" xr:uid="{00000000-0005-0000-0000-00005C050000}"/>
-    <cellStyle name="常规 22 2 2" xfId="1247" xr:uid="{00000000-0005-0000-0000-00005D050000}"/>
-    <cellStyle name="常规 22 2 3" xfId="1248" xr:uid="{00000000-0005-0000-0000-00005E050000}"/>
-    <cellStyle name="常规 22 2 4" xfId="1249" xr:uid="{00000000-0005-0000-0000-00005F050000}"/>
-    <cellStyle name="常规 22 2 5" xfId="103" xr:uid="{00000000-0005-0000-0000-000060050000}"/>
-    <cellStyle name="常规 22 3" xfId="1184" xr:uid="{00000000-0005-0000-0000-000061050000}"/>
-    <cellStyle name="常规 22 4" xfId="1250" xr:uid="{00000000-0005-0000-0000-000062050000}"/>
-    <cellStyle name="常规 22 5" xfId="1251" xr:uid="{00000000-0005-0000-0000-000063050000}"/>
-    <cellStyle name="常规 22 6" xfId="1252" xr:uid="{00000000-0005-0000-0000-000064050000}"/>
-    <cellStyle name="常规 23" xfId="1186" xr:uid="{00000000-0005-0000-0000-000065050000}"/>
-    <cellStyle name="常规 23 2" xfId="1188" xr:uid="{00000000-0005-0000-0000-000066050000}"/>
-    <cellStyle name="常规 23 2 2" xfId="1253" xr:uid="{00000000-0005-0000-0000-000067050000}"/>
-    <cellStyle name="常规 23 2 3" xfId="1254" xr:uid="{00000000-0005-0000-0000-000068050000}"/>
-    <cellStyle name="常规 23 2 4" xfId="1255" xr:uid="{00000000-0005-0000-0000-000069050000}"/>
-    <cellStyle name="常规 23 2 5" xfId="142" xr:uid="{00000000-0005-0000-0000-00006A050000}"/>
-    <cellStyle name="常规 23 3" xfId="1190" xr:uid="{00000000-0005-0000-0000-00006B050000}"/>
-    <cellStyle name="常规 23 4" xfId="1256" xr:uid="{00000000-0005-0000-0000-00006C050000}"/>
-    <cellStyle name="常规 23 5" xfId="1257" xr:uid="{00000000-0005-0000-0000-00006D050000}"/>
-    <cellStyle name="常规 23 6" xfId="1258" xr:uid="{00000000-0005-0000-0000-00006E050000}"/>
-    <cellStyle name="常规 24" xfId="1192" xr:uid="{00000000-0005-0000-0000-00006F050000}"/>
-    <cellStyle name="常规 24 2" xfId="1194" xr:uid="{00000000-0005-0000-0000-000070050000}"/>
-    <cellStyle name="常规 25" xfId="1260" xr:uid="{00000000-0005-0000-0000-000071050000}"/>
-    <cellStyle name="常规 25 2" xfId="1261" xr:uid="{00000000-0005-0000-0000-000072050000}"/>
-    <cellStyle name="常规 26" xfId="1263" xr:uid="{00000000-0005-0000-0000-000073050000}"/>
-    <cellStyle name="常规 26 2" xfId="31" xr:uid="{00000000-0005-0000-0000-000074050000}"/>
-    <cellStyle name="常规 27" xfId="1265" xr:uid="{00000000-0005-0000-0000-000075050000}"/>
-    <cellStyle name="常规 27 2" xfId="1267" xr:uid="{00000000-0005-0000-0000-000076050000}"/>
-    <cellStyle name="常规 27 2 2" xfId="1268" xr:uid="{00000000-0005-0000-0000-000077050000}"/>
-    <cellStyle name="常规 27 2 3" xfId="1269" xr:uid="{00000000-0005-0000-0000-000078050000}"/>
-    <cellStyle name="常规 27 2 4" xfId="1270" xr:uid="{00000000-0005-0000-0000-000079050000}"/>
-    <cellStyle name="常规 27 2 5" xfId="1271" xr:uid="{00000000-0005-0000-0000-00007A050000}"/>
-    <cellStyle name="常规 27 3" xfId="1273" xr:uid="{00000000-0005-0000-0000-00007B050000}"/>
-    <cellStyle name="常规 27 4" xfId="1275" xr:uid="{00000000-0005-0000-0000-00007C050000}"/>
-    <cellStyle name="常规 27 5" xfId="1277" xr:uid="{00000000-0005-0000-0000-00007D050000}"/>
-    <cellStyle name="常规 27 6" xfId="1278" xr:uid="{00000000-0005-0000-0000-00007E050000}"/>
-    <cellStyle name="常规 28" xfId="1280" xr:uid="{00000000-0005-0000-0000-00007F050000}"/>
-    <cellStyle name="常规 28 2" xfId="153" xr:uid="{00000000-0005-0000-0000-000080050000}"/>
-    <cellStyle name="常规 28 2 2" xfId="1281" xr:uid="{00000000-0005-0000-0000-000081050000}"/>
-    <cellStyle name="常规 28 2 3" xfId="1282" xr:uid="{00000000-0005-0000-0000-000082050000}"/>
-    <cellStyle name="常规 28 2 4" xfId="1283" xr:uid="{00000000-0005-0000-0000-000083050000}"/>
-    <cellStyle name="常规 28 2 5" xfId="1284" xr:uid="{00000000-0005-0000-0000-000084050000}"/>
-    <cellStyle name="常规 28 3" xfId="161" xr:uid="{00000000-0005-0000-0000-000085050000}"/>
-    <cellStyle name="常规 28 4" xfId="1285" xr:uid="{00000000-0005-0000-0000-000086050000}"/>
-    <cellStyle name="常规 28 5" xfId="1286" xr:uid="{00000000-0005-0000-0000-000087050000}"/>
-    <cellStyle name="常规 28 6" xfId="1288" xr:uid="{00000000-0005-0000-0000-000088050000}"/>
-    <cellStyle name="常规 29" xfId="1290" xr:uid="{00000000-0005-0000-0000-000089050000}"/>
-    <cellStyle name="常规 29 2" xfId="1292" xr:uid="{00000000-0005-0000-0000-00008A050000}"/>
-    <cellStyle name="常规 29 2 2" xfId="1293" xr:uid="{00000000-0005-0000-0000-00008B050000}"/>
-    <cellStyle name="常规 29 2 3" xfId="1294" xr:uid="{00000000-0005-0000-0000-00008C050000}"/>
-    <cellStyle name="常规 29 2 4" xfId="1295" xr:uid="{00000000-0005-0000-0000-00008D050000}"/>
-    <cellStyle name="常规 29 2 5" xfId="1296" xr:uid="{00000000-0005-0000-0000-00008E050000}"/>
-    <cellStyle name="常规 29 3" xfId="1297" xr:uid="{00000000-0005-0000-0000-00008F050000}"/>
-    <cellStyle name="常规 29 4" xfId="1298" xr:uid="{00000000-0005-0000-0000-000090050000}"/>
-    <cellStyle name="常规 29 5" xfId="1299" xr:uid="{00000000-0005-0000-0000-000091050000}"/>
-    <cellStyle name="常规 29 6" xfId="1301" xr:uid="{00000000-0005-0000-0000-000092050000}"/>
-    <cellStyle name="常规 3" xfId="1302" xr:uid="{00000000-0005-0000-0000-000093050000}"/>
-    <cellStyle name="常规 3 10" xfId="1659" xr:uid="{00000000-0005-0000-0000-000094050000}"/>
-    <cellStyle name="常规 3 2" xfId="1002" xr:uid="{00000000-0005-0000-0000-000095050000}"/>
-    <cellStyle name="常规 3 2 2" xfId="1004" xr:uid="{00000000-0005-0000-0000-000096050000}"/>
-    <cellStyle name="常规 3 2 2 2" xfId="397" xr:uid="{00000000-0005-0000-0000-000097050000}"/>
-    <cellStyle name="常规 3 2 2 2 2" xfId="1303" xr:uid="{00000000-0005-0000-0000-000098050000}"/>
-    <cellStyle name="常规 3 2 2 2 3" xfId="1304" xr:uid="{00000000-0005-0000-0000-000099050000}"/>
-    <cellStyle name="常规 3 2 2 2 4" xfId="1305" xr:uid="{00000000-0005-0000-0000-00009A050000}"/>
-    <cellStyle name="常规 3 2 2 2 5" xfId="1306" xr:uid="{00000000-0005-0000-0000-00009B050000}"/>
-    <cellStyle name="常规 3 2 2 3" xfId="401" xr:uid="{00000000-0005-0000-0000-00009C050000}"/>
-    <cellStyle name="常规 3 2 2 4" xfId="1307" xr:uid="{00000000-0005-0000-0000-00009D050000}"/>
-    <cellStyle name="常规 3 2 2 5" xfId="1308" xr:uid="{00000000-0005-0000-0000-00009E050000}"/>
-    <cellStyle name="常规 3 2 2 6" xfId="1309" xr:uid="{00000000-0005-0000-0000-00009F050000}"/>
-    <cellStyle name="常规 3 2 3" xfId="1310" xr:uid="{00000000-0005-0000-0000-0000A0050000}"/>
-    <cellStyle name="常规 3 2 3 2" xfId="1311" xr:uid="{00000000-0005-0000-0000-0000A1050000}"/>
-    <cellStyle name="常规 3 2 3 3" xfId="1312" xr:uid="{00000000-0005-0000-0000-0000A2050000}"/>
-    <cellStyle name="常规 3 2 3 4" xfId="1313" xr:uid="{00000000-0005-0000-0000-0000A3050000}"/>
-    <cellStyle name="常规 3 2 3 5" xfId="867" xr:uid="{00000000-0005-0000-0000-0000A4050000}"/>
-    <cellStyle name="常规 3 2 4" xfId="1314" xr:uid="{00000000-0005-0000-0000-0000A5050000}"/>
-    <cellStyle name="常规 3 2 5" xfId="927" xr:uid="{00000000-0005-0000-0000-0000A6050000}"/>
-    <cellStyle name="常规 3 2 6" xfId="871" xr:uid="{00000000-0005-0000-0000-0000A7050000}"/>
-    <cellStyle name="常规 3 2 7" xfId="874" xr:uid="{00000000-0005-0000-0000-0000A8050000}"/>
-    <cellStyle name="常规 3 3" xfId="1006" xr:uid="{00000000-0005-0000-0000-0000A9050000}"/>
-    <cellStyle name="常规 3 3 2" xfId="1008" xr:uid="{00000000-0005-0000-0000-0000AA050000}"/>
-    <cellStyle name="常规 3 3 2 2" xfId="1315" xr:uid="{00000000-0005-0000-0000-0000AB050000}"/>
-    <cellStyle name="常规 3 3 2 3" xfId="1316" xr:uid="{00000000-0005-0000-0000-0000AC050000}"/>
-    <cellStyle name="常规 3 3 2 4" xfId="1317" xr:uid="{00000000-0005-0000-0000-0000AD050000}"/>
-    <cellStyle name="常规 3 3 2 5" xfId="1318" xr:uid="{00000000-0005-0000-0000-0000AE050000}"/>
-    <cellStyle name="常规 3 3 3" xfId="1319" xr:uid="{00000000-0005-0000-0000-0000AF050000}"/>
-    <cellStyle name="常规 3 3 4" xfId="1320" xr:uid="{00000000-0005-0000-0000-0000B0050000}"/>
-    <cellStyle name="常规 3 3 5" xfId="1321" xr:uid="{00000000-0005-0000-0000-0000B1050000}"/>
-    <cellStyle name="常规 3 3 6" xfId="1322" xr:uid="{00000000-0005-0000-0000-0000B2050000}"/>
-    <cellStyle name="常规 3 4" xfId="1323" xr:uid="{00000000-0005-0000-0000-0000B3050000}"/>
-    <cellStyle name="常规 3 5" xfId="1324" xr:uid="{00000000-0005-0000-0000-0000B4050000}"/>
-    <cellStyle name="常规 3 5 2" xfId="1325" xr:uid="{00000000-0005-0000-0000-0000B5050000}"/>
-    <cellStyle name="常规 3 5 3" xfId="1326" xr:uid="{00000000-0005-0000-0000-0000B6050000}"/>
-    <cellStyle name="常规 3 5 4" xfId="1327" xr:uid="{00000000-0005-0000-0000-0000B7050000}"/>
-    <cellStyle name="常规 3 5 5" xfId="1329" xr:uid="{00000000-0005-0000-0000-0000B8050000}"/>
-    <cellStyle name="常规 3 6" xfId="1330" xr:uid="{00000000-0005-0000-0000-0000B9050000}"/>
-    <cellStyle name="常规 3 6 2" xfId="1331" xr:uid="{00000000-0005-0000-0000-0000BA050000}"/>
-    <cellStyle name="常规 3 7" xfId="1332" xr:uid="{00000000-0005-0000-0000-0000BB050000}"/>
-    <cellStyle name="常规 3 7 2" xfId="92" xr:uid="{00000000-0005-0000-0000-0000BC050000}"/>
-    <cellStyle name="常规 3 7 3" xfId="1333" xr:uid="{00000000-0005-0000-0000-0000BD050000}"/>
-    <cellStyle name="常规 3 8" xfId="1334" xr:uid="{00000000-0005-0000-0000-0000BE050000}"/>
-    <cellStyle name="常规 3 9" xfId="1649" xr:uid="{00000000-0005-0000-0000-0000BF050000}"/>
-    <cellStyle name="常规 30" xfId="1259" xr:uid="{00000000-0005-0000-0000-0000C0050000}"/>
-    <cellStyle name="常规 31" xfId="1262" xr:uid="{00000000-0005-0000-0000-0000C1050000}"/>
-    <cellStyle name="常规 31 2" xfId="30" xr:uid="{00000000-0005-0000-0000-0000C2050000}"/>
-    <cellStyle name="常规 31 2 2" xfId="1335" xr:uid="{00000000-0005-0000-0000-0000C3050000}"/>
-    <cellStyle name="常规 31 2 3" xfId="1336" xr:uid="{00000000-0005-0000-0000-0000C4050000}"/>
-    <cellStyle name="常规 31 2 4" xfId="1337" xr:uid="{00000000-0005-0000-0000-0000C5050000}"/>
-    <cellStyle name="常规 31 2 5" xfId="1338" xr:uid="{00000000-0005-0000-0000-0000C6050000}"/>
-    <cellStyle name="常规 31 3" xfId="67" xr:uid="{00000000-0005-0000-0000-0000C7050000}"/>
-    <cellStyle name="常规 31 4" xfId="70" xr:uid="{00000000-0005-0000-0000-0000C8050000}"/>
-    <cellStyle name="常规 31 5" xfId="74" xr:uid="{00000000-0005-0000-0000-0000C9050000}"/>
-    <cellStyle name="常规 31 6" xfId="1339" xr:uid="{00000000-0005-0000-0000-0000CA050000}"/>
-    <cellStyle name="常规 32" xfId="1264" xr:uid="{00000000-0005-0000-0000-0000CB050000}"/>
-    <cellStyle name="常规 32 2" xfId="1266" xr:uid="{00000000-0005-0000-0000-0000CC050000}"/>
-    <cellStyle name="常规 32 3" xfId="1272" xr:uid="{00000000-0005-0000-0000-0000CD050000}"/>
-    <cellStyle name="常规 32 4" xfId="1274" xr:uid="{00000000-0005-0000-0000-0000CE050000}"/>
-    <cellStyle name="常规 32 5" xfId="1276" xr:uid="{00000000-0005-0000-0000-0000CF050000}"/>
-    <cellStyle name="常规 33" xfId="8" xr:uid="{00000000-0005-0000-0000-0000D0050000}"/>
-    <cellStyle name="常规 33 2" xfId="152" xr:uid="{00000000-0005-0000-0000-0000D1050000}"/>
-    <cellStyle name="常规 33 3" xfId="1279" xr:uid="{00000000-0005-0000-0000-0000D2050000}"/>
-    <cellStyle name="常规 34" xfId="1289" xr:uid="{00000000-0005-0000-0000-0000D3050000}"/>
-    <cellStyle name="常规 34 2" xfId="1291" xr:uid="{00000000-0005-0000-0000-0000D4050000}"/>
-    <cellStyle name="常规 35" xfId="12" xr:uid="{00000000-0005-0000-0000-0000D5050000}"/>
-    <cellStyle name="常规 35 2" xfId="1341" xr:uid="{00000000-0005-0000-0000-0000D6050000}"/>
-    <cellStyle name="常规 36" xfId="1343" xr:uid="{00000000-0005-0000-0000-0000D7050000}"/>
-    <cellStyle name="常规 36 2" xfId="1345" xr:uid="{00000000-0005-0000-0000-0000D8050000}"/>
-    <cellStyle name="常规 37" xfId="1347" xr:uid="{00000000-0005-0000-0000-0000D9050000}"/>
-    <cellStyle name="常规 37 2" xfId="1349" xr:uid="{00000000-0005-0000-0000-0000DA050000}"/>
-    <cellStyle name="常规 37 3" xfId="1350" xr:uid="{00000000-0005-0000-0000-0000DB050000}"/>
-    <cellStyle name="常规 38" xfId="824" xr:uid="{00000000-0005-0000-0000-0000DC050000}"/>
-    <cellStyle name="常规 38 2" xfId="827" xr:uid="{00000000-0005-0000-0000-0000DD050000}"/>
-    <cellStyle name="常规 38 3" xfId="829" xr:uid="{00000000-0005-0000-0000-0000DE050000}"/>
-    <cellStyle name="常规 38 4" xfId="831" xr:uid="{00000000-0005-0000-0000-0000DF050000}"/>
-    <cellStyle name="常规 38 5" xfId="833" xr:uid="{00000000-0005-0000-0000-0000E0050000}"/>
-    <cellStyle name="常规 39" xfId="23" xr:uid="{00000000-0005-0000-0000-0000E1050000}"/>
-    <cellStyle name="常规 39 2" xfId="1352" xr:uid="{00000000-0005-0000-0000-0000E2050000}"/>
-    <cellStyle name="常规 39 3" xfId="1353" xr:uid="{00000000-0005-0000-0000-0000E3050000}"/>
-    <cellStyle name="常规 39 4" xfId="1354" xr:uid="{00000000-0005-0000-0000-0000E4050000}"/>
-    <cellStyle name="常规 4" xfId="1355" xr:uid="{00000000-0005-0000-0000-0000E5050000}"/>
-    <cellStyle name="常规 4 2" xfId="1356" xr:uid="{00000000-0005-0000-0000-0000E6050000}"/>
-    <cellStyle name="常规 4 2 2" xfId="1358" xr:uid="{00000000-0005-0000-0000-0000E7050000}"/>
-    <cellStyle name="常规 4 2 2 2" xfId="1361" xr:uid="{00000000-0005-0000-0000-0000E8050000}"/>
-    <cellStyle name="常规 4 2 2 2 2" xfId="1363" xr:uid="{00000000-0005-0000-0000-0000E9050000}"/>
-    <cellStyle name="常规 4 2 2 2 3" xfId="1365" xr:uid="{00000000-0005-0000-0000-0000EA050000}"/>
-    <cellStyle name="常规 4 2 2 2 4" xfId="1367" xr:uid="{00000000-0005-0000-0000-0000EB050000}"/>
-    <cellStyle name="常规 4 2 2 2 5" xfId="1369" xr:uid="{00000000-0005-0000-0000-0000EC050000}"/>
-    <cellStyle name="常规 4 2 2 3" xfId="41" xr:uid="{00000000-0005-0000-0000-0000ED050000}"/>
-    <cellStyle name="常规 4 2 2 4" xfId="1372" xr:uid="{00000000-0005-0000-0000-0000EE050000}"/>
-    <cellStyle name="常规 4 2 2 5" xfId="1375" xr:uid="{00000000-0005-0000-0000-0000EF050000}"/>
-    <cellStyle name="常规 4 2 2 6" xfId="1377" xr:uid="{00000000-0005-0000-0000-0000F0050000}"/>
-    <cellStyle name="常规 4 2 3" xfId="1379" xr:uid="{00000000-0005-0000-0000-0000F1050000}"/>
-    <cellStyle name="常规 4 2 3 2" xfId="1380" xr:uid="{00000000-0005-0000-0000-0000F2050000}"/>
-    <cellStyle name="常规 4 2 3 3" xfId="1381" xr:uid="{00000000-0005-0000-0000-0000F3050000}"/>
-    <cellStyle name="常规 4 2 3 4" xfId="1382" xr:uid="{00000000-0005-0000-0000-0000F4050000}"/>
-    <cellStyle name="常规 4 2 3 5" xfId="1384" xr:uid="{00000000-0005-0000-0000-0000F5050000}"/>
-    <cellStyle name="常规 4 2 4" xfId="1386" xr:uid="{00000000-0005-0000-0000-0000F6050000}"/>
-    <cellStyle name="常规 4 2 5" xfId="1388" xr:uid="{00000000-0005-0000-0000-0000F7050000}"/>
-    <cellStyle name="常规 4 2 6" xfId="1391" xr:uid="{00000000-0005-0000-0000-0000F8050000}"/>
-    <cellStyle name="常规 4 2 7" xfId="1393" xr:uid="{00000000-0005-0000-0000-0000F9050000}"/>
-    <cellStyle name="常规 4 3" xfId="1394" xr:uid="{00000000-0005-0000-0000-0000FA050000}"/>
-    <cellStyle name="常规 4 3 2" xfId="1396" xr:uid="{00000000-0005-0000-0000-0000FB050000}"/>
-    <cellStyle name="常规 4 3 2 2" xfId="1398" xr:uid="{00000000-0005-0000-0000-0000FC050000}"/>
-    <cellStyle name="常规 4 3 2 3" xfId="1400" xr:uid="{00000000-0005-0000-0000-0000FD050000}"/>
-    <cellStyle name="常规 4 3 2 4" xfId="1402" xr:uid="{00000000-0005-0000-0000-0000FE050000}"/>
-    <cellStyle name="常规 4 3 2 5" xfId="1404" xr:uid="{00000000-0005-0000-0000-0000FF050000}"/>
-    <cellStyle name="常规 4 3 3" xfId="1406" xr:uid="{00000000-0005-0000-0000-000000060000}"/>
-    <cellStyle name="常规 4 3 4" xfId="1408" xr:uid="{00000000-0005-0000-0000-000001060000}"/>
-    <cellStyle name="常规 4 3 5" xfId="1410" xr:uid="{00000000-0005-0000-0000-000002060000}"/>
-    <cellStyle name="常规 4 3 6" xfId="1413" xr:uid="{00000000-0005-0000-0000-000003060000}"/>
-    <cellStyle name="常规 4 4" xfId="1357" xr:uid="{00000000-0005-0000-0000-000004060000}"/>
-    <cellStyle name="常规 4 4 2" xfId="1360" xr:uid="{00000000-0005-0000-0000-000005060000}"/>
-    <cellStyle name="常规 4 4 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000006060000}"/>
-    <cellStyle name="常规 4 4 4" xfId="1371" xr:uid="{00000000-0005-0000-0000-000007060000}"/>
-    <cellStyle name="常规 4 4 5" xfId="1374" xr:uid="{00000000-0005-0000-0000-000008060000}"/>
-    <cellStyle name="常规 4 5" xfId="1378" xr:uid="{00000000-0005-0000-0000-000009060000}"/>
-    <cellStyle name="常规 4 6" xfId="1385" xr:uid="{00000000-0005-0000-0000-00000A060000}"/>
-    <cellStyle name="常规 4 7" xfId="1387" xr:uid="{00000000-0005-0000-0000-00000B060000}"/>
-    <cellStyle name="常规 4 8" xfId="1390" xr:uid="{00000000-0005-0000-0000-00000C060000}"/>
-    <cellStyle name="常规 40" xfId="1340" xr:uid="{00000000-0005-0000-0000-00000D060000}"/>
-    <cellStyle name="常规 40 2" xfId="1414" xr:uid="{00000000-0005-0000-0000-00000E060000}"/>
-    <cellStyle name="常规 41" xfId="1342" xr:uid="{00000000-0005-0000-0000-00000F060000}"/>
-    <cellStyle name="常规 41 2" xfId="1344" xr:uid="{00000000-0005-0000-0000-000010060000}"/>
-    <cellStyle name="常规 42" xfId="1346" xr:uid="{00000000-0005-0000-0000-000011060000}"/>
-    <cellStyle name="常规 42 2" xfId="1348" xr:uid="{00000000-0005-0000-0000-000012060000}"/>
-    <cellStyle name="常规 43" xfId="823" xr:uid="{00000000-0005-0000-0000-000013060000}"/>
-    <cellStyle name="常规 43 2" xfId="826" xr:uid="{00000000-0005-0000-0000-000014060000}"/>
-    <cellStyle name="常规 44" xfId="22" xr:uid="{00000000-0005-0000-0000-000015060000}"/>
-    <cellStyle name="常规 44 2" xfId="1351" xr:uid="{00000000-0005-0000-0000-000016060000}"/>
-    <cellStyle name="常规 45" xfId="836" xr:uid="{00000000-0005-0000-0000-000017060000}"/>
-    <cellStyle name="常规 45 2" xfId="1415" xr:uid="{00000000-0005-0000-0000-000018060000}"/>
-    <cellStyle name="常规 46" xfId="839" xr:uid="{00000000-0005-0000-0000-000019060000}"/>
-    <cellStyle name="常规 47" xfId="842" xr:uid="{00000000-0005-0000-0000-00001A060000}"/>
-    <cellStyle name="常规 47 2" xfId="1416" xr:uid="{00000000-0005-0000-0000-00001B060000}"/>
-    <cellStyle name="常规 48" xfId="1418" xr:uid="{00000000-0005-0000-0000-00001C060000}"/>
-    <cellStyle name="常规 49" xfId="1420" xr:uid="{00000000-0005-0000-0000-00001D060000}"/>
-    <cellStyle name="常规 5" xfId="1421" xr:uid="{00000000-0005-0000-0000-00001E060000}"/>
-    <cellStyle name="常规 5 2" xfId="1422" xr:uid="{00000000-0005-0000-0000-00001F060000}"/>
-    <cellStyle name="常规 5 2 2" xfId="1423" xr:uid="{00000000-0005-0000-0000-000020060000}"/>
-    <cellStyle name="常规 5 2 2 2" xfId="1424" xr:uid="{00000000-0005-0000-0000-000021060000}"/>
-    <cellStyle name="常规 5 2 2 2 2" xfId="1149" xr:uid="{00000000-0005-0000-0000-000022060000}"/>
-    <cellStyle name="常规 5 2 2 2 3" xfId="1154" xr:uid="{00000000-0005-0000-0000-000023060000}"/>
-    <cellStyle name="常规 5 2 2 2 4" xfId="1156" xr:uid="{00000000-0005-0000-0000-000024060000}"/>
-    <cellStyle name="常规 5 2 2 2 5" xfId="1158" xr:uid="{00000000-0005-0000-0000-000025060000}"/>
-    <cellStyle name="常规 5 2 2 3" xfId="1425" xr:uid="{00000000-0005-0000-0000-000026060000}"/>
-    <cellStyle name="常规 5 2 2 4" xfId="1426" xr:uid="{00000000-0005-0000-0000-000027060000}"/>
-    <cellStyle name="常规 5 2 2 5" xfId="1427" xr:uid="{00000000-0005-0000-0000-000028060000}"/>
-    <cellStyle name="常规 5 2 2 6" xfId="1428" xr:uid="{00000000-0005-0000-0000-000029060000}"/>
-    <cellStyle name="常规 5 2 3" xfId="1429" xr:uid="{00000000-0005-0000-0000-00002A060000}"/>
-    <cellStyle name="常规 5 2 3 2" xfId="1045" xr:uid="{00000000-0005-0000-0000-00002B060000}"/>
-    <cellStyle name="常规 5 2 3 3" xfId="1430" xr:uid="{00000000-0005-0000-0000-00002C060000}"/>
-    <cellStyle name="常规 5 2 3 4" xfId="1431" xr:uid="{00000000-0005-0000-0000-00002D060000}"/>
-    <cellStyle name="常规 5 2 3 5" xfId="1432" xr:uid="{00000000-0005-0000-0000-00002E060000}"/>
-    <cellStyle name="常规 5 2 4" xfId="1433" xr:uid="{00000000-0005-0000-0000-00002F060000}"/>
-    <cellStyle name="常规 5 2 5" xfId="1434" xr:uid="{00000000-0005-0000-0000-000030060000}"/>
-    <cellStyle name="常规 5 2 6" xfId="1436" xr:uid="{00000000-0005-0000-0000-000031060000}"/>
-    <cellStyle name="常规 5 2 7" xfId="1438" xr:uid="{00000000-0005-0000-0000-000032060000}"/>
-    <cellStyle name="常规 5 3" xfId="1439" xr:uid="{00000000-0005-0000-0000-000033060000}"/>
-    <cellStyle name="常规 5 3 2" xfId="337" xr:uid="{00000000-0005-0000-0000-000034060000}"/>
-    <cellStyle name="常规 5 3 2 2" xfId="341" xr:uid="{00000000-0005-0000-0000-000035060000}"/>
-    <cellStyle name="常规 5 3 2 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000036060000}"/>
-    <cellStyle name="常规 5 3 2 4" xfId="1440" xr:uid="{00000000-0005-0000-0000-000037060000}"/>
-    <cellStyle name="常规 5 3 2 5" xfId="1441" xr:uid="{00000000-0005-0000-0000-000038060000}"/>
-    <cellStyle name="常规 5 3 3" xfId="499" xr:uid="{00000000-0005-0000-0000-000039060000}"/>
-    <cellStyle name="常规 5 3 4" xfId="503" xr:uid="{00000000-0005-0000-0000-00003A060000}"/>
-    <cellStyle name="常规 5 3 5" xfId="505" xr:uid="{00000000-0005-0000-0000-00003B060000}"/>
-    <cellStyle name="常规 5 3 6" xfId="507" xr:uid="{00000000-0005-0000-0000-00003C060000}"/>
-    <cellStyle name="常规 5 4" xfId="1395" xr:uid="{00000000-0005-0000-0000-00003D060000}"/>
-    <cellStyle name="常规 5 4 2" xfId="1397" xr:uid="{00000000-0005-0000-0000-00003E060000}"/>
-    <cellStyle name="常规 5 4 3" xfId="1399" xr:uid="{00000000-0005-0000-0000-00003F060000}"/>
-    <cellStyle name="常规 5 4 4" xfId="1401" xr:uid="{00000000-0005-0000-0000-000040060000}"/>
-    <cellStyle name="常规 5 4 5" xfId="1403" xr:uid="{00000000-0005-0000-0000-000041060000}"/>
-    <cellStyle name="常规 5 5" xfId="1405" xr:uid="{00000000-0005-0000-0000-000042060000}"/>
-    <cellStyle name="常规 5 6" xfId="1407" xr:uid="{00000000-0005-0000-0000-000043060000}"/>
-    <cellStyle name="常规 5 7" xfId="1409" xr:uid="{00000000-0005-0000-0000-000044060000}"/>
-    <cellStyle name="常规 5 8" xfId="1412" xr:uid="{00000000-0005-0000-0000-000045060000}"/>
-    <cellStyle name="常规 50" xfId="835" xr:uid="{00000000-0005-0000-0000-000046060000}"/>
-    <cellStyle name="常规 51" xfId="838" xr:uid="{00000000-0005-0000-0000-000047060000}"/>
-    <cellStyle name="常规 52" xfId="841" xr:uid="{00000000-0005-0000-0000-000048060000}"/>
-    <cellStyle name="常规 53" xfId="1417" xr:uid="{00000000-0005-0000-0000-000049060000}"/>
-    <cellStyle name="常规 54" xfId="1419" xr:uid="{00000000-0005-0000-0000-00004A060000}"/>
-    <cellStyle name="常规 55" xfId="85" xr:uid="{00000000-0005-0000-0000-00004B060000}"/>
-    <cellStyle name="常规 56" xfId="105" xr:uid="{00000000-0005-0000-0000-00004C060000}"/>
-    <cellStyle name="常规 57" xfId="109" xr:uid="{00000000-0005-0000-0000-00004D060000}"/>
-    <cellStyle name="常规 6" xfId="1442" xr:uid="{00000000-0005-0000-0000-00004E060000}"/>
-    <cellStyle name="常规 6 2" xfId="1443" xr:uid="{00000000-0005-0000-0000-00004F060000}"/>
-    <cellStyle name="常规 6 2 2" xfId="634" xr:uid="{00000000-0005-0000-0000-000050060000}"/>
-    <cellStyle name="常规 6 2 2 2" xfId="1444" xr:uid="{00000000-0005-0000-0000-000051060000}"/>
-    <cellStyle name="常规 6 2 2 2 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000052060000}"/>
-    <cellStyle name="常规 6 2 2 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-000053060000}"/>
-    <cellStyle name="常规 6 2 2 2 4" xfId="783" xr:uid="{00000000-0005-0000-0000-000054060000}"/>
-    <cellStyle name="常规 6 2 2 2 5" xfId="785" xr:uid="{00000000-0005-0000-0000-000055060000}"/>
-    <cellStyle name="常规 6 2 2 3" xfId="1445" xr:uid="{00000000-0005-0000-0000-000056060000}"/>
-    <cellStyle name="常规 6 2 2 4" xfId="1446" xr:uid="{00000000-0005-0000-0000-000057060000}"/>
-    <cellStyle name="常规 6 2 2 5" xfId="1447" xr:uid="{00000000-0005-0000-0000-000058060000}"/>
-    <cellStyle name="常规 6 2 2 6" xfId="1448" xr:uid="{00000000-0005-0000-0000-000059060000}"/>
-    <cellStyle name="常规 6 2 3" xfId="636" xr:uid="{00000000-0005-0000-0000-00005A060000}"/>
-    <cellStyle name="常规 6 2 3 2" xfId="1449" xr:uid="{00000000-0005-0000-0000-00005B060000}"/>
-    <cellStyle name="常规 6 2 3 3" xfId="1450" xr:uid="{00000000-0005-0000-0000-00005C060000}"/>
-    <cellStyle name="常规 6 2 3 4" xfId="1451" xr:uid="{00000000-0005-0000-0000-00005D060000}"/>
-    <cellStyle name="常规 6 2 3 5" xfId="1452" xr:uid="{00000000-0005-0000-0000-00005E060000}"/>
-    <cellStyle name="常规 6 2 4" xfId="638" xr:uid="{00000000-0005-0000-0000-00005F060000}"/>
-    <cellStyle name="常规 6 2 5" xfId="1453" xr:uid="{00000000-0005-0000-0000-000060060000}"/>
-    <cellStyle name="常规 6 2 6" xfId="738" xr:uid="{00000000-0005-0000-0000-000061060000}"/>
-    <cellStyle name="常规 6 2 7" xfId="750" xr:uid="{00000000-0005-0000-0000-000062060000}"/>
-    <cellStyle name="常规 6 3" xfId="1454" xr:uid="{00000000-0005-0000-0000-000063060000}"/>
-    <cellStyle name="常规 6 3 2" xfId="645" xr:uid="{00000000-0005-0000-0000-000064060000}"/>
-    <cellStyle name="常规 6 3 2 2" xfId="1455" xr:uid="{00000000-0005-0000-0000-000065060000}"/>
-    <cellStyle name="常规 6 3 2 3" xfId="1456" xr:uid="{00000000-0005-0000-0000-000066060000}"/>
-    <cellStyle name="常规 6 3 2 4" xfId="1457" xr:uid="{00000000-0005-0000-0000-000067060000}"/>
-    <cellStyle name="常规 6 3 2 5" xfId="1458" xr:uid="{00000000-0005-0000-0000-000068060000}"/>
-    <cellStyle name="常规 6 3 3" xfId="647" xr:uid="{00000000-0005-0000-0000-000069060000}"/>
-    <cellStyle name="常规 6 3 4" xfId="1459" xr:uid="{00000000-0005-0000-0000-00006A060000}"/>
-    <cellStyle name="常规 6 3 5" xfId="1460" xr:uid="{00000000-0005-0000-0000-00006B060000}"/>
-    <cellStyle name="常规 6 3 6" xfId="763" xr:uid="{00000000-0005-0000-0000-00006C060000}"/>
-    <cellStyle name="常规 6 4" xfId="1359" xr:uid="{00000000-0005-0000-0000-00006D060000}"/>
-    <cellStyle name="常规 6 4 2" xfId="1362" xr:uid="{00000000-0005-0000-0000-00006E060000}"/>
-    <cellStyle name="常规 6 4 3" xfId="1364" xr:uid="{00000000-0005-0000-0000-00006F060000}"/>
-    <cellStyle name="常规 6 4 4" xfId="1366" xr:uid="{00000000-0005-0000-0000-000070060000}"/>
-    <cellStyle name="常规 6 4 5" xfId="1368" xr:uid="{00000000-0005-0000-0000-000071060000}"/>
-    <cellStyle name="常规 6 5" xfId="39" xr:uid="{00000000-0005-0000-0000-000072060000}"/>
-    <cellStyle name="常规 6 6" xfId="1370" xr:uid="{00000000-0005-0000-0000-000073060000}"/>
-    <cellStyle name="常规 6 7" xfId="1373" xr:uid="{00000000-0005-0000-0000-000074060000}"/>
-    <cellStyle name="常规 6 8" xfId="1376" xr:uid="{00000000-0005-0000-0000-000075060000}"/>
-    <cellStyle name="常规 60" xfId="1643" xr:uid="{00000000-0005-0000-0000-000076060000}"/>
-    <cellStyle name="常规 60 2" xfId="1652" xr:uid="{00000000-0005-0000-0000-000077060000}"/>
-    <cellStyle name="常规 61" xfId="1644" xr:uid="{00000000-0005-0000-0000-000078060000}"/>
-    <cellStyle name="常规 61 2" xfId="1653" xr:uid="{00000000-0005-0000-0000-000079060000}"/>
-    <cellStyle name="常规 7" xfId="1461" xr:uid="{00000000-0005-0000-0000-00007A060000}"/>
-    <cellStyle name="常规 8" xfId="1462" xr:uid="{00000000-0005-0000-0000-00007B060000}"/>
-    <cellStyle name="常规 8 2" xfId="1463" xr:uid="{00000000-0005-0000-0000-00007C060000}"/>
-    <cellStyle name="常规 9" xfId="6" xr:uid="{00000000-0005-0000-0000-00007D060000}"/>
+    <cellStyle name="Стиль 1" xfId="693"/>
+    <cellStyle name="Стиль 1 2" xfId="985"/>
+    <cellStyle name="Стиль 1 2 2" xfId="986"/>
+    <cellStyle name="Стиль 1 3" xfId="987"/>
+    <cellStyle name="Стиль 1 3 2" xfId="988"/>
+    <cellStyle name="Стиль 1 4" xfId="989"/>
+    <cellStyle name="Стиль 1 4 2" xfId="990"/>
+    <cellStyle name="Стиль 1 5" xfId="991"/>
+    <cellStyle name="Стиль 1 5 2" xfId="993"/>
+    <cellStyle name="Финансовый 2" xfId="994"/>
+    <cellStyle name="Финансовый 2 10" xfId="995"/>
+    <cellStyle name="Финансовый 2 10 2" xfId="997"/>
+    <cellStyle name="Финансовый 2 2" xfId="221"/>
+    <cellStyle name="Финансовый 2 3" xfId="236"/>
+    <cellStyle name="Финансовый 2 4" xfId="260"/>
+    <cellStyle name="Финансовый 2 4 2" xfId="263"/>
+    <cellStyle name="Финансовый 2 5" xfId="272"/>
+    <cellStyle name="Финансовый 2 5 2" xfId="998"/>
+    <cellStyle name="Финансовый 2 6" xfId="274"/>
+    <cellStyle name="Финансовый 2 6 2" xfId="999"/>
+    <cellStyle name="Финансовый 2 7" xfId="276"/>
+    <cellStyle name="Финансовый 2 7 2" xfId="1001"/>
+    <cellStyle name="Финансовый 2 8" xfId="1003"/>
+    <cellStyle name="Финансовый 2 8 2" xfId="1005"/>
+    <cellStyle name="Финансовый 2 9" xfId="1007"/>
+    <cellStyle name="Финансовый 2 9 2" xfId="1009"/>
+    <cellStyle name="Финансовый 3" xfId="33"/>
+    <cellStyle name="Финансовый 4" xfId="1642"/>
+    <cellStyle name="Финансовый 5" xfId="1651"/>
+    <cellStyle name="千位分隔 10" xfId="1464"/>
+    <cellStyle name="千位分隔 10 2" xfId="1465"/>
+    <cellStyle name="千位分隔 10 2 2" xfId="1466"/>
+    <cellStyle name="千位分隔 10 2 3" xfId="1467"/>
+    <cellStyle name="千位分隔 10 2 4" xfId="1468"/>
+    <cellStyle name="千位分隔 10 2 5" xfId="1469"/>
+    <cellStyle name="千位分隔 10 3" xfId="1470"/>
+    <cellStyle name="千位分隔 10 4" xfId="1471"/>
+    <cellStyle name="千位分隔 10 5" xfId="1472"/>
+    <cellStyle name="千位分隔 10 6" xfId="1473"/>
+    <cellStyle name="千位分隔 11" xfId="1474"/>
+    <cellStyle name="千位分隔 11 2" xfId="1475"/>
+    <cellStyle name="千位分隔 12" xfId="1476"/>
+    <cellStyle name="千位分隔 12 2" xfId="46"/>
+    <cellStyle name="千位分隔 12 2 2" xfId="1328"/>
+    <cellStyle name="千位分隔 12 2 3" xfId="1477"/>
+    <cellStyle name="千位分隔 12 2 4" xfId="1478"/>
+    <cellStyle name="千位分隔 12 2 5" xfId="1479"/>
+    <cellStyle name="千位分隔 12 3" xfId="929"/>
+    <cellStyle name="千位分隔 12 4" xfId="1480"/>
+    <cellStyle name="千位分隔 12 5" xfId="1481"/>
+    <cellStyle name="千位分隔 12 6" xfId="1482"/>
+    <cellStyle name="千位分隔 13" xfId="14"/>
+    <cellStyle name="千位分隔 13 2" xfId="938"/>
+    <cellStyle name="千位分隔 13 2 2" xfId="1383"/>
+    <cellStyle name="千位分隔 13 2 3" xfId="1484"/>
+    <cellStyle name="千位分隔 13 2 4" xfId="1485"/>
+    <cellStyle name="千位分隔 13 2 5" xfId="1486"/>
+    <cellStyle name="千位分隔 13 3" xfId="1487"/>
+    <cellStyle name="千位分隔 13 4" xfId="1488"/>
+    <cellStyle name="千位分隔 13 5" xfId="1489"/>
+    <cellStyle name="千位分隔 13 6" xfId="1490"/>
+    <cellStyle name="千位分隔 13 7" xfId="1483"/>
+    <cellStyle name="千位分隔 14" xfId="1491"/>
+    <cellStyle name="千位分隔 14 2" xfId="1492"/>
+    <cellStyle name="千位分隔 14 2 2" xfId="1493"/>
+    <cellStyle name="千位分隔 14 2 3" xfId="1494"/>
+    <cellStyle name="千位分隔 14 2 4" xfId="1495"/>
+    <cellStyle name="千位分隔 14 2 5" xfId="1496"/>
+    <cellStyle name="千位分隔 14 3" xfId="1497"/>
+    <cellStyle name="千位分隔 14 4" xfId="1498"/>
+    <cellStyle name="千位分隔 14 5" xfId="1499"/>
+    <cellStyle name="千位分隔 14 6" xfId="1500"/>
+    <cellStyle name="千位分隔 15" xfId="9"/>
+    <cellStyle name="千位分隔 15 2" xfId="1503"/>
+    <cellStyle name="千位分隔 15 3" xfId="1504"/>
+    <cellStyle name="千位分隔 15 4" xfId="1505"/>
+    <cellStyle name="千位分隔 15 5" xfId="1506"/>
+    <cellStyle name="千位分隔 15 6" xfId="1502"/>
+    <cellStyle name="千位分隔 16" xfId="605"/>
+    <cellStyle name="千位分隔 17" xfId="624"/>
+    <cellStyle name="千位分隔 17 2" xfId="626"/>
+    <cellStyle name="千位分隔 17 3" xfId="632"/>
+    <cellStyle name="千位分隔 18" xfId="11"/>
+    <cellStyle name="千位分隔 18 2" xfId="641"/>
+    <cellStyle name="千位分隔 19" xfId="16"/>
+    <cellStyle name="千位分隔 2" xfId="296"/>
+    <cellStyle name="千位分隔 2 10" xfId="1507"/>
+    <cellStyle name="千位分隔 2 11" xfId="1508"/>
+    <cellStyle name="千位分隔 2 12" xfId="290"/>
+    <cellStyle name="千位分隔 2 2" xfId="1509"/>
+    <cellStyle name="千位分隔 2 2 2" xfId="1287"/>
+    <cellStyle name="千位分隔 2 2 2 2" xfId="1510"/>
+    <cellStyle name="千位分隔 2 2 2 2 2" xfId="1511"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 2" xfId="1512"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 3" xfId="1513"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 4" xfId="1514"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 5" xfId="1515"/>
+    <cellStyle name="千位分隔 2 2 2 2 3" xfId="1516"/>
+    <cellStyle name="千位分隔 2 2 2 2 4" xfId="1517"/>
+    <cellStyle name="千位分隔 2 2 2 2 5" xfId="1518"/>
+    <cellStyle name="千位分隔 2 2 2 2 6" xfId="1089"/>
+    <cellStyle name="千位分隔 2 2 2 3" xfId="1519"/>
+    <cellStyle name="千位分隔 2 2 2 3 2" xfId="1520"/>
+    <cellStyle name="千位分隔 2 2 2 3 3" xfId="1521"/>
+    <cellStyle name="千位分隔 2 2 2 3 4" xfId="1522"/>
+    <cellStyle name="千位分隔 2 2 2 3 5" xfId="1523"/>
+    <cellStyle name="千位分隔 2 2 2 4" xfId="1524"/>
+    <cellStyle name="千位分隔 2 2 2 5" xfId="1525"/>
+    <cellStyle name="千位分隔 2 2 2 6" xfId="1526"/>
+    <cellStyle name="千位分隔 2 2 2 7" xfId="1527"/>
+    <cellStyle name="千位分隔 2 2 3" xfId="1528"/>
+    <cellStyle name="千位分隔 2 2 3 2" xfId="1529"/>
+    <cellStyle name="千位分隔 2 2 3 2 2" xfId="1530"/>
+    <cellStyle name="千位分隔 2 2 3 2 3" xfId="1531"/>
+    <cellStyle name="千位分隔 2 2 3 2 4" xfId="1532"/>
+    <cellStyle name="千位分隔 2 2 3 2 5" xfId="1533"/>
+    <cellStyle name="千位分隔 2 2 3 3" xfId="1534"/>
+    <cellStyle name="千位分隔 2 2 3 4" xfId="1535"/>
+    <cellStyle name="千位分隔 2 2 3 5" xfId="1536"/>
+    <cellStyle name="千位分隔 2 2 3 6" xfId="1537"/>
+    <cellStyle name="千位分隔 2 2 4" xfId="992"/>
+    <cellStyle name="千位分隔 2 2 4 2" xfId="62"/>
+    <cellStyle name="千位分隔 2 2 4 3" xfId="64"/>
+    <cellStyle name="千位分隔 2 2 4 4" xfId="68"/>
+    <cellStyle name="千位分隔 2 2 4 5" xfId="72"/>
+    <cellStyle name="千位分隔 2 2 5" xfId="1203"/>
+    <cellStyle name="千位分隔 2 2 6" xfId="1205"/>
+    <cellStyle name="千位分隔 2 2 7" xfId="512"/>
+    <cellStyle name="千位分隔 2 2 8" xfId="1207"/>
+    <cellStyle name="千位分隔 2 3" xfId="7"/>
+    <cellStyle name="千位分隔 2 3 2" xfId="1300"/>
+    <cellStyle name="千位分隔 2 3 2 2" xfId="1539"/>
+    <cellStyle name="千位分隔 2 3 2 2 2" xfId="724"/>
+    <cellStyle name="千位分隔 2 3 2 2 3" xfId="727"/>
+    <cellStyle name="千位分隔 2 3 2 2 4" xfId="1540"/>
+    <cellStyle name="千位分隔 2 3 2 2 5" xfId="1541"/>
+    <cellStyle name="千位分隔 2 3 2 3" xfId="1542"/>
+    <cellStyle name="千位分隔 2 3 2 4" xfId="1543"/>
+    <cellStyle name="千位分隔 2 3 2 5" xfId="1544"/>
+    <cellStyle name="千位分隔 2 3 2 6" xfId="1545"/>
+    <cellStyle name="千位分隔 2 3 3" xfId="1546"/>
+    <cellStyle name="千位分隔 2 3 3 2" xfId="1547"/>
+    <cellStyle name="千位分隔 2 3 3 3" xfId="1548"/>
+    <cellStyle name="千位分隔 2 3 3 4" xfId="1549"/>
+    <cellStyle name="千位分隔 2 3 3 5" xfId="1550"/>
+    <cellStyle name="千位分隔 2 3 4" xfId="1551"/>
+    <cellStyle name="千位分隔 2 3 5" xfId="1552"/>
+    <cellStyle name="千位分隔 2 3 6" xfId="1553"/>
+    <cellStyle name="千位分隔 2 3 7" xfId="187"/>
+    <cellStyle name="千位分隔 2 3 8" xfId="1538"/>
+    <cellStyle name="千位分隔 2 4" xfId="544"/>
+    <cellStyle name="千位分隔 2 4 2" xfId="547"/>
+    <cellStyle name="千位分隔 2 4 2 2" xfId="1554"/>
+    <cellStyle name="千位分隔 2 4 2 3" xfId="1555"/>
+    <cellStyle name="千位分隔 2 4 2 4" xfId="1556"/>
+    <cellStyle name="千位分隔 2 4 2 5" xfId="1557"/>
+    <cellStyle name="千位分隔 2 4 3" xfId="550"/>
+    <cellStyle name="千位分隔 2 4 4" xfId="34"/>
+    <cellStyle name="千位分隔 2 4 5" xfId="194"/>
+    <cellStyle name="千位分隔 2 4 6" xfId="197"/>
+    <cellStyle name="千位分隔 2 5" xfId="579"/>
+    <cellStyle name="千位分隔 2 5 2" xfId="349"/>
+    <cellStyle name="千位分隔 2 5 2 2" xfId="354"/>
+    <cellStyle name="千位分隔 2 5 2 3" xfId="357"/>
+    <cellStyle name="千位分隔 2 5 2 4" xfId="360"/>
+    <cellStyle name="千位分隔 2 5 2 5" xfId="315"/>
+    <cellStyle name="千位分隔 2 5 3" xfId="90"/>
+    <cellStyle name="千位分隔 2 5 4" xfId="586"/>
+    <cellStyle name="千位分隔 2 5 5" xfId="591"/>
+    <cellStyle name="千位分隔 2 5 6" xfId="593"/>
+    <cellStyle name="千位分隔 2 6" xfId="28"/>
+    <cellStyle name="千位分隔 2 6 2" xfId="1558"/>
+    <cellStyle name="千位分隔 2 6 2 2" xfId="1559"/>
+    <cellStyle name="千位分隔 2 6 2 3" xfId="1560"/>
+    <cellStyle name="千位分隔 2 6 2 4" xfId="1561"/>
+    <cellStyle name="千位分隔 2 6 2 5" xfId="1562"/>
+    <cellStyle name="千位分隔 2 6 3" xfId="1563"/>
+    <cellStyle name="千位分隔 2 6 4" xfId="1564"/>
+    <cellStyle name="千位分隔 2 6 5" xfId="1565"/>
+    <cellStyle name="千位分隔 2 6 6" xfId="1566"/>
+    <cellStyle name="千位分隔 2 7" xfId="596"/>
+    <cellStyle name="千位分隔 2 7 2" xfId="1567"/>
+    <cellStyle name="千位分隔 2 7 3" xfId="1568"/>
+    <cellStyle name="千位分隔 2 7 4" xfId="1569"/>
+    <cellStyle name="千位分隔 2 7 5" xfId="1570"/>
+    <cellStyle name="千位分隔 2 8" xfId="598"/>
+    <cellStyle name="千位分隔 2 8 2" xfId="1571"/>
+    <cellStyle name="千位分隔 2 8 3" xfId="1572"/>
+    <cellStyle name="千位分隔 2 8 4" xfId="996"/>
+    <cellStyle name="千位分隔 2 8 5" xfId="1573"/>
+    <cellStyle name="千位分隔 2 9" xfId="510"/>
+    <cellStyle name="千位分隔 2 9 2" xfId="1574"/>
+    <cellStyle name="千位分隔 2 9 3" xfId="1575"/>
+    <cellStyle name="千位分隔 2 9 4" xfId="1576"/>
+    <cellStyle name="千位分隔 20" xfId="15"/>
+    <cellStyle name="千位分隔 20 2" xfId="1501"/>
+    <cellStyle name="千位分隔 21" xfId="604"/>
+    <cellStyle name="千位分隔 22" xfId="623"/>
+    <cellStyle name="千位分隔 23" xfId="640"/>
+    <cellStyle name="千位分隔 24" xfId="649"/>
+    <cellStyle name="千位分隔 25" xfId="651"/>
+    <cellStyle name="千位分隔 3" xfId="299"/>
+    <cellStyle name="千位分隔 3 2" xfId="1577"/>
+    <cellStyle name="千位分隔 3 2 2" xfId="1578"/>
+    <cellStyle name="千位分隔 3 2 2 2" xfId="900"/>
+    <cellStyle name="千位分隔 3 2 2 2 2" xfId="1579"/>
+    <cellStyle name="千位分隔 3 2 2 2 3" xfId="1580"/>
+    <cellStyle name="千位分隔 3 2 2 2 4" xfId="1581"/>
+    <cellStyle name="千位分隔 3 2 2 2 5" xfId="1582"/>
+    <cellStyle name="千位分隔 3 2 2 3" xfId="902"/>
+    <cellStyle name="千位分隔 3 2 2 4" xfId="904"/>
+    <cellStyle name="千位分隔 3 2 2 5" xfId="1583"/>
+    <cellStyle name="千位分隔 3 2 2 6" xfId="1584"/>
+    <cellStyle name="千位分隔 3 2 3" xfId="1585"/>
+    <cellStyle name="千位分隔 3 2 3 2" xfId="1586"/>
+    <cellStyle name="千位分隔 3 2 3 3" xfId="1587"/>
+    <cellStyle name="千位分隔 3 2 3 4" xfId="1588"/>
+    <cellStyle name="千位分隔 3 2 3 5" xfId="1589"/>
+    <cellStyle name="千位分隔 3 2 4" xfId="1590"/>
+    <cellStyle name="千位分隔 3 2 5" xfId="1591"/>
+    <cellStyle name="千位分隔 3 2 6" xfId="1592"/>
+    <cellStyle name="千位分隔 3 2 7" xfId="1593"/>
+    <cellStyle name="千位分隔 3 3" xfId="1594"/>
+    <cellStyle name="千位分隔 3 3 2" xfId="1595"/>
+    <cellStyle name="千位分隔 3 3 2 2" xfId="1596"/>
+    <cellStyle name="千位分隔 3 3 2 3" xfId="1597"/>
+    <cellStyle name="千位分隔 3 3 2 4" xfId="1598"/>
+    <cellStyle name="千位分隔 3 3 2 5" xfId="1599"/>
+    <cellStyle name="千位分隔 3 3 3" xfId="1600"/>
+    <cellStyle name="千位分隔 3 3 4" xfId="1601"/>
+    <cellStyle name="千位分隔 3 3 5" xfId="1602"/>
+    <cellStyle name="千位分隔 3 3 6" xfId="1603"/>
+    <cellStyle name="千位分隔 3 4" xfId="601"/>
+    <cellStyle name="千位分隔 3 4 2" xfId="43"/>
+    <cellStyle name="千位分隔 3 4 3" xfId="655"/>
+    <cellStyle name="千位分隔 3 4 4" xfId="680"/>
+    <cellStyle name="千位分隔 3 4 5" xfId="695"/>
+    <cellStyle name="千位分隔 3 5" xfId="714"/>
+    <cellStyle name="千位分隔 3 6" xfId="717"/>
+    <cellStyle name="千位分隔 3 7" xfId="720"/>
+    <cellStyle name="千位分隔 3 8" xfId="723"/>
+    <cellStyle name="千位分隔 4" xfId="1604"/>
+    <cellStyle name="千位分隔 4 2" xfId="884"/>
+    <cellStyle name="千位分隔 4 2 2" xfId="886"/>
+    <cellStyle name="千位分隔 4 2 2 2" xfId="1389"/>
+    <cellStyle name="千位分隔 4 2 2 2 2" xfId="1605"/>
+    <cellStyle name="千位分隔 4 2 2 2 3" xfId="1606"/>
+    <cellStyle name="千位分隔 4 2 2 2 4" xfId="1607"/>
+    <cellStyle name="千位分隔 4 2 2 2 5" xfId="1608"/>
+    <cellStyle name="千位分隔 4 2 2 3" xfId="1392"/>
+    <cellStyle name="千位分隔 4 2 2 4" xfId="1609"/>
+    <cellStyle name="千位分隔 4 2 2 5" xfId="1610"/>
+    <cellStyle name="千位分隔 4 2 2 6" xfId="1611"/>
+    <cellStyle name="千位分隔 4 2 3" xfId="888"/>
+    <cellStyle name="千位分隔 4 2 3 2" xfId="1411"/>
+    <cellStyle name="千位分隔 4 2 3 3" xfId="1612"/>
+    <cellStyle name="千位分隔 4 2 3 4" xfId="1613"/>
+    <cellStyle name="千位分隔 4 2 3 5" xfId="1614"/>
+    <cellStyle name="千位分隔 4 2 4" xfId="890"/>
+    <cellStyle name="千位分隔 4 2 5" xfId="892"/>
+    <cellStyle name="千位分隔 4 2 6" xfId="1615"/>
+    <cellStyle name="千位分隔 4 2 7" xfId="1616"/>
+    <cellStyle name="千位分隔 4 3" xfId="894"/>
+    <cellStyle name="千位分隔 4 3 2" xfId="1617"/>
+    <cellStyle name="千位分隔 4 3 2 2" xfId="1435"/>
+    <cellStyle name="千位分隔 4 3 2 3" xfId="1437"/>
+    <cellStyle name="千位分隔 4 3 2 4" xfId="1618"/>
+    <cellStyle name="千位分隔 4 3 2 5" xfId="1619"/>
+    <cellStyle name="千位分隔 4 3 3" xfId="1620"/>
+    <cellStyle name="千位分隔 4 3 4" xfId="1621"/>
+    <cellStyle name="千位分隔 4 3 5" xfId="1622"/>
+    <cellStyle name="千位分隔 4 3 6" xfId="1623"/>
+    <cellStyle name="千位分隔 4 4" xfId="733"/>
+    <cellStyle name="千位分隔 4 4 2" xfId="736"/>
+    <cellStyle name="千位分隔 4 4 3" xfId="761"/>
+    <cellStyle name="千位分隔 4 4 4" xfId="773"/>
+    <cellStyle name="千位分隔 4 4 5" xfId="780"/>
+    <cellStyle name="千位分隔 4 5" xfId="788"/>
+    <cellStyle name="千位分隔 4 6" xfId="809"/>
+    <cellStyle name="千位分隔 4 7" xfId="821"/>
+    <cellStyle name="千位分隔 4 8" xfId="844"/>
+    <cellStyle name="千位分隔 5" xfId="1624"/>
+    <cellStyle name="千位分隔 5 2" xfId="906"/>
+    <cellStyle name="千位分隔 6" xfId="1102"/>
+    <cellStyle name="千位分隔 6 2" xfId="916"/>
+    <cellStyle name="千位分隔 7" xfId="1625"/>
+    <cellStyle name="千位分隔 7 2" xfId="1626"/>
+    <cellStyle name="千位分隔 7 2 2" xfId="1627"/>
+    <cellStyle name="千位分隔 7 2 2 2" xfId="1628"/>
+    <cellStyle name="千位分隔 7 2 2 3" xfId="1629"/>
+    <cellStyle name="千位分隔 7 2 2 4" xfId="1630"/>
+    <cellStyle name="千位分隔 7 2 2 5" xfId="1631"/>
+    <cellStyle name="千位分隔 7 2 3" xfId="657"/>
+    <cellStyle name="千位分隔 7 2 4" xfId="668"/>
+    <cellStyle name="千位分隔 7 2 5" xfId="674"/>
+    <cellStyle name="千位分隔 7 2 6" xfId="676"/>
+    <cellStyle name="千位分隔 7 3" xfId="1632"/>
+    <cellStyle name="千位分隔 7 3 2" xfId="1633"/>
+    <cellStyle name="千位分隔 7 3 3" xfId="682"/>
+    <cellStyle name="千位分隔 7 3 4" xfId="688"/>
+    <cellStyle name="千位分隔 7 3 5" xfId="690"/>
+    <cellStyle name="千位分隔 7 4" xfId="983"/>
+    <cellStyle name="千位分隔 7 5" xfId="1634"/>
+    <cellStyle name="千位分隔 7 6" xfId="1635"/>
+    <cellStyle name="千位分隔 7 7" xfId="1636"/>
+    <cellStyle name="千位分隔 8" xfId="1637"/>
+    <cellStyle name="千位分隔 8 2" xfId="1638"/>
+    <cellStyle name="千位分隔 8 3" xfId="1639"/>
+    <cellStyle name="千位分隔 9" xfId="1640"/>
+    <cellStyle name="常规 10" xfId="439"/>
+    <cellStyle name="常规 10 10" xfId="1010"/>
+    <cellStyle name="常规 10 11" xfId="1011"/>
+    <cellStyle name="常规 10 12" xfId="1654"/>
+    <cellStyle name="常规 10 2" xfId="441"/>
+    <cellStyle name="常规 10 2 2" xfId="443"/>
+    <cellStyle name="常规 10 2 2 2" xfId="1012"/>
+    <cellStyle name="常规 10 2 2 2 2" xfId="1013"/>
+    <cellStyle name="常规 10 2 2 2 2 2" xfId="1014"/>
+    <cellStyle name="常规 10 2 2 2 3" xfId="1015"/>
+    <cellStyle name="常规 10 2 2 2 4" xfId="1016"/>
+    <cellStyle name="常规 10 2 2 2 5" xfId="1017"/>
+    <cellStyle name="常规 10 2 2 2 6" xfId="1018"/>
+    <cellStyle name="常规 10 2 2 3" xfId="1019"/>
+    <cellStyle name="常规 10 2 2 3 2" xfId="1020"/>
+    <cellStyle name="常规 10 2 2 4" xfId="1021"/>
+    <cellStyle name="常规 10 2 2 5" xfId="1022"/>
+    <cellStyle name="常规 10 2 2 6" xfId="1023"/>
+    <cellStyle name="常规 10 2 3" xfId="445"/>
+    <cellStyle name="常规 10 2 3 2" xfId="556"/>
+    <cellStyle name="常规 10 2 3 2 2" xfId="1024"/>
+    <cellStyle name="常规 10 2 3 2 2 2" xfId="1025"/>
+    <cellStyle name="常规 10 2 3 2 3" xfId="1026"/>
+    <cellStyle name="常规 10 2 3 2 4" xfId="1027"/>
+    <cellStyle name="常规 10 2 3 2 5" xfId="1028"/>
+    <cellStyle name="常规 10 2 3 2 6" xfId="1029"/>
+    <cellStyle name="常规 10 2 3 3" xfId="1030"/>
+    <cellStyle name="常规 10 2 3 3 2" xfId="1031"/>
+    <cellStyle name="常规 10 2 3 4" xfId="1032"/>
+    <cellStyle name="常规 10 2 3 5" xfId="1033"/>
+    <cellStyle name="常规 10 2 3 6" xfId="1034"/>
+    <cellStyle name="常规 10 2 4" xfId="169"/>
+    <cellStyle name="常规 10 2 4 2" xfId="490"/>
+    <cellStyle name="常规 10 2 4 2 2" xfId="1035"/>
+    <cellStyle name="常规 10 2 4 2 2 2" xfId="459"/>
+    <cellStyle name="常规 10 2 4 2 3" xfId="1036"/>
+    <cellStyle name="常规 10 2 4 2 4" xfId="1037"/>
+    <cellStyle name="常规 10 2 4 2 5" xfId="1038"/>
+    <cellStyle name="常规 10 2 4 3" xfId="1039"/>
+    <cellStyle name="常规 10 2 4 3 2" xfId="1040"/>
+    <cellStyle name="常规 10 2 4 3 2 2" xfId="1041"/>
+    <cellStyle name="常规 10 2 4 3 3" xfId="1042"/>
+    <cellStyle name="常规 10 2 4 3 4" xfId="1043"/>
+    <cellStyle name="常规 10 2 4 3 5" xfId="1044"/>
+    <cellStyle name="常规 10 2 4 3 6" xfId="1046"/>
+    <cellStyle name="常规 10 2 4 4" xfId="1047"/>
+    <cellStyle name="常规 10 2 4 4 2" xfId="1048"/>
+    <cellStyle name="常规 10 2 4 5" xfId="1049"/>
+    <cellStyle name="常规 10 2 4 6" xfId="1050"/>
+    <cellStyle name="常规 10 2 4 7" xfId="1051"/>
+    <cellStyle name="常规 10 2 5" xfId="173"/>
+    <cellStyle name="常规 10 2 5 2" xfId="1052"/>
+    <cellStyle name="常规 10 2 5 2 2" xfId="1053"/>
+    <cellStyle name="常规 10 2 5 3" xfId="1054"/>
+    <cellStyle name="常规 10 2 5 4" xfId="1055"/>
+    <cellStyle name="常规 10 2 5 5" xfId="1056"/>
+    <cellStyle name="常规 10 2 5 6" xfId="1057"/>
+    <cellStyle name="常规 10 2 6" xfId="1058"/>
+    <cellStyle name="常规 10 2 6 2" xfId="1059"/>
+    <cellStyle name="常规 10 2 7" xfId="1060"/>
+    <cellStyle name="常规 10 2 8" xfId="1061"/>
+    <cellStyle name="常规 10 2 9" xfId="1062"/>
+    <cellStyle name="常规 10 3" xfId="447"/>
+    <cellStyle name="常规 10 3 2" xfId="1063"/>
+    <cellStyle name="常规 10 3 2 2" xfId="1064"/>
+    <cellStyle name="常规 10 3 2 2 2" xfId="1065"/>
+    <cellStyle name="常规 10 3 2 3" xfId="1066"/>
+    <cellStyle name="常规 10 3 2 4" xfId="1067"/>
+    <cellStyle name="常规 10 3 2 5" xfId="1068"/>
+    <cellStyle name="常规 10 3 3" xfId="1069"/>
+    <cellStyle name="常规 10 3 3 2" xfId="1070"/>
+    <cellStyle name="常规 10 3 3 2 2" xfId="1071"/>
+    <cellStyle name="常规 10 3 3 3" xfId="1072"/>
+    <cellStyle name="常规 10 3 3 4" xfId="1073"/>
+    <cellStyle name="常规 10 3 3 5" xfId="1074"/>
+    <cellStyle name="常规 10 3 3 6" xfId="1075"/>
+    <cellStyle name="常规 10 3 4" xfId="1076"/>
+    <cellStyle name="常规 10 3 4 2" xfId="1077"/>
+    <cellStyle name="常规 10 3 5" xfId="1078"/>
+    <cellStyle name="常规 10 3 6" xfId="1079"/>
+    <cellStyle name="常规 10 3 7" xfId="1080"/>
+    <cellStyle name="常规 10 4" xfId="449"/>
+    <cellStyle name="常规 10 4 2" xfId="1081"/>
+    <cellStyle name="常规 10 4 2 2" xfId="1082"/>
+    <cellStyle name="常规 10 4 2 2 2" xfId="1083"/>
+    <cellStyle name="常规 10 4 2 3" xfId="1084"/>
+    <cellStyle name="常规 10 4 2 4" xfId="1085"/>
+    <cellStyle name="常规 10 4 2 5" xfId="1086"/>
+    <cellStyle name="常规 10 4 3" xfId="1087"/>
+    <cellStyle name="常规 10 4 3 2" xfId="1088"/>
+    <cellStyle name="常规 10 4 3 2 2" xfId="1090"/>
+    <cellStyle name="常规 10 4 3 3" xfId="1091"/>
+    <cellStyle name="常规 10 4 3 4" xfId="1092"/>
+    <cellStyle name="常规 10 4 3 5" xfId="1093"/>
+    <cellStyle name="常规 10 4 3 6" xfId="1094"/>
+    <cellStyle name="常规 10 4 4" xfId="1095"/>
+    <cellStyle name="常规 10 4 4 2" xfId="1096"/>
+    <cellStyle name="常规 10 4 5" xfId="1097"/>
+    <cellStyle name="常规 10 4 6" xfId="1098"/>
+    <cellStyle name="常规 10 4 7" xfId="1099"/>
+    <cellStyle name="常规 10 5" xfId="451"/>
+    <cellStyle name="常规 10 5 2" xfId="1100"/>
+    <cellStyle name="常规 10 5 2 2" xfId="1101"/>
+    <cellStyle name="常规 10 5 2 2 2" xfId="1103"/>
+    <cellStyle name="常规 10 5 2 3" xfId="1104"/>
+    <cellStyle name="常规 10 5 2 4" xfId="1105"/>
+    <cellStyle name="常规 10 5 2 5" xfId="1106"/>
+    <cellStyle name="常规 10 5 3" xfId="1107"/>
+    <cellStyle name="常规 10 5 3 2" xfId="1108"/>
+    <cellStyle name="常规 10 5 3 2 2" xfId="1109"/>
+    <cellStyle name="常规 10 5 3 3" xfId="1110"/>
+    <cellStyle name="常规 10 5 3 4" xfId="1111"/>
+    <cellStyle name="常规 10 5 3 5" xfId="1112"/>
+    <cellStyle name="常规 10 5 3 6" xfId="1113"/>
+    <cellStyle name="常规 10 5 4" xfId="1114"/>
+    <cellStyle name="常规 10 5 4 2" xfId="1115"/>
+    <cellStyle name="常规 10 5 5" xfId="1116"/>
+    <cellStyle name="常规 10 5 6" xfId="1118"/>
+    <cellStyle name="常规 10 5 7" xfId="1120"/>
+    <cellStyle name="常规 10 6" xfId="453"/>
+    <cellStyle name="常规 10 6 2" xfId="1121"/>
+    <cellStyle name="常规 10 6 2 2" xfId="1122"/>
+    <cellStyle name="常规 10 6 3" xfId="1123"/>
+    <cellStyle name="常规 10 6 4" xfId="1124"/>
+    <cellStyle name="常规 10 6 5" xfId="1125"/>
+    <cellStyle name="常规 10 6 6" xfId="429"/>
+    <cellStyle name="常规 10 7" xfId="1126"/>
+    <cellStyle name="常规 10 7 2" xfId="1127"/>
+    <cellStyle name="常规 10 7 2 2" xfId="1128"/>
+    <cellStyle name="常规 10 7 3" xfId="1129"/>
+    <cellStyle name="常规 10 7 4" xfId="1130"/>
+    <cellStyle name="常规 10 7 5" xfId="1131"/>
+    <cellStyle name="常规 10 7 6" xfId="1133"/>
+    <cellStyle name="常规 10 8" xfId="1134"/>
+    <cellStyle name="常规 10 8 2" xfId="1135"/>
+    <cellStyle name="常规 10 8 3" xfId="1136"/>
+    <cellStyle name="常规 10 8 4" xfId="1137"/>
+    <cellStyle name="常规 10 8 5" xfId="1138"/>
+    <cellStyle name="常规 10 9" xfId="1139"/>
+    <cellStyle name="常规 11" xfId="455"/>
+    <cellStyle name="常规 11 2" xfId="457"/>
+    <cellStyle name="常规 11 3" xfId="1647"/>
+    <cellStyle name="常规 12" xfId="463"/>
+    <cellStyle name="常规 12 2" xfId="745"/>
+    <cellStyle name="常规 13" xfId="363"/>
+    <cellStyle name="常规 13 2" xfId="753"/>
+    <cellStyle name="常规 14" xfId="405"/>
+    <cellStyle name="常规 14 2" xfId="1140"/>
+    <cellStyle name="常规 15" xfId="5"/>
+    <cellStyle name="常规 15 2" xfId="1142"/>
+    <cellStyle name="常规 15 2 2" xfId="1143"/>
+    <cellStyle name="常规 15 2 2 2" xfId="1144"/>
+    <cellStyle name="常规 15 2 2 3" xfId="1145"/>
+    <cellStyle name="常规 15 2 2 4" xfId="1146"/>
+    <cellStyle name="常规 15 2 2 5" xfId="1147"/>
+    <cellStyle name="常规 15 2 3" xfId="1148"/>
+    <cellStyle name="常规 15 2 4" xfId="897"/>
+    <cellStyle name="常规 15 2 5" xfId="907"/>
+    <cellStyle name="常规 15 2 6" xfId="909"/>
+    <cellStyle name="常规 15 3" xfId="1151"/>
+    <cellStyle name="常规 15 3 2" xfId="1152"/>
+    <cellStyle name="常规 15 3 3" xfId="1153"/>
+    <cellStyle name="常规 15 3 4" xfId="914"/>
+    <cellStyle name="常规 15 3 5" xfId="917"/>
+    <cellStyle name="常规 15 4" xfId="1155"/>
+    <cellStyle name="常规 15 5" xfId="1157"/>
+    <cellStyle name="常规 15 6" xfId="1159"/>
+    <cellStyle name="常规 15 7" xfId="1160"/>
+    <cellStyle name="常规 15 8" xfId="239"/>
+    <cellStyle name="常规 16" xfId="1162"/>
+    <cellStyle name="常规 16 2" xfId="1164"/>
+    <cellStyle name="常规 16 2 2" xfId="1165"/>
+    <cellStyle name="常规 16 2 2 2" xfId="1167"/>
+    <cellStyle name="常规 16 2 2 3" xfId="1169"/>
+    <cellStyle name="常规 16 2 2 4" xfId="171"/>
+    <cellStyle name="常规 16 2 2 5" xfId="175"/>
+    <cellStyle name="常规 16 2 3" xfId="1170"/>
+    <cellStyle name="常规 16 2 4" xfId="932"/>
+    <cellStyle name="常规 16 2 5" xfId="934"/>
+    <cellStyle name="常规 16 2 6" xfId="936"/>
+    <cellStyle name="常规 16 3" xfId="1171"/>
+    <cellStyle name="常规 16 3 2" xfId="1172"/>
+    <cellStyle name="常规 16 3 3" xfId="1173"/>
+    <cellStyle name="常规 16 3 4" xfId="1174"/>
+    <cellStyle name="常规 16 3 5" xfId="1175"/>
+    <cellStyle name="常规 16 4" xfId="1176"/>
+    <cellStyle name="常规 16 5" xfId="1177"/>
+    <cellStyle name="常规 16 6" xfId="1178"/>
+    <cellStyle name="常规 16 7" xfId="1179"/>
+    <cellStyle name="常规 17" xfId="1181"/>
+    <cellStyle name="常规 17 2" xfId="1183"/>
+    <cellStyle name="常规 17 3" xfId="1185"/>
+    <cellStyle name="常规 18" xfId="1187"/>
+    <cellStyle name="常规 18 2" xfId="1189"/>
+    <cellStyle name="常规 18 3" xfId="1191"/>
+    <cellStyle name="常规 19" xfId="1193"/>
+    <cellStyle name="常规 19 2" xfId="10"/>
+    <cellStyle name="常规 19 3" xfId="1195"/>
+    <cellStyle name="常规 2" xfId="1196"/>
+    <cellStyle name="常规 2 10" xfId="1658"/>
+    <cellStyle name="常规 2 2" xfId="1197"/>
+    <cellStyle name="常规 2 2 2" xfId="1198"/>
+    <cellStyle name="常规 2 2 2 2" xfId="1117"/>
+    <cellStyle name="常规 2 2 2 2 2" xfId="1199"/>
+    <cellStyle name="常规 2 2 2 2 3" xfId="1200"/>
+    <cellStyle name="常规 2 2 2 2 4" xfId="1201"/>
+    <cellStyle name="常规 2 2 2 2 5" xfId="1202"/>
+    <cellStyle name="常规 2 2 2 3" xfId="1119"/>
+    <cellStyle name="常规 2 2 2 4" xfId="61"/>
+    <cellStyle name="常规 2 2 2 5" xfId="50"/>
+    <cellStyle name="常规 2 2 2 6" xfId="63"/>
+    <cellStyle name="常规 2 2 3" xfId="567"/>
+    <cellStyle name="常规 2 2 3 2" xfId="428"/>
+    <cellStyle name="常规 2 2 3 2 2" xfId="1204"/>
+    <cellStyle name="常规 2 2 3 2 3" xfId="1206"/>
+    <cellStyle name="常规 2 2 3 2 4" xfId="513"/>
+    <cellStyle name="常规 2 2 3 2 5" xfId="1208"/>
+    <cellStyle name="常规 2 2 3 3" xfId="432"/>
+    <cellStyle name="常规 2 2 3 4" xfId="435"/>
+    <cellStyle name="常规 2 2 3 5" xfId="569"/>
+    <cellStyle name="常规 2 2 3 6" xfId="1209"/>
+    <cellStyle name="常规 2 2 4" xfId="25"/>
+    <cellStyle name="常规 2 2 4 2" xfId="1132"/>
+    <cellStyle name="常规 2 2 4 3" xfId="1210"/>
+    <cellStyle name="常规 2 2 4 4" xfId="1211"/>
+    <cellStyle name="常规 2 2 4 5" xfId="1212"/>
+    <cellStyle name="常规 2 2 5" xfId="571"/>
+    <cellStyle name="常规 2 2 6" xfId="573"/>
+    <cellStyle name="常规 2 2 7" xfId="575"/>
+    <cellStyle name="常规 2 2 8" xfId="1213"/>
+    <cellStyle name="常规 2 3" xfId="1214"/>
+    <cellStyle name="常规 2 3 2" xfId="1215"/>
+    <cellStyle name="常规 2 3 2 2" xfId="1216"/>
+    <cellStyle name="常规 2 3 2 3" xfId="1217"/>
+    <cellStyle name="常规 2 3 2 4" xfId="1218"/>
+    <cellStyle name="常规 2 3 2 5" xfId="1219"/>
+    <cellStyle name="常规 2 3 3" xfId="577"/>
+    <cellStyle name="常规 2 3 4" xfId="416"/>
+    <cellStyle name="常规 2 3 5" xfId="419"/>
+    <cellStyle name="常规 2 3 6" xfId="422"/>
+    <cellStyle name="常规 2 4" xfId="1220"/>
+    <cellStyle name="常规 2 4 2" xfId="1221"/>
+    <cellStyle name="常规 2 4 2 2" xfId="1222"/>
+    <cellStyle name="常规 2 4 2 3" xfId="1223"/>
+    <cellStyle name="常规 2 4 2 4" xfId="1224"/>
+    <cellStyle name="常规 2 4 2 5" xfId="1225"/>
+    <cellStyle name="常规 2 4 3" xfId="1226"/>
+    <cellStyle name="常规 2 4 4" xfId="1227"/>
+    <cellStyle name="常规 2 4 5" xfId="1228"/>
+    <cellStyle name="常规 2 4 6" xfId="1229"/>
+    <cellStyle name="常规 2 5" xfId="1230"/>
+    <cellStyle name="常规 2 5 2" xfId="1231"/>
+    <cellStyle name="常规 2 5 2 2" xfId="1232"/>
+    <cellStyle name="常规 2 5 2 3" xfId="1233"/>
+    <cellStyle name="常规 2 5 2 4" xfId="1234"/>
+    <cellStyle name="常规 2 5 2 5" xfId="1000"/>
+    <cellStyle name="常规 2 5 3" xfId="1235"/>
+    <cellStyle name="常规 2 5 4" xfId="1236"/>
+    <cellStyle name="常规 2 5 5" xfId="1237"/>
+    <cellStyle name="常规 2 5 6" xfId="1238"/>
+    <cellStyle name="常规 2 6" xfId="1239"/>
+    <cellStyle name="常规 2 6 2" xfId="1240"/>
+    <cellStyle name="常规 2 6 3" xfId="1241"/>
+    <cellStyle name="常规 2 6 4" xfId="1242"/>
+    <cellStyle name="常规 2 6 5" xfId="1243"/>
+    <cellStyle name="常规 2 7" xfId="1166"/>
+    <cellStyle name="常规 2 7 2" xfId="1244"/>
+    <cellStyle name="常规 2 7 3" xfId="1245"/>
+    <cellStyle name="常规 2 7 4" xfId="1246"/>
+    <cellStyle name="常规 2 8" xfId="1168"/>
+    <cellStyle name="常规 2 8 2" xfId="967"/>
+    <cellStyle name="常规 2 8 3" xfId="969"/>
+    <cellStyle name="常规 2 9" xfId="1648"/>
+    <cellStyle name="常规 20" xfId="238"/>
+    <cellStyle name="常规 20 2" xfId="1141"/>
+    <cellStyle name="常规 20 3" xfId="1150"/>
+    <cellStyle name="常规 21" xfId="1161"/>
+    <cellStyle name="常规 21 2" xfId="1163"/>
+    <cellStyle name="常规 22" xfId="1180"/>
+    <cellStyle name="常规 22 2" xfId="1182"/>
+    <cellStyle name="常规 22 2 2" xfId="1247"/>
+    <cellStyle name="常规 22 2 3" xfId="1248"/>
+    <cellStyle name="常规 22 2 4" xfId="1249"/>
+    <cellStyle name="常规 22 2 5" xfId="103"/>
+    <cellStyle name="常规 22 3" xfId="1184"/>
+    <cellStyle name="常规 22 4" xfId="1250"/>
+    <cellStyle name="常规 22 5" xfId="1251"/>
+    <cellStyle name="常规 22 6" xfId="1252"/>
+    <cellStyle name="常规 23" xfId="1186"/>
+    <cellStyle name="常规 23 2" xfId="1188"/>
+    <cellStyle name="常规 23 2 2" xfId="1253"/>
+    <cellStyle name="常规 23 2 3" xfId="1254"/>
+    <cellStyle name="常规 23 2 4" xfId="1255"/>
+    <cellStyle name="常规 23 2 5" xfId="142"/>
+    <cellStyle name="常规 23 3" xfId="1190"/>
+    <cellStyle name="常规 23 4" xfId="1256"/>
+    <cellStyle name="常规 23 5" xfId="1257"/>
+    <cellStyle name="常规 23 6" xfId="1258"/>
+    <cellStyle name="常规 24" xfId="1192"/>
+    <cellStyle name="常规 24 2" xfId="1194"/>
+    <cellStyle name="常规 25" xfId="1260"/>
+    <cellStyle name="常规 25 2" xfId="1261"/>
+    <cellStyle name="常规 26" xfId="1263"/>
+    <cellStyle name="常规 26 2" xfId="31"/>
+    <cellStyle name="常规 27" xfId="1265"/>
+    <cellStyle name="常规 27 2" xfId="1267"/>
+    <cellStyle name="常规 27 2 2" xfId="1268"/>
+    <cellStyle name="常规 27 2 3" xfId="1269"/>
+    <cellStyle name="常规 27 2 4" xfId="1270"/>
+    <cellStyle name="常规 27 2 5" xfId="1271"/>
+    <cellStyle name="常规 27 3" xfId="1273"/>
+    <cellStyle name="常规 27 4" xfId="1275"/>
+    <cellStyle name="常规 27 5" xfId="1277"/>
+    <cellStyle name="常规 27 6" xfId="1278"/>
+    <cellStyle name="常规 28" xfId="1280"/>
+    <cellStyle name="常规 28 2" xfId="153"/>
+    <cellStyle name="常规 28 2 2" xfId="1281"/>
+    <cellStyle name="常规 28 2 3" xfId="1282"/>
+    <cellStyle name="常规 28 2 4" xfId="1283"/>
+    <cellStyle name="常规 28 2 5" xfId="1284"/>
+    <cellStyle name="常规 28 3" xfId="161"/>
+    <cellStyle name="常规 28 4" xfId="1285"/>
+    <cellStyle name="常规 28 5" xfId="1286"/>
+    <cellStyle name="常规 28 6" xfId="1288"/>
+    <cellStyle name="常规 29" xfId="1290"/>
+    <cellStyle name="常规 29 2" xfId="1292"/>
+    <cellStyle name="常规 29 2 2" xfId="1293"/>
+    <cellStyle name="常规 29 2 3" xfId="1294"/>
+    <cellStyle name="常规 29 2 4" xfId="1295"/>
+    <cellStyle name="常规 29 2 5" xfId="1296"/>
+    <cellStyle name="常规 29 3" xfId="1297"/>
+    <cellStyle name="常规 29 4" xfId="1298"/>
+    <cellStyle name="常规 29 5" xfId="1299"/>
+    <cellStyle name="常规 29 6" xfId="1301"/>
+    <cellStyle name="常规 3" xfId="1302"/>
+    <cellStyle name="常规 3 10" xfId="1659"/>
+    <cellStyle name="常规 3 2" xfId="1002"/>
+    <cellStyle name="常规 3 2 2" xfId="1004"/>
+    <cellStyle name="常规 3 2 2 2" xfId="397"/>
+    <cellStyle name="常规 3 2 2 2 2" xfId="1303"/>
+    <cellStyle name="常规 3 2 2 2 3" xfId="1304"/>
+    <cellStyle name="常规 3 2 2 2 4" xfId="1305"/>
+    <cellStyle name="常规 3 2 2 2 5" xfId="1306"/>
+    <cellStyle name="常规 3 2 2 3" xfId="401"/>
+    <cellStyle name="常规 3 2 2 4" xfId="1307"/>
+    <cellStyle name="常规 3 2 2 5" xfId="1308"/>
+    <cellStyle name="常规 3 2 2 6" xfId="1309"/>
+    <cellStyle name="常规 3 2 3" xfId="1310"/>
+    <cellStyle name="常规 3 2 3 2" xfId="1311"/>
+    <cellStyle name="常规 3 2 3 3" xfId="1312"/>
+    <cellStyle name="常规 3 2 3 4" xfId="1313"/>
+    <cellStyle name="常规 3 2 3 5" xfId="867"/>
+    <cellStyle name="常规 3 2 4" xfId="1314"/>
+    <cellStyle name="常规 3 2 5" xfId="927"/>
+    <cellStyle name="常规 3 2 6" xfId="871"/>
+    <cellStyle name="常规 3 2 7" xfId="874"/>
+    <cellStyle name="常规 3 3" xfId="1006"/>
+    <cellStyle name="常规 3 3 2" xfId="1008"/>
+    <cellStyle name="常规 3 3 2 2" xfId="1315"/>
+    <cellStyle name="常规 3 3 2 3" xfId="1316"/>
+    <cellStyle name="常规 3 3 2 4" xfId="1317"/>
+    <cellStyle name="常规 3 3 2 5" xfId="1318"/>
+    <cellStyle name="常规 3 3 3" xfId="1319"/>
+    <cellStyle name="常规 3 3 4" xfId="1320"/>
+    <cellStyle name="常规 3 3 5" xfId="1321"/>
+    <cellStyle name="常规 3 3 6" xfId="1322"/>
+    <cellStyle name="常规 3 4" xfId="1323"/>
+    <cellStyle name="常规 3 5" xfId="1324"/>
+    <cellStyle name="常规 3 5 2" xfId="1325"/>
+    <cellStyle name="常规 3 5 3" xfId="1326"/>
+    <cellStyle name="常规 3 5 4" xfId="1327"/>
+    <cellStyle name="常规 3 5 5" xfId="1329"/>
+    <cellStyle name="常规 3 6" xfId="1330"/>
+    <cellStyle name="常规 3 6 2" xfId="1331"/>
+    <cellStyle name="常规 3 7" xfId="1332"/>
+    <cellStyle name="常规 3 7 2" xfId="92"/>
+    <cellStyle name="常规 3 7 3" xfId="1333"/>
+    <cellStyle name="常规 3 8" xfId="1334"/>
+    <cellStyle name="常规 3 9" xfId="1649"/>
+    <cellStyle name="常规 30" xfId="1259"/>
+    <cellStyle name="常规 31" xfId="1262"/>
+    <cellStyle name="常规 31 2" xfId="30"/>
+    <cellStyle name="常规 31 2 2" xfId="1335"/>
+    <cellStyle name="常规 31 2 3" xfId="1336"/>
+    <cellStyle name="常规 31 2 4" xfId="1337"/>
+    <cellStyle name="常规 31 2 5" xfId="1338"/>
+    <cellStyle name="常规 31 3" xfId="67"/>
+    <cellStyle name="常规 31 4" xfId="70"/>
+    <cellStyle name="常规 31 5" xfId="74"/>
+    <cellStyle name="常规 31 6" xfId="1339"/>
+    <cellStyle name="常规 32" xfId="1264"/>
+    <cellStyle name="常规 32 2" xfId="1266"/>
+    <cellStyle name="常规 32 3" xfId="1272"/>
+    <cellStyle name="常规 32 4" xfId="1274"/>
+    <cellStyle name="常规 32 5" xfId="1276"/>
+    <cellStyle name="常规 33" xfId="8"/>
+    <cellStyle name="常规 33 2" xfId="152"/>
+    <cellStyle name="常规 33 3" xfId="1279"/>
+    <cellStyle name="常规 34" xfId="1289"/>
+    <cellStyle name="常规 34 2" xfId="1291"/>
+    <cellStyle name="常规 35" xfId="12"/>
+    <cellStyle name="常规 35 2" xfId="1341"/>
+    <cellStyle name="常规 36" xfId="1343"/>
+    <cellStyle name="常规 36 2" xfId="1345"/>
+    <cellStyle name="常规 37" xfId="1347"/>
+    <cellStyle name="常规 37 2" xfId="1349"/>
+    <cellStyle name="常规 37 3" xfId="1350"/>
+    <cellStyle name="常规 38" xfId="824"/>
+    <cellStyle name="常规 38 2" xfId="827"/>
+    <cellStyle name="常规 38 3" xfId="829"/>
+    <cellStyle name="常规 38 4" xfId="831"/>
+    <cellStyle name="常规 38 5" xfId="833"/>
+    <cellStyle name="常规 39" xfId="23"/>
+    <cellStyle name="常规 39 2" xfId="1352"/>
+    <cellStyle name="常规 39 3" xfId="1353"/>
+    <cellStyle name="常规 39 4" xfId="1354"/>
+    <cellStyle name="常规 4" xfId="1355"/>
+    <cellStyle name="常规 4 2" xfId="1356"/>
+    <cellStyle name="常规 4 2 2" xfId="1358"/>
+    <cellStyle name="常规 4 2 2 2" xfId="1361"/>
+    <cellStyle name="常规 4 2 2 2 2" xfId="1363"/>
+    <cellStyle name="常规 4 2 2 2 3" xfId="1365"/>
+    <cellStyle name="常规 4 2 2 2 4" xfId="1367"/>
+    <cellStyle name="常规 4 2 2 2 5" xfId="1369"/>
+    <cellStyle name="常规 4 2 2 3" xfId="41"/>
+    <cellStyle name="常规 4 2 2 4" xfId="1372"/>
+    <cellStyle name="常规 4 2 2 5" xfId="1375"/>
+    <cellStyle name="常规 4 2 2 6" xfId="1377"/>
+    <cellStyle name="常规 4 2 3" xfId="1379"/>
+    <cellStyle name="常规 4 2 3 2" xfId="1380"/>
+    <cellStyle name="常规 4 2 3 3" xfId="1381"/>
+    <cellStyle name="常规 4 2 3 4" xfId="1382"/>
+    <cellStyle name="常规 4 2 3 5" xfId="1384"/>
+    <cellStyle name="常规 4 2 4" xfId="1386"/>
+    <cellStyle name="常规 4 2 5" xfId="1388"/>
+    <cellStyle name="常规 4 2 6" xfId="1391"/>
+    <cellStyle name="常规 4 2 7" xfId="1393"/>
+    <cellStyle name="常规 4 3" xfId="1394"/>
+    <cellStyle name="常规 4 3 2" xfId="1396"/>
+    <cellStyle name="常规 4 3 2 2" xfId="1398"/>
+    <cellStyle name="常规 4 3 2 3" xfId="1400"/>
+    <cellStyle name="常规 4 3 2 4" xfId="1402"/>
+    <cellStyle name="常规 4 3 2 5" xfId="1404"/>
+    <cellStyle name="常规 4 3 3" xfId="1406"/>
+    <cellStyle name="常规 4 3 4" xfId="1408"/>
+    <cellStyle name="常规 4 3 5" xfId="1410"/>
+    <cellStyle name="常规 4 3 6" xfId="1413"/>
+    <cellStyle name="常规 4 4" xfId="1357"/>
+    <cellStyle name="常规 4 4 2" xfId="1360"/>
+    <cellStyle name="常规 4 4 3" xfId="40"/>
+    <cellStyle name="常规 4 4 4" xfId="1371"/>
+    <cellStyle name="常规 4 4 5" xfId="1374"/>
+    <cellStyle name="常规 4 5" xfId="1378"/>
+    <cellStyle name="常规 4 6" xfId="1385"/>
+    <cellStyle name="常规 4 7" xfId="1387"/>
+    <cellStyle name="常规 4 8" xfId="1390"/>
+    <cellStyle name="常规 40" xfId="1340"/>
+    <cellStyle name="常规 40 2" xfId="1414"/>
+    <cellStyle name="常规 41" xfId="1342"/>
+    <cellStyle name="常规 41 2" xfId="1344"/>
+    <cellStyle name="常规 42" xfId="1346"/>
+    <cellStyle name="常规 42 2" xfId="1348"/>
+    <cellStyle name="常规 43" xfId="823"/>
+    <cellStyle name="常规 43 2" xfId="826"/>
+    <cellStyle name="常规 44" xfId="22"/>
+    <cellStyle name="常规 44 2" xfId="1351"/>
+    <cellStyle name="常规 45" xfId="836"/>
+    <cellStyle name="常规 45 2" xfId="1415"/>
+    <cellStyle name="常规 46" xfId="839"/>
+    <cellStyle name="常规 47" xfId="842"/>
+    <cellStyle name="常规 47 2" xfId="1416"/>
+    <cellStyle name="常规 48" xfId="1418"/>
+    <cellStyle name="常规 49" xfId="1420"/>
+    <cellStyle name="常规 5" xfId="1421"/>
+    <cellStyle name="常规 5 2" xfId="1422"/>
+    <cellStyle name="常规 5 2 2" xfId="1423"/>
+    <cellStyle name="常规 5 2 2 2" xfId="1424"/>
+    <cellStyle name="常规 5 2 2 2 2" xfId="1149"/>
+    <cellStyle name="常规 5 2 2 2 3" xfId="1154"/>
+    <cellStyle name="常规 5 2 2 2 4" xfId="1156"/>
+    <cellStyle name="常规 5 2 2 2 5" xfId="1158"/>
+    <cellStyle name="常规 5 2 2 3" xfId="1425"/>
+    <cellStyle name="常规 5 2 2 4" xfId="1426"/>
+    <cellStyle name="常规 5 2 2 5" xfId="1427"/>
+    <cellStyle name="常规 5 2 2 6" xfId="1428"/>
+    <cellStyle name="常规 5 2 3" xfId="1429"/>
+    <cellStyle name="常规 5 2 3 2" xfId="1045"/>
+    <cellStyle name="常规 5 2 3 3" xfId="1430"/>
+    <cellStyle name="常规 5 2 3 4" xfId="1431"/>
+    <cellStyle name="常规 5 2 3 5" xfId="1432"/>
+    <cellStyle name="常规 5 2 4" xfId="1433"/>
+    <cellStyle name="常规 5 2 5" xfId="1434"/>
+    <cellStyle name="常规 5 2 6" xfId="1436"/>
+    <cellStyle name="常规 5 2 7" xfId="1438"/>
+    <cellStyle name="常规 5 3" xfId="1439"/>
+    <cellStyle name="常规 5 3 2" xfId="337"/>
+    <cellStyle name="常规 5 3 2 2" xfId="341"/>
+    <cellStyle name="常规 5 3 2 3" xfId="345"/>
+    <cellStyle name="常规 5 3 2 4" xfId="1440"/>
+    <cellStyle name="常规 5 3 2 5" xfId="1441"/>
+    <cellStyle name="常规 5 3 3" xfId="499"/>
+    <cellStyle name="常规 5 3 4" xfId="503"/>
+    <cellStyle name="常规 5 3 5" xfId="505"/>
+    <cellStyle name="常规 5 3 6" xfId="507"/>
+    <cellStyle name="常规 5 4" xfId="1395"/>
+    <cellStyle name="常规 5 4 2" xfId="1397"/>
+    <cellStyle name="常规 5 4 3" xfId="1399"/>
+    <cellStyle name="常规 5 4 4" xfId="1401"/>
+    <cellStyle name="常规 5 4 5" xfId="1403"/>
+    <cellStyle name="常规 5 5" xfId="1405"/>
+    <cellStyle name="常规 5 6" xfId="1407"/>
+    <cellStyle name="常规 5 7" xfId="1409"/>
+    <cellStyle name="常规 5 8" xfId="1412"/>
+    <cellStyle name="常规 50" xfId="835"/>
+    <cellStyle name="常规 51" xfId="838"/>
+    <cellStyle name="常规 52" xfId="841"/>
+    <cellStyle name="常规 53" xfId="1417"/>
+    <cellStyle name="常规 54" xfId="1419"/>
+    <cellStyle name="常规 55" xfId="85"/>
+    <cellStyle name="常规 56" xfId="105"/>
+    <cellStyle name="常规 57" xfId="109"/>
+    <cellStyle name="常规 6" xfId="1442"/>
+    <cellStyle name="常规 6 2" xfId="1443"/>
+    <cellStyle name="常规 6 2 2" xfId="634"/>
+    <cellStyle name="常规 6 2 2 2" xfId="1444"/>
+    <cellStyle name="常规 6 2 2 2 2" xfId="774"/>
+    <cellStyle name="常规 6 2 2 2 3" xfId="781"/>
+    <cellStyle name="常规 6 2 2 2 4" xfId="783"/>
+    <cellStyle name="常规 6 2 2 2 5" xfId="785"/>
+    <cellStyle name="常规 6 2 2 3" xfId="1445"/>
+    <cellStyle name="常规 6 2 2 4" xfId="1446"/>
+    <cellStyle name="常规 6 2 2 5" xfId="1447"/>
+    <cellStyle name="常规 6 2 2 6" xfId="1448"/>
+    <cellStyle name="常规 6 2 3" xfId="636"/>
+    <cellStyle name="常规 6 2 3 2" xfId="1449"/>
+    <cellStyle name="常规 6 2 3 3" xfId="1450"/>
+    <cellStyle name="常规 6 2 3 4" xfId="1451"/>
+    <cellStyle name="常规 6 2 3 5" xfId="1452"/>
+    <cellStyle name="常规 6 2 4" xfId="638"/>
+    <cellStyle name="常规 6 2 5" xfId="1453"/>
+    <cellStyle name="常规 6 2 6" xfId="738"/>
+    <cellStyle name="常规 6 2 7" xfId="750"/>
+    <cellStyle name="常规 6 3" xfId="1454"/>
+    <cellStyle name="常规 6 3 2" xfId="645"/>
+    <cellStyle name="常规 6 3 2 2" xfId="1455"/>
+    <cellStyle name="常规 6 3 2 3" xfId="1456"/>
+    <cellStyle name="常规 6 3 2 4" xfId="1457"/>
+    <cellStyle name="常规 6 3 2 5" xfId="1458"/>
+    <cellStyle name="常规 6 3 3" xfId="647"/>
+    <cellStyle name="常规 6 3 4" xfId="1459"/>
+    <cellStyle name="常规 6 3 5" xfId="1460"/>
+    <cellStyle name="常规 6 3 6" xfId="763"/>
+    <cellStyle name="常规 6 4" xfId="1359"/>
+    <cellStyle name="常规 6 4 2" xfId="1362"/>
+    <cellStyle name="常规 6 4 3" xfId="1364"/>
+    <cellStyle name="常规 6 4 4" xfId="1366"/>
+    <cellStyle name="常规 6 4 5" xfId="1368"/>
+    <cellStyle name="常规 6 5" xfId="39"/>
+    <cellStyle name="常规 6 6" xfId="1370"/>
+    <cellStyle name="常规 6 7" xfId="1373"/>
+    <cellStyle name="常规 6 8" xfId="1376"/>
+    <cellStyle name="常规 60" xfId="1643"/>
+    <cellStyle name="常规 60 2" xfId="1652"/>
+    <cellStyle name="常规 61" xfId="1644"/>
+    <cellStyle name="常规 61 2" xfId="1653"/>
+    <cellStyle name="常规 7" xfId="1461"/>
+    <cellStyle name="常规 8" xfId="1462"/>
+    <cellStyle name="常规 8 2" xfId="1463"/>
+    <cellStyle name="常规 9" xfId="6"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -5368,23 +5364,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -5420,23 +5399,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -5612,7 +5574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
@@ -5628,7 +5590,7 @@
     <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" style="149" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="148" customWidth="1"/>
     <col min="10" max="11" width="20.6640625" style="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
@@ -5652,23 +5614,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="166" t="s">
+      <c r="B1" s="165" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="167"/>
-      <c r="L1" s="167"/>
-      <c r="M1" s="167"/>
-      <c r="N1" s="167"/>
-      <c r="O1" s="168"/>
-      <c r="AD1" s="172"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="167"/>
+      <c r="AD1" s="171"/>
       <c r="AU1"/>
       <c r="AV1"/>
       <c r="AW1"/>
@@ -5685,14 +5647,14 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="142"/>
+      <c r="I2" s="141"/>
       <c r="J2" s="6"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="135"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="135"/>
-      <c r="Z2" s="135"/>
-      <c r="AD2" s="172"/>
+      <c r="V2" s="134"/>
+      <c r="W2" s="134"/>
+      <c r="X2" s="134"/>
+      <c r="Y2" s="134"/>
+      <c r="Z2" s="134"/>
+      <c r="AD2" s="171"/>
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
@@ -5711,7 +5673,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="142"/>
+      <c r="I3" s="141"/>
       <c r="J3" s="5"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5720,12 +5682,12 @@
       <c r="O3" s="5"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
-      <c r="V3" s="135"/>
-      <c r="W3" s="135"/>
-      <c r="X3" s="135"/>
-      <c r="Y3" s="135"/>
-      <c r="Z3" s="135"/>
-      <c r="AD3" s="172"/>
+      <c r="V3" s="134"/>
+      <c r="W3" s="134"/>
+      <c r="X3" s="134"/>
+      <c r="Y3" s="134"/>
+      <c r="Z3" s="134"/>
+      <c r="AD3" s="171"/>
       <c r="AU3"/>
       <c r="AV3"/>
       <c r="AW3"/>
@@ -5744,25 +5706,25 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="142"/>
+      <c r="I4" s="141"/>
       <c r="J4" s="5"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="170"/>
-      <c r="R4" s="170"/>
-      <c r="S4" s="170"/>
-      <c r="T4" s="170"/>
-      <c r="U4" s="171"/>
-      <c r="V4" s="135"/>
-      <c r="W4" s="135"/>
-      <c r="X4" s="135"/>
-      <c r="Y4" s="135"/>
-      <c r="Z4" s="135"/>
-      <c r="AD4" s="172"/>
+      <c r="P4" s="168"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="169"/>
+      <c r="S4" s="169"/>
+      <c r="T4" s="169"/>
+      <c r="U4" s="170"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="134"/>
+      <c r="X4" s="134"/>
+      <c r="Y4" s="134"/>
+      <c r="Z4" s="134"/>
+      <c r="AD4" s="171"/>
       <c r="AU4"/>
       <c r="AV4"/>
       <c r="AW4"/>
@@ -5782,7 +5744,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="143"/>
+      <c r="I5" s="142"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -5795,12 +5757,12 @@
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="135"/>
-      <c r="Z5" s="135"/>
-      <c r="AD5" s="172"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="134"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="134"/>
+      <c r="Z5" s="134"/>
+      <c r="AD5" s="171"/>
       <c r="AU5"/>
       <c r="AV5"/>
       <c r="AW5"/>
@@ -5810,28 +5772,28 @@
     </row>
     <row r="6" spans="1:52" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="138"/>
+      <c r="C6" s="137"/>
       <c r="D6" s="18"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
-      <c r="I6" s="144"/>
+      <c r="I6" s="143"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
-      <c r="V6" s="136"/>
-      <c r="W6" s="136"/>
-      <c r="X6" s="136"/>
-      <c r="Y6" s="136"/>
-      <c r="Z6" s="136"/>
-      <c r="AD6" s="172"/>
+      <c r="V6" s="135"/>
+      <c r="W6" s="135"/>
+      <c r="X6" s="135"/>
+      <c r="Y6" s="135"/>
+      <c r="Z6" s="135"/>
+      <c r="AD6" s="171"/>
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6"/>
@@ -5841,36 +5803,36 @@
     </row>
     <row r="7" spans="1:52" ht="15" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="141" t="s">
+      <c r="B7" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="145"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="133" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="133"/>
-      <c r="Q7" s="133"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="133"/>
-      <c r="T7" s="133"/>
-      <c r="U7" s="133"/>
-      <c r="V7" s="133"/>
-      <c r="W7" s="133"/>
-      <c r="X7" s="133"/>
-      <c r="Y7" s="133"/>
-      <c r="Z7" s="134"/>
-      <c r="AD7" s="172"/>
+      <c r="L7" s="132"/>
+      <c r="M7" s="132"/>
+      <c r="N7" s="132"/>
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="132"/>
+      <c r="R7" s="132"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="132"/>
+      <c r="U7" s="132"/>
+      <c r="V7" s="132"/>
+      <c r="W7" s="132"/>
+      <c r="X7" s="132"/>
+      <c r="Y7" s="132"/>
+      <c r="Z7" s="133"/>
+      <c r="AD7" s="171"/>
       <c r="AU7"/>
       <c r="AV7"/>
       <c r="AW7"/>
@@ -5901,7 +5863,7 @@
       <c r="H8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="146" t="s">
+      <c r="I8" s="145" t="s">
         <v>26</v>
       </c>
       <c r="J8" s="26" t="s">
@@ -5946,17 +5908,17 @@
       <c r="W8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="X8" s="139" t="s">
+      <c r="X8" s="138" t="s">
         <v>23</v>
       </c>
-      <c r="Y8" s="140"/>
+      <c r="Y8" s="139"/>
       <c r="Z8" s="25" t="s">
         <v>22</v>
       </c>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
       <c r="AC8" s="30"/>
-      <c r="AD8" s="172"/>
+      <c r="AD8" s="171"/>
       <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8"/>
@@ -5966,22 +5928,22 @@
     </row>
     <row r="9" spans="1:52" s="40" customFormat="1" ht="19.5" customHeight="1">
       <c r="A9" s="31"/>
-      <c r="B9" s="137">
+      <c r="B9" s="136">
         <v>1</v>
       </c>
-      <c r="C9" s="137"/>
+      <c r="C9" s="136"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126">
+      <c r="E9" s="125"/>
+      <c r="F9" s="125">
         <v>2</v>
       </c>
-      <c r="G9" s="126">
+      <c r="G9" s="125">
         <v>3</v>
       </c>
       <c r="H9" s="33">
         <v>4</v>
       </c>
-      <c r="I9" s="147">
+      <c r="I9" s="146">
         <v>5</v>
       </c>
       <c r="J9" s="34"/>
@@ -6030,7 +5992,7 @@
       <c r="AA9" s="38"/>
       <c r="AB9" s="38"/>
       <c r="AC9" s="39"/>
-      <c r="AD9" s="172"/>
+      <c r="AD9" s="171"/>
       <c r="AU9"/>
       <c r="AV9"/>
       <c r="AW9"/>
@@ -6051,11 +6013,11 @@
       <c r="F10" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="162" t="s">
+      <c r="G10" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="47"/>
-      <c r="I10" s="148" t="e">
+      <c r="H10" s="147"/>
+      <c r="I10" s="147" t="e">
         <f>G10*H10</f>
         <v>#VALUE!</v>
       </c>
@@ -6081,14 +6043,14 @@
         <f>M10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P10" s="163" t="s">
+      <c r="P10" s="162" t="s">
         <v>81</v>
       </c>
       <c r="Q10" s="54" t="e">
         <f>P10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R10" s="104" t="e">
+      <c r="R10" s="55" t="e">
         <f>$U$14/$Q$11*P10/12*0.3</f>
         <v>#VALUE!</v>
       </c>
@@ -6126,7 +6088,7 @@
       <c r="AA10" s="60"/>
       <c r="AB10" s="60"/>
       <c r="AC10" s="60"/>
-      <c r="AD10" s="172"/>
+      <c r="AD10" s="171"/>
       <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
@@ -6140,9 +6102,9 @@
       <c r="C11" s="63"/>
       <c r="D11" s="63"/>
       <c r="F11" s="64"/>
-      <c r="G11" s="132"/>
+      <c r="G11" s="131"/>
       <c r="H11" s="65"/>
-      <c r="I11" s="148" t="e">
+      <c r="I11" s="147" t="e">
         <f>SUM(I10:I10)</f>
         <v>#VALUE!</v>
       </c>
@@ -6187,7 +6149,7 @@
       <c r="AA11" s="60"/>
       <c r="AB11" s="60"/>
       <c r="AC11" s="60"/>
-      <c r="AD11" s="172"/>
+      <c r="AD11" s="171"/>
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
@@ -6202,11 +6164,11 @@
       <c r="D12" s="80"/>
       <c r="E12" s="79"/>
       <c r="F12" s="81"/>
-      <c r="G12" s="131"/>
+      <c r="G12" s="130"/>
       <c r="H12" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="148" t="e">
+      <c r="I12" s="147" t="e">
         <f>I11*1.2</f>
         <v>#VALUE!</v>
       </c>
@@ -6228,7 +6190,7 @@
       <c r="Y12" s="93"/>
       <c r="Z12" s="94"/>
       <c r="AC12" s="95"/>
-      <c r="AD12" s="172"/>
+      <c r="AD12" s="171"/>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
@@ -6237,19 +6199,19 @@
       <c r="AZ12"/>
     </row>
     <row r="13" spans="1:52" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A13" s="129" t="s">
+      <c r="A13" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="128"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="149"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="148"/>
       <c r="K13" s="97"/>
       <c r="L13" s="97"/>
       <c r="P13"/>
@@ -6264,7 +6226,7 @@
       <c r="Y13"/>
       <c r="Z13"/>
       <c r="AA13"/>
-      <c r="AD13" s="172"/>
+      <c r="AD13" s="171"/>
       <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13"/>
@@ -6273,33 +6235,33 @@
       <c r="AZ13"/>
     </row>
     <row r="14" spans="1:52" ht="14.1" customHeight="1">
-      <c r="A14" s="129" t="s">
+      <c r="A14" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="105" t="s">
+      <c r="B14" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="150"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="149"/>
       <c r="J14" s="6"/>
       <c r="K14" s="97"/>
       <c r="L14" s="97"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-      <c r="O14" s="109"/>
+      <c r="O14" s="108"/>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14"/>
-      <c r="T14" s="165" t="s">
+      <c r="T14" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="U14" s="164" t="s">
+      <c r="U14" s="163" t="s">
         <v>82</v>
       </c>
       <c r="V14"/>
@@ -6308,7 +6270,7 @@
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
-      <c r="AD14" s="172"/>
+      <c r="AD14" s="171"/>
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
@@ -6320,16 +6282,16 @@
       <c r="A15" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="106"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="151">
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="150">
         <v>150</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -6352,7 +6314,7 @@
       <c r="Y15"/>
       <c r="Z15"/>
       <c r="AA15"/>
-      <c r="AD15" s="172"/>
+      <c r="AD15" s="171"/>
       <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
@@ -6364,25 +6326,25 @@
       <c r="A16" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="152">
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="151">
         <v>30</v>
       </c>
-      <c r="J16" s="110"/>
+      <c r="J16" s="109"/>
       <c r="K16" s="97"/>
       <c r="L16" s="97"/>
       <c r="N16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O16" s="111" t="e">
+      <c r="O16" s="110" t="e">
         <f>I11*14</f>
         <v>#VALUE!</v>
       </c>
@@ -6398,7 +6360,7 @@
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
-      <c r="AD16" s="172"/>
+      <c r="AD16" s="171"/>
       <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
@@ -6410,23 +6372,23 @@
       <c r="A17" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="116"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="153"/>
-      <c r="J17" s="112"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="152"/>
+      <c r="J17" s="111"/>
       <c r="K17" s="97"/>
       <c r="L17" s="97"/>
       <c r="N17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O17" s="111" t="e">
+      <c r="O17" s="110" t="e">
         <f>I12*14</f>
         <v>#VALUE!</v>
       </c>
@@ -6442,7 +6404,7 @@
       <c r="Y17"/>
       <c r="Z17"/>
       <c r="AA17"/>
-      <c r="AD17" s="172"/>
+      <c r="AD17" s="171"/>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
@@ -6454,17 +6416,17 @@
       <c r="A18" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="115" t="s">
+      <c r="B18" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="154"/>
-      <c r="J18" s="113"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="112"/>
       <c r="K18" s="97"/>
       <c r="L18" s="97"/>
       <c r="P18"/>
@@ -6479,7 +6441,7 @@
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
-      <c r="AD18" s="172"/>
+      <c r="AD18" s="171"/>
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18"/>
@@ -6491,20 +6453,20 @@
       <c r="A19" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="115" t="s">
+      <c r="B19" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="155" t="e">
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="154" t="e">
         <f>I11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="114"/>
+      <c r="J19" s="113"/>
       <c r="K19" s="97"/>
       <c r="L19" s="97"/>
       <c r="M19" s="8"/>
@@ -6520,7 +6482,7 @@
       <c r="Y19"/>
       <c r="Z19"/>
       <c r="AA19"/>
-      <c r="AD19" s="172"/>
+      <c r="AD19" s="171"/>
       <c r="AU19"/>
       <c r="AV19"/>
       <c r="AW19"/>
@@ -6532,14 +6494,14 @@
       <c r="A20" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="115"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="155"/>
+      <c r="B20" s="114"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="154"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
@@ -6558,7 +6520,7 @@
       <c r="Y20"/>
       <c r="Z20"/>
       <c r="AA20"/>
-      <c r="AD20" s="172"/>
+      <c r="AD20" s="171"/>
       <c r="AU20"/>
       <c r="AV20"/>
       <c r="AW20"/>
@@ -6570,14 +6532,14 @@
       <c r="A21" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="115"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="155"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="154"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
@@ -6596,7 +6558,7 @@
       <c r="Y21"/>
       <c r="Z21"/>
       <c r="AA21"/>
-      <c r="AD21" s="172"/>
+      <c r="AD21" s="171"/>
       <c r="AU21"/>
       <c r="AV21"/>
       <c r="AW21"/>
@@ -6608,14 +6570,14 @@
       <c r="A22" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="115"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="155"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="154"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
@@ -6634,7 +6596,7 @@
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
-      <c r="AD22" s="172"/>
+      <c r="AD22" s="171"/>
       <c r="AU22"/>
       <c r="AV22"/>
       <c r="AW22"/>
@@ -6646,16 +6608,16 @@
       <c r="A23" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="119" t="s">
+      <c r="B23" s="118" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="116"/>
-      <c r="F23" s="116"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="156"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="155"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
@@ -6674,7 +6636,7 @@
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23"/>
-      <c r="AD23" s="172"/>
+      <c r="AD23" s="171"/>
       <c r="AU23"/>
       <c r="AV23"/>
       <c r="AW23"/>
@@ -6684,16 +6646,16 @@
     </row>
     <row r="24" spans="1:52" s="99" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="102"/>
-      <c r="B24" s="115" t="s">
+      <c r="B24" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="116"/>
-      <c r="D24" s="116"/>
-      <c r="E24" s="116"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="157" t="e">
+      <c r="C24" s="115"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="156" t="e">
         <f>I12</f>
         <v>#VALUE!</v>
       </c>
@@ -6715,7 +6677,7 @@
       <c r="Y24"/>
       <c r="Z24"/>
       <c r="AA24"/>
-      <c r="AD24" s="172"/>
+      <c r="AD24" s="171"/>
       <c r="AU24"/>
       <c r="AV24"/>
       <c r="AW24"/>
@@ -6725,16 +6687,16 @@
     </row>
     <row r="25" spans="1:52" s="61" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="41"/>
-      <c r="B25" s="115" t="s">
+      <c r="B25" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="158" t="e">
+      <c r="C25" s="115"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="157" t="e">
         <f>I24/120*20</f>
         <v>#VALUE!</v>
       </c>
@@ -6756,7 +6718,7 @@
       <c r="Y25"/>
       <c r="Z25"/>
       <c r="AA25"/>
-      <c r="AD25" s="172"/>
+      <c r="AD25" s="171"/>
       <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
@@ -6766,16 +6728,16 @@
     </row>
     <row r="26" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="103"/>
-      <c r="B26" s="115" t="s">
+      <c r="B26" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="116"/>
-      <c r="D26" s="116"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="158" t="e">
+      <c r="C26" s="115"/>
+      <c r="D26" s="115"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="157" t="e">
         <f>I24-I25</f>
         <v>#VALUE!</v>
       </c>
@@ -6797,7 +6759,7 @@
       <c r="Y26"/>
       <c r="Z26"/>
       <c r="AA26"/>
-      <c r="AD26" s="172"/>
+      <c r="AD26" s="171"/>
       <c r="AU26"/>
       <c r="AV26"/>
       <c r="AW26"/>
@@ -6807,16 +6769,16 @@
     </row>
     <row r="27" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="103"/>
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="114" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="158" t="e">
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="157" t="e">
         <f>SUM(I28:I37)</f>
         <v>#VALUE!</v>
       </c>
@@ -6838,7 +6800,7 @@
       <c r="Y27"/>
       <c r="Z27"/>
       <c r="AA27"/>
-      <c r="AD27" s="172"/>
+      <c r="AD27" s="171"/>
       <c r="AU27"/>
       <c r="AV27"/>
       <c r="AW27"/>
@@ -6848,16 +6810,16 @@
     </row>
     <row r="28" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="103"/>
-      <c r="B28" s="115" t="s">
+      <c r="B28" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="116"/>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="117"/>
-      <c r="I28" s="158" t="e">
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="116"/>
+      <c r="I28" s="157" t="e">
         <f>O11</f>
         <v>#VALUE!</v>
       </c>
@@ -6879,7 +6841,7 @@
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28"/>
-      <c r="AD28" s="172"/>
+      <c r="AD28" s="171"/>
       <c r="AU28"/>
       <c r="AV28"/>
       <c r="AW28"/>
@@ -6889,18 +6851,18 @@
     </row>
     <row r="29" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="103"/>
-      <c r="B29" s="123" t="s">
+      <c r="B29" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="124"/>
-      <c r="D29" s="124"/>
-      <c r="E29" s="124"/>
-      <c r="F29" s="124"/>
-      <c r="G29" s="121"/>
-      <c r="H29" s="120" t="s">
+      <c r="C29" s="123"/>
+      <c r="D29" s="123"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="123"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="159" t="e">
+      <c r="I29" s="158" t="e">
         <f>IF(H29=D43,I28*3.2%,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -6922,7 +6884,7 @@
       <c r="Y29"/>
       <c r="Z29"/>
       <c r="AA29"/>
-      <c r="AD29" s="172"/>
+      <c r="AD29" s="171"/>
       <c r="AU29"/>
       <c r="AV29"/>
       <c r="AW29"/>
@@ -6932,16 +6894,16 @@
     </row>
     <row r="30" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="103"/>
-      <c r="B30" s="115" t="s">
+      <c r="B30" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="116"/>
-      <c r="D30" s="116"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="116"/>
-      <c r="H30" s="117"/>
-      <c r="I30" s="158">
+      <c r="C30" s="115"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="115"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="116"/>
+      <c r="I30" s="157">
         <f>AA11</f>
         <v>0</v>
       </c>
@@ -6963,7 +6925,7 @@
       <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
-      <c r="AD30" s="172"/>
+      <c r="AD30" s="171"/>
       <c r="AU30"/>
       <c r="AV30"/>
       <c r="AW30"/>
@@ -6973,16 +6935,16 @@
     </row>
     <row r="31" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="103"/>
-      <c r="B31" s="122" t="s">
+      <c r="B31" s="121" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="158">
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="157">
         <f>AB11</f>
         <v>0</v>
       </c>
@@ -7006,7 +6968,7 @@
       <c r="AA31"/>
       <c r="AB31" s="100"/>
       <c r="AC31" s="100"/>
-      <c r="AD31" s="172"/>
+      <c r="AD31" s="171"/>
       <c r="AE31" s="100"/>
       <c r="AF31" s="100"/>
       <c r="AU31"/>
@@ -7018,16 +6980,16 @@
     </row>
     <row r="32" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="103"/>
-      <c r="B32" s="122" t="s">
+      <c r="B32" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="116"/>
-      <c r="D32" s="116"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="116"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="158">
+      <c r="C32" s="115"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="115"/>
+      <c r="G32" s="115"/>
+      <c r="H32" s="116"/>
+      <c r="I32" s="157">
         <f>AC11</f>
         <v>0</v>
       </c>
@@ -7051,7 +7013,7 @@
       <c r="AA32"/>
       <c r="AB32" s="100"/>
       <c r="AC32" s="100"/>
-      <c r="AD32" s="172"/>
+      <c r="AD32" s="171"/>
       <c r="AE32" s="100"/>
       <c r="AF32" s="100"/>
       <c r="AU32"/>
@@ -7063,18 +7025,18 @@
     </row>
     <row r="33" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="103"/>
-      <c r="B33" s="123" t="s">
+      <c r="B33" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="124"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="124"/>
-      <c r="G33" s="121"/>
-      <c r="H33" s="120" t="s">
+      <c r="C33" s="123"/>
+      <c r="D33" s="123"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="120"/>
+      <c r="H33" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="I33" s="159" t="e">
+      <c r="I33" s="158" t="e">
         <f>IF(H33="ДА",I28*16%/365*Длина_сделки,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -7098,7 +7060,7 @@
       <c r="AA33"/>
       <c r="AB33" s="100"/>
       <c r="AC33" s="100"/>
-      <c r="AD33" s="172"/>
+      <c r="AD33" s="171"/>
       <c r="AE33" s="100"/>
       <c r="AF33" s="100"/>
       <c r="AU33"/>
@@ -7110,16 +7072,16 @@
     </row>
     <row r="34" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="103"/>
-      <c r="B34" s="122" t="s">
+      <c r="B34" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="116"/>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="158">
+      <c r="C34" s="115"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="115"/>
+      <c r="H34" s="116"/>
+      <c r="I34" s="157">
         <f>AA11</f>
         <v>0</v>
       </c>
@@ -7143,7 +7105,7 @@
       <c r="AA34"/>
       <c r="AB34" s="100"/>
       <c r="AC34" s="100"/>
-      <c r="AD34" s="172"/>
+      <c r="AD34" s="171"/>
       <c r="AE34" s="100"/>
       <c r="AF34" s="100"/>
       <c r="AG34" s="100"/>
@@ -7156,16 +7118,16 @@
     </row>
     <row r="35" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="103"/>
-      <c r="B35" s="122" t="s">
+      <c r="B35" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="116"/>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="117"/>
-      <c r="I35" s="158">
+      <c r="C35" s="115"/>
+      <c r="D35" s="115"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="115"/>
+      <c r="G35" s="115"/>
+      <c r="H35" s="116"/>
+      <c r="I35" s="157">
         <f>AB11</f>
         <v>0</v>
       </c>
@@ -7189,7 +7151,7 @@
       <c r="AA35"/>
       <c r="AB35" s="100"/>
       <c r="AC35" s="100"/>
-      <c r="AD35" s="172"/>
+      <c r="AD35" s="171"/>
       <c r="AE35" s="100"/>
       <c r="AF35" s="100"/>
       <c r="AG35" s="100"/>
@@ -7202,16 +7164,16 @@
     </row>
     <row r="36" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="103"/>
-      <c r="B36" s="122" t="s">
+      <c r="B36" s="121" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="116"/>
-      <c r="D36" s="116"/>
-      <c r="E36" s="116"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="116"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="158">
+      <c r="C36" s="115"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="115"/>
+      <c r="G36" s="115"/>
+      <c r="H36" s="116"/>
+      <c r="I36" s="157">
         <f>AC11</f>
         <v>0</v>
       </c>
@@ -7235,7 +7197,7 @@
       <c r="AA36"/>
       <c r="AB36" s="100"/>
       <c r="AC36" s="100"/>
-      <c r="AD36" s="172"/>
+      <c r="AD36" s="171"/>
       <c r="AE36" s="100"/>
       <c r="AF36" s="100"/>
       <c r="AG36" s="100"/>
@@ -7248,18 +7210,18 @@
     </row>
     <row r="37" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="103"/>
-      <c r="B37" s="123" t="s">
+      <c r="B37" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="124"/>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="121"/>
-      <c r="H37" s="120" t="s">
+      <c r="C37" s="123"/>
+      <c r="D37" s="123"/>
+      <c r="E37" s="123"/>
+      <c r="F37" s="123"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="I37" s="159">
+      <c r="I37" s="158">
         <f>IF(H37="ДА",I24*3%/365*(I15+I16),0)</f>
         <v>0</v>
       </c>
@@ -7283,7 +7245,7 @@
       <c r="AA37"/>
       <c r="AB37" s="100"/>
       <c r="AC37" s="100"/>
-      <c r="AD37" s="172"/>
+      <c r="AD37" s="171"/>
       <c r="AE37" s="100"/>
       <c r="AF37" s="100"/>
       <c r="AG37" s="100"/>
@@ -7296,16 +7258,16 @@
     </row>
     <row r="38" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="103"/>
-      <c r="B38" s="122" t="s">
+      <c r="B38" s="121" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="116"/>
-      <c r="D38" s="116"/>
-      <c r="E38" s="116"/>
-      <c r="F38" s="116"/>
-      <c r="G38" s="116"/>
-      <c r="H38" s="117"/>
-      <c r="I38" s="158" t="e">
+      <c r="C38" s="115"/>
+      <c r="D38" s="115"/>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="115"/>
+      <c r="H38" s="116"/>
+      <c r="I38" s="157" t="e">
         <f>I26-I27</f>
         <v>#VALUE!</v>
       </c>
@@ -7329,7 +7291,7 @@
       <c r="AA38"/>
       <c r="AB38" s="100"/>
       <c r="AC38" s="100"/>
-      <c r="AD38" s="172"/>
+      <c r="AD38" s="171"/>
       <c r="AE38" s="100"/>
       <c r="AF38" s="100"/>
       <c r="AG38" s="100"/>
@@ -7342,16 +7304,16 @@
     </row>
     <row r="39" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="103"/>
-      <c r="B39" s="122" t="s">
+      <c r="B39" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="116"/>
-      <c r="D39" s="116"/>
-      <c r="E39" s="116"/>
-      <c r="F39" s="116"/>
-      <c r="G39" s="116"/>
-      <c r="H39" s="117"/>
-      <c r="I39" s="158"/>
+      <c r="C39" s="115"/>
+      <c r="D39" s="115"/>
+      <c r="E39" s="115"/>
+      <c r="F39" s="115"/>
+      <c r="G39" s="115"/>
+      <c r="H39" s="116"/>
+      <c r="I39" s="157"/>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39"/>
@@ -7372,7 +7334,7 @@
       <c r="AA39"/>
       <c r="AB39" s="100"/>
       <c r="AC39" s="100"/>
-      <c r="AD39" s="172"/>
+      <c r="AD39" s="171"/>
       <c r="AE39" s="100"/>
       <c r="AF39" s="100"/>
       <c r="AG39" s="100"/>
@@ -7385,16 +7347,16 @@
     </row>
     <row r="40" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="103"/>
-      <c r="B40" s="122" t="s">
+      <c r="B40" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="117"/>
-      <c r="I40" s="160" t="e">
+      <c r="C40" s="115"/>
+      <c r="D40" s="115"/>
+      <c r="E40" s="115"/>
+      <c r="F40" s="115"/>
+      <c r="G40" s="115"/>
+      <c r="H40" s="116"/>
+      <c r="I40" s="159" t="e">
         <f>I38/I26</f>
         <v>#VALUE!</v>
       </c>
@@ -7418,7 +7380,7 @@
       <c r="AA40"/>
       <c r="AB40" s="100"/>
       <c r="AC40" s="100"/>
-      <c r="AD40" s="172"/>
+      <c r="AD40" s="171"/>
       <c r="AE40" s="100"/>
       <c r="AF40" s="100"/>
       <c r="AG40" s="100"/>
@@ -7438,7 +7400,7 @@
       <c r="F41"/>
       <c r="G41"/>
       <c r="H41"/>
-      <c r="I41" s="161"/>
+      <c r="I41" s="160"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
@@ -7459,7 +7421,7 @@
       <c r="AA41"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-      <c r="AD41" s="172"/>
+      <c r="AD41" s="171"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
@@ -7478,7 +7440,7 @@
       <c r="F42"/>
       <c r="G42"/>
       <c r="H42"/>
-      <c r="I42" s="161"/>
+      <c r="I42" s="160"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42"/>
@@ -7499,7 +7461,7 @@
       <c r="AA42"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="172"/>
+      <c r="AD42" s="171"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
@@ -7521,7 +7483,7 @@
       <c r="F43"/>
       <c r="G43"/>
       <c r="H43"/>
-      <c r="I43" s="161"/>
+      <c r="I43" s="160"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
@@ -7542,7 +7504,7 @@
       <c r="AA43"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="172"/>
+      <c r="AD43" s="171"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
@@ -7564,7 +7526,7 @@
       <c r="F44"/>
       <c r="G44"/>
       <c r="H44"/>
-      <c r="I44" s="161"/>
+      <c r="I44" s="160"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
@@ -7583,7 +7545,7 @@
       <c r="Y44"/>
       <c r="Z44"/>
       <c r="AA44"/>
-      <c r="AD44" s="172"/>
+      <c r="AD44" s="171"/>
       <c r="AU44"/>
       <c r="AV44"/>
       <c r="AW44"/>
@@ -7599,7 +7561,7 @@
       <c r="F45"/>
       <c r="G45"/>
       <c r="H45"/>
-      <c r="I45" s="161"/>
+      <c r="I45" s="160"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45"/>
@@ -7618,7 +7580,7 @@
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AD45" s="172"/>
+      <c r="AD45" s="171"/>
       <c r="AU45"/>
       <c r="AV45"/>
       <c r="AW45"/>
@@ -7634,7 +7596,7 @@
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46"/>
-      <c r="I46" s="161"/>
+      <c r="I46" s="160"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46"/>
@@ -7653,7 +7615,7 @@
       <c r="Y46"/>
       <c r="Z46"/>
       <c r="AA46"/>
-      <c r="AD46" s="172"/>
+      <c r="AD46" s="171"/>
       <c r="AU46"/>
       <c r="AV46"/>
       <c r="AW46"/>
@@ -7669,7 +7631,7 @@
       <c r="F47"/>
       <c r="G47"/>
       <c r="H47"/>
-      <c r="I47" s="161"/>
+      <c r="I47" s="160"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47"/>
@@ -7688,7 +7650,7 @@
       <c r="Y47"/>
       <c r="Z47"/>
       <c r="AA47"/>
-      <c r="AD47" s="172"/>
+      <c r="AD47" s="171"/>
       <c r="AU47"/>
       <c r="AV47"/>
       <c r="AW47"/>
@@ -7697,7 +7659,7 @@
       <c r="AZ47"/>
     </row>
     <row r="48" spans="1:52" ht="11.45" customHeight="1">
-      <c r="AD48" s="172"/>
+      <c r="AD48" s="171"/>
       <c r="AU48"/>
       <c r="AV48"/>
       <c r="AW48"/>
@@ -7706,7 +7668,7 @@
       <c r="AZ48"/>
     </row>
     <row r="49" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD49" s="172"/>
+      <c r="AD49" s="171"/>
       <c r="AU49"/>
       <c r="AV49"/>
       <c r="AW49"/>
@@ -7715,7 +7677,7 @@
       <c r="AZ49"/>
     </row>
     <row r="50" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD50" s="172"/>
+      <c r="AD50" s="171"/>
       <c r="AU50"/>
       <c r="AV50"/>
       <c r="AW50"/>
@@ -7724,7 +7686,7 @@
       <c r="AZ50"/>
     </row>
     <row r="51" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD51" s="172"/>
+      <c r="AD51" s="171"/>
       <c r="AU51"/>
       <c r="AV51"/>
       <c r="AW51"/>
@@ -7733,7 +7695,7 @@
       <c r="AZ51"/>
     </row>
     <row r="52" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD52" s="172"/>
+      <c r="AD52" s="171"/>
       <c r="AU52"/>
       <c r="AV52"/>
       <c r="AW52"/>
@@ -7742,7 +7704,7 @@
       <c r="AZ52"/>
     </row>
     <row r="53" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD53" s="172"/>
+      <c r="AD53" s="171"/>
       <c r="AU53"/>
       <c r="AV53"/>
       <c r="AW53"/>
@@ -7751,7 +7713,7 @@
       <c r="AZ53"/>
     </row>
     <row r="54" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD54" s="172"/>
+      <c r="AD54" s="171"/>
       <c r="AU54"/>
       <c r="AV54"/>
       <c r="AW54"/>
@@ -7760,7 +7722,7 @@
       <c r="AZ54"/>
     </row>
     <row r="55" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD55" s="172"/>
+      <c r="AD55" s="171"/>
       <c r="AU55"/>
       <c r="AV55"/>
       <c r="AW55"/>
@@ -7769,7 +7731,7 @@
       <c r="AZ55"/>
     </row>
     <row r="56" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD56" s="172"/>
+      <c r="AD56" s="171"/>
       <c r="AU56"/>
       <c r="AV56"/>
       <c r="AW56"/>
@@ -7778,7 +7740,7 @@
       <c r="AZ56"/>
     </row>
     <row r="57" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD57" s="172"/>
+      <c r="AD57" s="171"/>
       <c r="AU57"/>
       <c r="AV57"/>
       <c r="AW57"/>
@@ -7787,7 +7749,7 @@
       <c r="AZ57"/>
     </row>
     <row r="58" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD58" s="172"/>
+      <c r="AD58" s="171"/>
       <c r="AU58"/>
       <c r="AV58"/>
       <c r="AW58"/>
@@ -7796,7 +7758,7 @@
       <c r="AZ58"/>
     </row>
     <row r="59" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD59" s="172"/>
+      <c r="AD59" s="171"/>
       <c r="AU59"/>
       <c r="AV59"/>
       <c r="AW59"/>
@@ -7805,7 +7767,7 @@
       <c r="AZ59"/>
     </row>
     <row r="60" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD60" s="172"/>
+      <c r="AD60" s="171"/>
       <c r="AU60"/>
       <c r="AV60"/>
       <c r="AW60"/>
@@ -7814,7 +7776,7 @@
       <c r="AZ60"/>
     </row>
     <row r="61" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD61" s="172"/>
+      <c r="AD61" s="171"/>
       <c r="AU61"/>
       <c r="AV61"/>
       <c r="AW61"/>
@@ -7823,7 +7785,7 @@
       <c r="AZ61"/>
     </row>
     <row r="62" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD62" s="172"/>
+      <c r="AD62" s="171"/>
       <c r="AU62"/>
       <c r="AV62"/>
       <c r="AW62"/>
@@ -7832,7 +7794,7 @@
       <c r="AZ62"/>
     </row>
     <row r="63" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD63" s="172"/>
+      <c r="AD63" s="171"/>
       <c r="AU63"/>
       <c r="AV63"/>
       <c r="AW63"/>
@@ -7841,7 +7803,7 @@
       <c r="AZ63"/>
     </row>
     <row r="64" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD64" s="172"/>
+      <c r="AD64" s="171"/>
       <c r="AU64"/>
       <c r="AV64"/>
       <c r="AW64"/>
@@ -7850,7 +7812,7 @@
       <c r="AZ64"/>
     </row>
     <row r="65" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD65" s="172"/>
+      <c r="AD65" s="171"/>
       <c r="AU65"/>
       <c r="AV65"/>
       <c r="AW65"/>
@@ -7859,7 +7821,7 @@
       <c r="AZ65"/>
     </row>
     <row r="66" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD66" s="172"/>
+      <c r="AD66" s="171"/>
       <c r="AU66"/>
       <c r="AV66"/>
       <c r="AW66"/>
@@ -7868,7 +7830,7 @@
       <c r="AZ66"/>
     </row>
     <row r="67" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD67" s="172"/>
+      <c r="AD67" s="171"/>
       <c r="AU67"/>
       <c r="AV67"/>
       <c r="AW67"/>
@@ -7877,7 +7839,7 @@
       <c r="AZ67"/>
     </row>
     <row r="68" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD68" s="172"/>
+      <c r="AD68" s="171"/>
       <c r="AU68"/>
       <c r="AV68"/>
       <c r="AW68"/>
@@ -7886,7 +7848,7 @@
       <c r="AZ68"/>
     </row>
     <row r="69" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD69" s="172"/>
+      <c r="AD69" s="171"/>
       <c r="AU69"/>
       <c r="AV69"/>
       <c r="AW69"/>
@@ -7895,7 +7857,7 @@
       <c r="AZ69"/>
     </row>
     <row r="70" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD70" s="172"/>
+      <c r="AD70" s="171"/>
       <c r="AU70"/>
       <c r="AV70"/>
       <c r="AW70"/>
@@ -7904,7 +7866,7 @@
       <c r="AZ70"/>
     </row>
     <row r="71" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD71" s="172"/>
+      <c r="AD71" s="171"/>
       <c r="AU71"/>
       <c r="AV71"/>
       <c r="AW71"/>
@@ -7913,7 +7875,7 @@
       <c r="AZ71"/>
     </row>
     <row r="72" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD72" s="172"/>
+      <c r="AD72" s="171"/>
       <c r="AU72"/>
       <c r="AV72"/>
       <c r="AW72"/>
@@ -7922,7 +7884,7 @@
       <c r="AZ72"/>
     </row>
     <row r="73" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD73" s="172"/>
+      <c r="AD73" s="171"/>
       <c r="AU73"/>
       <c r="AV73"/>
       <c r="AW73"/>
@@ -7931,7 +7893,7 @@
       <c r="AZ73"/>
     </row>
     <row r="74" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD74" s="172"/>
+      <c r="AD74" s="171"/>
       <c r="AU74"/>
       <c r="AV74"/>
       <c r="AW74"/>
@@ -7940,7 +7902,7 @@
       <c r="AZ74"/>
     </row>
     <row r="75" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD75" s="172"/>
+      <c r="AD75" s="171"/>
       <c r="AU75"/>
       <c r="AV75"/>
       <c r="AW75"/>
@@ -7949,7 +7911,7 @@
       <c r="AZ75"/>
     </row>
     <row r="76" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD76" s="172"/>
+      <c r="AD76" s="171"/>
       <c r="AU76"/>
       <c r="AV76"/>
       <c r="AW76"/>
@@ -7958,7 +7920,7 @@
       <c r="AZ76"/>
     </row>
     <row r="77" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD77" s="172"/>
+      <c r="AD77" s="171"/>
       <c r="AU77"/>
       <c r="AV77"/>
       <c r="AW77"/>
@@ -7967,7 +7929,7 @@
       <c r="AZ77"/>
     </row>
     <row r="78" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD78" s="172"/>
+      <c r="AD78" s="171"/>
       <c r="AU78"/>
       <c r="AV78"/>
       <c r="AW78"/>
@@ -7976,7 +7938,7 @@
       <c r="AZ78"/>
     </row>
     <row r="79" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD79" s="172"/>
+      <c r="AD79" s="171"/>
       <c r="AU79"/>
       <c r="AV79"/>
       <c r="AW79"/>
@@ -7985,7 +7947,7 @@
       <c r="AZ79"/>
     </row>
     <row r="80" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD80" s="172"/>
+      <c r="AD80" s="171"/>
       <c r="AU80"/>
       <c r="AV80"/>
       <c r="AW80"/>
@@ -7994,7 +7956,7 @@
       <c r="AZ80"/>
     </row>
     <row r="81" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD81" s="172"/>
+      <c r="AD81" s="171"/>
       <c r="AU81"/>
       <c r="AV81"/>
       <c r="AW81"/>
@@ -8003,7 +7965,7 @@
       <c r="AZ81"/>
     </row>
     <row r="82" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD82" s="172"/>
+      <c r="AD82" s="171"/>
       <c r="AU82"/>
       <c r="AV82"/>
       <c r="AW82"/>
@@ -8012,7 +7974,7 @@
       <c r="AZ82"/>
     </row>
     <row r="83" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD83" s="172"/>
+      <c r="AD83" s="171"/>
       <c r="AU83"/>
       <c r="AV83"/>
       <c r="AW83"/>
@@ -8021,7 +7983,7 @@
       <c r="AZ83"/>
     </row>
     <row r="84" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD84" s="172"/>
+      <c r="AD84" s="171"/>
       <c r="AU84"/>
       <c r="AV84"/>
       <c r="AW84"/>
@@ -8030,7 +7992,7 @@
       <c r="AZ84"/>
     </row>
     <row r="85" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD85" s="172"/>
+      <c r="AD85" s="171"/>
       <c r="AU85"/>
       <c r="AV85"/>
       <c r="AW85"/>
@@ -8039,7 +8001,7 @@
       <c r="AZ85"/>
     </row>
     <row r="86" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD86" s="172"/>
+      <c r="AD86" s="171"/>
       <c r="AU86"/>
       <c r="AV86"/>
       <c r="AW86"/>
@@ -8048,7 +8010,7 @@
       <c r="AZ86"/>
     </row>
     <row r="87" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD87" s="172"/>
+      <c r="AD87" s="171"/>
       <c r="AU87"/>
       <c r="AV87"/>
       <c r="AW87"/>
@@ -8057,7 +8019,7 @@
       <c r="AZ87"/>
     </row>
     <row r="88" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD88" s="172"/>
+      <c r="AD88" s="171"/>
       <c r="AU88"/>
       <c r="AV88"/>
       <c r="AW88"/>
@@ -8066,7 +8028,7 @@
       <c r="AZ88"/>
     </row>
     <row r="89" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD89" s="172"/>
+      <c r="AD89" s="171"/>
       <c r="AU89"/>
       <c r="AV89"/>
       <c r="AW89"/>
@@ -8075,7 +8037,7 @@
       <c r="AZ89"/>
     </row>
     <row r="90" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD90" s="172"/>
+      <c r="AD90" s="171"/>
       <c r="AU90"/>
       <c r="AV90"/>
       <c r="AW90"/>
@@ -8084,7 +8046,7 @@
       <c r="AZ90"/>
     </row>
     <row r="91" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD91" s="172"/>
+      <c r="AD91" s="171"/>
       <c r="AU91"/>
       <c r="AV91"/>
       <c r="AW91"/>
@@ -8093,7 +8055,7 @@
       <c r="AZ91"/>
     </row>
     <row r="92" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD92" s="172"/>
+      <c r="AD92" s="171"/>
       <c r="AU92"/>
       <c r="AV92"/>
       <c r="AW92"/>
@@ -8102,7 +8064,7 @@
       <c r="AZ92"/>
     </row>
     <row r="93" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD93" s="172"/>
+      <c r="AD93" s="171"/>
       <c r="AU93"/>
       <c r="AV93"/>
       <c r="AW93"/>
@@ -8111,7 +8073,7 @@
       <c r="AZ93"/>
     </row>
     <row r="94" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD94" s="172"/>
+      <c r="AD94" s="171"/>
       <c r="AU94"/>
       <c r="AV94"/>
       <c r="AW94"/>
@@ -8120,7 +8082,7 @@
       <c r="AZ94"/>
     </row>
     <row r="95" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD95" s="172"/>
+      <c r="AD95" s="171"/>
       <c r="AU95"/>
       <c r="AV95"/>
       <c r="AW95"/>
@@ -8129,7 +8091,7 @@
       <c r="AZ95"/>
     </row>
     <row r="96" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD96" s="172"/>
+      <c r="AD96" s="171"/>
       <c r="AU96"/>
       <c r="AV96"/>
       <c r="AW96"/>
@@ -8138,7 +8100,7 @@
       <c r="AZ96"/>
     </row>
     <row r="97" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD97" s="172"/>
+      <c r="AD97" s="171"/>
       <c r="AU97"/>
       <c r="AV97"/>
       <c r="AW97"/>
@@ -8147,7 +8109,7 @@
       <c r="AZ97"/>
     </row>
     <row r="98" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD98" s="172"/>
+      <c r="AD98" s="171"/>
       <c r="AU98"/>
       <c r="AV98"/>
       <c r="AW98"/>
@@ -8156,7 +8118,7 @@
       <c r="AZ98"/>
     </row>
     <row r="99" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD99" s="172"/>
+      <c r="AD99" s="171"/>
       <c r="AU99"/>
       <c r="AV99"/>
       <c r="AW99"/>
@@ -8165,7 +8127,7 @@
       <c r="AZ99"/>
     </row>
     <row r="100" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD100" s="172"/>
+      <c r="AD100" s="171"/>
       <c r="AU100"/>
       <c r="AV100"/>
       <c r="AW100"/>
@@ -8174,7 +8136,7 @@
       <c r="AZ100"/>
     </row>
     <row r="101" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD101" s="172"/>
+      <c r="AD101" s="171"/>
       <c r="AU101"/>
       <c r="AV101"/>
       <c r="AW101"/>
@@ -8183,7 +8145,7 @@
       <c r="AZ101"/>
     </row>
     <row r="102" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD102" s="172"/>
+      <c r="AD102" s="171"/>
       <c r="AU102"/>
       <c r="AV102"/>
       <c r="AW102"/>
@@ -8192,7 +8154,7 @@
       <c r="AZ102"/>
     </row>
     <row r="103" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD103" s="172"/>
+      <c r="AD103" s="171"/>
       <c r="AU103"/>
       <c r="AV103"/>
       <c r="AW103"/>
@@ -8201,7 +8163,7 @@
       <c r="AZ103"/>
     </row>
     <row r="104" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD104" s="172"/>
+      <c r="AD104" s="171"/>
       <c r="AU104"/>
       <c r="AV104"/>
       <c r="AW104"/>
@@ -8210,7 +8172,7 @@
       <c r="AZ104"/>
     </row>
     <row r="105" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD105" s="172"/>
+      <c r="AD105" s="171"/>
       <c r="AU105"/>
       <c r="AV105"/>
       <c r="AW105"/>
@@ -8219,7 +8181,7 @@
       <c r="AZ105"/>
     </row>
     <row r="106" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD106" s="172"/>
+      <c r="AD106" s="171"/>
       <c r="AU106"/>
       <c r="AV106"/>
       <c r="AW106"/>
@@ -8228,7 +8190,7 @@
       <c r="AZ106"/>
     </row>
     <row r="107" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD107" s="172"/>
+      <c r="AD107" s="171"/>
       <c r="AU107"/>
       <c r="AV107"/>
       <c r="AW107"/>
@@ -8237,7 +8199,7 @@
       <c r="AZ107"/>
     </row>
     <row r="108" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD108" s="172"/>
+      <c r="AD108" s="171"/>
       <c r="AU108"/>
       <c r="AV108"/>
       <c r="AW108"/>
@@ -8246,7 +8208,7 @@
       <c r="AZ108"/>
     </row>
     <row r="109" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD109" s="172"/>
+      <c r="AD109" s="171"/>
       <c r="AU109"/>
       <c r="AV109"/>
       <c r="AW109"/>
@@ -8255,7 +8217,7 @@
       <c r="AZ109"/>
     </row>
     <row r="110" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD110" s="172"/>
+      <c r="AD110" s="171"/>
       <c r="AU110"/>
       <c r="AV110"/>
       <c r="AW110"/>
@@ -8264,7 +8226,7 @@
       <c r="AZ110"/>
     </row>
     <row r="111" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD111" s="172"/>
+      <c r="AD111" s="171"/>
       <c r="AU111"/>
       <c r="AV111"/>
       <c r="AW111"/>
@@ -8273,7 +8235,7 @@
       <c r="AZ111"/>
     </row>
     <row r="112" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD112" s="172"/>
+      <c r="AD112" s="171"/>
       <c r="AU112"/>
       <c r="AV112"/>
       <c r="AW112"/>
@@ -8282,7 +8244,7 @@
       <c r="AZ112"/>
     </row>
     <row r="113" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD113" s="172"/>
+      <c r="AD113" s="171"/>
       <c r="AU113"/>
       <c r="AV113"/>
       <c r="AW113"/>
@@ -8291,7 +8253,7 @@
       <c r="AZ113"/>
     </row>
     <row r="114" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD114" s="172"/>
+      <c r="AD114" s="171"/>
       <c r="AU114"/>
       <c r="AV114"/>
       <c r="AW114"/>
@@ -8300,7 +8262,7 @@
       <c r="AZ114"/>
     </row>
     <row r="115" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD115" s="172"/>
+      <c r="AD115" s="171"/>
       <c r="AU115"/>
       <c r="AV115"/>
       <c r="AW115"/>
@@ -8309,7 +8271,7 @@
       <c r="AZ115"/>
     </row>
     <row r="116" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD116" s="172"/>
+      <c r="AD116" s="171"/>
       <c r="AU116"/>
       <c r="AV116"/>
       <c r="AW116"/>
@@ -8318,7 +8280,7 @@
       <c r="AZ116"/>
     </row>
     <row r="117" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD117" s="172"/>
+      <c r="AD117" s="171"/>
       <c r="AU117"/>
       <c r="AV117"/>
       <c r="AW117"/>
@@ -8327,7 +8289,7 @@
       <c r="AZ117"/>
     </row>
     <row r="118" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD118" s="172"/>
+      <c r="AD118" s="171"/>
       <c r="AU118"/>
       <c r="AV118"/>
       <c r="AW118"/>
@@ -8336,7 +8298,7 @@
       <c r="AZ118"/>
     </row>
     <row r="119" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD119" s="172"/>
+      <c r="AD119" s="171"/>
       <c r="AU119"/>
       <c r="AV119"/>
       <c r="AW119"/>
@@ -8345,7 +8307,7 @@
       <c r="AZ119"/>
     </row>
     <row r="120" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD120" s="172"/>
+      <c r="AD120" s="171"/>
       <c r="AU120"/>
       <c r="AV120"/>
       <c r="AW120"/>
@@ -8354,7 +8316,7 @@
       <c r="AZ120"/>
     </row>
     <row r="121" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD121" s="172"/>
+      <c r="AD121" s="171"/>
       <c r="AU121"/>
       <c r="AV121"/>
       <c r="AW121"/>
@@ -8363,7 +8325,7 @@
       <c r="AZ121"/>
     </row>
     <row r="122" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD122" s="172"/>
+      <c r="AD122" s="171"/>
       <c r="AU122"/>
       <c r="AV122"/>
       <c r="AW122"/>
@@ -8372,7 +8334,7 @@
       <c r="AZ122"/>
     </row>
     <row r="123" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD123" s="172"/>
+      <c r="AD123" s="171"/>
       <c r="AU123"/>
       <c r="AV123"/>
       <c r="AW123"/>
@@ -8381,7 +8343,7 @@
       <c r="AZ123"/>
     </row>
     <row r="124" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD124" s="172"/>
+      <c r="AD124" s="171"/>
       <c r="AU124"/>
       <c r="AV124"/>
       <c r="AW124"/>
@@ -8390,7 +8352,7 @@
       <c r="AZ124"/>
     </row>
     <row r="125" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD125" s="172"/>
+      <c r="AD125" s="171"/>
       <c r="AU125"/>
       <c r="AV125"/>
       <c r="AW125"/>
@@ -8399,7 +8361,7 @@
       <c r="AZ125"/>
     </row>
     <row r="126" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD126" s="172"/>
+      <c r="AD126" s="171"/>
       <c r="AU126"/>
       <c r="AV126"/>
       <c r="AW126"/>
@@ -8408,7 +8370,7 @@
       <c r="AZ126"/>
     </row>
     <row r="127" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD127" s="172"/>
+      <c r="AD127" s="171"/>
       <c r="AU127"/>
       <c r="AV127"/>
       <c r="AW127"/>
@@ -8417,7 +8379,7 @@
       <c r="AZ127"/>
     </row>
     <row r="128" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD128" s="172"/>
+      <c r="AD128" s="171"/>
       <c r="AU128"/>
       <c r="AV128"/>
       <c r="AW128"/>
@@ -8426,7 +8388,7 @@
       <c r="AZ128"/>
     </row>
     <row r="129" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD129" s="172"/>
+      <c r="AD129" s="171"/>
       <c r="AU129"/>
       <c r="AV129"/>
       <c r="AW129"/>
@@ -8435,7 +8397,7 @@
       <c r="AZ129"/>
     </row>
     <row r="130" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD130" s="172"/>
+      <c r="AD130" s="171"/>
       <c r="AU130"/>
       <c r="AV130"/>
       <c r="AW130"/>
@@ -8444,7 +8406,7 @@
       <c r="AZ130"/>
     </row>
     <row r="131" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD131" s="172"/>
+      <c r="AD131" s="171"/>
       <c r="AU131"/>
       <c r="AV131"/>
       <c r="AW131"/>
@@ -8453,7 +8415,7 @@
       <c r="AZ131"/>
     </row>
     <row r="132" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD132" s="172"/>
+      <c r="AD132" s="171"/>
       <c r="AU132"/>
       <c r="AV132"/>
       <c r="AW132"/>
@@ -8462,7 +8424,7 @@
       <c r="AZ132"/>
     </row>
     <row r="133" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD133" s="172"/>
+      <c r="AD133" s="171"/>
       <c r="AU133"/>
       <c r="AV133"/>
       <c r="AW133"/>
@@ -8471,7 +8433,7 @@
       <c r="AZ133"/>
     </row>
     <row r="134" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD134" s="172"/>
+      <c r="AD134" s="171"/>
       <c r="AU134"/>
       <c r="AV134"/>
       <c r="AW134"/>
@@ -8480,7 +8442,7 @@
       <c r="AZ134"/>
     </row>
     <row r="135" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD135" s="172"/>
+      <c r="AD135" s="171"/>
       <c r="AU135"/>
       <c r="AV135"/>
       <c r="AW135"/>
@@ -8489,7 +8451,7 @@
       <c r="AZ135"/>
     </row>
     <row r="136" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD136" s="172"/>
+      <c r="AD136" s="171"/>
       <c r="AU136"/>
       <c r="AV136"/>
       <c r="AW136"/>
@@ -8498,7 +8460,7 @@
       <c r="AZ136"/>
     </row>
     <row r="137" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD137" s="172"/>
+      <c r="AD137" s="171"/>
       <c r="AU137"/>
       <c r="AV137"/>
       <c r="AW137"/>
@@ -8507,7 +8469,7 @@
       <c r="AZ137"/>
     </row>
     <row r="138" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD138" s="172"/>
+      <c r="AD138" s="171"/>
       <c r="AU138"/>
       <c r="AV138"/>
       <c r="AW138"/>
@@ -8516,7 +8478,7 @@
       <c r="AZ138"/>
     </row>
     <row r="139" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD139" s="172"/>
+      <c r="AD139" s="171"/>
       <c r="AU139"/>
       <c r="AV139"/>
       <c r="AW139"/>
@@ -8525,7 +8487,7 @@
       <c r="AZ139"/>
     </row>
     <row r="140" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD140" s="172"/>
+      <c r="AD140" s="171"/>
       <c r="AU140"/>
       <c r="AV140"/>
       <c r="AW140"/>
@@ -8534,7 +8496,7 @@
       <c r="AZ140"/>
     </row>
     <row r="141" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD141" s="172"/>
+      <c r="AD141" s="171"/>
       <c r="AU141"/>
       <c r="AV141"/>
       <c r="AW141"/>
@@ -8543,7 +8505,7 @@
       <c r="AZ141"/>
     </row>
     <row r="142" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD142" s="172"/>
+      <c r="AD142" s="171"/>
       <c r="AU142"/>
       <c r="AV142"/>
       <c r="AW142"/>
@@ -8552,7 +8514,7 @@
       <c r="AZ142"/>
     </row>
     <row r="143" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD143" s="172"/>
+      <c r="AD143" s="171"/>
       <c r="AU143"/>
       <c r="AV143"/>
       <c r="AW143"/>
@@ -8561,7 +8523,7 @@
       <c r="AZ143"/>
     </row>
     <row r="144" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD144" s="172"/>
+      <c r="AD144" s="171"/>
       <c r="AU144"/>
       <c r="AV144"/>
       <c r="AW144"/>
@@ -8570,7 +8532,7 @@
       <c r="AZ144"/>
     </row>
     <row r="145" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD145" s="172"/>
+      <c r="AD145" s="171"/>
       <c r="AU145"/>
       <c r="AV145"/>
       <c r="AW145"/>
@@ -8579,7 +8541,7 @@
       <c r="AZ145"/>
     </row>
     <row r="146" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD146" s="172"/>
+      <c r="AD146" s="171"/>
       <c r="AU146"/>
       <c r="AV146"/>
       <c r="AW146"/>
@@ -8588,7 +8550,7 @@
       <c r="AZ146"/>
     </row>
     <row r="147" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD147" s="172"/>
+      <c r="AD147" s="171"/>
       <c r="AU147"/>
       <c r="AV147"/>
       <c r="AW147"/>
@@ -8597,7 +8559,7 @@
       <c r="AZ147"/>
     </row>
     <row r="148" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD148" s="172"/>
+      <c r="AD148" s="171"/>
       <c r="AU148"/>
       <c r="AV148"/>
       <c r="AW148"/>
@@ -8606,7 +8568,7 @@
       <c r="AZ148"/>
     </row>
     <row r="149" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD149" s="172"/>
+      <c r="AD149" s="171"/>
       <c r="AU149"/>
       <c r="AV149"/>
       <c r="AW149"/>
@@ -8615,7 +8577,7 @@
       <c r="AZ149"/>
     </row>
     <row r="150" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD150" s="172"/>
+      <c r="AD150" s="171"/>
       <c r="AU150"/>
       <c r="AV150"/>
       <c r="AW150"/>
@@ -8624,7 +8586,7 @@
       <c r="AZ150"/>
     </row>
     <row r="151" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD151" s="172"/>
+      <c r="AD151" s="171"/>
       <c r="AU151"/>
       <c r="AV151"/>
       <c r="AW151"/>
@@ -8633,7 +8595,7 @@
       <c r="AZ151"/>
     </row>
     <row r="152" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD152" s="172"/>
+      <c r="AD152" s="171"/>
       <c r="AU152"/>
       <c r="AV152"/>
       <c r="AW152"/>
@@ -8642,7 +8604,7 @@
       <c r="AZ152"/>
     </row>
     <row r="153" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD153" s="172"/>
+      <c r="AD153" s="171"/>
       <c r="AU153"/>
       <c r="AV153"/>
       <c r="AW153"/>
@@ -8651,7 +8613,7 @@
       <c r="AZ153"/>
     </row>
     <row r="154" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD154" s="172"/>
+      <c r="AD154" s="171"/>
       <c r="AU154"/>
       <c r="AV154"/>
       <c r="AW154"/>
@@ -8660,7 +8622,7 @@
       <c r="AZ154"/>
     </row>
     <row r="155" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD155" s="172"/>
+      <c r="AD155" s="171"/>
       <c r="AU155"/>
       <c r="AV155"/>
       <c r="AW155"/>
@@ -8669,7 +8631,7 @@
       <c r="AZ155"/>
     </row>
     <row r="156" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD156" s="172"/>
+      <c r="AD156" s="171"/>
       <c r="AU156"/>
       <c r="AV156"/>
       <c r="AW156"/>
@@ -8678,7 +8640,7 @@
       <c r="AZ156"/>
     </row>
     <row r="157" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD157" s="172"/>
+      <c r="AD157" s="171"/>
       <c r="AU157"/>
       <c r="AV157"/>
       <c r="AW157"/>
@@ -8687,7 +8649,7 @@
       <c r="AZ157"/>
     </row>
     <row r="158" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD158" s="172"/>
+      <c r="AD158" s="171"/>
       <c r="AU158"/>
       <c r="AV158"/>
       <c r="AW158"/>
@@ -8696,7 +8658,7 @@
       <c r="AZ158"/>
     </row>
     <row r="159" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD159" s="172"/>
+      <c r="AD159" s="171"/>
       <c r="AU159"/>
       <c r="AV159"/>
       <c r="AW159"/>
@@ -8705,7 +8667,7 @@
       <c r="AZ159"/>
     </row>
     <row r="160" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD160" s="172"/>
+      <c r="AD160" s="171"/>
       <c r="AU160"/>
       <c r="AV160"/>
       <c r="AW160"/>
@@ -8714,7 +8676,7 @@
       <c r="AZ160"/>
     </row>
     <row r="161" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD161" s="172"/>
+      <c r="AD161" s="171"/>
       <c r="AU161"/>
       <c r="AV161"/>
       <c r="AW161"/>
@@ -8723,7 +8685,7 @@
       <c r="AZ161"/>
     </row>
     <row r="162" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD162" s="172"/>
+      <c r="AD162" s="171"/>
       <c r="AU162"/>
       <c r="AV162"/>
       <c r="AW162"/>
@@ -8732,7 +8694,7 @@
       <c r="AZ162"/>
     </row>
     <row r="163" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD163" s="172"/>
+      <c r="AD163" s="171"/>
       <c r="AU163"/>
       <c r="AV163"/>
       <c r="AW163"/>
@@ -8741,7 +8703,7 @@
       <c r="AZ163"/>
     </row>
     <row r="164" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD164" s="172"/>
+      <c r="AD164" s="171"/>
       <c r="AU164"/>
       <c r="AV164"/>
       <c r="AW164"/>
@@ -8750,7 +8712,7 @@
       <c r="AZ164"/>
     </row>
     <row r="165" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD165" s="172"/>
+      <c r="AD165" s="171"/>
       <c r="AU165"/>
       <c r="AV165"/>
       <c r="AW165"/>
@@ -8759,7 +8721,7 @@
       <c r="AZ165"/>
     </row>
     <row r="166" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD166" s="172"/>
+      <c r="AD166" s="171"/>
       <c r="AU166"/>
       <c r="AV166"/>
       <c r="AW166"/>
@@ -8768,7 +8730,7 @@
       <c r="AZ166"/>
     </row>
     <row r="167" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD167" s="172"/>
+      <c r="AD167" s="171"/>
       <c r="AU167"/>
       <c r="AV167"/>
       <c r="AW167"/>
@@ -8777,7 +8739,7 @@
       <c r="AZ167"/>
     </row>
     <row r="168" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD168" s="172"/>
+      <c r="AD168" s="171"/>
       <c r="AU168"/>
       <c r="AV168"/>
       <c r="AW168"/>
@@ -8786,7 +8748,7 @@
       <c r="AZ168"/>
     </row>
     <row r="169" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD169" s="172"/>
+      <c r="AD169" s="171"/>
       <c r="AU169"/>
       <c r="AV169"/>
       <c r="AW169"/>
@@ -8795,7 +8757,7 @@
       <c r="AZ169"/>
     </row>
     <row r="170" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD170" s="172"/>
+      <c r="AD170" s="171"/>
       <c r="AU170"/>
       <c r="AV170"/>
       <c r="AW170"/>
@@ -8804,7 +8766,7 @@
       <c r="AZ170"/>
     </row>
     <row r="171" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD171" s="172"/>
+      <c r="AD171" s="171"/>
       <c r="AU171"/>
       <c r="AV171"/>
       <c r="AW171"/>
@@ -8813,7 +8775,7 @@
       <c r="AZ171"/>
     </row>
     <row r="172" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD172" s="172"/>
+      <c r="AD172" s="171"/>
       <c r="AU172"/>
       <c r="AV172"/>
       <c r="AW172"/>
@@ -8822,7 +8784,7 @@
       <c r="AZ172"/>
     </row>
     <row r="173" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD173" s="172"/>
+      <c r="AD173" s="171"/>
       <c r="AU173"/>
       <c r="AV173"/>
       <c r="AW173"/>
@@ -8831,7 +8793,7 @@
       <c r="AZ173"/>
     </row>
     <row r="174" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD174" s="172"/>
+      <c r="AD174" s="171"/>
       <c r="AU174"/>
       <c r="AV174"/>
       <c r="AW174"/>
@@ -8840,7 +8802,7 @@
       <c r="AZ174"/>
     </row>
     <row r="175" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD175" s="172"/>
+      <c r="AD175" s="171"/>
       <c r="AU175"/>
       <c r="AV175"/>
       <c r="AW175"/>
@@ -8849,7 +8811,7 @@
       <c r="AZ175"/>
     </row>
     <row r="176" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD176" s="172"/>
+      <c r="AD176" s="171"/>
       <c r="AU176"/>
       <c r="AV176"/>
       <c r="AW176"/>
@@ -8858,7 +8820,7 @@
       <c r="AZ176"/>
     </row>
     <row r="177" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD177" s="172"/>
+      <c r="AD177" s="171"/>
       <c r="AU177"/>
       <c r="AV177"/>
       <c r="AW177"/>
@@ -8867,7 +8829,7 @@
       <c r="AZ177"/>
     </row>
     <row r="178" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD178" s="172"/>
+      <c r="AD178" s="171"/>
       <c r="AU178"/>
       <c r="AV178"/>
       <c r="AW178"/>
@@ -8876,7 +8838,7 @@
       <c r="AZ178"/>
     </row>
     <row r="179" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD179" s="172"/>
+      <c r="AD179" s="171"/>
       <c r="AU179"/>
       <c r="AV179"/>
       <c r="AW179"/>
@@ -8885,7 +8847,7 @@
       <c r="AZ179"/>
     </row>
     <row r="180" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD180" s="172"/>
+      <c r="AD180" s="171"/>
       <c r="AU180"/>
       <c r="AV180"/>
       <c r="AW180"/>
@@ -8894,7 +8856,7 @@
       <c r="AZ180"/>
     </row>
     <row r="181" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD181" s="172"/>
+      <c r="AD181" s="171"/>
       <c r="AU181"/>
       <c r="AV181"/>
       <c r="AW181"/>
@@ -8903,7 +8865,7 @@
       <c r="AZ181"/>
     </row>
     <row r="182" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD182" s="172"/>
+      <c r="AD182" s="171"/>
       <c r="AU182"/>
       <c r="AV182"/>
       <c r="AW182"/>
@@ -8912,7 +8874,7 @@
       <c r="AZ182"/>
     </row>
     <row r="183" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD183" s="172"/>
+      <c r="AD183" s="171"/>
       <c r="AU183"/>
       <c r="AV183"/>
       <c r="AW183"/>
@@ -8921,7 +8883,7 @@
       <c r="AZ183"/>
     </row>
     <row r="184" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD184" s="172"/>
+      <c r="AD184" s="171"/>
       <c r="AU184"/>
       <c r="AV184"/>
       <c r="AW184"/>
@@ -8930,7 +8892,7 @@
       <c r="AZ184"/>
     </row>
     <row r="185" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD185" s="172"/>
+      <c r="AD185" s="171"/>
       <c r="AU185"/>
       <c r="AV185"/>
       <c r="AW185"/>
@@ -8939,7 +8901,7 @@
       <c r="AZ185"/>
     </row>
     <row r="186" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD186" s="172"/>
+      <c r="AD186" s="171"/>
       <c r="AU186"/>
       <c r="AV186"/>
       <c r="AW186"/>
@@ -8948,7 +8910,7 @@
       <c r="AZ186"/>
     </row>
     <row r="187" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD187" s="172"/>
+      <c r="AD187" s="171"/>
       <c r="AU187"/>
       <c r="AV187"/>
       <c r="AW187"/>
@@ -8957,7 +8919,7 @@
       <c r="AZ187"/>
     </row>
     <row r="188" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD188" s="172"/>
+      <c r="AD188" s="171"/>
       <c r="AU188"/>
       <c r="AV188"/>
       <c r="AW188"/>
@@ -8966,7 +8928,7 @@
       <c r="AZ188"/>
     </row>
     <row r="189" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD189" s="172"/>
+      <c r="AD189" s="171"/>
       <c r="AU189"/>
       <c r="AV189"/>
       <c r="AW189"/>
@@ -8975,7 +8937,7 @@
       <c r="AZ189"/>
     </row>
     <row r="190" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD190" s="172"/>
+      <c r="AD190" s="171"/>
       <c r="AU190"/>
       <c r="AV190"/>
       <c r="AW190"/>
@@ -8984,7 +8946,7 @@
       <c r="AZ190"/>
     </row>
     <row r="191" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD191" s="172"/>
+      <c r="AD191" s="171"/>
       <c r="AU191"/>
       <c r="AV191"/>
       <c r="AW191"/>
@@ -8993,7 +8955,7 @@
       <c r="AZ191"/>
     </row>
     <row r="192" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD192" s="172"/>
+      <c r="AD192" s="171"/>
       <c r="AU192"/>
       <c r="AV192"/>
       <c r="AW192"/>
@@ -9002,7 +8964,7 @@
       <c r="AZ192"/>
     </row>
     <row r="193" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD193" s="172"/>
+      <c r="AD193" s="171"/>
       <c r="AU193"/>
       <c r="AV193"/>
       <c r="AW193"/>
@@ -9011,7 +8973,7 @@
       <c r="AZ193"/>
     </row>
     <row r="194" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD194" s="172"/>
+      <c r="AD194" s="171"/>
       <c r="AU194"/>
       <c r="AV194"/>
       <c r="AW194"/>
@@ -9020,7 +8982,7 @@
       <c r="AZ194"/>
     </row>
     <row r="195" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD195" s="172"/>
+      <c r="AD195" s="171"/>
       <c r="AU195"/>
       <c r="AV195"/>
       <c r="AW195"/>
@@ -9029,7 +8991,7 @@
       <c r="AZ195"/>
     </row>
     <row r="196" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD196" s="172"/>
+      <c r="AD196" s="171"/>
       <c r="AU196"/>
       <c r="AV196"/>
       <c r="AW196"/>
@@ -9038,7 +9000,7 @@
       <c r="AZ196"/>
     </row>
     <row r="197" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD197" s="172"/>
+      <c r="AD197" s="171"/>
       <c r="AU197"/>
       <c r="AV197"/>
       <c r="AW197"/>
@@ -9047,7 +9009,7 @@
       <c r="AZ197"/>
     </row>
     <row r="198" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD198" s="172"/>
+      <c r="AD198" s="171"/>
       <c r="AU198"/>
       <c r="AV198"/>
       <c r="AW198"/>
@@ -9056,7 +9018,7 @@
       <c r="AZ198"/>
     </row>
     <row r="199" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD199" s="172"/>
+      <c r="AD199" s="171"/>
       <c r="AU199"/>
       <c r="AV199"/>
       <c r="AW199"/>
@@ -9065,7 +9027,7 @@
       <c r="AZ199"/>
     </row>
     <row r="200" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD200" s="172"/>
+      <c r="AD200" s="171"/>
       <c r="AU200"/>
       <c r="AV200"/>
       <c r="AW200"/>
@@ -11650,7 +11612,7 @@
       <c r="AZ522"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:AC10">
+  <sortState ref="B9:AC10">
     <sortCondition ref="B9"/>
   </sortState>
   <mergeCells count="3">
@@ -11664,10 +11626,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29" xr:uid="{7DB9EFD9-E784-464D-B93C-ABBEF7F1E8CE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
       <formula1>$D$43:$D$44</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37" xr:uid="{9801D4AE-E571-4CBA-A92E-D326A24D3A44}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37">
       <formula1>$C$43:$C$44</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="90">
   <si>
     <t>По номенклатуре:</t>
   </si>
@@ -295,6 +295,21 @@
   </si>
   <si>
     <t>{{ tender_number }}</t>
+  </si>
+  <si>
+    <t>Менеджер:</t>
+  </si>
+  <si>
+    <t>Коммерческий директор:</t>
+  </si>
+  <si>
+    <t>Тунегов Я.Ю.</t>
+  </si>
+  <si>
+    <t>Ген. директор</t>
+  </si>
+  <si>
+    <t>Бондарева В. В.</t>
   </si>
 </sst>
 </file>
@@ -3113,7 +3128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3583,6 +3598,12 @@
     </xf>
     <xf numFmtId="182" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5614,23 +5635,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="165" t="s">
+      <c r="B1" s="167" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-      <c r="L1" s="166"/>
-      <c r="M1" s="166"/>
-      <c r="N1" s="166"/>
-      <c r="O1" s="167"/>
-      <c r="AD1" s="171"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="169"/>
+      <c r="AD1" s="173"/>
       <c r="AU1"/>
       <c r="AV1"/>
       <c r="AW1"/>
@@ -5654,7 +5675,7 @@
       <c r="X2" s="134"/>
       <c r="Y2" s="134"/>
       <c r="Z2" s="134"/>
-      <c r="AD2" s="171"/>
+      <c r="AD2" s="173"/>
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
@@ -5687,7 +5708,7 @@
       <c r="X3" s="134"/>
       <c r="Y3" s="134"/>
       <c r="Z3" s="134"/>
-      <c r="AD3" s="171"/>
+      <c r="AD3" s="173"/>
       <c r="AU3"/>
       <c r="AV3"/>
       <c r="AW3"/>
@@ -5713,18 +5734,18 @@
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="168"/>
-      <c r="Q4" s="169"/>
-      <c r="R4" s="169"/>
-      <c r="S4" s="169"/>
-      <c r="T4" s="169"/>
-      <c r="U4" s="170"/>
+      <c r="P4" s="170"/>
+      <c r="Q4" s="171"/>
+      <c r="R4" s="171"/>
+      <c r="S4" s="171"/>
+      <c r="T4" s="171"/>
+      <c r="U4" s="172"/>
       <c r="V4" s="134"/>
       <c r="W4" s="134"/>
       <c r="X4" s="134"/>
       <c r="Y4" s="134"/>
       <c r="Z4" s="134"/>
-      <c r="AD4" s="171"/>
+      <c r="AD4" s="173"/>
       <c r="AU4"/>
       <c r="AV4"/>
       <c r="AW4"/>
@@ -5762,7 +5783,7 @@
       <c r="X5" s="134"/>
       <c r="Y5" s="134"/>
       <c r="Z5" s="134"/>
-      <c r="AD5" s="171"/>
+      <c r="AD5" s="173"/>
       <c r="AU5"/>
       <c r="AV5"/>
       <c r="AW5"/>
@@ -5793,7 +5814,7 @@
       <c r="X6" s="135"/>
       <c r="Y6" s="135"/>
       <c r="Z6" s="135"/>
-      <c r="AD6" s="171"/>
+      <c r="AD6" s="173"/>
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6"/>
@@ -5832,7 +5853,7 @@
       <c r="X7" s="132"/>
       <c r="Y7" s="132"/>
       <c r="Z7" s="133"/>
-      <c r="AD7" s="171"/>
+      <c r="AD7" s="173"/>
       <c r="AU7"/>
       <c r="AV7"/>
       <c r="AW7"/>
@@ -5918,7 +5939,7 @@
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
       <c r="AC8" s="30"/>
-      <c r="AD8" s="171"/>
+      <c r="AD8" s="173"/>
       <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8"/>
@@ -5992,7 +6013,7 @@
       <c r="AA9" s="38"/>
       <c r="AB9" s="38"/>
       <c r="AC9" s="39"/>
-      <c r="AD9" s="171"/>
+      <c r="AD9" s="173"/>
       <c r="AU9"/>
       <c r="AV9"/>
       <c r="AW9"/>
@@ -6088,7 +6109,7 @@
       <c r="AA10" s="60"/>
       <c r="AB10" s="60"/>
       <c r="AC10" s="60"/>
-      <c r="AD10" s="171"/>
+      <c r="AD10" s="173"/>
       <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
@@ -6149,7 +6170,7 @@
       <c r="AA11" s="60"/>
       <c r="AB11" s="60"/>
       <c r="AC11" s="60"/>
-      <c r="AD11" s="171"/>
+      <c r="AD11" s="173"/>
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
@@ -6190,7 +6211,7 @@
       <c r="Y12" s="93"/>
       <c r="Z12" s="94"/>
       <c r="AC12" s="95"/>
-      <c r="AD12" s="171"/>
+      <c r="AD12" s="173"/>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
@@ -6226,7 +6247,7 @@
       <c r="Y13"/>
       <c r="Z13"/>
       <c r="AA13"/>
-      <c r="AD13" s="171"/>
+      <c r="AD13" s="173"/>
       <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13"/>
@@ -6270,7 +6291,7 @@
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
-      <c r="AD14" s="171"/>
+      <c r="AD14" s="173"/>
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
@@ -6314,7 +6335,7 @@
       <c r="Y15"/>
       <c r="Z15"/>
       <c r="AA15"/>
-      <c r="AD15" s="171"/>
+      <c r="AD15" s="173"/>
       <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
@@ -6360,7 +6381,7 @@
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
-      <c r="AD16" s="171"/>
+      <c r="AD16" s="173"/>
       <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
@@ -6404,7 +6425,7 @@
       <c r="Y17"/>
       <c r="Z17"/>
       <c r="AA17"/>
-      <c r="AD17" s="171"/>
+      <c r="AD17" s="173"/>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
@@ -6441,7 +6462,7 @@
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
-      <c r="AD18" s="171"/>
+      <c r="AD18" s="173"/>
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18"/>
@@ -6482,7 +6503,7 @@
       <c r="Y19"/>
       <c r="Z19"/>
       <c r="AA19"/>
-      <c r="AD19" s="171"/>
+      <c r="AD19" s="173"/>
       <c r="AU19"/>
       <c r="AV19"/>
       <c r="AW19"/>
@@ -6520,7 +6541,7 @@
       <c r="Y20"/>
       <c r="Z20"/>
       <c r="AA20"/>
-      <c r="AD20" s="171"/>
+      <c r="AD20" s="173"/>
       <c r="AU20"/>
       <c r="AV20"/>
       <c r="AW20"/>
@@ -6558,7 +6579,7 @@
       <c r="Y21"/>
       <c r="Z21"/>
       <c r="AA21"/>
-      <c r="AD21" s="171"/>
+      <c r="AD21" s="173"/>
       <c r="AU21"/>
       <c r="AV21"/>
       <c r="AW21"/>
@@ -6581,8 +6602,10 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
-      <c r="M22"/>
-      <c r="N22"/>
+      <c r="M22" s="165" t="s">
+        <v>85</v>
+      </c>
+      <c r="N22" s="166"/>
       <c r="O22"/>
       <c r="P22"/>
       <c r="Q22"/>
@@ -6596,7 +6619,7 @@
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
-      <c r="AD22" s="171"/>
+      <c r="AD22" s="173"/>
       <c r="AU22"/>
       <c r="AV22"/>
       <c r="AW22"/>
@@ -6621,8 +6644,6 @@
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
       <c r="O23"/>
       <c r="P23"/>
       <c r="Q23"/>
@@ -6636,7 +6657,7 @@
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23"/>
-      <c r="AD23" s="171"/>
+      <c r="AD23" s="173"/>
       <c r="AU23"/>
       <c r="AV23"/>
       <c r="AW23"/>
@@ -6662,8 +6683,12 @@
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24"/>
+      <c r="M24" s="165" t="s">
+        <v>86</v>
+      </c>
+      <c r="N24" s="166" t="s">
+        <v>87</v>
+      </c>
       <c r="O24"/>
       <c r="P24"/>
       <c r="Q24"/>
@@ -6677,7 +6702,7 @@
       <c r="Y24"/>
       <c r="Z24"/>
       <c r="AA24"/>
-      <c r="AD24" s="171"/>
+      <c r="AD24" s="173"/>
       <c r="AU24"/>
       <c r="AV24"/>
       <c r="AW24"/>
@@ -6703,8 +6728,8 @@
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
-      <c r="M25"/>
-      <c r="N25"/>
+      <c r="M25" s="101"/>
+      <c r="N25" s="101"/>
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25"/>
@@ -6718,7 +6743,7 @@
       <c r="Y25"/>
       <c r="Z25"/>
       <c r="AA25"/>
-      <c r="AD25" s="171"/>
+      <c r="AD25" s="173"/>
       <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
@@ -6744,8 +6769,12 @@
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
+      <c r="M26" s="165" t="s">
+        <v>88</v>
+      </c>
+      <c r="N26" s="166" t="s">
+        <v>89</v>
+      </c>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -6759,7 +6788,7 @@
       <c r="Y26"/>
       <c r="Z26"/>
       <c r="AA26"/>
-      <c r="AD26" s="171"/>
+      <c r="AD26" s="173"/>
       <c r="AU26"/>
       <c r="AV26"/>
       <c r="AW26"/>
@@ -6800,7 +6829,7 @@
       <c r="Y27"/>
       <c r="Z27"/>
       <c r="AA27"/>
-      <c r="AD27" s="171"/>
+      <c r="AD27" s="173"/>
       <c r="AU27"/>
       <c r="AV27"/>
       <c r="AW27"/>
@@ -6841,7 +6870,7 @@
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28"/>
-      <c r="AD28" s="171"/>
+      <c r="AD28" s="173"/>
       <c r="AU28"/>
       <c r="AV28"/>
       <c r="AW28"/>
@@ -6884,7 +6913,7 @@
       <c r="Y29"/>
       <c r="Z29"/>
       <c r="AA29"/>
-      <c r="AD29" s="171"/>
+      <c r="AD29" s="173"/>
       <c r="AU29"/>
       <c r="AV29"/>
       <c r="AW29"/>
@@ -6925,7 +6954,7 @@
       <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
-      <c r="AD30" s="171"/>
+      <c r="AD30" s="173"/>
       <c r="AU30"/>
       <c r="AV30"/>
       <c r="AW30"/>
@@ -6968,7 +6997,7 @@
       <c r="AA31"/>
       <c r="AB31" s="100"/>
       <c r="AC31" s="100"/>
-      <c r="AD31" s="171"/>
+      <c r="AD31" s="173"/>
       <c r="AE31" s="100"/>
       <c r="AF31" s="100"/>
       <c r="AU31"/>
@@ -7013,7 +7042,7 @@
       <c r="AA32"/>
       <c r="AB32" s="100"/>
       <c r="AC32" s="100"/>
-      <c r="AD32" s="171"/>
+      <c r="AD32" s="173"/>
       <c r="AE32" s="100"/>
       <c r="AF32" s="100"/>
       <c r="AU32"/>
@@ -7060,7 +7089,7 @@
       <c r="AA33"/>
       <c r="AB33" s="100"/>
       <c r="AC33" s="100"/>
-      <c r="AD33" s="171"/>
+      <c r="AD33" s="173"/>
       <c r="AE33" s="100"/>
       <c r="AF33" s="100"/>
       <c r="AU33"/>
@@ -7105,7 +7134,7 @@
       <c r="AA34"/>
       <c r="AB34" s="100"/>
       <c r="AC34" s="100"/>
-      <c r="AD34" s="171"/>
+      <c r="AD34" s="173"/>
       <c r="AE34" s="100"/>
       <c r="AF34" s="100"/>
       <c r="AG34" s="100"/>
@@ -7151,7 +7180,7 @@
       <c r="AA35"/>
       <c r="AB35" s="100"/>
       <c r="AC35" s="100"/>
-      <c r="AD35" s="171"/>
+      <c r="AD35" s="173"/>
       <c r="AE35" s="100"/>
       <c r="AF35" s="100"/>
       <c r="AG35" s="100"/>
@@ -7197,7 +7226,7 @@
       <c r="AA36"/>
       <c r="AB36" s="100"/>
       <c r="AC36" s="100"/>
-      <c r="AD36" s="171"/>
+      <c r="AD36" s="173"/>
       <c r="AE36" s="100"/>
       <c r="AF36" s="100"/>
       <c r="AG36" s="100"/>
@@ -7245,7 +7274,7 @@
       <c r="AA37"/>
       <c r="AB37" s="100"/>
       <c r="AC37" s="100"/>
-      <c r="AD37" s="171"/>
+      <c r="AD37" s="173"/>
       <c r="AE37" s="100"/>
       <c r="AF37" s="100"/>
       <c r="AG37" s="100"/>
@@ -7291,7 +7320,7 @@
       <c r="AA38"/>
       <c r="AB38" s="100"/>
       <c r="AC38" s="100"/>
-      <c r="AD38" s="171"/>
+      <c r="AD38" s="173"/>
       <c r="AE38" s="100"/>
       <c r="AF38" s="100"/>
       <c r="AG38" s="100"/>
@@ -7334,7 +7363,7 @@
       <c r="AA39"/>
       <c r="AB39" s="100"/>
       <c r="AC39" s="100"/>
-      <c r="AD39" s="171"/>
+      <c r="AD39" s="173"/>
       <c r="AE39" s="100"/>
       <c r="AF39" s="100"/>
       <c r="AG39" s="100"/>
@@ -7380,7 +7409,7 @@
       <c r="AA40"/>
       <c r="AB40" s="100"/>
       <c r="AC40" s="100"/>
-      <c r="AD40" s="171"/>
+      <c r="AD40" s="173"/>
       <c r="AE40" s="100"/>
       <c r="AF40" s="100"/>
       <c r="AG40" s="100"/>
@@ -7421,7 +7450,7 @@
       <c r="AA41"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-      <c r="AD41" s="171"/>
+      <c r="AD41" s="173"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
@@ -7461,7 +7490,7 @@
       <c r="AA42"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="171"/>
+      <c r="AD42" s="173"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
@@ -7504,7 +7533,7 @@
       <c r="AA43"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="171"/>
+      <c r="AD43" s="173"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
@@ -7545,7 +7574,7 @@
       <c r="Y44"/>
       <c r="Z44"/>
       <c r="AA44"/>
-      <c r="AD44" s="171"/>
+      <c r="AD44" s="173"/>
       <c r="AU44"/>
       <c r="AV44"/>
       <c r="AW44"/>
@@ -7580,7 +7609,7 @@
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AD45" s="171"/>
+      <c r="AD45" s="173"/>
       <c r="AU45"/>
       <c r="AV45"/>
       <c r="AW45"/>
@@ -7615,7 +7644,7 @@
       <c r="Y46"/>
       <c r="Z46"/>
       <c r="AA46"/>
-      <c r="AD46" s="171"/>
+      <c r="AD46" s="173"/>
       <c r="AU46"/>
       <c r="AV46"/>
       <c r="AW46"/>
@@ -7650,7 +7679,7 @@
       <c r="Y47"/>
       <c r="Z47"/>
       <c r="AA47"/>
-      <c r="AD47" s="171"/>
+      <c r="AD47" s="173"/>
       <c r="AU47"/>
       <c r="AV47"/>
       <c r="AW47"/>
@@ -7659,7 +7688,7 @@
       <c r="AZ47"/>
     </row>
     <row r="48" spans="1:52" ht="11.45" customHeight="1">
-      <c r="AD48" s="171"/>
+      <c r="AD48" s="173"/>
       <c r="AU48"/>
       <c r="AV48"/>
       <c r="AW48"/>
@@ -7668,7 +7697,7 @@
       <c r="AZ48"/>
     </row>
     <row r="49" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD49" s="171"/>
+      <c r="AD49" s="173"/>
       <c r="AU49"/>
       <c r="AV49"/>
       <c r="AW49"/>
@@ -7677,7 +7706,7 @@
       <c r="AZ49"/>
     </row>
     <row r="50" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD50" s="171"/>
+      <c r="AD50" s="173"/>
       <c r="AU50"/>
       <c r="AV50"/>
       <c r="AW50"/>
@@ -7686,7 +7715,7 @@
       <c r="AZ50"/>
     </row>
     <row r="51" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD51" s="171"/>
+      <c r="AD51" s="173"/>
       <c r="AU51"/>
       <c r="AV51"/>
       <c r="AW51"/>
@@ -7695,7 +7724,7 @@
       <c r="AZ51"/>
     </row>
     <row r="52" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD52" s="171"/>
+      <c r="AD52" s="173"/>
       <c r="AU52"/>
       <c r="AV52"/>
       <c r="AW52"/>
@@ -7704,7 +7733,7 @@
       <c r="AZ52"/>
     </row>
     <row r="53" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD53" s="171"/>
+      <c r="AD53" s="173"/>
       <c r="AU53"/>
       <c r="AV53"/>
       <c r="AW53"/>
@@ -7713,7 +7742,7 @@
       <c r="AZ53"/>
     </row>
     <row r="54" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD54" s="171"/>
+      <c r="AD54" s="173"/>
       <c r="AU54"/>
       <c r="AV54"/>
       <c r="AW54"/>
@@ -7722,7 +7751,7 @@
       <c r="AZ54"/>
     </row>
     <row r="55" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD55" s="171"/>
+      <c r="AD55" s="173"/>
       <c r="AU55"/>
       <c r="AV55"/>
       <c r="AW55"/>
@@ -7731,7 +7760,7 @@
       <c r="AZ55"/>
     </row>
     <row r="56" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD56" s="171"/>
+      <c r="AD56" s="173"/>
       <c r="AU56"/>
       <c r="AV56"/>
       <c r="AW56"/>
@@ -7740,7 +7769,7 @@
       <c r="AZ56"/>
     </row>
     <row r="57" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD57" s="171"/>
+      <c r="AD57" s="173"/>
       <c r="AU57"/>
       <c r="AV57"/>
       <c r="AW57"/>
@@ -7749,7 +7778,7 @@
       <c r="AZ57"/>
     </row>
     <row r="58" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD58" s="171"/>
+      <c r="AD58" s="173"/>
       <c r="AU58"/>
       <c r="AV58"/>
       <c r="AW58"/>
@@ -7758,7 +7787,7 @@
       <c r="AZ58"/>
     </row>
     <row r="59" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD59" s="171"/>
+      <c r="AD59" s="173"/>
       <c r="AU59"/>
       <c r="AV59"/>
       <c r="AW59"/>
@@ -7767,7 +7796,7 @@
       <c r="AZ59"/>
     </row>
     <row r="60" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD60" s="171"/>
+      <c r="AD60" s="173"/>
       <c r="AU60"/>
       <c r="AV60"/>
       <c r="AW60"/>
@@ -7776,7 +7805,7 @@
       <c r="AZ60"/>
     </row>
     <row r="61" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD61" s="171"/>
+      <c r="AD61" s="173"/>
       <c r="AU61"/>
       <c r="AV61"/>
       <c r="AW61"/>
@@ -7785,7 +7814,7 @@
       <c r="AZ61"/>
     </row>
     <row r="62" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD62" s="171"/>
+      <c r="AD62" s="173"/>
       <c r="AU62"/>
       <c r="AV62"/>
       <c r="AW62"/>
@@ -7794,7 +7823,7 @@
       <c r="AZ62"/>
     </row>
     <row r="63" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD63" s="171"/>
+      <c r="AD63" s="173"/>
       <c r="AU63"/>
       <c r="AV63"/>
       <c r="AW63"/>
@@ -7803,7 +7832,7 @@
       <c r="AZ63"/>
     </row>
     <row r="64" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD64" s="171"/>
+      <c r="AD64" s="173"/>
       <c r="AU64"/>
       <c r="AV64"/>
       <c r="AW64"/>
@@ -7812,7 +7841,7 @@
       <c r="AZ64"/>
     </row>
     <row r="65" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD65" s="171"/>
+      <c r="AD65" s="173"/>
       <c r="AU65"/>
       <c r="AV65"/>
       <c r="AW65"/>
@@ -7821,7 +7850,7 @@
       <c r="AZ65"/>
     </row>
     <row r="66" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD66" s="171"/>
+      <c r="AD66" s="173"/>
       <c r="AU66"/>
       <c r="AV66"/>
       <c r="AW66"/>
@@ -7830,7 +7859,7 @@
       <c r="AZ66"/>
     </row>
     <row r="67" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD67" s="171"/>
+      <c r="AD67" s="173"/>
       <c r="AU67"/>
       <c r="AV67"/>
       <c r="AW67"/>
@@ -7839,7 +7868,7 @@
       <c r="AZ67"/>
     </row>
     <row r="68" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD68" s="171"/>
+      <c r="AD68" s="173"/>
       <c r="AU68"/>
       <c r="AV68"/>
       <c r="AW68"/>
@@ -7848,7 +7877,7 @@
       <c r="AZ68"/>
     </row>
     <row r="69" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD69" s="171"/>
+      <c r="AD69" s="173"/>
       <c r="AU69"/>
       <c r="AV69"/>
       <c r="AW69"/>
@@ -7857,7 +7886,7 @@
       <c r="AZ69"/>
     </row>
     <row r="70" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD70" s="171"/>
+      <c r="AD70" s="173"/>
       <c r="AU70"/>
       <c r="AV70"/>
       <c r="AW70"/>
@@ -7866,7 +7895,7 @@
       <c r="AZ70"/>
     </row>
     <row r="71" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD71" s="171"/>
+      <c r="AD71" s="173"/>
       <c r="AU71"/>
       <c r="AV71"/>
       <c r="AW71"/>
@@ -7875,7 +7904,7 @@
       <c r="AZ71"/>
     </row>
     <row r="72" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD72" s="171"/>
+      <c r="AD72" s="173"/>
       <c r="AU72"/>
       <c r="AV72"/>
       <c r="AW72"/>
@@ -7884,7 +7913,7 @@
       <c r="AZ72"/>
     </row>
     <row r="73" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD73" s="171"/>
+      <c r="AD73" s="173"/>
       <c r="AU73"/>
       <c r="AV73"/>
       <c r="AW73"/>
@@ -7893,7 +7922,7 @@
       <c r="AZ73"/>
     </row>
     <row r="74" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD74" s="171"/>
+      <c r="AD74" s="173"/>
       <c r="AU74"/>
       <c r="AV74"/>
       <c r="AW74"/>
@@ -7902,7 +7931,7 @@
       <c r="AZ74"/>
     </row>
     <row r="75" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD75" s="171"/>
+      <c r="AD75" s="173"/>
       <c r="AU75"/>
       <c r="AV75"/>
       <c r="AW75"/>
@@ -7911,7 +7940,7 @@
       <c r="AZ75"/>
     </row>
     <row r="76" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD76" s="171"/>
+      <c r="AD76" s="173"/>
       <c r="AU76"/>
       <c r="AV76"/>
       <c r="AW76"/>
@@ -7920,7 +7949,7 @@
       <c r="AZ76"/>
     </row>
     <row r="77" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD77" s="171"/>
+      <c r="AD77" s="173"/>
       <c r="AU77"/>
       <c r="AV77"/>
       <c r="AW77"/>
@@ -7929,7 +7958,7 @@
       <c r="AZ77"/>
     </row>
     <row r="78" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD78" s="171"/>
+      <c r="AD78" s="173"/>
       <c r="AU78"/>
       <c r="AV78"/>
       <c r="AW78"/>
@@ -7938,7 +7967,7 @@
       <c r="AZ78"/>
     </row>
     <row r="79" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD79" s="171"/>
+      <c r="AD79" s="173"/>
       <c r="AU79"/>
       <c r="AV79"/>
       <c r="AW79"/>
@@ -7947,7 +7976,7 @@
       <c r="AZ79"/>
     </row>
     <row r="80" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD80" s="171"/>
+      <c r="AD80" s="173"/>
       <c r="AU80"/>
       <c r="AV80"/>
       <c r="AW80"/>
@@ -7956,7 +7985,7 @@
       <c r="AZ80"/>
     </row>
     <row r="81" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD81" s="171"/>
+      <c r="AD81" s="173"/>
       <c r="AU81"/>
       <c r="AV81"/>
       <c r="AW81"/>
@@ -7965,7 +7994,7 @@
       <c r="AZ81"/>
     </row>
     <row r="82" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD82" s="171"/>
+      <c r="AD82" s="173"/>
       <c r="AU82"/>
       <c r="AV82"/>
       <c r="AW82"/>
@@ -7974,7 +8003,7 @@
       <c r="AZ82"/>
     </row>
     <row r="83" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD83" s="171"/>
+      <c r="AD83" s="173"/>
       <c r="AU83"/>
       <c r="AV83"/>
       <c r="AW83"/>
@@ -7983,7 +8012,7 @@
       <c r="AZ83"/>
     </row>
     <row r="84" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD84" s="171"/>
+      <c r="AD84" s="173"/>
       <c r="AU84"/>
       <c r="AV84"/>
       <c r="AW84"/>
@@ -7992,7 +8021,7 @@
       <c r="AZ84"/>
     </row>
     <row r="85" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD85" s="171"/>
+      <c r="AD85" s="173"/>
       <c r="AU85"/>
       <c r="AV85"/>
       <c r="AW85"/>
@@ -8001,7 +8030,7 @@
       <c r="AZ85"/>
     </row>
     <row r="86" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD86" s="171"/>
+      <c r="AD86" s="173"/>
       <c r="AU86"/>
       <c r="AV86"/>
       <c r="AW86"/>
@@ -8010,7 +8039,7 @@
       <c r="AZ86"/>
     </row>
     <row r="87" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD87" s="171"/>
+      <c r="AD87" s="173"/>
       <c r="AU87"/>
       <c r="AV87"/>
       <c r="AW87"/>
@@ -8019,7 +8048,7 @@
       <c r="AZ87"/>
     </row>
     <row r="88" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD88" s="171"/>
+      <c r="AD88" s="173"/>
       <c r="AU88"/>
       <c r="AV88"/>
       <c r="AW88"/>
@@ -8028,7 +8057,7 @@
       <c r="AZ88"/>
     </row>
     <row r="89" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD89" s="171"/>
+      <c r="AD89" s="173"/>
       <c r="AU89"/>
       <c r="AV89"/>
       <c r="AW89"/>
@@ -8037,7 +8066,7 @@
       <c r="AZ89"/>
     </row>
     <row r="90" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD90" s="171"/>
+      <c r="AD90" s="173"/>
       <c r="AU90"/>
       <c r="AV90"/>
       <c r="AW90"/>
@@ -8046,7 +8075,7 @@
       <c r="AZ90"/>
     </row>
     <row r="91" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD91" s="171"/>
+      <c r="AD91" s="173"/>
       <c r="AU91"/>
       <c r="AV91"/>
       <c r="AW91"/>
@@ -8055,7 +8084,7 @@
       <c r="AZ91"/>
     </row>
     <row r="92" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD92" s="171"/>
+      <c r="AD92" s="173"/>
       <c r="AU92"/>
       <c r="AV92"/>
       <c r="AW92"/>
@@ -8064,7 +8093,7 @@
       <c r="AZ92"/>
     </row>
     <row r="93" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD93" s="171"/>
+      <c r="AD93" s="173"/>
       <c r="AU93"/>
       <c r="AV93"/>
       <c r="AW93"/>
@@ -8073,7 +8102,7 @@
       <c r="AZ93"/>
     </row>
     <row r="94" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD94" s="171"/>
+      <c r="AD94" s="173"/>
       <c r="AU94"/>
       <c r="AV94"/>
       <c r="AW94"/>
@@ -8082,7 +8111,7 @@
       <c r="AZ94"/>
     </row>
     <row r="95" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD95" s="171"/>
+      <c r="AD95" s="173"/>
       <c r="AU95"/>
       <c r="AV95"/>
       <c r="AW95"/>
@@ -8091,7 +8120,7 @@
       <c r="AZ95"/>
     </row>
     <row r="96" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD96" s="171"/>
+      <c r="AD96" s="173"/>
       <c r="AU96"/>
       <c r="AV96"/>
       <c r="AW96"/>
@@ -8100,7 +8129,7 @@
       <c r="AZ96"/>
     </row>
     <row r="97" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD97" s="171"/>
+      <c r="AD97" s="173"/>
       <c r="AU97"/>
       <c r="AV97"/>
       <c r="AW97"/>
@@ -8109,7 +8138,7 @@
       <c r="AZ97"/>
     </row>
     <row r="98" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD98" s="171"/>
+      <c r="AD98" s="173"/>
       <c r="AU98"/>
       <c r="AV98"/>
       <c r="AW98"/>
@@ -8118,7 +8147,7 @@
       <c r="AZ98"/>
     </row>
     <row r="99" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD99" s="171"/>
+      <c r="AD99" s="173"/>
       <c r="AU99"/>
       <c r="AV99"/>
       <c r="AW99"/>
@@ -8127,7 +8156,7 @@
       <c r="AZ99"/>
     </row>
     <row r="100" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD100" s="171"/>
+      <c r="AD100" s="173"/>
       <c r="AU100"/>
       <c r="AV100"/>
       <c r="AW100"/>
@@ -8136,7 +8165,7 @@
       <c r="AZ100"/>
     </row>
     <row r="101" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD101" s="171"/>
+      <c r="AD101" s="173"/>
       <c r="AU101"/>
       <c r="AV101"/>
       <c r="AW101"/>
@@ -8145,7 +8174,7 @@
       <c r="AZ101"/>
     </row>
     <row r="102" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD102" s="171"/>
+      <c r="AD102" s="173"/>
       <c r="AU102"/>
       <c r="AV102"/>
       <c r="AW102"/>
@@ -8154,7 +8183,7 @@
       <c r="AZ102"/>
     </row>
     <row r="103" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD103" s="171"/>
+      <c r="AD103" s="173"/>
       <c r="AU103"/>
       <c r="AV103"/>
       <c r="AW103"/>
@@ -8163,7 +8192,7 @@
       <c r="AZ103"/>
     </row>
     <row r="104" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD104" s="171"/>
+      <c r="AD104" s="173"/>
       <c r="AU104"/>
       <c r="AV104"/>
       <c r="AW104"/>
@@ -8172,7 +8201,7 @@
       <c r="AZ104"/>
     </row>
     <row r="105" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD105" s="171"/>
+      <c r="AD105" s="173"/>
       <c r="AU105"/>
       <c r="AV105"/>
       <c r="AW105"/>
@@ -8181,7 +8210,7 @@
       <c r="AZ105"/>
     </row>
     <row r="106" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD106" s="171"/>
+      <c r="AD106" s="173"/>
       <c r="AU106"/>
       <c r="AV106"/>
       <c r="AW106"/>
@@ -8190,7 +8219,7 @@
       <c r="AZ106"/>
     </row>
     <row r="107" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD107" s="171"/>
+      <c r="AD107" s="173"/>
       <c r="AU107"/>
       <c r="AV107"/>
       <c r="AW107"/>
@@ -8199,7 +8228,7 @@
       <c r="AZ107"/>
     </row>
     <row r="108" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD108" s="171"/>
+      <c r="AD108" s="173"/>
       <c r="AU108"/>
       <c r="AV108"/>
       <c r="AW108"/>
@@ -8208,7 +8237,7 @@
       <c r="AZ108"/>
     </row>
     <row r="109" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD109" s="171"/>
+      <c r="AD109" s="173"/>
       <c r="AU109"/>
       <c r="AV109"/>
       <c r="AW109"/>
@@ -8217,7 +8246,7 @@
       <c r="AZ109"/>
     </row>
     <row r="110" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD110" s="171"/>
+      <c r="AD110" s="173"/>
       <c r="AU110"/>
       <c r="AV110"/>
       <c r="AW110"/>
@@ -8226,7 +8255,7 @@
       <c r="AZ110"/>
     </row>
     <row r="111" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD111" s="171"/>
+      <c r="AD111" s="173"/>
       <c r="AU111"/>
       <c r="AV111"/>
       <c r="AW111"/>
@@ -8235,7 +8264,7 @@
       <c r="AZ111"/>
     </row>
     <row r="112" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD112" s="171"/>
+      <c r="AD112" s="173"/>
       <c r="AU112"/>
       <c r="AV112"/>
       <c r="AW112"/>
@@ -8244,7 +8273,7 @@
       <c r="AZ112"/>
     </row>
     <row r="113" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD113" s="171"/>
+      <c r="AD113" s="173"/>
       <c r="AU113"/>
       <c r="AV113"/>
       <c r="AW113"/>
@@ -8253,7 +8282,7 @@
       <c r="AZ113"/>
     </row>
     <row r="114" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD114" s="171"/>
+      <c r="AD114" s="173"/>
       <c r="AU114"/>
       <c r="AV114"/>
       <c r="AW114"/>
@@ -8262,7 +8291,7 @@
       <c r="AZ114"/>
     </row>
     <row r="115" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD115" s="171"/>
+      <c r="AD115" s="173"/>
       <c r="AU115"/>
       <c r="AV115"/>
       <c r="AW115"/>
@@ -8271,7 +8300,7 @@
       <c r="AZ115"/>
     </row>
     <row r="116" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD116" s="171"/>
+      <c r="AD116" s="173"/>
       <c r="AU116"/>
       <c r="AV116"/>
       <c r="AW116"/>
@@ -8280,7 +8309,7 @@
       <c r="AZ116"/>
     </row>
     <row r="117" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD117" s="171"/>
+      <c r="AD117" s="173"/>
       <c r="AU117"/>
       <c r="AV117"/>
       <c r="AW117"/>
@@ -8289,7 +8318,7 @@
       <c r="AZ117"/>
     </row>
     <row r="118" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD118" s="171"/>
+      <c r="AD118" s="173"/>
       <c r="AU118"/>
       <c r="AV118"/>
       <c r="AW118"/>
@@ -8298,7 +8327,7 @@
       <c r="AZ118"/>
     </row>
     <row r="119" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD119" s="171"/>
+      <c r="AD119" s="173"/>
       <c r="AU119"/>
       <c r="AV119"/>
       <c r="AW119"/>
@@ -8307,7 +8336,7 @@
       <c r="AZ119"/>
     </row>
     <row r="120" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD120" s="171"/>
+      <c r="AD120" s="173"/>
       <c r="AU120"/>
       <c r="AV120"/>
       <c r="AW120"/>
@@ -8316,7 +8345,7 @@
       <c r="AZ120"/>
     </row>
     <row r="121" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD121" s="171"/>
+      <c r="AD121" s="173"/>
       <c r="AU121"/>
       <c r="AV121"/>
       <c r="AW121"/>
@@ -8325,7 +8354,7 @@
       <c r="AZ121"/>
     </row>
     <row r="122" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD122" s="171"/>
+      <c r="AD122" s="173"/>
       <c r="AU122"/>
       <c r="AV122"/>
       <c r="AW122"/>
@@ -8334,7 +8363,7 @@
       <c r="AZ122"/>
     </row>
     <row r="123" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD123" s="171"/>
+      <c r="AD123" s="173"/>
       <c r="AU123"/>
       <c r="AV123"/>
       <c r="AW123"/>
@@ -8343,7 +8372,7 @@
       <c r="AZ123"/>
     </row>
     <row r="124" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD124" s="171"/>
+      <c r="AD124" s="173"/>
       <c r="AU124"/>
       <c r="AV124"/>
       <c r="AW124"/>
@@ -8352,7 +8381,7 @@
       <c r="AZ124"/>
     </row>
     <row r="125" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD125" s="171"/>
+      <c r="AD125" s="173"/>
       <c r="AU125"/>
       <c r="AV125"/>
       <c r="AW125"/>
@@ -8361,7 +8390,7 @@
       <c r="AZ125"/>
     </row>
     <row r="126" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD126" s="171"/>
+      <c r="AD126" s="173"/>
       <c r="AU126"/>
       <c r="AV126"/>
       <c r="AW126"/>
@@ -8370,7 +8399,7 @@
       <c r="AZ126"/>
     </row>
     <row r="127" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD127" s="171"/>
+      <c r="AD127" s="173"/>
       <c r="AU127"/>
       <c r="AV127"/>
       <c r="AW127"/>
@@ -8379,7 +8408,7 @@
       <c r="AZ127"/>
     </row>
     <row r="128" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD128" s="171"/>
+      <c r="AD128" s="173"/>
       <c r="AU128"/>
       <c r="AV128"/>
       <c r="AW128"/>
@@ -8388,7 +8417,7 @@
       <c r="AZ128"/>
     </row>
     <row r="129" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD129" s="171"/>
+      <c r="AD129" s="173"/>
       <c r="AU129"/>
       <c r="AV129"/>
       <c r="AW129"/>
@@ -8397,7 +8426,7 @@
       <c r="AZ129"/>
     </row>
     <row r="130" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD130" s="171"/>
+      <c r="AD130" s="173"/>
       <c r="AU130"/>
       <c r="AV130"/>
       <c r="AW130"/>
@@ -8406,7 +8435,7 @@
       <c r="AZ130"/>
     </row>
     <row r="131" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD131" s="171"/>
+      <c r="AD131" s="173"/>
       <c r="AU131"/>
       <c r="AV131"/>
       <c r="AW131"/>
@@ -8415,7 +8444,7 @@
       <c r="AZ131"/>
     </row>
     <row r="132" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD132" s="171"/>
+      <c r="AD132" s="173"/>
       <c r="AU132"/>
       <c r="AV132"/>
       <c r="AW132"/>
@@ -8424,7 +8453,7 @@
       <c r="AZ132"/>
     </row>
     <row r="133" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD133" s="171"/>
+      <c r="AD133" s="173"/>
       <c r="AU133"/>
       <c r="AV133"/>
       <c r="AW133"/>
@@ -8433,7 +8462,7 @@
       <c r="AZ133"/>
     </row>
     <row r="134" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD134" s="171"/>
+      <c r="AD134" s="173"/>
       <c r="AU134"/>
       <c r="AV134"/>
       <c r="AW134"/>
@@ -8442,7 +8471,7 @@
       <c r="AZ134"/>
     </row>
     <row r="135" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD135" s="171"/>
+      <c r="AD135" s="173"/>
       <c r="AU135"/>
       <c r="AV135"/>
       <c r="AW135"/>
@@ -8451,7 +8480,7 @@
       <c r="AZ135"/>
     </row>
     <row r="136" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD136" s="171"/>
+      <c r="AD136" s="173"/>
       <c r="AU136"/>
       <c r="AV136"/>
       <c r="AW136"/>
@@ -8460,7 +8489,7 @@
       <c r="AZ136"/>
     </row>
     <row r="137" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD137" s="171"/>
+      <c r="AD137" s="173"/>
       <c r="AU137"/>
       <c r="AV137"/>
       <c r="AW137"/>
@@ -8469,7 +8498,7 @@
       <c r="AZ137"/>
     </row>
     <row r="138" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD138" s="171"/>
+      <c r="AD138" s="173"/>
       <c r="AU138"/>
       <c r="AV138"/>
       <c r="AW138"/>
@@ -8478,7 +8507,7 @@
       <c r="AZ138"/>
     </row>
     <row r="139" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD139" s="171"/>
+      <c r="AD139" s="173"/>
       <c r="AU139"/>
       <c r="AV139"/>
       <c r="AW139"/>
@@ -8487,7 +8516,7 @@
       <c r="AZ139"/>
     </row>
     <row r="140" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD140" s="171"/>
+      <c r="AD140" s="173"/>
       <c r="AU140"/>
       <c r="AV140"/>
       <c r="AW140"/>
@@ -8496,7 +8525,7 @@
       <c r="AZ140"/>
     </row>
     <row r="141" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD141" s="171"/>
+      <c r="AD141" s="173"/>
       <c r="AU141"/>
       <c r="AV141"/>
       <c r="AW141"/>
@@ -8505,7 +8534,7 @@
       <c r="AZ141"/>
     </row>
     <row r="142" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD142" s="171"/>
+      <c r="AD142" s="173"/>
       <c r="AU142"/>
       <c r="AV142"/>
       <c r="AW142"/>
@@ -8514,7 +8543,7 @@
       <c r="AZ142"/>
     </row>
     <row r="143" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD143" s="171"/>
+      <c r="AD143" s="173"/>
       <c r="AU143"/>
       <c r="AV143"/>
       <c r="AW143"/>
@@ -8523,7 +8552,7 @@
       <c r="AZ143"/>
     </row>
     <row r="144" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD144" s="171"/>
+      <c r="AD144" s="173"/>
       <c r="AU144"/>
       <c r="AV144"/>
       <c r="AW144"/>
@@ -8532,7 +8561,7 @@
       <c r="AZ144"/>
     </row>
     <row r="145" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD145" s="171"/>
+      <c r="AD145" s="173"/>
       <c r="AU145"/>
       <c r="AV145"/>
       <c r="AW145"/>
@@ -8541,7 +8570,7 @@
       <c r="AZ145"/>
     </row>
     <row r="146" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD146" s="171"/>
+      <c r="AD146" s="173"/>
       <c r="AU146"/>
       <c r="AV146"/>
       <c r="AW146"/>
@@ -8550,7 +8579,7 @@
       <c r="AZ146"/>
     </row>
     <row r="147" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD147" s="171"/>
+      <c r="AD147" s="173"/>
       <c r="AU147"/>
       <c r="AV147"/>
       <c r="AW147"/>
@@ -8559,7 +8588,7 @@
       <c r="AZ147"/>
     </row>
     <row r="148" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD148" s="171"/>
+      <c r="AD148" s="173"/>
       <c r="AU148"/>
       <c r="AV148"/>
       <c r="AW148"/>
@@ -8568,7 +8597,7 @@
       <c r="AZ148"/>
     </row>
     <row r="149" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD149" s="171"/>
+      <c r="AD149" s="173"/>
       <c r="AU149"/>
       <c r="AV149"/>
       <c r="AW149"/>
@@ -8577,7 +8606,7 @@
       <c r="AZ149"/>
     </row>
     <row r="150" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD150" s="171"/>
+      <c r="AD150" s="173"/>
       <c r="AU150"/>
       <c r="AV150"/>
       <c r="AW150"/>
@@ -8586,7 +8615,7 @@
       <c r="AZ150"/>
     </row>
     <row r="151" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD151" s="171"/>
+      <c r="AD151" s="173"/>
       <c r="AU151"/>
       <c r="AV151"/>
       <c r="AW151"/>
@@ -8595,7 +8624,7 @@
       <c r="AZ151"/>
     </row>
     <row r="152" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD152" s="171"/>
+      <c r="AD152" s="173"/>
       <c r="AU152"/>
       <c r="AV152"/>
       <c r="AW152"/>
@@ -8604,7 +8633,7 @@
       <c r="AZ152"/>
     </row>
     <row r="153" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD153" s="171"/>
+      <c r="AD153" s="173"/>
       <c r="AU153"/>
       <c r="AV153"/>
       <c r="AW153"/>
@@ -8613,7 +8642,7 @@
       <c r="AZ153"/>
     </row>
     <row r="154" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD154" s="171"/>
+      <c r="AD154" s="173"/>
       <c r="AU154"/>
       <c r="AV154"/>
       <c r="AW154"/>
@@ -8622,7 +8651,7 @@
       <c r="AZ154"/>
     </row>
     <row r="155" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD155" s="171"/>
+      <c r="AD155" s="173"/>
       <c r="AU155"/>
       <c r="AV155"/>
       <c r="AW155"/>
@@ -8631,7 +8660,7 @@
       <c r="AZ155"/>
     </row>
     <row r="156" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD156" s="171"/>
+      <c r="AD156" s="173"/>
       <c r="AU156"/>
       <c r="AV156"/>
       <c r="AW156"/>
@@ -8640,7 +8669,7 @@
       <c r="AZ156"/>
     </row>
     <row r="157" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD157" s="171"/>
+      <c r="AD157" s="173"/>
       <c r="AU157"/>
       <c r="AV157"/>
       <c r="AW157"/>
@@ -8649,7 +8678,7 @@
       <c r="AZ157"/>
     </row>
     <row r="158" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD158" s="171"/>
+      <c r="AD158" s="173"/>
       <c r="AU158"/>
       <c r="AV158"/>
       <c r="AW158"/>
@@ -8658,7 +8687,7 @@
       <c r="AZ158"/>
     </row>
     <row r="159" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD159" s="171"/>
+      <c r="AD159" s="173"/>
       <c r="AU159"/>
       <c r="AV159"/>
       <c r="AW159"/>
@@ -8667,7 +8696,7 @@
       <c r="AZ159"/>
     </row>
     <row r="160" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD160" s="171"/>
+      <c r="AD160" s="173"/>
       <c r="AU160"/>
       <c r="AV160"/>
       <c r="AW160"/>
@@ -8676,7 +8705,7 @@
       <c r="AZ160"/>
     </row>
     <row r="161" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD161" s="171"/>
+      <c r="AD161" s="173"/>
       <c r="AU161"/>
       <c r="AV161"/>
       <c r="AW161"/>
@@ -8685,7 +8714,7 @@
       <c r="AZ161"/>
     </row>
     <row r="162" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD162" s="171"/>
+      <c r="AD162" s="173"/>
       <c r="AU162"/>
       <c r="AV162"/>
       <c r="AW162"/>
@@ -8694,7 +8723,7 @@
       <c r="AZ162"/>
     </row>
     <row r="163" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD163" s="171"/>
+      <c r="AD163" s="173"/>
       <c r="AU163"/>
       <c r="AV163"/>
       <c r="AW163"/>
@@ -8703,7 +8732,7 @@
       <c r="AZ163"/>
     </row>
     <row r="164" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD164" s="171"/>
+      <c r="AD164" s="173"/>
       <c r="AU164"/>
       <c r="AV164"/>
       <c r="AW164"/>
@@ -8712,7 +8741,7 @@
       <c r="AZ164"/>
     </row>
     <row r="165" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD165" s="171"/>
+      <c r="AD165" s="173"/>
       <c r="AU165"/>
       <c r="AV165"/>
       <c r="AW165"/>
@@ -8721,7 +8750,7 @@
       <c r="AZ165"/>
     </row>
     <row r="166" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD166" s="171"/>
+      <c r="AD166" s="173"/>
       <c r="AU166"/>
       <c r="AV166"/>
       <c r="AW166"/>
@@ -8730,7 +8759,7 @@
       <c r="AZ166"/>
     </row>
     <row r="167" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD167" s="171"/>
+      <c r="AD167" s="173"/>
       <c r="AU167"/>
       <c r="AV167"/>
       <c r="AW167"/>
@@ -8739,7 +8768,7 @@
       <c r="AZ167"/>
     </row>
     <row r="168" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD168" s="171"/>
+      <c r="AD168" s="173"/>
       <c r="AU168"/>
       <c r="AV168"/>
       <c r="AW168"/>
@@ -8748,7 +8777,7 @@
       <c r="AZ168"/>
     </row>
     <row r="169" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD169" s="171"/>
+      <c r="AD169" s="173"/>
       <c r="AU169"/>
       <c r="AV169"/>
       <c r="AW169"/>
@@ -8757,7 +8786,7 @@
       <c r="AZ169"/>
     </row>
     <row r="170" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD170" s="171"/>
+      <c r="AD170" s="173"/>
       <c r="AU170"/>
       <c r="AV170"/>
       <c r="AW170"/>
@@ -8766,7 +8795,7 @@
       <c r="AZ170"/>
     </row>
     <row r="171" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD171" s="171"/>
+      <c r="AD171" s="173"/>
       <c r="AU171"/>
       <c r="AV171"/>
       <c r="AW171"/>
@@ -8775,7 +8804,7 @@
       <c r="AZ171"/>
     </row>
     <row r="172" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD172" s="171"/>
+      <c r="AD172" s="173"/>
       <c r="AU172"/>
       <c r="AV172"/>
       <c r="AW172"/>
@@ -8784,7 +8813,7 @@
       <c r="AZ172"/>
     </row>
     <row r="173" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD173" s="171"/>
+      <c r="AD173" s="173"/>
       <c r="AU173"/>
       <c r="AV173"/>
       <c r="AW173"/>
@@ -8793,7 +8822,7 @@
       <c r="AZ173"/>
     </row>
     <row r="174" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD174" s="171"/>
+      <c r="AD174" s="173"/>
       <c r="AU174"/>
       <c r="AV174"/>
       <c r="AW174"/>
@@ -8802,7 +8831,7 @@
       <c r="AZ174"/>
     </row>
     <row r="175" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD175" s="171"/>
+      <c r="AD175" s="173"/>
       <c r="AU175"/>
       <c r="AV175"/>
       <c r="AW175"/>
@@ -8811,7 +8840,7 @@
       <c r="AZ175"/>
     </row>
     <row r="176" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD176" s="171"/>
+      <c r="AD176" s="173"/>
       <c r="AU176"/>
       <c r="AV176"/>
       <c r="AW176"/>
@@ -8820,7 +8849,7 @@
       <c r="AZ176"/>
     </row>
     <row r="177" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD177" s="171"/>
+      <c r="AD177" s="173"/>
       <c r="AU177"/>
       <c r="AV177"/>
       <c r="AW177"/>
@@ -8829,7 +8858,7 @@
       <c r="AZ177"/>
     </row>
     <row r="178" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD178" s="171"/>
+      <c r="AD178" s="173"/>
       <c r="AU178"/>
       <c r="AV178"/>
       <c r="AW178"/>
@@ -8838,7 +8867,7 @@
       <c r="AZ178"/>
     </row>
     <row r="179" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD179" s="171"/>
+      <c r="AD179" s="173"/>
       <c r="AU179"/>
       <c r="AV179"/>
       <c r="AW179"/>
@@ -8847,7 +8876,7 @@
       <c r="AZ179"/>
     </row>
     <row r="180" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD180" s="171"/>
+      <c r="AD180" s="173"/>
       <c r="AU180"/>
       <c r="AV180"/>
       <c r="AW180"/>
@@ -8856,7 +8885,7 @@
       <c r="AZ180"/>
     </row>
     <row r="181" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD181" s="171"/>
+      <c r="AD181" s="173"/>
       <c r="AU181"/>
       <c r="AV181"/>
       <c r="AW181"/>
@@ -8865,7 +8894,7 @@
       <c r="AZ181"/>
     </row>
     <row r="182" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD182" s="171"/>
+      <c r="AD182" s="173"/>
       <c r="AU182"/>
       <c r="AV182"/>
       <c r="AW182"/>
@@ -8874,7 +8903,7 @@
       <c r="AZ182"/>
     </row>
     <row r="183" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD183" s="171"/>
+      <c r="AD183" s="173"/>
       <c r="AU183"/>
       <c r="AV183"/>
       <c r="AW183"/>
@@ -8883,7 +8912,7 @@
       <c r="AZ183"/>
     </row>
     <row r="184" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD184" s="171"/>
+      <c r="AD184" s="173"/>
       <c r="AU184"/>
       <c r="AV184"/>
       <c r="AW184"/>
@@ -8892,7 +8921,7 @@
       <c r="AZ184"/>
     </row>
     <row r="185" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD185" s="171"/>
+      <c r="AD185" s="173"/>
       <c r="AU185"/>
       <c r="AV185"/>
       <c r="AW185"/>
@@ -8901,7 +8930,7 @@
       <c r="AZ185"/>
     </row>
     <row r="186" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD186" s="171"/>
+      <c r="AD186" s="173"/>
       <c r="AU186"/>
       <c r="AV186"/>
       <c r="AW186"/>
@@ -8910,7 +8939,7 @@
       <c r="AZ186"/>
     </row>
     <row r="187" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD187" s="171"/>
+      <c r="AD187" s="173"/>
       <c r="AU187"/>
       <c r="AV187"/>
       <c r="AW187"/>
@@ -8919,7 +8948,7 @@
       <c r="AZ187"/>
     </row>
     <row r="188" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD188" s="171"/>
+      <c r="AD188" s="173"/>
       <c r="AU188"/>
       <c r="AV188"/>
       <c r="AW188"/>
@@ -8928,7 +8957,7 @@
       <c r="AZ188"/>
     </row>
     <row r="189" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD189" s="171"/>
+      <c r="AD189" s="173"/>
       <c r="AU189"/>
       <c r="AV189"/>
       <c r="AW189"/>
@@ -8937,7 +8966,7 @@
       <c r="AZ189"/>
     </row>
     <row r="190" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD190" s="171"/>
+      <c r="AD190" s="173"/>
       <c r="AU190"/>
       <c r="AV190"/>
       <c r="AW190"/>
@@ -8946,7 +8975,7 @@
       <c r="AZ190"/>
     </row>
     <row r="191" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD191" s="171"/>
+      <c r="AD191" s="173"/>
       <c r="AU191"/>
       <c r="AV191"/>
       <c r="AW191"/>
@@ -8955,7 +8984,7 @@
       <c r="AZ191"/>
     </row>
     <row r="192" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD192" s="171"/>
+      <c r="AD192" s="173"/>
       <c r="AU192"/>
       <c r="AV192"/>
       <c r="AW192"/>
@@ -8964,7 +8993,7 @@
       <c r="AZ192"/>
     </row>
     <row r="193" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD193" s="171"/>
+      <c r="AD193" s="173"/>
       <c r="AU193"/>
       <c r="AV193"/>
       <c r="AW193"/>
@@ -8973,7 +9002,7 @@
       <c r="AZ193"/>
     </row>
     <row r="194" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD194" s="171"/>
+      <c r="AD194" s="173"/>
       <c r="AU194"/>
       <c r="AV194"/>
       <c r="AW194"/>
@@ -8982,7 +9011,7 @@
       <c r="AZ194"/>
     </row>
     <row r="195" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD195" s="171"/>
+      <c r="AD195" s="173"/>
       <c r="AU195"/>
       <c r="AV195"/>
       <c r="AW195"/>
@@ -8991,7 +9020,7 @@
       <c r="AZ195"/>
     </row>
     <row r="196" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD196" s="171"/>
+      <c r="AD196" s="173"/>
       <c r="AU196"/>
       <c r="AV196"/>
       <c r="AW196"/>
@@ -9000,7 +9029,7 @@
       <c r="AZ196"/>
     </row>
     <row r="197" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD197" s="171"/>
+      <c r="AD197" s="173"/>
       <c r="AU197"/>
       <c r="AV197"/>
       <c r="AW197"/>
@@ -9009,7 +9038,7 @@
       <c r="AZ197"/>
     </row>
     <row r="198" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD198" s="171"/>
+      <c r="AD198" s="173"/>
       <c r="AU198"/>
       <c r="AV198"/>
       <c r="AW198"/>
@@ -9018,7 +9047,7 @@
       <c r="AZ198"/>
     </row>
     <row r="199" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD199" s="171"/>
+      <c r="AD199" s="173"/>
       <c r="AU199"/>
       <c r="AV199"/>
       <c r="AW199"/>
@@ -9027,7 +9056,7 @@
       <c r="AZ199"/>
     </row>
     <row r="200" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD200" s="171"/>
+      <c r="AD200" s="173"/>
       <c r="AU200"/>
       <c r="AV200"/>
       <c r="AW200"/>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -3257,9 +3257,6 @@
     <xf numFmtId="0" fontId="36" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3624,6 +3621,9 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1662">
@@ -5611,14 +5611,14 @@
     <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" style="148" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="147" customWidth="1"/>
     <col min="10" max="11" width="20.6640625" style="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="16.1640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.1640625" style="97" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" style="97" customWidth="1"/>
+    <col min="16" max="16" width="11.1640625" style="96" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" style="96" customWidth="1"/>
     <col min="18" max="18" width="16.6640625" style="8" customWidth="1"/>
     <col min="19" max="19" width="15.6640625" style="8" customWidth="1"/>
     <col min="20" max="20" width="16.1640625" style="8" customWidth="1"/>
@@ -5635,23 +5635,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="167" t="s">
+      <c r="B1" s="166" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="168"/>
-      <c r="I1" s="168"/>
-      <c r="J1" s="168"/>
-      <c r="K1" s="168"/>
-      <c r="L1" s="168"/>
-      <c r="M1" s="168"/>
-      <c r="N1" s="168"/>
-      <c r="O1" s="169"/>
-      <c r="AD1" s="173"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="167"/>
+      <c r="N1" s="167"/>
+      <c r="O1" s="168"/>
+      <c r="AD1" s="172"/>
       <c r="AU1"/>
       <c r="AV1"/>
       <c r="AW1"/>
@@ -5668,14 +5668,14 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="141"/>
+      <c r="I2" s="140"/>
       <c r="J2" s="6"/>
-      <c r="V2" s="134"/>
-      <c r="W2" s="134"/>
-      <c r="X2" s="134"/>
-      <c r="Y2" s="134"/>
-      <c r="Z2" s="134"/>
-      <c r="AD2" s="173"/>
+      <c r="V2" s="133"/>
+      <c r="W2" s="133"/>
+      <c r="X2" s="133"/>
+      <c r="Y2" s="133"/>
+      <c r="Z2" s="133"/>
+      <c r="AD2" s="172"/>
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
@@ -5694,7 +5694,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="141"/>
+      <c r="I3" s="140"/>
       <c r="J3" s="5"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5703,12 +5703,12 @@
       <c r="O3" s="5"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
-      <c r="V3" s="134"/>
-      <c r="W3" s="134"/>
-      <c r="X3" s="134"/>
-      <c r="Y3" s="134"/>
-      <c r="Z3" s="134"/>
-      <c r="AD3" s="173"/>
+      <c r="V3" s="133"/>
+      <c r="W3" s="133"/>
+      <c r="X3" s="133"/>
+      <c r="Y3" s="133"/>
+      <c r="Z3" s="133"/>
+      <c r="AD3" s="172"/>
       <c r="AU3"/>
       <c r="AV3"/>
       <c r="AW3"/>
@@ -5727,25 +5727,25 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="141"/>
+      <c r="I4" s="140"/>
       <c r="J4" s="5"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="170"/>
-      <c r="Q4" s="171"/>
-      <c r="R4" s="171"/>
-      <c r="S4" s="171"/>
-      <c r="T4" s="171"/>
-      <c r="U4" s="172"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="134"/>
-      <c r="X4" s="134"/>
-      <c r="Y4" s="134"/>
-      <c r="Z4" s="134"/>
-      <c r="AD4" s="173"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="170"/>
+      <c r="R4" s="170"/>
+      <c r="S4" s="170"/>
+      <c r="T4" s="170"/>
+      <c r="U4" s="171"/>
+      <c r="V4" s="133"/>
+      <c r="W4" s="133"/>
+      <c r="X4" s="133"/>
+      <c r="Y4" s="133"/>
+      <c r="Z4" s="133"/>
+      <c r="AD4" s="172"/>
       <c r="AU4"/>
       <c r="AV4"/>
       <c r="AW4"/>
@@ -5765,7 +5765,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="142"/>
+      <c r="I5" s="141"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -5778,12 +5778,12 @@
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="134"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AD5" s="173"/>
+      <c r="V5" s="133"/>
+      <c r="W5" s="133"/>
+      <c r="X5" s="133"/>
+      <c r="Y5" s="133"/>
+      <c r="Z5" s="133"/>
+      <c r="AD5" s="172"/>
       <c r="AU5"/>
       <c r="AV5"/>
       <c r="AW5"/>
@@ -5793,28 +5793,28 @@
     </row>
     <row r="6" spans="1:52" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="137"/>
+      <c r="C6" s="136"/>
       <c r="D6" s="18"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
-      <c r="I6" s="143"/>
+      <c r="I6" s="142"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
-      <c r="V6" s="135"/>
-      <c r="W6" s="135"/>
-      <c r="X6" s="135"/>
-      <c r="Y6" s="135"/>
-      <c r="Z6" s="135"/>
-      <c r="AD6" s="173"/>
+      <c r="V6" s="134"/>
+      <c r="W6" s="134"/>
+      <c r="X6" s="134"/>
+      <c r="Y6" s="134"/>
+      <c r="Z6" s="134"/>
+      <c r="AD6" s="172"/>
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6"/>
@@ -5824,36 +5824,36 @@
     </row>
     <row r="7" spans="1:52" ht="15" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="140" t="s">
+      <c r="B7" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="144"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="132" t="s">
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="132"/>
-      <c r="M7" s="132"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="132"/>
-      <c r="R7" s="132"/>
-      <c r="S7" s="132"/>
-      <c r="T7" s="132"/>
-      <c r="U7" s="132"/>
-      <c r="V7" s="132"/>
-      <c r="W7" s="132"/>
-      <c r="X7" s="132"/>
-      <c r="Y7" s="132"/>
-      <c r="Z7" s="133"/>
-      <c r="AD7" s="173"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="131"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="131"/>
+      <c r="V7" s="131"/>
+      <c r="W7" s="131"/>
+      <c r="X7" s="131"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="132"/>
+      <c r="AD7" s="172"/>
       <c r="AU7"/>
       <c r="AV7"/>
       <c r="AW7"/>
@@ -5884,7 +5884,7 @@
       <c r="H8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="145" t="s">
+      <c r="I8" s="144" t="s">
         <v>26</v>
       </c>
       <c r="J8" s="26" t="s">
@@ -5929,17 +5929,17 @@
       <c r="W8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="X8" s="138" t="s">
+      <c r="X8" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="Y8" s="139"/>
+      <c r="Y8" s="138"/>
       <c r="Z8" s="25" t="s">
         <v>22</v>
       </c>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
       <c r="AC8" s="30"/>
-      <c r="AD8" s="173"/>
+      <c r="AD8" s="172"/>
       <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8"/>
@@ -5949,22 +5949,22 @@
     </row>
     <row r="9" spans="1:52" s="40" customFormat="1" ht="19.5" customHeight="1">
       <c r="A9" s="31"/>
-      <c r="B9" s="136">
+      <c r="B9" s="135">
         <v>1</v>
       </c>
-      <c r="C9" s="136"/>
+      <c r="C9" s="135"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125">
+      <c r="E9" s="124"/>
+      <c r="F9" s="124">
         <v>2</v>
       </c>
-      <c r="G9" s="125">
+      <c r="G9" s="124">
         <v>3</v>
       </c>
       <c r="H9" s="33">
         <v>4</v>
       </c>
-      <c r="I9" s="146">
+      <c r="I9" s="145">
         <v>5</v>
       </c>
       <c r="J9" s="34"/>
@@ -6013,7 +6013,7 @@
       <c r="AA9" s="38"/>
       <c r="AB9" s="38"/>
       <c r="AC9" s="39"/>
-      <c r="AD9" s="173"/>
+      <c r="AD9" s="172"/>
       <c r="AU9"/>
       <c r="AV9"/>
       <c r="AW9"/>
@@ -6021,7 +6021,7 @@
       <c r="AY9"/>
       <c r="AZ9"/>
     </row>
-    <row r="10" spans="1:52" s="61" customFormat="1" ht="56.25" customHeight="1">
+    <row r="10" spans="1:52" s="60" customFormat="1" ht="56.25" customHeight="1">
       <c r="A10" s="41"/>
       <c r="B10" s="42">
         <v>1</v>
@@ -6029,87 +6029,87 @@
       <c r="C10" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="46" t="s">
+      <c r="D10" s="173"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="161" t="s">
+      <c r="G10" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147" t="e">
+      <c r="H10" s="146"/>
+      <c r="I10" s="146" t="e">
         <f>G10*H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="48" t="e">
+      <c r="J10" s="47" t="e">
         <f>I10*14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="K10" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="50" t="str">
+      <c r="L10" s="49" t="str">
         <f>G10</f>
         <v>{{ quantity }}</v>
       </c>
-      <c r="M10" s="51" t="s">
+      <c r="M10" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="N10" s="52" t="e">
+      <c r="N10" s="51" t="e">
         <f>M10/P10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O10" s="53" t="e">
+      <c r="O10" s="52" t="e">
         <f>M10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P10" s="162" t="s">
+      <c r="P10" s="161" t="s">
         <v>81</v>
       </c>
-      <c r="Q10" s="54" t="e">
+      <c r="Q10" s="53" t="e">
         <f>P10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R10" s="55" t="e">
+      <c r="R10" s="54" t="e">
         <f>$U$14/$Q$11*P10/12*0.3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S10" s="55" t="e">
+      <c r="S10" s="54" t="e">
         <f>R10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="T10" s="55" t="e">
+      <c r="T10" s="54" t="e">
         <f>$U$14/$Q$11*P10/12*0.7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U10" s="55" t="e">
+      <c r="U10" s="54" t="e">
         <f>T10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V10" s="56" t="e">
+      <c r="V10" s="55" t="e">
         <f>H10/P10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W10" s="52" t="e">
+      <c r="W10" s="51" t="e">
         <f>N10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X10" s="57" t="s">
+      <c r="X10" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="Y10" s="58" t="e">
+      <c r="Y10" s="57" t="e">
         <f>L10*(M10+R10)*X10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z10" s="59" t="e">
+      <c r="Z10" s="58" t="e">
         <f>(I10-O10-S10-U10-Y10-AA10-AC10-AB10)/I10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA10" s="60"/>
-      <c r="AB10" s="60"/>
-      <c r="AC10" s="60"/>
-      <c r="AD10" s="173"/>
+      <c r="AA10" s="59"/>
+      <c r="AB10" s="59"/>
+      <c r="AC10" s="59"/>
+      <c r="AD10" s="172"/>
       <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
@@ -6117,60 +6117,60 @@
       <c r="AY10"/>
       <c r="AZ10"/>
     </row>
-    <row r="11" spans="1:52" s="61" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:52" s="60" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="41"/>
-      <c r="B11" s="62"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="147" t="e">
+      <c r="B11" s="61"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="146" t="e">
         <f>SUM(I10:I10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="66"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="47" t="e">
+      <c r="J11" s="65"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="46" t="e">
         <f>SUM(O10:O10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="72" t="e">
+      <c r="P11" s="70"/>
+      <c r="Q11" s="71" t="e">
         <f>SUM(Q10:Q10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R11" s="73"/>
-      <c r="S11" s="47" t="e">
+      <c r="R11" s="72"/>
+      <c r="S11" s="46" t="e">
         <f>SUM(S10:S10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="T11" s="74"/>
-      <c r="U11" s="74" t="e">
+      <c r="T11" s="73"/>
+      <c r="U11" s="73" t="e">
         <f>SUM(U10:U10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V11" s="75"/>
-      <c r="W11" s="76"/>
-      <c r="X11" s="77" t="e">
+      <c r="V11" s="74"/>
+      <c r="W11" s="75"/>
+      <c r="X11" s="76" t="e">
         <f>AVERAGE(X10:X10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y11" s="47" t="e">
+      <c r="Y11" s="46" t="e">
         <f>SUM(Y10:Y10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z11" s="78" t="e">
+      <c r="Z11" s="77" t="e">
         <f>(I11-O11-S11-U11-Y11-AA11-AC11-AB11)/I11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA11" s="60"/>
-      <c r="AB11" s="60"/>
-      <c r="AC11" s="60"/>
-      <c r="AD11" s="173"/>
+      <c r="AA11" s="59"/>
+      <c r="AB11" s="59"/>
+      <c r="AC11" s="59"/>
+      <c r="AD11" s="172"/>
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
@@ -6178,40 +6178,40 @@
       <c r="AY11"/>
       <c r="AZ11"/>
     </row>
-    <row r="12" spans="1:52" s="61" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="1:52" s="60" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="41"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="65" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="147" t="e">
+      <c r="I12" s="146" t="e">
         <f>I11*1.2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="82"/>
+      <c r="J12" s="81"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="85"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="87"/>
-      <c r="R12" s="88"/>
-      <c r="S12" s="89"/>
-      <c r="T12" s="90"/>
-      <c r="U12" s="91"/>
-      <c r="V12" s="75"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="92"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="94"/>
-      <c r="AC12" s="95"/>
-      <c r="AD12" s="173"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="84"/>
+      <c r="P12" s="85"/>
+      <c r="Q12" s="86"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="89"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="75"/>
+      <c r="X12" s="91"/>
+      <c r="Y12" s="92"/>
+      <c r="Z12" s="93"/>
+      <c r="AC12" s="94"/>
+      <c r="AD12" s="172"/>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
@@ -6220,21 +6220,21 @@
       <c r="AZ12"/>
     </row>
     <row r="13" spans="1:52" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A13" s="128" t="s">
+      <c r="A13" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="126" t="s">
+      <c r="B13" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="127"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="148"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="147"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13"/>
@@ -6247,7 +6247,7 @@
       <c r="Y13"/>
       <c r="Z13"/>
       <c r="AA13"/>
-      <c r="AD13" s="173"/>
+      <c r="AD13" s="172"/>
       <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13"/>
@@ -6256,33 +6256,33 @@
       <c r="AZ13"/>
     </row>
     <row r="14" spans="1:52" ht="14.1" customHeight="1">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="149"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="148"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="97"/>
-      <c r="L14" s="97"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-      <c r="O14" s="108"/>
+      <c r="O14" s="107"/>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14"/>
-      <c r="T14" s="164" t="s">
+      <c r="T14" s="163" t="s">
         <v>83</v>
       </c>
-      <c r="U14" s="163" t="s">
+      <c r="U14" s="162" t="s">
         <v>82</v>
       </c>
       <c r="V14"/>
@@ -6291,7 +6291,7 @@
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
-      <c r="AD14" s="173"/>
+      <c r="AD14" s="172"/>
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
@@ -6300,29 +6300,29 @@
       <c r="AZ14"/>
     </row>
     <row r="15" spans="1:52" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="150">
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="149">
         <v>150</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="97">
+      <c r="K15" s="96">
         <f>I15+I16</f>
         <v>180</v>
       </c>
-      <c r="L15" s="97"/>
+      <c r="L15" s="96"/>
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15"/>
@@ -6335,7 +6335,7 @@
       <c r="Y15"/>
       <c r="Z15"/>
       <c r="AA15"/>
-      <c r="AD15" s="173"/>
+      <c r="AD15" s="172"/>
       <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
@@ -6344,28 +6344,28 @@
       <c r="AZ15"/>
     </row>
     <row r="16" spans="1:52" s="40" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="106" t="s">
+      <c r="B16" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="151">
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="150">
         <v>30</v>
       </c>
-      <c r="J16" s="109"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="97"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
       <c r="N16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O16" s="110" t="e">
+      <c r="O16" s="109" t="e">
         <f>I11*14</f>
         <v>#VALUE!</v>
       </c>
@@ -6381,7 +6381,7 @@
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
-      <c r="AD16" s="173"/>
+      <c r="AD16" s="172"/>
       <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
@@ -6390,26 +6390,26 @@
       <c r="AZ16"/>
     </row>
     <row r="17" spans="1:52" ht="14.1" customHeight="1">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="116"/>
-      <c r="I17" s="152"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="97"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="151"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
       <c r="N17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O17" s="110" t="e">
+      <c r="O17" s="109" t="e">
         <f>I12*14</f>
         <v>#VALUE!</v>
       </c>
@@ -6425,7 +6425,7 @@
       <c r="Y17"/>
       <c r="Z17"/>
       <c r="AA17"/>
-      <c r="AD17" s="173"/>
+      <c r="AD17" s="172"/>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
@@ -6434,22 +6434,22 @@
       <c r="AZ17"/>
     </row>
     <row r="18" spans="1:52" ht="14.1" customHeight="1">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="114" t="s">
+      <c r="B18" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="152"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18"/>
@@ -6462,7 +6462,7 @@
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
-      <c r="AD18" s="173"/>
+      <c r="AD18" s="172"/>
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18"/>
@@ -6471,25 +6471,25 @@
       <c r="AZ18"/>
     </row>
     <row r="19" spans="1:52" ht="18.75" customHeight="1">
-      <c r="A19" s="96" t="s">
+      <c r="A19" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="154" t="e">
+      <c r="C19" s="114"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="153" t="e">
         <f>I11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="113"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="97"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
       <c r="M19" s="8"/>
       <c r="P19"/>
       <c r="Q19"/>
@@ -6503,7 +6503,7 @@
       <c r="Y19"/>
       <c r="Z19"/>
       <c r="AA19"/>
-      <c r="AD19" s="173"/>
+      <c r="AD19" s="172"/>
       <c r="AU19"/>
       <c r="AV19"/>
       <c r="AW19"/>
@@ -6512,17 +6512,17 @@
       <c r="AZ19"/>
     </row>
     <row r="20" spans="1:52" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="114"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="154"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="153"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
@@ -6541,7 +6541,7 @@
       <c r="Y20"/>
       <c r="Z20"/>
       <c r="AA20"/>
-      <c r="AD20" s="173"/>
+      <c r="AD20" s="172"/>
       <c r="AU20"/>
       <c r="AV20"/>
       <c r="AW20"/>
@@ -6550,17 +6550,17 @@
       <c r="AZ20"/>
     </row>
     <row r="21" spans="1:52" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="114"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="154"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="153"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
@@ -6579,7 +6579,7 @@
       <c r="Y21"/>
       <c r="Z21"/>
       <c r="AA21"/>
-      <c r="AD21" s="173"/>
+      <c r="AD21" s="172"/>
       <c r="AU21"/>
       <c r="AV21"/>
       <c r="AW21"/>
@@ -6588,24 +6588,24 @@
       <c r="AZ21"/>
     </row>
     <row r="22" spans="1:52" s="1" customFormat="1" ht="11.1" customHeight="1">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="154"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="114"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="153"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
-      <c r="M22" s="165" t="s">
+      <c r="M22" s="164" t="s">
         <v>85</v>
       </c>
-      <c r="N22" s="166"/>
+      <c r="N22" s="165"/>
       <c r="O22"/>
       <c r="P22"/>
       <c r="Q22"/>
@@ -6619,7 +6619,7 @@
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
-      <c r="AD22" s="173"/>
+      <c r="AD22" s="172"/>
       <c r="AU22"/>
       <c r="AV22"/>
       <c r="AW22"/>
@@ -6627,20 +6627,20 @@
       <c r="AY22"/>
       <c r="AZ22"/>
     </row>
-    <row r="23" spans="1:52" s="101" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="98" t="s">
+    <row r="23" spans="1:52" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="118" t="s">
+      <c r="B23" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="117"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="116"/>
-      <c r="I23" s="155"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="114"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="154"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
@@ -6657,7 +6657,7 @@
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23"/>
-      <c r="AD23" s="173"/>
+      <c r="AD23" s="172"/>
       <c r="AU23"/>
       <c r="AV23"/>
       <c r="AW23"/>
@@ -6665,28 +6665,28 @@
       <c r="AY23"/>
       <c r="AZ23"/>
     </row>
-    <row r="24" spans="1:52" s="99" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="114" t="s">
+    <row r="24" spans="1:52" s="98" customFormat="1" ht="15" customHeight="1">
+      <c r="A24" s="101"/>
+      <c r="B24" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="115"/>
-      <c r="D24" s="115"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="115"/>
-      <c r="G24" s="115"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="156" t="e">
+      <c r="C24" s="114"/>
+      <c r="D24" s="114"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="114"/>
+      <c r="G24" s="114"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="155" t="e">
         <f>I12</f>
         <v>#VALUE!</v>
       </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
-      <c r="M24" s="165" t="s">
+      <c r="M24" s="164" t="s">
         <v>86</v>
       </c>
-      <c r="N24" s="166" t="s">
+      <c r="N24" s="165" t="s">
         <v>87</v>
       </c>
       <c r="O24"/>
@@ -6702,7 +6702,7 @@
       <c r="Y24"/>
       <c r="Z24"/>
       <c r="AA24"/>
-      <c r="AD24" s="173"/>
+      <c r="AD24" s="172"/>
       <c r="AU24"/>
       <c r="AV24"/>
       <c r="AW24"/>
@@ -6710,26 +6710,26 @@
       <c r="AY24"/>
       <c r="AZ24"/>
     </row>
-    <row r="25" spans="1:52" s="61" customFormat="1" ht="15" customHeight="1">
+    <row r="25" spans="1:52" s="60" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="41"/>
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="115"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="116"/>
-      <c r="I25" s="157" t="e">
+      <c r="C25" s="114"/>
+      <c r="D25" s="114"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="156" t="e">
         <f>I24/120*20</f>
         <v>#VALUE!</v>
       </c>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
-      <c r="M25" s="101"/>
-      <c r="N25" s="101"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="100"/>
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25"/>
@@ -6743,7 +6743,7 @@
       <c r="Y25"/>
       <c r="Z25"/>
       <c r="AA25"/>
-      <c r="AD25" s="173"/>
+      <c r="AD25" s="172"/>
       <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
@@ -6751,28 +6751,28 @@
       <c r="AY25"/>
       <c r="AZ25"/>
     </row>
-    <row r="26" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="103"/>
-      <c r="B26" s="114" t="s">
+    <row r="26" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="102"/>
+      <c r="B26" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="115"/>
-      <c r="D26" s="115"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="115"/>
-      <c r="G26" s="115"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="157" t="e">
+      <c r="C26" s="114"/>
+      <c r="D26" s="114"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="156" t="e">
         <f>I24-I25</f>
         <v>#VALUE!</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26"/>
-      <c r="M26" s="165" t="s">
+      <c r="M26" s="164" t="s">
         <v>88</v>
       </c>
-      <c r="N26" s="166" t="s">
+      <c r="N26" s="165" t="s">
         <v>89</v>
       </c>
       <c r="O26"/>
@@ -6788,7 +6788,7 @@
       <c r="Y26"/>
       <c r="Z26"/>
       <c r="AA26"/>
-      <c r="AD26" s="173"/>
+      <c r="AD26" s="172"/>
       <c r="AU26"/>
       <c r="AV26"/>
       <c r="AW26"/>
@@ -6796,18 +6796,18 @@
       <c r="AY26"/>
       <c r="AZ26"/>
     </row>
-    <row r="27" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="103"/>
-      <c r="B27" s="114" t="s">
+    <row r="27" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="102"/>
+      <c r="B27" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="157" t="e">
+      <c r="C27" s="114"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="114"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="156" t="e">
         <f>SUM(I28:I37)</f>
         <v>#VALUE!</v>
       </c>
@@ -6829,7 +6829,7 @@
       <c r="Y27"/>
       <c r="Z27"/>
       <c r="AA27"/>
-      <c r="AD27" s="173"/>
+      <c r="AD27" s="172"/>
       <c r="AU27"/>
       <c r="AV27"/>
       <c r="AW27"/>
@@ -6837,18 +6837,18 @@
       <c r="AY27"/>
       <c r="AZ27"/>
     </row>
-    <row r="28" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="103"/>
-      <c r="B28" s="114" t="s">
+    <row r="28" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="102"/>
+      <c r="B28" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="157" t="e">
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="156" t="e">
         <f>O11</f>
         <v>#VALUE!</v>
       </c>
@@ -6870,7 +6870,7 @@
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28"/>
-      <c r="AD28" s="173"/>
+      <c r="AD28" s="172"/>
       <c r="AU28"/>
       <c r="AV28"/>
       <c r="AW28"/>
@@ -6878,20 +6878,20 @@
       <c r="AY28"/>
       <c r="AZ28"/>
     </row>
-    <row r="29" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A29" s="103"/>
-      <c r="B29" s="122" t="s">
+    <row r="29" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="102"/>
+      <c r="B29" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="123"/>
-      <c r="D29" s="123"/>
-      <c r="E29" s="123"/>
-      <c r="F29" s="123"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="119" t="s">
+      <c r="C29" s="122"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="118" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="158" t="e">
+      <c r="I29" s="157" t="e">
         <f>IF(H29=D43,I28*3.2%,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -6913,7 +6913,7 @@
       <c r="Y29"/>
       <c r="Z29"/>
       <c r="AA29"/>
-      <c r="AD29" s="173"/>
+      <c r="AD29" s="172"/>
       <c r="AU29"/>
       <c r="AV29"/>
       <c r="AW29"/>
@@ -6921,18 +6921,18 @@
       <c r="AY29"/>
       <c r="AZ29"/>
     </row>
-    <row r="30" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="103"/>
-      <c r="B30" s="114" t="s">
+    <row r="30" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="102"/>
+      <c r="B30" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="115"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="116"/>
-      <c r="I30" s="157">
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="156">
         <f>AA11</f>
         <v>0</v>
       </c>
@@ -6954,7 +6954,7 @@
       <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
-      <c r="AD30" s="173"/>
+      <c r="AD30" s="172"/>
       <c r="AU30"/>
       <c r="AV30"/>
       <c r="AW30"/>
@@ -6962,18 +6962,18 @@
       <c r="AY30"/>
       <c r="AZ30"/>
     </row>
-    <row r="31" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="103"/>
-      <c r="B31" s="121" t="s">
+    <row r="31" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="102"/>
+      <c r="B31" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="157">
+      <c r="C31" s="114"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="114"/>
+      <c r="G31" s="114"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="156">
         <f>AB11</f>
         <v>0</v>
       </c>
@@ -6995,11 +6995,11 @@
       <c r="Y31"/>
       <c r="Z31"/>
       <c r="AA31"/>
-      <c r="AB31" s="100"/>
-      <c r="AC31" s="100"/>
-      <c r="AD31" s="173"/>
-      <c r="AE31" s="100"/>
-      <c r="AF31" s="100"/>
+      <c r="AB31" s="99"/>
+      <c r="AC31" s="99"/>
+      <c r="AD31" s="172"/>
+      <c r="AE31" s="99"/>
+      <c r="AF31" s="99"/>
       <c r="AU31"/>
       <c r="AV31"/>
       <c r="AW31"/>
@@ -7007,18 +7007,18 @@
       <c r="AY31"/>
       <c r="AZ31"/>
     </row>
-    <row r="32" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A32" s="103"/>
-      <c r="B32" s="121" t="s">
+    <row r="32" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="102"/>
+      <c r="B32" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="115"/>
-      <c r="H32" s="116"/>
-      <c r="I32" s="157">
+      <c r="C32" s="114"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="115"/>
+      <c r="I32" s="156">
         <f>AC11</f>
         <v>0</v>
       </c>
@@ -7040,11 +7040,11 @@
       <c r="Y32"/>
       <c r="Z32"/>
       <c r="AA32"/>
-      <c r="AB32" s="100"/>
-      <c r="AC32" s="100"/>
-      <c r="AD32" s="173"/>
-      <c r="AE32" s="100"/>
-      <c r="AF32" s="100"/>
+      <c r="AB32" s="99"/>
+      <c r="AC32" s="99"/>
+      <c r="AD32" s="172"/>
+      <c r="AE32" s="99"/>
+      <c r="AF32" s="99"/>
       <c r="AU32"/>
       <c r="AV32"/>
       <c r="AW32"/>
@@ -7052,20 +7052,20 @@
       <c r="AY32"/>
       <c r="AZ32"/>
     </row>
-    <row r="33" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A33" s="103"/>
-      <c r="B33" s="122" t="s">
+    <row r="33" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="102"/>
+      <c r="B33" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="123"/>
-      <c r="D33" s="123"/>
-      <c r="E33" s="123"/>
-      <c r="F33" s="123"/>
-      <c r="G33" s="120"/>
-      <c r="H33" s="119" t="s">
+      <c r="C33" s="122"/>
+      <c r="D33" s="122"/>
+      <c r="E33" s="122"/>
+      <c r="F33" s="122"/>
+      <c r="G33" s="119"/>
+      <c r="H33" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="I33" s="158" t="e">
+      <c r="I33" s="157" t="e">
         <f>IF(H33="ДА",I28*16%/365*Длина_сделки,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -7087,11 +7087,11 @@
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
-      <c r="AB33" s="100"/>
-      <c r="AC33" s="100"/>
-      <c r="AD33" s="173"/>
-      <c r="AE33" s="100"/>
-      <c r="AF33" s="100"/>
+      <c r="AB33" s="99"/>
+      <c r="AC33" s="99"/>
+      <c r="AD33" s="172"/>
+      <c r="AE33" s="99"/>
+      <c r="AF33" s="99"/>
       <c r="AU33"/>
       <c r="AV33"/>
       <c r="AW33"/>
@@ -7099,18 +7099,18 @@
       <c r="AY33"/>
       <c r="AZ33"/>
     </row>
-    <row r="34" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A34" s="103"/>
-      <c r="B34" s="121" t="s">
+    <row r="34" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A34" s="102"/>
+      <c r="B34" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
-      <c r="F34" s="115"/>
-      <c r="G34" s="115"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="157">
+      <c r="C34" s="114"/>
+      <c r="D34" s="114"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="114"/>
+      <c r="G34" s="114"/>
+      <c r="H34" s="115"/>
+      <c r="I34" s="156">
         <f>AA11</f>
         <v>0</v>
       </c>
@@ -7132,12 +7132,12 @@
       <c r="Y34"/>
       <c r="Z34"/>
       <c r="AA34"/>
-      <c r="AB34" s="100"/>
-      <c r="AC34" s="100"/>
-      <c r="AD34" s="173"/>
-      <c r="AE34" s="100"/>
-      <c r="AF34" s="100"/>
-      <c r="AG34" s="100"/>
+      <c r="AB34" s="99"/>
+      <c r="AC34" s="99"/>
+      <c r="AD34" s="172"/>
+      <c r="AE34" s="99"/>
+      <c r="AF34" s="99"/>
+      <c r="AG34" s="99"/>
       <c r="AU34"/>
       <c r="AV34"/>
       <c r="AW34"/>
@@ -7145,18 +7145,18 @@
       <c r="AY34"/>
       <c r="AZ34"/>
     </row>
-    <row r="35" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="103"/>
-      <c r="B35" s="121" t="s">
+    <row r="35" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A35" s="102"/>
+      <c r="B35" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="115"/>
-      <c r="G35" s="115"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="157">
+      <c r="C35" s="114"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="114"/>
+      <c r="G35" s="114"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="156">
         <f>AB11</f>
         <v>0</v>
       </c>
@@ -7178,12 +7178,12 @@
       <c r="Y35"/>
       <c r="Z35"/>
       <c r="AA35"/>
-      <c r="AB35" s="100"/>
-      <c r="AC35" s="100"/>
-      <c r="AD35" s="173"/>
-      <c r="AE35" s="100"/>
-      <c r="AF35" s="100"/>
-      <c r="AG35" s="100"/>
+      <c r="AB35" s="99"/>
+      <c r="AC35" s="99"/>
+      <c r="AD35" s="172"/>
+      <c r="AE35" s="99"/>
+      <c r="AF35" s="99"/>
+      <c r="AG35" s="99"/>
       <c r="AU35"/>
       <c r="AV35"/>
       <c r="AW35"/>
@@ -7191,18 +7191,18 @@
       <c r="AY35"/>
       <c r="AZ35"/>
     </row>
-    <row r="36" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A36" s="103"/>
-      <c r="B36" s="121" t="s">
+    <row r="36" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A36" s="102"/>
+      <c r="B36" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="115"/>
-      <c r="G36" s="115"/>
-      <c r="H36" s="116"/>
-      <c r="I36" s="157">
+      <c r="C36" s="114"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="114"/>
+      <c r="H36" s="115"/>
+      <c r="I36" s="156">
         <f>AC11</f>
         <v>0</v>
       </c>
@@ -7224,12 +7224,12 @@
       <c r="Y36"/>
       <c r="Z36"/>
       <c r="AA36"/>
-      <c r="AB36" s="100"/>
-      <c r="AC36" s="100"/>
-      <c r="AD36" s="173"/>
-      <c r="AE36" s="100"/>
-      <c r="AF36" s="100"/>
-      <c r="AG36" s="100"/>
+      <c r="AB36" s="99"/>
+      <c r="AC36" s="99"/>
+      <c r="AD36" s="172"/>
+      <c r="AE36" s="99"/>
+      <c r="AF36" s="99"/>
+      <c r="AG36" s="99"/>
       <c r="AU36"/>
       <c r="AV36"/>
       <c r="AW36"/>
@@ -7237,20 +7237,20 @@
       <c r="AY36"/>
       <c r="AZ36"/>
     </row>
-    <row r="37" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A37" s="103"/>
-      <c r="B37" s="122" t="s">
+    <row r="37" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A37" s="102"/>
+      <c r="B37" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="123"/>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="123"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="119" t="s">
+      <c r="C37" s="122"/>
+      <c r="D37" s="122"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="119"/>
+      <c r="H37" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="I37" s="158">
+      <c r="I37" s="157">
         <f>IF(H37="ДА",I24*3%/365*(I15+I16),0)</f>
         <v>0</v>
       </c>
@@ -7272,12 +7272,12 @@
       <c r="Y37"/>
       <c r="Z37"/>
       <c r="AA37"/>
-      <c r="AB37" s="100"/>
-      <c r="AC37" s="100"/>
-      <c r="AD37" s="173"/>
-      <c r="AE37" s="100"/>
-      <c r="AF37" s="100"/>
-      <c r="AG37" s="100"/>
+      <c r="AB37" s="99"/>
+      <c r="AC37" s="99"/>
+      <c r="AD37" s="172"/>
+      <c r="AE37" s="99"/>
+      <c r="AF37" s="99"/>
+      <c r="AG37" s="99"/>
       <c r="AU37"/>
       <c r="AV37"/>
       <c r="AW37"/>
@@ -7285,18 +7285,18 @@
       <c r="AY37"/>
       <c r="AZ37"/>
     </row>
-    <row r="38" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A38" s="103"/>
-      <c r="B38" s="121" t="s">
+    <row r="38" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A38" s="102"/>
+      <c r="B38" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="115"/>
-      <c r="D38" s="115"/>
-      <c r="E38" s="115"/>
-      <c r="F38" s="115"/>
-      <c r="G38" s="115"/>
-      <c r="H38" s="116"/>
-      <c r="I38" s="157" t="e">
+      <c r="C38" s="114"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="114"/>
+      <c r="F38" s="114"/>
+      <c r="G38" s="114"/>
+      <c r="H38" s="115"/>
+      <c r="I38" s="156" t="e">
         <f>I26-I27</f>
         <v>#VALUE!</v>
       </c>
@@ -7318,12 +7318,12 @@
       <c r="Y38"/>
       <c r="Z38"/>
       <c r="AA38"/>
-      <c r="AB38" s="100"/>
-      <c r="AC38" s="100"/>
-      <c r="AD38" s="173"/>
-      <c r="AE38" s="100"/>
-      <c r="AF38" s="100"/>
-      <c r="AG38" s="100"/>
+      <c r="AB38" s="99"/>
+      <c r="AC38" s="99"/>
+      <c r="AD38" s="172"/>
+      <c r="AE38" s="99"/>
+      <c r="AF38" s="99"/>
+      <c r="AG38" s="99"/>
       <c r="AU38"/>
       <c r="AV38"/>
       <c r="AW38"/>
@@ -7331,18 +7331,18 @@
       <c r="AY38"/>
       <c r="AZ38"/>
     </row>
-    <row r="39" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A39" s="103"/>
-      <c r="B39" s="121" t="s">
+    <row r="39" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A39" s="102"/>
+      <c r="B39" s="120" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="115"/>
-      <c r="D39" s="115"/>
-      <c r="E39" s="115"/>
-      <c r="F39" s="115"/>
-      <c r="G39" s="115"/>
-      <c r="H39" s="116"/>
-      <c r="I39" s="157"/>
+      <c r="C39" s="114"/>
+      <c r="D39" s="114"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="114"/>
+      <c r="G39" s="114"/>
+      <c r="H39" s="115"/>
+      <c r="I39" s="156"/>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39"/>
@@ -7361,12 +7361,12 @@
       <c r="Y39"/>
       <c r="Z39"/>
       <c r="AA39"/>
-      <c r="AB39" s="100"/>
-      <c r="AC39" s="100"/>
-      <c r="AD39" s="173"/>
-      <c r="AE39" s="100"/>
-      <c r="AF39" s="100"/>
-      <c r="AG39" s="100"/>
+      <c r="AB39" s="99"/>
+      <c r="AC39" s="99"/>
+      <c r="AD39" s="172"/>
+      <c r="AE39" s="99"/>
+      <c r="AF39" s="99"/>
+      <c r="AG39" s="99"/>
       <c r="AU39"/>
       <c r="AV39"/>
       <c r="AW39"/>
@@ -7374,18 +7374,18 @@
       <c r="AY39"/>
       <c r="AZ39"/>
     </row>
-    <row r="40" spans="1:52" s="97" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="103"/>
-      <c r="B40" s="121" t="s">
+    <row r="40" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
+      <c r="A40" s="102"/>
+      <c r="B40" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="115"/>
-      <c r="D40" s="115"/>
-      <c r="E40" s="115"/>
-      <c r="F40" s="115"/>
-      <c r="G40" s="115"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="159" t="e">
+      <c r="C40" s="114"/>
+      <c r="D40" s="114"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="114"/>
+      <c r="H40" s="115"/>
+      <c r="I40" s="158" t="e">
         <f>I38/I26</f>
         <v>#VALUE!</v>
       </c>
@@ -7407,12 +7407,12 @@
       <c r="Y40"/>
       <c r="Z40"/>
       <c r="AA40"/>
-      <c r="AB40" s="100"/>
-      <c r="AC40" s="100"/>
-      <c r="AD40" s="173"/>
-      <c r="AE40" s="100"/>
-      <c r="AF40" s="100"/>
-      <c r="AG40" s="100"/>
+      <c r="AB40" s="99"/>
+      <c r="AC40" s="99"/>
+      <c r="AD40" s="172"/>
+      <c r="AE40" s="99"/>
+      <c r="AF40" s="99"/>
+      <c r="AG40" s="99"/>
       <c r="AU40"/>
       <c r="AV40"/>
       <c r="AW40"/>
@@ -7420,7 +7420,7 @@
       <c r="AY40"/>
       <c r="AZ40"/>
     </row>
-    <row r="41" spans="1:52" s="97" customFormat="1" ht="12" customHeight="1">
+    <row r="41" spans="1:52" s="96" customFormat="1" ht="12" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41"/>
       <c r="C41"/>
@@ -7429,7 +7429,7 @@
       <c r="F41"/>
       <c r="G41"/>
       <c r="H41"/>
-      <c r="I41" s="160"/>
+      <c r="I41" s="159"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
@@ -7450,7 +7450,7 @@
       <c r="AA41"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-      <c r="AD41" s="173"/>
+      <c r="AD41" s="172"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
@@ -7469,7 +7469,7 @@
       <c r="F42"/>
       <c r="G42"/>
       <c r="H42"/>
-      <c r="I42" s="160"/>
+      <c r="I42" s="159"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42"/>
@@ -7490,7 +7490,7 @@
       <c r="AA42"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="173"/>
+      <c r="AD42" s="172"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
@@ -7512,7 +7512,7 @@
       <c r="F43"/>
       <c r="G43"/>
       <c r="H43"/>
-      <c r="I43" s="160"/>
+      <c r="I43" s="159"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
@@ -7533,7 +7533,7 @@
       <c r="AA43"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="173"/>
+      <c r="AD43" s="172"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
@@ -7555,7 +7555,7 @@
       <c r="F44"/>
       <c r="G44"/>
       <c r="H44"/>
-      <c r="I44" s="160"/>
+      <c r="I44" s="159"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
@@ -7574,7 +7574,7 @@
       <c r="Y44"/>
       <c r="Z44"/>
       <c r="AA44"/>
-      <c r="AD44" s="173"/>
+      <c r="AD44" s="172"/>
       <c r="AU44"/>
       <c r="AV44"/>
       <c r="AW44"/>
@@ -7590,7 +7590,7 @@
       <c r="F45"/>
       <c r="G45"/>
       <c r="H45"/>
-      <c r="I45" s="160"/>
+      <c r="I45" s="159"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45"/>
@@ -7609,7 +7609,7 @@
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AD45" s="173"/>
+      <c r="AD45" s="172"/>
       <c r="AU45"/>
       <c r="AV45"/>
       <c r="AW45"/>
@@ -7625,7 +7625,7 @@
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46"/>
-      <c r="I46" s="160"/>
+      <c r="I46" s="159"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46"/>
@@ -7644,7 +7644,7 @@
       <c r="Y46"/>
       <c r="Z46"/>
       <c r="AA46"/>
-      <c r="AD46" s="173"/>
+      <c r="AD46" s="172"/>
       <c r="AU46"/>
       <c r="AV46"/>
       <c r="AW46"/>
@@ -7660,7 +7660,7 @@
       <c r="F47"/>
       <c r="G47"/>
       <c r="H47"/>
-      <c r="I47" s="160"/>
+      <c r="I47" s="159"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47"/>
@@ -7679,7 +7679,7 @@
       <c r="Y47"/>
       <c r="Z47"/>
       <c r="AA47"/>
-      <c r="AD47" s="173"/>
+      <c r="AD47" s="172"/>
       <c r="AU47"/>
       <c r="AV47"/>
       <c r="AW47"/>
@@ -7688,7 +7688,7 @@
       <c r="AZ47"/>
     </row>
     <row r="48" spans="1:52" ht="11.45" customHeight="1">
-      <c r="AD48" s="173"/>
+      <c r="AD48" s="172"/>
       <c r="AU48"/>
       <c r="AV48"/>
       <c r="AW48"/>
@@ -7697,7 +7697,7 @@
       <c r="AZ48"/>
     </row>
     <row r="49" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD49" s="173"/>
+      <c r="AD49" s="172"/>
       <c r="AU49"/>
       <c r="AV49"/>
       <c r="AW49"/>
@@ -7706,7 +7706,7 @@
       <c r="AZ49"/>
     </row>
     <row r="50" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD50" s="173"/>
+      <c r="AD50" s="172"/>
       <c r="AU50"/>
       <c r="AV50"/>
       <c r="AW50"/>
@@ -7715,7 +7715,7 @@
       <c r="AZ50"/>
     </row>
     <row r="51" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD51" s="173"/>
+      <c r="AD51" s="172"/>
       <c r="AU51"/>
       <c r="AV51"/>
       <c r="AW51"/>
@@ -7724,7 +7724,7 @@
       <c r="AZ51"/>
     </row>
     <row r="52" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD52" s="173"/>
+      <c r="AD52" s="172"/>
       <c r="AU52"/>
       <c r="AV52"/>
       <c r="AW52"/>
@@ -7733,7 +7733,7 @@
       <c r="AZ52"/>
     </row>
     <row r="53" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD53" s="173"/>
+      <c r="AD53" s="172"/>
       <c r="AU53"/>
       <c r="AV53"/>
       <c r="AW53"/>
@@ -7742,7 +7742,7 @@
       <c r="AZ53"/>
     </row>
     <row r="54" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD54" s="173"/>
+      <c r="AD54" s="172"/>
       <c r="AU54"/>
       <c r="AV54"/>
       <c r="AW54"/>
@@ -7751,7 +7751,7 @@
       <c r="AZ54"/>
     </row>
     <row r="55" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD55" s="173"/>
+      <c r="AD55" s="172"/>
       <c r="AU55"/>
       <c r="AV55"/>
       <c r="AW55"/>
@@ -7760,7 +7760,7 @@
       <c r="AZ55"/>
     </row>
     <row r="56" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD56" s="173"/>
+      <c r="AD56" s="172"/>
       <c r="AU56"/>
       <c r="AV56"/>
       <c r="AW56"/>
@@ -7769,7 +7769,7 @@
       <c r="AZ56"/>
     </row>
     <row r="57" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD57" s="173"/>
+      <c r="AD57" s="172"/>
       <c r="AU57"/>
       <c r="AV57"/>
       <c r="AW57"/>
@@ -7778,7 +7778,7 @@
       <c r="AZ57"/>
     </row>
     <row r="58" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD58" s="173"/>
+      <c r="AD58" s="172"/>
       <c r="AU58"/>
       <c r="AV58"/>
       <c r="AW58"/>
@@ -7787,7 +7787,7 @@
       <c r="AZ58"/>
     </row>
     <row r="59" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD59" s="173"/>
+      <c r="AD59" s="172"/>
       <c r="AU59"/>
       <c r="AV59"/>
       <c r="AW59"/>
@@ -7796,7 +7796,7 @@
       <c r="AZ59"/>
     </row>
     <row r="60" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD60" s="173"/>
+      <c r="AD60" s="172"/>
       <c r="AU60"/>
       <c r="AV60"/>
       <c r="AW60"/>
@@ -7805,7 +7805,7 @@
       <c r="AZ60"/>
     </row>
     <row r="61" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD61" s="173"/>
+      <c r="AD61" s="172"/>
       <c r="AU61"/>
       <c r="AV61"/>
       <c r="AW61"/>
@@ -7814,7 +7814,7 @@
       <c r="AZ61"/>
     </row>
     <row r="62" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD62" s="173"/>
+      <c r="AD62" s="172"/>
       <c r="AU62"/>
       <c r="AV62"/>
       <c r="AW62"/>
@@ -7823,7 +7823,7 @@
       <c r="AZ62"/>
     </row>
     <row r="63" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD63" s="173"/>
+      <c r="AD63" s="172"/>
       <c r="AU63"/>
       <c r="AV63"/>
       <c r="AW63"/>
@@ -7832,7 +7832,7 @@
       <c r="AZ63"/>
     </row>
     <row r="64" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD64" s="173"/>
+      <c r="AD64" s="172"/>
       <c r="AU64"/>
       <c r="AV64"/>
       <c r="AW64"/>
@@ -7841,7 +7841,7 @@
       <c r="AZ64"/>
     </row>
     <row r="65" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD65" s="173"/>
+      <c r="AD65" s="172"/>
       <c r="AU65"/>
       <c r="AV65"/>
       <c r="AW65"/>
@@ -7850,7 +7850,7 @@
       <c r="AZ65"/>
     </row>
     <row r="66" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD66" s="173"/>
+      <c r="AD66" s="172"/>
       <c r="AU66"/>
       <c r="AV66"/>
       <c r="AW66"/>
@@ -7859,7 +7859,7 @@
       <c r="AZ66"/>
     </row>
     <row r="67" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD67" s="173"/>
+      <c r="AD67" s="172"/>
       <c r="AU67"/>
       <c r="AV67"/>
       <c r="AW67"/>
@@ -7868,7 +7868,7 @@
       <c r="AZ67"/>
     </row>
     <row r="68" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD68" s="173"/>
+      <c r="AD68" s="172"/>
       <c r="AU68"/>
       <c r="AV68"/>
       <c r="AW68"/>
@@ -7877,7 +7877,7 @@
       <c r="AZ68"/>
     </row>
     <row r="69" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD69" s="173"/>
+      <c r="AD69" s="172"/>
       <c r="AU69"/>
       <c r="AV69"/>
       <c r="AW69"/>
@@ -7886,7 +7886,7 @@
       <c r="AZ69"/>
     </row>
     <row r="70" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD70" s="173"/>
+      <c r="AD70" s="172"/>
       <c r="AU70"/>
       <c r="AV70"/>
       <c r="AW70"/>
@@ -7895,7 +7895,7 @@
       <c r="AZ70"/>
     </row>
     <row r="71" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD71" s="173"/>
+      <c r="AD71" s="172"/>
       <c r="AU71"/>
       <c r="AV71"/>
       <c r="AW71"/>
@@ -7904,7 +7904,7 @@
       <c r="AZ71"/>
     </row>
     <row r="72" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD72" s="173"/>
+      <c r="AD72" s="172"/>
       <c r="AU72"/>
       <c r="AV72"/>
       <c r="AW72"/>
@@ -7913,7 +7913,7 @@
       <c r="AZ72"/>
     </row>
     <row r="73" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD73" s="173"/>
+      <c r="AD73" s="172"/>
       <c r="AU73"/>
       <c r="AV73"/>
       <c r="AW73"/>
@@ -7922,7 +7922,7 @@
       <c r="AZ73"/>
     </row>
     <row r="74" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD74" s="173"/>
+      <c r="AD74" s="172"/>
       <c r="AU74"/>
       <c r="AV74"/>
       <c r="AW74"/>
@@ -7931,7 +7931,7 @@
       <c r="AZ74"/>
     </row>
     <row r="75" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD75" s="173"/>
+      <c r="AD75" s="172"/>
       <c r="AU75"/>
       <c r="AV75"/>
       <c r="AW75"/>
@@ -7940,7 +7940,7 @@
       <c r="AZ75"/>
     </row>
     <row r="76" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD76" s="173"/>
+      <c r="AD76" s="172"/>
       <c r="AU76"/>
       <c r="AV76"/>
       <c r="AW76"/>
@@ -7949,7 +7949,7 @@
       <c r="AZ76"/>
     </row>
     <row r="77" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD77" s="173"/>
+      <c r="AD77" s="172"/>
       <c r="AU77"/>
       <c r="AV77"/>
       <c r="AW77"/>
@@ -7958,7 +7958,7 @@
       <c r="AZ77"/>
     </row>
     <row r="78" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD78" s="173"/>
+      <c r="AD78" s="172"/>
       <c r="AU78"/>
       <c r="AV78"/>
       <c r="AW78"/>
@@ -7967,7 +7967,7 @@
       <c r="AZ78"/>
     </row>
     <row r="79" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD79" s="173"/>
+      <c r="AD79" s="172"/>
       <c r="AU79"/>
       <c r="AV79"/>
       <c r="AW79"/>
@@ -7976,7 +7976,7 @@
       <c r="AZ79"/>
     </row>
     <row r="80" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD80" s="173"/>
+      <c r="AD80" s="172"/>
       <c r="AU80"/>
       <c r="AV80"/>
       <c r="AW80"/>
@@ -7985,7 +7985,7 @@
       <c r="AZ80"/>
     </row>
     <row r="81" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD81" s="173"/>
+      <c r="AD81" s="172"/>
       <c r="AU81"/>
       <c r="AV81"/>
       <c r="AW81"/>
@@ -7994,7 +7994,7 @@
       <c r="AZ81"/>
     </row>
     <row r="82" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD82" s="173"/>
+      <c r="AD82" s="172"/>
       <c r="AU82"/>
       <c r="AV82"/>
       <c r="AW82"/>
@@ -8003,7 +8003,7 @@
       <c r="AZ82"/>
     </row>
     <row r="83" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD83" s="173"/>
+      <c r="AD83" s="172"/>
       <c r="AU83"/>
       <c r="AV83"/>
       <c r="AW83"/>
@@ -8012,7 +8012,7 @@
       <c r="AZ83"/>
     </row>
     <row r="84" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD84" s="173"/>
+      <c r="AD84" s="172"/>
       <c r="AU84"/>
       <c r="AV84"/>
       <c r="AW84"/>
@@ -8021,7 +8021,7 @@
       <c r="AZ84"/>
     </row>
     <row r="85" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD85" s="173"/>
+      <c r="AD85" s="172"/>
       <c r="AU85"/>
       <c r="AV85"/>
       <c r="AW85"/>
@@ -8030,7 +8030,7 @@
       <c r="AZ85"/>
     </row>
     <row r="86" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD86" s="173"/>
+      <c r="AD86" s="172"/>
       <c r="AU86"/>
       <c r="AV86"/>
       <c r="AW86"/>
@@ -8039,7 +8039,7 @@
       <c r="AZ86"/>
     </row>
     <row r="87" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD87" s="173"/>
+      <c r="AD87" s="172"/>
       <c r="AU87"/>
       <c r="AV87"/>
       <c r="AW87"/>
@@ -8048,7 +8048,7 @@
       <c r="AZ87"/>
     </row>
     <row r="88" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD88" s="173"/>
+      <c r="AD88" s="172"/>
       <c r="AU88"/>
       <c r="AV88"/>
       <c r="AW88"/>
@@ -8057,7 +8057,7 @@
       <c r="AZ88"/>
     </row>
     <row r="89" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD89" s="173"/>
+      <c r="AD89" s="172"/>
       <c r="AU89"/>
       <c r="AV89"/>
       <c r="AW89"/>
@@ -8066,7 +8066,7 @@
       <c r="AZ89"/>
     </row>
     <row r="90" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD90" s="173"/>
+      <c r="AD90" s="172"/>
       <c r="AU90"/>
       <c r="AV90"/>
       <c r="AW90"/>
@@ -8075,7 +8075,7 @@
       <c r="AZ90"/>
     </row>
     <row r="91" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD91" s="173"/>
+      <c r="AD91" s="172"/>
       <c r="AU91"/>
       <c r="AV91"/>
       <c r="AW91"/>
@@ -8084,7 +8084,7 @@
       <c r="AZ91"/>
     </row>
     <row r="92" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD92" s="173"/>
+      <c r="AD92" s="172"/>
       <c r="AU92"/>
       <c r="AV92"/>
       <c r="AW92"/>
@@ -8093,7 +8093,7 @@
       <c r="AZ92"/>
     </row>
     <row r="93" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD93" s="173"/>
+      <c r="AD93" s="172"/>
       <c r="AU93"/>
       <c r="AV93"/>
       <c r="AW93"/>
@@ -8102,7 +8102,7 @@
       <c r="AZ93"/>
     </row>
     <row r="94" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD94" s="173"/>
+      <c r="AD94" s="172"/>
       <c r="AU94"/>
       <c r="AV94"/>
       <c r="AW94"/>
@@ -8111,7 +8111,7 @@
       <c r="AZ94"/>
     </row>
     <row r="95" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD95" s="173"/>
+      <c r="AD95" s="172"/>
       <c r="AU95"/>
       <c r="AV95"/>
       <c r="AW95"/>
@@ -8120,7 +8120,7 @@
       <c r="AZ95"/>
     </row>
     <row r="96" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD96" s="173"/>
+      <c r="AD96" s="172"/>
       <c r="AU96"/>
       <c r="AV96"/>
       <c r="AW96"/>
@@ -8129,7 +8129,7 @@
       <c r="AZ96"/>
     </row>
     <row r="97" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD97" s="173"/>
+      <c r="AD97" s="172"/>
       <c r="AU97"/>
       <c r="AV97"/>
       <c r="AW97"/>
@@ -8138,7 +8138,7 @@
       <c r="AZ97"/>
     </row>
     <row r="98" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD98" s="173"/>
+      <c r="AD98" s="172"/>
       <c r="AU98"/>
       <c r="AV98"/>
       <c r="AW98"/>
@@ -8147,7 +8147,7 @@
       <c r="AZ98"/>
     </row>
     <row r="99" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD99" s="173"/>
+      <c r="AD99" s="172"/>
       <c r="AU99"/>
       <c r="AV99"/>
       <c r="AW99"/>
@@ -8156,7 +8156,7 @@
       <c r="AZ99"/>
     </row>
     <row r="100" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD100" s="173"/>
+      <c r="AD100" s="172"/>
       <c r="AU100"/>
       <c r="AV100"/>
       <c r="AW100"/>
@@ -8165,7 +8165,7 @@
       <c r="AZ100"/>
     </row>
     <row r="101" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD101" s="173"/>
+      <c r="AD101" s="172"/>
       <c r="AU101"/>
       <c r="AV101"/>
       <c r="AW101"/>
@@ -8174,7 +8174,7 @@
       <c r="AZ101"/>
     </row>
     <row r="102" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD102" s="173"/>
+      <c r="AD102" s="172"/>
       <c r="AU102"/>
       <c r="AV102"/>
       <c r="AW102"/>
@@ -8183,7 +8183,7 @@
       <c r="AZ102"/>
     </row>
     <row r="103" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD103" s="173"/>
+      <c r="AD103" s="172"/>
       <c r="AU103"/>
       <c r="AV103"/>
       <c r="AW103"/>
@@ -8192,7 +8192,7 @@
       <c r="AZ103"/>
     </row>
     <row r="104" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD104" s="173"/>
+      <c r="AD104" s="172"/>
       <c r="AU104"/>
       <c r="AV104"/>
       <c r="AW104"/>
@@ -8201,7 +8201,7 @@
       <c r="AZ104"/>
     </row>
     <row r="105" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD105" s="173"/>
+      <c r="AD105" s="172"/>
       <c r="AU105"/>
       <c r="AV105"/>
       <c r="AW105"/>
@@ -8210,7 +8210,7 @@
       <c r="AZ105"/>
     </row>
     <row r="106" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD106" s="173"/>
+      <c r="AD106" s="172"/>
       <c r="AU106"/>
       <c r="AV106"/>
       <c r="AW106"/>
@@ -8219,7 +8219,7 @@
       <c r="AZ106"/>
     </row>
     <row r="107" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD107" s="173"/>
+      <c r="AD107" s="172"/>
       <c r="AU107"/>
       <c r="AV107"/>
       <c r="AW107"/>
@@ -8228,7 +8228,7 @@
       <c r="AZ107"/>
     </row>
     <row r="108" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD108" s="173"/>
+      <c r="AD108" s="172"/>
       <c r="AU108"/>
       <c r="AV108"/>
       <c r="AW108"/>
@@ -8237,7 +8237,7 @@
       <c r="AZ108"/>
     </row>
     <row r="109" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD109" s="173"/>
+      <c r="AD109" s="172"/>
       <c r="AU109"/>
       <c r="AV109"/>
       <c r="AW109"/>
@@ -8246,7 +8246,7 @@
       <c r="AZ109"/>
     </row>
     <row r="110" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD110" s="173"/>
+      <c r="AD110" s="172"/>
       <c r="AU110"/>
       <c r="AV110"/>
       <c r="AW110"/>
@@ -8255,7 +8255,7 @@
       <c r="AZ110"/>
     </row>
     <row r="111" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD111" s="173"/>
+      <c r="AD111" s="172"/>
       <c r="AU111"/>
       <c r="AV111"/>
       <c r="AW111"/>
@@ -8264,7 +8264,7 @@
       <c r="AZ111"/>
     </row>
     <row r="112" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD112" s="173"/>
+      <c r="AD112" s="172"/>
       <c r="AU112"/>
       <c r="AV112"/>
       <c r="AW112"/>
@@ -8273,7 +8273,7 @@
       <c r="AZ112"/>
     </row>
     <row r="113" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD113" s="173"/>
+      <c r="AD113" s="172"/>
       <c r="AU113"/>
       <c r="AV113"/>
       <c r="AW113"/>
@@ -8282,7 +8282,7 @@
       <c r="AZ113"/>
     </row>
     <row r="114" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD114" s="173"/>
+      <c r="AD114" s="172"/>
       <c r="AU114"/>
       <c r="AV114"/>
       <c r="AW114"/>
@@ -8291,7 +8291,7 @@
       <c r="AZ114"/>
     </row>
     <row r="115" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD115" s="173"/>
+      <c r="AD115" s="172"/>
       <c r="AU115"/>
       <c r="AV115"/>
       <c r="AW115"/>
@@ -8300,7 +8300,7 @@
       <c r="AZ115"/>
     </row>
     <row r="116" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD116" s="173"/>
+      <c r="AD116" s="172"/>
       <c r="AU116"/>
       <c r="AV116"/>
       <c r="AW116"/>
@@ -8309,7 +8309,7 @@
       <c r="AZ116"/>
     </row>
     <row r="117" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD117" s="173"/>
+      <c r="AD117" s="172"/>
       <c r="AU117"/>
       <c r="AV117"/>
       <c r="AW117"/>
@@ -8318,7 +8318,7 @@
       <c r="AZ117"/>
     </row>
     <row r="118" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD118" s="173"/>
+      <c r="AD118" s="172"/>
       <c r="AU118"/>
       <c r="AV118"/>
       <c r="AW118"/>
@@ -8327,7 +8327,7 @@
       <c r="AZ118"/>
     </row>
     <row r="119" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD119" s="173"/>
+      <c r="AD119" s="172"/>
       <c r="AU119"/>
       <c r="AV119"/>
       <c r="AW119"/>
@@ -8336,7 +8336,7 @@
       <c r="AZ119"/>
     </row>
     <row r="120" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD120" s="173"/>
+      <c r="AD120" s="172"/>
       <c r="AU120"/>
       <c r="AV120"/>
       <c r="AW120"/>
@@ -8345,7 +8345,7 @@
       <c r="AZ120"/>
     </row>
     <row r="121" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD121" s="173"/>
+      <c r="AD121" s="172"/>
       <c r="AU121"/>
       <c r="AV121"/>
       <c r="AW121"/>
@@ -8354,7 +8354,7 @@
       <c r="AZ121"/>
     </row>
     <row r="122" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD122" s="173"/>
+      <c r="AD122" s="172"/>
       <c r="AU122"/>
       <c r="AV122"/>
       <c r="AW122"/>
@@ -8363,7 +8363,7 @@
       <c r="AZ122"/>
     </row>
     <row r="123" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD123" s="173"/>
+      <c r="AD123" s="172"/>
       <c r="AU123"/>
       <c r="AV123"/>
       <c r="AW123"/>
@@ -8372,7 +8372,7 @@
       <c r="AZ123"/>
     </row>
     <row r="124" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD124" s="173"/>
+      <c r="AD124" s="172"/>
       <c r="AU124"/>
       <c r="AV124"/>
       <c r="AW124"/>
@@ -8381,7 +8381,7 @@
       <c r="AZ124"/>
     </row>
     <row r="125" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD125" s="173"/>
+      <c r="AD125" s="172"/>
       <c r="AU125"/>
       <c r="AV125"/>
       <c r="AW125"/>
@@ -8390,7 +8390,7 @@
       <c r="AZ125"/>
     </row>
     <row r="126" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD126" s="173"/>
+      <c r="AD126" s="172"/>
       <c r="AU126"/>
       <c r="AV126"/>
       <c r="AW126"/>
@@ -8399,7 +8399,7 @@
       <c r="AZ126"/>
     </row>
     <row r="127" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD127" s="173"/>
+      <c r="AD127" s="172"/>
       <c r="AU127"/>
       <c r="AV127"/>
       <c r="AW127"/>
@@ -8408,7 +8408,7 @@
       <c r="AZ127"/>
     </row>
     <row r="128" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD128" s="173"/>
+      <c r="AD128" s="172"/>
       <c r="AU128"/>
       <c r="AV128"/>
       <c r="AW128"/>
@@ -8417,7 +8417,7 @@
       <c r="AZ128"/>
     </row>
     <row r="129" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD129" s="173"/>
+      <c r="AD129" s="172"/>
       <c r="AU129"/>
       <c r="AV129"/>
       <c r="AW129"/>
@@ -8426,7 +8426,7 @@
       <c r="AZ129"/>
     </row>
     <row r="130" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD130" s="173"/>
+      <c r="AD130" s="172"/>
       <c r="AU130"/>
       <c r="AV130"/>
       <c r="AW130"/>
@@ -8435,7 +8435,7 @@
       <c r="AZ130"/>
     </row>
     <row r="131" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD131" s="173"/>
+      <c r="AD131" s="172"/>
       <c r="AU131"/>
       <c r="AV131"/>
       <c r="AW131"/>
@@ -8444,7 +8444,7 @@
       <c r="AZ131"/>
     </row>
     <row r="132" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD132" s="173"/>
+      <c r="AD132" s="172"/>
       <c r="AU132"/>
       <c r="AV132"/>
       <c r="AW132"/>
@@ -8453,7 +8453,7 @@
       <c r="AZ132"/>
     </row>
     <row r="133" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD133" s="173"/>
+      <c r="AD133" s="172"/>
       <c r="AU133"/>
       <c r="AV133"/>
       <c r="AW133"/>
@@ -8462,7 +8462,7 @@
       <c r="AZ133"/>
     </row>
     <row r="134" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD134" s="173"/>
+      <c r="AD134" s="172"/>
       <c r="AU134"/>
       <c r="AV134"/>
       <c r="AW134"/>
@@ -8471,7 +8471,7 @@
       <c r="AZ134"/>
     </row>
     <row r="135" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD135" s="173"/>
+      <c r="AD135" s="172"/>
       <c r="AU135"/>
       <c r="AV135"/>
       <c r="AW135"/>
@@ -8480,7 +8480,7 @@
       <c r="AZ135"/>
     </row>
     <row r="136" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD136" s="173"/>
+      <c r="AD136" s="172"/>
       <c r="AU136"/>
       <c r="AV136"/>
       <c r="AW136"/>
@@ -8489,7 +8489,7 @@
       <c r="AZ136"/>
     </row>
     <row r="137" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD137" s="173"/>
+      <c r="AD137" s="172"/>
       <c r="AU137"/>
       <c r="AV137"/>
       <c r="AW137"/>
@@ -8498,7 +8498,7 @@
       <c r="AZ137"/>
     </row>
     <row r="138" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD138" s="173"/>
+      <c r="AD138" s="172"/>
       <c r="AU138"/>
       <c r="AV138"/>
       <c r="AW138"/>
@@ -8507,7 +8507,7 @@
       <c r="AZ138"/>
     </row>
     <row r="139" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD139" s="173"/>
+      <c r="AD139" s="172"/>
       <c r="AU139"/>
       <c r="AV139"/>
       <c r="AW139"/>
@@ -8516,7 +8516,7 @@
       <c r="AZ139"/>
     </row>
     <row r="140" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD140" s="173"/>
+      <c r="AD140" s="172"/>
       <c r="AU140"/>
       <c r="AV140"/>
       <c r="AW140"/>
@@ -8525,7 +8525,7 @@
       <c r="AZ140"/>
     </row>
     <row r="141" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD141" s="173"/>
+      <c r="AD141" s="172"/>
       <c r="AU141"/>
       <c r="AV141"/>
       <c r="AW141"/>
@@ -8534,7 +8534,7 @@
       <c r="AZ141"/>
     </row>
     <row r="142" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD142" s="173"/>
+      <c r="AD142" s="172"/>
       <c r="AU142"/>
       <c r="AV142"/>
       <c r="AW142"/>
@@ -8543,7 +8543,7 @@
       <c r="AZ142"/>
     </row>
     <row r="143" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD143" s="173"/>
+      <c r="AD143" s="172"/>
       <c r="AU143"/>
       <c r="AV143"/>
       <c r="AW143"/>
@@ -8552,7 +8552,7 @@
       <c r="AZ143"/>
     </row>
     <row r="144" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD144" s="173"/>
+      <c r="AD144" s="172"/>
       <c r="AU144"/>
       <c r="AV144"/>
       <c r="AW144"/>
@@ -8561,7 +8561,7 @@
       <c r="AZ144"/>
     </row>
     <row r="145" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD145" s="173"/>
+      <c r="AD145" s="172"/>
       <c r="AU145"/>
       <c r="AV145"/>
       <c r="AW145"/>
@@ -8570,7 +8570,7 @@
       <c r="AZ145"/>
     </row>
     <row r="146" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD146" s="173"/>
+      <c r="AD146" s="172"/>
       <c r="AU146"/>
       <c r="AV146"/>
       <c r="AW146"/>
@@ -8579,7 +8579,7 @@
       <c r="AZ146"/>
     </row>
     <row r="147" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD147" s="173"/>
+      <c r="AD147" s="172"/>
       <c r="AU147"/>
       <c r="AV147"/>
       <c r="AW147"/>
@@ -8588,7 +8588,7 @@
       <c r="AZ147"/>
     </row>
     <row r="148" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD148" s="173"/>
+      <c r="AD148" s="172"/>
       <c r="AU148"/>
       <c r="AV148"/>
       <c r="AW148"/>
@@ -8597,7 +8597,7 @@
       <c r="AZ148"/>
     </row>
     <row r="149" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD149" s="173"/>
+      <c r="AD149" s="172"/>
       <c r="AU149"/>
       <c r="AV149"/>
       <c r="AW149"/>
@@ -8606,7 +8606,7 @@
       <c r="AZ149"/>
     </row>
     <row r="150" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD150" s="173"/>
+      <c r="AD150" s="172"/>
       <c r="AU150"/>
       <c r="AV150"/>
       <c r="AW150"/>
@@ -8615,7 +8615,7 @@
       <c r="AZ150"/>
     </row>
     <row r="151" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD151" s="173"/>
+      <c r="AD151" s="172"/>
       <c r="AU151"/>
       <c r="AV151"/>
       <c r="AW151"/>
@@ -8624,7 +8624,7 @@
       <c r="AZ151"/>
     </row>
     <row r="152" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD152" s="173"/>
+      <c r="AD152" s="172"/>
       <c r="AU152"/>
       <c r="AV152"/>
       <c r="AW152"/>
@@ -8633,7 +8633,7 @@
       <c r="AZ152"/>
     </row>
     <row r="153" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD153" s="173"/>
+      <c r="AD153" s="172"/>
       <c r="AU153"/>
       <c r="AV153"/>
       <c r="AW153"/>
@@ -8642,7 +8642,7 @@
       <c r="AZ153"/>
     </row>
     <row r="154" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD154" s="173"/>
+      <c r="AD154" s="172"/>
       <c r="AU154"/>
       <c r="AV154"/>
       <c r="AW154"/>
@@ -8651,7 +8651,7 @@
       <c r="AZ154"/>
     </row>
     <row r="155" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD155" s="173"/>
+      <c r="AD155" s="172"/>
       <c r="AU155"/>
       <c r="AV155"/>
       <c r="AW155"/>
@@ -8660,7 +8660,7 @@
       <c r="AZ155"/>
     </row>
     <row r="156" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD156" s="173"/>
+      <c r="AD156" s="172"/>
       <c r="AU156"/>
       <c r="AV156"/>
       <c r="AW156"/>
@@ -8669,7 +8669,7 @@
       <c r="AZ156"/>
     </row>
     <row r="157" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD157" s="173"/>
+      <c r="AD157" s="172"/>
       <c r="AU157"/>
       <c r="AV157"/>
       <c r="AW157"/>
@@ -8678,7 +8678,7 @@
       <c r="AZ157"/>
     </row>
     <row r="158" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD158" s="173"/>
+      <c r="AD158" s="172"/>
       <c r="AU158"/>
       <c r="AV158"/>
       <c r="AW158"/>
@@ -8687,7 +8687,7 @@
       <c r="AZ158"/>
     </row>
     <row r="159" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD159" s="173"/>
+      <c r="AD159" s="172"/>
       <c r="AU159"/>
       <c r="AV159"/>
       <c r="AW159"/>
@@ -8696,7 +8696,7 @@
       <c r="AZ159"/>
     </row>
     <row r="160" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD160" s="173"/>
+      <c r="AD160" s="172"/>
       <c r="AU160"/>
       <c r="AV160"/>
       <c r="AW160"/>
@@ -8705,7 +8705,7 @@
       <c r="AZ160"/>
     </row>
     <row r="161" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD161" s="173"/>
+      <c r="AD161" s="172"/>
       <c r="AU161"/>
       <c r="AV161"/>
       <c r="AW161"/>
@@ -8714,7 +8714,7 @@
       <c r="AZ161"/>
     </row>
     <row r="162" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD162" s="173"/>
+      <c r="AD162" s="172"/>
       <c r="AU162"/>
       <c r="AV162"/>
       <c r="AW162"/>
@@ -8723,7 +8723,7 @@
       <c r="AZ162"/>
     </row>
     <row r="163" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD163" s="173"/>
+      <c r="AD163" s="172"/>
       <c r="AU163"/>
       <c r="AV163"/>
       <c r="AW163"/>
@@ -8732,7 +8732,7 @@
       <c r="AZ163"/>
     </row>
     <row r="164" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD164" s="173"/>
+      <c r="AD164" s="172"/>
       <c r="AU164"/>
       <c r="AV164"/>
       <c r="AW164"/>
@@ -8741,7 +8741,7 @@
       <c r="AZ164"/>
     </row>
     <row r="165" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD165" s="173"/>
+      <c r="AD165" s="172"/>
       <c r="AU165"/>
       <c r="AV165"/>
       <c r="AW165"/>
@@ -8750,7 +8750,7 @@
       <c r="AZ165"/>
     </row>
     <row r="166" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD166" s="173"/>
+      <c r="AD166" s="172"/>
       <c r="AU166"/>
       <c r="AV166"/>
       <c r="AW166"/>
@@ -8759,7 +8759,7 @@
       <c r="AZ166"/>
     </row>
     <row r="167" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD167" s="173"/>
+      <c r="AD167" s="172"/>
       <c r="AU167"/>
       <c r="AV167"/>
       <c r="AW167"/>
@@ -8768,7 +8768,7 @@
       <c r="AZ167"/>
     </row>
     <row r="168" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD168" s="173"/>
+      <c r="AD168" s="172"/>
       <c r="AU168"/>
       <c r="AV168"/>
       <c r="AW168"/>
@@ -8777,7 +8777,7 @@
       <c r="AZ168"/>
     </row>
     <row r="169" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD169" s="173"/>
+      <c r="AD169" s="172"/>
       <c r="AU169"/>
       <c r="AV169"/>
       <c r="AW169"/>
@@ -8786,7 +8786,7 @@
       <c r="AZ169"/>
     </row>
     <row r="170" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD170" s="173"/>
+      <c r="AD170" s="172"/>
       <c r="AU170"/>
       <c r="AV170"/>
       <c r="AW170"/>
@@ -8795,7 +8795,7 @@
       <c r="AZ170"/>
     </row>
     <row r="171" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD171" s="173"/>
+      <c r="AD171" s="172"/>
       <c r="AU171"/>
       <c r="AV171"/>
       <c r="AW171"/>
@@ -8804,7 +8804,7 @@
       <c r="AZ171"/>
     </row>
     <row r="172" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD172" s="173"/>
+      <c r="AD172" s="172"/>
       <c r="AU172"/>
       <c r="AV172"/>
       <c r="AW172"/>
@@ -8813,7 +8813,7 @@
       <c r="AZ172"/>
     </row>
     <row r="173" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD173" s="173"/>
+      <c r="AD173" s="172"/>
       <c r="AU173"/>
       <c r="AV173"/>
       <c r="AW173"/>
@@ -8822,7 +8822,7 @@
       <c r="AZ173"/>
     </row>
     <row r="174" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD174" s="173"/>
+      <c r="AD174" s="172"/>
       <c r="AU174"/>
       <c r="AV174"/>
       <c r="AW174"/>
@@ -8831,7 +8831,7 @@
       <c r="AZ174"/>
     </row>
     <row r="175" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD175" s="173"/>
+      <c r="AD175" s="172"/>
       <c r="AU175"/>
       <c r="AV175"/>
       <c r="AW175"/>
@@ -8840,7 +8840,7 @@
       <c r="AZ175"/>
     </row>
     <row r="176" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD176" s="173"/>
+      <c r="AD176" s="172"/>
       <c r="AU176"/>
       <c r="AV176"/>
       <c r="AW176"/>
@@ -8849,7 +8849,7 @@
       <c r="AZ176"/>
     </row>
     <row r="177" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD177" s="173"/>
+      <c r="AD177" s="172"/>
       <c r="AU177"/>
       <c r="AV177"/>
       <c r="AW177"/>
@@ -8858,7 +8858,7 @@
       <c r="AZ177"/>
     </row>
     <row r="178" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD178" s="173"/>
+      <c r="AD178" s="172"/>
       <c r="AU178"/>
       <c r="AV178"/>
       <c r="AW178"/>
@@ -8867,7 +8867,7 @@
       <c r="AZ178"/>
     </row>
     <row r="179" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD179" s="173"/>
+      <c r="AD179" s="172"/>
       <c r="AU179"/>
       <c r="AV179"/>
       <c r="AW179"/>
@@ -8876,7 +8876,7 @@
       <c r="AZ179"/>
     </row>
     <row r="180" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD180" s="173"/>
+      <c r="AD180" s="172"/>
       <c r="AU180"/>
       <c r="AV180"/>
       <c r="AW180"/>
@@ -8885,7 +8885,7 @@
       <c r="AZ180"/>
     </row>
     <row r="181" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD181" s="173"/>
+      <c r="AD181" s="172"/>
       <c r="AU181"/>
       <c r="AV181"/>
       <c r="AW181"/>
@@ -8894,7 +8894,7 @@
       <c r="AZ181"/>
     </row>
     <row r="182" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD182" s="173"/>
+      <c r="AD182" s="172"/>
       <c r="AU182"/>
       <c r="AV182"/>
       <c r="AW182"/>
@@ -8903,7 +8903,7 @@
       <c r="AZ182"/>
     </row>
     <row r="183" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD183" s="173"/>
+      <c r="AD183" s="172"/>
       <c r="AU183"/>
       <c r="AV183"/>
       <c r="AW183"/>
@@ -8912,7 +8912,7 @@
       <c r="AZ183"/>
     </row>
     <row r="184" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD184" s="173"/>
+      <c r="AD184" s="172"/>
       <c r="AU184"/>
       <c r="AV184"/>
       <c r="AW184"/>
@@ -8921,7 +8921,7 @@
       <c r="AZ184"/>
     </row>
     <row r="185" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD185" s="173"/>
+      <c r="AD185" s="172"/>
       <c r="AU185"/>
       <c r="AV185"/>
       <c r="AW185"/>
@@ -8930,7 +8930,7 @@
       <c r="AZ185"/>
     </row>
     <row r="186" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD186" s="173"/>
+      <c r="AD186" s="172"/>
       <c r="AU186"/>
       <c r="AV186"/>
       <c r="AW186"/>
@@ -8939,7 +8939,7 @@
       <c r="AZ186"/>
     </row>
     <row r="187" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD187" s="173"/>
+      <c r="AD187" s="172"/>
       <c r="AU187"/>
       <c r="AV187"/>
       <c r="AW187"/>
@@ -8948,7 +8948,7 @@
       <c r="AZ187"/>
     </row>
     <row r="188" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD188" s="173"/>
+      <c r="AD188" s="172"/>
       <c r="AU188"/>
       <c r="AV188"/>
       <c r="AW188"/>
@@ -8957,7 +8957,7 @@
       <c r="AZ188"/>
     </row>
     <row r="189" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD189" s="173"/>
+      <c r="AD189" s="172"/>
       <c r="AU189"/>
       <c r="AV189"/>
       <c r="AW189"/>
@@ -8966,7 +8966,7 @@
       <c r="AZ189"/>
     </row>
     <row r="190" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD190" s="173"/>
+      <c r="AD190" s="172"/>
       <c r="AU190"/>
       <c r="AV190"/>
       <c r="AW190"/>
@@ -8975,7 +8975,7 @@
       <c r="AZ190"/>
     </row>
     <row r="191" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD191" s="173"/>
+      <c r="AD191" s="172"/>
       <c r="AU191"/>
       <c r="AV191"/>
       <c r="AW191"/>
@@ -8984,7 +8984,7 @@
       <c r="AZ191"/>
     </row>
     <row r="192" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD192" s="173"/>
+      <c r="AD192" s="172"/>
       <c r="AU192"/>
       <c r="AV192"/>
       <c r="AW192"/>
@@ -8993,7 +8993,7 @@
       <c r="AZ192"/>
     </row>
     <row r="193" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD193" s="173"/>
+      <c r="AD193" s="172"/>
       <c r="AU193"/>
       <c r="AV193"/>
       <c r="AW193"/>
@@ -9002,7 +9002,7 @@
       <c r="AZ193"/>
     </row>
     <row r="194" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD194" s="173"/>
+      <c r="AD194" s="172"/>
       <c r="AU194"/>
       <c r="AV194"/>
       <c r="AW194"/>
@@ -9011,7 +9011,7 @@
       <c r="AZ194"/>
     </row>
     <row r="195" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD195" s="173"/>
+      <c r="AD195" s="172"/>
       <c r="AU195"/>
       <c r="AV195"/>
       <c r="AW195"/>
@@ -9020,7 +9020,7 @@
       <c r="AZ195"/>
     </row>
     <row r="196" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD196" s="173"/>
+      <c r="AD196" s="172"/>
       <c r="AU196"/>
       <c r="AV196"/>
       <c r="AW196"/>
@@ -9029,7 +9029,7 @@
       <c r="AZ196"/>
     </row>
     <row r="197" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD197" s="173"/>
+      <c r="AD197" s="172"/>
       <c r="AU197"/>
       <c r="AV197"/>
       <c r="AW197"/>
@@ -9038,7 +9038,7 @@
       <c r="AZ197"/>
     </row>
     <row r="198" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD198" s="173"/>
+      <c r="AD198" s="172"/>
       <c r="AU198"/>
       <c r="AV198"/>
       <c r="AW198"/>
@@ -9047,7 +9047,7 @@
       <c r="AZ198"/>
     </row>
     <row r="199" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD199" s="173"/>
+      <c r="AD199" s="172"/>
       <c r="AU199"/>
       <c r="AV199"/>
       <c r="AW199"/>
@@ -9056,7 +9056,7 @@
       <c r="AZ199"/>
     </row>
     <row r="200" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD200" s="173"/>
+      <c r="AD200" s="172"/>
       <c r="AU200"/>
       <c r="AV200"/>
       <c r="AW200"/>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -3601,6 +3601,9 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -3621,9 +3624,6 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1662">
@@ -5635,23 +5635,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="166" t="s">
+      <c r="B1" s="167" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="167"/>
-      <c r="L1" s="167"/>
-      <c r="M1" s="167"/>
-      <c r="N1" s="167"/>
-      <c r="O1" s="168"/>
-      <c r="AD1" s="172"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="169"/>
+      <c r="AD1" s="173"/>
       <c r="AU1"/>
       <c r="AV1"/>
       <c r="AW1"/>
@@ -5675,7 +5675,7 @@
       <c r="X2" s="133"/>
       <c r="Y2" s="133"/>
       <c r="Z2" s="133"/>
-      <c r="AD2" s="172"/>
+      <c r="AD2" s="173"/>
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
@@ -5708,7 +5708,7 @@
       <c r="X3" s="133"/>
       <c r="Y3" s="133"/>
       <c r="Z3" s="133"/>
-      <c r="AD3" s="172"/>
+      <c r="AD3" s="173"/>
       <c r="AU3"/>
       <c r="AV3"/>
       <c r="AW3"/>
@@ -5734,18 +5734,18 @@
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="170"/>
-      <c r="R4" s="170"/>
-      <c r="S4" s="170"/>
-      <c r="T4" s="170"/>
-      <c r="U4" s="171"/>
+      <c r="P4" s="170"/>
+      <c r="Q4" s="171"/>
+      <c r="R4" s="171"/>
+      <c r="S4" s="171"/>
+      <c r="T4" s="171"/>
+      <c r="U4" s="172"/>
       <c r="V4" s="133"/>
       <c r="W4" s="133"/>
       <c r="X4" s="133"/>
       <c r="Y4" s="133"/>
       <c r="Z4" s="133"/>
-      <c r="AD4" s="172"/>
+      <c r="AD4" s="173"/>
       <c r="AU4"/>
       <c r="AV4"/>
       <c r="AW4"/>
@@ -5783,7 +5783,7 @@
       <c r="X5" s="133"/>
       <c r="Y5" s="133"/>
       <c r="Z5" s="133"/>
-      <c r="AD5" s="172"/>
+      <c r="AD5" s="173"/>
       <c r="AU5"/>
       <c r="AV5"/>
       <c r="AW5"/>
@@ -5814,7 +5814,7 @@
       <c r="X6" s="134"/>
       <c r="Y6" s="134"/>
       <c r="Z6" s="134"/>
-      <c r="AD6" s="172"/>
+      <c r="AD6" s="173"/>
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6"/>
@@ -5853,7 +5853,7 @@
       <c r="X7" s="131"/>
       <c r="Y7" s="131"/>
       <c r="Z7" s="132"/>
-      <c r="AD7" s="172"/>
+      <c r="AD7" s="173"/>
       <c r="AU7"/>
       <c r="AV7"/>
       <c r="AW7"/>
@@ -5939,7 +5939,7 @@
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
       <c r="AC8" s="30"/>
-      <c r="AD8" s="172"/>
+      <c r="AD8" s="173"/>
       <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8"/>
@@ -6013,7 +6013,7 @@
       <c r="AA9" s="38"/>
       <c r="AB9" s="38"/>
       <c r="AC9" s="39"/>
-      <c r="AD9" s="172"/>
+      <c r="AD9" s="173"/>
       <c r="AU9"/>
       <c r="AV9"/>
       <c r="AW9"/>
@@ -6029,7 +6029,7 @@
       <c r="C10" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="173"/>
+      <c r="D10" s="166"/>
       <c r="E10" s="44"/>
       <c r="F10" s="45" t="s">
         <v>31</v>
@@ -6109,7 +6109,7 @@
       <c r="AA10" s="59"/>
       <c r="AB10" s="59"/>
       <c r="AC10" s="59"/>
-      <c r="AD10" s="172"/>
+      <c r="AD10" s="173"/>
       <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
@@ -6170,7 +6170,7 @@
       <c r="AA11" s="59"/>
       <c r="AB11" s="59"/>
       <c r="AC11" s="59"/>
-      <c r="AD11" s="172"/>
+      <c r="AD11" s="173"/>
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
@@ -6211,7 +6211,7 @@
       <c r="Y12" s="92"/>
       <c r="Z12" s="93"/>
       <c r="AC12" s="94"/>
-      <c r="AD12" s="172"/>
+      <c r="AD12" s="173"/>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
@@ -6247,7 +6247,7 @@
       <c r="Y13"/>
       <c r="Z13"/>
       <c r="AA13"/>
-      <c r="AD13" s="172"/>
+      <c r="AD13" s="173"/>
       <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13"/>
@@ -6291,7 +6291,7 @@
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
-      <c r="AD14" s="172"/>
+      <c r="AD14" s="173"/>
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
@@ -6335,7 +6335,7 @@
       <c r="Y15"/>
       <c r="Z15"/>
       <c r="AA15"/>
-      <c r="AD15" s="172"/>
+      <c r="AD15" s="173"/>
       <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
@@ -6381,7 +6381,7 @@
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
-      <c r="AD16" s="172"/>
+      <c r="AD16" s="173"/>
       <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
@@ -6425,7 +6425,7 @@
       <c r="Y17"/>
       <c r="Z17"/>
       <c r="AA17"/>
-      <c r="AD17" s="172"/>
+      <c r="AD17" s="173"/>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
@@ -6462,7 +6462,7 @@
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
-      <c r="AD18" s="172"/>
+      <c r="AD18" s="173"/>
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18"/>
@@ -6503,7 +6503,7 @@
       <c r="Y19"/>
       <c r="Z19"/>
       <c r="AA19"/>
-      <c r="AD19" s="172"/>
+      <c r="AD19" s="173"/>
       <c r="AU19"/>
       <c r="AV19"/>
       <c r="AW19"/>
@@ -6541,7 +6541,7 @@
       <c r="Y20"/>
       <c r="Z20"/>
       <c r="AA20"/>
-      <c r="AD20" s="172"/>
+      <c r="AD20" s="173"/>
       <c r="AU20"/>
       <c r="AV20"/>
       <c r="AW20"/>
@@ -6579,7 +6579,7 @@
       <c r="Y21"/>
       <c r="Z21"/>
       <c r="AA21"/>
-      <c r="AD21" s="172"/>
+      <c r="AD21" s="173"/>
       <c r="AU21"/>
       <c r="AV21"/>
       <c r="AW21"/>
@@ -6619,7 +6619,7 @@
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
-      <c r="AD22" s="172"/>
+      <c r="AD22" s="173"/>
       <c r="AU22"/>
       <c r="AV22"/>
       <c r="AW22"/>
@@ -6657,7 +6657,7 @@
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23"/>
-      <c r="AD23" s="172"/>
+      <c r="AD23" s="173"/>
       <c r="AU23"/>
       <c r="AV23"/>
       <c r="AW23"/>
@@ -6702,7 +6702,7 @@
       <c r="Y24"/>
       <c r="Z24"/>
       <c r="AA24"/>
-      <c r="AD24" s="172"/>
+      <c r="AD24" s="173"/>
       <c r="AU24"/>
       <c r="AV24"/>
       <c r="AW24"/>
@@ -6743,7 +6743,7 @@
       <c r="Y25"/>
       <c r="Z25"/>
       <c r="AA25"/>
-      <c r="AD25" s="172"/>
+      <c r="AD25" s="173"/>
       <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
@@ -6788,7 +6788,7 @@
       <c r="Y26"/>
       <c r="Z26"/>
       <c r="AA26"/>
-      <c r="AD26" s="172"/>
+      <c r="AD26" s="173"/>
       <c r="AU26"/>
       <c r="AV26"/>
       <c r="AW26"/>
@@ -6829,7 +6829,7 @@
       <c r="Y27"/>
       <c r="Z27"/>
       <c r="AA27"/>
-      <c r="AD27" s="172"/>
+      <c r="AD27" s="173"/>
       <c r="AU27"/>
       <c r="AV27"/>
       <c r="AW27"/>
@@ -6870,7 +6870,7 @@
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28"/>
-      <c r="AD28" s="172"/>
+      <c r="AD28" s="173"/>
       <c r="AU28"/>
       <c r="AV28"/>
       <c r="AW28"/>
@@ -6913,7 +6913,7 @@
       <c r="Y29"/>
       <c r="Z29"/>
       <c r="AA29"/>
-      <c r="AD29" s="172"/>
+      <c r="AD29" s="173"/>
       <c r="AU29"/>
       <c r="AV29"/>
       <c r="AW29"/>
@@ -6954,7 +6954,7 @@
       <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
-      <c r="AD30" s="172"/>
+      <c r="AD30" s="173"/>
       <c r="AU30"/>
       <c r="AV30"/>
       <c r="AW30"/>
@@ -6997,7 +6997,7 @@
       <c r="AA31"/>
       <c r="AB31" s="99"/>
       <c r="AC31" s="99"/>
-      <c r="AD31" s="172"/>
+      <c r="AD31" s="173"/>
       <c r="AE31" s="99"/>
       <c r="AF31" s="99"/>
       <c r="AU31"/>
@@ -7042,7 +7042,7 @@
       <c r="AA32"/>
       <c r="AB32" s="99"/>
       <c r="AC32" s="99"/>
-      <c r="AD32" s="172"/>
+      <c r="AD32" s="173"/>
       <c r="AE32" s="99"/>
       <c r="AF32" s="99"/>
       <c r="AU32"/>
@@ -7063,11 +7063,11 @@
       <c r="F33" s="122"/>
       <c r="G33" s="119"/>
       <c r="H33" s="118" t="s">
-        <v>66</v>
-      </c>
-      <c r="I33" s="157" t="e">
+        <v>67</v>
+      </c>
+      <c r="I33" s="157">
         <f>IF(H33="ДА",I28*16%/365*Длина_сделки,0)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="J33"/>
       <c r="K33"/>
@@ -7089,7 +7089,7 @@
       <c r="AA33"/>
       <c r="AB33" s="99"/>
       <c r="AC33" s="99"/>
-      <c r="AD33" s="172"/>
+      <c r="AD33" s="173"/>
       <c r="AE33" s="99"/>
       <c r="AF33" s="99"/>
       <c r="AU33"/>
@@ -7134,7 +7134,7 @@
       <c r="AA34"/>
       <c r="AB34" s="99"/>
       <c r="AC34" s="99"/>
-      <c r="AD34" s="172"/>
+      <c r="AD34" s="173"/>
       <c r="AE34" s="99"/>
       <c r="AF34" s="99"/>
       <c r="AG34" s="99"/>
@@ -7180,7 +7180,7 @@
       <c r="AA35"/>
       <c r="AB35" s="99"/>
       <c r="AC35" s="99"/>
-      <c r="AD35" s="172"/>
+      <c r="AD35" s="173"/>
       <c r="AE35" s="99"/>
       <c r="AF35" s="99"/>
       <c r="AG35" s="99"/>
@@ -7226,7 +7226,7 @@
       <c r="AA36"/>
       <c r="AB36" s="99"/>
       <c r="AC36" s="99"/>
-      <c r="AD36" s="172"/>
+      <c r="AD36" s="173"/>
       <c r="AE36" s="99"/>
       <c r="AF36" s="99"/>
       <c r="AG36" s="99"/>
@@ -7274,7 +7274,7 @@
       <c r="AA37"/>
       <c r="AB37" s="99"/>
       <c r="AC37" s="99"/>
-      <c r="AD37" s="172"/>
+      <c r="AD37" s="173"/>
       <c r="AE37" s="99"/>
       <c r="AF37" s="99"/>
       <c r="AG37" s="99"/>
@@ -7320,7 +7320,7 @@
       <c r="AA38"/>
       <c r="AB38" s="99"/>
       <c r="AC38" s="99"/>
-      <c r="AD38" s="172"/>
+      <c r="AD38" s="173"/>
       <c r="AE38" s="99"/>
       <c r="AF38" s="99"/>
       <c r="AG38" s="99"/>
@@ -7363,7 +7363,7 @@
       <c r="AA39"/>
       <c r="AB39" s="99"/>
       <c r="AC39" s="99"/>
-      <c r="AD39" s="172"/>
+      <c r="AD39" s="173"/>
       <c r="AE39" s="99"/>
       <c r="AF39" s="99"/>
       <c r="AG39" s="99"/>
@@ -7409,7 +7409,7 @@
       <c r="AA40"/>
       <c r="AB40" s="99"/>
       <c r="AC40" s="99"/>
-      <c r="AD40" s="172"/>
+      <c r="AD40" s="173"/>
       <c r="AE40" s="99"/>
       <c r="AF40" s="99"/>
       <c r="AG40" s="99"/>
@@ -7450,7 +7450,7 @@
       <c r="AA41"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-      <c r="AD41" s="172"/>
+      <c r="AD41" s="173"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
@@ -7490,7 +7490,7 @@
       <c r="AA42"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="172"/>
+      <c r="AD42" s="173"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
@@ -7533,7 +7533,7 @@
       <c r="AA43"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="172"/>
+      <c r="AD43" s="173"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
@@ -7574,7 +7574,7 @@
       <c r="Y44"/>
       <c r="Z44"/>
       <c r="AA44"/>
-      <c r="AD44" s="172"/>
+      <c r="AD44" s="173"/>
       <c r="AU44"/>
       <c r="AV44"/>
       <c r="AW44"/>
@@ -7609,7 +7609,7 @@
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AD45" s="172"/>
+      <c r="AD45" s="173"/>
       <c r="AU45"/>
       <c r="AV45"/>
       <c r="AW45"/>
@@ -7644,7 +7644,7 @@
       <c r="Y46"/>
       <c r="Z46"/>
       <c r="AA46"/>
-      <c r="AD46" s="172"/>
+      <c r="AD46" s="173"/>
       <c r="AU46"/>
       <c r="AV46"/>
       <c r="AW46"/>
@@ -7679,7 +7679,7 @@
       <c r="Y47"/>
       <c r="Z47"/>
       <c r="AA47"/>
-      <c r="AD47" s="172"/>
+      <c r="AD47" s="173"/>
       <c r="AU47"/>
       <c r="AV47"/>
       <c r="AW47"/>
@@ -7688,7 +7688,7 @@
       <c r="AZ47"/>
     </row>
     <row r="48" spans="1:52" ht="11.45" customHeight="1">
-      <c r="AD48" s="172"/>
+      <c r="AD48" s="173"/>
       <c r="AU48"/>
       <c r="AV48"/>
       <c r="AW48"/>
@@ -7697,7 +7697,7 @@
       <c r="AZ48"/>
     </row>
     <row r="49" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD49" s="172"/>
+      <c r="AD49" s="173"/>
       <c r="AU49"/>
       <c r="AV49"/>
       <c r="AW49"/>
@@ -7706,7 +7706,7 @@
       <c r="AZ49"/>
     </row>
     <row r="50" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD50" s="172"/>
+      <c r="AD50" s="173"/>
       <c r="AU50"/>
       <c r="AV50"/>
       <c r="AW50"/>
@@ -7715,7 +7715,7 @@
       <c r="AZ50"/>
     </row>
     <row r="51" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD51" s="172"/>
+      <c r="AD51" s="173"/>
       <c r="AU51"/>
       <c r="AV51"/>
       <c r="AW51"/>
@@ -7724,7 +7724,7 @@
       <c r="AZ51"/>
     </row>
     <row r="52" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD52" s="172"/>
+      <c r="AD52" s="173"/>
       <c r="AU52"/>
       <c r="AV52"/>
       <c r="AW52"/>
@@ -7733,7 +7733,7 @@
       <c r="AZ52"/>
     </row>
     <row r="53" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD53" s="172"/>
+      <c r="AD53" s="173"/>
       <c r="AU53"/>
       <c r="AV53"/>
       <c r="AW53"/>
@@ -7742,7 +7742,7 @@
       <c r="AZ53"/>
     </row>
     <row r="54" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD54" s="172"/>
+      <c r="AD54" s="173"/>
       <c r="AU54"/>
       <c r="AV54"/>
       <c r="AW54"/>
@@ -7751,7 +7751,7 @@
       <c r="AZ54"/>
     </row>
     <row r="55" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD55" s="172"/>
+      <c r="AD55" s="173"/>
       <c r="AU55"/>
       <c r="AV55"/>
       <c r="AW55"/>
@@ -7760,7 +7760,7 @@
       <c r="AZ55"/>
     </row>
     <row r="56" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD56" s="172"/>
+      <c r="AD56" s="173"/>
       <c r="AU56"/>
       <c r="AV56"/>
       <c r="AW56"/>
@@ -7769,7 +7769,7 @@
       <c r="AZ56"/>
     </row>
     <row r="57" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD57" s="172"/>
+      <c r="AD57" s="173"/>
       <c r="AU57"/>
       <c r="AV57"/>
       <c r="AW57"/>
@@ -7778,7 +7778,7 @@
       <c r="AZ57"/>
     </row>
     <row r="58" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD58" s="172"/>
+      <c r="AD58" s="173"/>
       <c r="AU58"/>
       <c r="AV58"/>
       <c r="AW58"/>
@@ -7787,7 +7787,7 @@
       <c r="AZ58"/>
     </row>
     <row r="59" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD59" s="172"/>
+      <c r="AD59" s="173"/>
       <c r="AU59"/>
       <c r="AV59"/>
       <c r="AW59"/>
@@ -7796,7 +7796,7 @@
       <c r="AZ59"/>
     </row>
     <row r="60" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD60" s="172"/>
+      <c r="AD60" s="173"/>
       <c r="AU60"/>
       <c r="AV60"/>
       <c r="AW60"/>
@@ -7805,7 +7805,7 @@
       <c r="AZ60"/>
     </row>
     <row r="61" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD61" s="172"/>
+      <c r="AD61" s="173"/>
       <c r="AU61"/>
       <c r="AV61"/>
       <c r="AW61"/>
@@ -7814,7 +7814,7 @@
       <c r="AZ61"/>
     </row>
     <row r="62" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD62" s="172"/>
+      <c r="AD62" s="173"/>
       <c r="AU62"/>
       <c r="AV62"/>
       <c r="AW62"/>
@@ -7823,7 +7823,7 @@
       <c r="AZ62"/>
     </row>
     <row r="63" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD63" s="172"/>
+      <c r="AD63" s="173"/>
       <c r="AU63"/>
       <c r="AV63"/>
       <c r="AW63"/>
@@ -7832,7 +7832,7 @@
       <c r="AZ63"/>
     </row>
     <row r="64" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD64" s="172"/>
+      <c r="AD64" s="173"/>
       <c r="AU64"/>
       <c r="AV64"/>
       <c r="AW64"/>
@@ -7841,7 +7841,7 @@
       <c r="AZ64"/>
     </row>
     <row r="65" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD65" s="172"/>
+      <c r="AD65" s="173"/>
       <c r="AU65"/>
       <c r="AV65"/>
       <c r="AW65"/>
@@ -7850,7 +7850,7 @@
       <c r="AZ65"/>
     </row>
     <row r="66" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD66" s="172"/>
+      <c r="AD66" s="173"/>
       <c r="AU66"/>
       <c r="AV66"/>
       <c r="AW66"/>
@@ -7859,7 +7859,7 @@
       <c r="AZ66"/>
     </row>
     <row r="67" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD67" s="172"/>
+      <c r="AD67" s="173"/>
       <c r="AU67"/>
       <c r="AV67"/>
       <c r="AW67"/>
@@ -7868,7 +7868,7 @@
       <c r="AZ67"/>
     </row>
     <row r="68" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD68" s="172"/>
+      <c r="AD68" s="173"/>
       <c r="AU68"/>
       <c r="AV68"/>
       <c r="AW68"/>
@@ -7877,7 +7877,7 @@
       <c r="AZ68"/>
     </row>
     <row r="69" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD69" s="172"/>
+      <c r="AD69" s="173"/>
       <c r="AU69"/>
       <c r="AV69"/>
       <c r="AW69"/>
@@ -7886,7 +7886,7 @@
       <c r="AZ69"/>
     </row>
     <row r="70" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD70" s="172"/>
+      <c r="AD70" s="173"/>
       <c r="AU70"/>
       <c r="AV70"/>
       <c r="AW70"/>
@@ -7895,7 +7895,7 @@
       <c r="AZ70"/>
     </row>
     <row r="71" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD71" s="172"/>
+      <c r="AD71" s="173"/>
       <c r="AU71"/>
       <c r="AV71"/>
       <c r="AW71"/>
@@ -7904,7 +7904,7 @@
       <c r="AZ71"/>
     </row>
     <row r="72" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD72" s="172"/>
+      <c r="AD72" s="173"/>
       <c r="AU72"/>
       <c r="AV72"/>
       <c r="AW72"/>
@@ -7913,7 +7913,7 @@
       <c r="AZ72"/>
     </row>
     <row r="73" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD73" s="172"/>
+      <c r="AD73" s="173"/>
       <c r="AU73"/>
       <c r="AV73"/>
       <c r="AW73"/>
@@ -7922,7 +7922,7 @@
       <c r="AZ73"/>
     </row>
     <row r="74" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD74" s="172"/>
+      <c r="AD74" s="173"/>
       <c r="AU74"/>
       <c r="AV74"/>
       <c r="AW74"/>
@@ -7931,7 +7931,7 @@
       <c r="AZ74"/>
     </row>
     <row r="75" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD75" s="172"/>
+      <c r="AD75" s="173"/>
       <c r="AU75"/>
       <c r="AV75"/>
       <c r="AW75"/>
@@ -7940,7 +7940,7 @@
       <c r="AZ75"/>
     </row>
     <row r="76" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD76" s="172"/>
+      <c r="AD76" s="173"/>
       <c r="AU76"/>
       <c r="AV76"/>
       <c r="AW76"/>
@@ -7949,7 +7949,7 @@
       <c r="AZ76"/>
     </row>
     <row r="77" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD77" s="172"/>
+      <c r="AD77" s="173"/>
       <c r="AU77"/>
       <c r="AV77"/>
       <c r="AW77"/>
@@ -7958,7 +7958,7 @@
       <c r="AZ77"/>
     </row>
     <row r="78" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD78" s="172"/>
+      <c r="AD78" s="173"/>
       <c r="AU78"/>
       <c r="AV78"/>
       <c r="AW78"/>
@@ -7967,7 +7967,7 @@
       <c r="AZ78"/>
     </row>
     <row r="79" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD79" s="172"/>
+      <c r="AD79" s="173"/>
       <c r="AU79"/>
       <c r="AV79"/>
       <c r="AW79"/>
@@ -7976,7 +7976,7 @@
       <c r="AZ79"/>
     </row>
     <row r="80" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD80" s="172"/>
+      <c r="AD80" s="173"/>
       <c r="AU80"/>
       <c r="AV80"/>
       <c r="AW80"/>
@@ -7985,7 +7985,7 @@
       <c r="AZ80"/>
     </row>
     <row r="81" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD81" s="172"/>
+      <c r="AD81" s="173"/>
       <c r="AU81"/>
       <c r="AV81"/>
       <c r="AW81"/>
@@ -7994,7 +7994,7 @@
       <c r="AZ81"/>
     </row>
     <row r="82" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD82" s="172"/>
+      <c r="AD82" s="173"/>
       <c r="AU82"/>
       <c r="AV82"/>
       <c r="AW82"/>
@@ -8003,7 +8003,7 @@
       <c r="AZ82"/>
     </row>
     <row r="83" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD83" s="172"/>
+      <c r="AD83" s="173"/>
       <c r="AU83"/>
       <c r="AV83"/>
       <c r="AW83"/>
@@ -8012,7 +8012,7 @@
       <c r="AZ83"/>
     </row>
     <row r="84" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD84" s="172"/>
+      <c r="AD84" s="173"/>
       <c r="AU84"/>
       <c r="AV84"/>
       <c r="AW84"/>
@@ -8021,7 +8021,7 @@
       <c r="AZ84"/>
     </row>
     <row r="85" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD85" s="172"/>
+      <c r="AD85" s="173"/>
       <c r="AU85"/>
       <c r="AV85"/>
       <c r="AW85"/>
@@ -8030,7 +8030,7 @@
       <c r="AZ85"/>
     </row>
     <row r="86" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD86" s="172"/>
+      <c r="AD86" s="173"/>
       <c r="AU86"/>
       <c r="AV86"/>
       <c r="AW86"/>
@@ -8039,7 +8039,7 @@
       <c r="AZ86"/>
     </row>
     <row r="87" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD87" s="172"/>
+      <c r="AD87" s="173"/>
       <c r="AU87"/>
       <c r="AV87"/>
       <c r="AW87"/>
@@ -8048,7 +8048,7 @@
       <c r="AZ87"/>
     </row>
     <row r="88" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD88" s="172"/>
+      <c r="AD88" s="173"/>
       <c r="AU88"/>
       <c r="AV88"/>
       <c r="AW88"/>
@@ -8057,7 +8057,7 @@
       <c r="AZ88"/>
     </row>
     <row r="89" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD89" s="172"/>
+      <c r="AD89" s="173"/>
       <c r="AU89"/>
       <c r="AV89"/>
       <c r="AW89"/>
@@ -8066,7 +8066,7 @@
       <c r="AZ89"/>
     </row>
     <row r="90" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD90" s="172"/>
+      <c r="AD90" s="173"/>
       <c r="AU90"/>
       <c r="AV90"/>
       <c r="AW90"/>
@@ -8075,7 +8075,7 @@
       <c r="AZ90"/>
     </row>
     <row r="91" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD91" s="172"/>
+      <c r="AD91" s="173"/>
       <c r="AU91"/>
       <c r="AV91"/>
       <c r="AW91"/>
@@ -8084,7 +8084,7 @@
       <c r="AZ91"/>
     </row>
     <row r="92" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD92" s="172"/>
+      <c r="AD92" s="173"/>
       <c r="AU92"/>
       <c r="AV92"/>
       <c r="AW92"/>
@@ -8093,7 +8093,7 @@
       <c r="AZ92"/>
     </row>
     <row r="93" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD93" s="172"/>
+      <c r="AD93" s="173"/>
       <c r="AU93"/>
       <c r="AV93"/>
       <c r="AW93"/>
@@ -8102,7 +8102,7 @@
       <c r="AZ93"/>
     </row>
     <row r="94" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD94" s="172"/>
+      <c r="AD94" s="173"/>
       <c r="AU94"/>
       <c r="AV94"/>
       <c r="AW94"/>
@@ -8111,7 +8111,7 @@
       <c r="AZ94"/>
     </row>
     <row r="95" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD95" s="172"/>
+      <c r="AD95" s="173"/>
       <c r="AU95"/>
       <c r="AV95"/>
       <c r="AW95"/>
@@ -8120,7 +8120,7 @@
       <c r="AZ95"/>
     </row>
     <row r="96" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD96" s="172"/>
+      <c r="AD96" s="173"/>
       <c r="AU96"/>
       <c r="AV96"/>
       <c r="AW96"/>
@@ -8129,7 +8129,7 @@
       <c r="AZ96"/>
     </row>
     <row r="97" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD97" s="172"/>
+      <c r="AD97" s="173"/>
       <c r="AU97"/>
       <c r="AV97"/>
       <c r="AW97"/>
@@ -8138,7 +8138,7 @@
       <c r="AZ97"/>
     </row>
     <row r="98" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD98" s="172"/>
+      <c r="AD98" s="173"/>
       <c r="AU98"/>
       <c r="AV98"/>
       <c r="AW98"/>
@@ -8147,7 +8147,7 @@
       <c r="AZ98"/>
     </row>
     <row r="99" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD99" s="172"/>
+      <c r="AD99" s="173"/>
       <c r="AU99"/>
       <c r="AV99"/>
       <c r="AW99"/>
@@ -8156,7 +8156,7 @@
       <c r="AZ99"/>
     </row>
     <row r="100" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD100" s="172"/>
+      <c r="AD100" s="173"/>
       <c r="AU100"/>
       <c r="AV100"/>
       <c r="AW100"/>
@@ -8165,7 +8165,7 @@
       <c r="AZ100"/>
     </row>
     <row r="101" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD101" s="172"/>
+      <c r="AD101" s="173"/>
       <c r="AU101"/>
       <c r="AV101"/>
       <c r="AW101"/>
@@ -8174,7 +8174,7 @@
       <c r="AZ101"/>
     </row>
     <row r="102" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD102" s="172"/>
+      <c r="AD102" s="173"/>
       <c r="AU102"/>
       <c r="AV102"/>
       <c r="AW102"/>
@@ -8183,7 +8183,7 @@
       <c r="AZ102"/>
     </row>
     <row r="103" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD103" s="172"/>
+      <c r="AD103" s="173"/>
       <c r="AU103"/>
       <c r="AV103"/>
       <c r="AW103"/>
@@ -8192,7 +8192,7 @@
       <c r="AZ103"/>
     </row>
     <row r="104" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD104" s="172"/>
+      <c r="AD104" s="173"/>
       <c r="AU104"/>
       <c r="AV104"/>
       <c r="AW104"/>
@@ -8201,7 +8201,7 @@
       <c r="AZ104"/>
     </row>
     <row r="105" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD105" s="172"/>
+      <c r="AD105" s="173"/>
       <c r="AU105"/>
       <c r="AV105"/>
       <c r="AW105"/>
@@ -8210,7 +8210,7 @@
       <c r="AZ105"/>
     </row>
     <row r="106" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD106" s="172"/>
+      <c r="AD106" s="173"/>
       <c r="AU106"/>
       <c r="AV106"/>
       <c r="AW106"/>
@@ -8219,7 +8219,7 @@
       <c r="AZ106"/>
     </row>
     <row r="107" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD107" s="172"/>
+      <c r="AD107" s="173"/>
       <c r="AU107"/>
       <c r="AV107"/>
       <c r="AW107"/>
@@ -8228,7 +8228,7 @@
       <c r="AZ107"/>
     </row>
     <row r="108" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD108" s="172"/>
+      <c r="AD108" s="173"/>
       <c r="AU108"/>
       <c r="AV108"/>
       <c r="AW108"/>
@@ -8237,7 +8237,7 @@
       <c r="AZ108"/>
     </row>
     <row r="109" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD109" s="172"/>
+      <c r="AD109" s="173"/>
       <c r="AU109"/>
       <c r="AV109"/>
       <c r="AW109"/>
@@ -8246,7 +8246,7 @@
       <c r="AZ109"/>
     </row>
     <row r="110" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD110" s="172"/>
+      <c r="AD110" s="173"/>
       <c r="AU110"/>
       <c r="AV110"/>
       <c r="AW110"/>
@@ -8255,7 +8255,7 @@
       <c r="AZ110"/>
     </row>
     <row r="111" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD111" s="172"/>
+      <c r="AD111" s="173"/>
       <c r="AU111"/>
       <c r="AV111"/>
       <c r="AW111"/>
@@ -8264,7 +8264,7 @@
       <c r="AZ111"/>
     </row>
     <row r="112" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD112" s="172"/>
+      <c r="AD112" s="173"/>
       <c r="AU112"/>
       <c r="AV112"/>
       <c r="AW112"/>
@@ -8273,7 +8273,7 @@
       <c r="AZ112"/>
     </row>
     <row r="113" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD113" s="172"/>
+      <c r="AD113" s="173"/>
       <c r="AU113"/>
       <c r="AV113"/>
       <c r="AW113"/>
@@ -8282,7 +8282,7 @@
       <c r="AZ113"/>
     </row>
     <row r="114" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD114" s="172"/>
+      <c r="AD114" s="173"/>
       <c r="AU114"/>
       <c r="AV114"/>
       <c r="AW114"/>
@@ -8291,7 +8291,7 @@
       <c r="AZ114"/>
     </row>
     <row r="115" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD115" s="172"/>
+      <c r="AD115" s="173"/>
       <c r="AU115"/>
       <c r="AV115"/>
       <c r="AW115"/>
@@ -8300,7 +8300,7 @@
       <c r="AZ115"/>
     </row>
     <row r="116" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD116" s="172"/>
+      <c r="AD116" s="173"/>
       <c r="AU116"/>
       <c r="AV116"/>
       <c r="AW116"/>
@@ -8309,7 +8309,7 @@
       <c r="AZ116"/>
     </row>
     <row r="117" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD117" s="172"/>
+      <c r="AD117" s="173"/>
       <c r="AU117"/>
       <c r="AV117"/>
       <c r="AW117"/>
@@ -8318,7 +8318,7 @@
       <c r="AZ117"/>
     </row>
     <row r="118" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD118" s="172"/>
+      <c r="AD118" s="173"/>
       <c r="AU118"/>
       <c r="AV118"/>
       <c r="AW118"/>
@@ -8327,7 +8327,7 @@
       <c r="AZ118"/>
     </row>
     <row r="119" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD119" s="172"/>
+      <c r="AD119" s="173"/>
       <c r="AU119"/>
       <c r="AV119"/>
       <c r="AW119"/>
@@ -8336,7 +8336,7 @@
       <c r="AZ119"/>
     </row>
     <row r="120" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD120" s="172"/>
+      <c r="AD120" s="173"/>
       <c r="AU120"/>
       <c r="AV120"/>
       <c r="AW120"/>
@@ -8345,7 +8345,7 @@
       <c r="AZ120"/>
     </row>
     <row r="121" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD121" s="172"/>
+      <c r="AD121" s="173"/>
       <c r="AU121"/>
       <c r="AV121"/>
       <c r="AW121"/>
@@ -8354,7 +8354,7 @@
       <c r="AZ121"/>
     </row>
     <row r="122" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD122" s="172"/>
+      <c r="AD122" s="173"/>
       <c r="AU122"/>
       <c r="AV122"/>
       <c r="AW122"/>
@@ -8363,7 +8363,7 @@
       <c r="AZ122"/>
     </row>
     <row r="123" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD123" s="172"/>
+      <c r="AD123" s="173"/>
       <c r="AU123"/>
       <c r="AV123"/>
       <c r="AW123"/>
@@ -8372,7 +8372,7 @@
       <c r="AZ123"/>
     </row>
     <row r="124" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD124" s="172"/>
+      <c r="AD124" s="173"/>
       <c r="AU124"/>
       <c r="AV124"/>
       <c r="AW124"/>
@@ -8381,7 +8381,7 @@
       <c r="AZ124"/>
     </row>
     <row r="125" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD125" s="172"/>
+      <c r="AD125" s="173"/>
       <c r="AU125"/>
       <c r="AV125"/>
       <c r="AW125"/>
@@ -8390,7 +8390,7 @@
       <c r="AZ125"/>
     </row>
     <row r="126" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD126" s="172"/>
+      <c r="AD126" s="173"/>
       <c r="AU126"/>
       <c r="AV126"/>
       <c r="AW126"/>
@@ -8399,7 +8399,7 @@
       <c r="AZ126"/>
     </row>
     <row r="127" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD127" s="172"/>
+      <c r="AD127" s="173"/>
       <c r="AU127"/>
       <c r="AV127"/>
       <c r="AW127"/>
@@ -8408,7 +8408,7 @@
       <c r="AZ127"/>
     </row>
     <row r="128" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD128" s="172"/>
+      <c r="AD128" s="173"/>
       <c r="AU128"/>
       <c r="AV128"/>
       <c r="AW128"/>
@@ -8417,7 +8417,7 @@
       <c r="AZ128"/>
     </row>
     <row r="129" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD129" s="172"/>
+      <c r="AD129" s="173"/>
       <c r="AU129"/>
       <c r="AV129"/>
       <c r="AW129"/>
@@ -8426,7 +8426,7 @@
       <c r="AZ129"/>
     </row>
     <row r="130" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD130" s="172"/>
+      <c r="AD130" s="173"/>
       <c r="AU130"/>
       <c r="AV130"/>
       <c r="AW130"/>
@@ -8435,7 +8435,7 @@
       <c r="AZ130"/>
     </row>
     <row r="131" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD131" s="172"/>
+      <c r="AD131" s="173"/>
       <c r="AU131"/>
       <c r="AV131"/>
       <c r="AW131"/>
@@ -8444,7 +8444,7 @@
       <c r="AZ131"/>
     </row>
     <row r="132" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD132" s="172"/>
+      <c r="AD132" s="173"/>
       <c r="AU132"/>
       <c r="AV132"/>
       <c r="AW132"/>
@@ -8453,7 +8453,7 @@
       <c r="AZ132"/>
     </row>
     <row r="133" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD133" s="172"/>
+      <c r="AD133" s="173"/>
       <c r="AU133"/>
       <c r="AV133"/>
       <c r="AW133"/>
@@ -8462,7 +8462,7 @@
       <c r="AZ133"/>
     </row>
     <row r="134" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD134" s="172"/>
+      <c r="AD134" s="173"/>
       <c r="AU134"/>
       <c r="AV134"/>
       <c r="AW134"/>
@@ -8471,7 +8471,7 @@
       <c r="AZ134"/>
     </row>
     <row r="135" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD135" s="172"/>
+      <c r="AD135" s="173"/>
       <c r="AU135"/>
       <c r="AV135"/>
       <c r="AW135"/>
@@ -8480,7 +8480,7 @@
       <c r="AZ135"/>
     </row>
     <row r="136" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD136" s="172"/>
+      <c r="AD136" s="173"/>
       <c r="AU136"/>
       <c r="AV136"/>
       <c r="AW136"/>
@@ -8489,7 +8489,7 @@
       <c r="AZ136"/>
     </row>
     <row r="137" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD137" s="172"/>
+      <c r="AD137" s="173"/>
       <c r="AU137"/>
       <c r="AV137"/>
       <c r="AW137"/>
@@ -8498,7 +8498,7 @@
       <c r="AZ137"/>
     </row>
     <row r="138" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD138" s="172"/>
+      <c r="AD138" s="173"/>
       <c r="AU138"/>
       <c r="AV138"/>
       <c r="AW138"/>
@@ -8507,7 +8507,7 @@
       <c r="AZ138"/>
     </row>
     <row r="139" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD139" s="172"/>
+      <c r="AD139" s="173"/>
       <c r="AU139"/>
       <c r="AV139"/>
       <c r="AW139"/>
@@ -8516,7 +8516,7 @@
       <c r="AZ139"/>
     </row>
     <row r="140" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD140" s="172"/>
+      <c r="AD140" s="173"/>
       <c r="AU140"/>
       <c r="AV140"/>
       <c r="AW140"/>
@@ -8525,7 +8525,7 @@
       <c r="AZ140"/>
     </row>
     <row r="141" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD141" s="172"/>
+      <c r="AD141" s="173"/>
       <c r="AU141"/>
       <c r="AV141"/>
       <c r="AW141"/>
@@ -8534,7 +8534,7 @@
       <c r="AZ141"/>
     </row>
     <row r="142" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD142" s="172"/>
+      <c r="AD142" s="173"/>
       <c r="AU142"/>
       <c r="AV142"/>
       <c r="AW142"/>
@@ -8543,7 +8543,7 @@
       <c r="AZ142"/>
     </row>
     <row r="143" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD143" s="172"/>
+      <c r="AD143" s="173"/>
       <c r="AU143"/>
       <c r="AV143"/>
       <c r="AW143"/>
@@ -8552,7 +8552,7 @@
       <c r="AZ143"/>
     </row>
     <row r="144" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD144" s="172"/>
+      <c r="AD144" s="173"/>
       <c r="AU144"/>
       <c r="AV144"/>
       <c r="AW144"/>
@@ -8561,7 +8561,7 @@
       <c r="AZ144"/>
     </row>
     <row r="145" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD145" s="172"/>
+      <c r="AD145" s="173"/>
       <c r="AU145"/>
       <c r="AV145"/>
       <c r="AW145"/>
@@ -8570,7 +8570,7 @@
       <c r="AZ145"/>
     </row>
     <row r="146" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD146" s="172"/>
+      <c r="AD146" s="173"/>
       <c r="AU146"/>
       <c r="AV146"/>
       <c r="AW146"/>
@@ -8579,7 +8579,7 @@
       <c r="AZ146"/>
     </row>
     <row r="147" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD147" s="172"/>
+      <c r="AD147" s="173"/>
       <c r="AU147"/>
       <c r="AV147"/>
       <c r="AW147"/>
@@ -8588,7 +8588,7 @@
       <c r="AZ147"/>
     </row>
     <row r="148" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD148" s="172"/>
+      <c r="AD148" s="173"/>
       <c r="AU148"/>
       <c r="AV148"/>
       <c r="AW148"/>
@@ -8597,7 +8597,7 @@
       <c r="AZ148"/>
     </row>
     <row r="149" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD149" s="172"/>
+      <c r="AD149" s="173"/>
       <c r="AU149"/>
       <c r="AV149"/>
       <c r="AW149"/>
@@ -8606,7 +8606,7 @@
       <c r="AZ149"/>
     </row>
     <row r="150" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD150" s="172"/>
+      <c r="AD150" s="173"/>
       <c r="AU150"/>
       <c r="AV150"/>
       <c r="AW150"/>
@@ -8615,7 +8615,7 @@
       <c r="AZ150"/>
     </row>
     <row r="151" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD151" s="172"/>
+      <c r="AD151" s="173"/>
       <c r="AU151"/>
       <c r="AV151"/>
       <c r="AW151"/>
@@ -8624,7 +8624,7 @@
       <c r="AZ151"/>
     </row>
     <row r="152" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD152" s="172"/>
+      <c r="AD152" s="173"/>
       <c r="AU152"/>
       <c r="AV152"/>
       <c r="AW152"/>
@@ -8633,7 +8633,7 @@
       <c r="AZ152"/>
     </row>
     <row r="153" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD153" s="172"/>
+      <c r="AD153" s="173"/>
       <c r="AU153"/>
       <c r="AV153"/>
       <c r="AW153"/>
@@ -8642,7 +8642,7 @@
       <c r="AZ153"/>
     </row>
     <row r="154" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD154" s="172"/>
+      <c r="AD154" s="173"/>
       <c r="AU154"/>
       <c r="AV154"/>
       <c r="AW154"/>
@@ -8651,7 +8651,7 @@
       <c r="AZ154"/>
     </row>
     <row r="155" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD155" s="172"/>
+      <c r="AD155" s="173"/>
       <c r="AU155"/>
       <c r="AV155"/>
       <c r="AW155"/>
@@ -8660,7 +8660,7 @@
       <c r="AZ155"/>
     </row>
     <row r="156" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD156" s="172"/>
+      <c r="AD156" s="173"/>
       <c r="AU156"/>
       <c r="AV156"/>
       <c r="AW156"/>
@@ -8669,7 +8669,7 @@
       <c r="AZ156"/>
     </row>
     <row r="157" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD157" s="172"/>
+      <c r="AD157" s="173"/>
       <c r="AU157"/>
       <c r="AV157"/>
       <c r="AW157"/>
@@ -8678,7 +8678,7 @@
       <c r="AZ157"/>
     </row>
     <row r="158" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD158" s="172"/>
+      <c r="AD158" s="173"/>
       <c r="AU158"/>
       <c r="AV158"/>
       <c r="AW158"/>
@@ -8687,7 +8687,7 @@
       <c r="AZ158"/>
     </row>
     <row r="159" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD159" s="172"/>
+      <c r="AD159" s="173"/>
       <c r="AU159"/>
       <c r="AV159"/>
       <c r="AW159"/>
@@ -8696,7 +8696,7 @@
       <c r="AZ159"/>
     </row>
     <row r="160" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD160" s="172"/>
+      <c r="AD160" s="173"/>
       <c r="AU160"/>
       <c r="AV160"/>
       <c r="AW160"/>
@@ -8705,7 +8705,7 @@
       <c r="AZ160"/>
     </row>
     <row r="161" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD161" s="172"/>
+      <c r="AD161" s="173"/>
       <c r="AU161"/>
       <c r="AV161"/>
       <c r="AW161"/>
@@ -8714,7 +8714,7 @@
       <c r="AZ161"/>
     </row>
     <row r="162" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD162" s="172"/>
+      <c r="AD162" s="173"/>
       <c r="AU162"/>
       <c r="AV162"/>
       <c r="AW162"/>
@@ -8723,7 +8723,7 @@
       <c r="AZ162"/>
     </row>
     <row r="163" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD163" s="172"/>
+      <c r="AD163" s="173"/>
       <c r="AU163"/>
       <c r="AV163"/>
       <c r="AW163"/>
@@ -8732,7 +8732,7 @@
       <c r="AZ163"/>
     </row>
     <row r="164" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD164" s="172"/>
+      <c r="AD164" s="173"/>
       <c r="AU164"/>
       <c r="AV164"/>
       <c r="AW164"/>
@@ -8741,7 +8741,7 @@
       <c r="AZ164"/>
     </row>
     <row r="165" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD165" s="172"/>
+      <c r="AD165" s="173"/>
       <c r="AU165"/>
       <c r="AV165"/>
       <c r="AW165"/>
@@ -8750,7 +8750,7 @@
       <c r="AZ165"/>
     </row>
     <row r="166" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD166" s="172"/>
+      <c r="AD166" s="173"/>
       <c r="AU166"/>
       <c r="AV166"/>
       <c r="AW166"/>
@@ -8759,7 +8759,7 @@
       <c r="AZ166"/>
     </row>
     <row r="167" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD167" s="172"/>
+      <c r="AD167" s="173"/>
       <c r="AU167"/>
       <c r="AV167"/>
       <c r="AW167"/>
@@ -8768,7 +8768,7 @@
       <c r="AZ167"/>
     </row>
     <row r="168" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD168" s="172"/>
+      <c r="AD168" s="173"/>
       <c r="AU168"/>
       <c r="AV168"/>
       <c r="AW168"/>
@@ -8777,7 +8777,7 @@
       <c r="AZ168"/>
     </row>
     <row r="169" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD169" s="172"/>
+      <c r="AD169" s="173"/>
       <c r="AU169"/>
       <c r="AV169"/>
       <c r="AW169"/>
@@ -8786,7 +8786,7 @@
       <c r="AZ169"/>
     </row>
     <row r="170" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD170" s="172"/>
+      <c r="AD170" s="173"/>
       <c r="AU170"/>
       <c r="AV170"/>
       <c r="AW170"/>
@@ -8795,7 +8795,7 @@
       <c r="AZ170"/>
     </row>
     <row r="171" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD171" s="172"/>
+      <c r="AD171" s="173"/>
       <c r="AU171"/>
       <c r="AV171"/>
       <c r="AW171"/>
@@ -8804,7 +8804,7 @@
       <c r="AZ171"/>
     </row>
     <row r="172" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD172" s="172"/>
+      <c r="AD172" s="173"/>
       <c r="AU172"/>
       <c r="AV172"/>
       <c r="AW172"/>
@@ -8813,7 +8813,7 @@
       <c r="AZ172"/>
     </row>
     <row r="173" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD173" s="172"/>
+      <c r="AD173" s="173"/>
       <c r="AU173"/>
       <c r="AV173"/>
       <c r="AW173"/>
@@ -8822,7 +8822,7 @@
       <c r="AZ173"/>
     </row>
     <row r="174" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD174" s="172"/>
+      <c r="AD174" s="173"/>
       <c r="AU174"/>
       <c r="AV174"/>
       <c r="AW174"/>
@@ -8831,7 +8831,7 @@
       <c r="AZ174"/>
     </row>
     <row r="175" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD175" s="172"/>
+      <c r="AD175" s="173"/>
       <c r="AU175"/>
       <c r="AV175"/>
       <c r="AW175"/>
@@ -8840,7 +8840,7 @@
       <c r="AZ175"/>
     </row>
     <row r="176" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD176" s="172"/>
+      <c r="AD176" s="173"/>
       <c r="AU176"/>
       <c r="AV176"/>
       <c r="AW176"/>
@@ -8849,7 +8849,7 @@
       <c r="AZ176"/>
     </row>
     <row r="177" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD177" s="172"/>
+      <c r="AD177" s="173"/>
       <c r="AU177"/>
       <c r="AV177"/>
       <c r="AW177"/>
@@ -8858,7 +8858,7 @@
       <c r="AZ177"/>
     </row>
     <row r="178" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD178" s="172"/>
+      <c r="AD178" s="173"/>
       <c r="AU178"/>
       <c r="AV178"/>
       <c r="AW178"/>
@@ -8867,7 +8867,7 @@
       <c r="AZ178"/>
     </row>
     <row r="179" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD179" s="172"/>
+      <c r="AD179" s="173"/>
       <c r="AU179"/>
       <c r="AV179"/>
       <c r="AW179"/>
@@ -8876,7 +8876,7 @@
       <c r="AZ179"/>
     </row>
     <row r="180" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD180" s="172"/>
+      <c r="AD180" s="173"/>
       <c r="AU180"/>
       <c r="AV180"/>
       <c r="AW180"/>
@@ -8885,7 +8885,7 @@
       <c r="AZ180"/>
     </row>
     <row r="181" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD181" s="172"/>
+      <c r="AD181" s="173"/>
       <c r="AU181"/>
       <c r="AV181"/>
       <c r="AW181"/>
@@ -8894,7 +8894,7 @@
       <c r="AZ181"/>
     </row>
     <row r="182" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD182" s="172"/>
+      <c r="AD182" s="173"/>
       <c r="AU182"/>
       <c r="AV182"/>
       <c r="AW182"/>
@@ -8903,7 +8903,7 @@
       <c r="AZ182"/>
     </row>
     <row r="183" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD183" s="172"/>
+      <c r="AD183" s="173"/>
       <c r="AU183"/>
       <c r="AV183"/>
       <c r="AW183"/>
@@ -8912,7 +8912,7 @@
       <c r="AZ183"/>
     </row>
     <row r="184" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD184" s="172"/>
+      <c r="AD184" s="173"/>
       <c r="AU184"/>
       <c r="AV184"/>
       <c r="AW184"/>
@@ -8921,7 +8921,7 @@
       <c r="AZ184"/>
     </row>
     <row r="185" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD185" s="172"/>
+      <c r="AD185" s="173"/>
       <c r="AU185"/>
       <c r="AV185"/>
       <c r="AW185"/>
@@ -8930,7 +8930,7 @@
       <c r="AZ185"/>
     </row>
     <row r="186" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD186" s="172"/>
+      <c r="AD186" s="173"/>
       <c r="AU186"/>
       <c r="AV186"/>
       <c r="AW186"/>
@@ -8939,7 +8939,7 @@
       <c r="AZ186"/>
     </row>
     <row r="187" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD187" s="172"/>
+      <c r="AD187" s="173"/>
       <c r="AU187"/>
       <c r="AV187"/>
       <c r="AW187"/>
@@ -8948,7 +8948,7 @@
       <c r="AZ187"/>
     </row>
     <row r="188" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD188" s="172"/>
+      <c r="AD188" s="173"/>
       <c r="AU188"/>
       <c r="AV188"/>
       <c r="AW188"/>
@@ -8957,7 +8957,7 @@
       <c r="AZ188"/>
     </row>
     <row r="189" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD189" s="172"/>
+      <c r="AD189" s="173"/>
       <c r="AU189"/>
       <c r="AV189"/>
       <c r="AW189"/>
@@ -8966,7 +8966,7 @@
       <c r="AZ189"/>
     </row>
     <row r="190" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD190" s="172"/>
+      <c r="AD190" s="173"/>
       <c r="AU190"/>
       <c r="AV190"/>
       <c r="AW190"/>
@@ -8975,7 +8975,7 @@
       <c r="AZ190"/>
     </row>
     <row r="191" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD191" s="172"/>
+      <c r="AD191" s="173"/>
       <c r="AU191"/>
       <c r="AV191"/>
       <c r="AW191"/>
@@ -8984,7 +8984,7 @@
       <c r="AZ191"/>
     </row>
     <row r="192" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD192" s="172"/>
+      <c r="AD192" s="173"/>
       <c r="AU192"/>
       <c r="AV192"/>
       <c r="AW192"/>
@@ -8993,7 +8993,7 @@
       <c r="AZ192"/>
     </row>
     <row r="193" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD193" s="172"/>
+      <c r="AD193" s="173"/>
       <c r="AU193"/>
       <c r="AV193"/>
       <c r="AW193"/>
@@ -9002,7 +9002,7 @@
       <c r="AZ193"/>
     </row>
     <row r="194" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD194" s="172"/>
+      <c r="AD194" s="173"/>
       <c r="AU194"/>
       <c r="AV194"/>
       <c r="AW194"/>
@@ -9011,7 +9011,7 @@
       <c r="AZ194"/>
     </row>
     <row r="195" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD195" s="172"/>
+      <c r="AD195" s="173"/>
       <c r="AU195"/>
       <c r="AV195"/>
       <c r="AW195"/>
@@ -9020,7 +9020,7 @@
       <c r="AZ195"/>
     </row>
     <row r="196" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD196" s="172"/>
+      <c r="AD196" s="173"/>
       <c r="AU196"/>
       <c r="AV196"/>
       <c r="AW196"/>
@@ -9029,7 +9029,7 @@
       <c r="AZ196"/>
     </row>
     <row r="197" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD197" s="172"/>
+      <c r="AD197" s="173"/>
       <c r="AU197"/>
       <c r="AV197"/>
       <c r="AW197"/>
@@ -9038,7 +9038,7 @@
       <c r="AZ197"/>
     </row>
     <row r="198" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD198" s="172"/>
+      <c r="AD198" s="173"/>
       <c r="AU198"/>
       <c r="AV198"/>
       <c r="AW198"/>
@@ -9047,7 +9047,7 @@
       <c r="AZ198"/>
     </row>
     <row r="199" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD199" s="172"/>
+      <c r="AD199" s="173"/>
       <c r="AU199"/>
       <c r="AV199"/>
       <c r="AW199"/>
@@ -9056,7 +9056,7 @@
       <c r="AZ199"/>
     </row>
     <row r="200" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD200" s="172"/>
+      <c r="AD200" s="173"/>
       <c r="AU200"/>
       <c r="AV200"/>
       <c r="AW200"/>
@@ -11654,7 +11654,7 @@
       <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
       <formula1>$D$43:$D$44</formula1>
     </dataValidation>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\kp_generator\templates_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeck\kp_generator\templates_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205E0639-8186-4F44-8352-437FC2ED41AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="294"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="294" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="расчет" sheetId="4" r:id="rId1"/>
@@ -18,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$36</definedName>
     <definedName name="Длина_сделки">расчет!$K$15</definedName>
   </definedNames>
-  <calcPr calcId="162913" fullPrecision="0"/>
+  <calcPr calcId="191029" fullPrecision="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -315,31 +318,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="23">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="[$-415]General"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="[$$-409]#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* &quot;-&quot;??[$€-1]_-"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="[$¥-478]#,##0.00"/>
-    <numFmt numFmtId="175" formatCode="_ [$¥-478]* #,##0_ ;_ [$¥-478]* \-#,##0_ ;_ [$¥-478]* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="[$¥-478]#,##0"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="178" formatCode="[$¥-804]#,##0.00"/>
-    <numFmt numFmtId="179" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
-    <numFmt numFmtId="180" formatCode="[$¥-478]#,##0.0"/>
-    <numFmt numFmtId="181" formatCode="#,##0.00\ &quot;₽&quot;;[Red]#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="182" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
-    <numFmt numFmtId="183" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="184" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-415]General"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* &quot;-&quot;??[$€-1]_-"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="[$¥-478]#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="_ [$¥-478]* #,##0_ ;_ [$¥-478]* \-#,##0_ ;_ [$¥-478]* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="[$¥-478]#,##0"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="179" formatCode="[$¥-804]#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="181" formatCode="[$¥-478]#,##0.0"/>
+    <numFmt numFmtId="182" formatCode="#,##0.00\ &quot;₽&quot;;[Red]#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="183" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
+    <numFmt numFmtId="184" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="185" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -902,24 +905,24 @@
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3">
@@ -937,17 +940,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -958,10 +961,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -973,23 +976,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1007,7 +1010,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1114,21 +1117,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1154,7 +1157,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1169,7 +1172,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -1195,23 +1198,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
@@ -1225,7 +1228,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -1233,12 +1236,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
@@ -1254,7 +1257,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1265,49 +1268,49 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1453,11 +1456,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1465,22 +1468,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -1503,17 +1506,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1548,201 +1551,201 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
@@ -1750,12 +1753,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1782,77 +1785,77 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1887,69 +1890,69 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1959,13 +1962,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -1983,7 +1986,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -2000,7 +2003,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2017,7 +2020,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2062,7 +2065,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -2073,119 +2076,119 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
@@ -2346,15 +2349,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
@@ -2488,7 +2491,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
@@ -2503,7 +2506,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2533,7 +2536,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2590,39 +2593,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2648,11 +2651,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2681,407 +2684,407 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3">
@@ -3102,7 +3105,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="3">
@@ -3242,7 +3245,7 @@
     <xf numFmtId="0" fontId="32" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3264,10 +3267,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3276,34 +3279,34 @@
     <xf numFmtId="0" fontId="38" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="38" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="38" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="37" fillId="3" borderId="14" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="37" fillId="3" borderId="14" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3316,10 +3319,10 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="32" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3328,28 +3331,28 @@
     <xf numFmtId="3" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="39" fillId="0" borderId="13" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="39" fillId="0" borderId="13" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="39" fillId="0" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="39" fillId="0" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="32" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="32" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="14" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3369,13 +3372,13 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="32" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="0" borderId="10" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="39" fillId="0" borderId="10" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="32" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3384,31 +3387,31 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="32" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="3" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3549,7 +3552,7 @@
     <xf numFmtId="1" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3568,19 +3571,19 @@
     <xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="37" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="37" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="37" fillId="4" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3593,7 +3596,7 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -3604,6 +3607,9 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -3622,1673 +3628,1670 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1662">
-    <cellStyle name="Excel Built-in Normal" xfId="78"/>
-    <cellStyle name="Excel Built-in Normal 2" xfId="95"/>
-    <cellStyle name="Excel Built-in Normal 2 2" xfId="89"/>
-    <cellStyle name="Excel Built-in Normal 3" xfId="96"/>
-    <cellStyle name="Excel Built-in Normal 4" xfId="97"/>
-    <cellStyle name="Excel Built-in Normal 4 2" xfId="81"/>
-    <cellStyle name="Excel Built-in Normal 5" xfId="76"/>
-    <cellStyle name="Excel Built-in Normal 5 2" xfId="77"/>
-    <cellStyle name="Гиперссылка 2" xfId="48"/>
-    <cellStyle name="Гиперссылка 2 10" xfId="94"/>
-    <cellStyle name="Гиперссылка 2 2" xfId="98"/>
-    <cellStyle name="Гиперссылка 2 2 2" xfId="99"/>
-    <cellStyle name="Гиперссылка 2 2 2 2" xfId="84"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2" xfId="104"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 2" xfId="83"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 3" xfId="88"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 4" xfId="108"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 5" xfId="113"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 3" xfId="114"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 4" xfId="116"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 5" xfId="118"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 6" xfId="120"/>
-    <cellStyle name="Гиперссылка 2 2 2 3" xfId="121"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 2" xfId="122"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 3" xfId="123"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 4" xfId="125"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 5" xfId="127"/>
-    <cellStyle name="Гиперссылка 2 2 2 4" xfId="128"/>
-    <cellStyle name="Гиперссылка 2 2 2 5" xfId="130"/>
-    <cellStyle name="Гиперссылка 2 2 2 6" xfId="132"/>
-    <cellStyle name="Гиперссылка 2 2 2 7" xfId="134"/>
-    <cellStyle name="Гиперссылка 2 2 3" xfId="136"/>
-    <cellStyle name="Гиперссылка 2 2 3 2" xfId="138"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 2" xfId="143"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 3" xfId="145"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 4" xfId="147"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 5" xfId="149"/>
-    <cellStyle name="Гиперссылка 2 2 3 3" xfId="151"/>
-    <cellStyle name="Гиперссылка 2 2 3 4" xfId="158"/>
-    <cellStyle name="Гиперссылка 2 2 3 5" xfId="163"/>
-    <cellStyle name="Гиперссылка 2 2 3 6" xfId="166"/>
-    <cellStyle name="Гиперссылка 2 2 4" xfId="168"/>
-    <cellStyle name="Гиперссылка 2 2 4 2" xfId="172"/>
-    <cellStyle name="Гиперссылка 2 2 4 3" xfId="176"/>
-    <cellStyle name="Гиперссылка 2 2 4 4" xfId="177"/>
-    <cellStyle name="Гиперссылка 2 2 4 5" xfId="178"/>
-    <cellStyle name="Гиперссылка 2 2 5" xfId="180"/>
-    <cellStyle name="Гиперссылка 2 2 6" xfId="183"/>
-    <cellStyle name="Гиперссылка 2 2 7" xfId="185"/>
-    <cellStyle name="Гиперссылка 2 2 8" xfId="186"/>
-    <cellStyle name="Гиперссылка 2 3" xfId="189"/>
-    <cellStyle name="Гиперссылка 2 3 2" xfId="190"/>
-    <cellStyle name="Гиперссылка 2 3 2 2" xfId="193"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 2" xfId="36"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 3" xfId="196"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 4" xfId="199"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 5" xfId="201"/>
-    <cellStyle name="Гиперссылка 2 3 2 3" xfId="203"/>
-    <cellStyle name="Гиперссылка 2 3 2 4" xfId="205"/>
-    <cellStyle name="Гиперссылка 2 3 2 5" xfId="206"/>
-    <cellStyle name="Гиперссылка 2 3 2 6" xfId="207"/>
-    <cellStyle name="Гиперссылка 2 3 3" xfId="209"/>
-    <cellStyle name="Гиперссылка 2 3 3 2" xfId="210"/>
-    <cellStyle name="Гиперссылка 2 3 3 3" xfId="211"/>
-    <cellStyle name="Гиперссылка 2 3 3 4" xfId="213"/>
-    <cellStyle name="Гиперссылка 2 3 3 5" xfId="215"/>
-    <cellStyle name="Гиперссылка 2 3 4" xfId="217"/>
-    <cellStyle name="Гиперссылка 2 3 5" xfId="52"/>
-    <cellStyle name="Гиперссылка 2 3 6" xfId="219"/>
-    <cellStyle name="Гиперссылка 2 3 7" xfId="220"/>
-    <cellStyle name="Гиперссылка 2 4" xfId="222"/>
-    <cellStyle name="Гиперссылка 2 4 2" xfId="224"/>
-    <cellStyle name="Гиперссылка 2 4 2 2" xfId="38"/>
-    <cellStyle name="Гиперссылка 2 4 2 3" xfId="226"/>
-    <cellStyle name="Гиперссылка 2 4 2 4" xfId="228"/>
-    <cellStyle name="Гиперссылка 2 4 2 5" xfId="231"/>
-    <cellStyle name="Гиперссылка 2 4 3" xfId="54"/>
-    <cellStyle name="Гиперссылка 2 4 4" xfId="232"/>
-    <cellStyle name="Гиперссылка 2 4 5" xfId="233"/>
-    <cellStyle name="Гиперссылка 2 4 6" xfId="235"/>
-    <cellStyle name="Гиперссылка 2 5" xfId="237"/>
-    <cellStyle name="Гиперссылка 2 5 2" xfId="242"/>
-    <cellStyle name="Гиперссылка 2 5 2 2" xfId="244"/>
-    <cellStyle name="Гиперссылка 2 5 2 3" xfId="246"/>
-    <cellStyle name="Гиперссылка 2 5 2 4" xfId="248"/>
-    <cellStyle name="Гиперссылка 2 5 2 5" xfId="250"/>
-    <cellStyle name="Гиперссылка 2 5 3" xfId="252"/>
-    <cellStyle name="Гиперссылка 2 5 4" xfId="254"/>
-    <cellStyle name="Гиперссылка 2 5 5" xfId="256"/>
-    <cellStyle name="Гиперссылка 2 5 6" xfId="259"/>
-    <cellStyle name="Гиперссылка 2 6" xfId="261"/>
-    <cellStyle name="Гиперссылка 2 6 2" xfId="264"/>
-    <cellStyle name="Гиперссылка 2 6 3" xfId="266"/>
-    <cellStyle name="Гиперссылка 2 6 4" xfId="268"/>
-    <cellStyle name="Гиперссылка 2 6 5" xfId="270"/>
-    <cellStyle name="Гиперссылка 2 7" xfId="273"/>
-    <cellStyle name="Гиперссылка 2 8" xfId="275"/>
-    <cellStyle name="Гиперссылка 2 9" xfId="277"/>
+    <cellStyle name="Excel Built-in Normal" xfId="78" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Excel Built-in Normal 2" xfId="95" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Excel Built-in Normal 2 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Excel Built-in Normal 3" xfId="96" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Excel Built-in Normal 4" xfId="97" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Excel Built-in Normal 4 2" xfId="81" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Excel Built-in Normal 5" xfId="76" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Excel Built-in Normal 5 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Гиперссылка 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Гиперссылка 2 10" xfId="94" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Гиперссылка 2 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2" xfId="99" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2" xfId="84" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2" xfId="104" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 4" xfId="108" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 5" xfId="113" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 3" xfId="114" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 5" xfId="118" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 6" xfId="120" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 3" xfId="121" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 2" xfId="122" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 3" xfId="123" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 4" xfId="125" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 5" xfId="127" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 4" xfId="128" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 5" xfId="130" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 6" xfId="132" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Гиперссылка 2 2 2 7" xfId="134" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3" xfId="136" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 2" xfId="138" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 2" xfId="143" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 3" xfId="145" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 4" xfId="147" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 5" xfId="149" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 3" xfId="151" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 4" xfId="158" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 5" xfId="163" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Гиперссылка 2 2 3 6" xfId="166" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Гиперссылка 2 2 4" xfId="168" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Гиперссылка 2 2 4 2" xfId="172" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Гиперссылка 2 2 4 3" xfId="176" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Гиперссылка 2 2 4 4" xfId="177" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Гиперссылка 2 2 4 5" xfId="178" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Гиперссылка 2 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Гиперссылка 2 2 6" xfId="183" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Гиперссылка 2 2 7" xfId="185" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Гиперссылка 2 2 8" xfId="186" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Гиперссылка 2 3" xfId="189" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2" xfId="190" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 2" xfId="193" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 3" xfId="196" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 4" xfId="199" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 5" xfId="201" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 3" xfId="203" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 4" xfId="205" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 5" xfId="206" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="Гиперссылка 2 3 2 6" xfId="207" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="Гиперссылка 2 3 3" xfId="209" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="Гиперссылка 2 3 3 2" xfId="210" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="Гиперссылка 2 3 3 3" xfId="211" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Гиперссылка 2 3 3 4" xfId="213" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="Гиперссылка 2 3 3 5" xfId="215" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="Гиперссылка 2 3 4" xfId="217" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="Гиперссылка 2 3 5" xfId="52" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="Гиперссылка 2 3 6" xfId="219" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="Гиперссылка 2 3 7" xfId="220" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Гиперссылка 2 4" xfId="222" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Гиперссылка 2 4 2" xfId="224" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Гиперссылка 2 4 2 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Гиперссылка 2 4 2 3" xfId="226" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Гиперссылка 2 4 2 4" xfId="228" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Гиперссылка 2 4 2 5" xfId="231" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Гиперссылка 2 4 3" xfId="54" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Гиперссылка 2 4 4" xfId="232" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Гиперссылка 2 4 5" xfId="233" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Гиперссылка 2 4 6" xfId="235" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Гиперссылка 2 5" xfId="237" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Гиперссылка 2 5 2" xfId="242" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Гиперссылка 2 5 2 2" xfId="244" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Гиперссылка 2 5 2 3" xfId="246" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Гиперссылка 2 5 2 4" xfId="248" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Гиперссылка 2 5 2 5" xfId="250" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Гиперссылка 2 5 3" xfId="252" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Гиперссылка 2 5 4" xfId="254" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Гиперссылка 2 5 5" xfId="256" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Гиперссылка 2 5 6" xfId="259" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Гиперссылка 2 6" xfId="261" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Гиперссылка 2 6 2" xfId="264" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Гиперссылка 2 6 3" xfId="266" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Гиперссылка 2 6 4" xfId="268" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Гиперссылка 2 6 5" xfId="270" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Гиперссылка 2 7" xfId="273" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Гиперссылка 2 8" xfId="275" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Гиперссылка 2 9" xfId="277" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
     <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Денежный 2" xfId="112"/>
-    <cellStyle name="Денежный 2 2" xfId="278"/>
-    <cellStyle name="Денежный 2 2 2" xfId="157"/>
+    <cellStyle name="Денежный 2" xfId="112" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Денежный 2 2" xfId="278" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Денежный 2 2 2" xfId="157" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="279"/>
-    <cellStyle name="Обычный 10 2" xfId="281"/>
-    <cellStyle name="Обычный 11" xfId="282"/>
-    <cellStyle name="Обычный 11 2" xfId="286"/>
-    <cellStyle name="Обычный 12" xfId="287"/>
-    <cellStyle name="Обычный 12 2" xfId="291"/>
-    <cellStyle name="Обычный 13" xfId="293"/>
-    <cellStyle name="Обычный 13 2" xfId="69"/>
-    <cellStyle name="Обычный 14" xfId="295"/>
-    <cellStyle name="Обычный 14 2" xfId="131"/>
-    <cellStyle name="Обычный 15" xfId="298"/>
-    <cellStyle name="Обычный 15 2" xfId="165"/>
-    <cellStyle name="Обычный 16" xfId="301"/>
-    <cellStyle name="Обычный 16 2" xfId="302"/>
-    <cellStyle name="Обычный 17" xfId="303"/>
-    <cellStyle name="Обычный 17 2" xfId="305"/>
-    <cellStyle name="Обычный 18" xfId="306"/>
-    <cellStyle name="Обычный 18 2" xfId="309"/>
-    <cellStyle name="Обычный 19" xfId="19"/>
-    <cellStyle name="Обычный 2" xfId="4"/>
-    <cellStyle name="Обычный 2 10" xfId="310"/>
-    <cellStyle name="Обычный 2 10 2" xfId="182"/>
-    <cellStyle name="Обычный 2 11" xfId="311"/>
-    <cellStyle name="Обычный 2 12" xfId="37"/>
-    <cellStyle name="Обычный 2 12 2" xfId="234"/>
-    <cellStyle name="Обычный 2 12 3" xfId="312"/>
-    <cellStyle name="Обычный 2 13" xfId="225"/>
-    <cellStyle name="Обычный 2 13 2" xfId="258"/>
-    <cellStyle name="Обычный 2 14" xfId="227"/>
-    <cellStyle name="Обычный 2 14 2" xfId="314"/>
-    <cellStyle name="Обычный 2 15" xfId="229"/>
-    <cellStyle name="Обычный 2 15 2" xfId="317"/>
-    <cellStyle name="Обычный 2 16" xfId="319"/>
-    <cellStyle name="Обычный 2 16 2" xfId="322"/>
-    <cellStyle name="Обычный 2 17" xfId="325"/>
-    <cellStyle name="Обычный 2 17 2" xfId="329"/>
-    <cellStyle name="Обычный 2 18" xfId="333"/>
-    <cellStyle name="Обычный 2 18 2" xfId="57"/>
-    <cellStyle name="Обычный 2 19" xfId="338"/>
-    <cellStyle name="Обычный 2 19 2" xfId="342"/>
-    <cellStyle name="Обычный 2 19 3" xfId="346"/>
-    <cellStyle name="Обычный 2 2" xfId="348"/>
-    <cellStyle name="Обычный 2 2 10" xfId="353"/>
-    <cellStyle name="Обычный 2 2 10 2" xfId="356"/>
-    <cellStyle name="Обычный 2 2 10 3" xfId="359"/>
-    <cellStyle name="Обычный 2 2 10 4" xfId="362"/>
-    <cellStyle name="Обычный 2 2 11" xfId="93"/>
-    <cellStyle name="Обычный 2 2 2" xfId="365"/>
-    <cellStyle name="Обычный 2 2 2 2" xfId="366"/>
-    <cellStyle name="Обычный 2 2 2 2 2" xfId="367"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2" xfId="71"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2" xfId="369"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 2" xfId="292"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 3" xfId="294"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 4" xfId="297"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 5" xfId="300"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 3" xfId="371"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 4" xfId="372"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 5" xfId="373"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 6" xfId="374"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3" xfId="75"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 2" xfId="376"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 3" xfId="191"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 4" xfId="202"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 5" xfId="204"/>
-    <cellStyle name="Обычный 2 2 2 2 2 4" xfId="377"/>
-    <cellStyle name="Обычный 2 2 2 2 2 5" xfId="378"/>
-    <cellStyle name="Обычный 2 2 2 2 2 6" xfId="379"/>
-    <cellStyle name="Обычный 2 2 2 2 2 7" xfId="380"/>
-    <cellStyle name="Обычный 2 2 2 2 3" xfId="82"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2" xfId="42"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 2" xfId="381"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 3" xfId="382"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 4" xfId="383"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 5" xfId="384"/>
-    <cellStyle name="Обычный 2 2 2 2 3 3" xfId="385"/>
-    <cellStyle name="Обычный 2 2 2 2 3 4" xfId="386"/>
-    <cellStyle name="Обычный 2 2 2 2 3 5" xfId="387"/>
-    <cellStyle name="Обычный 2 2 2 2 3 6" xfId="388"/>
-    <cellStyle name="Обычный 2 2 2 2 4" xfId="87"/>
-    <cellStyle name="Обычный 2 2 2 2 4 2" xfId="390"/>
-    <cellStyle name="Обычный 2 2 2 2 4 3" xfId="392"/>
-    <cellStyle name="Обычный 2 2 2 2 4 4" xfId="394"/>
-    <cellStyle name="Обычный 2 2 2 2 4 5" xfId="102"/>
-    <cellStyle name="Обычный 2 2 2 2 5" xfId="107"/>
-    <cellStyle name="Обычный 2 2 2 2 6" xfId="111"/>
-    <cellStyle name="Обычный 2 2 2 2 7" xfId="398"/>
-    <cellStyle name="Обычный 2 2 2 2 8" xfId="402"/>
-    <cellStyle name="Обычный 2 2 2 3" xfId="403"/>
-    <cellStyle name="Обычный 2 2 2 3 2" xfId="404"/>
-    <cellStyle name="Обычный 2 2 3" xfId="407"/>
-    <cellStyle name="Обычный 2 2 3 2" xfId="408"/>
-    <cellStyle name="Обычный 2 2 4" xfId="241"/>
-    <cellStyle name="Обычный 2 2 4 2" xfId="243"/>
-    <cellStyle name="Обычный 2 2 4 2 2" xfId="409"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2" xfId="135"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 2" xfId="137"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 3" xfId="150"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 4" xfId="154"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 5" xfId="162"/>
-    <cellStyle name="Обычный 2 2 4 2 2 3" xfId="167"/>
-    <cellStyle name="Обычный 2 2 4 2 2 4" xfId="179"/>
-    <cellStyle name="Обычный 2 2 4 2 2 5" xfId="181"/>
-    <cellStyle name="Обычный 2 2 4 2 2 6" xfId="184"/>
-    <cellStyle name="Обычный 2 2 4 2 3" xfId="410"/>
-    <cellStyle name="Обычный 2 2 4 2 3 2" xfId="208"/>
-    <cellStyle name="Обычный 2 2 4 2 3 3" xfId="216"/>
-    <cellStyle name="Обычный 2 2 4 2 3 4" xfId="51"/>
-    <cellStyle name="Обычный 2 2 4 2 3 5" xfId="218"/>
-    <cellStyle name="Обычный 2 2 4 2 4" xfId="412"/>
-    <cellStyle name="Обычный 2 2 4 2 5" xfId="308"/>
-    <cellStyle name="Обычный 2 2 4 2 6" xfId="414"/>
-    <cellStyle name="Обычный 2 2 4 2 7" xfId="352"/>
-    <cellStyle name="Обычный 2 2 4 3" xfId="245"/>
-    <cellStyle name="Обычный 2 2 4 3 2" xfId="415"/>
-    <cellStyle name="Обычный 2 2 4 3 2 2" xfId="417"/>
-    <cellStyle name="Обычный 2 2 4 3 2 3" xfId="420"/>
-    <cellStyle name="Обычный 2 2 4 3 2 4" xfId="423"/>
-    <cellStyle name="Обычный 2 2 4 3 2 5" xfId="425"/>
-    <cellStyle name="Обычный 2 2 4 3 3" xfId="426"/>
-    <cellStyle name="Обычный 2 2 4 3 4" xfId="427"/>
-    <cellStyle name="Обычный 2 2 4 3 5" xfId="60"/>
-    <cellStyle name="Обычный 2 2 4 3 6" xfId="49"/>
-    <cellStyle name="Обычный 2 2 4 4" xfId="247"/>
-    <cellStyle name="Обычный 2 2 4 4 2" xfId="27"/>
-    <cellStyle name="Обычный 2 2 4 4 3" xfId="431"/>
-    <cellStyle name="Обычный 2 2 4 4 4" xfId="434"/>
-    <cellStyle name="Обычный 2 2 4 4 5" xfId="437"/>
-    <cellStyle name="Обычный 2 2 4 5" xfId="249"/>
-    <cellStyle name="Обычный 2 2 4 6" xfId="438"/>
-    <cellStyle name="Обычный 2 2 4 7" xfId="223"/>
-    <cellStyle name="Обычный 2 2 4 8" xfId="53"/>
-    <cellStyle name="Обычный 2 2 5" xfId="251"/>
-    <cellStyle name="Обычный 2 2 5 2" xfId="440"/>
-    <cellStyle name="Обычный 2 2 5 2 2" xfId="442"/>
-    <cellStyle name="Обычный 2 2 5 2 2 2" xfId="444"/>
-    <cellStyle name="Обычный 2 2 5 2 2 3" xfId="446"/>
-    <cellStyle name="Обычный 2 2 5 2 2 4" xfId="170"/>
-    <cellStyle name="Обычный 2 2 5 2 2 5" xfId="174"/>
-    <cellStyle name="Обычный 2 2 5 2 3" xfId="448"/>
-    <cellStyle name="Обычный 2 2 5 2 4" xfId="450"/>
-    <cellStyle name="Обычный 2 2 5 2 5" xfId="452"/>
-    <cellStyle name="Обычный 2 2 5 2 6" xfId="454"/>
-    <cellStyle name="Обычный 2 2 5 3" xfId="456"/>
-    <cellStyle name="Обычный 2 2 5 3 2" xfId="458"/>
-    <cellStyle name="Обычный 2 2 5 3 3" xfId="460"/>
-    <cellStyle name="Обычный 2 2 5 3 4" xfId="461"/>
-    <cellStyle name="Обычный 2 2 5 3 5" xfId="462"/>
-    <cellStyle name="Обычный 2 2 5 4" xfId="464"/>
-    <cellStyle name="Обычный 2 2 5 5" xfId="364"/>
-    <cellStyle name="Обычный 2 2 5 6" xfId="406"/>
-    <cellStyle name="Обычный 2 2 5 7" xfId="240"/>
-    <cellStyle name="Обычный 2 2 6" xfId="253"/>
-    <cellStyle name="Обычный 2 2 6 2" xfId="86"/>
-    <cellStyle name="Обычный 2 2 6 2 2" xfId="389"/>
-    <cellStyle name="Обычный 2 2 6 2 3" xfId="391"/>
-    <cellStyle name="Обычный 2 2 6 2 4" xfId="393"/>
-    <cellStyle name="Обычный 2 2 6 2 5" xfId="100"/>
-    <cellStyle name="Обычный 2 2 6 3" xfId="106"/>
-    <cellStyle name="Обычный 2 2 6 4" xfId="110"/>
-    <cellStyle name="Обычный 2 2 6 5" xfId="396"/>
-    <cellStyle name="Обычный 2 2 6 6" xfId="400"/>
-    <cellStyle name="Обычный 2 2 7" xfId="255"/>
-    <cellStyle name="Обычный 2 2 7 2" xfId="465"/>
-    <cellStyle name="Обычный 2 2 7 2 2" xfId="468"/>
-    <cellStyle name="Обычный 2 2 7 2 3" xfId="285"/>
-    <cellStyle name="Обычный 2 2 7 2 4" xfId="473"/>
-    <cellStyle name="Обычный 2 2 7 2 5" xfId="141"/>
-    <cellStyle name="Обычный 2 2 7 3" xfId="474"/>
-    <cellStyle name="Обычный 2 2 7 4" xfId="280"/>
-    <cellStyle name="Обычный 2 2 7 5" xfId="476"/>
-    <cellStyle name="Обычный 2 2 7 6" xfId="478"/>
-    <cellStyle name="Обычный 2 2 8" xfId="257"/>
-    <cellStyle name="Обычный 2 2 8 2" xfId="479"/>
-    <cellStyle name="Обычный 2 2 8 2 2" xfId="482"/>
-    <cellStyle name="Обычный 2 2 8 2 3" xfId="485"/>
-    <cellStyle name="Обычный 2 2 8 2 4" xfId="488"/>
-    <cellStyle name="Обычный 2 2 8 2 5" xfId="491"/>
-    <cellStyle name="Обычный 2 2 8 3" xfId="466"/>
-    <cellStyle name="Обычный 2 2 8 4" xfId="283"/>
-    <cellStyle name="Обычный 2 2 8 5" xfId="469"/>
-    <cellStyle name="Обычный 2 2 8 6" xfId="140"/>
-    <cellStyle name="Обычный 2 2 9" xfId="492"/>
-    <cellStyle name="Обычный 2 2 9 2" xfId="493"/>
-    <cellStyle name="Обычный 2 2 9 3" xfId="79"/>
-    <cellStyle name="Обычный 2 2 9 4" xfId="288"/>
-    <cellStyle name="Обычный 2 2 9 5" xfId="496"/>
-    <cellStyle name="Обычный 2 20" xfId="230"/>
-    <cellStyle name="Обычный 2 20 2" xfId="318"/>
-    <cellStyle name="Обычный 2 21" xfId="320"/>
-    <cellStyle name="Обычный 2 21 2" xfId="323"/>
-    <cellStyle name="Обычный 2 22" xfId="326"/>
-    <cellStyle name="Обычный 2 22 2" xfId="330"/>
-    <cellStyle name="Обычный 2 23" xfId="334"/>
-    <cellStyle name="Обычный 2 24" xfId="339"/>
-    <cellStyle name="Обычный 2 25" xfId="500"/>
-    <cellStyle name="Обычный 2 26" xfId="504"/>
-    <cellStyle name="Обычный 2 27" xfId="506"/>
-    <cellStyle name="Обычный 2 28" xfId="508"/>
-    <cellStyle name="Обычный 2 29" xfId="156"/>
-    <cellStyle name="Обычный 2 3" xfId="509"/>
-    <cellStyle name="Обычный 2 3 10" xfId="324"/>
-    <cellStyle name="Обычный 2 3 10 2" xfId="328"/>
-    <cellStyle name="Обычный 2 3 11" xfId="332"/>
-    <cellStyle name="Обычный 2 3 11 2" xfId="56"/>
-    <cellStyle name="Обычный 2 3 12" xfId="336"/>
-    <cellStyle name="Обычный 2 3 12 2" xfId="340"/>
-    <cellStyle name="Обычный 2 3 13" xfId="498"/>
-    <cellStyle name="Обычный 2 3 13 2" xfId="514"/>
-    <cellStyle name="Обычный 2 3 14" xfId="502"/>
-    <cellStyle name="Обычный 2 3 14 2" xfId="188"/>
-    <cellStyle name="Обычный 2 3 2" xfId="395"/>
-    <cellStyle name="Обычный 2 3 2 2" xfId="515"/>
-    <cellStyle name="Обычный 2 3 2 2 2" xfId="212"/>
-    <cellStyle name="Обычный 2 3 3" xfId="399"/>
-    <cellStyle name="Обычный 2 3 3 2" xfId="516"/>
-    <cellStyle name="Обычный 2 3 4" xfId="262"/>
-    <cellStyle name="Обычный 2 3 5" xfId="265"/>
-    <cellStyle name="Обычный 2 3 5 2" xfId="517"/>
-    <cellStyle name="Обычный 2 3 5 3" xfId="518"/>
-    <cellStyle name="Обычный 2 3 6" xfId="267"/>
-    <cellStyle name="Обычный 2 3 6 2" xfId="519"/>
-    <cellStyle name="Обычный 2 3 7" xfId="269"/>
-    <cellStyle name="Обычный 2 3 7 2" xfId="520"/>
-    <cellStyle name="Обычный 2 3 8" xfId="313"/>
-    <cellStyle name="Обычный 2 3 9" xfId="521"/>
-    <cellStyle name="Обычный 2 3 9 2" xfId="271"/>
-    <cellStyle name="Обычный 2 30" xfId="1655"/>
-    <cellStyle name="Обычный 2 4" xfId="1"/>
-    <cellStyle name="Обычный 2 4 2" xfId="475"/>
-    <cellStyle name="Обычный 2 4 2 2" xfId="129"/>
-    <cellStyle name="Обычный 2 4 3" xfId="477"/>
-    <cellStyle name="Обычный 2 4 4" xfId="522"/>
-    <cellStyle name="Обычный 2 5" xfId="523"/>
-    <cellStyle name="Обычный 2 5 2" xfId="472"/>
-    <cellStyle name="Обычный 2 5 3" xfId="139"/>
-    <cellStyle name="Обычный 2 5 3 2" xfId="214"/>
-    <cellStyle name="Обычный 2 5 4" xfId="144"/>
-    <cellStyle name="Обычный 2 6" xfId="524"/>
-    <cellStyle name="Обычный 2 6 2" xfId="495"/>
-    <cellStyle name="Обычный 2 6 3" xfId="525"/>
-    <cellStyle name="Обычный 2 6 3 2" xfId="526"/>
-    <cellStyle name="Обычный 2 7" xfId="55"/>
-    <cellStyle name="Обычный 2 7 2" xfId="73"/>
-    <cellStyle name="Обычный 2 7 3" xfId="347"/>
-    <cellStyle name="Обычный 2 8" xfId="527"/>
-    <cellStyle name="Обычный 2 8 2" xfId="133"/>
-    <cellStyle name="Обычный 2 9" xfId="528"/>
-    <cellStyle name="Обычный 2 9 2" xfId="529"/>
-    <cellStyle name="Обычный 20" xfId="18"/>
-    <cellStyle name="Обычный 21" xfId="1641"/>
-    <cellStyle name="Обычный 22" xfId="1650"/>
-    <cellStyle name="Обычный 23" xfId="1660"/>
-    <cellStyle name="Обычный 24" xfId="1661"/>
-    <cellStyle name="Обычный 3" xfId="17"/>
-    <cellStyle name="Обычный 3 2" xfId="531"/>
-    <cellStyle name="Обычный 3 2 2" xfId="532"/>
-    <cellStyle name="Обычный 3 2 2 2" xfId="484"/>
-    <cellStyle name="Обычный 3 2 2 3" xfId="487"/>
-    <cellStyle name="Обычный 3 2 2 4" xfId="489"/>
-    <cellStyle name="Обычный 3 2 2 5" xfId="533"/>
-    <cellStyle name="Обычный 3 2 3" xfId="534"/>
-    <cellStyle name="Обычный 3 2 4" xfId="535"/>
-    <cellStyle name="Обычный 3 2 5" xfId="536"/>
-    <cellStyle name="Обычный 3 2 6" xfId="537"/>
-    <cellStyle name="Обычный 3 3" xfId="538"/>
-    <cellStyle name="Обычный 3 3 2" xfId="539"/>
-    <cellStyle name="Обычный 3 4" xfId="540"/>
-    <cellStyle name="Обычный 3 4 2" xfId="542"/>
-    <cellStyle name="Обычный 3 5" xfId="543"/>
-    <cellStyle name="Обычный 3 5 2" xfId="486"/>
-    <cellStyle name="Обычный 3 6" xfId="160"/>
-    <cellStyle name="Обычный 3 7" xfId="1645"/>
-    <cellStyle name="Обычный 3 8" xfId="1656"/>
-    <cellStyle name="Обычный 4" xfId="164"/>
-    <cellStyle name="Обычный 4 10" xfId="1657"/>
-    <cellStyle name="Обычный 4 2" xfId="545"/>
-    <cellStyle name="Обычный 4 2 10" xfId="546"/>
-    <cellStyle name="Обычный 4 2 2" xfId="548"/>
-    <cellStyle name="Обычный 4 2 3" xfId="551"/>
-    <cellStyle name="Обычный 4 2 3 2" xfId="115"/>
-    <cellStyle name="Обычный 4 2 3 2 2" xfId="553"/>
-    <cellStyle name="Обычный 4 2 3 2 2 2" xfId="554"/>
-    <cellStyle name="Обычный 4 2 3 2 2 3" xfId="555"/>
-    <cellStyle name="Обычный 4 2 3 2 2 4" xfId="541"/>
-    <cellStyle name="Обычный 4 2 3 2 2 5" xfId="557"/>
-    <cellStyle name="Обычный 4 2 3 2 3" xfId="480"/>
-    <cellStyle name="Обычный 4 2 3 2 4" xfId="467"/>
-    <cellStyle name="Обычный 4 2 3 2 5" xfId="284"/>
-    <cellStyle name="Обычный 4 2 3 2 6" xfId="470"/>
-    <cellStyle name="Обычный 4 2 3 3" xfId="117"/>
-    <cellStyle name="Обычный 4 2 3 3 2" xfId="558"/>
-    <cellStyle name="Обычный 4 2 3 3 3" xfId="494"/>
-    <cellStyle name="Обычный 4 2 3 3 4" xfId="80"/>
-    <cellStyle name="Обычный 4 2 3 3 5" xfId="289"/>
-    <cellStyle name="Обычный 4 2 3 4" xfId="119"/>
-    <cellStyle name="Обычный 4 2 3 5" xfId="559"/>
-    <cellStyle name="Обычный 4 2 3 6" xfId="560"/>
-    <cellStyle name="Обычный 4 2 3 7" xfId="561"/>
-    <cellStyle name="Обычный 4 2 4" xfId="35"/>
-    <cellStyle name="Обычный 4 2 4 2" xfId="124"/>
-    <cellStyle name="Обычный 4 2 4 2 2" xfId="562"/>
-    <cellStyle name="Обычный 4 2 4 2 3" xfId="563"/>
-    <cellStyle name="Обычный 4 2 4 2 4" xfId="481"/>
-    <cellStyle name="Обычный 4 2 4 2 5" xfId="483"/>
-    <cellStyle name="Обычный 4 2 4 3" xfId="126"/>
-    <cellStyle name="Обычный 4 2 4 4" xfId="564"/>
-    <cellStyle name="Обычный 4 2 4 5" xfId="565"/>
-    <cellStyle name="Обычный 4 2 4 6" xfId="566"/>
-    <cellStyle name="Обычный 4 2 5" xfId="195"/>
-    <cellStyle name="Обычный 4 2 5 2" xfId="568"/>
-    <cellStyle name="Обычный 4 2 5 2 2" xfId="430"/>
-    <cellStyle name="Обычный 4 2 5 2 3" xfId="433"/>
-    <cellStyle name="Обычный 4 2 5 2 4" xfId="436"/>
-    <cellStyle name="Обычный 4 2 5 2 5" xfId="570"/>
-    <cellStyle name="Обычный 4 2 5 3" xfId="26"/>
-    <cellStyle name="Обычный 4 2 5 4" xfId="572"/>
-    <cellStyle name="Обычный 4 2 5 5" xfId="574"/>
-    <cellStyle name="Обычный 4 2 5 6" xfId="576"/>
-    <cellStyle name="Обычный 4 2 6" xfId="198"/>
-    <cellStyle name="Обычный 4 2 6 2" xfId="578"/>
-    <cellStyle name="Обычный 4 2 6 3" xfId="418"/>
-    <cellStyle name="Обычный 4 2 6 4" xfId="421"/>
-    <cellStyle name="Обычный 4 2 6 5" xfId="424"/>
-    <cellStyle name="Обычный 4 2 7" xfId="200"/>
-    <cellStyle name="Обычный 4 2 8" xfId="368"/>
-    <cellStyle name="Обычный 4 2 9" xfId="370"/>
-    <cellStyle name="Обычный 4 3" xfId="580"/>
-    <cellStyle name="Обычный 4 3 2" xfId="350"/>
-    <cellStyle name="Обычный 4 3 2 2" xfId="355"/>
-    <cellStyle name="Обычный 4 3 2 2 2" xfId="581"/>
-    <cellStyle name="Обычный 4 3 2 2 2 2" xfId="331"/>
-    <cellStyle name="Обычный 4 3 2 2 2 3" xfId="335"/>
-    <cellStyle name="Обычный 4 3 2 2 2 4" xfId="497"/>
-    <cellStyle name="Обычный 4 3 2 2 2 5" xfId="501"/>
-    <cellStyle name="Обычный 4 3 2 2 3" xfId="304"/>
-    <cellStyle name="Обычный 4 3 2 2 4" xfId="582"/>
-    <cellStyle name="Обычный 4 3 2 2 5" xfId="549"/>
-    <cellStyle name="Обычный 4 3 2 2 6" xfId="552"/>
-    <cellStyle name="Обычный 4 3 2 3" xfId="358"/>
-    <cellStyle name="Обычный 4 3 2 3 2" xfId="411"/>
-    <cellStyle name="Обычный 4 3 2 3 3" xfId="307"/>
-    <cellStyle name="Обычный 4 3 2 3 4" xfId="413"/>
-    <cellStyle name="Обычный 4 3 2 3 5" xfId="351"/>
-    <cellStyle name="Обычный 4 3 2 4" xfId="361"/>
-    <cellStyle name="Обычный 4 3 2 5" xfId="316"/>
-    <cellStyle name="Обычный 4 3 2 6" xfId="583"/>
-    <cellStyle name="Обычный 4 3 2 7" xfId="32"/>
-    <cellStyle name="Обычный 4 3 3" xfId="91"/>
-    <cellStyle name="Обычный 4 3 3 2" xfId="146"/>
-    <cellStyle name="Обычный 4 3 3 2 2" xfId="21"/>
-    <cellStyle name="Обычный 4 3 3 2 3" xfId="65"/>
-    <cellStyle name="Обычный 4 3 3 2 4" xfId="58"/>
-    <cellStyle name="Обычный 4 3 3 2 5" xfId="45"/>
-    <cellStyle name="Обычный 4 3 3 3" xfId="148"/>
-    <cellStyle name="Обычный 4 3 3 4" xfId="584"/>
-    <cellStyle name="Обычный 4 3 3 5" xfId="321"/>
-    <cellStyle name="Обычный 4 3 3 6" xfId="585"/>
-    <cellStyle name="Обычный 4 3 4" xfId="587"/>
-    <cellStyle name="Обычный 4 3 4 2" xfId="588"/>
-    <cellStyle name="Обычный 4 3 4 3" xfId="589"/>
-    <cellStyle name="Обычный 4 3 4 4" xfId="590"/>
-    <cellStyle name="Обычный 4 3 4 5" xfId="327"/>
-    <cellStyle name="Обычный 4 3 5" xfId="592"/>
-    <cellStyle name="Обычный 4 3 6" xfId="594"/>
-    <cellStyle name="Обычный 4 3 7" xfId="595"/>
-    <cellStyle name="Обычный 4 3 8" xfId="375"/>
-    <cellStyle name="Обычный 4 4" xfId="29"/>
-    <cellStyle name="Обычный 4 5" xfId="597"/>
-    <cellStyle name="Обычный 4 6" xfId="599"/>
-    <cellStyle name="Обычный 4 7" xfId="511"/>
-    <cellStyle name="Обычный 4 8" xfId="600"/>
-    <cellStyle name="Обычный 4 9" xfId="1646"/>
-    <cellStyle name="Обычный 4_Капекс_НВ_ 12.09.11" xfId="344"/>
-    <cellStyle name="Обычный 5" xfId="530"/>
-    <cellStyle name="Обычный 5 2" xfId="602"/>
-    <cellStyle name="Обычный 5 2 10" xfId="603"/>
-    <cellStyle name="Обычный 5 2 2" xfId="44"/>
-    <cellStyle name="Обычный 5 2 2 2" xfId="606"/>
-    <cellStyle name="Обычный 5 2 2 2 2" xfId="607"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2" xfId="608"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 2" xfId="101"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 3" xfId="609"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 4" xfId="610"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 5" xfId="611"/>
-    <cellStyle name="Обычный 5 2 2 2 2 3" xfId="612"/>
-    <cellStyle name="Обычный 5 2 2 2 2 4" xfId="613"/>
-    <cellStyle name="Обычный 5 2 2 2 2 5" xfId="614"/>
-    <cellStyle name="Обычный 5 2 2 2 2 6" xfId="615"/>
-    <cellStyle name="Обычный 5 2 2 2 3" xfId="616"/>
-    <cellStyle name="Обычный 5 2 2 2 3 2" xfId="617"/>
-    <cellStyle name="Обычный 5 2 2 2 3 3" xfId="618"/>
-    <cellStyle name="Обычный 5 2 2 2 3 4" xfId="155"/>
-    <cellStyle name="Обычный 5 2 2 2 3 5" xfId="159"/>
-    <cellStyle name="Обычный 5 2 2 2 4" xfId="619"/>
-    <cellStyle name="Обычный 5 2 2 2 5" xfId="620"/>
-    <cellStyle name="Обычный 5 2 2 2 6" xfId="621"/>
-    <cellStyle name="Обычный 5 2 2 2 7" xfId="622"/>
-    <cellStyle name="Обычный 5 2 2 3" xfId="625"/>
-    <cellStyle name="Обычный 5 2 2 3 2" xfId="627"/>
-    <cellStyle name="Обычный 5 2 2 3 2 2" xfId="628"/>
-    <cellStyle name="Обычный 5 2 2 3 2 3" xfId="629"/>
-    <cellStyle name="Обычный 5 2 2 3 2 4" xfId="630"/>
-    <cellStyle name="Обычный 5 2 2 3 2 5" xfId="631"/>
-    <cellStyle name="Обычный 5 2 2 3 3" xfId="633"/>
-    <cellStyle name="Обычный 5 2 2 3 4" xfId="635"/>
-    <cellStyle name="Обычный 5 2 2 3 5" xfId="637"/>
-    <cellStyle name="Обычный 5 2 2 3 6" xfId="639"/>
-    <cellStyle name="Обычный 5 2 2 4" xfId="642"/>
-    <cellStyle name="Обычный 5 2 2 4 2" xfId="643"/>
-    <cellStyle name="Обычный 5 2 2 4 3" xfId="644"/>
-    <cellStyle name="Обычный 5 2 2 4 4" xfId="646"/>
-    <cellStyle name="Обычный 5 2 2 4 5" xfId="648"/>
-    <cellStyle name="Обычный 5 2 2 5" xfId="650"/>
-    <cellStyle name="Обычный 5 2 2 6" xfId="652"/>
-    <cellStyle name="Обычный 5 2 2 7" xfId="653"/>
-    <cellStyle name="Обычный 5 2 2 8" xfId="654"/>
-    <cellStyle name="Обычный 5 2 3" xfId="656"/>
-    <cellStyle name="Обычный 5 2 3 2" xfId="658"/>
-    <cellStyle name="Обычный 5 2 3 2 2" xfId="659"/>
-    <cellStyle name="Обычный 5 2 3 2 2 2" xfId="660"/>
-    <cellStyle name="Обычный 5 2 3 2 2 3" xfId="661"/>
-    <cellStyle name="Обычный 5 2 3 2 2 4" xfId="662"/>
-    <cellStyle name="Обычный 5 2 3 2 2 5" xfId="663"/>
-    <cellStyle name="Обычный 5 2 3 2 3" xfId="664"/>
-    <cellStyle name="Обычный 5 2 3 2 4" xfId="665"/>
-    <cellStyle name="Обычный 5 2 3 2 5" xfId="666"/>
-    <cellStyle name="Обычный 5 2 3 2 6" xfId="667"/>
-    <cellStyle name="Обычный 5 2 3 3" xfId="669"/>
-    <cellStyle name="Обычный 5 2 3 3 2" xfId="670"/>
-    <cellStyle name="Обычный 5 2 3 3 3" xfId="671"/>
-    <cellStyle name="Обычный 5 2 3 3 4" xfId="672"/>
-    <cellStyle name="Обычный 5 2 3 3 5" xfId="673"/>
-    <cellStyle name="Обычный 5 2 3 4" xfId="675"/>
-    <cellStyle name="Обычный 5 2 3 5" xfId="677"/>
-    <cellStyle name="Обычный 5 2 3 6" xfId="678"/>
-    <cellStyle name="Обычный 5 2 3 7" xfId="679"/>
-    <cellStyle name="Обычный 5 2 4" xfId="681"/>
-    <cellStyle name="Обычный 5 2 4 2" xfId="683"/>
-    <cellStyle name="Обычный 5 2 4 2 2" xfId="684"/>
-    <cellStyle name="Обычный 5 2 4 2 3" xfId="685"/>
-    <cellStyle name="Обычный 5 2 4 2 4" xfId="686"/>
-    <cellStyle name="Обычный 5 2 4 2 5" xfId="687"/>
-    <cellStyle name="Обычный 5 2 4 3" xfId="689"/>
-    <cellStyle name="Обычный 5 2 4 4" xfId="691"/>
-    <cellStyle name="Обычный 5 2 4 5" xfId="692"/>
-    <cellStyle name="Обычный 5 2 4 6" xfId="694"/>
-    <cellStyle name="Обычный 5 2 5" xfId="696"/>
-    <cellStyle name="Обычный 5 2 5 2" xfId="697"/>
-    <cellStyle name="Обычный 5 2 5 2 2" xfId="698"/>
-    <cellStyle name="Обычный 5 2 5 2 3" xfId="699"/>
-    <cellStyle name="Обычный 5 2 5 2 4" xfId="700"/>
-    <cellStyle name="Обычный 5 2 5 2 5" xfId="701"/>
-    <cellStyle name="Обычный 5 2 5 3" xfId="702"/>
-    <cellStyle name="Обычный 5 2 5 4" xfId="703"/>
-    <cellStyle name="Обычный 5 2 5 5" xfId="704"/>
-    <cellStyle name="Обычный 5 2 5 6" xfId="705"/>
-    <cellStyle name="Обычный 5 2 6" xfId="706"/>
-    <cellStyle name="Обычный 5 2 6 2" xfId="707"/>
-    <cellStyle name="Обычный 5 2 6 3" xfId="708"/>
-    <cellStyle name="Обычный 5 2 6 4" xfId="709"/>
-    <cellStyle name="Обычный 5 2 6 5" xfId="710"/>
-    <cellStyle name="Обычный 5 2 7" xfId="711"/>
-    <cellStyle name="Обычный 5 2 8" xfId="712"/>
-    <cellStyle name="Обычный 5 2 9" xfId="713"/>
-    <cellStyle name="Обычный 5 3" xfId="715"/>
-    <cellStyle name="Обычный 5 3 2" xfId="716"/>
-    <cellStyle name="Обычный 5 4" xfId="718"/>
-    <cellStyle name="Обычный 5 4 2" xfId="719"/>
-    <cellStyle name="Обычный 5 5" xfId="721"/>
-    <cellStyle name="Обычный 5 5 2" xfId="722"/>
-    <cellStyle name="Обычный 5 6" xfId="725"/>
-    <cellStyle name="Обычный 5 6 2" xfId="726"/>
-    <cellStyle name="Обычный 5 7" xfId="728"/>
-    <cellStyle name="Обычный 5 7 2" xfId="729"/>
-    <cellStyle name="Обычный 6" xfId="3"/>
-    <cellStyle name="Обычный 6 10" xfId="731"/>
-    <cellStyle name="Обычный 6 11" xfId="732"/>
-    <cellStyle name="Обычный 6 12" xfId="730"/>
-    <cellStyle name="Обычный 6 2" xfId="735"/>
-    <cellStyle name="Обычный 6 2 2" xfId="737"/>
-    <cellStyle name="Обычный 6 2 2 2" xfId="739"/>
-    <cellStyle name="Обычный 6 2 2 2 2" xfId="740"/>
-    <cellStyle name="Обычный 6 2 2 2 2 2" xfId="741"/>
-    <cellStyle name="Обычный 6 2 2 2 2 3" xfId="742"/>
-    <cellStyle name="Обычный 6 2 2 2 2 4" xfId="743"/>
-    <cellStyle name="Обычный 6 2 2 2 2 5" xfId="744"/>
-    <cellStyle name="Обычный 6 2 2 2 3" xfId="746"/>
-    <cellStyle name="Обычный 6 2 2 2 4" xfId="747"/>
-    <cellStyle name="Обычный 6 2 2 2 5" xfId="748"/>
-    <cellStyle name="Обычный 6 2 2 2 6" xfId="749"/>
-    <cellStyle name="Обычный 6 2 2 3" xfId="751"/>
-    <cellStyle name="Обычный 6 2 2 3 2" xfId="752"/>
-    <cellStyle name="Обычный 6 2 2 3 3" xfId="754"/>
-    <cellStyle name="Обычный 6 2 2 3 4" xfId="755"/>
-    <cellStyle name="Обычный 6 2 2 3 5" xfId="756"/>
-    <cellStyle name="Обычный 6 2 2 4" xfId="757"/>
-    <cellStyle name="Обычный 6 2 2 5" xfId="758"/>
-    <cellStyle name="Обычный 6 2 2 6" xfId="759"/>
-    <cellStyle name="Обычный 6 2 2 7" xfId="760"/>
-    <cellStyle name="Обычный 6 2 3" xfId="762"/>
-    <cellStyle name="Обычный 6 2 3 2" xfId="764"/>
-    <cellStyle name="Обычный 6 2 3 2 2" xfId="765"/>
-    <cellStyle name="Обычный 6 2 3 2 3" xfId="766"/>
-    <cellStyle name="Обычный 6 2 3 2 4" xfId="767"/>
-    <cellStyle name="Обычный 6 2 3 2 5" xfId="768"/>
-    <cellStyle name="Обычный 6 2 3 3" xfId="769"/>
-    <cellStyle name="Обычный 6 2 3 4" xfId="770"/>
-    <cellStyle name="Обычный 6 2 3 5" xfId="771"/>
-    <cellStyle name="Обычный 6 2 3 6" xfId="772"/>
-    <cellStyle name="Обычный 6 2 4" xfId="775"/>
-    <cellStyle name="Обычный 6 2 4 2" xfId="776"/>
-    <cellStyle name="Обычный 6 2 4 3" xfId="777"/>
-    <cellStyle name="Обычный 6 2 4 4" xfId="778"/>
-    <cellStyle name="Обычный 6 2 4 5" xfId="779"/>
-    <cellStyle name="Обычный 6 2 5" xfId="782"/>
-    <cellStyle name="Обычный 6 2 6" xfId="784"/>
-    <cellStyle name="Обычный 6 2 7" xfId="786"/>
-    <cellStyle name="Обычный 6 2 8" xfId="787"/>
-    <cellStyle name="Обычный 6 3" xfId="790"/>
-    <cellStyle name="Обычный 6 3 2" xfId="791"/>
-    <cellStyle name="Обычный 6 3 2 2" xfId="792"/>
-    <cellStyle name="Обычный 6 3 2 2 2" xfId="793"/>
-    <cellStyle name="Обычный 6 3 2 2 3" xfId="794"/>
-    <cellStyle name="Обычный 6 3 2 2 4" xfId="795"/>
-    <cellStyle name="Обычный 6 3 2 2 5" xfId="796"/>
-    <cellStyle name="Обычный 6 3 2 3" xfId="797"/>
-    <cellStyle name="Обычный 6 3 2 4" xfId="798"/>
-    <cellStyle name="Обычный 6 3 2 5" xfId="799"/>
-    <cellStyle name="Обычный 6 3 2 6" xfId="471"/>
-    <cellStyle name="Обычный 6 3 3" xfId="800"/>
-    <cellStyle name="Обычный 6 3 3 2" xfId="801"/>
-    <cellStyle name="Обычный 6 3 3 3" xfId="802"/>
-    <cellStyle name="Обычный 6 3 3 4" xfId="803"/>
-    <cellStyle name="Обычный 6 3 3 5" xfId="804"/>
-    <cellStyle name="Обычный 6 3 4" xfId="805"/>
-    <cellStyle name="Обычный 6 3 5" xfId="806"/>
-    <cellStyle name="Обычный 6 3 6" xfId="807"/>
-    <cellStyle name="Обычный 6 3 7" xfId="808"/>
-    <cellStyle name="Обычный 6 4" xfId="811"/>
-    <cellStyle name="Обычный 6 4 2" xfId="812"/>
-    <cellStyle name="Обычный 6 4 2 2" xfId="813"/>
-    <cellStyle name="Обычный 6 4 2 3" xfId="814"/>
-    <cellStyle name="Обычный 6 4 2 4" xfId="815"/>
-    <cellStyle name="Обычный 6 4 2 5" xfId="816"/>
-    <cellStyle name="Обычный 6 4 3" xfId="817"/>
-    <cellStyle name="Обычный 6 4 4" xfId="818"/>
-    <cellStyle name="Обычный 6 4 5" xfId="819"/>
-    <cellStyle name="Обычный 6 4 6" xfId="820"/>
-    <cellStyle name="Обычный 6 5" xfId="822"/>
-    <cellStyle name="Обычный 6 5 2" xfId="825"/>
-    <cellStyle name="Обычный 6 5 2 2" xfId="828"/>
-    <cellStyle name="Обычный 6 5 2 3" xfId="830"/>
-    <cellStyle name="Обычный 6 5 2 4" xfId="832"/>
-    <cellStyle name="Обычный 6 5 2 5" xfId="834"/>
-    <cellStyle name="Обычный 6 5 3" xfId="24"/>
-    <cellStyle name="Обычный 6 5 4" xfId="837"/>
-    <cellStyle name="Обычный 6 5 5" xfId="840"/>
-    <cellStyle name="Обычный 6 5 6" xfId="843"/>
-    <cellStyle name="Обычный 6 6" xfId="845"/>
-    <cellStyle name="Обычный 6 6 2" xfId="846"/>
-    <cellStyle name="Обычный 6 6 2 2" xfId="847"/>
-    <cellStyle name="Обычный 6 6 2 3" xfId="848"/>
-    <cellStyle name="Обычный 6 6 2 4" xfId="849"/>
-    <cellStyle name="Обычный 6 6 2 5" xfId="850"/>
-    <cellStyle name="Обычный 6 6 3" xfId="851"/>
-    <cellStyle name="Обычный 6 6 4" xfId="852"/>
-    <cellStyle name="Обычный 6 6 5" xfId="853"/>
-    <cellStyle name="Обычный 6 6 6" xfId="854"/>
-    <cellStyle name="Обычный 6 7" xfId="855"/>
-    <cellStyle name="Обычный 6 7 2" xfId="856"/>
-    <cellStyle name="Обычный 6 7 3" xfId="857"/>
-    <cellStyle name="Обычный 6 7 4" xfId="858"/>
-    <cellStyle name="Обычный 6 7 5" xfId="859"/>
-    <cellStyle name="Обычный 6 8" xfId="860"/>
-    <cellStyle name="Обычный 6 9" xfId="861"/>
-    <cellStyle name="Обычный 7" xfId="862"/>
-    <cellStyle name="Обычный 7 10" xfId="863"/>
-    <cellStyle name="Обычный 7 11" xfId="864"/>
-    <cellStyle name="Обычный 7 2" xfId="866"/>
-    <cellStyle name="Обычный 7 2 2" xfId="868"/>
-    <cellStyle name="Обычный 7 2 2 2" xfId="869"/>
-    <cellStyle name="Обычный 7 2 2 2 2" xfId="870"/>
-    <cellStyle name="Обычный 7 2 2 2 2 2" xfId="873"/>
-    <cellStyle name="Обычный 7 2 2 2 2 3" xfId="876"/>
-    <cellStyle name="Обычный 7 2 2 2 2 4" xfId="878"/>
-    <cellStyle name="Обычный 7 2 2 2 2 5" xfId="879"/>
-    <cellStyle name="Обычный 7 2 2 2 3" xfId="880"/>
-    <cellStyle name="Обычный 7 2 2 2 4" xfId="881"/>
-    <cellStyle name="Обычный 7 2 2 2 5" xfId="882"/>
-    <cellStyle name="Обычный 7 2 2 2 6" xfId="883"/>
-    <cellStyle name="Обычный 7 2 2 3" xfId="885"/>
-    <cellStyle name="Обычный 7 2 2 3 2" xfId="887"/>
-    <cellStyle name="Обычный 7 2 2 3 3" xfId="889"/>
-    <cellStyle name="Обычный 7 2 2 3 4" xfId="891"/>
-    <cellStyle name="Обычный 7 2 2 3 5" xfId="893"/>
-    <cellStyle name="Обычный 7 2 2 4" xfId="895"/>
-    <cellStyle name="Обычный 7 2 2 5" xfId="734"/>
-    <cellStyle name="Обычный 7 2 2 6" xfId="789"/>
-    <cellStyle name="Обычный 7 2 2 7" xfId="810"/>
-    <cellStyle name="Обычный 7 2 3" xfId="896"/>
-    <cellStyle name="Обычный 7 2 3 2" xfId="898"/>
-    <cellStyle name="Обычный 7 2 3 2 2" xfId="899"/>
-    <cellStyle name="Обычный 7 2 3 2 3" xfId="901"/>
-    <cellStyle name="Обычный 7 2 3 2 4" xfId="903"/>
-    <cellStyle name="Обычный 7 2 3 2 5" xfId="905"/>
-    <cellStyle name="Обычный 7 2 3 3" xfId="908"/>
-    <cellStyle name="Обычный 7 2 3 4" xfId="910"/>
-    <cellStyle name="Обычный 7 2 3 5" xfId="865"/>
-    <cellStyle name="Обычный 7 2 3 6" xfId="912"/>
-    <cellStyle name="Обычный 7 2 4" xfId="913"/>
-    <cellStyle name="Обычный 7 2 4 2" xfId="915"/>
-    <cellStyle name="Обычный 7 2 4 3" xfId="918"/>
-    <cellStyle name="Обычный 7 2 4 4" xfId="919"/>
-    <cellStyle name="Обычный 7 2 4 5" xfId="921"/>
-    <cellStyle name="Обычный 7 2 5" xfId="922"/>
-    <cellStyle name="Обычный 7 2 6" xfId="923"/>
-    <cellStyle name="Обычный 7 2 7" xfId="924"/>
-    <cellStyle name="Обычный 7 2 8" xfId="925"/>
-    <cellStyle name="Обычный 7 3" xfId="911"/>
-    <cellStyle name="Обычный 7 3 2" xfId="926"/>
-    <cellStyle name="Обычный 7 3 2 2" xfId="20"/>
-    <cellStyle name="Обычный 7 3 2 2 2" xfId="928"/>
-    <cellStyle name="Обычный 7 3 2 2 3" xfId="872"/>
-    <cellStyle name="Обычный 7 3 2 2 4" xfId="875"/>
-    <cellStyle name="Обычный 7 3 2 2 5" xfId="877"/>
-    <cellStyle name="Обычный 7 3 2 3" xfId="66"/>
-    <cellStyle name="Обычный 7 3 2 4" xfId="59"/>
-    <cellStyle name="Обычный 7 3 2 5" xfId="47"/>
-    <cellStyle name="Обычный 7 3 2 6" xfId="930"/>
-    <cellStyle name="Обычный 7 3 3" xfId="931"/>
-    <cellStyle name="Обычный 7 3 3 2" xfId="933"/>
-    <cellStyle name="Обычный 7 3 3 3" xfId="935"/>
-    <cellStyle name="Обычный 7 3 3 4" xfId="937"/>
-    <cellStyle name="Обычный 7 3 3 5" xfId="939"/>
-    <cellStyle name="Обычный 7 3 4" xfId="940"/>
-    <cellStyle name="Обычный 7 3 5" xfId="941"/>
-    <cellStyle name="Обычный 7 3 6" xfId="942"/>
-    <cellStyle name="Обычный 7 3 7" xfId="943"/>
-    <cellStyle name="Обычный 7 4" xfId="944"/>
-    <cellStyle name="Обычный 7 4 2" xfId="945"/>
-    <cellStyle name="Обычный 7 4 2 2" xfId="946"/>
-    <cellStyle name="Обычный 7 4 2 3" xfId="947"/>
-    <cellStyle name="Обычный 7 4 2 4" xfId="948"/>
-    <cellStyle name="Обычный 7 4 2 5" xfId="949"/>
-    <cellStyle name="Обычный 7 4 3" xfId="950"/>
-    <cellStyle name="Обычный 7 4 4" xfId="951"/>
-    <cellStyle name="Обычный 7 4 5" xfId="952"/>
-    <cellStyle name="Обычный 7 4 6" xfId="953"/>
-    <cellStyle name="Обычный 7 5" xfId="954"/>
-    <cellStyle name="Обычный 7 5 2" xfId="955"/>
-    <cellStyle name="Обычный 7 5 2 2" xfId="956"/>
-    <cellStyle name="Обычный 7 5 2 3" xfId="957"/>
-    <cellStyle name="Обычный 7 5 2 4" xfId="958"/>
-    <cellStyle name="Обычный 7 5 2 5" xfId="959"/>
-    <cellStyle name="Обычный 7 5 3" xfId="960"/>
-    <cellStyle name="Обычный 7 5 4" xfId="961"/>
-    <cellStyle name="Обычный 7 5 5" xfId="962"/>
-    <cellStyle name="Обычный 7 5 6" xfId="963"/>
-    <cellStyle name="Обычный 7 6" xfId="964"/>
-    <cellStyle name="Обычный 7 6 2" xfId="965"/>
-    <cellStyle name="Обычный 7 6 2 2" xfId="966"/>
-    <cellStyle name="Обычный 7 6 2 3" xfId="968"/>
-    <cellStyle name="Обычный 7 6 2 4" xfId="970"/>
-    <cellStyle name="Обычный 7 6 2 5" xfId="971"/>
-    <cellStyle name="Обычный 7 6 3" xfId="972"/>
-    <cellStyle name="Обычный 7 6 4" xfId="973"/>
-    <cellStyle name="Обычный 7 6 5" xfId="974"/>
-    <cellStyle name="Обычный 7 6 6" xfId="343"/>
-    <cellStyle name="Обычный 7 7" xfId="975"/>
-    <cellStyle name="Обычный 7 7 2" xfId="976"/>
-    <cellStyle name="Обычный 7 7 3" xfId="977"/>
-    <cellStyle name="Обычный 7 7 4" xfId="978"/>
-    <cellStyle name="Обычный 7 7 5" xfId="979"/>
-    <cellStyle name="Обычный 7 8" xfId="980"/>
-    <cellStyle name="Обычный 7 9" xfId="192"/>
-    <cellStyle name="Обычный 8" xfId="981"/>
-    <cellStyle name="Обычный 8 2" xfId="920"/>
-    <cellStyle name="Обычный 9" xfId="982"/>
-    <cellStyle name="Обычный 9 2" xfId="984"/>
+    <cellStyle name="Обычный 10" xfId="279" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Обычный 10 2" xfId="281" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Обычный 11" xfId="282" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Обычный 11 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Обычный 12" xfId="287" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="Обычный 12 2" xfId="291" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="Обычный 13" xfId="293" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Обычный 13 2" xfId="69" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Обычный 14" xfId="295" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Обычный 14 2" xfId="131" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Обычный 15" xfId="298" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="Обычный 15 2" xfId="165" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="Обычный 16" xfId="301" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="Обычный 16 2" xfId="302" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="Обычный 17" xfId="303" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="Обычный 17 2" xfId="305" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="Обычный 18" xfId="306" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="Обычный 18 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="Обычный 19" xfId="19" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="Обычный 2" xfId="4" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="Обычный 2 10" xfId="310" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="Обычный 2 10 2" xfId="182" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="Обычный 2 11" xfId="311" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="Обычный 2 12" xfId="37" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="Обычный 2 12 2" xfId="234" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="Обычный 2 12 3" xfId="312" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="Обычный 2 13" xfId="225" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="Обычный 2 13 2" xfId="258" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="Обычный 2 14" xfId="227" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="Обычный 2 14 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="Обычный 2 15" xfId="229" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="Обычный 2 15 2" xfId="317" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="Обычный 2 16" xfId="319" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="Обычный 2 16 2" xfId="322" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="Обычный 2 17" xfId="325" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="Обычный 2 17 2" xfId="329" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="Обычный 2 18" xfId="333" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="Обычный 2 18 2" xfId="57" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="Обычный 2 19" xfId="338" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="Обычный 2 19 2" xfId="342" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="Обычный 2 19 3" xfId="346" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="348" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="Обычный 2 2 10" xfId="353" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="Обычный 2 2 10 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="Обычный 2 2 10 3" xfId="359" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="Обычный 2 2 10 4" xfId="362" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="Обычный 2 2 11" xfId="93" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="Обычный 2 2 2" xfId="365" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="Обычный 2 2 2 2" xfId="366" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2" xfId="367" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2" xfId="369" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 2" xfId="292" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 3" xfId="294" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 4" xfId="297" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 5" xfId="300" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 3" xfId="371" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 4" xfId="372" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 5" xfId="373" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 6" xfId="374" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3" xfId="75" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 2" xfId="376" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 3" xfId="191" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 4" xfId="202" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 5" xfId="204" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 4" xfId="377" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 5" xfId="378" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 6" xfId="379" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 2 7" xfId="380" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3" xfId="82" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2" xfId="42" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 2" xfId="381" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 3" xfId="382" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 4" xfId="383" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 5" xfId="384" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 3" xfId="385" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 4" xfId="386" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 5" xfId="387" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 3 6" xfId="388" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 4" xfId="87" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 4 2" xfId="390" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 4 3" xfId="392" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 4 4" xfId="394" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 4 5" xfId="102" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 5" xfId="107" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 6" xfId="111" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 7" xfId="398" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="Обычный 2 2 2 2 8" xfId="402" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="Обычный 2 2 2 3" xfId="403" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
+    <cellStyle name="Обычный 2 2 2 3 2" xfId="404" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
+    <cellStyle name="Обычный 2 2 3" xfId="407" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="Обычный 2 2 3 2" xfId="408" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="Обычный 2 2 4" xfId="241" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="Обычный 2 2 4 2" xfId="243" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2" xfId="409" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 2" xfId="137" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 3" xfId="150" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 4" xfId="154" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 5" xfId="162" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 3" xfId="167" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 4" xfId="179" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 2 6" xfId="184" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 3" xfId="410" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 3 2" xfId="208" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 3 3" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 3 4" xfId="51" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 3 5" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 4" xfId="412" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 5" xfId="308" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 6" xfId="414" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="Обычный 2 2 4 2 7" xfId="352" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="Обычный 2 2 4 3" xfId="245" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 2" xfId="415" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 2 4" xfId="423" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 2 5" xfId="425" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 3" xfId="426" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 4" xfId="427" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 5" xfId="60" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
+    <cellStyle name="Обычный 2 2 4 3 6" xfId="49" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
+    <cellStyle name="Обычный 2 2 4 4" xfId="247" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="Обычный 2 2 4 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="Обычный 2 2 4 4 3" xfId="431" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
+    <cellStyle name="Обычный 2 2 4 4 4" xfId="434" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
+    <cellStyle name="Обычный 2 2 4 4 5" xfId="437" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="Обычный 2 2 4 5" xfId="249" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="Обычный 2 2 4 6" xfId="438" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="Обычный 2 2 4 7" xfId="223" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
+    <cellStyle name="Обычный 2 2 4 8" xfId="53" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
+    <cellStyle name="Обычный 2 2 5" xfId="251" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="Обычный 2 2 5 2" xfId="440" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 2" xfId="442" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 2 2" xfId="444" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 2 3" xfId="446" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 2 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 2 5" xfId="174" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 3" xfId="448" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 4" xfId="450" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 5" xfId="452" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
+    <cellStyle name="Обычный 2 2 5 2 6" xfId="454" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="Обычный 2 2 5 3" xfId="456" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="Обычный 2 2 5 3 2" xfId="458" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="Обычный 2 2 5 3 3" xfId="460" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="Обычный 2 2 5 3 4" xfId="461" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
+    <cellStyle name="Обычный 2 2 5 3 5" xfId="462" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="Обычный 2 2 5 4" xfId="464" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="Обычный 2 2 5 5" xfId="364" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="Обычный 2 2 5 6" xfId="406" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="Обычный 2 2 5 7" xfId="240" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="Обычный 2 2 6" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="Обычный 2 2 6 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="Обычный 2 2 6 2 2" xfId="389" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="Обычный 2 2 6 2 3" xfId="391" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="Обычный 2 2 6 2 4" xfId="393" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="Обычный 2 2 6 2 5" xfId="100" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="Обычный 2 2 6 3" xfId="106" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="Обычный 2 2 6 4" xfId="110" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
+    <cellStyle name="Обычный 2 2 6 5" xfId="396" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
+    <cellStyle name="Обычный 2 2 6 6" xfId="400" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="Обычный 2 2 7" xfId="255" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="Обычный 2 2 7 2" xfId="465" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
+    <cellStyle name="Обычный 2 2 7 2 2" xfId="468" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
+    <cellStyle name="Обычный 2 2 7 2 3" xfId="285" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="Обычный 2 2 7 2 4" xfId="473" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="Обычный 2 2 7 2 5" xfId="141" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="Обычный 2 2 7 3" xfId="474" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="Обычный 2 2 7 4" xfId="280" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="Обычный 2 2 7 5" xfId="476" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
+    <cellStyle name="Обычный 2 2 7 6" xfId="478" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
+    <cellStyle name="Обычный 2 2 8" xfId="257" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="Обычный 2 2 8 2" xfId="479" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+    <cellStyle name="Обычный 2 2 8 2 2" xfId="482" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
+    <cellStyle name="Обычный 2 2 8 2 3" xfId="485" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
+    <cellStyle name="Обычный 2 2 8 2 4" xfId="488" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="Обычный 2 2 8 2 5" xfId="491" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="Обычный 2 2 8 3" xfId="466" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="Обычный 2 2 8 4" xfId="283" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="Обычный 2 2 8 5" xfId="469" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="Обычный 2 2 8 6" xfId="140" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="Обычный 2 2 9" xfId="492" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="Обычный 2 2 9 2" xfId="493" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="Обычный 2 2 9 3" xfId="79" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="Обычный 2 2 9 4" xfId="288" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="Обычный 2 2 9 5" xfId="496" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="Обычный 2 20" xfId="230" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="Обычный 2 20 2" xfId="318" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="Обычный 2 21" xfId="320" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="Обычный 2 21 2" xfId="323" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="Обычный 2 22" xfId="326" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="Обычный 2 22 2" xfId="330" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="Обычный 2 23" xfId="334" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="Обычный 2 24" xfId="339" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Обычный 2 25" xfId="500" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Обычный 2 26" xfId="504" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Обычный 2 27" xfId="506" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Обычный 2 28" xfId="508" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Обычный 2 29" xfId="156" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Обычный 2 3" xfId="509" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Обычный 2 3 10" xfId="324" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Обычный 2 3 10 2" xfId="328" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Обычный 2 3 11" xfId="332" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Обычный 2 3 11 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Обычный 2 3 12" xfId="336" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Обычный 2 3 12 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Обычный 2 3 13" xfId="498" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Обычный 2 3 13 2" xfId="514" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Обычный 2 3 14" xfId="502" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Обычный 2 3 14 2" xfId="188" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Обычный 2 3 2" xfId="395" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Обычный 2 3 2 2" xfId="515" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Обычный 2 3 2 2 2" xfId="212" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Обычный 2 3 3" xfId="399" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Обычный 2 3 3 2" xfId="516" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Обычный 2 3 4" xfId="262" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Обычный 2 3 5" xfId="265" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Обычный 2 3 5 2" xfId="517" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Обычный 2 3 5 3" xfId="518" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Обычный 2 3 6" xfId="267" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Обычный 2 3 6 2" xfId="519" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Обычный 2 3 7" xfId="269" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Обычный 2 3 7 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Обычный 2 3 8" xfId="313" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Обычный 2 3 9" xfId="521" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Обычный 2 3 9 2" xfId="271" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Обычный 2 30" xfId="1655" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Обычный 2 4" xfId="1" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Обычный 2 4 2" xfId="475" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Обычный 2 4 2 2" xfId="129" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Обычный 2 4 3" xfId="477" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Обычный 2 4 4" xfId="522" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Обычный 2 5" xfId="523" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Обычный 2 5 2" xfId="472" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="Обычный 2 5 3" xfId="139" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="Обычный 2 5 3 2" xfId="214" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="Обычный 2 5 4" xfId="144" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="Обычный 2 6" xfId="524" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="Обычный 2 6 2" xfId="495" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="Обычный 2 6 3" xfId="525" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="Обычный 2 6 3 2" xfId="526" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="Обычный 2 7" xfId="55" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="Обычный 2 7 2" xfId="73" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="Обычный 2 7 3" xfId="347" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="Обычный 2 8" xfId="527" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="Обычный 2 8 2" xfId="133" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="Обычный 2 9" xfId="528" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="Обычный 2 9 2" xfId="529" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="Обычный 20" xfId="18" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="Обычный 21" xfId="1641" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="Обычный 22" xfId="1650" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="Обычный 23" xfId="1660" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="Обычный 24" xfId="1661" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="Обычный 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="Обычный 3 2" xfId="531" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="Обычный 3 2 2" xfId="532" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="Обычный 3 2 2 2" xfId="484" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="Обычный 3 2 2 3" xfId="487" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="Обычный 3 2 2 4" xfId="489" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
+    <cellStyle name="Обычный 3 2 2 5" xfId="533" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
+    <cellStyle name="Обычный 3 2 3" xfId="534" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
+    <cellStyle name="Обычный 3 2 4" xfId="535" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
+    <cellStyle name="Обычный 3 2 5" xfId="536" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
+    <cellStyle name="Обычный 3 2 6" xfId="537" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
+    <cellStyle name="Обычный 3 3" xfId="538" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
+    <cellStyle name="Обычный 3 3 2" xfId="539" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
+    <cellStyle name="Обычный 3 4" xfId="540" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
+    <cellStyle name="Обычный 3 4 2" xfId="542" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
+    <cellStyle name="Обычный 3 5" xfId="543" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
+    <cellStyle name="Обычный 3 5 2" xfId="486" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
+    <cellStyle name="Обычный 3 6" xfId="160" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
+    <cellStyle name="Обычный 3 7" xfId="1645" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
+    <cellStyle name="Обычный 3 8" xfId="1656" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
+    <cellStyle name="Обычный 4" xfId="164" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
+    <cellStyle name="Обычный 4 10" xfId="1657" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
+    <cellStyle name="Обычный 4 2" xfId="545" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
+    <cellStyle name="Обычный 4 2 10" xfId="546" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
+    <cellStyle name="Обычный 4 2 2" xfId="548" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
+    <cellStyle name="Обычный 4 2 3" xfId="551" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
+    <cellStyle name="Обычный 4 2 3 2" xfId="115" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 2" xfId="553" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 2 2" xfId="554" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 2 3" xfId="555" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 2 4" xfId="541" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 2 5" xfId="557" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 3" xfId="480" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 4" xfId="467" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 5" xfId="284" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
+    <cellStyle name="Обычный 4 2 3 2 6" xfId="470" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
+    <cellStyle name="Обычный 4 2 3 3" xfId="117" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
+    <cellStyle name="Обычный 4 2 3 3 2" xfId="558" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
+    <cellStyle name="Обычный 4 2 3 3 3" xfId="494" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
+    <cellStyle name="Обычный 4 2 3 3 4" xfId="80" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
+    <cellStyle name="Обычный 4 2 3 3 5" xfId="289" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
+    <cellStyle name="Обычный 4 2 3 4" xfId="119" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
+    <cellStyle name="Обычный 4 2 3 5" xfId="559" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
+    <cellStyle name="Обычный 4 2 3 6" xfId="560" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
+    <cellStyle name="Обычный 4 2 3 7" xfId="561" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
+    <cellStyle name="Обычный 4 2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
+    <cellStyle name="Обычный 4 2 4 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
+    <cellStyle name="Обычный 4 2 4 2 2" xfId="562" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
+    <cellStyle name="Обычный 4 2 4 2 3" xfId="563" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
+    <cellStyle name="Обычный 4 2 4 2 4" xfId="481" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
+    <cellStyle name="Обычный 4 2 4 2 5" xfId="483" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
+    <cellStyle name="Обычный 4 2 4 3" xfId="126" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
+    <cellStyle name="Обычный 4 2 4 4" xfId="564" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
+    <cellStyle name="Обычный 4 2 4 5" xfId="565" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
+    <cellStyle name="Обычный 4 2 4 6" xfId="566" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="Обычный 4 2 5" xfId="195" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
+    <cellStyle name="Обычный 4 2 5 2" xfId="568" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
+    <cellStyle name="Обычный 4 2 5 2 2" xfId="430" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
+    <cellStyle name="Обычный 4 2 5 2 3" xfId="433" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
+    <cellStyle name="Обычный 4 2 5 2 4" xfId="436" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
+    <cellStyle name="Обычный 4 2 5 2 5" xfId="570" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
+    <cellStyle name="Обычный 4 2 5 3" xfId="26" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
+    <cellStyle name="Обычный 4 2 5 4" xfId="572" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
+    <cellStyle name="Обычный 4 2 5 5" xfId="574" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
+    <cellStyle name="Обычный 4 2 5 6" xfId="576" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
+    <cellStyle name="Обычный 4 2 6" xfId="198" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
+    <cellStyle name="Обычный 4 2 6 2" xfId="578" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
+    <cellStyle name="Обычный 4 2 6 3" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
+    <cellStyle name="Обычный 4 2 6 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
+    <cellStyle name="Обычный 4 2 6 5" xfId="424" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
+    <cellStyle name="Обычный 4 2 7" xfId="200" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
+    <cellStyle name="Обычный 4 2 8" xfId="368" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
+    <cellStyle name="Обычный 4 2 9" xfId="370" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
+    <cellStyle name="Обычный 4 3" xfId="580" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
+    <cellStyle name="Обычный 4 3 2" xfId="350" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
+    <cellStyle name="Обычный 4 3 2 2" xfId="355" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 2" xfId="581" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 2 2" xfId="331" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 2 3" xfId="335" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 2 4" xfId="497" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 2 5" xfId="501" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 3" xfId="304" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 4" xfId="582" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 5" xfId="549" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
+    <cellStyle name="Обычный 4 3 2 2 6" xfId="552" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
+    <cellStyle name="Обычный 4 3 2 3" xfId="358" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
+    <cellStyle name="Обычный 4 3 2 3 2" xfId="411" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
+    <cellStyle name="Обычный 4 3 2 3 3" xfId="307" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
+    <cellStyle name="Обычный 4 3 2 3 4" xfId="413" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
+    <cellStyle name="Обычный 4 3 2 3 5" xfId="351" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
+    <cellStyle name="Обычный 4 3 2 4" xfId="361" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
+    <cellStyle name="Обычный 4 3 2 5" xfId="316" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
+    <cellStyle name="Обычный 4 3 2 6" xfId="583" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
+    <cellStyle name="Обычный 4 3 2 7" xfId="32" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
+    <cellStyle name="Обычный 4 3 3" xfId="91" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
+    <cellStyle name="Обычный 4 3 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
+    <cellStyle name="Обычный 4 3 3 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Обычный 4 3 3 2 3" xfId="65" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
+    <cellStyle name="Обычный 4 3 3 2 4" xfId="58" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
+    <cellStyle name="Обычный 4 3 3 2 5" xfId="45" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
+    <cellStyle name="Обычный 4 3 3 3" xfId="148" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
+    <cellStyle name="Обычный 4 3 3 4" xfId="584" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
+    <cellStyle name="Обычный 4 3 3 5" xfId="321" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
+    <cellStyle name="Обычный 4 3 3 6" xfId="585" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
+    <cellStyle name="Обычный 4 3 4" xfId="587" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
+    <cellStyle name="Обычный 4 3 4 2" xfId="588" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
+    <cellStyle name="Обычный 4 3 4 3" xfId="589" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
+    <cellStyle name="Обычный 4 3 4 4" xfId="590" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
+    <cellStyle name="Обычный 4 3 4 5" xfId="327" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
+    <cellStyle name="Обычный 4 3 5" xfId="592" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
+    <cellStyle name="Обычный 4 3 6" xfId="594" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
+    <cellStyle name="Обычный 4 3 7" xfId="595" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
+    <cellStyle name="Обычный 4 3 8" xfId="375" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
+    <cellStyle name="Обычный 4 4" xfId="29" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
+    <cellStyle name="Обычный 4 5" xfId="597" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
+    <cellStyle name="Обычный 4 6" xfId="599" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
+    <cellStyle name="Обычный 4 7" xfId="511" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
+    <cellStyle name="Обычный 4 8" xfId="600" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
+    <cellStyle name="Обычный 4 9" xfId="1646" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
+    <cellStyle name="Обычный 4_Капекс_НВ_ 12.09.11" xfId="344" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
+    <cellStyle name="Обычный 5" xfId="530" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
+    <cellStyle name="Обычный 5 2" xfId="602" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
+    <cellStyle name="Обычный 5 2 10" xfId="603" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
+    <cellStyle name="Обычный 5 2 2" xfId="44" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
+    <cellStyle name="Обычный 5 2 2 2" xfId="606" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2" xfId="607" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2" xfId="608" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 2" xfId="101" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 3" xfId="609" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 4" xfId="610" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 5" xfId="611" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 3" xfId="612" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 4" xfId="613" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 5" xfId="614" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 2 6" xfId="615" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 3" xfId="616" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 3 2" xfId="617" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 3 3" xfId="618" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 3 4" xfId="155" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 3 5" xfId="159" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 4" xfId="619" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 5" xfId="620" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 6" xfId="621" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
+    <cellStyle name="Обычный 5 2 2 2 7" xfId="622" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Обычный 5 2 2 3" xfId="625" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 2" xfId="627" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 2 2" xfId="628" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 2 3" xfId="629" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 2 4" xfId="630" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 2 5" xfId="631" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 3" xfId="633" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 4" xfId="635" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 5" xfId="637" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
+    <cellStyle name="Обычный 5 2 2 3 6" xfId="639" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
+    <cellStyle name="Обычный 5 2 2 4" xfId="642" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
+    <cellStyle name="Обычный 5 2 2 4 2" xfId="643" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
+    <cellStyle name="Обычный 5 2 2 4 3" xfId="644" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
+    <cellStyle name="Обычный 5 2 2 4 4" xfId="646" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="Обычный 5 2 2 4 5" xfId="648" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
+    <cellStyle name="Обычный 5 2 2 5" xfId="650" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
+    <cellStyle name="Обычный 5 2 2 6" xfId="652" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
+    <cellStyle name="Обычный 5 2 2 7" xfId="653" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
+    <cellStyle name="Обычный 5 2 2 8" xfId="654" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
+    <cellStyle name="Обычный 5 2 3" xfId="656" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
+    <cellStyle name="Обычный 5 2 3 2" xfId="658" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 2" xfId="659" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 2 2" xfId="660" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 2 3" xfId="661" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 2 4" xfId="662" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 2 5" xfId="663" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 3" xfId="664" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 4" xfId="665" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 5" xfId="666" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
+    <cellStyle name="Обычный 5 2 3 2 6" xfId="667" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
+    <cellStyle name="Обычный 5 2 3 3" xfId="669" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
+    <cellStyle name="Обычный 5 2 3 3 2" xfId="670" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
+    <cellStyle name="Обычный 5 2 3 3 3" xfId="671" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
+    <cellStyle name="Обычный 5 2 3 3 4" xfId="672" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
+    <cellStyle name="Обычный 5 2 3 3 5" xfId="673" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
+    <cellStyle name="Обычный 5 2 3 4" xfId="675" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
+    <cellStyle name="Обычный 5 2 3 5" xfId="677" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
+    <cellStyle name="Обычный 5 2 3 6" xfId="678" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
+    <cellStyle name="Обычный 5 2 3 7" xfId="679" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
+    <cellStyle name="Обычный 5 2 4" xfId="681" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
+    <cellStyle name="Обычный 5 2 4 2" xfId="683" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Обычный 5 2 4 2 2" xfId="684" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Обычный 5 2 4 2 3" xfId="685" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Обычный 5 2 4 2 4" xfId="686" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Обычный 5 2 4 2 5" xfId="687" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Обычный 5 2 4 3" xfId="689" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Обычный 5 2 4 4" xfId="691" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Обычный 5 2 4 5" xfId="692" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Обычный 5 2 4 6" xfId="694" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Обычный 5 2 5" xfId="696" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Обычный 5 2 5 2" xfId="697" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Обычный 5 2 5 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Обычный 5 2 5 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Обычный 5 2 5 2 4" xfId="700" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Обычный 5 2 5 2 5" xfId="701" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Обычный 5 2 5 3" xfId="702" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Обычный 5 2 5 4" xfId="703" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Обычный 5 2 5 5" xfId="704" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Обычный 5 2 5 6" xfId="705" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Обычный 5 2 6" xfId="706" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Обычный 5 2 6 2" xfId="707" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Обычный 5 2 6 3" xfId="708" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Обычный 5 2 6 4" xfId="709" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Обычный 5 2 6 5" xfId="710" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Обычный 5 2 7" xfId="711" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Обычный 5 2 8" xfId="712" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Обычный 5 2 9" xfId="713" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Обычный 5 3" xfId="715" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Обычный 5 3 2" xfId="716" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Обычный 5 4" xfId="718" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Обычный 5 4 2" xfId="719" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Обычный 5 5" xfId="721" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Обычный 5 5 2" xfId="722" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Обычный 5 6" xfId="725" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Обычный 5 6 2" xfId="726" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Обычный 5 7" xfId="728" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Обычный 5 7 2" xfId="729" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Обычный 6 10" xfId="731" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Обычный 6 11" xfId="732" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Обычный 6 12" xfId="730" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Обычный 6 2" xfId="735" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Обычный 6 2 2" xfId="737" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Обычный 6 2 2 2" xfId="739" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 2" xfId="740" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 2 3" xfId="742" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 2 4" xfId="743" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 2 5" xfId="744" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 3" xfId="746" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 4" xfId="747" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 5" xfId="748" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Обычный 6 2 2 2 6" xfId="749" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Обычный 6 2 2 3" xfId="751" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Обычный 6 2 2 3 2" xfId="752" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Обычный 6 2 2 3 3" xfId="754" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Обычный 6 2 2 3 4" xfId="755" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Обычный 6 2 2 3 5" xfId="756" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Обычный 6 2 2 4" xfId="757" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Обычный 6 2 2 5" xfId="758" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Обычный 6 2 2 6" xfId="759" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Обычный 6 2 2 7" xfId="760" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Обычный 6 2 3" xfId="762" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Обычный 6 2 3 2" xfId="764" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Обычный 6 2 3 2 2" xfId="765" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Обычный 6 2 3 2 3" xfId="766" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Обычный 6 2 3 2 4" xfId="767" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Обычный 6 2 3 2 5" xfId="768" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Обычный 6 2 3 3" xfId="769" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Обычный 6 2 3 4" xfId="770" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Обычный 6 2 3 5" xfId="771" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Обычный 6 2 3 6" xfId="772" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Обычный 6 2 4" xfId="775" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Обычный 6 2 4 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Обычный 6 2 4 3" xfId="777" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Обычный 6 2 4 4" xfId="778" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Обычный 6 2 4 5" xfId="779" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Обычный 6 2 5" xfId="782" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Обычный 6 2 6" xfId="784" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="Обычный 6 2 7" xfId="786" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="Обычный 6 2 8" xfId="787" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Обычный 6 3" xfId="790" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Обычный 6 3 2" xfId="791" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Обычный 6 3 2 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Обычный 6 3 2 2 2" xfId="793" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Обычный 6 3 2 2 3" xfId="794" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Обычный 6 3 2 2 4" xfId="795" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Обычный 6 3 2 2 5" xfId="796" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="Обычный 6 3 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Обычный 6 3 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Обычный 6 3 2 5" xfId="799" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Обычный 6 3 2 6" xfId="471" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Обычный 6 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Обычный 6 3 3 2" xfId="801" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Обычный 6 3 3 3" xfId="802" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="Обычный 6 3 3 4" xfId="803" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Обычный 6 3 3 5" xfId="804" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Обычный 6 3 4" xfId="805" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Обычный 6 3 5" xfId="806" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="Обычный 6 3 6" xfId="807" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Обычный 6 3 7" xfId="808" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Обычный 6 4" xfId="811" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Обычный 6 4 2" xfId="812" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Обычный 6 4 2 2" xfId="813" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Обычный 6 4 2 3" xfId="814" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Обычный 6 4 2 4" xfId="815" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="Обычный 6 4 2 5" xfId="816" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Обычный 6 4 3" xfId="817" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Обычный 6 4 4" xfId="818" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
+    <cellStyle name="Обычный 6 4 5" xfId="819" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
+    <cellStyle name="Обычный 6 4 6" xfId="820" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
+    <cellStyle name="Обычный 6 5" xfId="822" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
+    <cellStyle name="Обычный 6 5 2" xfId="825" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
+    <cellStyle name="Обычный 6 5 2 2" xfId="828" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
+    <cellStyle name="Обычный 6 5 2 3" xfId="830" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
+    <cellStyle name="Обычный 6 5 2 4" xfId="832" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
+    <cellStyle name="Обычный 6 5 2 5" xfId="834" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
+    <cellStyle name="Обычный 6 5 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
+    <cellStyle name="Обычный 6 5 4" xfId="837" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
+    <cellStyle name="Обычный 6 5 5" xfId="840" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
+    <cellStyle name="Обычный 6 5 6" xfId="843" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
+    <cellStyle name="Обычный 6 6" xfId="845" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
+    <cellStyle name="Обычный 6 6 2" xfId="846" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
+    <cellStyle name="Обычный 6 6 2 2" xfId="847" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
+    <cellStyle name="Обычный 6 6 2 3" xfId="848" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
+    <cellStyle name="Обычный 6 6 2 4" xfId="849" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
+    <cellStyle name="Обычный 6 6 2 5" xfId="850" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
+    <cellStyle name="Обычный 6 6 3" xfId="851" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
+    <cellStyle name="Обычный 6 6 4" xfId="852" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
+    <cellStyle name="Обычный 6 6 5" xfId="853" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
+    <cellStyle name="Обычный 6 6 6" xfId="854" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
+    <cellStyle name="Обычный 6 7" xfId="855" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
+    <cellStyle name="Обычный 6 7 2" xfId="856" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
+    <cellStyle name="Обычный 6 7 3" xfId="857" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
+    <cellStyle name="Обычный 6 7 4" xfId="858" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
+    <cellStyle name="Обычный 6 7 5" xfId="859" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
+    <cellStyle name="Обычный 6 8" xfId="860" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
+    <cellStyle name="Обычный 6 9" xfId="861" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
+    <cellStyle name="Обычный 7" xfId="862" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
+    <cellStyle name="Обычный 7 10" xfId="863" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
+    <cellStyle name="Обычный 7 11" xfId="864" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
+    <cellStyle name="Обычный 7 2" xfId="866" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
+    <cellStyle name="Обычный 7 2 2" xfId="868" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
+    <cellStyle name="Обычный 7 2 2 2" xfId="869" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 2" xfId="870" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 2 2" xfId="873" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 2 3" xfId="876" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 2 4" xfId="878" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 2 5" xfId="879" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 3" xfId="880" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 4" xfId="881" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 5" xfId="882" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
+    <cellStyle name="Обычный 7 2 2 2 6" xfId="883" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
+    <cellStyle name="Обычный 7 2 2 3" xfId="885" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
+    <cellStyle name="Обычный 7 2 2 3 2" xfId="887" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
+    <cellStyle name="Обычный 7 2 2 3 3" xfId="889" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
+    <cellStyle name="Обычный 7 2 2 3 4" xfId="891" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
+    <cellStyle name="Обычный 7 2 2 3 5" xfId="893" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
+    <cellStyle name="Обычный 7 2 2 4" xfId="895" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
+    <cellStyle name="Обычный 7 2 2 5" xfId="734" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
+    <cellStyle name="Обычный 7 2 2 6" xfId="789" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
+    <cellStyle name="Обычный 7 2 2 7" xfId="810" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
+    <cellStyle name="Обычный 7 2 3" xfId="896" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
+    <cellStyle name="Обычный 7 2 3 2" xfId="898" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
+    <cellStyle name="Обычный 7 2 3 2 2" xfId="899" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
+    <cellStyle name="Обычный 7 2 3 2 3" xfId="901" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
+    <cellStyle name="Обычный 7 2 3 2 4" xfId="903" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
+    <cellStyle name="Обычный 7 2 3 2 5" xfId="905" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
+    <cellStyle name="Обычный 7 2 3 3" xfId="908" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
+    <cellStyle name="Обычный 7 2 3 4" xfId="910" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
+    <cellStyle name="Обычный 7 2 3 5" xfId="865" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
+    <cellStyle name="Обычный 7 2 3 6" xfId="912" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
+    <cellStyle name="Обычный 7 2 4" xfId="913" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
+    <cellStyle name="Обычный 7 2 4 2" xfId="915" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
+    <cellStyle name="Обычный 7 2 4 3" xfId="918" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
+    <cellStyle name="Обычный 7 2 4 4" xfId="919" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
+    <cellStyle name="Обычный 7 2 4 5" xfId="921" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
+    <cellStyle name="Обычный 7 2 5" xfId="922" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
+    <cellStyle name="Обычный 7 2 6" xfId="923" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
+    <cellStyle name="Обычный 7 2 7" xfId="924" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="Обычный 7 2 8" xfId="925" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
+    <cellStyle name="Обычный 7 3" xfId="911" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
+    <cellStyle name="Обычный 7 3 2" xfId="926" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
+    <cellStyle name="Обычный 7 3 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
+    <cellStyle name="Обычный 7 3 2 2 2" xfId="928" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
+    <cellStyle name="Обычный 7 3 2 2 3" xfId="872" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
+    <cellStyle name="Обычный 7 3 2 2 4" xfId="875" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
+    <cellStyle name="Обычный 7 3 2 2 5" xfId="877" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
+    <cellStyle name="Обычный 7 3 2 3" xfId="66" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
+    <cellStyle name="Обычный 7 3 2 4" xfId="59" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
+    <cellStyle name="Обычный 7 3 2 5" xfId="47" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
+    <cellStyle name="Обычный 7 3 2 6" xfId="930" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
+    <cellStyle name="Обычный 7 3 3" xfId="931" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
+    <cellStyle name="Обычный 7 3 3 2" xfId="933" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
+    <cellStyle name="Обычный 7 3 3 3" xfId="935" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
+    <cellStyle name="Обычный 7 3 3 4" xfId="937" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
+    <cellStyle name="Обычный 7 3 3 5" xfId="939" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
+    <cellStyle name="Обычный 7 3 4" xfId="940" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
+    <cellStyle name="Обычный 7 3 5" xfId="941" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
+    <cellStyle name="Обычный 7 3 6" xfId="942" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
+    <cellStyle name="Обычный 7 3 7" xfId="943" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
+    <cellStyle name="Обычный 7 4" xfId="944" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
+    <cellStyle name="Обычный 7 4 2" xfId="945" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
+    <cellStyle name="Обычный 7 4 2 2" xfId="946" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
+    <cellStyle name="Обычный 7 4 2 3" xfId="947" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
+    <cellStyle name="Обычный 7 4 2 4" xfId="948" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
+    <cellStyle name="Обычный 7 4 2 5" xfId="949" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
+    <cellStyle name="Обычный 7 4 3" xfId="950" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
+    <cellStyle name="Обычный 7 4 4" xfId="951" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
+    <cellStyle name="Обычный 7 4 5" xfId="952" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
+    <cellStyle name="Обычный 7 4 6" xfId="953" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
+    <cellStyle name="Обычный 7 5" xfId="954" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
+    <cellStyle name="Обычный 7 5 2" xfId="955" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
+    <cellStyle name="Обычный 7 5 2 2" xfId="956" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
+    <cellStyle name="Обычный 7 5 2 3" xfId="957" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
+    <cellStyle name="Обычный 7 5 2 4" xfId="958" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
+    <cellStyle name="Обычный 7 5 2 5" xfId="959" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
+    <cellStyle name="Обычный 7 5 3" xfId="960" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
+    <cellStyle name="Обычный 7 5 4" xfId="961" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
+    <cellStyle name="Обычный 7 5 5" xfId="962" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
+    <cellStyle name="Обычный 7 5 6" xfId="963" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
+    <cellStyle name="Обычный 7 6" xfId="964" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
+    <cellStyle name="Обычный 7 6 2" xfId="965" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
+    <cellStyle name="Обычный 7 6 2 2" xfId="966" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
+    <cellStyle name="Обычный 7 6 2 3" xfId="968" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
+    <cellStyle name="Обычный 7 6 2 4" xfId="970" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
+    <cellStyle name="Обычный 7 6 2 5" xfId="971" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
+    <cellStyle name="Обычный 7 6 3" xfId="972" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
+    <cellStyle name="Обычный 7 6 4" xfId="973" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
+    <cellStyle name="Обычный 7 6 5" xfId="974" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
+    <cellStyle name="Обычный 7 6 6" xfId="343" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
+    <cellStyle name="Обычный 7 7" xfId="975" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
+    <cellStyle name="Обычный 7 7 2" xfId="976" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
+    <cellStyle name="Обычный 7 7 3" xfId="977" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
+    <cellStyle name="Обычный 7 7 4" xfId="978" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
+    <cellStyle name="Обычный 7 7 5" xfId="979" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
+    <cellStyle name="Обычный 7 8" xfId="980" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
+    <cellStyle name="Обычный 7 9" xfId="192" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
+    <cellStyle name="Обычный 8" xfId="981" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
+    <cellStyle name="Обычный 8 2" xfId="920" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
+    <cellStyle name="Обычный 9" xfId="982" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
+    <cellStyle name="Обычный 9 2" xfId="984" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
     <cellStyle name="Процентный" xfId="13" builtinId="5"/>
-    <cellStyle name="Стиль 1" xfId="693"/>
-    <cellStyle name="Стиль 1 2" xfId="985"/>
-    <cellStyle name="Стиль 1 2 2" xfId="986"/>
-    <cellStyle name="Стиль 1 3" xfId="987"/>
-    <cellStyle name="Стиль 1 3 2" xfId="988"/>
-    <cellStyle name="Стиль 1 4" xfId="989"/>
-    <cellStyle name="Стиль 1 4 2" xfId="990"/>
-    <cellStyle name="Стиль 1 5" xfId="991"/>
-    <cellStyle name="Стиль 1 5 2" xfId="993"/>
-    <cellStyle name="Финансовый 2" xfId="994"/>
-    <cellStyle name="Финансовый 2 10" xfId="995"/>
-    <cellStyle name="Финансовый 2 10 2" xfId="997"/>
-    <cellStyle name="Финансовый 2 2" xfId="221"/>
-    <cellStyle name="Финансовый 2 3" xfId="236"/>
-    <cellStyle name="Финансовый 2 4" xfId="260"/>
-    <cellStyle name="Финансовый 2 4 2" xfId="263"/>
-    <cellStyle name="Финансовый 2 5" xfId="272"/>
-    <cellStyle name="Финансовый 2 5 2" xfId="998"/>
-    <cellStyle name="Финансовый 2 6" xfId="274"/>
-    <cellStyle name="Финансовый 2 6 2" xfId="999"/>
-    <cellStyle name="Финансовый 2 7" xfId="276"/>
-    <cellStyle name="Финансовый 2 7 2" xfId="1001"/>
-    <cellStyle name="Финансовый 2 8" xfId="1003"/>
-    <cellStyle name="Финансовый 2 8 2" xfId="1005"/>
-    <cellStyle name="Финансовый 2 9" xfId="1007"/>
-    <cellStyle name="Финансовый 2 9 2" xfId="1009"/>
-    <cellStyle name="Финансовый 3" xfId="33"/>
-    <cellStyle name="Финансовый 4" xfId="1642"/>
-    <cellStyle name="Финансовый 5" xfId="1651"/>
-    <cellStyle name="千位分隔 10" xfId="1464"/>
-    <cellStyle name="千位分隔 10 2" xfId="1465"/>
-    <cellStyle name="千位分隔 10 2 2" xfId="1466"/>
-    <cellStyle name="千位分隔 10 2 3" xfId="1467"/>
-    <cellStyle name="千位分隔 10 2 4" xfId="1468"/>
-    <cellStyle name="千位分隔 10 2 5" xfId="1469"/>
-    <cellStyle name="千位分隔 10 3" xfId="1470"/>
-    <cellStyle name="千位分隔 10 4" xfId="1471"/>
-    <cellStyle name="千位分隔 10 5" xfId="1472"/>
-    <cellStyle name="千位分隔 10 6" xfId="1473"/>
-    <cellStyle name="千位分隔 11" xfId="1474"/>
-    <cellStyle name="千位分隔 11 2" xfId="1475"/>
-    <cellStyle name="千位分隔 12" xfId="1476"/>
-    <cellStyle name="千位分隔 12 2" xfId="46"/>
-    <cellStyle name="千位分隔 12 2 2" xfId="1328"/>
-    <cellStyle name="千位分隔 12 2 3" xfId="1477"/>
-    <cellStyle name="千位分隔 12 2 4" xfId="1478"/>
-    <cellStyle name="千位分隔 12 2 5" xfId="1479"/>
-    <cellStyle name="千位分隔 12 3" xfId="929"/>
-    <cellStyle name="千位分隔 12 4" xfId="1480"/>
-    <cellStyle name="千位分隔 12 5" xfId="1481"/>
-    <cellStyle name="千位分隔 12 6" xfId="1482"/>
-    <cellStyle name="千位分隔 13" xfId="14"/>
-    <cellStyle name="千位分隔 13 2" xfId="938"/>
-    <cellStyle name="千位分隔 13 2 2" xfId="1383"/>
-    <cellStyle name="千位分隔 13 2 3" xfId="1484"/>
-    <cellStyle name="千位分隔 13 2 4" xfId="1485"/>
-    <cellStyle name="千位分隔 13 2 5" xfId="1486"/>
-    <cellStyle name="千位分隔 13 3" xfId="1487"/>
-    <cellStyle name="千位分隔 13 4" xfId="1488"/>
-    <cellStyle name="千位分隔 13 5" xfId="1489"/>
-    <cellStyle name="千位分隔 13 6" xfId="1490"/>
-    <cellStyle name="千位分隔 13 7" xfId="1483"/>
-    <cellStyle name="千位分隔 14" xfId="1491"/>
-    <cellStyle name="千位分隔 14 2" xfId="1492"/>
-    <cellStyle name="千位分隔 14 2 2" xfId="1493"/>
-    <cellStyle name="千位分隔 14 2 3" xfId="1494"/>
-    <cellStyle name="千位分隔 14 2 4" xfId="1495"/>
-    <cellStyle name="千位分隔 14 2 5" xfId="1496"/>
-    <cellStyle name="千位分隔 14 3" xfId="1497"/>
-    <cellStyle name="千位分隔 14 4" xfId="1498"/>
-    <cellStyle name="千位分隔 14 5" xfId="1499"/>
-    <cellStyle name="千位分隔 14 6" xfId="1500"/>
-    <cellStyle name="千位分隔 15" xfId="9"/>
-    <cellStyle name="千位分隔 15 2" xfId="1503"/>
-    <cellStyle name="千位分隔 15 3" xfId="1504"/>
-    <cellStyle name="千位分隔 15 4" xfId="1505"/>
-    <cellStyle name="千位分隔 15 5" xfId="1506"/>
-    <cellStyle name="千位分隔 15 6" xfId="1502"/>
-    <cellStyle name="千位分隔 16" xfId="605"/>
-    <cellStyle name="千位分隔 17" xfId="624"/>
-    <cellStyle name="千位分隔 17 2" xfId="626"/>
-    <cellStyle name="千位分隔 17 3" xfId="632"/>
-    <cellStyle name="千位分隔 18" xfId="11"/>
-    <cellStyle name="千位分隔 18 2" xfId="641"/>
-    <cellStyle name="千位分隔 19" xfId="16"/>
-    <cellStyle name="千位分隔 2" xfId="296"/>
-    <cellStyle name="千位分隔 2 10" xfId="1507"/>
-    <cellStyle name="千位分隔 2 11" xfId="1508"/>
-    <cellStyle name="千位分隔 2 12" xfId="290"/>
-    <cellStyle name="千位分隔 2 2" xfId="1509"/>
-    <cellStyle name="千位分隔 2 2 2" xfId="1287"/>
-    <cellStyle name="千位分隔 2 2 2 2" xfId="1510"/>
-    <cellStyle name="千位分隔 2 2 2 2 2" xfId="1511"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 2" xfId="1512"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 3" xfId="1513"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 4" xfId="1514"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 5" xfId="1515"/>
-    <cellStyle name="千位分隔 2 2 2 2 3" xfId="1516"/>
-    <cellStyle name="千位分隔 2 2 2 2 4" xfId="1517"/>
-    <cellStyle name="千位分隔 2 2 2 2 5" xfId="1518"/>
-    <cellStyle name="千位分隔 2 2 2 2 6" xfId="1089"/>
-    <cellStyle name="千位分隔 2 2 2 3" xfId="1519"/>
-    <cellStyle name="千位分隔 2 2 2 3 2" xfId="1520"/>
-    <cellStyle name="千位分隔 2 2 2 3 3" xfId="1521"/>
-    <cellStyle name="千位分隔 2 2 2 3 4" xfId="1522"/>
-    <cellStyle name="千位分隔 2 2 2 3 5" xfId="1523"/>
-    <cellStyle name="千位分隔 2 2 2 4" xfId="1524"/>
-    <cellStyle name="千位分隔 2 2 2 5" xfId="1525"/>
-    <cellStyle name="千位分隔 2 2 2 6" xfId="1526"/>
-    <cellStyle name="千位分隔 2 2 2 7" xfId="1527"/>
-    <cellStyle name="千位分隔 2 2 3" xfId="1528"/>
-    <cellStyle name="千位分隔 2 2 3 2" xfId="1529"/>
-    <cellStyle name="千位分隔 2 2 3 2 2" xfId="1530"/>
-    <cellStyle name="千位分隔 2 2 3 2 3" xfId="1531"/>
-    <cellStyle name="千位分隔 2 2 3 2 4" xfId="1532"/>
-    <cellStyle name="千位分隔 2 2 3 2 5" xfId="1533"/>
-    <cellStyle name="千位分隔 2 2 3 3" xfId="1534"/>
-    <cellStyle name="千位分隔 2 2 3 4" xfId="1535"/>
-    <cellStyle name="千位分隔 2 2 3 5" xfId="1536"/>
-    <cellStyle name="千位分隔 2 2 3 6" xfId="1537"/>
-    <cellStyle name="千位分隔 2 2 4" xfId="992"/>
-    <cellStyle name="千位分隔 2 2 4 2" xfId="62"/>
-    <cellStyle name="千位分隔 2 2 4 3" xfId="64"/>
-    <cellStyle name="千位分隔 2 2 4 4" xfId="68"/>
-    <cellStyle name="千位分隔 2 2 4 5" xfId="72"/>
-    <cellStyle name="千位分隔 2 2 5" xfId="1203"/>
-    <cellStyle name="千位分隔 2 2 6" xfId="1205"/>
-    <cellStyle name="千位分隔 2 2 7" xfId="512"/>
-    <cellStyle name="千位分隔 2 2 8" xfId="1207"/>
-    <cellStyle name="千位分隔 2 3" xfId="7"/>
-    <cellStyle name="千位分隔 2 3 2" xfId="1300"/>
-    <cellStyle name="千位分隔 2 3 2 2" xfId="1539"/>
-    <cellStyle name="千位分隔 2 3 2 2 2" xfId="724"/>
-    <cellStyle name="千位分隔 2 3 2 2 3" xfId="727"/>
-    <cellStyle name="千位分隔 2 3 2 2 4" xfId="1540"/>
-    <cellStyle name="千位分隔 2 3 2 2 5" xfId="1541"/>
-    <cellStyle name="千位分隔 2 3 2 3" xfId="1542"/>
-    <cellStyle name="千位分隔 2 3 2 4" xfId="1543"/>
-    <cellStyle name="千位分隔 2 3 2 5" xfId="1544"/>
-    <cellStyle name="千位分隔 2 3 2 6" xfId="1545"/>
-    <cellStyle name="千位分隔 2 3 3" xfId="1546"/>
-    <cellStyle name="千位分隔 2 3 3 2" xfId="1547"/>
-    <cellStyle name="千位分隔 2 3 3 3" xfId="1548"/>
-    <cellStyle name="千位分隔 2 3 3 4" xfId="1549"/>
-    <cellStyle name="千位分隔 2 3 3 5" xfId="1550"/>
-    <cellStyle name="千位分隔 2 3 4" xfId="1551"/>
-    <cellStyle name="千位分隔 2 3 5" xfId="1552"/>
-    <cellStyle name="千位分隔 2 3 6" xfId="1553"/>
-    <cellStyle name="千位分隔 2 3 7" xfId="187"/>
-    <cellStyle name="千位分隔 2 3 8" xfId="1538"/>
-    <cellStyle name="千位分隔 2 4" xfId="544"/>
-    <cellStyle name="千位分隔 2 4 2" xfId="547"/>
-    <cellStyle name="千位分隔 2 4 2 2" xfId="1554"/>
-    <cellStyle name="千位分隔 2 4 2 3" xfId="1555"/>
-    <cellStyle name="千位分隔 2 4 2 4" xfId="1556"/>
-    <cellStyle name="千位分隔 2 4 2 5" xfId="1557"/>
-    <cellStyle name="千位分隔 2 4 3" xfId="550"/>
-    <cellStyle name="千位分隔 2 4 4" xfId="34"/>
-    <cellStyle name="千位分隔 2 4 5" xfId="194"/>
-    <cellStyle name="千位分隔 2 4 6" xfId="197"/>
-    <cellStyle name="千位分隔 2 5" xfId="579"/>
-    <cellStyle name="千位分隔 2 5 2" xfId="349"/>
-    <cellStyle name="千位分隔 2 5 2 2" xfId="354"/>
-    <cellStyle name="千位分隔 2 5 2 3" xfId="357"/>
-    <cellStyle name="千位分隔 2 5 2 4" xfId="360"/>
-    <cellStyle name="千位分隔 2 5 2 5" xfId="315"/>
-    <cellStyle name="千位分隔 2 5 3" xfId="90"/>
-    <cellStyle name="千位分隔 2 5 4" xfId="586"/>
-    <cellStyle name="千位分隔 2 5 5" xfId="591"/>
-    <cellStyle name="千位分隔 2 5 6" xfId="593"/>
-    <cellStyle name="千位分隔 2 6" xfId="28"/>
-    <cellStyle name="千位分隔 2 6 2" xfId="1558"/>
-    <cellStyle name="千位分隔 2 6 2 2" xfId="1559"/>
-    <cellStyle name="千位分隔 2 6 2 3" xfId="1560"/>
-    <cellStyle name="千位分隔 2 6 2 4" xfId="1561"/>
-    <cellStyle name="千位分隔 2 6 2 5" xfId="1562"/>
-    <cellStyle name="千位分隔 2 6 3" xfId="1563"/>
-    <cellStyle name="千位分隔 2 6 4" xfId="1564"/>
-    <cellStyle name="千位分隔 2 6 5" xfId="1565"/>
-    <cellStyle name="千位分隔 2 6 6" xfId="1566"/>
-    <cellStyle name="千位分隔 2 7" xfId="596"/>
-    <cellStyle name="千位分隔 2 7 2" xfId="1567"/>
-    <cellStyle name="千位分隔 2 7 3" xfId="1568"/>
-    <cellStyle name="千位分隔 2 7 4" xfId="1569"/>
-    <cellStyle name="千位分隔 2 7 5" xfId="1570"/>
-    <cellStyle name="千位分隔 2 8" xfId="598"/>
-    <cellStyle name="千位分隔 2 8 2" xfId="1571"/>
-    <cellStyle name="千位分隔 2 8 3" xfId="1572"/>
-    <cellStyle name="千位分隔 2 8 4" xfId="996"/>
-    <cellStyle name="千位分隔 2 8 5" xfId="1573"/>
-    <cellStyle name="千位分隔 2 9" xfId="510"/>
-    <cellStyle name="千位分隔 2 9 2" xfId="1574"/>
-    <cellStyle name="千位分隔 2 9 3" xfId="1575"/>
-    <cellStyle name="千位分隔 2 9 4" xfId="1576"/>
-    <cellStyle name="千位分隔 20" xfId="15"/>
-    <cellStyle name="千位分隔 20 2" xfId="1501"/>
-    <cellStyle name="千位分隔 21" xfId="604"/>
-    <cellStyle name="千位分隔 22" xfId="623"/>
-    <cellStyle name="千位分隔 23" xfId="640"/>
-    <cellStyle name="千位分隔 24" xfId="649"/>
-    <cellStyle name="千位分隔 25" xfId="651"/>
-    <cellStyle name="千位分隔 3" xfId="299"/>
-    <cellStyle name="千位分隔 3 2" xfId="1577"/>
-    <cellStyle name="千位分隔 3 2 2" xfId="1578"/>
-    <cellStyle name="千位分隔 3 2 2 2" xfId="900"/>
-    <cellStyle name="千位分隔 3 2 2 2 2" xfId="1579"/>
-    <cellStyle name="千位分隔 3 2 2 2 3" xfId="1580"/>
-    <cellStyle name="千位分隔 3 2 2 2 4" xfId="1581"/>
-    <cellStyle name="千位分隔 3 2 2 2 5" xfId="1582"/>
-    <cellStyle name="千位分隔 3 2 2 3" xfId="902"/>
-    <cellStyle name="千位分隔 3 2 2 4" xfId="904"/>
-    <cellStyle name="千位分隔 3 2 2 5" xfId="1583"/>
-    <cellStyle name="千位分隔 3 2 2 6" xfId="1584"/>
-    <cellStyle name="千位分隔 3 2 3" xfId="1585"/>
-    <cellStyle name="千位分隔 3 2 3 2" xfId="1586"/>
-    <cellStyle name="千位分隔 3 2 3 3" xfId="1587"/>
-    <cellStyle name="千位分隔 3 2 3 4" xfId="1588"/>
-    <cellStyle name="千位分隔 3 2 3 5" xfId="1589"/>
-    <cellStyle name="千位分隔 3 2 4" xfId="1590"/>
-    <cellStyle name="千位分隔 3 2 5" xfId="1591"/>
-    <cellStyle name="千位分隔 3 2 6" xfId="1592"/>
-    <cellStyle name="千位分隔 3 2 7" xfId="1593"/>
-    <cellStyle name="千位分隔 3 3" xfId="1594"/>
-    <cellStyle name="千位分隔 3 3 2" xfId="1595"/>
-    <cellStyle name="千位分隔 3 3 2 2" xfId="1596"/>
-    <cellStyle name="千位分隔 3 3 2 3" xfId="1597"/>
-    <cellStyle name="千位分隔 3 3 2 4" xfId="1598"/>
-    <cellStyle name="千位分隔 3 3 2 5" xfId="1599"/>
-    <cellStyle name="千位分隔 3 3 3" xfId="1600"/>
-    <cellStyle name="千位分隔 3 3 4" xfId="1601"/>
-    <cellStyle name="千位分隔 3 3 5" xfId="1602"/>
-    <cellStyle name="千位分隔 3 3 6" xfId="1603"/>
-    <cellStyle name="千位分隔 3 4" xfId="601"/>
-    <cellStyle name="千位分隔 3 4 2" xfId="43"/>
-    <cellStyle name="千位分隔 3 4 3" xfId="655"/>
-    <cellStyle name="千位分隔 3 4 4" xfId="680"/>
-    <cellStyle name="千位分隔 3 4 5" xfId="695"/>
-    <cellStyle name="千位分隔 3 5" xfId="714"/>
-    <cellStyle name="千位分隔 3 6" xfId="717"/>
-    <cellStyle name="千位分隔 3 7" xfId="720"/>
-    <cellStyle name="千位分隔 3 8" xfId="723"/>
-    <cellStyle name="千位分隔 4" xfId="1604"/>
-    <cellStyle name="千位分隔 4 2" xfId="884"/>
-    <cellStyle name="千位分隔 4 2 2" xfId="886"/>
-    <cellStyle name="千位分隔 4 2 2 2" xfId="1389"/>
-    <cellStyle name="千位分隔 4 2 2 2 2" xfId="1605"/>
-    <cellStyle name="千位分隔 4 2 2 2 3" xfId="1606"/>
-    <cellStyle name="千位分隔 4 2 2 2 4" xfId="1607"/>
-    <cellStyle name="千位分隔 4 2 2 2 5" xfId="1608"/>
-    <cellStyle name="千位分隔 4 2 2 3" xfId="1392"/>
-    <cellStyle name="千位分隔 4 2 2 4" xfId="1609"/>
-    <cellStyle name="千位分隔 4 2 2 5" xfId="1610"/>
-    <cellStyle name="千位分隔 4 2 2 6" xfId="1611"/>
-    <cellStyle name="千位分隔 4 2 3" xfId="888"/>
-    <cellStyle name="千位分隔 4 2 3 2" xfId="1411"/>
-    <cellStyle name="千位分隔 4 2 3 3" xfId="1612"/>
-    <cellStyle name="千位分隔 4 2 3 4" xfId="1613"/>
-    <cellStyle name="千位分隔 4 2 3 5" xfId="1614"/>
-    <cellStyle name="千位分隔 4 2 4" xfId="890"/>
-    <cellStyle name="千位分隔 4 2 5" xfId="892"/>
-    <cellStyle name="千位分隔 4 2 6" xfId="1615"/>
-    <cellStyle name="千位分隔 4 2 7" xfId="1616"/>
-    <cellStyle name="千位分隔 4 3" xfId="894"/>
-    <cellStyle name="千位分隔 4 3 2" xfId="1617"/>
-    <cellStyle name="千位分隔 4 3 2 2" xfId="1435"/>
-    <cellStyle name="千位分隔 4 3 2 3" xfId="1437"/>
-    <cellStyle name="千位分隔 4 3 2 4" xfId="1618"/>
-    <cellStyle name="千位分隔 4 3 2 5" xfId="1619"/>
-    <cellStyle name="千位分隔 4 3 3" xfId="1620"/>
-    <cellStyle name="千位分隔 4 3 4" xfId="1621"/>
-    <cellStyle name="千位分隔 4 3 5" xfId="1622"/>
-    <cellStyle name="千位分隔 4 3 6" xfId="1623"/>
-    <cellStyle name="千位分隔 4 4" xfId="733"/>
-    <cellStyle name="千位分隔 4 4 2" xfId="736"/>
-    <cellStyle name="千位分隔 4 4 3" xfId="761"/>
-    <cellStyle name="千位分隔 4 4 4" xfId="773"/>
-    <cellStyle name="千位分隔 4 4 5" xfId="780"/>
-    <cellStyle name="千位分隔 4 5" xfId="788"/>
-    <cellStyle name="千位分隔 4 6" xfId="809"/>
-    <cellStyle name="千位分隔 4 7" xfId="821"/>
-    <cellStyle name="千位分隔 4 8" xfId="844"/>
-    <cellStyle name="千位分隔 5" xfId="1624"/>
-    <cellStyle name="千位分隔 5 2" xfId="906"/>
-    <cellStyle name="千位分隔 6" xfId="1102"/>
-    <cellStyle name="千位分隔 6 2" xfId="916"/>
-    <cellStyle name="千位分隔 7" xfId="1625"/>
-    <cellStyle name="千位分隔 7 2" xfId="1626"/>
-    <cellStyle name="千位分隔 7 2 2" xfId="1627"/>
-    <cellStyle name="千位分隔 7 2 2 2" xfId="1628"/>
-    <cellStyle name="千位分隔 7 2 2 3" xfId="1629"/>
-    <cellStyle name="千位分隔 7 2 2 4" xfId="1630"/>
-    <cellStyle name="千位分隔 7 2 2 5" xfId="1631"/>
-    <cellStyle name="千位分隔 7 2 3" xfId="657"/>
-    <cellStyle name="千位分隔 7 2 4" xfId="668"/>
-    <cellStyle name="千位分隔 7 2 5" xfId="674"/>
-    <cellStyle name="千位分隔 7 2 6" xfId="676"/>
-    <cellStyle name="千位分隔 7 3" xfId="1632"/>
-    <cellStyle name="千位分隔 7 3 2" xfId="1633"/>
-    <cellStyle name="千位分隔 7 3 3" xfId="682"/>
-    <cellStyle name="千位分隔 7 3 4" xfId="688"/>
-    <cellStyle name="千位分隔 7 3 5" xfId="690"/>
-    <cellStyle name="千位分隔 7 4" xfId="983"/>
-    <cellStyle name="千位分隔 7 5" xfId="1634"/>
-    <cellStyle name="千位分隔 7 6" xfId="1635"/>
-    <cellStyle name="千位分隔 7 7" xfId="1636"/>
-    <cellStyle name="千位分隔 8" xfId="1637"/>
-    <cellStyle name="千位分隔 8 2" xfId="1638"/>
-    <cellStyle name="千位分隔 8 3" xfId="1639"/>
-    <cellStyle name="千位分隔 9" xfId="1640"/>
-    <cellStyle name="常规 10" xfId="439"/>
-    <cellStyle name="常规 10 10" xfId="1010"/>
-    <cellStyle name="常规 10 11" xfId="1011"/>
-    <cellStyle name="常规 10 12" xfId="1654"/>
-    <cellStyle name="常规 10 2" xfId="441"/>
-    <cellStyle name="常规 10 2 2" xfId="443"/>
-    <cellStyle name="常规 10 2 2 2" xfId="1012"/>
-    <cellStyle name="常规 10 2 2 2 2" xfId="1013"/>
-    <cellStyle name="常规 10 2 2 2 2 2" xfId="1014"/>
-    <cellStyle name="常规 10 2 2 2 3" xfId="1015"/>
-    <cellStyle name="常规 10 2 2 2 4" xfId="1016"/>
-    <cellStyle name="常规 10 2 2 2 5" xfId="1017"/>
-    <cellStyle name="常规 10 2 2 2 6" xfId="1018"/>
-    <cellStyle name="常规 10 2 2 3" xfId="1019"/>
-    <cellStyle name="常规 10 2 2 3 2" xfId="1020"/>
-    <cellStyle name="常规 10 2 2 4" xfId="1021"/>
-    <cellStyle name="常规 10 2 2 5" xfId="1022"/>
-    <cellStyle name="常规 10 2 2 6" xfId="1023"/>
-    <cellStyle name="常规 10 2 3" xfId="445"/>
-    <cellStyle name="常规 10 2 3 2" xfId="556"/>
-    <cellStyle name="常规 10 2 3 2 2" xfId="1024"/>
-    <cellStyle name="常规 10 2 3 2 2 2" xfId="1025"/>
-    <cellStyle name="常规 10 2 3 2 3" xfId="1026"/>
-    <cellStyle name="常规 10 2 3 2 4" xfId="1027"/>
-    <cellStyle name="常规 10 2 3 2 5" xfId="1028"/>
-    <cellStyle name="常规 10 2 3 2 6" xfId="1029"/>
-    <cellStyle name="常规 10 2 3 3" xfId="1030"/>
-    <cellStyle name="常规 10 2 3 3 2" xfId="1031"/>
-    <cellStyle name="常规 10 2 3 4" xfId="1032"/>
-    <cellStyle name="常规 10 2 3 5" xfId="1033"/>
-    <cellStyle name="常规 10 2 3 6" xfId="1034"/>
-    <cellStyle name="常规 10 2 4" xfId="169"/>
-    <cellStyle name="常规 10 2 4 2" xfId="490"/>
-    <cellStyle name="常规 10 2 4 2 2" xfId="1035"/>
-    <cellStyle name="常规 10 2 4 2 2 2" xfId="459"/>
-    <cellStyle name="常规 10 2 4 2 3" xfId="1036"/>
-    <cellStyle name="常规 10 2 4 2 4" xfId="1037"/>
-    <cellStyle name="常规 10 2 4 2 5" xfId="1038"/>
-    <cellStyle name="常规 10 2 4 3" xfId="1039"/>
-    <cellStyle name="常规 10 2 4 3 2" xfId="1040"/>
-    <cellStyle name="常规 10 2 4 3 2 2" xfId="1041"/>
-    <cellStyle name="常规 10 2 4 3 3" xfId="1042"/>
-    <cellStyle name="常规 10 2 4 3 4" xfId="1043"/>
-    <cellStyle name="常规 10 2 4 3 5" xfId="1044"/>
-    <cellStyle name="常规 10 2 4 3 6" xfId="1046"/>
-    <cellStyle name="常规 10 2 4 4" xfId="1047"/>
-    <cellStyle name="常规 10 2 4 4 2" xfId="1048"/>
-    <cellStyle name="常规 10 2 4 5" xfId="1049"/>
-    <cellStyle name="常规 10 2 4 6" xfId="1050"/>
-    <cellStyle name="常规 10 2 4 7" xfId="1051"/>
-    <cellStyle name="常规 10 2 5" xfId="173"/>
-    <cellStyle name="常规 10 2 5 2" xfId="1052"/>
-    <cellStyle name="常规 10 2 5 2 2" xfId="1053"/>
-    <cellStyle name="常规 10 2 5 3" xfId="1054"/>
-    <cellStyle name="常规 10 2 5 4" xfId="1055"/>
-    <cellStyle name="常规 10 2 5 5" xfId="1056"/>
-    <cellStyle name="常规 10 2 5 6" xfId="1057"/>
-    <cellStyle name="常规 10 2 6" xfId="1058"/>
-    <cellStyle name="常规 10 2 6 2" xfId="1059"/>
-    <cellStyle name="常规 10 2 7" xfId="1060"/>
-    <cellStyle name="常规 10 2 8" xfId="1061"/>
-    <cellStyle name="常规 10 2 9" xfId="1062"/>
-    <cellStyle name="常规 10 3" xfId="447"/>
-    <cellStyle name="常规 10 3 2" xfId="1063"/>
-    <cellStyle name="常规 10 3 2 2" xfId="1064"/>
-    <cellStyle name="常规 10 3 2 2 2" xfId="1065"/>
-    <cellStyle name="常规 10 3 2 3" xfId="1066"/>
-    <cellStyle name="常规 10 3 2 4" xfId="1067"/>
-    <cellStyle name="常规 10 3 2 5" xfId="1068"/>
-    <cellStyle name="常规 10 3 3" xfId="1069"/>
-    <cellStyle name="常规 10 3 3 2" xfId="1070"/>
-    <cellStyle name="常规 10 3 3 2 2" xfId="1071"/>
-    <cellStyle name="常规 10 3 3 3" xfId="1072"/>
-    <cellStyle name="常规 10 3 3 4" xfId="1073"/>
-    <cellStyle name="常规 10 3 3 5" xfId="1074"/>
-    <cellStyle name="常规 10 3 3 6" xfId="1075"/>
-    <cellStyle name="常规 10 3 4" xfId="1076"/>
-    <cellStyle name="常规 10 3 4 2" xfId="1077"/>
-    <cellStyle name="常规 10 3 5" xfId="1078"/>
-    <cellStyle name="常规 10 3 6" xfId="1079"/>
-    <cellStyle name="常规 10 3 7" xfId="1080"/>
-    <cellStyle name="常规 10 4" xfId="449"/>
-    <cellStyle name="常规 10 4 2" xfId="1081"/>
-    <cellStyle name="常规 10 4 2 2" xfId="1082"/>
-    <cellStyle name="常规 10 4 2 2 2" xfId="1083"/>
-    <cellStyle name="常规 10 4 2 3" xfId="1084"/>
-    <cellStyle name="常规 10 4 2 4" xfId="1085"/>
-    <cellStyle name="常规 10 4 2 5" xfId="1086"/>
-    <cellStyle name="常规 10 4 3" xfId="1087"/>
-    <cellStyle name="常规 10 4 3 2" xfId="1088"/>
-    <cellStyle name="常规 10 4 3 2 2" xfId="1090"/>
-    <cellStyle name="常规 10 4 3 3" xfId="1091"/>
-    <cellStyle name="常规 10 4 3 4" xfId="1092"/>
-    <cellStyle name="常规 10 4 3 5" xfId="1093"/>
-    <cellStyle name="常规 10 4 3 6" xfId="1094"/>
-    <cellStyle name="常规 10 4 4" xfId="1095"/>
-    <cellStyle name="常规 10 4 4 2" xfId="1096"/>
-    <cellStyle name="常规 10 4 5" xfId="1097"/>
-    <cellStyle name="常规 10 4 6" xfId="1098"/>
-    <cellStyle name="常规 10 4 7" xfId="1099"/>
-    <cellStyle name="常规 10 5" xfId="451"/>
-    <cellStyle name="常规 10 5 2" xfId="1100"/>
-    <cellStyle name="常规 10 5 2 2" xfId="1101"/>
-    <cellStyle name="常规 10 5 2 2 2" xfId="1103"/>
-    <cellStyle name="常规 10 5 2 3" xfId="1104"/>
-    <cellStyle name="常规 10 5 2 4" xfId="1105"/>
-    <cellStyle name="常规 10 5 2 5" xfId="1106"/>
-    <cellStyle name="常规 10 5 3" xfId="1107"/>
-    <cellStyle name="常规 10 5 3 2" xfId="1108"/>
-    <cellStyle name="常规 10 5 3 2 2" xfId="1109"/>
-    <cellStyle name="常规 10 5 3 3" xfId="1110"/>
-    <cellStyle name="常规 10 5 3 4" xfId="1111"/>
-    <cellStyle name="常规 10 5 3 5" xfId="1112"/>
-    <cellStyle name="常规 10 5 3 6" xfId="1113"/>
-    <cellStyle name="常规 10 5 4" xfId="1114"/>
-    <cellStyle name="常规 10 5 4 2" xfId="1115"/>
-    <cellStyle name="常规 10 5 5" xfId="1116"/>
-    <cellStyle name="常规 10 5 6" xfId="1118"/>
-    <cellStyle name="常规 10 5 7" xfId="1120"/>
-    <cellStyle name="常规 10 6" xfId="453"/>
-    <cellStyle name="常规 10 6 2" xfId="1121"/>
-    <cellStyle name="常规 10 6 2 2" xfId="1122"/>
-    <cellStyle name="常规 10 6 3" xfId="1123"/>
-    <cellStyle name="常规 10 6 4" xfId="1124"/>
-    <cellStyle name="常规 10 6 5" xfId="1125"/>
-    <cellStyle name="常规 10 6 6" xfId="429"/>
-    <cellStyle name="常规 10 7" xfId="1126"/>
-    <cellStyle name="常规 10 7 2" xfId="1127"/>
-    <cellStyle name="常规 10 7 2 2" xfId="1128"/>
-    <cellStyle name="常规 10 7 3" xfId="1129"/>
-    <cellStyle name="常规 10 7 4" xfId="1130"/>
-    <cellStyle name="常规 10 7 5" xfId="1131"/>
-    <cellStyle name="常规 10 7 6" xfId="1133"/>
-    <cellStyle name="常规 10 8" xfId="1134"/>
-    <cellStyle name="常规 10 8 2" xfId="1135"/>
-    <cellStyle name="常规 10 8 3" xfId="1136"/>
-    <cellStyle name="常规 10 8 4" xfId="1137"/>
-    <cellStyle name="常规 10 8 5" xfId="1138"/>
-    <cellStyle name="常规 10 9" xfId="1139"/>
-    <cellStyle name="常规 11" xfId="455"/>
-    <cellStyle name="常规 11 2" xfId="457"/>
-    <cellStyle name="常规 11 3" xfId="1647"/>
-    <cellStyle name="常规 12" xfId="463"/>
-    <cellStyle name="常规 12 2" xfId="745"/>
-    <cellStyle name="常规 13" xfId="363"/>
-    <cellStyle name="常规 13 2" xfId="753"/>
-    <cellStyle name="常规 14" xfId="405"/>
-    <cellStyle name="常规 14 2" xfId="1140"/>
-    <cellStyle name="常规 15" xfId="5"/>
-    <cellStyle name="常规 15 2" xfId="1142"/>
-    <cellStyle name="常规 15 2 2" xfId="1143"/>
-    <cellStyle name="常规 15 2 2 2" xfId="1144"/>
-    <cellStyle name="常规 15 2 2 3" xfId="1145"/>
-    <cellStyle name="常规 15 2 2 4" xfId="1146"/>
-    <cellStyle name="常规 15 2 2 5" xfId="1147"/>
-    <cellStyle name="常规 15 2 3" xfId="1148"/>
-    <cellStyle name="常规 15 2 4" xfId="897"/>
-    <cellStyle name="常规 15 2 5" xfId="907"/>
-    <cellStyle name="常规 15 2 6" xfId="909"/>
-    <cellStyle name="常规 15 3" xfId="1151"/>
-    <cellStyle name="常规 15 3 2" xfId="1152"/>
-    <cellStyle name="常规 15 3 3" xfId="1153"/>
-    <cellStyle name="常规 15 3 4" xfId="914"/>
-    <cellStyle name="常规 15 3 5" xfId="917"/>
-    <cellStyle name="常规 15 4" xfId="1155"/>
-    <cellStyle name="常规 15 5" xfId="1157"/>
-    <cellStyle name="常规 15 6" xfId="1159"/>
-    <cellStyle name="常规 15 7" xfId="1160"/>
-    <cellStyle name="常规 15 8" xfId="239"/>
-    <cellStyle name="常规 16" xfId="1162"/>
-    <cellStyle name="常规 16 2" xfId="1164"/>
-    <cellStyle name="常规 16 2 2" xfId="1165"/>
-    <cellStyle name="常规 16 2 2 2" xfId="1167"/>
-    <cellStyle name="常规 16 2 2 3" xfId="1169"/>
-    <cellStyle name="常规 16 2 2 4" xfId="171"/>
-    <cellStyle name="常规 16 2 2 5" xfId="175"/>
-    <cellStyle name="常规 16 2 3" xfId="1170"/>
-    <cellStyle name="常规 16 2 4" xfId="932"/>
-    <cellStyle name="常规 16 2 5" xfId="934"/>
-    <cellStyle name="常规 16 2 6" xfId="936"/>
-    <cellStyle name="常规 16 3" xfId="1171"/>
-    <cellStyle name="常规 16 3 2" xfId="1172"/>
-    <cellStyle name="常规 16 3 3" xfId="1173"/>
-    <cellStyle name="常规 16 3 4" xfId="1174"/>
-    <cellStyle name="常规 16 3 5" xfId="1175"/>
-    <cellStyle name="常规 16 4" xfId="1176"/>
-    <cellStyle name="常规 16 5" xfId="1177"/>
-    <cellStyle name="常规 16 6" xfId="1178"/>
-    <cellStyle name="常规 16 7" xfId="1179"/>
-    <cellStyle name="常规 17" xfId="1181"/>
-    <cellStyle name="常规 17 2" xfId="1183"/>
-    <cellStyle name="常规 17 3" xfId="1185"/>
-    <cellStyle name="常规 18" xfId="1187"/>
-    <cellStyle name="常规 18 2" xfId="1189"/>
-    <cellStyle name="常规 18 3" xfId="1191"/>
-    <cellStyle name="常规 19" xfId="1193"/>
-    <cellStyle name="常规 19 2" xfId="10"/>
-    <cellStyle name="常规 19 3" xfId="1195"/>
-    <cellStyle name="常规 2" xfId="1196"/>
-    <cellStyle name="常规 2 10" xfId="1658"/>
-    <cellStyle name="常规 2 2" xfId="1197"/>
-    <cellStyle name="常规 2 2 2" xfId="1198"/>
-    <cellStyle name="常规 2 2 2 2" xfId="1117"/>
-    <cellStyle name="常规 2 2 2 2 2" xfId="1199"/>
-    <cellStyle name="常规 2 2 2 2 3" xfId="1200"/>
-    <cellStyle name="常规 2 2 2 2 4" xfId="1201"/>
-    <cellStyle name="常规 2 2 2 2 5" xfId="1202"/>
-    <cellStyle name="常规 2 2 2 3" xfId="1119"/>
-    <cellStyle name="常规 2 2 2 4" xfId="61"/>
-    <cellStyle name="常规 2 2 2 5" xfId="50"/>
-    <cellStyle name="常规 2 2 2 6" xfId="63"/>
-    <cellStyle name="常规 2 2 3" xfId="567"/>
-    <cellStyle name="常规 2 2 3 2" xfId="428"/>
-    <cellStyle name="常规 2 2 3 2 2" xfId="1204"/>
-    <cellStyle name="常规 2 2 3 2 3" xfId="1206"/>
-    <cellStyle name="常规 2 2 3 2 4" xfId="513"/>
-    <cellStyle name="常规 2 2 3 2 5" xfId="1208"/>
-    <cellStyle name="常规 2 2 3 3" xfId="432"/>
-    <cellStyle name="常规 2 2 3 4" xfId="435"/>
-    <cellStyle name="常规 2 2 3 5" xfId="569"/>
-    <cellStyle name="常规 2 2 3 6" xfId="1209"/>
-    <cellStyle name="常规 2 2 4" xfId="25"/>
-    <cellStyle name="常规 2 2 4 2" xfId="1132"/>
-    <cellStyle name="常规 2 2 4 3" xfId="1210"/>
-    <cellStyle name="常规 2 2 4 4" xfId="1211"/>
-    <cellStyle name="常规 2 2 4 5" xfId="1212"/>
-    <cellStyle name="常规 2 2 5" xfId="571"/>
-    <cellStyle name="常规 2 2 6" xfId="573"/>
-    <cellStyle name="常规 2 2 7" xfId="575"/>
-    <cellStyle name="常规 2 2 8" xfId="1213"/>
-    <cellStyle name="常规 2 3" xfId="1214"/>
-    <cellStyle name="常规 2 3 2" xfId="1215"/>
-    <cellStyle name="常规 2 3 2 2" xfId="1216"/>
-    <cellStyle name="常规 2 3 2 3" xfId="1217"/>
-    <cellStyle name="常规 2 3 2 4" xfId="1218"/>
-    <cellStyle name="常规 2 3 2 5" xfId="1219"/>
-    <cellStyle name="常规 2 3 3" xfId="577"/>
-    <cellStyle name="常规 2 3 4" xfId="416"/>
-    <cellStyle name="常规 2 3 5" xfId="419"/>
-    <cellStyle name="常规 2 3 6" xfId="422"/>
-    <cellStyle name="常规 2 4" xfId="1220"/>
-    <cellStyle name="常规 2 4 2" xfId="1221"/>
-    <cellStyle name="常规 2 4 2 2" xfId="1222"/>
-    <cellStyle name="常规 2 4 2 3" xfId="1223"/>
-    <cellStyle name="常规 2 4 2 4" xfId="1224"/>
-    <cellStyle name="常规 2 4 2 5" xfId="1225"/>
-    <cellStyle name="常规 2 4 3" xfId="1226"/>
-    <cellStyle name="常规 2 4 4" xfId="1227"/>
-    <cellStyle name="常规 2 4 5" xfId="1228"/>
-    <cellStyle name="常规 2 4 6" xfId="1229"/>
-    <cellStyle name="常规 2 5" xfId="1230"/>
-    <cellStyle name="常规 2 5 2" xfId="1231"/>
-    <cellStyle name="常规 2 5 2 2" xfId="1232"/>
-    <cellStyle name="常规 2 5 2 3" xfId="1233"/>
-    <cellStyle name="常规 2 5 2 4" xfId="1234"/>
-    <cellStyle name="常规 2 5 2 5" xfId="1000"/>
-    <cellStyle name="常规 2 5 3" xfId="1235"/>
-    <cellStyle name="常规 2 5 4" xfId="1236"/>
-    <cellStyle name="常规 2 5 5" xfId="1237"/>
-    <cellStyle name="常规 2 5 6" xfId="1238"/>
-    <cellStyle name="常规 2 6" xfId="1239"/>
-    <cellStyle name="常规 2 6 2" xfId="1240"/>
-    <cellStyle name="常规 2 6 3" xfId="1241"/>
-    <cellStyle name="常规 2 6 4" xfId="1242"/>
-    <cellStyle name="常规 2 6 5" xfId="1243"/>
-    <cellStyle name="常规 2 7" xfId="1166"/>
-    <cellStyle name="常规 2 7 2" xfId="1244"/>
-    <cellStyle name="常规 2 7 3" xfId="1245"/>
-    <cellStyle name="常规 2 7 4" xfId="1246"/>
-    <cellStyle name="常规 2 8" xfId="1168"/>
-    <cellStyle name="常规 2 8 2" xfId="967"/>
-    <cellStyle name="常规 2 8 3" xfId="969"/>
-    <cellStyle name="常规 2 9" xfId="1648"/>
-    <cellStyle name="常规 20" xfId="238"/>
-    <cellStyle name="常规 20 2" xfId="1141"/>
-    <cellStyle name="常规 20 3" xfId="1150"/>
-    <cellStyle name="常规 21" xfId="1161"/>
-    <cellStyle name="常规 21 2" xfId="1163"/>
-    <cellStyle name="常规 22" xfId="1180"/>
-    <cellStyle name="常规 22 2" xfId="1182"/>
-    <cellStyle name="常规 22 2 2" xfId="1247"/>
-    <cellStyle name="常规 22 2 3" xfId="1248"/>
-    <cellStyle name="常规 22 2 4" xfId="1249"/>
-    <cellStyle name="常规 22 2 5" xfId="103"/>
-    <cellStyle name="常规 22 3" xfId="1184"/>
-    <cellStyle name="常规 22 4" xfId="1250"/>
-    <cellStyle name="常规 22 5" xfId="1251"/>
-    <cellStyle name="常规 22 6" xfId="1252"/>
-    <cellStyle name="常规 23" xfId="1186"/>
-    <cellStyle name="常规 23 2" xfId="1188"/>
-    <cellStyle name="常规 23 2 2" xfId="1253"/>
-    <cellStyle name="常规 23 2 3" xfId="1254"/>
-    <cellStyle name="常规 23 2 4" xfId="1255"/>
-    <cellStyle name="常规 23 2 5" xfId="142"/>
-    <cellStyle name="常规 23 3" xfId="1190"/>
-    <cellStyle name="常规 23 4" xfId="1256"/>
-    <cellStyle name="常规 23 5" xfId="1257"/>
-    <cellStyle name="常规 23 6" xfId="1258"/>
-    <cellStyle name="常规 24" xfId="1192"/>
-    <cellStyle name="常规 24 2" xfId="1194"/>
-    <cellStyle name="常规 25" xfId="1260"/>
-    <cellStyle name="常规 25 2" xfId="1261"/>
-    <cellStyle name="常规 26" xfId="1263"/>
-    <cellStyle name="常规 26 2" xfId="31"/>
-    <cellStyle name="常规 27" xfId="1265"/>
-    <cellStyle name="常规 27 2" xfId="1267"/>
-    <cellStyle name="常规 27 2 2" xfId="1268"/>
-    <cellStyle name="常规 27 2 3" xfId="1269"/>
-    <cellStyle name="常规 27 2 4" xfId="1270"/>
-    <cellStyle name="常规 27 2 5" xfId="1271"/>
-    <cellStyle name="常规 27 3" xfId="1273"/>
-    <cellStyle name="常规 27 4" xfId="1275"/>
-    <cellStyle name="常规 27 5" xfId="1277"/>
-    <cellStyle name="常规 27 6" xfId="1278"/>
-    <cellStyle name="常规 28" xfId="1280"/>
-    <cellStyle name="常规 28 2" xfId="153"/>
-    <cellStyle name="常规 28 2 2" xfId="1281"/>
-    <cellStyle name="常规 28 2 3" xfId="1282"/>
-    <cellStyle name="常规 28 2 4" xfId="1283"/>
-    <cellStyle name="常规 28 2 5" xfId="1284"/>
-    <cellStyle name="常规 28 3" xfId="161"/>
-    <cellStyle name="常规 28 4" xfId="1285"/>
-    <cellStyle name="常规 28 5" xfId="1286"/>
-    <cellStyle name="常规 28 6" xfId="1288"/>
-    <cellStyle name="常规 29" xfId="1290"/>
-    <cellStyle name="常规 29 2" xfId="1292"/>
-    <cellStyle name="常规 29 2 2" xfId="1293"/>
-    <cellStyle name="常规 29 2 3" xfId="1294"/>
-    <cellStyle name="常规 29 2 4" xfId="1295"/>
-    <cellStyle name="常规 29 2 5" xfId="1296"/>
-    <cellStyle name="常规 29 3" xfId="1297"/>
-    <cellStyle name="常规 29 4" xfId="1298"/>
-    <cellStyle name="常规 29 5" xfId="1299"/>
-    <cellStyle name="常规 29 6" xfId="1301"/>
-    <cellStyle name="常规 3" xfId="1302"/>
-    <cellStyle name="常规 3 10" xfId="1659"/>
-    <cellStyle name="常规 3 2" xfId="1002"/>
-    <cellStyle name="常规 3 2 2" xfId="1004"/>
-    <cellStyle name="常规 3 2 2 2" xfId="397"/>
-    <cellStyle name="常规 3 2 2 2 2" xfId="1303"/>
-    <cellStyle name="常规 3 2 2 2 3" xfId="1304"/>
-    <cellStyle name="常规 3 2 2 2 4" xfId="1305"/>
-    <cellStyle name="常规 3 2 2 2 5" xfId="1306"/>
-    <cellStyle name="常规 3 2 2 3" xfId="401"/>
-    <cellStyle name="常规 3 2 2 4" xfId="1307"/>
-    <cellStyle name="常规 3 2 2 5" xfId="1308"/>
-    <cellStyle name="常规 3 2 2 6" xfId="1309"/>
-    <cellStyle name="常规 3 2 3" xfId="1310"/>
-    <cellStyle name="常规 3 2 3 2" xfId="1311"/>
-    <cellStyle name="常规 3 2 3 3" xfId="1312"/>
-    <cellStyle name="常规 3 2 3 4" xfId="1313"/>
-    <cellStyle name="常规 3 2 3 5" xfId="867"/>
-    <cellStyle name="常规 3 2 4" xfId="1314"/>
-    <cellStyle name="常规 3 2 5" xfId="927"/>
-    <cellStyle name="常规 3 2 6" xfId="871"/>
-    <cellStyle name="常规 3 2 7" xfId="874"/>
-    <cellStyle name="常规 3 3" xfId="1006"/>
-    <cellStyle name="常规 3 3 2" xfId="1008"/>
-    <cellStyle name="常规 3 3 2 2" xfId="1315"/>
-    <cellStyle name="常规 3 3 2 3" xfId="1316"/>
-    <cellStyle name="常规 3 3 2 4" xfId="1317"/>
-    <cellStyle name="常规 3 3 2 5" xfId="1318"/>
-    <cellStyle name="常规 3 3 3" xfId="1319"/>
-    <cellStyle name="常规 3 3 4" xfId="1320"/>
-    <cellStyle name="常规 3 3 5" xfId="1321"/>
-    <cellStyle name="常规 3 3 6" xfId="1322"/>
-    <cellStyle name="常规 3 4" xfId="1323"/>
-    <cellStyle name="常规 3 5" xfId="1324"/>
-    <cellStyle name="常规 3 5 2" xfId="1325"/>
-    <cellStyle name="常规 3 5 3" xfId="1326"/>
-    <cellStyle name="常规 3 5 4" xfId="1327"/>
-    <cellStyle name="常规 3 5 5" xfId="1329"/>
-    <cellStyle name="常规 3 6" xfId="1330"/>
-    <cellStyle name="常规 3 6 2" xfId="1331"/>
-    <cellStyle name="常规 3 7" xfId="1332"/>
-    <cellStyle name="常规 3 7 2" xfId="92"/>
-    <cellStyle name="常规 3 7 3" xfId="1333"/>
-    <cellStyle name="常规 3 8" xfId="1334"/>
-    <cellStyle name="常规 3 9" xfId="1649"/>
-    <cellStyle name="常规 30" xfId="1259"/>
-    <cellStyle name="常规 31" xfId="1262"/>
-    <cellStyle name="常规 31 2" xfId="30"/>
-    <cellStyle name="常规 31 2 2" xfId="1335"/>
-    <cellStyle name="常规 31 2 3" xfId="1336"/>
-    <cellStyle name="常规 31 2 4" xfId="1337"/>
-    <cellStyle name="常规 31 2 5" xfId="1338"/>
-    <cellStyle name="常规 31 3" xfId="67"/>
-    <cellStyle name="常规 31 4" xfId="70"/>
-    <cellStyle name="常规 31 5" xfId="74"/>
-    <cellStyle name="常规 31 6" xfId="1339"/>
-    <cellStyle name="常规 32" xfId="1264"/>
-    <cellStyle name="常规 32 2" xfId="1266"/>
-    <cellStyle name="常规 32 3" xfId="1272"/>
-    <cellStyle name="常规 32 4" xfId="1274"/>
-    <cellStyle name="常规 32 5" xfId="1276"/>
-    <cellStyle name="常规 33" xfId="8"/>
-    <cellStyle name="常规 33 2" xfId="152"/>
-    <cellStyle name="常规 33 3" xfId="1279"/>
-    <cellStyle name="常规 34" xfId="1289"/>
-    <cellStyle name="常规 34 2" xfId="1291"/>
-    <cellStyle name="常规 35" xfId="12"/>
-    <cellStyle name="常规 35 2" xfId="1341"/>
-    <cellStyle name="常规 36" xfId="1343"/>
-    <cellStyle name="常规 36 2" xfId="1345"/>
-    <cellStyle name="常规 37" xfId="1347"/>
-    <cellStyle name="常规 37 2" xfId="1349"/>
-    <cellStyle name="常规 37 3" xfId="1350"/>
-    <cellStyle name="常规 38" xfId="824"/>
-    <cellStyle name="常规 38 2" xfId="827"/>
-    <cellStyle name="常规 38 3" xfId="829"/>
-    <cellStyle name="常规 38 4" xfId="831"/>
-    <cellStyle name="常规 38 5" xfId="833"/>
-    <cellStyle name="常规 39" xfId="23"/>
-    <cellStyle name="常规 39 2" xfId="1352"/>
-    <cellStyle name="常规 39 3" xfId="1353"/>
-    <cellStyle name="常规 39 4" xfId="1354"/>
-    <cellStyle name="常规 4" xfId="1355"/>
-    <cellStyle name="常规 4 2" xfId="1356"/>
-    <cellStyle name="常规 4 2 2" xfId="1358"/>
-    <cellStyle name="常规 4 2 2 2" xfId="1361"/>
-    <cellStyle name="常规 4 2 2 2 2" xfId="1363"/>
-    <cellStyle name="常规 4 2 2 2 3" xfId="1365"/>
-    <cellStyle name="常规 4 2 2 2 4" xfId="1367"/>
-    <cellStyle name="常规 4 2 2 2 5" xfId="1369"/>
-    <cellStyle name="常规 4 2 2 3" xfId="41"/>
-    <cellStyle name="常规 4 2 2 4" xfId="1372"/>
-    <cellStyle name="常规 4 2 2 5" xfId="1375"/>
-    <cellStyle name="常规 4 2 2 6" xfId="1377"/>
-    <cellStyle name="常规 4 2 3" xfId="1379"/>
-    <cellStyle name="常规 4 2 3 2" xfId="1380"/>
-    <cellStyle name="常规 4 2 3 3" xfId="1381"/>
-    <cellStyle name="常规 4 2 3 4" xfId="1382"/>
-    <cellStyle name="常规 4 2 3 5" xfId="1384"/>
-    <cellStyle name="常规 4 2 4" xfId="1386"/>
-    <cellStyle name="常规 4 2 5" xfId="1388"/>
-    <cellStyle name="常规 4 2 6" xfId="1391"/>
-    <cellStyle name="常规 4 2 7" xfId="1393"/>
-    <cellStyle name="常规 4 3" xfId="1394"/>
-    <cellStyle name="常规 4 3 2" xfId="1396"/>
-    <cellStyle name="常规 4 3 2 2" xfId="1398"/>
-    <cellStyle name="常规 4 3 2 3" xfId="1400"/>
-    <cellStyle name="常规 4 3 2 4" xfId="1402"/>
-    <cellStyle name="常规 4 3 2 5" xfId="1404"/>
-    <cellStyle name="常规 4 3 3" xfId="1406"/>
-    <cellStyle name="常规 4 3 4" xfId="1408"/>
-    <cellStyle name="常规 4 3 5" xfId="1410"/>
-    <cellStyle name="常规 4 3 6" xfId="1413"/>
-    <cellStyle name="常规 4 4" xfId="1357"/>
-    <cellStyle name="常规 4 4 2" xfId="1360"/>
-    <cellStyle name="常规 4 4 3" xfId="40"/>
-    <cellStyle name="常规 4 4 4" xfId="1371"/>
-    <cellStyle name="常规 4 4 5" xfId="1374"/>
-    <cellStyle name="常规 4 5" xfId="1378"/>
-    <cellStyle name="常规 4 6" xfId="1385"/>
-    <cellStyle name="常规 4 7" xfId="1387"/>
-    <cellStyle name="常规 4 8" xfId="1390"/>
-    <cellStyle name="常规 40" xfId="1340"/>
-    <cellStyle name="常规 40 2" xfId="1414"/>
-    <cellStyle name="常规 41" xfId="1342"/>
-    <cellStyle name="常规 41 2" xfId="1344"/>
-    <cellStyle name="常规 42" xfId="1346"/>
-    <cellStyle name="常规 42 2" xfId="1348"/>
-    <cellStyle name="常规 43" xfId="823"/>
-    <cellStyle name="常规 43 2" xfId="826"/>
-    <cellStyle name="常规 44" xfId="22"/>
-    <cellStyle name="常规 44 2" xfId="1351"/>
-    <cellStyle name="常规 45" xfId="836"/>
-    <cellStyle name="常规 45 2" xfId="1415"/>
-    <cellStyle name="常规 46" xfId="839"/>
-    <cellStyle name="常规 47" xfId="842"/>
-    <cellStyle name="常规 47 2" xfId="1416"/>
-    <cellStyle name="常规 48" xfId="1418"/>
-    <cellStyle name="常规 49" xfId="1420"/>
-    <cellStyle name="常规 5" xfId="1421"/>
-    <cellStyle name="常规 5 2" xfId="1422"/>
-    <cellStyle name="常规 5 2 2" xfId="1423"/>
-    <cellStyle name="常规 5 2 2 2" xfId="1424"/>
-    <cellStyle name="常规 5 2 2 2 2" xfId="1149"/>
-    <cellStyle name="常规 5 2 2 2 3" xfId="1154"/>
-    <cellStyle name="常规 5 2 2 2 4" xfId="1156"/>
-    <cellStyle name="常规 5 2 2 2 5" xfId="1158"/>
-    <cellStyle name="常规 5 2 2 3" xfId="1425"/>
-    <cellStyle name="常规 5 2 2 4" xfId="1426"/>
-    <cellStyle name="常规 5 2 2 5" xfId="1427"/>
-    <cellStyle name="常规 5 2 2 6" xfId="1428"/>
-    <cellStyle name="常规 5 2 3" xfId="1429"/>
-    <cellStyle name="常规 5 2 3 2" xfId="1045"/>
-    <cellStyle name="常规 5 2 3 3" xfId="1430"/>
-    <cellStyle name="常规 5 2 3 4" xfId="1431"/>
-    <cellStyle name="常规 5 2 3 5" xfId="1432"/>
-    <cellStyle name="常规 5 2 4" xfId="1433"/>
-    <cellStyle name="常规 5 2 5" xfId="1434"/>
-    <cellStyle name="常规 5 2 6" xfId="1436"/>
-    <cellStyle name="常规 5 2 7" xfId="1438"/>
-    <cellStyle name="常规 5 3" xfId="1439"/>
-    <cellStyle name="常规 5 3 2" xfId="337"/>
-    <cellStyle name="常规 5 3 2 2" xfId="341"/>
-    <cellStyle name="常规 5 3 2 3" xfId="345"/>
-    <cellStyle name="常规 5 3 2 4" xfId="1440"/>
-    <cellStyle name="常规 5 3 2 5" xfId="1441"/>
-    <cellStyle name="常规 5 3 3" xfId="499"/>
-    <cellStyle name="常规 5 3 4" xfId="503"/>
-    <cellStyle name="常规 5 3 5" xfId="505"/>
-    <cellStyle name="常规 5 3 6" xfId="507"/>
-    <cellStyle name="常规 5 4" xfId="1395"/>
-    <cellStyle name="常规 5 4 2" xfId="1397"/>
-    <cellStyle name="常规 5 4 3" xfId="1399"/>
-    <cellStyle name="常规 5 4 4" xfId="1401"/>
-    <cellStyle name="常规 5 4 5" xfId="1403"/>
-    <cellStyle name="常规 5 5" xfId="1405"/>
-    <cellStyle name="常规 5 6" xfId="1407"/>
-    <cellStyle name="常规 5 7" xfId="1409"/>
-    <cellStyle name="常规 5 8" xfId="1412"/>
-    <cellStyle name="常规 50" xfId="835"/>
-    <cellStyle name="常规 51" xfId="838"/>
-    <cellStyle name="常规 52" xfId="841"/>
-    <cellStyle name="常规 53" xfId="1417"/>
-    <cellStyle name="常规 54" xfId="1419"/>
-    <cellStyle name="常规 55" xfId="85"/>
-    <cellStyle name="常规 56" xfId="105"/>
-    <cellStyle name="常规 57" xfId="109"/>
-    <cellStyle name="常规 6" xfId="1442"/>
-    <cellStyle name="常规 6 2" xfId="1443"/>
-    <cellStyle name="常规 6 2 2" xfId="634"/>
-    <cellStyle name="常规 6 2 2 2" xfId="1444"/>
-    <cellStyle name="常规 6 2 2 2 2" xfId="774"/>
-    <cellStyle name="常规 6 2 2 2 3" xfId="781"/>
-    <cellStyle name="常规 6 2 2 2 4" xfId="783"/>
-    <cellStyle name="常规 6 2 2 2 5" xfId="785"/>
-    <cellStyle name="常规 6 2 2 3" xfId="1445"/>
-    <cellStyle name="常规 6 2 2 4" xfId="1446"/>
-    <cellStyle name="常规 6 2 2 5" xfId="1447"/>
-    <cellStyle name="常规 6 2 2 6" xfId="1448"/>
-    <cellStyle name="常规 6 2 3" xfId="636"/>
-    <cellStyle name="常规 6 2 3 2" xfId="1449"/>
-    <cellStyle name="常规 6 2 3 3" xfId="1450"/>
-    <cellStyle name="常规 6 2 3 4" xfId="1451"/>
-    <cellStyle name="常规 6 2 3 5" xfId="1452"/>
-    <cellStyle name="常规 6 2 4" xfId="638"/>
-    <cellStyle name="常规 6 2 5" xfId="1453"/>
-    <cellStyle name="常规 6 2 6" xfId="738"/>
-    <cellStyle name="常规 6 2 7" xfId="750"/>
-    <cellStyle name="常规 6 3" xfId="1454"/>
-    <cellStyle name="常规 6 3 2" xfId="645"/>
-    <cellStyle name="常规 6 3 2 2" xfId="1455"/>
-    <cellStyle name="常规 6 3 2 3" xfId="1456"/>
-    <cellStyle name="常规 6 3 2 4" xfId="1457"/>
-    <cellStyle name="常规 6 3 2 5" xfId="1458"/>
-    <cellStyle name="常规 6 3 3" xfId="647"/>
-    <cellStyle name="常规 6 3 4" xfId="1459"/>
-    <cellStyle name="常规 6 3 5" xfId="1460"/>
-    <cellStyle name="常规 6 3 6" xfId="763"/>
-    <cellStyle name="常规 6 4" xfId="1359"/>
-    <cellStyle name="常规 6 4 2" xfId="1362"/>
-    <cellStyle name="常规 6 4 3" xfId="1364"/>
-    <cellStyle name="常规 6 4 4" xfId="1366"/>
-    <cellStyle name="常规 6 4 5" xfId="1368"/>
-    <cellStyle name="常规 6 5" xfId="39"/>
-    <cellStyle name="常规 6 6" xfId="1370"/>
-    <cellStyle name="常规 6 7" xfId="1373"/>
-    <cellStyle name="常规 6 8" xfId="1376"/>
-    <cellStyle name="常规 60" xfId="1643"/>
-    <cellStyle name="常规 60 2" xfId="1652"/>
-    <cellStyle name="常规 61" xfId="1644"/>
-    <cellStyle name="常规 61 2" xfId="1653"/>
-    <cellStyle name="常规 7" xfId="1461"/>
-    <cellStyle name="常规 8" xfId="1462"/>
-    <cellStyle name="常规 8 2" xfId="1463"/>
-    <cellStyle name="常规 9" xfId="6"/>
+    <cellStyle name="Стиль 1" xfId="693" xr:uid="{00000000-0005-0000-0000-000010030000}"/>
+    <cellStyle name="Стиль 1 2" xfId="985" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
+    <cellStyle name="Стиль 1 2 2" xfId="986" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
+    <cellStyle name="Стиль 1 3" xfId="987" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
+    <cellStyle name="Стиль 1 3 2" xfId="988" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
+    <cellStyle name="Стиль 1 4" xfId="989" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
+    <cellStyle name="Стиль 1 4 2" xfId="990" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
+    <cellStyle name="Стиль 1 5" xfId="991" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
+    <cellStyle name="Стиль 1 5 2" xfId="993" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
+    <cellStyle name="Финансовый 2" xfId="994" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
+    <cellStyle name="Финансовый 2 10" xfId="995" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
+    <cellStyle name="Финансовый 2 10 2" xfId="997" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
+    <cellStyle name="Финансовый 2 2" xfId="221" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
+    <cellStyle name="Финансовый 2 3" xfId="236" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
+    <cellStyle name="Финансовый 2 4" xfId="260" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
+    <cellStyle name="Финансовый 2 4 2" xfId="263" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
+    <cellStyle name="Финансовый 2 5" xfId="272" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
+    <cellStyle name="Финансовый 2 5 2" xfId="998" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
+    <cellStyle name="Финансовый 2 6" xfId="274" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
+    <cellStyle name="Финансовый 2 6 2" xfId="999" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
+    <cellStyle name="Финансовый 2 7" xfId="276" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
+    <cellStyle name="Финансовый 2 7 2" xfId="1001" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
+    <cellStyle name="Финансовый 2 8" xfId="1003" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
+    <cellStyle name="Финансовый 2 8 2" xfId="1005" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
+    <cellStyle name="Финансовый 2 9" xfId="1007" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
+    <cellStyle name="Финансовый 2 9 2" xfId="1009" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
+    <cellStyle name="Финансовый 3" xfId="33" xr:uid="{00000000-0005-0000-0000-00002A030000}"/>
+    <cellStyle name="Финансовый 4" xfId="1642" xr:uid="{00000000-0005-0000-0000-00002B030000}"/>
+    <cellStyle name="Финансовый 5" xfId="1651" xr:uid="{00000000-0005-0000-0000-00002C030000}"/>
+    <cellStyle name="千位分隔 10" xfId="1464" xr:uid="{00000000-0005-0000-0000-00002D030000}"/>
+    <cellStyle name="千位分隔 10 2" xfId="1465" xr:uid="{00000000-0005-0000-0000-00002E030000}"/>
+    <cellStyle name="千位分隔 10 2 2" xfId="1466" xr:uid="{00000000-0005-0000-0000-00002F030000}"/>
+    <cellStyle name="千位分隔 10 2 3" xfId="1467" xr:uid="{00000000-0005-0000-0000-000030030000}"/>
+    <cellStyle name="千位分隔 10 2 4" xfId="1468" xr:uid="{00000000-0005-0000-0000-000031030000}"/>
+    <cellStyle name="千位分隔 10 2 5" xfId="1469" xr:uid="{00000000-0005-0000-0000-000032030000}"/>
+    <cellStyle name="千位分隔 10 3" xfId="1470" xr:uid="{00000000-0005-0000-0000-000033030000}"/>
+    <cellStyle name="千位分隔 10 4" xfId="1471" xr:uid="{00000000-0005-0000-0000-000034030000}"/>
+    <cellStyle name="千位分隔 10 5" xfId="1472" xr:uid="{00000000-0005-0000-0000-000035030000}"/>
+    <cellStyle name="千位分隔 10 6" xfId="1473" xr:uid="{00000000-0005-0000-0000-000036030000}"/>
+    <cellStyle name="千位分隔 11" xfId="1474" xr:uid="{00000000-0005-0000-0000-000037030000}"/>
+    <cellStyle name="千位分隔 11 2" xfId="1475" xr:uid="{00000000-0005-0000-0000-000038030000}"/>
+    <cellStyle name="千位分隔 12" xfId="1476" xr:uid="{00000000-0005-0000-0000-000039030000}"/>
+    <cellStyle name="千位分隔 12 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00003A030000}"/>
+    <cellStyle name="千位分隔 12 2 2" xfId="1328" xr:uid="{00000000-0005-0000-0000-00003B030000}"/>
+    <cellStyle name="千位分隔 12 2 3" xfId="1477" xr:uid="{00000000-0005-0000-0000-00003C030000}"/>
+    <cellStyle name="千位分隔 12 2 4" xfId="1478" xr:uid="{00000000-0005-0000-0000-00003D030000}"/>
+    <cellStyle name="千位分隔 12 2 5" xfId="1479" xr:uid="{00000000-0005-0000-0000-00003E030000}"/>
+    <cellStyle name="千位分隔 12 3" xfId="929" xr:uid="{00000000-0005-0000-0000-00003F030000}"/>
+    <cellStyle name="千位分隔 12 4" xfId="1480" xr:uid="{00000000-0005-0000-0000-000040030000}"/>
+    <cellStyle name="千位分隔 12 5" xfId="1481" xr:uid="{00000000-0005-0000-0000-000041030000}"/>
+    <cellStyle name="千位分隔 12 6" xfId="1482" xr:uid="{00000000-0005-0000-0000-000042030000}"/>
+    <cellStyle name="千位分隔 13" xfId="14" xr:uid="{00000000-0005-0000-0000-000043030000}"/>
+    <cellStyle name="千位分隔 13 2" xfId="938" xr:uid="{00000000-0005-0000-0000-000044030000}"/>
+    <cellStyle name="千位分隔 13 2 2" xfId="1383" xr:uid="{00000000-0005-0000-0000-000045030000}"/>
+    <cellStyle name="千位分隔 13 2 3" xfId="1484" xr:uid="{00000000-0005-0000-0000-000046030000}"/>
+    <cellStyle name="千位分隔 13 2 4" xfId="1485" xr:uid="{00000000-0005-0000-0000-000047030000}"/>
+    <cellStyle name="千位分隔 13 2 5" xfId="1486" xr:uid="{00000000-0005-0000-0000-000048030000}"/>
+    <cellStyle name="千位分隔 13 3" xfId="1487" xr:uid="{00000000-0005-0000-0000-000049030000}"/>
+    <cellStyle name="千位分隔 13 4" xfId="1488" xr:uid="{00000000-0005-0000-0000-00004A030000}"/>
+    <cellStyle name="千位分隔 13 5" xfId="1489" xr:uid="{00000000-0005-0000-0000-00004B030000}"/>
+    <cellStyle name="千位分隔 13 6" xfId="1490" xr:uid="{00000000-0005-0000-0000-00004C030000}"/>
+    <cellStyle name="千位分隔 13 7" xfId="1483" xr:uid="{00000000-0005-0000-0000-00004D030000}"/>
+    <cellStyle name="千位分隔 14" xfId="1491" xr:uid="{00000000-0005-0000-0000-00004E030000}"/>
+    <cellStyle name="千位分隔 14 2" xfId="1492" xr:uid="{00000000-0005-0000-0000-00004F030000}"/>
+    <cellStyle name="千位分隔 14 2 2" xfId="1493" xr:uid="{00000000-0005-0000-0000-000050030000}"/>
+    <cellStyle name="千位分隔 14 2 3" xfId="1494" xr:uid="{00000000-0005-0000-0000-000051030000}"/>
+    <cellStyle name="千位分隔 14 2 4" xfId="1495" xr:uid="{00000000-0005-0000-0000-000052030000}"/>
+    <cellStyle name="千位分隔 14 2 5" xfId="1496" xr:uid="{00000000-0005-0000-0000-000053030000}"/>
+    <cellStyle name="千位分隔 14 3" xfId="1497" xr:uid="{00000000-0005-0000-0000-000054030000}"/>
+    <cellStyle name="千位分隔 14 4" xfId="1498" xr:uid="{00000000-0005-0000-0000-000055030000}"/>
+    <cellStyle name="千位分隔 14 5" xfId="1499" xr:uid="{00000000-0005-0000-0000-000056030000}"/>
+    <cellStyle name="千位分隔 14 6" xfId="1500" xr:uid="{00000000-0005-0000-0000-000057030000}"/>
+    <cellStyle name="千位分隔 15" xfId="9" xr:uid="{00000000-0005-0000-0000-000058030000}"/>
+    <cellStyle name="千位分隔 15 2" xfId="1503" xr:uid="{00000000-0005-0000-0000-000059030000}"/>
+    <cellStyle name="千位分隔 15 3" xfId="1504" xr:uid="{00000000-0005-0000-0000-00005A030000}"/>
+    <cellStyle name="千位分隔 15 4" xfId="1505" xr:uid="{00000000-0005-0000-0000-00005B030000}"/>
+    <cellStyle name="千位分隔 15 5" xfId="1506" xr:uid="{00000000-0005-0000-0000-00005C030000}"/>
+    <cellStyle name="千位分隔 15 6" xfId="1502" xr:uid="{00000000-0005-0000-0000-00005D030000}"/>
+    <cellStyle name="千位分隔 16" xfId="605" xr:uid="{00000000-0005-0000-0000-00005E030000}"/>
+    <cellStyle name="千位分隔 17" xfId="624" xr:uid="{00000000-0005-0000-0000-00005F030000}"/>
+    <cellStyle name="千位分隔 17 2" xfId="626" xr:uid="{00000000-0005-0000-0000-000060030000}"/>
+    <cellStyle name="千位分隔 17 3" xfId="632" xr:uid="{00000000-0005-0000-0000-000061030000}"/>
+    <cellStyle name="千位分隔 18" xfId="11" xr:uid="{00000000-0005-0000-0000-000062030000}"/>
+    <cellStyle name="千位分隔 18 2" xfId="641" xr:uid="{00000000-0005-0000-0000-000063030000}"/>
+    <cellStyle name="千位分隔 19" xfId="16" xr:uid="{00000000-0005-0000-0000-000064030000}"/>
+    <cellStyle name="千位分隔 2" xfId="296" xr:uid="{00000000-0005-0000-0000-000065030000}"/>
+    <cellStyle name="千位分隔 2 10" xfId="1507" xr:uid="{00000000-0005-0000-0000-000066030000}"/>
+    <cellStyle name="千位分隔 2 11" xfId="1508" xr:uid="{00000000-0005-0000-0000-000067030000}"/>
+    <cellStyle name="千位分隔 2 12" xfId="290" xr:uid="{00000000-0005-0000-0000-000068030000}"/>
+    <cellStyle name="千位分隔 2 2" xfId="1509" xr:uid="{00000000-0005-0000-0000-000069030000}"/>
+    <cellStyle name="千位分隔 2 2 2" xfId="1287" xr:uid="{00000000-0005-0000-0000-00006A030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2" xfId="1510" xr:uid="{00000000-0005-0000-0000-00006B030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 2" xfId="1511" xr:uid="{00000000-0005-0000-0000-00006C030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 2" xfId="1512" xr:uid="{00000000-0005-0000-0000-00006D030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 3" xfId="1513" xr:uid="{00000000-0005-0000-0000-00006E030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 4" xfId="1514" xr:uid="{00000000-0005-0000-0000-00006F030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 5" xfId="1515" xr:uid="{00000000-0005-0000-0000-000070030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 3" xfId="1516" xr:uid="{00000000-0005-0000-0000-000071030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 4" xfId="1517" xr:uid="{00000000-0005-0000-0000-000072030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 5" xfId="1518" xr:uid="{00000000-0005-0000-0000-000073030000}"/>
+    <cellStyle name="千位分隔 2 2 2 2 6" xfId="1089" xr:uid="{00000000-0005-0000-0000-000074030000}"/>
+    <cellStyle name="千位分隔 2 2 2 3" xfId="1519" xr:uid="{00000000-0005-0000-0000-000075030000}"/>
+    <cellStyle name="千位分隔 2 2 2 3 2" xfId="1520" xr:uid="{00000000-0005-0000-0000-000076030000}"/>
+    <cellStyle name="千位分隔 2 2 2 3 3" xfId="1521" xr:uid="{00000000-0005-0000-0000-000077030000}"/>
+    <cellStyle name="千位分隔 2 2 2 3 4" xfId="1522" xr:uid="{00000000-0005-0000-0000-000078030000}"/>
+    <cellStyle name="千位分隔 2 2 2 3 5" xfId="1523" xr:uid="{00000000-0005-0000-0000-000079030000}"/>
+    <cellStyle name="千位分隔 2 2 2 4" xfId="1524" xr:uid="{00000000-0005-0000-0000-00007A030000}"/>
+    <cellStyle name="千位分隔 2 2 2 5" xfId="1525" xr:uid="{00000000-0005-0000-0000-00007B030000}"/>
+    <cellStyle name="千位分隔 2 2 2 6" xfId="1526" xr:uid="{00000000-0005-0000-0000-00007C030000}"/>
+    <cellStyle name="千位分隔 2 2 2 7" xfId="1527" xr:uid="{00000000-0005-0000-0000-00007D030000}"/>
+    <cellStyle name="千位分隔 2 2 3" xfId="1528" xr:uid="{00000000-0005-0000-0000-00007E030000}"/>
+    <cellStyle name="千位分隔 2 2 3 2" xfId="1529" xr:uid="{00000000-0005-0000-0000-00007F030000}"/>
+    <cellStyle name="千位分隔 2 2 3 2 2" xfId="1530" xr:uid="{00000000-0005-0000-0000-000080030000}"/>
+    <cellStyle name="千位分隔 2 2 3 2 3" xfId="1531" xr:uid="{00000000-0005-0000-0000-000081030000}"/>
+    <cellStyle name="千位分隔 2 2 3 2 4" xfId="1532" xr:uid="{00000000-0005-0000-0000-000082030000}"/>
+    <cellStyle name="千位分隔 2 2 3 2 5" xfId="1533" xr:uid="{00000000-0005-0000-0000-000083030000}"/>
+    <cellStyle name="千位分隔 2 2 3 3" xfId="1534" xr:uid="{00000000-0005-0000-0000-000084030000}"/>
+    <cellStyle name="千位分隔 2 2 3 4" xfId="1535" xr:uid="{00000000-0005-0000-0000-000085030000}"/>
+    <cellStyle name="千位分隔 2 2 3 5" xfId="1536" xr:uid="{00000000-0005-0000-0000-000086030000}"/>
+    <cellStyle name="千位分隔 2 2 3 6" xfId="1537" xr:uid="{00000000-0005-0000-0000-000087030000}"/>
+    <cellStyle name="千位分隔 2 2 4" xfId="992" xr:uid="{00000000-0005-0000-0000-000088030000}"/>
+    <cellStyle name="千位分隔 2 2 4 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000089030000}"/>
+    <cellStyle name="千位分隔 2 2 4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00008A030000}"/>
+    <cellStyle name="千位分隔 2 2 4 4" xfId="68" xr:uid="{00000000-0005-0000-0000-00008B030000}"/>
+    <cellStyle name="千位分隔 2 2 4 5" xfId="72" xr:uid="{00000000-0005-0000-0000-00008C030000}"/>
+    <cellStyle name="千位分隔 2 2 5" xfId="1203" xr:uid="{00000000-0005-0000-0000-00008D030000}"/>
+    <cellStyle name="千位分隔 2 2 6" xfId="1205" xr:uid="{00000000-0005-0000-0000-00008E030000}"/>
+    <cellStyle name="千位分隔 2 2 7" xfId="512" xr:uid="{00000000-0005-0000-0000-00008F030000}"/>
+    <cellStyle name="千位分隔 2 2 8" xfId="1207" xr:uid="{00000000-0005-0000-0000-000090030000}"/>
+    <cellStyle name="千位分隔 2 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000091030000}"/>
+    <cellStyle name="千位分隔 2 3 2" xfId="1300" xr:uid="{00000000-0005-0000-0000-000092030000}"/>
+    <cellStyle name="千位分隔 2 3 2 2" xfId="1539" xr:uid="{00000000-0005-0000-0000-000093030000}"/>
+    <cellStyle name="千位分隔 2 3 2 2 2" xfId="724" xr:uid="{00000000-0005-0000-0000-000094030000}"/>
+    <cellStyle name="千位分隔 2 3 2 2 3" xfId="727" xr:uid="{00000000-0005-0000-0000-000095030000}"/>
+    <cellStyle name="千位分隔 2 3 2 2 4" xfId="1540" xr:uid="{00000000-0005-0000-0000-000096030000}"/>
+    <cellStyle name="千位分隔 2 3 2 2 5" xfId="1541" xr:uid="{00000000-0005-0000-0000-000097030000}"/>
+    <cellStyle name="千位分隔 2 3 2 3" xfId="1542" xr:uid="{00000000-0005-0000-0000-000098030000}"/>
+    <cellStyle name="千位分隔 2 3 2 4" xfId="1543" xr:uid="{00000000-0005-0000-0000-000099030000}"/>
+    <cellStyle name="千位分隔 2 3 2 5" xfId="1544" xr:uid="{00000000-0005-0000-0000-00009A030000}"/>
+    <cellStyle name="千位分隔 2 3 2 6" xfId="1545" xr:uid="{00000000-0005-0000-0000-00009B030000}"/>
+    <cellStyle name="千位分隔 2 3 3" xfId="1546" xr:uid="{00000000-0005-0000-0000-00009C030000}"/>
+    <cellStyle name="千位分隔 2 3 3 2" xfId="1547" xr:uid="{00000000-0005-0000-0000-00009D030000}"/>
+    <cellStyle name="千位分隔 2 3 3 3" xfId="1548" xr:uid="{00000000-0005-0000-0000-00009E030000}"/>
+    <cellStyle name="千位分隔 2 3 3 4" xfId="1549" xr:uid="{00000000-0005-0000-0000-00009F030000}"/>
+    <cellStyle name="千位分隔 2 3 3 5" xfId="1550" xr:uid="{00000000-0005-0000-0000-0000A0030000}"/>
+    <cellStyle name="千位分隔 2 3 4" xfId="1551" xr:uid="{00000000-0005-0000-0000-0000A1030000}"/>
+    <cellStyle name="千位分隔 2 3 5" xfId="1552" xr:uid="{00000000-0005-0000-0000-0000A2030000}"/>
+    <cellStyle name="千位分隔 2 3 6" xfId="1553" xr:uid="{00000000-0005-0000-0000-0000A3030000}"/>
+    <cellStyle name="千位分隔 2 3 7" xfId="187" xr:uid="{00000000-0005-0000-0000-0000A4030000}"/>
+    <cellStyle name="千位分隔 2 3 8" xfId="1538" xr:uid="{00000000-0005-0000-0000-0000A5030000}"/>
+    <cellStyle name="千位分隔 2 4" xfId="544" xr:uid="{00000000-0005-0000-0000-0000A6030000}"/>
+    <cellStyle name="千位分隔 2 4 2" xfId="547" xr:uid="{00000000-0005-0000-0000-0000A7030000}"/>
+    <cellStyle name="千位分隔 2 4 2 2" xfId="1554" xr:uid="{00000000-0005-0000-0000-0000A8030000}"/>
+    <cellStyle name="千位分隔 2 4 2 3" xfId="1555" xr:uid="{00000000-0005-0000-0000-0000A9030000}"/>
+    <cellStyle name="千位分隔 2 4 2 4" xfId="1556" xr:uid="{00000000-0005-0000-0000-0000AA030000}"/>
+    <cellStyle name="千位分隔 2 4 2 5" xfId="1557" xr:uid="{00000000-0005-0000-0000-0000AB030000}"/>
+    <cellStyle name="千位分隔 2 4 3" xfId="550" xr:uid="{00000000-0005-0000-0000-0000AC030000}"/>
+    <cellStyle name="千位分隔 2 4 4" xfId="34" xr:uid="{00000000-0005-0000-0000-0000AD030000}"/>
+    <cellStyle name="千位分隔 2 4 5" xfId="194" xr:uid="{00000000-0005-0000-0000-0000AE030000}"/>
+    <cellStyle name="千位分隔 2 4 6" xfId="197" xr:uid="{00000000-0005-0000-0000-0000AF030000}"/>
+    <cellStyle name="千位分隔 2 5" xfId="579" xr:uid="{00000000-0005-0000-0000-0000B0030000}"/>
+    <cellStyle name="千位分隔 2 5 2" xfId="349" xr:uid="{00000000-0005-0000-0000-0000B1030000}"/>
+    <cellStyle name="千位分隔 2 5 2 2" xfId="354" xr:uid="{00000000-0005-0000-0000-0000B2030000}"/>
+    <cellStyle name="千位分隔 2 5 2 3" xfId="357" xr:uid="{00000000-0005-0000-0000-0000B3030000}"/>
+    <cellStyle name="千位分隔 2 5 2 4" xfId="360" xr:uid="{00000000-0005-0000-0000-0000B4030000}"/>
+    <cellStyle name="千位分隔 2 5 2 5" xfId="315" xr:uid="{00000000-0005-0000-0000-0000B5030000}"/>
+    <cellStyle name="千位分隔 2 5 3" xfId="90" xr:uid="{00000000-0005-0000-0000-0000B6030000}"/>
+    <cellStyle name="千位分隔 2 5 4" xfId="586" xr:uid="{00000000-0005-0000-0000-0000B7030000}"/>
+    <cellStyle name="千位分隔 2 5 5" xfId="591" xr:uid="{00000000-0005-0000-0000-0000B8030000}"/>
+    <cellStyle name="千位分隔 2 5 6" xfId="593" xr:uid="{00000000-0005-0000-0000-0000B9030000}"/>
+    <cellStyle name="千位分隔 2 6" xfId="28" xr:uid="{00000000-0005-0000-0000-0000BA030000}"/>
+    <cellStyle name="千位分隔 2 6 2" xfId="1558" xr:uid="{00000000-0005-0000-0000-0000BB030000}"/>
+    <cellStyle name="千位分隔 2 6 2 2" xfId="1559" xr:uid="{00000000-0005-0000-0000-0000BC030000}"/>
+    <cellStyle name="千位分隔 2 6 2 3" xfId="1560" xr:uid="{00000000-0005-0000-0000-0000BD030000}"/>
+    <cellStyle name="千位分隔 2 6 2 4" xfId="1561" xr:uid="{00000000-0005-0000-0000-0000BE030000}"/>
+    <cellStyle name="千位分隔 2 6 2 5" xfId="1562" xr:uid="{00000000-0005-0000-0000-0000BF030000}"/>
+    <cellStyle name="千位分隔 2 6 3" xfId="1563" xr:uid="{00000000-0005-0000-0000-0000C0030000}"/>
+    <cellStyle name="千位分隔 2 6 4" xfId="1564" xr:uid="{00000000-0005-0000-0000-0000C1030000}"/>
+    <cellStyle name="千位分隔 2 6 5" xfId="1565" xr:uid="{00000000-0005-0000-0000-0000C2030000}"/>
+    <cellStyle name="千位分隔 2 6 6" xfId="1566" xr:uid="{00000000-0005-0000-0000-0000C3030000}"/>
+    <cellStyle name="千位分隔 2 7" xfId="596" xr:uid="{00000000-0005-0000-0000-0000C4030000}"/>
+    <cellStyle name="千位分隔 2 7 2" xfId="1567" xr:uid="{00000000-0005-0000-0000-0000C5030000}"/>
+    <cellStyle name="千位分隔 2 7 3" xfId="1568" xr:uid="{00000000-0005-0000-0000-0000C6030000}"/>
+    <cellStyle name="千位分隔 2 7 4" xfId="1569" xr:uid="{00000000-0005-0000-0000-0000C7030000}"/>
+    <cellStyle name="千位分隔 2 7 5" xfId="1570" xr:uid="{00000000-0005-0000-0000-0000C8030000}"/>
+    <cellStyle name="千位分隔 2 8" xfId="598" xr:uid="{00000000-0005-0000-0000-0000C9030000}"/>
+    <cellStyle name="千位分隔 2 8 2" xfId="1571" xr:uid="{00000000-0005-0000-0000-0000CA030000}"/>
+    <cellStyle name="千位分隔 2 8 3" xfId="1572" xr:uid="{00000000-0005-0000-0000-0000CB030000}"/>
+    <cellStyle name="千位分隔 2 8 4" xfId="996" xr:uid="{00000000-0005-0000-0000-0000CC030000}"/>
+    <cellStyle name="千位分隔 2 8 5" xfId="1573" xr:uid="{00000000-0005-0000-0000-0000CD030000}"/>
+    <cellStyle name="千位分隔 2 9" xfId="510" xr:uid="{00000000-0005-0000-0000-0000CE030000}"/>
+    <cellStyle name="千位分隔 2 9 2" xfId="1574" xr:uid="{00000000-0005-0000-0000-0000CF030000}"/>
+    <cellStyle name="千位分隔 2 9 3" xfId="1575" xr:uid="{00000000-0005-0000-0000-0000D0030000}"/>
+    <cellStyle name="千位分隔 2 9 4" xfId="1576" xr:uid="{00000000-0005-0000-0000-0000D1030000}"/>
+    <cellStyle name="千位分隔 20" xfId="15" xr:uid="{00000000-0005-0000-0000-0000D2030000}"/>
+    <cellStyle name="千位分隔 20 2" xfId="1501" xr:uid="{00000000-0005-0000-0000-0000D3030000}"/>
+    <cellStyle name="千位分隔 21" xfId="604" xr:uid="{00000000-0005-0000-0000-0000D4030000}"/>
+    <cellStyle name="千位分隔 22" xfId="623" xr:uid="{00000000-0005-0000-0000-0000D5030000}"/>
+    <cellStyle name="千位分隔 23" xfId="640" xr:uid="{00000000-0005-0000-0000-0000D6030000}"/>
+    <cellStyle name="千位分隔 24" xfId="649" xr:uid="{00000000-0005-0000-0000-0000D7030000}"/>
+    <cellStyle name="千位分隔 25" xfId="651" xr:uid="{00000000-0005-0000-0000-0000D8030000}"/>
+    <cellStyle name="千位分隔 3" xfId="299" xr:uid="{00000000-0005-0000-0000-0000D9030000}"/>
+    <cellStyle name="千位分隔 3 2" xfId="1577" xr:uid="{00000000-0005-0000-0000-0000DA030000}"/>
+    <cellStyle name="千位分隔 3 2 2" xfId="1578" xr:uid="{00000000-0005-0000-0000-0000DB030000}"/>
+    <cellStyle name="千位分隔 3 2 2 2" xfId="900" xr:uid="{00000000-0005-0000-0000-0000DC030000}"/>
+    <cellStyle name="千位分隔 3 2 2 2 2" xfId="1579" xr:uid="{00000000-0005-0000-0000-0000DD030000}"/>
+    <cellStyle name="千位分隔 3 2 2 2 3" xfId="1580" xr:uid="{00000000-0005-0000-0000-0000DE030000}"/>
+    <cellStyle name="千位分隔 3 2 2 2 4" xfId="1581" xr:uid="{00000000-0005-0000-0000-0000DF030000}"/>
+    <cellStyle name="千位分隔 3 2 2 2 5" xfId="1582" xr:uid="{00000000-0005-0000-0000-0000E0030000}"/>
+    <cellStyle name="千位分隔 3 2 2 3" xfId="902" xr:uid="{00000000-0005-0000-0000-0000E1030000}"/>
+    <cellStyle name="千位分隔 3 2 2 4" xfId="904" xr:uid="{00000000-0005-0000-0000-0000E2030000}"/>
+    <cellStyle name="千位分隔 3 2 2 5" xfId="1583" xr:uid="{00000000-0005-0000-0000-0000E3030000}"/>
+    <cellStyle name="千位分隔 3 2 2 6" xfId="1584" xr:uid="{00000000-0005-0000-0000-0000E4030000}"/>
+    <cellStyle name="千位分隔 3 2 3" xfId="1585" xr:uid="{00000000-0005-0000-0000-0000E5030000}"/>
+    <cellStyle name="千位分隔 3 2 3 2" xfId="1586" xr:uid="{00000000-0005-0000-0000-0000E6030000}"/>
+    <cellStyle name="千位分隔 3 2 3 3" xfId="1587" xr:uid="{00000000-0005-0000-0000-0000E7030000}"/>
+    <cellStyle name="千位分隔 3 2 3 4" xfId="1588" xr:uid="{00000000-0005-0000-0000-0000E8030000}"/>
+    <cellStyle name="千位分隔 3 2 3 5" xfId="1589" xr:uid="{00000000-0005-0000-0000-0000E9030000}"/>
+    <cellStyle name="千位分隔 3 2 4" xfId="1590" xr:uid="{00000000-0005-0000-0000-0000EA030000}"/>
+    <cellStyle name="千位分隔 3 2 5" xfId="1591" xr:uid="{00000000-0005-0000-0000-0000EB030000}"/>
+    <cellStyle name="千位分隔 3 2 6" xfId="1592" xr:uid="{00000000-0005-0000-0000-0000EC030000}"/>
+    <cellStyle name="千位分隔 3 2 7" xfId="1593" xr:uid="{00000000-0005-0000-0000-0000ED030000}"/>
+    <cellStyle name="千位分隔 3 3" xfId="1594" xr:uid="{00000000-0005-0000-0000-0000EE030000}"/>
+    <cellStyle name="千位分隔 3 3 2" xfId="1595" xr:uid="{00000000-0005-0000-0000-0000EF030000}"/>
+    <cellStyle name="千位分隔 3 3 2 2" xfId="1596" xr:uid="{00000000-0005-0000-0000-0000F0030000}"/>
+    <cellStyle name="千位分隔 3 3 2 3" xfId="1597" xr:uid="{00000000-0005-0000-0000-0000F1030000}"/>
+    <cellStyle name="千位分隔 3 3 2 4" xfId="1598" xr:uid="{00000000-0005-0000-0000-0000F2030000}"/>
+    <cellStyle name="千位分隔 3 3 2 5" xfId="1599" xr:uid="{00000000-0005-0000-0000-0000F3030000}"/>
+    <cellStyle name="千位分隔 3 3 3" xfId="1600" xr:uid="{00000000-0005-0000-0000-0000F4030000}"/>
+    <cellStyle name="千位分隔 3 3 4" xfId="1601" xr:uid="{00000000-0005-0000-0000-0000F5030000}"/>
+    <cellStyle name="千位分隔 3 3 5" xfId="1602" xr:uid="{00000000-0005-0000-0000-0000F6030000}"/>
+    <cellStyle name="千位分隔 3 3 6" xfId="1603" xr:uid="{00000000-0005-0000-0000-0000F7030000}"/>
+    <cellStyle name="千位分隔 3 4" xfId="601" xr:uid="{00000000-0005-0000-0000-0000F8030000}"/>
+    <cellStyle name="千位分隔 3 4 2" xfId="43" xr:uid="{00000000-0005-0000-0000-0000F9030000}"/>
+    <cellStyle name="千位分隔 3 4 3" xfId="655" xr:uid="{00000000-0005-0000-0000-0000FA030000}"/>
+    <cellStyle name="千位分隔 3 4 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000FB030000}"/>
+    <cellStyle name="千位分隔 3 4 5" xfId="695" xr:uid="{00000000-0005-0000-0000-0000FC030000}"/>
+    <cellStyle name="千位分隔 3 5" xfId="714" xr:uid="{00000000-0005-0000-0000-0000FD030000}"/>
+    <cellStyle name="千位分隔 3 6" xfId="717" xr:uid="{00000000-0005-0000-0000-0000FE030000}"/>
+    <cellStyle name="千位分隔 3 7" xfId="720" xr:uid="{00000000-0005-0000-0000-0000FF030000}"/>
+    <cellStyle name="千位分隔 3 8" xfId="723" xr:uid="{00000000-0005-0000-0000-000000040000}"/>
+    <cellStyle name="千位分隔 4" xfId="1604" xr:uid="{00000000-0005-0000-0000-000001040000}"/>
+    <cellStyle name="千位分隔 4 2" xfId="884" xr:uid="{00000000-0005-0000-0000-000002040000}"/>
+    <cellStyle name="千位分隔 4 2 2" xfId="886" xr:uid="{00000000-0005-0000-0000-000003040000}"/>
+    <cellStyle name="千位分隔 4 2 2 2" xfId="1389" xr:uid="{00000000-0005-0000-0000-000004040000}"/>
+    <cellStyle name="千位分隔 4 2 2 2 2" xfId="1605" xr:uid="{00000000-0005-0000-0000-000005040000}"/>
+    <cellStyle name="千位分隔 4 2 2 2 3" xfId="1606" xr:uid="{00000000-0005-0000-0000-000006040000}"/>
+    <cellStyle name="千位分隔 4 2 2 2 4" xfId="1607" xr:uid="{00000000-0005-0000-0000-000007040000}"/>
+    <cellStyle name="千位分隔 4 2 2 2 5" xfId="1608" xr:uid="{00000000-0005-0000-0000-000008040000}"/>
+    <cellStyle name="千位分隔 4 2 2 3" xfId="1392" xr:uid="{00000000-0005-0000-0000-000009040000}"/>
+    <cellStyle name="千位分隔 4 2 2 4" xfId="1609" xr:uid="{00000000-0005-0000-0000-00000A040000}"/>
+    <cellStyle name="千位分隔 4 2 2 5" xfId="1610" xr:uid="{00000000-0005-0000-0000-00000B040000}"/>
+    <cellStyle name="千位分隔 4 2 2 6" xfId="1611" xr:uid="{00000000-0005-0000-0000-00000C040000}"/>
+    <cellStyle name="千位分隔 4 2 3" xfId="888" xr:uid="{00000000-0005-0000-0000-00000D040000}"/>
+    <cellStyle name="千位分隔 4 2 3 2" xfId="1411" xr:uid="{00000000-0005-0000-0000-00000E040000}"/>
+    <cellStyle name="千位分隔 4 2 3 3" xfId="1612" xr:uid="{00000000-0005-0000-0000-00000F040000}"/>
+    <cellStyle name="千位分隔 4 2 3 4" xfId="1613" xr:uid="{00000000-0005-0000-0000-000010040000}"/>
+    <cellStyle name="千位分隔 4 2 3 5" xfId="1614" xr:uid="{00000000-0005-0000-0000-000011040000}"/>
+    <cellStyle name="千位分隔 4 2 4" xfId="890" xr:uid="{00000000-0005-0000-0000-000012040000}"/>
+    <cellStyle name="千位分隔 4 2 5" xfId="892" xr:uid="{00000000-0005-0000-0000-000013040000}"/>
+    <cellStyle name="千位分隔 4 2 6" xfId="1615" xr:uid="{00000000-0005-0000-0000-000014040000}"/>
+    <cellStyle name="千位分隔 4 2 7" xfId="1616" xr:uid="{00000000-0005-0000-0000-000015040000}"/>
+    <cellStyle name="千位分隔 4 3" xfId="894" xr:uid="{00000000-0005-0000-0000-000016040000}"/>
+    <cellStyle name="千位分隔 4 3 2" xfId="1617" xr:uid="{00000000-0005-0000-0000-000017040000}"/>
+    <cellStyle name="千位分隔 4 3 2 2" xfId="1435" xr:uid="{00000000-0005-0000-0000-000018040000}"/>
+    <cellStyle name="千位分隔 4 3 2 3" xfId="1437" xr:uid="{00000000-0005-0000-0000-000019040000}"/>
+    <cellStyle name="千位分隔 4 3 2 4" xfId="1618" xr:uid="{00000000-0005-0000-0000-00001A040000}"/>
+    <cellStyle name="千位分隔 4 3 2 5" xfId="1619" xr:uid="{00000000-0005-0000-0000-00001B040000}"/>
+    <cellStyle name="千位分隔 4 3 3" xfId="1620" xr:uid="{00000000-0005-0000-0000-00001C040000}"/>
+    <cellStyle name="千位分隔 4 3 4" xfId="1621" xr:uid="{00000000-0005-0000-0000-00001D040000}"/>
+    <cellStyle name="千位分隔 4 3 5" xfId="1622" xr:uid="{00000000-0005-0000-0000-00001E040000}"/>
+    <cellStyle name="千位分隔 4 3 6" xfId="1623" xr:uid="{00000000-0005-0000-0000-00001F040000}"/>
+    <cellStyle name="千位分隔 4 4" xfId="733" xr:uid="{00000000-0005-0000-0000-000020040000}"/>
+    <cellStyle name="千位分隔 4 4 2" xfId="736" xr:uid="{00000000-0005-0000-0000-000021040000}"/>
+    <cellStyle name="千位分隔 4 4 3" xfId="761" xr:uid="{00000000-0005-0000-0000-000022040000}"/>
+    <cellStyle name="千位分隔 4 4 4" xfId="773" xr:uid="{00000000-0005-0000-0000-000023040000}"/>
+    <cellStyle name="千位分隔 4 4 5" xfId="780" xr:uid="{00000000-0005-0000-0000-000024040000}"/>
+    <cellStyle name="千位分隔 4 5" xfId="788" xr:uid="{00000000-0005-0000-0000-000025040000}"/>
+    <cellStyle name="千位分隔 4 6" xfId="809" xr:uid="{00000000-0005-0000-0000-000026040000}"/>
+    <cellStyle name="千位分隔 4 7" xfId="821" xr:uid="{00000000-0005-0000-0000-000027040000}"/>
+    <cellStyle name="千位分隔 4 8" xfId="844" xr:uid="{00000000-0005-0000-0000-000028040000}"/>
+    <cellStyle name="千位分隔 5" xfId="1624" xr:uid="{00000000-0005-0000-0000-000029040000}"/>
+    <cellStyle name="千位分隔 5 2" xfId="906" xr:uid="{00000000-0005-0000-0000-00002A040000}"/>
+    <cellStyle name="千位分隔 6" xfId="1102" xr:uid="{00000000-0005-0000-0000-00002B040000}"/>
+    <cellStyle name="千位分隔 6 2" xfId="916" xr:uid="{00000000-0005-0000-0000-00002C040000}"/>
+    <cellStyle name="千位分隔 7" xfId="1625" xr:uid="{00000000-0005-0000-0000-00002D040000}"/>
+    <cellStyle name="千位分隔 7 2" xfId="1626" xr:uid="{00000000-0005-0000-0000-00002E040000}"/>
+    <cellStyle name="千位分隔 7 2 2" xfId="1627" xr:uid="{00000000-0005-0000-0000-00002F040000}"/>
+    <cellStyle name="千位分隔 7 2 2 2" xfId="1628" xr:uid="{00000000-0005-0000-0000-000030040000}"/>
+    <cellStyle name="千位分隔 7 2 2 3" xfId="1629" xr:uid="{00000000-0005-0000-0000-000031040000}"/>
+    <cellStyle name="千位分隔 7 2 2 4" xfId="1630" xr:uid="{00000000-0005-0000-0000-000032040000}"/>
+    <cellStyle name="千位分隔 7 2 2 5" xfId="1631" xr:uid="{00000000-0005-0000-0000-000033040000}"/>
+    <cellStyle name="千位分隔 7 2 3" xfId="657" xr:uid="{00000000-0005-0000-0000-000034040000}"/>
+    <cellStyle name="千位分隔 7 2 4" xfId="668" xr:uid="{00000000-0005-0000-0000-000035040000}"/>
+    <cellStyle name="千位分隔 7 2 5" xfId="674" xr:uid="{00000000-0005-0000-0000-000036040000}"/>
+    <cellStyle name="千位分隔 7 2 6" xfId="676" xr:uid="{00000000-0005-0000-0000-000037040000}"/>
+    <cellStyle name="千位分隔 7 3" xfId="1632" xr:uid="{00000000-0005-0000-0000-000038040000}"/>
+    <cellStyle name="千位分隔 7 3 2" xfId="1633" xr:uid="{00000000-0005-0000-0000-000039040000}"/>
+    <cellStyle name="千位分隔 7 3 3" xfId="682" xr:uid="{00000000-0005-0000-0000-00003A040000}"/>
+    <cellStyle name="千位分隔 7 3 4" xfId="688" xr:uid="{00000000-0005-0000-0000-00003B040000}"/>
+    <cellStyle name="千位分隔 7 3 5" xfId="690" xr:uid="{00000000-0005-0000-0000-00003C040000}"/>
+    <cellStyle name="千位分隔 7 4" xfId="983" xr:uid="{00000000-0005-0000-0000-00003D040000}"/>
+    <cellStyle name="千位分隔 7 5" xfId="1634" xr:uid="{00000000-0005-0000-0000-00003E040000}"/>
+    <cellStyle name="千位分隔 7 6" xfId="1635" xr:uid="{00000000-0005-0000-0000-00003F040000}"/>
+    <cellStyle name="千位分隔 7 7" xfId="1636" xr:uid="{00000000-0005-0000-0000-000040040000}"/>
+    <cellStyle name="千位分隔 8" xfId="1637" xr:uid="{00000000-0005-0000-0000-000041040000}"/>
+    <cellStyle name="千位分隔 8 2" xfId="1638" xr:uid="{00000000-0005-0000-0000-000042040000}"/>
+    <cellStyle name="千位分隔 8 3" xfId="1639" xr:uid="{00000000-0005-0000-0000-000043040000}"/>
+    <cellStyle name="千位分隔 9" xfId="1640" xr:uid="{00000000-0005-0000-0000-000044040000}"/>
+    <cellStyle name="常规 10" xfId="439" xr:uid="{00000000-0005-0000-0000-000045040000}"/>
+    <cellStyle name="常规 10 10" xfId="1010" xr:uid="{00000000-0005-0000-0000-000046040000}"/>
+    <cellStyle name="常规 10 11" xfId="1011" xr:uid="{00000000-0005-0000-0000-000047040000}"/>
+    <cellStyle name="常规 10 12" xfId="1654" xr:uid="{00000000-0005-0000-0000-000048040000}"/>
+    <cellStyle name="常规 10 2" xfId="441" xr:uid="{00000000-0005-0000-0000-000049040000}"/>
+    <cellStyle name="常规 10 2 2" xfId="443" xr:uid="{00000000-0005-0000-0000-00004A040000}"/>
+    <cellStyle name="常规 10 2 2 2" xfId="1012" xr:uid="{00000000-0005-0000-0000-00004B040000}"/>
+    <cellStyle name="常规 10 2 2 2 2" xfId="1013" xr:uid="{00000000-0005-0000-0000-00004C040000}"/>
+    <cellStyle name="常规 10 2 2 2 2 2" xfId="1014" xr:uid="{00000000-0005-0000-0000-00004D040000}"/>
+    <cellStyle name="常规 10 2 2 2 3" xfId="1015" xr:uid="{00000000-0005-0000-0000-00004E040000}"/>
+    <cellStyle name="常规 10 2 2 2 4" xfId="1016" xr:uid="{00000000-0005-0000-0000-00004F040000}"/>
+    <cellStyle name="常规 10 2 2 2 5" xfId="1017" xr:uid="{00000000-0005-0000-0000-000050040000}"/>
+    <cellStyle name="常规 10 2 2 2 6" xfId="1018" xr:uid="{00000000-0005-0000-0000-000051040000}"/>
+    <cellStyle name="常规 10 2 2 3" xfId="1019" xr:uid="{00000000-0005-0000-0000-000052040000}"/>
+    <cellStyle name="常规 10 2 2 3 2" xfId="1020" xr:uid="{00000000-0005-0000-0000-000053040000}"/>
+    <cellStyle name="常规 10 2 2 4" xfId="1021" xr:uid="{00000000-0005-0000-0000-000054040000}"/>
+    <cellStyle name="常规 10 2 2 5" xfId="1022" xr:uid="{00000000-0005-0000-0000-000055040000}"/>
+    <cellStyle name="常规 10 2 2 6" xfId="1023" xr:uid="{00000000-0005-0000-0000-000056040000}"/>
+    <cellStyle name="常规 10 2 3" xfId="445" xr:uid="{00000000-0005-0000-0000-000057040000}"/>
+    <cellStyle name="常规 10 2 3 2" xfId="556" xr:uid="{00000000-0005-0000-0000-000058040000}"/>
+    <cellStyle name="常规 10 2 3 2 2" xfId="1024" xr:uid="{00000000-0005-0000-0000-000059040000}"/>
+    <cellStyle name="常规 10 2 3 2 2 2" xfId="1025" xr:uid="{00000000-0005-0000-0000-00005A040000}"/>
+    <cellStyle name="常规 10 2 3 2 3" xfId="1026" xr:uid="{00000000-0005-0000-0000-00005B040000}"/>
+    <cellStyle name="常规 10 2 3 2 4" xfId="1027" xr:uid="{00000000-0005-0000-0000-00005C040000}"/>
+    <cellStyle name="常规 10 2 3 2 5" xfId="1028" xr:uid="{00000000-0005-0000-0000-00005D040000}"/>
+    <cellStyle name="常规 10 2 3 2 6" xfId="1029" xr:uid="{00000000-0005-0000-0000-00005E040000}"/>
+    <cellStyle name="常规 10 2 3 3" xfId="1030" xr:uid="{00000000-0005-0000-0000-00005F040000}"/>
+    <cellStyle name="常规 10 2 3 3 2" xfId="1031" xr:uid="{00000000-0005-0000-0000-000060040000}"/>
+    <cellStyle name="常规 10 2 3 4" xfId="1032" xr:uid="{00000000-0005-0000-0000-000061040000}"/>
+    <cellStyle name="常规 10 2 3 5" xfId="1033" xr:uid="{00000000-0005-0000-0000-000062040000}"/>
+    <cellStyle name="常规 10 2 3 6" xfId="1034" xr:uid="{00000000-0005-0000-0000-000063040000}"/>
+    <cellStyle name="常规 10 2 4" xfId="169" xr:uid="{00000000-0005-0000-0000-000064040000}"/>
+    <cellStyle name="常规 10 2 4 2" xfId="490" xr:uid="{00000000-0005-0000-0000-000065040000}"/>
+    <cellStyle name="常规 10 2 4 2 2" xfId="1035" xr:uid="{00000000-0005-0000-0000-000066040000}"/>
+    <cellStyle name="常规 10 2 4 2 2 2" xfId="459" xr:uid="{00000000-0005-0000-0000-000067040000}"/>
+    <cellStyle name="常规 10 2 4 2 3" xfId="1036" xr:uid="{00000000-0005-0000-0000-000068040000}"/>
+    <cellStyle name="常规 10 2 4 2 4" xfId="1037" xr:uid="{00000000-0005-0000-0000-000069040000}"/>
+    <cellStyle name="常规 10 2 4 2 5" xfId="1038" xr:uid="{00000000-0005-0000-0000-00006A040000}"/>
+    <cellStyle name="常规 10 2 4 3" xfId="1039" xr:uid="{00000000-0005-0000-0000-00006B040000}"/>
+    <cellStyle name="常规 10 2 4 3 2" xfId="1040" xr:uid="{00000000-0005-0000-0000-00006C040000}"/>
+    <cellStyle name="常规 10 2 4 3 2 2" xfId="1041" xr:uid="{00000000-0005-0000-0000-00006D040000}"/>
+    <cellStyle name="常规 10 2 4 3 3" xfId="1042" xr:uid="{00000000-0005-0000-0000-00006E040000}"/>
+    <cellStyle name="常规 10 2 4 3 4" xfId="1043" xr:uid="{00000000-0005-0000-0000-00006F040000}"/>
+    <cellStyle name="常规 10 2 4 3 5" xfId="1044" xr:uid="{00000000-0005-0000-0000-000070040000}"/>
+    <cellStyle name="常规 10 2 4 3 6" xfId="1046" xr:uid="{00000000-0005-0000-0000-000071040000}"/>
+    <cellStyle name="常规 10 2 4 4" xfId="1047" xr:uid="{00000000-0005-0000-0000-000072040000}"/>
+    <cellStyle name="常规 10 2 4 4 2" xfId="1048" xr:uid="{00000000-0005-0000-0000-000073040000}"/>
+    <cellStyle name="常规 10 2 4 5" xfId="1049" xr:uid="{00000000-0005-0000-0000-000074040000}"/>
+    <cellStyle name="常规 10 2 4 6" xfId="1050" xr:uid="{00000000-0005-0000-0000-000075040000}"/>
+    <cellStyle name="常规 10 2 4 7" xfId="1051" xr:uid="{00000000-0005-0000-0000-000076040000}"/>
+    <cellStyle name="常规 10 2 5" xfId="173" xr:uid="{00000000-0005-0000-0000-000077040000}"/>
+    <cellStyle name="常规 10 2 5 2" xfId="1052" xr:uid="{00000000-0005-0000-0000-000078040000}"/>
+    <cellStyle name="常规 10 2 5 2 2" xfId="1053" xr:uid="{00000000-0005-0000-0000-000079040000}"/>
+    <cellStyle name="常规 10 2 5 3" xfId="1054" xr:uid="{00000000-0005-0000-0000-00007A040000}"/>
+    <cellStyle name="常规 10 2 5 4" xfId="1055" xr:uid="{00000000-0005-0000-0000-00007B040000}"/>
+    <cellStyle name="常规 10 2 5 5" xfId="1056" xr:uid="{00000000-0005-0000-0000-00007C040000}"/>
+    <cellStyle name="常规 10 2 5 6" xfId="1057" xr:uid="{00000000-0005-0000-0000-00007D040000}"/>
+    <cellStyle name="常规 10 2 6" xfId="1058" xr:uid="{00000000-0005-0000-0000-00007E040000}"/>
+    <cellStyle name="常规 10 2 6 2" xfId="1059" xr:uid="{00000000-0005-0000-0000-00007F040000}"/>
+    <cellStyle name="常规 10 2 7" xfId="1060" xr:uid="{00000000-0005-0000-0000-000080040000}"/>
+    <cellStyle name="常规 10 2 8" xfId="1061" xr:uid="{00000000-0005-0000-0000-000081040000}"/>
+    <cellStyle name="常规 10 2 9" xfId="1062" xr:uid="{00000000-0005-0000-0000-000082040000}"/>
+    <cellStyle name="常规 10 3" xfId="447" xr:uid="{00000000-0005-0000-0000-000083040000}"/>
+    <cellStyle name="常规 10 3 2" xfId="1063" xr:uid="{00000000-0005-0000-0000-000084040000}"/>
+    <cellStyle name="常规 10 3 2 2" xfId="1064" xr:uid="{00000000-0005-0000-0000-000085040000}"/>
+    <cellStyle name="常规 10 3 2 2 2" xfId="1065" xr:uid="{00000000-0005-0000-0000-000086040000}"/>
+    <cellStyle name="常规 10 3 2 3" xfId="1066" xr:uid="{00000000-0005-0000-0000-000087040000}"/>
+    <cellStyle name="常规 10 3 2 4" xfId="1067" xr:uid="{00000000-0005-0000-0000-000088040000}"/>
+    <cellStyle name="常规 10 3 2 5" xfId="1068" xr:uid="{00000000-0005-0000-0000-000089040000}"/>
+    <cellStyle name="常规 10 3 3" xfId="1069" xr:uid="{00000000-0005-0000-0000-00008A040000}"/>
+    <cellStyle name="常规 10 3 3 2" xfId="1070" xr:uid="{00000000-0005-0000-0000-00008B040000}"/>
+    <cellStyle name="常规 10 3 3 2 2" xfId="1071" xr:uid="{00000000-0005-0000-0000-00008C040000}"/>
+    <cellStyle name="常规 10 3 3 3" xfId="1072" xr:uid="{00000000-0005-0000-0000-00008D040000}"/>
+    <cellStyle name="常规 10 3 3 4" xfId="1073" xr:uid="{00000000-0005-0000-0000-00008E040000}"/>
+    <cellStyle name="常规 10 3 3 5" xfId="1074" xr:uid="{00000000-0005-0000-0000-00008F040000}"/>
+    <cellStyle name="常规 10 3 3 6" xfId="1075" xr:uid="{00000000-0005-0000-0000-000090040000}"/>
+    <cellStyle name="常规 10 3 4" xfId="1076" xr:uid="{00000000-0005-0000-0000-000091040000}"/>
+    <cellStyle name="常规 10 3 4 2" xfId="1077" xr:uid="{00000000-0005-0000-0000-000092040000}"/>
+    <cellStyle name="常规 10 3 5" xfId="1078" xr:uid="{00000000-0005-0000-0000-000093040000}"/>
+    <cellStyle name="常规 10 3 6" xfId="1079" xr:uid="{00000000-0005-0000-0000-000094040000}"/>
+    <cellStyle name="常规 10 3 7" xfId="1080" xr:uid="{00000000-0005-0000-0000-000095040000}"/>
+    <cellStyle name="常规 10 4" xfId="449" xr:uid="{00000000-0005-0000-0000-000096040000}"/>
+    <cellStyle name="常规 10 4 2" xfId="1081" xr:uid="{00000000-0005-0000-0000-000097040000}"/>
+    <cellStyle name="常规 10 4 2 2" xfId="1082" xr:uid="{00000000-0005-0000-0000-000098040000}"/>
+    <cellStyle name="常规 10 4 2 2 2" xfId="1083" xr:uid="{00000000-0005-0000-0000-000099040000}"/>
+    <cellStyle name="常规 10 4 2 3" xfId="1084" xr:uid="{00000000-0005-0000-0000-00009A040000}"/>
+    <cellStyle name="常规 10 4 2 4" xfId="1085" xr:uid="{00000000-0005-0000-0000-00009B040000}"/>
+    <cellStyle name="常规 10 4 2 5" xfId="1086" xr:uid="{00000000-0005-0000-0000-00009C040000}"/>
+    <cellStyle name="常规 10 4 3" xfId="1087" xr:uid="{00000000-0005-0000-0000-00009D040000}"/>
+    <cellStyle name="常规 10 4 3 2" xfId="1088" xr:uid="{00000000-0005-0000-0000-00009E040000}"/>
+    <cellStyle name="常规 10 4 3 2 2" xfId="1090" xr:uid="{00000000-0005-0000-0000-00009F040000}"/>
+    <cellStyle name="常规 10 4 3 3" xfId="1091" xr:uid="{00000000-0005-0000-0000-0000A0040000}"/>
+    <cellStyle name="常规 10 4 3 4" xfId="1092" xr:uid="{00000000-0005-0000-0000-0000A1040000}"/>
+    <cellStyle name="常规 10 4 3 5" xfId="1093" xr:uid="{00000000-0005-0000-0000-0000A2040000}"/>
+    <cellStyle name="常规 10 4 3 6" xfId="1094" xr:uid="{00000000-0005-0000-0000-0000A3040000}"/>
+    <cellStyle name="常规 10 4 4" xfId="1095" xr:uid="{00000000-0005-0000-0000-0000A4040000}"/>
+    <cellStyle name="常规 10 4 4 2" xfId="1096" xr:uid="{00000000-0005-0000-0000-0000A5040000}"/>
+    <cellStyle name="常规 10 4 5" xfId="1097" xr:uid="{00000000-0005-0000-0000-0000A6040000}"/>
+    <cellStyle name="常规 10 4 6" xfId="1098" xr:uid="{00000000-0005-0000-0000-0000A7040000}"/>
+    <cellStyle name="常规 10 4 7" xfId="1099" xr:uid="{00000000-0005-0000-0000-0000A8040000}"/>
+    <cellStyle name="常规 10 5" xfId="451" xr:uid="{00000000-0005-0000-0000-0000A9040000}"/>
+    <cellStyle name="常规 10 5 2" xfId="1100" xr:uid="{00000000-0005-0000-0000-0000AA040000}"/>
+    <cellStyle name="常规 10 5 2 2" xfId="1101" xr:uid="{00000000-0005-0000-0000-0000AB040000}"/>
+    <cellStyle name="常规 10 5 2 2 2" xfId="1103" xr:uid="{00000000-0005-0000-0000-0000AC040000}"/>
+    <cellStyle name="常规 10 5 2 3" xfId="1104" xr:uid="{00000000-0005-0000-0000-0000AD040000}"/>
+    <cellStyle name="常规 10 5 2 4" xfId="1105" xr:uid="{00000000-0005-0000-0000-0000AE040000}"/>
+    <cellStyle name="常规 10 5 2 5" xfId="1106" xr:uid="{00000000-0005-0000-0000-0000AF040000}"/>
+    <cellStyle name="常规 10 5 3" xfId="1107" xr:uid="{00000000-0005-0000-0000-0000B0040000}"/>
+    <cellStyle name="常规 10 5 3 2" xfId="1108" xr:uid="{00000000-0005-0000-0000-0000B1040000}"/>
+    <cellStyle name="常规 10 5 3 2 2" xfId="1109" xr:uid="{00000000-0005-0000-0000-0000B2040000}"/>
+    <cellStyle name="常规 10 5 3 3" xfId="1110" xr:uid="{00000000-0005-0000-0000-0000B3040000}"/>
+    <cellStyle name="常规 10 5 3 4" xfId="1111" xr:uid="{00000000-0005-0000-0000-0000B4040000}"/>
+    <cellStyle name="常规 10 5 3 5" xfId="1112" xr:uid="{00000000-0005-0000-0000-0000B5040000}"/>
+    <cellStyle name="常规 10 5 3 6" xfId="1113" xr:uid="{00000000-0005-0000-0000-0000B6040000}"/>
+    <cellStyle name="常规 10 5 4" xfId="1114" xr:uid="{00000000-0005-0000-0000-0000B7040000}"/>
+    <cellStyle name="常规 10 5 4 2" xfId="1115" xr:uid="{00000000-0005-0000-0000-0000B8040000}"/>
+    <cellStyle name="常规 10 5 5" xfId="1116" xr:uid="{00000000-0005-0000-0000-0000B9040000}"/>
+    <cellStyle name="常规 10 5 6" xfId="1118" xr:uid="{00000000-0005-0000-0000-0000BA040000}"/>
+    <cellStyle name="常规 10 5 7" xfId="1120" xr:uid="{00000000-0005-0000-0000-0000BB040000}"/>
+    <cellStyle name="常规 10 6" xfId="453" xr:uid="{00000000-0005-0000-0000-0000BC040000}"/>
+    <cellStyle name="常规 10 6 2" xfId="1121" xr:uid="{00000000-0005-0000-0000-0000BD040000}"/>
+    <cellStyle name="常规 10 6 2 2" xfId="1122" xr:uid="{00000000-0005-0000-0000-0000BE040000}"/>
+    <cellStyle name="常规 10 6 3" xfId="1123" xr:uid="{00000000-0005-0000-0000-0000BF040000}"/>
+    <cellStyle name="常规 10 6 4" xfId="1124" xr:uid="{00000000-0005-0000-0000-0000C0040000}"/>
+    <cellStyle name="常规 10 6 5" xfId="1125" xr:uid="{00000000-0005-0000-0000-0000C1040000}"/>
+    <cellStyle name="常规 10 6 6" xfId="429" xr:uid="{00000000-0005-0000-0000-0000C2040000}"/>
+    <cellStyle name="常规 10 7" xfId="1126" xr:uid="{00000000-0005-0000-0000-0000C3040000}"/>
+    <cellStyle name="常规 10 7 2" xfId="1127" xr:uid="{00000000-0005-0000-0000-0000C4040000}"/>
+    <cellStyle name="常规 10 7 2 2" xfId="1128" xr:uid="{00000000-0005-0000-0000-0000C5040000}"/>
+    <cellStyle name="常规 10 7 3" xfId="1129" xr:uid="{00000000-0005-0000-0000-0000C6040000}"/>
+    <cellStyle name="常规 10 7 4" xfId="1130" xr:uid="{00000000-0005-0000-0000-0000C7040000}"/>
+    <cellStyle name="常规 10 7 5" xfId="1131" xr:uid="{00000000-0005-0000-0000-0000C8040000}"/>
+    <cellStyle name="常规 10 7 6" xfId="1133" xr:uid="{00000000-0005-0000-0000-0000C9040000}"/>
+    <cellStyle name="常规 10 8" xfId="1134" xr:uid="{00000000-0005-0000-0000-0000CA040000}"/>
+    <cellStyle name="常规 10 8 2" xfId="1135" xr:uid="{00000000-0005-0000-0000-0000CB040000}"/>
+    <cellStyle name="常规 10 8 3" xfId="1136" xr:uid="{00000000-0005-0000-0000-0000CC040000}"/>
+    <cellStyle name="常规 10 8 4" xfId="1137" xr:uid="{00000000-0005-0000-0000-0000CD040000}"/>
+    <cellStyle name="常规 10 8 5" xfId="1138" xr:uid="{00000000-0005-0000-0000-0000CE040000}"/>
+    <cellStyle name="常规 10 9" xfId="1139" xr:uid="{00000000-0005-0000-0000-0000CF040000}"/>
+    <cellStyle name="常规 11" xfId="455" xr:uid="{00000000-0005-0000-0000-0000D0040000}"/>
+    <cellStyle name="常规 11 2" xfId="457" xr:uid="{00000000-0005-0000-0000-0000D1040000}"/>
+    <cellStyle name="常规 11 3" xfId="1647" xr:uid="{00000000-0005-0000-0000-0000D2040000}"/>
+    <cellStyle name="常规 12" xfId="463" xr:uid="{00000000-0005-0000-0000-0000D3040000}"/>
+    <cellStyle name="常规 12 2" xfId="745" xr:uid="{00000000-0005-0000-0000-0000D4040000}"/>
+    <cellStyle name="常规 13" xfId="363" xr:uid="{00000000-0005-0000-0000-0000D5040000}"/>
+    <cellStyle name="常规 13 2" xfId="753" xr:uid="{00000000-0005-0000-0000-0000D6040000}"/>
+    <cellStyle name="常规 14" xfId="405" xr:uid="{00000000-0005-0000-0000-0000D7040000}"/>
+    <cellStyle name="常规 14 2" xfId="1140" xr:uid="{00000000-0005-0000-0000-0000D8040000}"/>
+    <cellStyle name="常规 15" xfId="5" xr:uid="{00000000-0005-0000-0000-0000D9040000}"/>
+    <cellStyle name="常规 15 2" xfId="1142" xr:uid="{00000000-0005-0000-0000-0000DA040000}"/>
+    <cellStyle name="常规 15 2 2" xfId="1143" xr:uid="{00000000-0005-0000-0000-0000DB040000}"/>
+    <cellStyle name="常规 15 2 2 2" xfId="1144" xr:uid="{00000000-0005-0000-0000-0000DC040000}"/>
+    <cellStyle name="常规 15 2 2 3" xfId="1145" xr:uid="{00000000-0005-0000-0000-0000DD040000}"/>
+    <cellStyle name="常规 15 2 2 4" xfId="1146" xr:uid="{00000000-0005-0000-0000-0000DE040000}"/>
+    <cellStyle name="常规 15 2 2 5" xfId="1147" xr:uid="{00000000-0005-0000-0000-0000DF040000}"/>
+    <cellStyle name="常规 15 2 3" xfId="1148" xr:uid="{00000000-0005-0000-0000-0000E0040000}"/>
+    <cellStyle name="常规 15 2 4" xfId="897" xr:uid="{00000000-0005-0000-0000-0000E1040000}"/>
+    <cellStyle name="常规 15 2 5" xfId="907" xr:uid="{00000000-0005-0000-0000-0000E2040000}"/>
+    <cellStyle name="常规 15 2 6" xfId="909" xr:uid="{00000000-0005-0000-0000-0000E3040000}"/>
+    <cellStyle name="常规 15 3" xfId="1151" xr:uid="{00000000-0005-0000-0000-0000E4040000}"/>
+    <cellStyle name="常规 15 3 2" xfId="1152" xr:uid="{00000000-0005-0000-0000-0000E5040000}"/>
+    <cellStyle name="常规 15 3 3" xfId="1153" xr:uid="{00000000-0005-0000-0000-0000E6040000}"/>
+    <cellStyle name="常规 15 3 4" xfId="914" xr:uid="{00000000-0005-0000-0000-0000E7040000}"/>
+    <cellStyle name="常规 15 3 5" xfId="917" xr:uid="{00000000-0005-0000-0000-0000E8040000}"/>
+    <cellStyle name="常规 15 4" xfId="1155" xr:uid="{00000000-0005-0000-0000-0000E9040000}"/>
+    <cellStyle name="常规 15 5" xfId="1157" xr:uid="{00000000-0005-0000-0000-0000EA040000}"/>
+    <cellStyle name="常规 15 6" xfId="1159" xr:uid="{00000000-0005-0000-0000-0000EB040000}"/>
+    <cellStyle name="常规 15 7" xfId="1160" xr:uid="{00000000-0005-0000-0000-0000EC040000}"/>
+    <cellStyle name="常规 15 8" xfId="239" xr:uid="{00000000-0005-0000-0000-0000ED040000}"/>
+    <cellStyle name="常规 16" xfId="1162" xr:uid="{00000000-0005-0000-0000-0000EE040000}"/>
+    <cellStyle name="常规 16 2" xfId="1164" xr:uid="{00000000-0005-0000-0000-0000EF040000}"/>
+    <cellStyle name="常规 16 2 2" xfId="1165" xr:uid="{00000000-0005-0000-0000-0000F0040000}"/>
+    <cellStyle name="常规 16 2 2 2" xfId="1167" xr:uid="{00000000-0005-0000-0000-0000F1040000}"/>
+    <cellStyle name="常规 16 2 2 3" xfId="1169" xr:uid="{00000000-0005-0000-0000-0000F2040000}"/>
+    <cellStyle name="常规 16 2 2 4" xfId="171" xr:uid="{00000000-0005-0000-0000-0000F3040000}"/>
+    <cellStyle name="常规 16 2 2 5" xfId="175" xr:uid="{00000000-0005-0000-0000-0000F4040000}"/>
+    <cellStyle name="常规 16 2 3" xfId="1170" xr:uid="{00000000-0005-0000-0000-0000F5040000}"/>
+    <cellStyle name="常规 16 2 4" xfId="932" xr:uid="{00000000-0005-0000-0000-0000F6040000}"/>
+    <cellStyle name="常规 16 2 5" xfId="934" xr:uid="{00000000-0005-0000-0000-0000F7040000}"/>
+    <cellStyle name="常规 16 2 6" xfId="936" xr:uid="{00000000-0005-0000-0000-0000F8040000}"/>
+    <cellStyle name="常规 16 3" xfId="1171" xr:uid="{00000000-0005-0000-0000-0000F9040000}"/>
+    <cellStyle name="常规 16 3 2" xfId="1172" xr:uid="{00000000-0005-0000-0000-0000FA040000}"/>
+    <cellStyle name="常规 16 3 3" xfId="1173" xr:uid="{00000000-0005-0000-0000-0000FB040000}"/>
+    <cellStyle name="常规 16 3 4" xfId="1174" xr:uid="{00000000-0005-0000-0000-0000FC040000}"/>
+    <cellStyle name="常规 16 3 5" xfId="1175" xr:uid="{00000000-0005-0000-0000-0000FD040000}"/>
+    <cellStyle name="常规 16 4" xfId="1176" xr:uid="{00000000-0005-0000-0000-0000FE040000}"/>
+    <cellStyle name="常规 16 5" xfId="1177" xr:uid="{00000000-0005-0000-0000-0000FF040000}"/>
+    <cellStyle name="常规 16 6" xfId="1178" xr:uid="{00000000-0005-0000-0000-000000050000}"/>
+    <cellStyle name="常规 16 7" xfId="1179" xr:uid="{00000000-0005-0000-0000-000001050000}"/>
+    <cellStyle name="常规 17" xfId="1181" xr:uid="{00000000-0005-0000-0000-000002050000}"/>
+    <cellStyle name="常规 17 2" xfId="1183" xr:uid="{00000000-0005-0000-0000-000003050000}"/>
+    <cellStyle name="常规 17 3" xfId="1185" xr:uid="{00000000-0005-0000-0000-000004050000}"/>
+    <cellStyle name="常规 18" xfId="1187" xr:uid="{00000000-0005-0000-0000-000005050000}"/>
+    <cellStyle name="常规 18 2" xfId="1189" xr:uid="{00000000-0005-0000-0000-000006050000}"/>
+    <cellStyle name="常规 18 3" xfId="1191" xr:uid="{00000000-0005-0000-0000-000007050000}"/>
+    <cellStyle name="常规 19" xfId="1193" xr:uid="{00000000-0005-0000-0000-000008050000}"/>
+    <cellStyle name="常规 19 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000009050000}"/>
+    <cellStyle name="常规 19 3" xfId="1195" xr:uid="{00000000-0005-0000-0000-00000A050000}"/>
+    <cellStyle name="常规 2" xfId="1196" xr:uid="{00000000-0005-0000-0000-00000B050000}"/>
+    <cellStyle name="常规 2 10" xfId="1658" xr:uid="{00000000-0005-0000-0000-00000C050000}"/>
+    <cellStyle name="常规 2 2" xfId="1197" xr:uid="{00000000-0005-0000-0000-00000D050000}"/>
+    <cellStyle name="常规 2 2 2" xfId="1198" xr:uid="{00000000-0005-0000-0000-00000E050000}"/>
+    <cellStyle name="常规 2 2 2 2" xfId="1117" xr:uid="{00000000-0005-0000-0000-00000F050000}"/>
+    <cellStyle name="常规 2 2 2 2 2" xfId="1199" xr:uid="{00000000-0005-0000-0000-000010050000}"/>
+    <cellStyle name="常规 2 2 2 2 3" xfId="1200" xr:uid="{00000000-0005-0000-0000-000011050000}"/>
+    <cellStyle name="常规 2 2 2 2 4" xfId="1201" xr:uid="{00000000-0005-0000-0000-000012050000}"/>
+    <cellStyle name="常规 2 2 2 2 5" xfId="1202" xr:uid="{00000000-0005-0000-0000-000013050000}"/>
+    <cellStyle name="常规 2 2 2 3" xfId="1119" xr:uid="{00000000-0005-0000-0000-000014050000}"/>
+    <cellStyle name="常规 2 2 2 4" xfId="61" xr:uid="{00000000-0005-0000-0000-000015050000}"/>
+    <cellStyle name="常规 2 2 2 5" xfId="50" xr:uid="{00000000-0005-0000-0000-000016050000}"/>
+    <cellStyle name="常规 2 2 2 6" xfId="63" xr:uid="{00000000-0005-0000-0000-000017050000}"/>
+    <cellStyle name="常规 2 2 3" xfId="567" xr:uid="{00000000-0005-0000-0000-000018050000}"/>
+    <cellStyle name="常规 2 2 3 2" xfId="428" xr:uid="{00000000-0005-0000-0000-000019050000}"/>
+    <cellStyle name="常规 2 2 3 2 2" xfId="1204" xr:uid="{00000000-0005-0000-0000-00001A050000}"/>
+    <cellStyle name="常规 2 2 3 2 3" xfId="1206" xr:uid="{00000000-0005-0000-0000-00001B050000}"/>
+    <cellStyle name="常规 2 2 3 2 4" xfId="513" xr:uid="{00000000-0005-0000-0000-00001C050000}"/>
+    <cellStyle name="常规 2 2 3 2 5" xfId="1208" xr:uid="{00000000-0005-0000-0000-00001D050000}"/>
+    <cellStyle name="常规 2 2 3 3" xfId="432" xr:uid="{00000000-0005-0000-0000-00001E050000}"/>
+    <cellStyle name="常规 2 2 3 4" xfId="435" xr:uid="{00000000-0005-0000-0000-00001F050000}"/>
+    <cellStyle name="常规 2 2 3 5" xfId="569" xr:uid="{00000000-0005-0000-0000-000020050000}"/>
+    <cellStyle name="常规 2 2 3 6" xfId="1209" xr:uid="{00000000-0005-0000-0000-000021050000}"/>
+    <cellStyle name="常规 2 2 4" xfId="25" xr:uid="{00000000-0005-0000-0000-000022050000}"/>
+    <cellStyle name="常规 2 2 4 2" xfId="1132" xr:uid="{00000000-0005-0000-0000-000023050000}"/>
+    <cellStyle name="常规 2 2 4 3" xfId="1210" xr:uid="{00000000-0005-0000-0000-000024050000}"/>
+    <cellStyle name="常规 2 2 4 4" xfId="1211" xr:uid="{00000000-0005-0000-0000-000025050000}"/>
+    <cellStyle name="常规 2 2 4 5" xfId="1212" xr:uid="{00000000-0005-0000-0000-000026050000}"/>
+    <cellStyle name="常规 2 2 5" xfId="571" xr:uid="{00000000-0005-0000-0000-000027050000}"/>
+    <cellStyle name="常规 2 2 6" xfId="573" xr:uid="{00000000-0005-0000-0000-000028050000}"/>
+    <cellStyle name="常规 2 2 7" xfId="575" xr:uid="{00000000-0005-0000-0000-000029050000}"/>
+    <cellStyle name="常规 2 2 8" xfId="1213" xr:uid="{00000000-0005-0000-0000-00002A050000}"/>
+    <cellStyle name="常规 2 3" xfId="1214" xr:uid="{00000000-0005-0000-0000-00002B050000}"/>
+    <cellStyle name="常规 2 3 2" xfId="1215" xr:uid="{00000000-0005-0000-0000-00002C050000}"/>
+    <cellStyle name="常规 2 3 2 2" xfId="1216" xr:uid="{00000000-0005-0000-0000-00002D050000}"/>
+    <cellStyle name="常规 2 3 2 3" xfId="1217" xr:uid="{00000000-0005-0000-0000-00002E050000}"/>
+    <cellStyle name="常规 2 3 2 4" xfId="1218" xr:uid="{00000000-0005-0000-0000-00002F050000}"/>
+    <cellStyle name="常规 2 3 2 5" xfId="1219" xr:uid="{00000000-0005-0000-0000-000030050000}"/>
+    <cellStyle name="常规 2 3 3" xfId="577" xr:uid="{00000000-0005-0000-0000-000031050000}"/>
+    <cellStyle name="常规 2 3 4" xfId="416" xr:uid="{00000000-0005-0000-0000-000032050000}"/>
+    <cellStyle name="常规 2 3 5" xfId="419" xr:uid="{00000000-0005-0000-0000-000033050000}"/>
+    <cellStyle name="常规 2 3 6" xfId="422" xr:uid="{00000000-0005-0000-0000-000034050000}"/>
+    <cellStyle name="常规 2 4" xfId="1220" xr:uid="{00000000-0005-0000-0000-000035050000}"/>
+    <cellStyle name="常规 2 4 2" xfId="1221" xr:uid="{00000000-0005-0000-0000-000036050000}"/>
+    <cellStyle name="常规 2 4 2 2" xfId="1222" xr:uid="{00000000-0005-0000-0000-000037050000}"/>
+    <cellStyle name="常规 2 4 2 3" xfId="1223" xr:uid="{00000000-0005-0000-0000-000038050000}"/>
+    <cellStyle name="常规 2 4 2 4" xfId="1224" xr:uid="{00000000-0005-0000-0000-000039050000}"/>
+    <cellStyle name="常规 2 4 2 5" xfId="1225" xr:uid="{00000000-0005-0000-0000-00003A050000}"/>
+    <cellStyle name="常规 2 4 3" xfId="1226" xr:uid="{00000000-0005-0000-0000-00003B050000}"/>
+    <cellStyle name="常规 2 4 4" xfId="1227" xr:uid="{00000000-0005-0000-0000-00003C050000}"/>
+    <cellStyle name="常规 2 4 5" xfId="1228" xr:uid="{00000000-0005-0000-0000-00003D050000}"/>
+    <cellStyle name="常规 2 4 6" xfId="1229" xr:uid="{00000000-0005-0000-0000-00003E050000}"/>
+    <cellStyle name="常规 2 5" xfId="1230" xr:uid="{00000000-0005-0000-0000-00003F050000}"/>
+    <cellStyle name="常规 2 5 2" xfId="1231" xr:uid="{00000000-0005-0000-0000-000040050000}"/>
+    <cellStyle name="常规 2 5 2 2" xfId="1232" xr:uid="{00000000-0005-0000-0000-000041050000}"/>
+    <cellStyle name="常规 2 5 2 3" xfId="1233" xr:uid="{00000000-0005-0000-0000-000042050000}"/>
+    <cellStyle name="常规 2 5 2 4" xfId="1234" xr:uid="{00000000-0005-0000-0000-000043050000}"/>
+    <cellStyle name="常规 2 5 2 5" xfId="1000" xr:uid="{00000000-0005-0000-0000-000044050000}"/>
+    <cellStyle name="常规 2 5 3" xfId="1235" xr:uid="{00000000-0005-0000-0000-000045050000}"/>
+    <cellStyle name="常规 2 5 4" xfId="1236" xr:uid="{00000000-0005-0000-0000-000046050000}"/>
+    <cellStyle name="常规 2 5 5" xfId="1237" xr:uid="{00000000-0005-0000-0000-000047050000}"/>
+    <cellStyle name="常规 2 5 6" xfId="1238" xr:uid="{00000000-0005-0000-0000-000048050000}"/>
+    <cellStyle name="常规 2 6" xfId="1239" xr:uid="{00000000-0005-0000-0000-000049050000}"/>
+    <cellStyle name="常规 2 6 2" xfId="1240" xr:uid="{00000000-0005-0000-0000-00004A050000}"/>
+    <cellStyle name="常规 2 6 3" xfId="1241" xr:uid="{00000000-0005-0000-0000-00004B050000}"/>
+    <cellStyle name="常规 2 6 4" xfId="1242" xr:uid="{00000000-0005-0000-0000-00004C050000}"/>
+    <cellStyle name="常规 2 6 5" xfId="1243" xr:uid="{00000000-0005-0000-0000-00004D050000}"/>
+    <cellStyle name="常规 2 7" xfId="1166" xr:uid="{00000000-0005-0000-0000-00004E050000}"/>
+    <cellStyle name="常规 2 7 2" xfId="1244" xr:uid="{00000000-0005-0000-0000-00004F050000}"/>
+    <cellStyle name="常规 2 7 3" xfId="1245" xr:uid="{00000000-0005-0000-0000-000050050000}"/>
+    <cellStyle name="常规 2 7 4" xfId="1246" xr:uid="{00000000-0005-0000-0000-000051050000}"/>
+    <cellStyle name="常规 2 8" xfId="1168" xr:uid="{00000000-0005-0000-0000-000052050000}"/>
+    <cellStyle name="常规 2 8 2" xfId="967" xr:uid="{00000000-0005-0000-0000-000053050000}"/>
+    <cellStyle name="常规 2 8 3" xfId="969" xr:uid="{00000000-0005-0000-0000-000054050000}"/>
+    <cellStyle name="常规 2 9" xfId="1648" xr:uid="{00000000-0005-0000-0000-000055050000}"/>
+    <cellStyle name="常规 20" xfId="238" xr:uid="{00000000-0005-0000-0000-000056050000}"/>
+    <cellStyle name="常规 20 2" xfId="1141" xr:uid="{00000000-0005-0000-0000-000057050000}"/>
+    <cellStyle name="常规 20 3" xfId="1150" xr:uid="{00000000-0005-0000-0000-000058050000}"/>
+    <cellStyle name="常规 21" xfId="1161" xr:uid="{00000000-0005-0000-0000-000059050000}"/>
+    <cellStyle name="常规 21 2" xfId="1163" xr:uid="{00000000-0005-0000-0000-00005A050000}"/>
+    <cellStyle name="常规 22" xfId="1180" xr:uid="{00000000-0005-0000-0000-00005B050000}"/>
+    <cellStyle name="常规 22 2" xfId="1182" xr:uid="{00000000-0005-0000-0000-00005C050000}"/>
+    <cellStyle name="常规 22 2 2" xfId="1247" xr:uid="{00000000-0005-0000-0000-00005D050000}"/>
+    <cellStyle name="常规 22 2 3" xfId="1248" xr:uid="{00000000-0005-0000-0000-00005E050000}"/>
+    <cellStyle name="常规 22 2 4" xfId="1249" xr:uid="{00000000-0005-0000-0000-00005F050000}"/>
+    <cellStyle name="常规 22 2 5" xfId="103" xr:uid="{00000000-0005-0000-0000-000060050000}"/>
+    <cellStyle name="常规 22 3" xfId="1184" xr:uid="{00000000-0005-0000-0000-000061050000}"/>
+    <cellStyle name="常规 22 4" xfId="1250" xr:uid="{00000000-0005-0000-0000-000062050000}"/>
+    <cellStyle name="常规 22 5" xfId="1251" xr:uid="{00000000-0005-0000-0000-000063050000}"/>
+    <cellStyle name="常规 22 6" xfId="1252" xr:uid="{00000000-0005-0000-0000-000064050000}"/>
+    <cellStyle name="常规 23" xfId="1186" xr:uid="{00000000-0005-0000-0000-000065050000}"/>
+    <cellStyle name="常规 23 2" xfId="1188" xr:uid="{00000000-0005-0000-0000-000066050000}"/>
+    <cellStyle name="常规 23 2 2" xfId="1253" xr:uid="{00000000-0005-0000-0000-000067050000}"/>
+    <cellStyle name="常规 23 2 3" xfId="1254" xr:uid="{00000000-0005-0000-0000-000068050000}"/>
+    <cellStyle name="常规 23 2 4" xfId="1255" xr:uid="{00000000-0005-0000-0000-000069050000}"/>
+    <cellStyle name="常规 23 2 5" xfId="142" xr:uid="{00000000-0005-0000-0000-00006A050000}"/>
+    <cellStyle name="常规 23 3" xfId="1190" xr:uid="{00000000-0005-0000-0000-00006B050000}"/>
+    <cellStyle name="常规 23 4" xfId="1256" xr:uid="{00000000-0005-0000-0000-00006C050000}"/>
+    <cellStyle name="常规 23 5" xfId="1257" xr:uid="{00000000-0005-0000-0000-00006D050000}"/>
+    <cellStyle name="常规 23 6" xfId="1258" xr:uid="{00000000-0005-0000-0000-00006E050000}"/>
+    <cellStyle name="常规 24" xfId="1192" xr:uid="{00000000-0005-0000-0000-00006F050000}"/>
+    <cellStyle name="常规 24 2" xfId="1194" xr:uid="{00000000-0005-0000-0000-000070050000}"/>
+    <cellStyle name="常规 25" xfId="1260" xr:uid="{00000000-0005-0000-0000-000071050000}"/>
+    <cellStyle name="常规 25 2" xfId="1261" xr:uid="{00000000-0005-0000-0000-000072050000}"/>
+    <cellStyle name="常规 26" xfId="1263" xr:uid="{00000000-0005-0000-0000-000073050000}"/>
+    <cellStyle name="常规 26 2" xfId="31" xr:uid="{00000000-0005-0000-0000-000074050000}"/>
+    <cellStyle name="常规 27" xfId="1265" xr:uid="{00000000-0005-0000-0000-000075050000}"/>
+    <cellStyle name="常规 27 2" xfId="1267" xr:uid="{00000000-0005-0000-0000-000076050000}"/>
+    <cellStyle name="常规 27 2 2" xfId="1268" xr:uid="{00000000-0005-0000-0000-000077050000}"/>
+    <cellStyle name="常规 27 2 3" xfId="1269" xr:uid="{00000000-0005-0000-0000-000078050000}"/>
+    <cellStyle name="常规 27 2 4" xfId="1270" xr:uid="{00000000-0005-0000-0000-000079050000}"/>
+    <cellStyle name="常规 27 2 5" xfId="1271" xr:uid="{00000000-0005-0000-0000-00007A050000}"/>
+    <cellStyle name="常规 27 3" xfId="1273" xr:uid="{00000000-0005-0000-0000-00007B050000}"/>
+    <cellStyle name="常规 27 4" xfId="1275" xr:uid="{00000000-0005-0000-0000-00007C050000}"/>
+    <cellStyle name="常规 27 5" xfId="1277" xr:uid="{00000000-0005-0000-0000-00007D050000}"/>
+    <cellStyle name="常规 27 6" xfId="1278" xr:uid="{00000000-0005-0000-0000-00007E050000}"/>
+    <cellStyle name="常规 28" xfId="1280" xr:uid="{00000000-0005-0000-0000-00007F050000}"/>
+    <cellStyle name="常规 28 2" xfId="153" xr:uid="{00000000-0005-0000-0000-000080050000}"/>
+    <cellStyle name="常规 28 2 2" xfId="1281" xr:uid="{00000000-0005-0000-0000-000081050000}"/>
+    <cellStyle name="常规 28 2 3" xfId="1282" xr:uid="{00000000-0005-0000-0000-000082050000}"/>
+    <cellStyle name="常规 28 2 4" xfId="1283" xr:uid="{00000000-0005-0000-0000-000083050000}"/>
+    <cellStyle name="常规 28 2 5" xfId="1284" xr:uid="{00000000-0005-0000-0000-000084050000}"/>
+    <cellStyle name="常规 28 3" xfId="161" xr:uid="{00000000-0005-0000-0000-000085050000}"/>
+    <cellStyle name="常规 28 4" xfId="1285" xr:uid="{00000000-0005-0000-0000-000086050000}"/>
+    <cellStyle name="常规 28 5" xfId="1286" xr:uid="{00000000-0005-0000-0000-000087050000}"/>
+    <cellStyle name="常规 28 6" xfId="1288" xr:uid="{00000000-0005-0000-0000-000088050000}"/>
+    <cellStyle name="常规 29" xfId="1290" xr:uid="{00000000-0005-0000-0000-000089050000}"/>
+    <cellStyle name="常规 29 2" xfId="1292" xr:uid="{00000000-0005-0000-0000-00008A050000}"/>
+    <cellStyle name="常规 29 2 2" xfId="1293" xr:uid="{00000000-0005-0000-0000-00008B050000}"/>
+    <cellStyle name="常规 29 2 3" xfId="1294" xr:uid="{00000000-0005-0000-0000-00008C050000}"/>
+    <cellStyle name="常规 29 2 4" xfId="1295" xr:uid="{00000000-0005-0000-0000-00008D050000}"/>
+    <cellStyle name="常规 29 2 5" xfId="1296" xr:uid="{00000000-0005-0000-0000-00008E050000}"/>
+    <cellStyle name="常规 29 3" xfId="1297" xr:uid="{00000000-0005-0000-0000-00008F050000}"/>
+    <cellStyle name="常规 29 4" xfId="1298" xr:uid="{00000000-0005-0000-0000-000090050000}"/>
+    <cellStyle name="常规 29 5" xfId="1299" xr:uid="{00000000-0005-0000-0000-000091050000}"/>
+    <cellStyle name="常规 29 6" xfId="1301" xr:uid="{00000000-0005-0000-0000-000092050000}"/>
+    <cellStyle name="常规 3" xfId="1302" xr:uid="{00000000-0005-0000-0000-000093050000}"/>
+    <cellStyle name="常规 3 10" xfId="1659" xr:uid="{00000000-0005-0000-0000-000094050000}"/>
+    <cellStyle name="常规 3 2" xfId="1002" xr:uid="{00000000-0005-0000-0000-000095050000}"/>
+    <cellStyle name="常规 3 2 2" xfId="1004" xr:uid="{00000000-0005-0000-0000-000096050000}"/>
+    <cellStyle name="常规 3 2 2 2" xfId="397" xr:uid="{00000000-0005-0000-0000-000097050000}"/>
+    <cellStyle name="常规 3 2 2 2 2" xfId="1303" xr:uid="{00000000-0005-0000-0000-000098050000}"/>
+    <cellStyle name="常规 3 2 2 2 3" xfId="1304" xr:uid="{00000000-0005-0000-0000-000099050000}"/>
+    <cellStyle name="常规 3 2 2 2 4" xfId="1305" xr:uid="{00000000-0005-0000-0000-00009A050000}"/>
+    <cellStyle name="常规 3 2 2 2 5" xfId="1306" xr:uid="{00000000-0005-0000-0000-00009B050000}"/>
+    <cellStyle name="常规 3 2 2 3" xfId="401" xr:uid="{00000000-0005-0000-0000-00009C050000}"/>
+    <cellStyle name="常规 3 2 2 4" xfId="1307" xr:uid="{00000000-0005-0000-0000-00009D050000}"/>
+    <cellStyle name="常规 3 2 2 5" xfId="1308" xr:uid="{00000000-0005-0000-0000-00009E050000}"/>
+    <cellStyle name="常规 3 2 2 6" xfId="1309" xr:uid="{00000000-0005-0000-0000-00009F050000}"/>
+    <cellStyle name="常规 3 2 3" xfId="1310" xr:uid="{00000000-0005-0000-0000-0000A0050000}"/>
+    <cellStyle name="常规 3 2 3 2" xfId="1311" xr:uid="{00000000-0005-0000-0000-0000A1050000}"/>
+    <cellStyle name="常规 3 2 3 3" xfId="1312" xr:uid="{00000000-0005-0000-0000-0000A2050000}"/>
+    <cellStyle name="常规 3 2 3 4" xfId="1313" xr:uid="{00000000-0005-0000-0000-0000A3050000}"/>
+    <cellStyle name="常规 3 2 3 5" xfId="867" xr:uid="{00000000-0005-0000-0000-0000A4050000}"/>
+    <cellStyle name="常规 3 2 4" xfId="1314" xr:uid="{00000000-0005-0000-0000-0000A5050000}"/>
+    <cellStyle name="常规 3 2 5" xfId="927" xr:uid="{00000000-0005-0000-0000-0000A6050000}"/>
+    <cellStyle name="常规 3 2 6" xfId="871" xr:uid="{00000000-0005-0000-0000-0000A7050000}"/>
+    <cellStyle name="常规 3 2 7" xfId="874" xr:uid="{00000000-0005-0000-0000-0000A8050000}"/>
+    <cellStyle name="常规 3 3" xfId="1006" xr:uid="{00000000-0005-0000-0000-0000A9050000}"/>
+    <cellStyle name="常规 3 3 2" xfId="1008" xr:uid="{00000000-0005-0000-0000-0000AA050000}"/>
+    <cellStyle name="常规 3 3 2 2" xfId="1315" xr:uid="{00000000-0005-0000-0000-0000AB050000}"/>
+    <cellStyle name="常规 3 3 2 3" xfId="1316" xr:uid="{00000000-0005-0000-0000-0000AC050000}"/>
+    <cellStyle name="常规 3 3 2 4" xfId="1317" xr:uid="{00000000-0005-0000-0000-0000AD050000}"/>
+    <cellStyle name="常规 3 3 2 5" xfId="1318" xr:uid="{00000000-0005-0000-0000-0000AE050000}"/>
+    <cellStyle name="常规 3 3 3" xfId="1319" xr:uid="{00000000-0005-0000-0000-0000AF050000}"/>
+    <cellStyle name="常规 3 3 4" xfId="1320" xr:uid="{00000000-0005-0000-0000-0000B0050000}"/>
+    <cellStyle name="常规 3 3 5" xfId="1321" xr:uid="{00000000-0005-0000-0000-0000B1050000}"/>
+    <cellStyle name="常规 3 3 6" xfId="1322" xr:uid="{00000000-0005-0000-0000-0000B2050000}"/>
+    <cellStyle name="常规 3 4" xfId="1323" xr:uid="{00000000-0005-0000-0000-0000B3050000}"/>
+    <cellStyle name="常规 3 5" xfId="1324" xr:uid="{00000000-0005-0000-0000-0000B4050000}"/>
+    <cellStyle name="常规 3 5 2" xfId="1325" xr:uid="{00000000-0005-0000-0000-0000B5050000}"/>
+    <cellStyle name="常规 3 5 3" xfId="1326" xr:uid="{00000000-0005-0000-0000-0000B6050000}"/>
+    <cellStyle name="常规 3 5 4" xfId="1327" xr:uid="{00000000-0005-0000-0000-0000B7050000}"/>
+    <cellStyle name="常规 3 5 5" xfId="1329" xr:uid="{00000000-0005-0000-0000-0000B8050000}"/>
+    <cellStyle name="常规 3 6" xfId="1330" xr:uid="{00000000-0005-0000-0000-0000B9050000}"/>
+    <cellStyle name="常规 3 6 2" xfId="1331" xr:uid="{00000000-0005-0000-0000-0000BA050000}"/>
+    <cellStyle name="常规 3 7" xfId="1332" xr:uid="{00000000-0005-0000-0000-0000BB050000}"/>
+    <cellStyle name="常规 3 7 2" xfId="92" xr:uid="{00000000-0005-0000-0000-0000BC050000}"/>
+    <cellStyle name="常规 3 7 3" xfId="1333" xr:uid="{00000000-0005-0000-0000-0000BD050000}"/>
+    <cellStyle name="常规 3 8" xfId="1334" xr:uid="{00000000-0005-0000-0000-0000BE050000}"/>
+    <cellStyle name="常规 3 9" xfId="1649" xr:uid="{00000000-0005-0000-0000-0000BF050000}"/>
+    <cellStyle name="常规 30" xfId="1259" xr:uid="{00000000-0005-0000-0000-0000C0050000}"/>
+    <cellStyle name="常规 31" xfId="1262" xr:uid="{00000000-0005-0000-0000-0000C1050000}"/>
+    <cellStyle name="常规 31 2" xfId="30" xr:uid="{00000000-0005-0000-0000-0000C2050000}"/>
+    <cellStyle name="常规 31 2 2" xfId="1335" xr:uid="{00000000-0005-0000-0000-0000C3050000}"/>
+    <cellStyle name="常规 31 2 3" xfId="1336" xr:uid="{00000000-0005-0000-0000-0000C4050000}"/>
+    <cellStyle name="常规 31 2 4" xfId="1337" xr:uid="{00000000-0005-0000-0000-0000C5050000}"/>
+    <cellStyle name="常规 31 2 5" xfId="1338" xr:uid="{00000000-0005-0000-0000-0000C6050000}"/>
+    <cellStyle name="常规 31 3" xfId="67" xr:uid="{00000000-0005-0000-0000-0000C7050000}"/>
+    <cellStyle name="常规 31 4" xfId="70" xr:uid="{00000000-0005-0000-0000-0000C8050000}"/>
+    <cellStyle name="常规 31 5" xfId="74" xr:uid="{00000000-0005-0000-0000-0000C9050000}"/>
+    <cellStyle name="常规 31 6" xfId="1339" xr:uid="{00000000-0005-0000-0000-0000CA050000}"/>
+    <cellStyle name="常规 32" xfId="1264" xr:uid="{00000000-0005-0000-0000-0000CB050000}"/>
+    <cellStyle name="常规 32 2" xfId="1266" xr:uid="{00000000-0005-0000-0000-0000CC050000}"/>
+    <cellStyle name="常规 32 3" xfId="1272" xr:uid="{00000000-0005-0000-0000-0000CD050000}"/>
+    <cellStyle name="常规 32 4" xfId="1274" xr:uid="{00000000-0005-0000-0000-0000CE050000}"/>
+    <cellStyle name="常规 32 5" xfId="1276" xr:uid="{00000000-0005-0000-0000-0000CF050000}"/>
+    <cellStyle name="常规 33" xfId="8" xr:uid="{00000000-0005-0000-0000-0000D0050000}"/>
+    <cellStyle name="常规 33 2" xfId="152" xr:uid="{00000000-0005-0000-0000-0000D1050000}"/>
+    <cellStyle name="常规 33 3" xfId="1279" xr:uid="{00000000-0005-0000-0000-0000D2050000}"/>
+    <cellStyle name="常规 34" xfId="1289" xr:uid="{00000000-0005-0000-0000-0000D3050000}"/>
+    <cellStyle name="常规 34 2" xfId="1291" xr:uid="{00000000-0005-0000-0000-0000D4050000}"/>
+    <cellStyle name="常规 35" xfId="12" xr:uid="{00000000-0005-0000-0000-0000D5050000}"/>
+    <cellStyle name="常规 35 2" xfId="1341" xr:uid="{00000000-0005-0000-0000-0000D6050000}"/>
+    <cellStyle name="常规 36" xfId="1343" xr:uid="{00000000-0005-0000-0000-0000D7050000}"/>
+    <cellStyle name="常规 36 2" xfId="1345" xr:uid="{00000000-0005-0000-0000-0000D8050000}"/>
+    <cellStyle name="常规 37" xfId="1347" xr:uid="{00000000-0005-0000-0000-0000D9050000}"/>
+    <cellStyle name="常规 37 2" xfId="1349" xr:uid="{00000000-0005-0000-0000-0000DA050000}"/>
+    <cellStyle name="常规 37 3" xfId="1350" xr:uid="{00000000-0005-0000-0000-0000DB050000}"/>
+    <cellStyle name="常规 38" xfId="824" xr:uid="{00000000-0005-0000-0000-0000DC050000}"/>
+    <cellStyle name="常规 38 2" xfId="827" xr:uid="{00000000-0005-0000-0000-0000DD050000}"/>
+    <cellStyle name="常规 38 3" xfId="829" xr:uid="{00000000-0005-0000-0000-0000DE050000}"/>
+    <cellStyle name="常规 38 4" xfId="831" xr:uid="{00000000-0005-0000-0000-0000DF050000}"/>
+    <cellStyle name="常规 38 5" xfId="833" xr:uid="{00000000-0005-0000-0000-0000E0050000}"/>
+    <cellStyle name="常规 39" xfId="23" xr:uid="{00000000-0005-0000-0000-0000E1050000}"/>
+    <cellStyle name="常规 39 2" xfId="1352" xr:uid="{00000000-0005-0000-0000-0000E2050000}"/>
+    <cellStyle name="常规 39 3" xfId="1353" xr:uid="{00000000-0005-0000-0000-0000E3050000}"/>
+    <cellStyle name="常规 39 4" xfId="1354" xr:uid="{00000000-0005-0000-0000-0000E4050000}"/>
+    <cellStyle name="常规 4" xfId="1355" xr:uid="{00000000-0005-0000-0000-0000E5050000}"/>
+    <cellStyle name="常规 4 2" xfId="1356" xr:uid="{00000000-0005-0000-0000-0000E6050000}"/>
+    <cellStyle name="常规 4 2 2" xfId="1358" xr:uid="{00000000-0005-0000-0000-0000E7050000}"/>
+    <cellStyle name="常规 4 2 2 2" xfId="1361" xr:uid="{00000000-0005-0000-0000-0000E8050000}"/>
+    <cellStyle name="常规 4 2 2 2 2" xfId="1363" xr:uid="{00000000-0005-0000-0000-0000E9050000}"/>
+    <cellStyle name="常规 4 2 2 2 3" xfId="1365" xr:uid="{00000000-0005-0000-0000-0000EA050000}"/>
+    <cellStyle name="常规 4 2 2 2 4" xfId="1367" xr:uid="{00000000-0005-0000-0000-0000EB050000}"/>
+    <cellStyle name="常规 4 2 2 2 5" xfId="1369" xr:uid="{00000000-0005-0000-0000-0000EC050000}"/>
+    <cellStyle name="常规 4 2 2 3" xfId="41" xr:uid="{00000000-0005-0000-0000-0000ED050000}"/>
+    <cellStyle name="常规 4 2 2 4" xfId="1372" xr:uid="{00000000-0005-0000-0000-0000EE050000}"/>
+    <cellStyle name="常规 4 2 2 5" xfId="1375" xr:uid="{00000000-0005-0000-0000-0000EF050000}"/>
+    <cellStyle name="常规 4 2 2 6" xfId="1377" xr:uid="{00000000-0005-0000-0000-0000F0050000}"/>
+    <cellStyle name="常规 4 2 3" xfId="1379" xr:uid="{00000000-0005-0000-0000-0000F1050000}"/>
+    <cellStyle name="常规 4 2 3 2" xfId="1380" xr:uid="{00000000-0005-0000-0000-0000F2050000}"/>
+    <cellStyle name="常规 4 2 3 3" xfId="1381" xr:uid="{00000000-0005-0000-0000-0000F3050000}"/>
+    <cellStyle name="常规 4 2 3 4" xfId="1382" xr:uid="{00000000-0005-0000-0000-0000F4050000}"/>
+    <cellStyle name="常规 4 2 3 5" xfId="1384" xr:uid="{00000000-0005-0000-0000-0000F5050000}"/>
+    <cellStyle name="常规 4 2 4" xfId="1386" xr:uid="{00000000-0005-0000-0000-0000F6050000}"/>
+    <cellStyle name="常规 4 2 5" xfId="1388" xr:uid="{00000000-0005-0000-0000-0000F7050000}"/>
+    <cellStyle name="常规 4 2 6" xfId="1391" xr:uid="{00000000-0005-0000-0000-0000F8050000}"/>
+    <cellStyle name="常规 4 2 7" xfId="1393" xr:uid="{00000000-0005-0000-0000-0000F9050000}"/>
+    <cellStyle name="常规 4 3" xfId="1394" xr:uid="{00000000-0005-0000-0000-0000FA050000}"/>
+    <cellStyle name="常规 4 3 2" xfId="1396" xr:uid="{00000000-0005-0000-0000-0000FB050000}"/>
+    <cellStyle name="常规 4 3 2 2" xfId="1398" xr:uid="{00000000-0005-0000-0000-0000FC050000}"/>
+    <cellStyle name="常规 4 3 2 3" xfId="1400" xr:uid="{00000000-0005-0000-0000-0000FD050000}"/>
+    <cellStyle name="常规 4 3 2 4" xfId="1402" xr:uid="{00000000-0005-0000-0000-0000FE050000}"/>
+    <cellStyle name="常规 4 3 2 5" xfId="1404" xr:uid="{00000000-0005-0000-0000-0000FF050000}"/>
+    <cellStyle name="常规 4 3 3" xfId="1406" xr:uid="{00000000-0005-0000-0000-000000060000}"/>
+    <cellStyle name="常规 4 3 4" xfId="1408" xr:uid="{00000000-0005-0000-0000-000001060000}"/>
+    <cellStyle name="常规 4 3 5" xfId="1410" xr:uid="{00000000-0005-0000-0000-000002060000}"/>
+    <cellStyle name="常规 4 3 6" xfId="1413" xr:uid="{00000000-0005-0000-0000-000003060000}"/>
+    <cellStyle name="常规 4 4" xfId="1357" xr:uid="{00000000-0005-0000-0000-000004060000}"/>
+    <cellStyle name="常规 4 4 2" xfId="1360" xr:uid="{00000000-0005-0000-0000-000005060000}"/>
+    <cellStyle name="常规 4 4 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000006060000}"/>
+    <cellStyle name="常规 4 4 4" xfId="1371" xr:uid="{00000000-0005-0000-0000-000007060000}"/>
+    <cellStyle name="常规 4 4 5" xfId="1374" xr:uid="{00000000-0005-0000-0000-000008060000}"/>
+    <cellStyle name="常规 4 5" xfId="1378" xr:uid="{00000000-0005-0000-0000-000009060000}"/>
+    <cellStyle name="常规 4 6" xfId="1385" xr:uid="{00000000-0005-0000-0000-00000A060000}"/>
+    <cellStyle name="常规 4 7" xfId="1387" xr:uid="{00000000-0005-0000-0000-00000B060000}"/>
+    <cellStyle name="常规 4 8" xfId="1390" xr:uid="{00000000-0005-0000-0000-00000C060000}"/>
+    <cellStyle name="常规 40" xfId="1340" xr:uid="{00000000-0005-0000-0000-00000D060000}"/>
+    <cellStyle name="常规 40 2" xfId="1414" xr:uid="{00000000-0005-0000-0000-00000E060000}"/>
+    <cellStyle name="常规 41" xfId="1342" xr:uid="{00000000-0005-0000-0000-00000F060000}"/>
+    <cellStyle name="常规 41 2" xfId="1344" xr:uid="{00000000-0005-0000-0000-000010060000}"/>
+    <cellStyle name="常规 42" xfId="1346" xr:uid="{00000000-0005-0000-0000-000011060000}"/>
+    <cellStyle name="常规 42 2" xfId="1348" xr:uid="{00000000-0005-0000-0000-000012060000}"/>
+    <cellStyle name="常规 43" xfId="823" xr:uid="{00000000-0005-0000-0000-000013060000}"/>
+    <cellStyle name="常规 43 2" xfId="826" xr:uid="{00000000-0005-0000-0000-000014060000}"/>
+    <cellStyle name="常规 44" xfId="22" xr:uid="{00000000-0005-0000-0000-000015060000}"/>
+    <cellStyle name="常规 44 2" xfId="1351" xr:uid="{00000000-0005-0000-0000-000016060000}"/>
+    <cellStyle name="常规 45" xfId="836" xr:uid="{00000000-0005-0000-0000-000017060000}"/>
+    <cellStyle name="常规 45 2" xfId="1415" xr:uid="{00000000-0005-0000-0000-000018060000}"/>
+    <cellStyle name="常规 46" xfId="839" xr:uid="{00000000-0005-0000-0000-000019060000}"/>
+    <cellStyle name="常规 47" xfId="842" xr:uid="{00000000-0005-0000-0000-00001A060000}"/>
+    <cellStyle name="常规 47 2" xfId="1416" xr:uid="{00000000-0005-0000-0000-00001B060000}"/>
+    <cellStyle name="常规 48" xfId="1418" xr:uid="{00000000-0005-0000-0000-00001C060000}"/>
+    <cellStyle name="常规 49" xfId="1420" xr:uid="{00000000-0005-0000-0000-00001D060000}"/>
+    <cellStyle name="常规 5" xfId="1421" xr:uid="{00000000-0005-0000-0000-00001E060000}"/>
+    <cellStyle name="常规 5 2" xfId="1422" xr:uid="{00000000-0005-0000-0000-00001F060000}"/>
+    <cellStyle name="常规 5 2 2" xfId="1423" xr:uid="{00000000-0005-0000-0000-000020060000}"/>
+    <cellStyle name="常规 5 2 2 2" xfId="1424" xr:uid="{00000000-0005-0000-0000-000021060000}"/>
+    <cellStyle name="常规 5 2 2 2 2" xfId="1149" xr:uid="{00000000-0005-0000-0000-000022060000}"/>
+    <cellStyle name="常规 5 2 2 2 3" xfId="1154" xr:uid="{00000000-0005-0000-0000-000023060000}"/>
+    <cellStyle name="常规 5 2 2 2 4" xfId="1156" xr:uid="{00000000-0005-0000-0000-000024060000}"/>
+    <cellStyle name="常规 5 2 2 2 5" xfId="1158" xr:uid="{00000000-0005-0000-0000-000025060000}"/>
+    <cellStyle name="常规 5 2 2 3" xfId="1425" xr:uid="{00000000-0005-0000-0000-000026060000}"/>
+    <cellStyle name="常规 5 2 2 4" xfId="1426" xr:uid="{00000000-0005-0000-0000-000027060000}"/>
+    <cellStyle name="常规 5 2 2 5" xfId="1427" xr:uid="{00000000-0005-0000-0000-000028060000}"/>
+    <cellStyle name="常规 5 2 2 6" xfId="1428" xr:uid="{00000000-0005-0000-0000-000029060000}"/>
+    <cellStyle name="常规 5 2 3" xfId="1429" xr:uid="{00000000-0005-0000-0000-00002A060000}"/>
+    <cellStyle name="常规 5 2 3 2" xfId="1045" xr:uid="{00000000-0005-0000-0000-00002B060000}"/>
+    <cellStyle name="常规 5 2 3 3" xfId="1430" xr:uid="{00000000-0005-0000-0000-00002C060000}"/>
+    <cellStyle name="常规 5 2 3 4" xfId="1431" xr:uid="{00000000-0005-0000-0000-00002D060000}"/>
+    <cellStyle name="常规 5 2 3 5" xfId="1432" xr:uid="{00000000-0005-0000-0000-00002E060000}"/>
+    <cellStyle name="常规 5 2 4" xfId="1433" xr:uid="{00000000-0005-0000-0000-00002F060000}"/>
+    <cellStyle name="常规 5 2 5" xfId="1434" xr:uid="{00000000-0005-0000-0000-000030060000}"/>
+    <cellStyle name="常规 5 2 6" xfId="1436" xr:uid="{00000000-0005-0000-0000-000031060000}"/>
+    <cellStyle name="常规 5 2 7" xfId="1438" xr:uid="{00000000-0005-0000-0000-000032060000}"/>
+    <cellStyle name="常规 5 3" xfId="1439" xr:uid="{00000000-0005-0000-0000-000033060000}"/>
+    <cellStyle name="常规 5 3 2" xfId="337" xr:uid="{00000000-0005-0000-0000-000034060000}"/>
+    <cellStyle name="常规 5 3 2 2" xfId="341" xr:uid="{00000000-0005-0000-0000-000035060000}"/>
+    <cellStyle name="常规 5 3 2 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000036060000}"/>
+    <cellStyle name="常规 5 3 2 4" xfId="1440" xr:uid="{00000000-0005-0000-0000-000037060000}"/>
+    <cellStyle name="常规 5 3 2 5" xfId="1441" xr:uid="{00000000-0005-0000-0000-000038060000}"/>
+    <cellStyle name="常规 5 3 3" xfId="499" xr:uid="{00000000-0005-0000-0000-000039060000}"/>
+    <cellStyle name="常规 5 3 4" xfId="503" xr:uid="{00000000-0005-0000-0000-00003A060000}"/>
+    <cellStyle name="常规 5 3 5" xfId="505" xr:uid="{00000000-0005-0000-0000-00003B060000}"/>
+    <cellStyle name="常规 5 3 6" xfId="507" xr:uid="{00000000-0005-0000-0000-00003C060000}"/>
+    <cellStyle name="常规 5 4" xfId="1395" xr:uid="{00000000-0005-0000-0000-00003D060000}"/>
+    <cellStyle name="常规 5 4 2" xfId="1397" xr:uid="{00000000-0005-0000-0000-00003E060000}"/>
+    <cellStyle name="常规 5 4 3" xfId="1399" xr:uid="{00000000-0005-0000-0000-00003F060000}"/>
+    <cellStyle name="常规 5 4 4" xfId="1401" xr:uid="{00000000-0005-0000-0000-000040060000}"/>
+    <cellStyle name="常规 5 4 5" xfId="1403" xr:uid="{00000000-0005-0000-0000-000041060000}"/>
+    <cellStyle name="常规 5 5" xfId="1405" xr:uid="{00000000-0005-0000-0000-000042060000}"/>
+    <cellStyle name="常规 5 6" xfId="1407" xr:uid="{00000000-0005-0000-0000-000043060000}"/>
+    <cellStyle name="常规 5 7" xfId="1409" xr:uid="{00000000-0005-0000-0000-000044060000}"/>
+    <cellStyle name="常规 5 8" xfId="1412" xr:uid="{00000000-0005-0000-0000-000045060000}"/>
+    <cellStyle name="常规 50" xfId="835" xr:uid="{00000000-0005-0000-0000-000046060000}"/>
+    <cellStyle name="常规 51" xfId="838" xr:uid="{00000000-0005-0000-0000-000047060000}"/>
+    <cellStyle name="常规 52" xfId="841" xr:uid="{00000000-0005-0000-0000-000048060000}"/>
+    <cellStyle name="常规 53" xfId="1417" xr:uid="{00000000-0005-0000-0000-000049060000}"/>
+    <cellStyle name="常规 54" xfId="1419" xr:uid="{00000000-0005-0000-0000-00004A060000}"/>
+    <cellStyle name="常规 55" xfId="85" xr:uid="{00000000-0005-0000-0000-00004B060000}"/>
+    <cellStyle name="常规 56" xfId="105" xr:uid="{00000000-0005-0000-0000-00004C060000}"/>
+    <cellStyle name="常规 57" xfId="109" xr:uid="{00000000-0005-0000-0000-00004D060000}"/>
+    <cellStyle name="常规 6" xfId="1442" xr:uid="{00000000-0005-0000-0000-00004E060000}"/>
+    <cellStyle name="常规 6 2" xfId="1443" xr:uid="{00000000-0005-0000-0000-00004F060000}"/>
+    <cellStyle name="常规 6 2 2" xfId="634" xr:uid="{00000000-0005-0000-0000-000050060000}"/>
+    <cellStyle name="常规 6 2 2 2" xfId="1444" xr:uid="{00000000-0005-0000-0000-000051060000}"/>
+    <cellStyle name="常规 6 2 2 2 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000052060000}"/>
+    <cellStyle name="常规 6 2 2 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-000053060000}"/>
+    <cellStyle name="常规 6 2 2 2 4" xfId="783" xr:uid="{00000000-0005-0000-0000-000054060000}"/>
+    <cellStyle name="常规 6 2 2 2 5" xfId="785" xr:uid="{00000000-0005-0000-0000-000055060000}"/>
+    <cellStyle name="常规 6 2 2 3" xfId="1445" xr:uid="{00000000-0005-0000-0000-000056060000}"/>
+    <cellStyle name="常规 6 2 2 4" xfId="1446" xr:uid="{00000000-0005-0000-0000-000057060000}"/>
+    <cellStyle name="常规 6 2 2 5" xfId="1447" xr:uid="{00000000-0005-0000-0000-000058060000}"/>
+    <cellStyle name="常规 6 2 2 6" xfId="1448" xr:uid="{00000000-0005-0000-0000-000059060000}"/>
+    <cellStyle name="常规 6 2 3" xfId="636" xr:uid="{00000000-0005-0000-0000-00005A060000}"/>
+    <cellStyle name="常规 6 2 3 2" xfId="1449" xr:uid="{00000000-0005-0000-0000-00005B060000}"/>
+    <cellStyle name="常规 6 2 3 3" xfId="1450" xr:uid="{00000000-0005-0000-0000-00005C060000}"/>
+    <cellStyle name="常规 6 2 3 4" xfId="1451" xr:uid="{00000000-0005-0000-0000-00005D060000}"/>
+    <cellStyle name="常规 6 2 3 5" xfId="1452" xr:uid="{00000000-0005-0000-0000-00005E060000}"/>
+    <cellStyle name="常规 6 2 4" xfId="638" xr:uid="{00000000-0005-0000-0000-00005F060000}"/>
+    <cellStyle name="常规 6 2 5" xfId="1453" xr:uid="{00000000-0005-0000-0000-000060060000}"/>
+    <cellStyle name="常规 6 2 6" xfId="738" xr:uid="{00000000-0005-0000-0000-000061060000}"/>
+    <cellStyle name="常规 6 2 7" xfId="750" xr:uid="{00000000-0005-0000-0000-000062060000}"/>
+    <cellStyle name="常规 6 3" xfId="1454" xr:uid="{00000000-0005-0000-0000-000063060000}"/>
+    <cellStyle name="常规 6 3 2" xfId="645" xr:uid="{00000000-0005-0000-0000-000064060000}"/>
+    <cellStyle name="常规 6 3 2 2" xfId="1455" xr:uid="{00000000-0005-0000-0000-000065060000}"/>
+    <cellStyle name="常规 6 3 2 3" xfId="1456" xr:uid="{00000000-0005-0000-0000-000066060000}"/>
+    <cellStyle name="常规 6 3 2 4" xfId="1457" xr:uid="{00000000-0005-0000-0000-000067060000}"/>
+    <cellStyle name="常规 6 3 2 5" xfId="1458" xr:uid="{00000000-0005-0000-0000-000068060000}"/>
+    <cellStyle name="常规 6 3 3" xfId="647" xr:uid="{00000000-0005-0000-0000-000069060000}"/>
+    <cellStyle name="常规 6 3 4" xfId="1459" xr:uid="{00000000-0005-0000-0000-00006A060000}"/>
+    <cellStyle name="常规 6 3 5" xfId="1460" xr:uid="{00000000-0005-0000-0000-00006B060000}"/>
+    <cellStyle name="常规 6 3 6" xfId="763" xr:uid="{00000000-0005-0000-0000-00006C060000}"/>
+    <cellStyle name="常规 6 4" xfId="1359" xr:uid="{00000000-0005-0000-0000-00006D060000}"/>
+    <cellStyle name="常规 6 4 2" xfId="1362" xr:uid="{00000000-0005-0000-0000-00006E060000}"/>
+    <cellStyle name="常规 6 4 3" xfId="1364" xr:uid="{00000000-0005-0000-0000-00006F060000}"/>
+    <cellStyle name="常规 6 4 4" xfId="1366" xr:uid="{00000000-0005-0000-0000-000070060000}"/>
+    <cellStyle name="常规 6 4 5" xfId="1368" xr:uid="{00000000-0005-0000-0000-000071060000}"/>
+    <cellStyle name="常规 6 5" xfId="39" xr:uid="{00000000-0005-0000-0000-000072060000}"/>
+    <cellStyle name="常规 6 6" xfId="1370" xr:uid="{00000000-0005-0000-0000-000073060000}"/>
+    <cellStyle name="常规 6 7" xfId="1373" xr:uid="{00000000-0005-0000-0000-000074060000}"/>
+    <cellStyle name="常规 6 8" xfId="1376" xr:uid="{00000000-0005-0000-0000-000075060000}"/>
+    <cellStyle name="常规 60" xfId="1643" xr:uid="{00000000-0005-0000-0000-000076060000}"/>
+    <cellStyle name="常规 60 2" xfId="1652" xr:uid="{00000000-0005-0000-0000-000077060000}"/>
+    <cellStyle name="常规 61" xfId="1644" xr:uid="{00000000-0005-0000-0000-000078060000}"/>
+    <cellStyle name="常规 61 2" xfId="1653" xr:uid="{00000000-0005-0000-0000-000079060000}"/>
+    <cellStyle name="常规 7" xfId="1461" xr:uid="{00000000-0005-0000-0000-00007A060000}"/>
+    <cellStyle name="常规 8" xfId="1462" xr:uid="{00000000-0005-0000-0000-00007B060000}"/>
+    <cellStyle name="常规 8 2" xfId="1463" xr:uid="{00000000-0005-0000-0000-00007C060000}"/>
+    <cellStyle name="常规 9" xfId="6" xr:uid="{00000000-0005-0000-0000-00007D060000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -5310,9 +5313,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5350,9 +5353,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5387,7 +5390,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5422,7 +5425,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5595,7 +5598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
@@ -5611,7 +5614,7 @@
     <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" style="147" customWidth="1"/>
+    <col min="9" max="9" width="34" style="147" customWidth="1"/>
     <col min="10" max="11" width="20.6640625" style="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
@@ -5635,23 +5638,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="167" t="s">
+      <c r="B1" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="168"/>
-      <c r="I1" s="168"/>
-      <c r="J1" s="168"/>
-      <c r="K1" s="168"/>
-      <c r="L1" s="168"/>
-      <c r="M1" s="168"/>
-      <c r="N1" s="168"/>
-      <c r="O1" s="169"/>
-      <c r="AD1" s="173"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="170"/>
+      <c r="AD1" s="167"/>
       <c r="AU1"/>
       <c r="AV1"/>
       <c r="AW1"/>
@@ -5675,7 +5678,7 @@
       <c r="X2" s="133"/>
       <c r="Y2" s="133"/>
       <c r="Z2" s="133"/>
-      <c r="AD2" s="173"/>
+      <c r="AD2" s="167"/>
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
@@ -5708,7 +5711,7 @@
       <c r="X3" s="133"/>
       <c r="Y3" s="133"/>
       <c r="Z3" s="133"/>
-      <c r="AD3" s="173"/>
+      <c r="AD3" s="167"/>
       <c r="AU3"/>
       <c r="AV3"/>
       <c r="AW3"/>
@@ -5734,18 +5737,18 @@
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="170"/>
-      <c r="Q4" s="171"/>
-      <c r="R4" s="171"/>
-      <c r="S4" s="171"/>
-      <c r="T4" s="171"/>
-      <c r="U4" s="172"/>
+      <c r="P4" s="171"/>
+      <c r="Q4" s="172"/>
+      <c r="R4" s="172"/>
+      <c r="S4" s="172"/>
+      <c r="T4" s="172"/>
+      <c r="U4" s="173"/>
       <c r="V4" s="133"/>
       <c r="W4" s="133"/>
       <c r="X4" s="133"/>
       <c r="Y4" s="133"/>
       <c r="Z4" s="133"/>
-      <c r="AD4" s="173"/>
+      <c r="AD4" s="167"/>
       <c r="AU4"/>
       <c r="AV4"/>
       <c r="AW4"/>
@@ -5783,7 +5786,7 @@
       <c r="X5" s="133"/>
       <c r="Y5" s="133"/>
       <c r="Z5" s="133"/>
-      <c r="AD5" s="173"/>
+      <c r="AD5" s="167"/>
       <c r="AU5"/>
       <c r="AV5"/>
       <c r="AW5"/>
@@ -5814,7 +5817,7 @@
       <c r="X6" s="134"/>
       <c r="Y6" s="134"/>
       <c r="Z6" s="134"/>
-      <c r="AD6" s="173"/>
+      <c r="AD6" s="167"/>
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6"/>
@@ -5853,7 +5856,7 @@
       <c r="X7" s="131"/>
       <c r="Y7" s="131"/>
       <c r="Z7" s="132"/>
-      <c r="AD7" s="173"/>
+      <c r="AD7" s="167"/>
       <c r="AU7"/>
       <c r="AV7"/>
       <c r="AW7"/>
@@ -5939,7 +5942,7 @@
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
       <c r="AC8" s="30"/>
-      <c r="AD8" s="173"/>
+      <c r="AD8" s="167"/>
       <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8"/>
@@ -6013,7 +6016,7 @@
       <c r="AA9" s="38"/>
       <c r="AB9" s="38"/>
       <c r="AC9" s="39"/>
-      <c r="AD9" s="173"/>
+      <c r="AD9" s="167"/>
       <c r="AU9"/>
       <c r="AV9"/>
       <c r="AW9"/>
@@ -6109,7 +6112,7 @@
       <c r="AA10" s="59"/>
       <c r="AB10" s="59"/>
       <c r="AC10" s="59"/>
-      <c r="AD10" s="173"/>
+      <c r="AD10" s="167"/>
       <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
@@ -6170,7 +6173,7 @@
       <c r="AA11" s="59"/>
       <c r="AB11" s="59"/>
       <c r="AC11" s="59"/>
-      <c r="AD11" s="173"/>
+      <c r="AD11" s="167"/>
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
@@ -6211,7 +6214,7 @@
       <c r="Y12" s="92"/>
       <c r="Z12" s="93"/>
       <c r="AC12" s="94"/>
-      <c r="AD12" s="173"/>
+      <c r="AD12" s="167"/>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
@@ -6247,7 +6250,7 @@
       <c r="Y13"/>
       <c r="Z13"/>
       <c r="AA13"/>
-      <c r="AD13" s="173"/>
+      <c r="AD13" s="167"/>
       <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13"/>
@@ -6291,7 +6294,7 @@
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
-      <c r="AD14" s="173"/>
+      <c r="AD14" s="167"/>
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
@@ -6335,7 +6338,7 @@
       <c r="Y15"/>
       <c r="Z15"/>
       <c r="AA15"/>
-      <c r="AD15" s="173"/>
+      <c r="AD15" s="167"/>
       <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
@@ -6381,7 +6384,7 @@
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
-      <c r="AD16" s="173"/>
+      <c r="AD16" s="167"/>
       <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
@@ -6425,7 +6428,7 @@
       <c r="Y17"/>
       <c r="Z17"/>
       <c r="AA17"/>
-      <c r="AD17" s="173"/>
+      <c r="AD17" s="167"/>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
@@ -6462,7 +6465,7 @@
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
-      <c r="AD18" s="173"/>
+      <c r="AD18" s="167"/>
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18"/>
@@ -6503,7 +6506,7 @@
       <c r="Y19"/>
       <c r="Z19"/>
       <c r="AA19"/>
-      <c r="AD19" s="173"/>
+      <c r="AD19" s="167"/>
       <c r="AU19"/>
       <c r="AV19"/>
       <c r="AW19"/>
@@ -6541,7 +6544,7 @@
       <c r="Y20"/>
       <c r="Z20"/>
       <c r="AA20"/>
-      <c r="AD20" s="173"/>
+      <c r="AD20" s="167"/>
       <c r="AU20"/>
       <c r="AV20"/>
       <c r="AW20"/>
@@ -6579,7 +6582,7 @@
       <c r="Y21"/>
       <c r="Z21"/>
       <c r="AA21"/>
-      <c r="AD21" s="173"/>
+      <c r="AD21" s="167"/>
       <c r="AU21"/>
       <c r="AV21"/>
       <c r="AW21"/>
@@ -6619,7 +6622,7 @@
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
-      <c r="AD22" s="173"/>
+      <c r="AD22" s="167"/>
       <c r="AU22"/>
       <c r="AV22"/>
       <c r="AW22"/>
@@ -6657,7 +6660,7 @@
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23"/>
-      <c r="AD23" s="173"/>
+      <c r="AD23" s="167"/>
       <c r="AU23"/>
       <c r="AV23"/>
       <c r="AW23"/>
@@ -6702,7 +6705,7 @@
       <c r="Y24"/>
       <c r="Z24"/>
       <c r="AA24"/>
-      <c r="AD24" s="173"/>
+      <c r="AD24" s="167"/>
       <c r="AU24"/>
       <c r="AV24"/>
       <c r="AW24"/>
@@ -6743,7 +6746,7 @@
       <c r="Y25"/>
       <c r="Z25"/>
       <c r="AA25"/>
-      <c r="AD25" s="173"/>
+      <c r="AD25" s="167"/>
       <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
@@ -6788,7 +6791,7 @@
       <c r="Y26"/>
       <c r="Z26"/>
       <c r="AA26"/>
-      <c r="AD26" s="173"/>
+      <c r="AD26" s="167"/>
       <c r="AU26"/>
       <c r="AV26"/>
       <c r="AW26"/>
@@ -6829,7 +6832,7 @@
       <c r="Y27"/>
       <c r="Z27"/>
       <c r="AA27"/>
-      <c r="AD27" s="173"/>
+      <c r="AD27" s="167"/>
       <c r="AU27"/>
       <c r="AV27"/>
       <c r="AW27"/>
@@ -6870,7 +6873,7 @@
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28"/>
-      <c r="AD28" s="173"/>
+      <c r="AD28" s="167"/>
       <c r="AU28"/>
       <c r="AV28"/>
       <c r="AW28"/>
@@ -6913,7 +6916,7 @@
       <c r="Y29"/>
       <c r="Z29"/>
       <c r="AA29"/>
-      <c r="AD29" s="173"/>
+      <c r="AD29" s="167"/>
       <c r="AU29"/>
       <c r="AV29"/>
       <c r="AW29"/>
@@ -6954,7 +6957,7 @@
       <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
-      <c r="AD30" s="173"/>
+      <c r="AD30" s="167"/>
       <c r="AU30"/>
       <c r="AV30"/>
       <c r="AW30"/>
@@ -6997,7 +7000,7 @@
       <c r="AA31"/>
       <c r="AB31" s="99"/>
       <c r="AC31" s="99"/>
-      <c r="AD31" s="173"/>
+      <c r="AD31" s="167"/>
       <c r="AE31" s="99"/>
       <c r="AF31" s="99"/>
       <c r="AU31"/>
@@ -7042,7 +7045,7 @@
       <c r="AA32"/>
       <c r="AB32" s="99"/>
       <c r="AC32" s="99"/>
-      <c r="AD32" s="173"/>
+      <c r="AD32" s="167"/>
       <c r="AE32" s="99"/>
       <c r="AF32" s="99"/>
       <c r="AU32"/>
@@ -7089,7 +7092,7 @@
       <c r="AA33"/>
       <c r="AB33" s="99"/>
       <c r="AC33" s="99"/>
-      <c r="AD33" s="173"/>
+      <c r="AD33" s="167"/>
       <c r="AE33" s="99"/>
       <c r="AF33" s="99"/>
       <c r="AU33"/>
@@ -7134,7 +7137,7 @@
       <c r="AA34"/>
       <c r="AB34" s="99"/>
       <c r="AC34" s="99"/>
-      <c r="AD34" s="173"/>
+      <c r="AD34" s="167"/>
       <c r="AE34" s="99"/>
       <c r="AF34" s="99"/>
       <c r="AG34" s="99"/>
@@ -7180,7 +7183,7 @@
       <c r="AA35"/>
       <c r="AB35" s="99"/>
       <c r="AC35" s="99"/>
-      <c r="AD35" s="173"/>
+      <c r="AD35" s="167"/>
       <c r="AE35" s="99"/>
       <c r="AF35" s="99"/>
       <c r="AG35" s="99"/>
@@ -7226,7 +7229,7 @@
       <c r="AA36"/>
       <c r="AB36" s="99"/>
       <c r="AC36" s="99"/>
-      <c r="AD36" s="173"/>
+      <c r="AD36" s="167"/>
       <c r="AE36" s="99"/>
       <c r="AF36" s="99"/>
       <c r="AG36" s="99"/>
@@ -7274,7 +7277,7 @@
       <c r="AA37"/>
       <c r="AB37" s="99"/>
       <c r="AC37" s="99"/>
-      <c r="AD37" s="173"/>
+      <c r="AD37" s="167"/>
       <c r="AE37" s="99"/>
       <c r="AF37" s="99"/>
       <c r="AG37" s="99"/>
@@ -7320,7 +7323,7 @@
       <c r="AA38"/>
       <c r="AB38" s="99"/>
       <c r="AC38" s="99"/>
-      <c r="AD38" s="173"/>
+      <c r="AD38" s="167"/>
       <c r="AE38" s="99"/>
       <c r="AF38" s="99"/>
       <c r="AG38" s="99"/>
@@ -7363,7 +7366,7 @@
       <c r="AA39"/>
       <c r="AB39" s="99"/>
       <c r="AC39" s="99"/>
-      <c r="AD39" s="173"/>
+      <c r="AD39" s="167"/>
       <c r="AE39" s="99"/>
       <c r="AF39" s="99"/>
       <c r="AG39" s="99"/>
@@ -7409,7 +7412,7 @@
       <c r="AA40"/>
       <c r="AB40" s="99"/>
       <c r="AC40" s="99"/>
-      <c r="AD40" s="173"/>
+      <c r="AD40" s="167"/>
       <c r="AE40" s="99"/>
       <c r="AF40" s="99"/>
       <c r="AG40" s="99"/>
@@ -7450,7 +7453,7 @@
       <c r="AA41"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-      <c r="AD41" s="173"/>
+      <c r="AD41" s="167"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
@@ -7490,7 +7493,7 @@
       <c r="AA42"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="173"/>
+      <c r="AD42" s="167"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
@@ -7533,7 +7536,7 @@
       <c r="AA43"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="173"/>
+      <c r="AD43" s="167"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
@@ -7574,7 +7577,7 @@
       <c r="Y44"/>
       <c r="Z44"/>
       <c r="AA44"/>
-      <c r="AD44" s="173"/>
+      <c r="AD44" s="167"/>
       <c r="AU44"/>
       <c r="AV44"/>
       <c r="AW44"/>
@@ -7609,7 +7612,7 @@
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AD45" s="173"/>
+      <c r="AD45" s="167"/>
       <c r="AU45"/>
       <c r="AV45"/>
       <c r="AW45"/>
@@ -7644,7 +7647,7 @@
       <c r="Y46"/>
       <c r="Z46"/>
       <c r="AA46"/>
-      <c r="AD46" s="173"/>
+      <c r="AD46" s="167"/>
       <c r="AU46"/>
       <c r="AV46"/>
       <c r="AW46"/>
@@ -7679,7 +7682,7 @@
       <c r="Y47"/>
       <c r="Z47"/>
       <c r="AA47"/>
-      <c r="AD47" s="173"/>
+      <c r="AD47" s="167"/>
       <c r="AU47"/>
       <c r="AV47"/>
       <c r="AW47"/>
@@ -7688,7 +7691,7 @@
       <c r="AZ47"/>
     </row>
     <row r="48" spans="1:52" ht="11.45" customHeight="1">
-      <c r="AD48" s="173"/>
+      <c r="AD48" s="167"/>
       <c r="AU48"/>
       <c r="AV48"/>
       <c r="AW48"/>
@@ -7696,170 +7699,278 @@
       <c r="AY48"/>
       <c r="AZ48"/>
     </row>
-    <row r="49" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD49" s="173"/>
+    <row r="49" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I49" s="1"/>
+      <c r="M49" s="96"/>
+      <c r="N49" s="96"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
+      <c r="Q49" s="8"/>
+      <c r="AA49" s="167"/>
+      <c r="AR49"/>
+      <c r="AS49"/>
+      <c r="AT49"/>
       <c r="AU49"/>
       <c r="AV49"/>
       <c r="AW49"/>
-      <c r="AX49"/>
-      <c r="AY49"/>
-      <c r="AZ49"/>
-    </row>
-    <row r="50" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD50" s="173"/>
+    </row>
+    <row r="50" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I50" s="1"/>
+      <c r="M50" s="96"/>
+      <c r="N50" s="96"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8"/>
+      <c r="AA50" s="167"/>
+      <c r="AR50"/>
+      <c r="AS50"/>
+      <c r="AT50"/>
       <c r="AU50"/>
       <c r="AV50"/>
       <c r="AW50"/>
-      <c r="AX50"/>
-      <c r="AY50"/>
-      <c r="AZ50"/>
-    </row>
-    <row r="51" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD51" s="173"/>
+    </row>
+    <row r="51" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I51" s="1"/>
+      <c r="M51" s="96"/>
+      <c r="N51" s="96"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
+      <c r="Q51" s="8"/>
+      <c r="AA51" s="167"/>
+      <c r="AR51"/>
+      <c r="AS51"/>
+      <c r="AT51"/>
       <c r="AU51"/>
       <c r="AV51"/>
       <c r="AW51"/>
-      <c r="AX51"/>
-      <c r="AY51"/>
-      <c r="AZ51"/>
-    </row>
-    <row r="52" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD52" s="173"/>
+    </row>
+    <row r="52" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I52" s="1"/>
+      <c r="M52" s="96"/>
+      <c r="N52" s="96"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="AA52" s="167"/>
+      <c r="AR52"/>
+      <c r="AS52"/>
+      <c r="AT52"/>
       <c r="AU52"/>
       <c r="AV52"/>
       <c r="AW52"/>
-      <c r="AX52"/>
-      <c r="AY52"/>
-      <c r="AZ52"/>
-    </row>
-    <row r="53" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD53" s="173"/>
+    </row>
+    <row r="53" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I53" s="1"/>
+      <c r="M53" s="96"/>
+      <c r="N53" s="96"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
+      <c r="Q53" s="8"/>
+      <c r="AA53" s="167"/>
+      <c r="AR53"/>
+      <c r="AS53"/>
+      <c r="AT53"/>
       <c r="AU53"/>
       <c r="AV53"/>
       <c r="AW53"/>
-      <c r="AX53"/>
-      <c r="AY53"/>
-      <c r="AZ53"/>
-    </row>
-    <row r="54" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD54" s="173"/>
+    </row>
+    <row r="54" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I54" s="1"/>
+      <c r="M54" s="96"/>
+      <c r="N54" s="96"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="8"/>
+      <c r="AA54" s="167"/>
+      <c r="AR54"/>
+      <c r="AS54"/>
+      <c r="AT54"/>
       <c r="AU54"/>
       <c r="AV54"/>
       <c r="AW54"/>
-      <c r="AX54"/>
-      <c r="AY54"/>
-      <c r="AZ54"/>
-    </row>
-    <row r="55" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD55" s="173"/>
+    </row>
+    <row r="55" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I55" s="1"/>
+      <c r="M55" s="96"/>
+      <c r="N55" s="96"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="8"/>
+      <c r="AA55" s="167"/>
+      <c r="AR55"/>
+      <c r="AS55"/>
+      <c r="AT55"/>
       <c r="AU55"/>
       <c r="AV55"/>
       <c r="AW55"/>
-      <c r="AX55"/>
-      <c r="AY55"/>
-      <c r="AZ55"/>
-    </row>
-    <row r="56" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD56" s="173"/>
+    </row>
+    <row r="56" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I56" s="1"/>
+      <c r="M56" s="96"/>
+      <c r="N56" s="96"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="AA56" s="167"/>
+      <c r="AR56"/>
+      <c r="AS56"/>
+      <c r="AT56"/>
       <c r="AU56"/>
       <c r="AV56"/>
       <c r="AW56"/>
-      <c r="AX56"/>
-      <c r="AY56"/>
-      <c r="AZ56"/>
-    </row>
-    <row r="57" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD57" s="173"/>
+    </row>
+    <row r="57" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I57" s="1"/>
+      <c r="M57" s="96"/>
+      <c r="N57" s="96"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="8"/>
+      <c r="AA57" s="167"/>
+      <c r="AR57"/>
+      <c r="AS57"/>
+      <c r="AT57"/>
       <c r="AU57"/>
       <c r="AV57"/>
       <c r="AW57"/>
-      <c r="AX57"/>
-      <c r="AY57"/>
-      <c r="AZ57"/>
-    </row>
-    <row r="58" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD58" s="173"/>
+    </row>
+    <row r="58" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I58" s="1"/>
+      <c r="M58" s="96"/>
+      <c r="N58" s="96"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
+      <c r="Q58" s="8"/>
+      <c r="AA58" s="167"/>
+      <c r="AR58"/>
+      <c r="AS58"/>
+      <c r="AT58"/>
       <c r="AU58"/>
       <c r="AV58"/>
       <c r="AW58"/>
-      <c r="AX58"/>
-      <c r="AY58"/>
-      <c r="AZ58"/>
-    </row>
-    <row r="59" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD59" s="173"/>
+    </row>
+    <row r="59" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I59" s="1"/>
+      <c r="M59" s="96"/>
+      <c r="N59" s="96"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
+      <c r="Q59" s="8"/>
+      <c r="AA59" s="167"/>
+      <c r="AR59"/>
+      <c r="AS59"/>
+      <c r="AT59"/>
       <c r="AU59"/>
       <c r="AV59"/>
       <c r="AW59"/>
-      <c r="AX59"/>
-      <c r="AY59"/>
-      <c r="AZ59"/>
-    </row>
-    <row r="60" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD60" s="173"/>
+    </row>
+    <row r="60" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I60" s="1"/>
+      <c r="M60" s="96"/>
+      <c r="N60" s="96"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
+      <c r="Q60" s="8"/>
+      <c r="AA60" s="167"/>
+      <c r="AR60"/>
+      <c r="AS60"/>
+      <c r="AT60"/>
       <c r="AU60"/>
       <c r="AV60"/>
       <c r="AW60"/>
-      <c r="AX60"/>
-      <c r="AY60"/>
-      <c r="AZ60"/>
-    </row>
-    <row r="61" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD61" s="173"/>
+    </row>
+    <row r="61" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I61" s="1"/>
+      <c r="M61" s="96"/>
+      <c r="N61" s="96"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
+      <c r="Q61" s="8"/>
+      <c r="AA61" s="167"/>
+      <c r="AR61"/>
+      <c r="AS61"/>
+      <c r="AT61"/>
       <c r="AU61"/>
       <c r="AV61"/>
       <c r="AW61"/>
-      <c r="AX61"/>
-      <c r="AY61"/>
-      <c r="AZ61"/>
-    </row>
-    <row r="62" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD62" s="173"/>
+    </row>
+    <row r="62" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I62" s="1"/>
+      <c r="M62" s="96"/>
+      <c r="N62" s="96"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="8"/>
+      <c r="AA62" s="167"/>
+      <c r="AR62"/>
+      <c r="AS62"/>
+      <c r="AT62"/>
       <c r="AU62"/>
       <c r="AV62"/>
       <c r="AW62"/>
-      <c r="AX62"/>
-      <c r="AY62"/>
-      <c r="AZ62"/>
-    </row>
-    <row r="63" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD63" s="173"/>
+    </row>
+    <row r="63" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I63" s="1"/>
+      <c r="M63" s="96"/>
+      <c r="N63" s="96"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8"/>
+      <c r="Q63" s="8"/>
+      <c r="AA63" s="167"/>
+      <c r="AR63"/>
+      <c r="AS63"/>
+      <c r="AT63"/>
       <c r="AU63"/>
       <c r="AV63"/>
       <c r="AW63"/>
-      <c r="AX63"/>
-      <c r="AY63"/>
-      <c r="AZ63"/>
-    </row>
-    <row r="64" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD64" s="173"/>
+    </row>
+    <row r="64" spans="9:49" ht="11.45" customHeight="1">
+      <c r="I64" s="1"/>
+      <c r="M64" s="96"/>
+      <c r="N64" s="96"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8"/>
+      <c r="Q64" s="8"/>
+      <c r="AA64" s="167"/>
+      <c r="AR64"/>
+      <c r="AS64"/>
+      <c r="AT64"/>
       <c r="AU64"/>
       <c r="AV64"/>
       <c r="AW64"/>
-      <c r="AX64"/>
-      <c r="AY64"/>
-      <c r="AZ64"/>
-    </row>
-    <row r="65" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD65" s="173"/>
+    </row>
+    <row r="65" spans="9:52" ht="11.45" customHeight="1">
+      <c r="I65" s="1"/>
+      <c r="M65" s="96"/>
+      <c r="N65" s="96"/>
+      <c r="O65" s="8"/>
+      <c r="P65" s="8"/>
+      <c r="Q65" s="8"/>
+      <c r="AA65" s="167"/>
+      <c r="AR65"/>
+      <c r="AS65"/>
+      <c r="AT65"/>
       <c r="AU65"/>
       <c r="AV65"/>
       <c r="AW65"/>
-      <c r="AX65"/>
-      <c r="AY65"/>
-      <c r="AZ65"/>
-    </row>
-    <row r="66" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD66" s="173"/>
+    </row>
+    <row r="66" spans="9:52" ht="11.45" customHeight="1">
+      <c r="I66" s="1"/>
+      <c r="M66" s="96"/>
+      <c r="N66" s="96"/>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8"/>
+      <c r="Q66" s="8"/>
+      <c r="AA66" s="167"/>
+      <c r="AR66"/>
+      <c r="AS66"/>
+      <c r="AT66"/>
       <c r="AU66"/>
       <c r="AV66"/>
       <c r="AW66"/>
-      <c r="AX66"/>
-      <c r="AY66"/>
-      <c r="AZ66"/>
-    </row>
-    <row r="67" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD67" s="173"/>
+    </row>
+    <row r="67" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD67" s="167"/>
       <c r="AU67"/>
       <c r="AV67"/>
       <c r="AW67"/>
@@ -7867,8 +7978,8 @@
       <c r="AY67"/>
       <c r="AZ67"/>
     </row>
-    <row r="68" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD68" s="173"/>
+    <row r="68" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD68" s="167"/>
       <c r="AU68"/>
       <c r="AV68"/>
       <c r="AW68"/>
@@ -7876,8 +7987,8 @@
       <c r="AY68"/>
       <c r="AZ68"/>
     </row>
-    <row r="69" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD69" s="173"/>
+    <row r="69" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD69" s="167"/>
       <c r="AU69"/>
       <c r="AV69"/>
       <c r="AW69"/>
@@ -7885,8 +7996,8 @@
       <c r="AY69"/>
       <c r="AZ69"/>
     </row>
-    <row r="70" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD70" s="173"/>
+    <row r="70" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD70" s="167"/>
       <c r="AU70"/>
       <c r="AV70"/>
       <c r="AW70"/>
@@ -7894,8 +8005,8 @@
       <c r="AY70"/>
       <c r="AZ70"/>
     </row>
-    <row r="71" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD71" s="173"/>
+    <row r="71" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD71" s="167"/>
       <c r="AU71"/>
       <c r="AV71"/>
       <c r="AW71"/>
@@ -7903,8 +8014,8 @@
       <c r="AY71"/>
       <c r="AZ71"/>
     </row>
-    <row r="72" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD72" s="173"/>
+    <row r="72" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD72" s="167"/>
       <c r="AU72"/>
       <c r="AV72"/>
       <c r="AW72"/>
@@ -7912,8 +8023,8 @@
       <c r="AY72"/>
       <c r="AZ72"/>
     </row>
-    <row r="73" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD73" s="173"/>
+    <row r="73" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD73" s="167"/>
       <c r="AU73"/>
       <c r="AV73"/>
       <c r="AW73"/>
@@ -7921,8 +8032,8 @@
       <c r="AY73"/>
       <c r="AZ73"/>
     </row>
-    <row r="74" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD74" s="173"/>
+    <row r="74" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD74" s="167"/>
       <c r="AU74"/>
       <c r="AV74"/>
       <c r="AW74"/>
@@ -7930,8 +8041,8 @@
       <c r="AY74"/>
       <c r="AZ74"/>
     </row>
-    <row r="75" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD75" s="173"/>
+    <row r="75" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD75" s="167"/>
       <c r="AU75"/>
       <c r="AV75"/>
       <c r="AW75"/>
@@ -7939,8 +8050,8 @@
       <c r="AY75"/>
       <c r="AZ75"/>
     </row>
-    <row r="76" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD76" s="173"/>
+    <row r="76" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD76" s="167"/>
       <c r="AU76"/>
       <c r="AV76"/>
       <c r="AW76"/>
@@ -7948,8 +8059,8 @@
       <c r="AY76"/>
       <c r="AZ76"/>
     </row>
-    <row r="77" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD77" s="173"/>
+    <row r="77" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD77" s="167"/>
       <c r="AU77"/>
       <c r="AV77"/>
       <c r="AW77"/>
@@ -7957,8 +8068,8 @@
       <c r="AY77"/>
       <c r="AZ77"/>
     </row>
-    <row r="78" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD78" s="173"/>
+    <row r="78" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD78" s="167"/>
       <c r="AU78"/>
       <c r="AV78"/>
       <c r="AW78"/>
@@ -7966,8 +8077,8 @@
       <c r="AY78"/>
       <c r="AZ78"/>
     </row>
-    <row r="79" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD79" s="173"/>
+    <row r="79" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD79" s="167"/>
       <c r="AU79"/>
       <c r="AV79"/>
       <c r="AW79"/>
@@ -7975,8 +8086,8 @@
       <c r="AY79"/>
       <c r="AZ79"/>
     </row>
-    <row r="80" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD80" s="173"/>
+    <row r="80" spans="9:52" ht="11.45" customHeight="1">
+      <c r="AD80" s="167"/>
       <c r="AU80"/>
       <c r="AV80"/>
       <c r="AW80"/>
@@ -7985,7 +8096,7 @@
       <c r="AZ80"/>
     </row>
     <row r="81" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD81" s="173"/>
+      <c r="AD81" s="167"/>
       <c r="AU81"/>
       <c r="AV81"/>
       <c r="AW81"/>
@@ -7994,7 +8105,7 @@
       <c r="AZ81"/>
     </row>
     <row r="82" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD82" s="173"/>
+      <c r="AD82" s="167"/>
       <c r="AU82"/>
       <c r="AV82"/>
       <c r="AW82"/>
@@ -8003,7 +8114,7 @@
       <c r="AZ82"/>
     </row>
     <row r="83" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD83" s="173"/>
+      <c r="AD83" s="167"/>
       <c r="AU83"/>
       <c r="AV83"/>
       <c r="AW83"/>
@@ -8012,7 +8123,7 @@
       <c r="AZ83"/>
     </row>
     <row r="84" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD84" s="173"/>
+      <c r="AD84" s="167"/>
       <c r="AU84"/>
       <c r="AV84"/>
       <c r="AW84"/>
@@ -8021,7 +8132,7 @@
       <c r="AZ84"/>
     </row>
     <row r="85" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD85" s="173"/>
+      <c r="AD85" s="167"/>
       <c r="AU85"/>
       <c r="AV85"/>
       <c r="AW85"/>
@@ -8030,7 +8141,7 @@
       <c r="AZ85"/>
     </row>
     <row r="86" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD86" s="173"/>
+      <c r="AD86" s="167"/>
       <c r="AU86"/>
       <c r="AV86"/>
       <c r="AW86"/>
@@ -8039,7 +8150,7 @@
       <c r="AZ86"/>
     </row>
     <row r="87" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD87" s="173"/>
+      <c r="AD87" s="167"/>
       <c r="AU87"/>
       <c r="AV87"/>
       <c r="AW87"/>
@@ -8048,7 +8159,7 @@
       <c r="AZ87"/>
     </row>
     <row r="88" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD88" s="173"/>
+      <c r="AD88" s="167"/>
       <c r="AU88"/>
       <c r="AV88"/>
       <c r="AW88"/>
@@ -8057,7 +8168,7 @@
       <c r="AZ88"/>
     </row>
     <row r="89" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD89" s="173"/>
+      <c r="AD89" s="167"/>
       <c r="AU89"/>
       <c r="AV89"/>
       <c r="AW89"/>
@@ -8066,7 +8177,7 @@
       <c r="AZ89"/>
     </row>
     <row r="90" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD90" s="173"/>
+      <c r="AD90" s="167"/>
       <c r="AU90"/>
       <c r="AV90"/>
       <c r="AW90"/>
@@ -8075,7 +8186,7 @@
       <c r="AZ90"/>
     </row>
     <row r="91" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD91" s="173"/>
+      <c r="AD91" s="167"/>
       <c r="AU91"/>
       <c r="AV91"/>
       <c r="AW91"/>
@@ -8084,7 +8195,7 @@
       <c r="AZ91"/>
     </row>
     <row r="92" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD92" s="173"/>
+      <c r="AD92" s="167"/>
       <c r="AU92"/>
       <c r="AV92"/>
       <c r="AW92"/>
@@ -8093,7 +8204,7 @@
       <c r="AZ92"/>
     </row>
     <row r="93" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD93" s="173"/>
+      <c r="AD93" s="167"/>
       <c r="AU93"/>
       <c r="AV93"/>
       <c r="AW93"/>
@@ -8102,7 +8213,7 @@
       <c r="AZ93"/>
     </row>
     <row r="94" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD94" s="173"/>
+      <c r="AD94" s="167"/>
       <c r="AU94"/>
       <c r="AV94"/>
       <c r="AW94"/>
@@ -8111,7 +8222,7 @@
       <c r="AZ94"/>
     </row>
     <row r="95" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD95" s="173"/>
+      <c r="AD95" s="167"/>
       <c r="AU95"/>
       <c r="AV95"/>
       <c r="AW95"/>
@@ -8120,7 +8231,7 @@
       <c r="AZ95"/>
     </row>
     <row r="96" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD96" s="173"/>
+      <c r="AD96" s="167"/>
       <c r="AU96"/>
       <c r="AV96"/>
       <c r="AW96"/>
@@ -8129,7 +8240,7 @@
       <c r="AZ96"/>
     </row>
     <row r="97" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD97" s="173"/>
+      <c r="AD97" s="167"/>
       <c r="AU97"/>
       <c r="AV97"/>
       <c r="AW97"/>
@@ -8138,7 +8249,7 @@
       <c r="AZ97"/>
     </row>
     <row r="98" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD98" s="173"/>
+      <c r="AD98" s="167"/>
       <c r="AU98"/>
       <c r="AV98"/>
       <c r="AW98"/>
@@ -8147,7 +8258,7 @@
       <c r="AZ98"/>
     </row>
     <row r="99" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD99" s="173"/>
+      <c r="AD99" s="167"/>
       <c r="AU99"/>
       <c r="AV99"/>
       <c r="AW99"/>
@@ -8156,7 +8267,7 @@
       <c r="AZ99"/>
     </row>
     <row r="100" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD100" s="173"/>
+      <c r="AD100" s="167"/>
       <c r="AU100"/>
       <c r="AV100"/>
       <c r="AW100"/>
@@ -8165,7 +8276,7 @@
       <c r="AZ100"/>
     </row>
     <row r="101" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD101" s="173"/>
+      <c r="AD101" s="167"/>
       <c r="AU101"/>
       <c r="AV101"/>
       <c r="AW101"/>
@@ -8174,7 +8285,7 @@
       <c r="AZ101"/>
     </row>
     <row r="102" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD102" s="173"/>
+      <c r="AD102" s="167"/>
       <c r="AU102"/>
       <c r="AV102"/>
       <c r="AW102"/>
@@ -8183,7 +8294,7 @@
       <c r="AZ102"/>
     </row>
     <row r="103" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD103" s="173"/>
+      <c r="AD103" s="167"/>
       <c r="AU103"/>
       <c r="AV103"/>
       <c r="AW103"/>
@@ -8192,7 +8303,7 @@
       <c r="AZ103"/>
     </row>
     <row r="104" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD104" s="173"/>
+      <c r="AD104" s="167"/>
       <c r="AU104"/>
       <c r="AV104"/>
       <c r="AW104"/>
@@ -8201,7 +8312,7 @@
       <c r="AZ104"/>
     </row>
     <row r="105" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD105" s="173"/>
+      <c r="AD105" s="167"/>
       <c r="AU105"/>
       <c r="AV105"/>
       <c r="AW105"/>
@@ -8210,7 +8321,7 @@
       <c r="AZ105"/>
     </row>
     <row r="106" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD106" s="173"/>
+      <c r="AD106" s="167"/>
       <c r="AU106"/>
       <c r="AV106"/>
       <c r="AW106"/>
@@ -8219,7 +8330,7 @@
       <c r="AZ106"/>
     </row>
     <row r="107" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD107" s="173"/>
+      <c r="AD107" s="167"/>
       <c r="AU107"/>
       <c r="AV107"/>
       <c r="AW107"/>
@@ -8228,7 +8339,7 @@
       <c r="AZ107"/>
     </row>
     <row r="108" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD108" s="173"/>
+      <c r="AD108" s="167"/>
       <c r="AU108"/>
       <c r="AV108"/>
       <c r="AW108"/>
@@ -8237,7 +8348,7 @@
       <c r="AZ108"/>
     </row>
     <row r="109" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD109" s="173"/>
+      <c r="AD109" s="167"/>
       <c r="AU109"/>
       <c r="AV109"/>
       <c r="AW109"/>
@@ -8246,7 +8357,7 @@
       <c r="AZ109"/>
     </row>
     <row r="110" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD110" s="173"/>
+      <c r="AD110" s="167"/>
       <c r="AU110"/>
       <c r="AV110"/>
       <c r="AW110"/>
@@ -8255,7 +8366,7 @@
       <c r="AZ110"/>
     </row>
     <row r="111" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD111" s="173"/>
+      <c r="AD111" s="167"/>
       <c r="AU111"/>
       <c r="AV111"/>
       <c r="AW111"/>
@@ -8264,7 +8375,7 @@
       <c r="AZ111"/>
     </row>
     <row r="112" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD112" s="173"/>
+      <c r="AD112" s="167"/>
       <c r="AU112"/>
       <c r="AV112"/>
       <c r="AW112"/>
@@ -8273,7 +8384,7 @@
       <c r="AZ112"/>
     </row>
     <row r="113" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD113" s="173"/>
+      <c r="AD113" s="167"/>
       <c r="AU113"/>
       <c r="AV113"/>
       <c r="AW113"/>
@@ -8282,7 +8393,7 @@
       <c r="AZ113"/>
     </row>
     <row r="114" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD114" s="173"/>
+      <c r="AD114" s="167"/>
       <c r="AU114"/>
       <c r="AV114"/>
       <c r="AW114"/>
@@ -8291,7 +8402,7 @@
       <c r="AZ114"/>
     </row>
     <row r="115" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD115" s="173"/>
+      <c r="AD115" s="167"/>
       <c r="AU115"/>
       <c r="AV115"/>
       <c r="AW115"/>
@@ -8300,7 +8411,7 @@
       <c r="AZ115"/>
     </row>
     <row r="116" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD116" s="173"/>
+      <c r="AD116" s="167"/>
       <c r="AU116"/>
       <c r="AV116"/>
       <c r="AW116"/>
@@ -8309,7 +8420,7 @@
       <c r="AZ116"/>
     </row>
     <row r="117" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD117" s="173"/>
+      <c r="AD117" s="167"/>
       <c r="AU117"/>
       <c r="AV117"/>
       <c r="AW117"/>
@@ -8318,7 +8429,7 @@
       <c r="AZ117"/>
     </row>
     <row r="118" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD118" s="173"/>
+      <c r="AD118" s="167"/>
       <c r="AU118"/>
       <c r="AV118"/>
       <c r="AW118"/>
@@ -8327,7 +8438,7 @@
       <c r="AZ118"/>
     </row>
     <row r="119" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD119" s="173"/>
+      <c r="AD119" s="167"/>
       <c r="AU119"/>
       <c r="AV119"/>
       <c r="AW119"/>
@@ -8336,7 +8447,7 @@
       <c r="AZ119"/>
     </row>
     <row r="120" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD120" s="173"/>
+      <c r="AD120" s="167"/>
       <c r="AU120"/>
       <c r="AV120"/>
       <c r="AW120"/>
@@ -8345,7 +8456,7 @@
       <c r="AZ120"/>
     </row>
     <row r="121" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD121" s="173"/>
+      <c r="AD121" s="167"/>
       <c r="AU121"/>
       <c r="AV121"/>
       <c r="AW121"/>
@@ -8354,7 +8465,7 @@
       <c r="AZ121"/>
     </row>
     <row r="122" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD122" s="173"/>
+      <c r="AD122" s="167"/>
       <c r="AU122"/>
       <c r="AV122"/>
       <c r="AW122"/>
@@ -8363,7 +8474,7 @@
       <c r="AZ122"/>
     </row>
     <row r="123" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD123" s="173"/>
+      <c r="AD123" s="167"/>
       <c r="AU123"/>
       <c r="AV123"/>
       <c r="AW123"/>
@@ -8372,7 +8483,7 @@
       <c r="AZ123"/>
     </row>
     <row r="124" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD124" s="173"/>
+      <c r="AD124" s="167"/>
       <c r="AU124"/>
       <c r="AV124"/>
       <c r="AW124"/>
@@ -8381,7 +8492,7 @@
       <c r="AZ124"/>
     </row>
     <row r="125" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD125" s="173"/>
+      <c r="AD125" s="167"/>
       <c r="AU125"/>
       <c r="AV125"/>
       <c r="AW125"/>
@@ -8390,7 +8501,7 @@
       <c r="AZ125"/>
     </row>
     <row r="126" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD126" s="173"/>
+      <c r="AD126" s="167"/>
       <c r="AU126"/>
       <c r="AV126"/>
       <c r="AW126"/>
@@ -8399,7 +8510,7 @@
       <c r="AZ126"/>
     </row>
     <row r="127" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD127" s="173"/>
+      <c r="AD127" s="167"/>
       <c r="AU127"/>
       <c r="AV127"/>
       <c r="AW127"/>
@@ -8408,7 +8519,7 @@
       <c r="AZ127"/>
     </row>
     <row r="128" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD128" s="173"/>
+      <c r="AD128" s="167"/>
       <c r="AU128"/>
       <c r="AV128"/>
       <c r="AW128"/>
@@ -8417,7 +8528,7 @@
       <c r="AZ128"/>
     </row>
     <row r="129" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD129" s="173"/>
+      <c r="AD129" s="167"/>
       <c r="AU129"/>
       <c r="AV129"/>
       <c r="AW129"/>
@@ -8426,7 +8537,7 @@
       <c r="AZ129"/>
     </row>
     <row r="130" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD130" s="173"/>
+      <c r="AD130" s="167"/>
       <c r="AU130"/>
       <c r="AV130"/>
       <c r="AW130"/>
@@ -8435,7 +8546,7 @@
       <c r="AZ130"/>
     </row>
     <row r="131" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD131" s="173"/>
+      <c r="AD131" s="167"/>
       <c r="AU131"/>
       <c r="AV131"/>
       <c r="AW131"/>
@@ -8444,7 +8555,7 @@
       <c r="AZ131"/>
     </row>
     <row r="132" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD132" s="173"/>
+      <c r="AD132" s="167"/>
       <c r="AU132"/>
       <c r="AV132"/>
       <c r="AW132"/>
@@ -8453,7 +8564,7 @@
       <c r="AZ132"/>
     </row>
     <row r="133" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD133" s="173"/>
+      <c r="AD133" s="167"/>
       <c r="AU133"/>
       <c r="AV133"/>
       <c r="AW133"/>
@@ -8462,7 +8573,7 @@
       <c r="AZ133"/>
     </row>
     <row r="134" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD134" s="173"/>
+      <c r="AD134" s="167"/>
       <c r="AU134"/>
       <c r="AV134"/>
       <c r="AW134"/>
@@ -8471,7 +8582,7 @@
       <c r="AZ134"/>
     </row>
     <row r="135" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD135" s="173"/>
+      <c r="AD135" s="167"/>
       <c r="AU135"/>
       <c r="AV135"/>
       <c r="AW135"/>
@@ -8480,7 +8591,7 @@
       <c r="AZ135"/>
     </row>
     <row r="136" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD136" s="173"/>
+      <c r="AD136" s="167"/>
       <c r="AU136"/>
       <c r="AV136"/>
       <c r="AW136"/>
@@ -8489,7 +8600,7 @@
       <c r="AZ136"/>
     </row>
     <row r="137" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD137" s="173"/>
+      <c r="AD137" s="167"/>
       <c r="AU137"/>
       <c r="AV137"/>
       <c r="AW137"/>
@@ -8498,7 +8609,7 @@
       <c r="AZ137"/>
     </row>
     <row r="138" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD138" s="173"/>
+      <c r="AD138" s="167"/>
       <c r="AU138"/>
       <c r="AV138"/>
       <c r="AW138"/>
@@ -8507,7 +8618,7 @@
       <c r="AZ138"/>
     </row>
     <row r="139" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD139" s="173"/>
+      <c r="AD139" s="167"/>
       <c r="AU139"/>
       <c r="AV139"/>
       <c r="AW139"/>
@@ -8516,7 +8627,7 @@
       <c r="AZ139"/>
     </row>
     <row r="140" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD140" s="173"/>
+      <c r="AD140" s="167"/>
       <c r="AU140"/>
       <c r="AV140"/>
       <c r="AW140"/>
@@ -8525,7 +8636,7 @@
       <c r="AZ140"/>
     </row>
     <row r="141" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD141" s="173"/>
+      <c r="AD141" s="167"/>
       <c r="AU141"/>
       <c r="AV141"/>
       <c r="AW141"/>
@@ -8534,7 +8645,7 @@
       <c r="AZ141"/>
     </row>
     <row r="142" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD142" s="173"/>
+      <c r="AD142" s="167"/>
       <c r="AU142"/>
       <c r="AV142"/>
       <c r="AW142"/>
@@ -8543,7 +8654,7 @@
       <c r="AZ142"/>
     </row>
     <row r="143" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD143" s="173"/>
+      <c r="AD143" s="167"/>
       <c r="AU143"/>
       <c r="AV143"/>
       <c r="AW143"/>
@@ -8552,7 +8663,7 @@
       <c r="AZ143"/>
     </row>
     <row r="144" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD144" s="173"/>
+      <c r="AD144" s="167"/>
       <c r="AU144"/>
       <c r="AV144"/>
       <c r="AW144"/>
@@ -8561,7 +8672,7 @@
       <c r="AZ144"/>
     </row>
     <row r="145" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD145" s="173"/>
+      <c r="AD145" s="167"/>
       <c r="AU145"/>
       <c r="AV145"/>
       <c r="AW145"/>
@@ -8570,7 +8681,7 @@
       <c r="AZ145"/>
     </row>
     <row r="146" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD146" s="173"/>
+      <c r="AD146" s="167"/>
       <c r="AU146"/>
       <c r="AV146"/>
       <c r="AW146"/>
@@ -8579,7 +8690,7 @@
       <c r="AZ146"/>
     </row>
     <row r="147" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD147" s="173"/>
+      <c r="AD147" s="167"/>
       <c r="AU147"/>
       <c r="AV147"/>
       <c r="AW147"/>
@@ -8588,7 +8699,7 @@
       <c r="AZ147"/>
     </row>
     <row r="148" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD148" s="173"/>
+      <c r="AD148" s="167"/>
       <c r="AU148"/>
       <c r="AV148"/>
       <c r="AW148"/>
@@ -8597,7 +8708,7 @@
       <c r="AZ148"/>
     </row>
     <row r="149" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD149" s="173"/>
+      <c r="AD149" s="167"/>
       <c r="AU149"/>
       <c r="AV149"/>
       <c r="AW149"/>
@@ -8606,7 +8717,7 @@
       <c r="AZ149"/>
     </row>
     <row r="150" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD150" s="173"/>
+      <c r="AD150" s="167"/>
       <c r="AU150"/>
       <c r="AV150"/>
       <c r="AW150"/>
@@ -8615,7 +8726,7 @@
       <c r="AZ150"/>
     </row>
     <row r="151" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD151" s="173"/>
+      <c r="AD151" s="167"/>
       <c r="AU151"/>
       <c r="AV151"/>
       <c r="AW151"/>
@@ -8624,7 +8735,7 @@
       <c r="AZ151"/>
     </row>
     <row r="152" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD152" s="173"/>
+      <c r="AD152" s="167"/>
       <c r="AU152"/>
       <c r="AV152"/>
       <c r="AW152"/>
@@ -8633,7 +8744,7 @@
       <c r="AZ152"/>
     </row>
     <row r="153" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD153" s="173"/>
+      <c r="AD153" s="167"/>
       <c r="AU153"/>
       <c r="AV153"/>
       <c r="AW153"/>
@@ -8642,7 +8753,7 @@
       <c r="AZ153"/>
     </row>
     <row r="154" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD154" s="173"/>
+      <c r="AD154" s="167"/>
       <c r="AU154"/>
       <c r="AV154"/>
       <c r="AW154"/>
@@ -8651,7 +8762,7 @@
       <c r="AZ154"/>
     </row>
     <row r="155" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD155" s="173"/>
+      <c r="AD155" s="167"/>
       <c r="AU155"/>
       <c r="AV155"/>
       <c r="AW155"/>
@@ -8660,7 +8771,7 @@
       <c r="AZ155"/>
     </row>
     <row r="156" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD156" s="173"/>
+      <c r="AD156" s="167"/>
       <c r="AU156"/>
       <c r="AV156"/>
       <c r="AW156"/>
@@ -8669,7 +8780,7 @@
       <c r="AZ156"/>
     </row>
     <row r="157" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD157" s="173"/>
+      <c r="AD157" s="167"/>
       <c r="AU157"/>
       <c r="AV157"/>
       <c r="AW157"/>
@@ -8678,7 +8789,7 @@
       <c r="AZ157"/>
     </row>
     <row r="158" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD158" s="173"/>
+      <c r="AD158" s="167"/>
       <c r="AU158"/>
       <c r="AV158"/>
       <c r="AW158"/>
@@ -8687,7 +8798,7 @@
       <c r="AZ158"/>
     </row>
     <row r="159" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD159" s="173"/>
+      <c r="AD159" s="167"/>
       <c r="AU159"/>
       <c r="AV159"/>
       <c r="AW159"/>
@@ -8696,7 +8807,7 @@
       <c r="AZ159"/>
     </row>
     <row r="160" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD160" s="173"/>
+      <c r="AD160" s="167"/>
       <c r="AU160"/>
       <c r="AV160"/>
       <c r="AW160"/>
@@ -8705,7 +8816,7 @@
       <c r="AZ160"/>
     </row>
     <row r="161" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD161" s="173"/>
+      <c r="AD161" s="167"/>
       <c r="AU161"/>
       <c r="AV161"/>
       <c r="AW161"/>
@@ -8714,7 +8825,7 @@
       <c r="AZ161"/>
     </row>
     <row r="162" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD162" s="173"/>
+      <c r="AD162" s="167"/>
       <c r="AU162"/>
       <c r="AV162"/>
       <c r="AW162"/>
@@ -8723,7 +8834,7 @@
       <c r="AZ162"/>
     </row>
     <row r="163" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD163" s="173"/>
+      <c r="AD163" s="167"/>
       <c r="AU163"/>
       <c r="AV163"/>
       <c r="AW163"/>
@@ -8732,7 +8843,7 @@
       <c r="AZ163"/>
     </row>
     <row r="164" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD164" s="173"/>
+      <c r="AD164" s="167"/>
       <c r="AU164"/>
       <c r="AV164"/>
       <c r="AW164"/>
@@ -8741,7 +8852,7 @@
       <c r="AZ164"/>
     </row>
     <row r="165" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD165" s="173"/>
+      <c r="AD165" s="167"/>
       <c r="AU165"/>
       <c r="AV165"/>
       <c r="AW165"/>
@@ -8750,7 +8861,7 @@
       <c r="AZ165"/>
     </row>
     <row r="166" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD166" s="173"/>
+      <c r="AD166" s="167"/>
       <c r="AU166"/>
       <c r="AV166"/>
       <c r="AW166"/>
@@ -8759,7 +8870,7 @@
       <c r="AZ166"/>
     </row>
     <row r="167" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD167" s="173"/>
+      <c r="AD167" s="167"/>
       <c r="AU167"/>
       <c r="AV167"/>
       <c r="AW167"/>
@@ -8768,7 +8879,7 @@
       <c r="AZ167"/>
     </row>
     <row r="168" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD168" s="173"/>
+      <c r="AD168" s="167"/>
       <c r="AU168"/>
       <c r="AV168"/>
       <c r="AW168"/>
@@ -8777,7 +8888,7 @@
       <c r="AZ168"/>
     </row>
     <row r="169" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD169" s="173"/>
+      <c r="AD169" s="167"/>
       <c r="AU169"/>
       <c r="AV169"/>
       <c r="AW169"/>
@@ -8786,7 +8897,7 @@
       <c r="AZ169"/>
     </row>
     <row r="170" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD170" s="173"/>
+      <c r="AD170" s="167"/>
       <c r="AU170"/>
       <c r="AV170"/>
       <c r="AW170"/>
@@ -8795,7 +8906,7 @@
       <c r="AZ170"/>
     </row>
     <row r="171" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD171" s="173"/>
+      <c r="AD171" s="167"/>
       <c r="AU171"/>
       <c r="AV171"/>
       <c r="AW171"/>
@@ -8804,7 +8915,7 @@
       <c r="AZ171"/>
     </row>
     <row r="172" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD172" s="173"/>
+      <c r="AD172" s="167"/>
       <c r="AU172"/>
       <c r="AV172"/>
       <c r="AW172"/>
@@ -8813,7 +8924,7 @@
       <c r="AZ172"/>
     </row>
     <row r="173" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD173" s="173"/>
+      <c r="AD173" s="167"/>
       <c r="AU173"/>
       <c r="AV173"/>
       <c r="AW173"/>
@@ -8822,7 +8933,7 @@
       <c r="AZ173"/>
     </row>
     <row r="174" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD174" s="173"/>
+      <c r="AD174" s="167"/>
       <c r="AU174"/>
       <c r="AV174"/>
       <c r="AW174"/>
@@ -8831,7 +8942,7 @@
       <c r="AZ174"/>
     </row>
     <row r="175" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD175" s="173"/>
+      <c r="AD175" s="167"/>
       <c r="AU175"/>
       <c r="AV175"/>
       <c r="AW175"/>
@@ -8840,7 +8951,7 @@
       <c r="AZ175"/>
     </row>
     <row r="176" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD176" s="173"/>
+      <c r="AD176" s="167"/>
       <c r="AU176"/>
       <c r="AV176"/>
       <c r="AW176"/>
@@ -8849,7 +8960,7 @@
       <c r="AZ176"/>
     </row>
     <row r="177" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD177" s="173"/>
+      <c r="AD177" s="167"/>
       <c r="AU177"/>
       <c r="AV177"/>
       <c r="AW177"/>
@@ -8858,7 +8969,7 @@
       <c r="AZ177"/>
     </row>
     <row r="178" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD178" s="173"/>
+      <c r="AD178" s="167"/>
       <c r="AU178"/>
       <c r="AV178"/>
       <c r="AW178"/>
@@ -8867,7 +8978,7 @@
       <c r="AZ178"/>
     </row>
     <row r="179" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD179" s="173"/>
+      <c r="AD179" s="167"/>
       <c r="AU179"/>
       <c r="AV179"/>
       <c r="AW179"/>
@@ -8876,7 +8987,7 @@
       <c r="AZ179"/>
     </row>
     <row r="180" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD180" s="173"/>
+      <c r="AD180" s="167"/>
       <c r="AU180"/>
       <c r="AV180"/>
       <c r="AW180"/>
@@ -8885,7 +8996,7 @@
       <c r="AZ180"/>
     </row>
     <row r="181" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD181" s="173"/>
+      <c r="AD181" s="167"/>
       <c r="AU181"/>
       <c r="AV181"/>
       <c r="AW181"/>
@@ -8894,7 +9005,7 @@
       <c r="AZ181"/>
     </row>
     <row r="182" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD182" s="173"/>
+      <c r="AD182" s="167"/>
       <c r="AU182"/>
       <c r="AV182"/>
       <c r="AW182"/>
@@ -8903,7 +9014,7 @@
       <c r="AZ182"/>
     </row>
     <row r="183" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD183" s="173"/>
+      <c r="AD183" s="167"/>
       <c r="AU183"/>
       <c r="AV183"/>
       <c r="AW183"/>
@@ -8912,7 +9023,7 @@
       <c r="AZ183"/>
     </row>
     <row r="184" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD184" s="173"/>
+      <c r="AD184" s="167"/>
       <c r="AU184"/>
       <c r="AV184"/>
       <c r="AW184"/>
@@ -8921,7 +9032,7 @@
       <c r="AZ184"/>
     </row>
     <row r="185" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD185" s="173"/>
+      <c r="AD185" s="167"/>
       <c r="AU185"/>
       <c r="AV185"/>
       <c r="AW185"/>
@@ -8930,7 +9041,7 @@
       <c r="AZ185"/>
     </row>
     <row r="186" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD186" s="173"/>
+      <c r="AD186" s="167"/>
       <c r="AU186"/>
       <c r="AV186"/>
       <c r="AW186"/>
@@ -8939,7 +9050,7 @@
       <c r="AZ186"/>
     </row>
     <row r="187" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD187" s="173"/>
+      <c r="AD187" s="167"/>
       <c r="AU187"/>
       <c r="AV187"/>
       <c r="AW187"/>
@@ -8948,7 +9059,7 @@
       <c r="AZ187"/>
     </row>
     <row r="188" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD188" s="173"/>
+      <c r="AD188" s="167"/>
       <c r="AU188"/>
       <c r="AV188"/>
       <c r="AW188"/>
@@ -8957,7 +9068,7 @@
       <c r="AZ188"/>
     </row>
     <row r="189" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD189" s="173"/>
+      <c r="AD189" s="167"/>
       <c r="AU189"/>
       <c r="AV189"/>
       <c r="AW189"/>
@@ -8966,7 +9077,7 @@
       <c r="AZ189"/>
     </row>
     <row r="190" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD190" s="173"/>
+      <c r="AD190" s="167"/>
       <c r="AU190"/>
       <c r="AV190"/>
       <c r="AW190"/>
@@ -8975,7 +9086,7 @@
       <c r="AZ190"/>
     </row>
     <row r="191" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD191" s="173"/>
+      <c r="AD191" s="167"/>
       <c r="AU191"/>
       <c r="AV191"/>
       <c r="AW191"/>
@@ -8984,7 +9095,7 @@
       <c r="AZ191"/>
     </row>
     <row r="192" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD192" s="173"/>
+      <c r="AD192" s="167"/>
       <c r="AU192"/>
       <c r="AV192"/>
       <c r="AW192"/>
@@ -8993,7 +9104,7 @@
       <c r="AZ192"/>
     </row>
     <row r="193" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD193" s="173"/>
+      <c r="AD193" s="167"/>
       <c r="AU193"/>
       <c r="AV193"/>
       <c r="AW193"/>
@@ -9002,7 +9113,7 @@
       <c r="AZ193"/>
     </row>
     <row r="194" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD194" s="173"/>
+      <c r="AD194" s="167"/>
       <c r="AU194"/>
       <c r="AV194"/>
       <c r="AW194"/>
@@ -9011,7 +9122,7 @@
       <c r="AZ194"/>
     </row>
     <row r="195" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD195" s="173"/>
+      <c r="AD195" s="167"/>
       <c r="AU195"/>
       <c r="AV195"/>
       <c r="AW195"/>
@@ -9020,7 +9131,7 @@
       <c r="AZ195"/>
     </row>
     <row r="196" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD196" s="173"/>
+      <c r="AD196" s="167"/>
       <c r="AU196"/>
       <c r="AV196"/>
       <c r="AW196"/>
@@ -9029,7 +9140,7 @@
       <c r="AZ196"/>
     </row>
     <row r="197" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD197" s="173"/>
+      <c r="AD197" s="167"/>
       <c r="AU197"/>
       <c r="AV197"/>
       <c r="AW197"/>
@@ -9038,7 +9149,7 @@
       <c r="AZ197"/>
     </row>
     <row r="198" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD198" s="173"/>
+      <c r="AD198" s="167"/>
       <c r="AU198"/>
       <c r="AV198"/>
       <c r="AW198"/>
@@ -9047,7 +9158,7 @@
       <c r="AZ198"/>
     </row>
     <row r="199" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD199" s="173"/>
+      <c r="AD199" s="167"/>
       <c r="AU199"/>
       <c r="AV199"/>
       <c r="AW199"/>
@@ -9056,7 +9167,7 @@
       <c r="AZ199"/>
     </row>
     <row r="200" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD200" s="173"/>
+      <c r="AD200" s="167"/>
       <c r="AU200"/>
       <c r="AV200"/>
       <c r="AW200"/>
@@ -11641,24 +11752,23 @@
       <c r="AZ522"/>
     </row>
   </sheetData>
-  <sortState ref="B9:AC10">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:AC10">
     <sortCondition ref="B9"/>
   </sortState>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="P4:U4"/>
-    <mergeCell ref="AD1:AD200"/>
   </mergeCells>
   <conditionalFormatting sqref="I40">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$D$43:$D$44</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$C$43:$C$44</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeck\kp_generator\templates_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\kp_generator\templates_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205E0639-8186-4F44-8352-437FC2ED41AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="294" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="294"/>
   </bookViews>
   <sheets>
     <sheet name="расчет" sheetId="4" r:id="rId1"/>
@@ -19,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$36</definedName>
     <definedName name="Длина_сделки">расчет!$K$15</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullPrecision="0"/>
+  <calcPr calcId="162913" fullPrecision="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -318,31 +317,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="23">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-415]General"/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="[$$-409]#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* &quot;-&quot;??[$€-1]_-"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0_ "/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="[$¥-478]#,##0.00"/>
-    <numFmt numFmtId="176" formatCode="_ [$¥-478]* #,##0_ ;_ [$¥-478]* \-#,##0_ ;_ [$¥-478]* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="[$¥-478]#,##0"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="179" formatCode="[$¥-804]#,##0.00"/>
-    <numFmt numFmtId="180" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
-    <numFmt numFmtId="181" formatCode="[$¥-478]#,##0.0"/>
-    <numFmt numFmtId="182" formatCode="#,##0.00\ &quot;₽&quot;;[Red]#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="183" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
-    <numFmt numFmtId="184" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="185" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="[$-415]General"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="[$$-409]#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* &quot;-&quot;??[$€-1]_-"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="[$¥-478]#,##0.00"/>
+    <numFmt numFmtId="175" formatCode="_ [$¥-478]* #,##0_ ;_ [$¥-478]* \-#,##0_ ;_ [$¥-478]* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$¥-478]#,##0"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="178" formatCode="[$¥-804]#,##0.00"/>
+    <numFmt numFmtId="179" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="[$¥-478]#,##0.0"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00\ &quot;₽&quot;;[Red]#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="182" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
+    <numFmt numFmtId="183" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="184" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -905,24 +904,24 @@
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3">
@@ -940,17 +939,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -961,10 +960,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -976,23 +975,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1010,7 +1009,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1117,21 +1116,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1157,7 +1156,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1172,7 +1171,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -1198,23 +1197,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
@@ -1228,7 +1227,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -1236,12 +1235,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
@@ -1257,7 +1256,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1268,49 +1267,49 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1456,11 +1455,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1468,22 +1467,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="3"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -1506,17 +1505,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1551,201 +1550,201 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3"/>
@@ -1753,12 +1752,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1785,77 +1784,77 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1890,69 +1889,69 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -1962,13 +1961,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -1986,7 +1985,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
@@ -2003,7 +2002,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2020,7 +2019,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2065,7 +2064,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
@@ -2076,119 +2075,119 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3"/>
@@ -2349,15 +2348,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
@@ -2491,7 +2490,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
@@ -2506,7 +2505,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2536,7 +2535,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2593,39 +2592,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2651,11 +2650,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3"/>
@@ -2684,407 +2683,407 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3">
@@ -3105,7 +3104,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="3">
@@ -3245,7 +3244,7 @@
     <xf numFmtId="0" fontId="32" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3267,10 +3266,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="180" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3279,34 +3278,34 @@
     <xf numFmtId="0" fontId="38" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="38" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="38" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="3" borderId="14" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="3" borderId="14" xfId="1624" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3319,10 +3318,10 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="32" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3331,28 +3330,28 @@
     <xf numFmtId="3" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="39" fillId="0" borderId="13" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="39" fillId="0" borderId="13" xfId="1509" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="39" fillId="0" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="39" fillId="0" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="32" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="32" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="14" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3372,13 +3371,13 @@
     <xf numFmtId="1" fontId="32" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="38" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="32" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="39" fillId="0" borderId="10" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="10" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="32" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3387,31 +3386,31 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="32" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="3" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="32" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3552,7 +3551,7 @@
     <xf numFmtId="1" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3571,19 +3570,19 @@
     <xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="37" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="37" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="37" fillId="4" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3596,7 +3595,7 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -3630,1668 +3629,1668 @@
     </xf>
   </cellXfs>
   <cellStyles count="1662">
-    <cellStyle name="Excel Built-in Normal" xfId="78" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Excel Built-in Normal 2" xfId="95" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Excel Built-in Normal 2 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Excel Built-in Normal 3" xfId="96" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Excel Built-in Normal 4" xfId="97" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Excel Built-in Normal 4 2" xfId="81" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Excel Built-in Normal 5" xfId="76" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Excel Built-in Normal 5 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Гиперссылка 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Гиперссылка 2 10" xfId="94" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Гиперссылка 2 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2" xfId="99" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2" xfId="84" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2" xfId="104" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 4" xfId="108" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 2 5" xfId="113" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 3" xfId="114" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 5" xfId="118" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 2 6" xfId="120" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3" xfId="121" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 2" xfId="122" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 3" xfId="123" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 4" xfId="125" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 3 5" xfId="127" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 4" xfId="128" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 5" xfId="130" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 6" xfId="132" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="Гиперссылка 2 2 2 7" xfId="134" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3" xfId="136" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2" xfId="138" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 2" xfId="143" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 3" xfId="145" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 4" xfId="147" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 2 5" xfId="149" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 3" xfId="151" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 4" xfId="158" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 5" xfId="163" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="Гиперссылка 2 2 3 6" xfId="166" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4" xfId="168" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 2" xfId="172" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 3" xfId="176" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 4" xfId="177" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="Гиперссылка 2 2 4 5" xfId="178" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="Гиперссылка 2 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="Гиперссылка 2 2 6" xfId="183" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="Гиперссылка 2 2 7" xfId="185" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="Гиперссылка 2 2 8" xfId="186" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Гиперссылка 2 3" xfId="189" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2" xfId="190" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2" xfId="193" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 3" xfId="196" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 4" xfId="199" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 2 5" xfId="201" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 3" xfId="203" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 4" xfId="205" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 5" xfId="206" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="Гиперссылка 2 3 2 6" xfId="207" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3" xfId="209" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 2" xfId="210" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 3" xfId="211" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 4" xfId="213" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="Гиперссылка 2 3 3 5" xfId="215" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="Гиперссылка 2 3 4" xfId="217" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="Гиперссылка 2 3 5" xfId="52" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="Гиперссылка 2 3 6" xfId="219" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="Гиперссылка 2 3 7" xfId="220" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="Гиперссылка 2 4" xfId="222" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2" xfId="224" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 3" xfId="226" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 4" xfId="228" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="Гиперссылка 2 4 2 5" xfId="231" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Гиперссылка 2 4 3" xfId="54" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Гиперссылка 2 4 4" xfId="232" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="Гиперссылка 2 4 5" xfId="233" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="Гиперссылка 2 4 6" xfId="235" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="Гиперссылка 2 5" xfId="237" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2" xfId="242" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 2" xfId="244" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 3" xfId="246" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 4" xfId="248" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="Гиперссылка 2 5 2 5" xfId="250" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="Гиперссылка 2 5 3" xfId="252" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="Гиперссылка 2 5 4" xfId="254" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="Гиперссылка 2 5 5" xfId="256" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="Гиперссылка 2 5 6" xfId="259" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="Гиперссылка 2 6" xfId="261" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="Гиперссылка 2 6 2" xfId="264" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="Гиперссылка 2 6 3" xfId="266" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="Гиперссылка 2 6 4" xfId="268" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="Гиперссылка 2 6 5" xfId="270" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="Гиперссылка 2 7" xfId="273" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="Гиперссылка 2 8" xfId="275" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="Гиперссылка 2 9" xfId="277" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="78"/>
+    <cellStyle name="Excel Built-in Normal 2" xfId="95"/>
+    <cellStyle name="Excel Built-in Normal 2 2" xfId="89"/>
+    <cellStyle name="Excel Built-in Normal 3" xfId="96"/>
+    <cellStyle name="Excel Built-in Normal 4" xfId="97"/>
+    <cellStyle name="Excel Built-in Normal 4 2" xfId="81"/>
+    <cellStyle name="Excel Built-in Normal 5" xfId="76"/>
+    <cellStyle name="Excel Built-in Normal 5 2" xfId="77"/>
+    <cellStyle name="Гиперссылка 2" xfId="48"/>
+    <cellStyle name="Гиперссылка 2 10" xfId="94"/>
+    <cellStyle name="Гиперссылка 2 2" xfId="98"/>
+    <cellStyle name="Гиперссылка 2 2 2" xfId="99"/>
+    <cellStyle name="Гиперссылка 2 2 2 2" xfId="84"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2" xfId="104"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 2" xfId="83"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 3" xfId="88"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 4" xfId="108"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 2 5" xfId="113"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 3" xfId="114"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 4" xfId="116"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 5" xfId="118"/>
+    <cellStyle name="Гиперссылка 2 2 2 2 6" xfId="120"/>
+    <cellStyle name="Гиперссылка 2 2 2 3" xfId="121"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 2" xfId="122"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 3" xfId="123"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 4" xfId="125"/>
+    <cellStyle name="Гиперссылка 2 2 2 3 5" xfId="127"/>
+    <cellStyle name="Гиперссылка 2 2 2 4" xfId="128"/>
+    <cellStyle name="Гиперссылка 2 2 2 5" xfId="130"/>
+    <cellStyle name="Гиперссылка 2 2 2 6" xfId="132"/>
+    <cellStyle name="Гиперссылка 2 2 2 7" xfId="134"/>
+    <cellStyle name="Гиперссылка 2 2 3" xfId="136"/>
+    <cellStyle name="Гиперссылка 2 2 3 2" xfId="138"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 2" xfId="143"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 3" xfId="145"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 4" xfId="147"/>
+    <cellStyle name="Гиперссылка 2 2 3 2 5" xfId="149"/>
+    <cellStyle name="Гиперссылка 2 2 3 3" xfId="151"/>
+    <cellStyle name="Гиперссылка 2 2 3 4" xfId="158"/>
+    <cellStyle name="Гиперссылка 2 2 3 5" xfId="163"/>
+    <cellStyle name="Гиперссылка 2 2 3 6" xfId="166"/>
+    <cellStyle name="Гиперссылка 2 2 4" xfId="168"/>
+    <cellStyle name="Гиперссылка 2 2 4 2" xfId="172"/>
+    <cellStyle name="Гиперссылка 2 2 4 3" xfId="176"/>
+    <cellStyle name="Гиперссылка 2 2 4 4" xfId="177"/>
+    <cellStyle name="Гиперссылка 2 2 4 5" xfId="178"/>
+    <cellStyle name="Гиперссылка 2 2 5" xfId="180"/>
+    <cellStyle name="Гиперссылка 2 2 6" xfId="183"/>
+    <cellStyle name="Гиперссылка 2 2 7" xfId="185"/>
+    <cellStyle name="Гиперссылка 2 2 8" xfId="186"/>
+    <cellStyle name="Гиперссылка 2 3" xfId="189"/>
+    <cellStyle name="Гиперссылка 2 3 2" xfId="190"/>
+    <cellStyle name="Гиперссылка 2 3 2 2" xfId="193"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 2" xfId="36"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 3" xfId="196"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 4" xfId="199"/>
+    <cellStyle name="Гиперссылка 2 3 2 2 5" xfId="201"/>
+    <cellStyle name="Гиперссылка 2 3 2 3" xfId="203"/>
+    <cellStyle name="Гиперссылка 2 3 2 4" xfId="205"/>
+    <cellStyle name="Гиперссылка 2 3 2 5" xfId="206"/>
+    <cellStyle name="Гиперссылка 2 3 2 6" xfId="207"/>
+    <cellStyle name="Гиперссылка 2 3 3" xfId="209"/>
+    <cellStyle name="Гиперссылка 2 3 3 2" xfId="210"/>
+    <cellStyle name="Гиперссылка 2 3 3 3" xfId="211"/>
+    <cellStyle name="Гиперссылка 2 3 3 4" xfId="213"/>
+    <cellStyle name="Гиперссылка 2 3 3 5" xfId="215"/>
+    <cellStyle name="Гиперссылка 2 3 4" xfId="217"/>
+    <cellStyle name="Гиперссылка 2 3 5" xfId="52"/>
+    <cellStyle name="Гиперссылка 2 3 6" xfId="219"/>
+    <cellStyle name="Гиперссылка 2 3 7" xfId="220"/>
+    <cellStyle name="Гиперссылка 2 4" xfId="222"/>
+    <cellStyle name="Гиперссылка 2 4 2" xfId="224"/>
+    <cellStyle name="Гиперссылка 2 4 2 2" xfId="38"/>
+    <cellStyle name="Гиперссылка 2 4 2 3" xfId="226"/>
+    <cellStyle name="Гиперссылка 2 4 2 4" xfId="228"/>
+    <cellStyle name="Гиперссылка 2 4 2 5" xfId="231"/>
+    <cellStyle name="Гиперссылка 2 4 3" xfId="54"/>
+    <cellStyle name="Гиперссылка 2 4 4" xfId="232"/>
+    <cellStyle name="Гиперссылка 2 4 5" xfId="233"/>
+    <cellStyle name="Гиперссылка 2 4 6" xfId="235"/>
+    <cellStyle name="Гиперссылка 2 5" xfId="237"/>
+    <cellStyle name="Гиперссылка 2 5 2" xfId="242"/>
+    <cellStyle name="Гиперссылка 2 5 2 2" xfId="244"/>
+    <cellStyle name="Гиперссылка 2 5 2 3" xfId="246"/>
+    <cellStyle name="Гиперссылка 2 5 2 4" xfId="248"/>
+    <cellStyle name="Гиперссылка 2 5 2 5" xfId="250"/>
+    <cellStyle name="Гиперссылка 2 5 3" xfId="252"/>
+    <cellStyle name="Гиперссылка 2 5 4" xfId="254"/>
+    <cellStyle name="Гиперссылка 2 5 5" xfId="256"/>
+    <cellStyle name="Гиперссылка 2 5 6" xfId="259"/>
+    <cellStyle name="Гиперссылка 2 6" xfId="261"/>
+    <cellStyle name="Гиперссылка 2 6 2" xfId="264"/>
+    <cellStyle name="Гиперссылка 2 6 3" xfId="266"/>
+    <cellStyle name="Гиперссылка 2 6 4" xfId="268"/>
+    <cellStyle name="Гиперссылка 2 6 5" xfId="270"/>
+    <cellStyle name="Гиперссылка 2 7" xfId="273"/>
+    <cellStyle name="Гиперссылка 2 8" xfId="275"/>
+    <cellStyle name="Гиперссылка 2 9" xfId="277"/>
     <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Денежный 2" xfId="112" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="Денежный 2 2" xfId="278" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="Денежный 2 2 2" xfId="157" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Денежный 2" xfId="112"/>
+    <cellStyle name="Денежный 2 2" xfId="278"/>
+    <cellStyle name="Денежный 2 2 2" xfId="157"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="279" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="Обычный 10 2" xfId="281" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="Обычный 11" xfId="282" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="Обычный 11 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="Обычный 12" xfId="287" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="Обычный 12 2" xfId="291" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="Обычный 13" xfId="293" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="Обычный 13 2" xfId="69" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="Обычный 14" xfId="295" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="Обычный 14 2" xfId="131" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="Обычный 15" xfId="298" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="Обычный 15 2" xfId="165" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="Обычный 16" xfId="301" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="Обычный 16 2" xfId="302" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="Обычный 17" xfId="303" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="Обычный 17 2" xfId="305" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="Обычный 18" xfId="306" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="Обычный 18 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="Обычный 19" xfId="19" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="Обычный 2" xfId="4" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="Обычный 2 10" xfId="310" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="Обычный 2 10 2" xfId="182" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="Обычный 2 11" xfId="311" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="Обычный 2 12" xfId="37" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="Обычный 2 12 2" xfId="234" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="Обычный 2 12 3" xfId="312" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="Обычный 2 13" xfId="225" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="Обычный 2 13 2" xfId="258" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="Обычный 2 14" xfId="227" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="Обычный 2 14 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="Обычный 2 15" xfId="229" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="Обычный 2 15 2" xfId="317" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="Обычный 2 16" xfId="319" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="Обычный 2 16 2" xfId="322" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="Обычный 2 17" xfId="325" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="Обычный 2 17 2" xfId="329" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="Обычный 2 18" xfId="333" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="Обычный 2 18 2" xfId="57" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="Обычный 2 19" xfId="338" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="Обычный 2 19 2" xfId="342" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="Обычный 2 19 3" xfId="346" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="Обычный 2 2" xfId="348" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="Обычный 2 2 10" xfId="353" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="Обычный 2 2 10 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="Обычный 2 2 10 3" xfId="359" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="Обычный 2 2 10 4" xfId="362" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="Обычный 2 2 11" xfId="93" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="Обычный 2 2 2" xfId="365" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="Обычный 2 2 2 2" xfId="366" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2" xfId="367" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2" xfId="369" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 2" xfId="292" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 3" xfId="294" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 4" xfId="297" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 2 5" xfId="300" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 3" xfId="371" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 4" xfId="372" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 5" xfId="373" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 2 6" xfId="374" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3" xfId="75" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 2" xfId="376" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 3" xfId="191" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 4" xfId="202" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 3 5" xfId="204" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 4" xfId="377" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 5" xfId="378" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 6" xfId="379" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 2 7" xfId="380" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3" xfId="82" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2" xfId="42" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 2" xfId="381" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 3" xfId="382" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 4" xfId="383" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 2 5" xfId="384" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 3" xfId="385" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 4" xfId="386" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 5" xfId="387" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 3 6" xfId="388" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4" xfId="87" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 2" xfId="390" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 3" xfId="392" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 4" xfId="394" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 4 5" xfId="102" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 5" xfId="107" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 6" xfId="111" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 7" xfId="398" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="Обычный 2 2 2 2 8" xfId="402" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="Обычный 2 2 2 3" xfId="403" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="Обычный 2 2 2 3 2" xfId="404" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="Обычный 2 2 3" xfId="407" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="Обычный 2 2 3 2" xfId="408" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="Обычный 2 2 4" xfId="241" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="Обычный 2 2 4 2" xfId="243" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2" xfId="409" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 2" xfId="137" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 3" xfId="150" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 4" xfId="154" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 2 5" xfId="162" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 3" xfId="167" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 4" xfId="179" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 2 6" xfId="184" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3" xfId="410" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 2" xfId="208" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 3" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 4" xfId="51" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 3 5" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 4" xfId="412" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 5" xfId="308" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 6" xfId="414" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="Обычный 2 2 4 2 7" xfId="352" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="Обычный 2 2 4 3" xfId="245" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2" xfId="415" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 4" xfId="423" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 2 5" xfId="425" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 3" xfId="426" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 4" xfId="427" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 5" xfId="60" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="Обычный 2 2 4 3 6" xfId="49" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="Обычный 2 2 4 4" xfId="247" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 3" xfId="431" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 4" xfId="434" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="Обычный 2 2 4 4 5" xfId="437" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="Обычный 2 2 4 5" xfId="249" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="Обычный 2 2 4 6" xfId="438" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="Обычный 2 2 4 7" xfId="223" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="Обычный 2 2 4 8" xfId="53" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="Обычный 2 2 5" xfId="251" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="Обычный 2 2 5 2" xfId="440" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2" xfId="442" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 2" xfId="444" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 3" xfId="446" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 2 5" xfId="174" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 3" xfId="448" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 4" xfId="450" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 5" xfId="452" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="Обычный 2 2 5 2 6" xfId="454" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="Обычный 2 2 5 3" xfId="456" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 2" xfId="458" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 3" xfId="460" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 4" xfId="461" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
-    <cellStyle name="Обычный 2 2 5 3 5" xfId="462" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="Обычный 2 2 5 4" xfId="464" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="Обычный 2 2 5 5" xfId="364" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="Обычный 2 2 5 6" xfId="406" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="Обычный 2 2 5 7" xfId="240" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="Обычный 2 2 6" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="Обычный 2 2 6 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 2" xfId="389" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 3" xfId="391" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 4" xfId="393" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="Обычный 2 2 6 2 5" xfId="100" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="Обычный 2 2 6 3" xfId="106" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="Обычный 2 2 6 4" xfId="110" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="Обычный 2 2 6 5" xfId="396" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="Обычный 2 2 6 6" xfId="400" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="Обычный 2 2 7" xfId="255" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="Обычный 2 2 7 2" xfId="465" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 2" xfId="468" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 3" xfId="285" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 4" xfId="473" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="Обычный 2 2 7 2 5" xfId="141" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="Обычный 2 2 7 3" xfId="474" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="Обычный 2 2 7 4" xfId="280" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="Обычный 2 2 7 5" xfId="476" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="Обычный 2 2 7 6" xfId="478" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="Обычный 2 2 8" xfId="257" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="Обычный 2 2 8 2" xfId="479" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 2" xfId="482" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 3" xfId="485" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 4" xfId="488" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="Обычный 2 2 8 2 5" xfId="491" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="Обычный 2 2 8 3" xfId="466" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="Обычный 2 2 8 4" xfId="283" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="Обычный 2 2 8 5" xfId="469" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="Обычный 2 2 8 6" xfId="140" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="Обычный 2 2 9" xfId="492" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="Обычный 2 2 9 2" xfId="493" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="Обычный 2 2 9 3" xfId="79" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="Обычный 2 2 9 4" xfId="288" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="Обычный 2 2 9 5" xfId="496" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="Обычный 2 20" xfId="230" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="Обычный 2 20 2" xfId="318" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="Обычный 2 21" xfId="320" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="Обычный 2 21 2" xfId="323" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="Обычный 2 22" xfId="326" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="Обычный 2 22 2" xfId="330" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="Обычный 2 23" xfId="334" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="Обычный 2 24" xfId="339" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="Обычный 2 25" xfId="500" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="Обычный 2 26" xfId="504" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="Обычный 2 27" xfId="506" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="Обычный 2 28" xfId="508" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="Обычный 2 29" xfId="156" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="Обычный 2 3" xfId="509" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="Обычный 2 3 10" xfId="324" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="Обычный 2 3 10 2" xfId="328" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="Обычный 2 3 11" xfId="332" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="Обычный 2 3 11 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="Обычный 2 3 12" xfId="336" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="Обычный 2 3 12 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="Обычный 2 3 13" xfId="498" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="Обычный 2 3 13 2" xfId="514" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="Обычный 2 3 14" xfId="502" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="Обычный 2 3 14 2" xfId="188" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Обычный 2 3 2" xfId="395" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="Обычный 2 3 2 2" xfId="515" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="Обычный 2 3 2 2 2" xfId="212" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="Обычный 2 3 3" xfId="399" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="Обычный 2 3 3 2" xfId="516" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="Обычный 2 3 4" xfId="262" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="Обычный 2 3 5" xfId="265" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="Обычный 2 3 5 2" xfId="517" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="Обычный 2 3 5 3" xfId="518" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="Обычный 2 3 6" xfId="267" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="Обычный 2 3 6 2" xfId="519" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="Обычный 2 3 7" xfId="269" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="Обычный 2 3 7 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="Обычный 2 3 8" xfId="313" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Обычный 2 3 9" xfId="521" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="Обычный 2 3 9 2" xfId="271" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="Обычный 2 30" xfId="1655" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="Обычный 2 4" xfId="1" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="Обычный 2 4 2" xfId="475" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="Обычный 2 4 2 2" xfId="129" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Обычный 2 4 3" xfId="477" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="Обычный 2 4 4" xfId="522" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="Обычный 2 5" xfId="523" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="Обычный 2 5 2" xfId="472" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="Обычный 2 5 3" xfId="139" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="Обычный 2 5 3 2" xfId="214" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="Обычный 2 5 4" xfId="144" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="Обычный 2 6" xfId="524" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="Обычный 2 6 2" xfId="495" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="Обычный 2 6 3" xfId="525" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="Обычный 2 6 3 2" xfId="526" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="Обычный 2 7" xfId="55" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="Обычный 2 7 2" xfId="73" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="Обычный 2 7 3" xfId="347" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="Обычный 2 8" xfId="527" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="Обычный 2 8 2" xfId="133" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="Обычный 2 9" xfId="528" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="Обычный 2 9 2" xfId="529" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="Обычный 20" xfId="18" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="Обычный 21" xfId="1641" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="Обычный 22" xfId="1650" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="Обычный 23" xfId="1660" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="Обычный 24" xfId="1661" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="Обычный 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="Обычный 3 2" xfId="531" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="Обычный 3 2 2" xfId="532" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="Обычный 3 2 2 2" xfId="484" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="Обычный 3 2 2 3" xfId="487" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
-    <cellStyle name="Обычный 3 2 2 4" xfId="489" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
-    <cellStyle name="Обычный 3 2 2 5" xfId="533" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
-    <cellStyle name="Обычный 3 2 3" xfId="534" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
-    <cellStyle name="Обычный 3 2 4" xfId="535" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
-    <cellStyle name="Обычный 3 2 5" xfId="536" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
-    <cellStyle name="Обычный 3 2 6" xfId="537" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
-    <cellStyle name="Обычный 3 3" xfId="538" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
-    <cellStyle name="Обычный 3 3 2" xfId="539" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
-    <cellStyle name="Обычный 3 4" xfId="540" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
-    <cellStyle name="Обычный 3 4 2" xfId="542" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
-    <cellStyle name="Обычный 3 5" xfId="543" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
-    <cellStyle name="Обычный 3 5 2" xfId="486" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
-    <cellStyle name="Обычный 3 6" xfId="160" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
-    <cellStyle name="Обычный 3 7" xfId="1645" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
-    <cellStyle name="Обычный 3 8" xfId="1656" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
-    <cellStyle name="Обычный 4" xfId="164" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
-    <cellStyle name="Обычный 4 10" xfId="1657" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
-    <cellStyle name="Обычный 4 2" xfId="545" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
-    <cellStyle name="Обычный 4 2 10" xfId="546" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
-    <cellStyle name="Обычный 4 2 2" xfId="548" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
-    <cellStyle name="Обычный 4 2 3" xfId="551" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
-    <cellStyle name="Обычный 4 2 3 2" xfId="115" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2" xfId="553" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 2" xfId="554" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 3" xfId="555" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 4" xfId="541" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 2 5" xfId="557" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 3" xfId="480" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 4" xfId="467" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 5" xfId="284" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
-    <cellStyle name="Обычный 4 2 3 2 6" xfId="470" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
-    <cellStyle name="Обычный 4 2 3 3" xfId="117" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 2" xfId="558" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 3" xfId="494" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 4" xfId="80" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
-    <cellStyle name="Обычный 4 2 3 3 5" xfId="289" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
-    <cellStyle name="Обычный 4 2 3 4" xfId="119" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
-    <cellStyle name="Обычный 4 2 3 5" xfId="559" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
-    <cellStyle name="Обычный 4 2 3 6" xfId="560" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
-    <cellStyle name="Обычный 4 2 3 7" xfId="561" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
-    <cellStyle name="Обычный 4 2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
-    <cellStyle name="Обычный 4 2 4 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 2" xfId="562" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 3" xfId="563" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 4" xfId="481" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
-    <cellStyle name="Обычный 4 2 4 2 5" xfId="483" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
-    <cellStyle name="Обычный 4 2 4 3" xfId="126" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
-    <cellStyle name="Обычный 4 2 4 4" xfId="564" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
-    <cellStyle name="Обычный 4 2 4 5" xfId="565" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
-    <cellStyle name="Обычный 4 2 4 6" xfId="566" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
-    <cellStyle name="Обычный 4 2 5" xfId="195" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
-    <cellStyle name="Обычный 4 2 5 2" xfId="568" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 2" xfId="430" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 3" xfId="433" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 4" xfId="436" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
-    <cellStyle name="Обычный 4 2 5 2 5" xfId="570" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
-    <cellStyle name="Обычный 4 2 5 3" xfId="26" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
-    <cellStyle name="Обычный 4 2 5 4" xfId="572" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
-    <cellStyle name="Обычный 4 2 5 5" xfId="574" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
-    <cellStyle name="Обычный 4 2 5 6" xfId="576" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
-    <cellStyle name="Обычный 4 2 6" xfId="198" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
-    <cellStyle name="Обычный 4 2 6 2" xfId="578" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
-    <cellStyle name="Обычный 4 2 6 3" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
-    <cellStyle name="Обычный 4 2 6 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
-    <cellStyle name="Обычный 4 2 6 5" xfId="424" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
-    <cellStyle name="Обычный 4 2 7" xfId="200" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
-    <cellStyle name="Обычный 4 2 8" xfId="368" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
-    <cellStyle name="Обычный 4 2 9" xfId="370" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
-    <cellStyle name="Обычный 4 3" xfId="580" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
-    <cellStyle name="Обычный 4 3 2" xfId="350" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
-    <cellStyle name="Обычный 4 3 2 2" xfId="355" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2" xfId="581" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 2" xfId="331" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 3" xfId="335" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 4" xfId="497" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 2 5" xfId="501" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 3" xfId="304" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 4" xfId="582" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 5" xfId="549" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
-    <cellStyle name="Обычный 4 3 2 2 6" xfId="552" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
-    <cellStyle name="Обычный 4 3 2 3" xfId="358" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 2" xfId="411" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 3" xfId="307" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 4" xfId="413" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
-    <cellStyle name="Обычный 4 3 2 3 5" xfId="351" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
-    <cellStyle name="Обычный 4 3 2 4" xfId="361" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
-    <cellStyle name="Обычный 4 3 2 5" xfId="316" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
-    <cellStyle name="Обычный 4 3 2 6" xfId="583" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
-    <cellStyle name="Обычный 4 3 2 7" xfId="32" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
-    <cellStyle name="Обычный 4 3 3" xfId="91" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
-    <cellStyle name="Обычный 4 3 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 3" xfId="65" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 4" xfId="58" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
-    <cellStyle name="Обычный 4 3 3 2 5" xfId="45" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
-    <cellStyle name="Обычный 4 3 3 3" xfId="148" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
-    <cellStyle name="Обычный 4 3 3 4" xfId="584" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
-    <cellStyle name="Обычный 4 3 3 5" xfId="321" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
-    <cellStyle name="Обычный 4 3 3 6" xfId="585" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
-    <cellStyle name="Обычный 4 3 4" xfId="587" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
-    <cellStyle name="Обычный 4 3 4 2" xfId="588" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
-    <cellStyle name="Обычный 4 3 4 3" xfId="589" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
-    <cellStyle name="Обычный 4 3 4 4" xfId="590" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
-    <cellStyle name="Обычный 4 3 4 5" xfId="327" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
-    <cellStyle name="Обычный 4 3 5" xfId="592" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
-    <cellStyle name="Обычный 4 3 6" xfId="594" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
-    <cellStyle name="Обычный 4 3 7" xfId="595" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
-    <cellStyle name="Обычный 4 3 8" xfId="375" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
-    <cellStyle name="Обычный 4 4" xfId="29" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
-    <cellStyle name="Обычный 4 5" xfId="597" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
-    <cellStyle name="Обычный 4 6" xfId="599" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
-    <cellStyle name="Обычный 4 7" xfId="511" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
-    <cellStyle name="Обычный 4 8" xfId="600" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
-    <cellStyle name="Обычный 4 9" xfId="1646" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
-    <cellStyle name="Обычный 4_Капекс_НВ_ 12.09.11" xfId="344" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
-    <cellStyle name="Обычный 5" xfId="530" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
-    <cellStyle name="Обычный 5 2" xfId="602" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
-    <cellStyle name="Обычный 5 2 10" xfId="603" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
-    <cellStyle name="Обычный 5 2 2" xfId="44" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
-    <cellStyle name="Обычный 5 2 2 2" xfId="606" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2" xfId="607" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2" xfId="608" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 2" xfId="101" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 3" xfId="609" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 4" xfId="610" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 2 5" xfId="611" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 3" xfId="612" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 4" xfId="613" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 5" xfId="614" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 2 6" xfId="615" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3" xfId="616" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 2" xfId="617" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 3" xfId="618" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 4" xfId="155" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 3 5" xfId="159" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 4" xfId="619" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 5" xfId="620" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 6" xfId="621" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
-    <cellStyle name="Обычный 5 2 2 2 7" xfId="622" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
-    <cellStyle name="Обычный 5 2 2 3" xfId="625" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2" xfId="627" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 2" xfId="628" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 3" xfId="629" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 4" xfId="630" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 2 5" xfId="631" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 3" xfId="633" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 4" xfId="635" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 5" xfId="637" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
-    <cellStyle name="Обычный 5 2 2 3 6" xfId="639" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
-    <cellStyle name="Обычный 5 2 2 4" xfId="642" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
-    <cellStyle name="Обычный 5 2 2 4 2" xfId="643" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
-    <cellStyle name="Обычный 5 2 2 4 3" xfId="644" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
-    <cellStyle name="Обычный 5 2 2 4 4" xfId="646" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
-    <cellStyle name="Обычный 5 2 2 4 5" xfId="648" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
-    <cellStyle name="Обычный 5 2 2 5" xfId="650" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
-    <cellStyle name="Обычный 5 2 2 6" xfId="652" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
-    <cellStyle name="Обычный 5 2 2 7" xfId="653" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
-    <cellStyle name="Обычный 5 2 2 8" xfId="654" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
-    <cellStyle name="Обычный 5 2 3" xfId="656" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
-    <cellStyle name="Обычный 5 2 3 2" xfId="658" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2" xfId="659" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 2" xfId="660" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 3" xfId="661" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 4" xfId="662" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 2 5" xfId="663" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 3" xfId="664" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 4" xfId="665" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 5" xfId="666" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
-    <cellStyle name="Обычный 5 2 3 2 6" xfId="667" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
-    <cellStyle name="Обычный 5 2 3 3" xfId="669" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 2" xfId="670" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 3" xfId="671" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 4" xfId="672" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
-    <cellStyle name="Обычный 5 2 3 3 5" xfId="673" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
-    <cellStyle name="Обычный 5 2 3 4" xfId="675" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
-    <cellStyle name="Обычный 5 2 3 5" xfId="677" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
-    <cellStyle name="Обычный 5 2 3 6" xfId="678" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
-    <cellStyle name="Обычный 5 2 3 7" xfId="679" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
-    <cellStyle name="Обычный 5 2 4" xfId="681" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="Обычный 5 2 4 2" xfId="683" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 2" xfId="684" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 3" xfId="685" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 4" xfId="686" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Обычный 5 2 4 2 5" xfId="687" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Обычный 5 2 4 3" xfId="689" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Обычный 5 2 4 4" xfId="691" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Обычный 5 2 4 5" xfId="692" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Обычный 5 2 4 6" xfId="694" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Обычный 5 2 5" xfId="696" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Обычный 5 2 5 2" xfId="697" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 4" xfId="700" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Обычный 5 2 5 2 5" xfId="701" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Обычный 5 2 5 3" xfId="702" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Обычный 5 2 5 4" xfId="703" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Обычный 5 2 5 5" xfId="704" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Обычный 5 2 5 6" xfId="705" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Обычный 5 2 6" xfId="706" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Обычный 5 2 6 2" xfId="707" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Обычный 5 2 6 3" xfId="708" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Обычный 5 2 6 4" xfId="709" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Обычный 5 2 6 5" xfId="710" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Обычный 5 2 7" xfId="711" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Обычный 5 2 8" xfId="712" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Обычный 5 2 9" xfId="713" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Обычный 5 3" xfId="715" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Обычный 5 3 2" xfId="716" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Обычный 5 4" xfId="718" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="Обычный 5 4 2" xfId="719" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="Обычный 5 5" xfId="721" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="Обычный 5 5 2" xfId="722" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Обычный 5 6" xfId="725" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Обычный 5 6 2" xfId="726" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="Обычный 5 7" xfId="728" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="Обычный 5 7 2" xfId="729" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="Обычный 6 10" xfId="731" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Обычный 6 11" xfId="732" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Обычный 6 12" xfId="730" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="Обычный 6 2" xfId="735" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Обычный 6 2 2" xfId="737" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="Обычный 6 2 2 2" xfId="739" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2" xfId="740" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 3" xfId="742" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 4" xfId="743" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 2 5" xfId="744" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 3" xfId="746" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 4" xfId="747" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 5" xfId="748" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Обычный 6 2 2 2 6" xfId="749" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Обычный 6 2 2 3" xfId="751" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 2" xfId="752" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 3" xfId="754" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 4" xfId="755" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Обычный 6 2 2 3 5" xfId="756" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Обычный 6 2 2 4" xfId="757" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Обычный 6 2 2 5" xfId="758" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Обычный 6 2 2 6" xfId="759" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Обычный 6 2 2 7" xfId="760" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Обычный 6 2 3" xfId="762" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Обычный 6 2 3 2" xfId="764" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 2" xfId="765" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 3" xfId="766" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 4" xfId="767" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Обычный 6 2 3 2 5" xfId="768" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Обычный 6 2 3 3" xfId="769" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="Обычный 6 2 3 4" xfId="770" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="Обычный 6 2 3 5" xfId="771" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Обычный 6 2 3 6" xfId="772" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Обычный 6 2 4" xfId="775" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Обычный 6 2 4 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Обычный 6 2 4 3" xfId="777" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Обычный 6 2 4 4" xfId="778" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="Обычный 6 2 4 5" xfId="779" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="Обычный 6 2 5" xfId="782" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="Обычный 6 2 6" xfId="784" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="Обычный 6 2 7" xfId="786" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="Обычный 6 2 8" xfId="787" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Обычный 6 3" xfId="790" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Обычный 6 3 2" xfId="791" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="Обычный 6 3 2 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 2" xfId="793" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 3" xfId="794" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 4" xfId="795" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="Обычный 6 3 2 2 5" xfId="796" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="Обычный 6 3 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="Обычный 6 3 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="Обычный 6 3 2 5" xfId="799" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Обычный 6 3 2 6" xfId="471" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Обычный 6 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="Обычный 6 3 3 2" xfId="801" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="Обычный 6 3 3 3" xfId="802" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="Обычный 6 3 3 4" xfId="803" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Обычный 6 3 3 5" xfId="804" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Обычный 6 3 4" xfId="805" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="Обычный 6 3 5" xfId="806" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="Обычный 6 3 6" xfId="807" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="Обычный 6 3 7" xfId="808" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="Обычный 6 4" xfId="811" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="Обычный 6 4 2" xfId="812" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="Обычный 6 4 2 2" xfId="813" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="Обычный 6 4 2 3" xfId="814" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="Обычный 6 4 2 4" xfId="815" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="Обычный 6 4 2 5" xfId="816" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="Обычный 6 4 3" xfId="817" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="Обычный 6 4 4" xfId="818" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
-    <cellStyle name="Обычный 6 4 5" xfId="819" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
-    <cellStyle name="Обычный 6 4 6" xfId="820" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
-    <cellStyle name="Обычный 6 5" xfId="822" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
-    <cellStyle name="Обычный 6 5 2" xfId="825" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
-    <cellStyle name="Обычный 6 5 2 2" xfId="828" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
-    <cellStyle name="Обычный 6 5 2 3" xfId="830" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
-    <cellStyle name="Обычный 6 5 2 4" xfId="832" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
-    <cellStyle name="Обычный 6 5 2 5" xfId="834" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
-    <cellStyle name="Обычный 6 5 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
-    <cellStyle name="Обычный 6 5 4" xfId="837" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
-    <cellStyle name="Обычный 6 5 5" xfId="840" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
-    <cellStyle name="Обычный 6 5 6" xfId="843" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
-    <cellStyle name="Обычный 6 6" xfId="845" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
-    <cellStyle name="Обычный 6 6 2" xfId="846" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
-    <cellStyle name="Обычный 6 6 2 2" xfId="847" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
-    <cellStyle name="Обычный 6 6 2 3" xfId="848" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
-    <cellStyle name="Обычный 6 6 2 4" xfId="849" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
-    <cellStyle name="Обычный 6 6 2 5" xfId="850" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
-    <cellStyle name="Обычный 6 6 3" xfId="851" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
-    <cellStyle name="Обычный 6 6 4" xfId="852" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
-    <cellStyle name="Обычный 6 6 5" xfId="853" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
-    <cellStyle name="Обычный 6 6 6" xfId="854" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
-    <cellStyle name="Обычный 6 7" xfId="855" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
-    <cellStyle name="Обычный 6 7 2" xfId="856" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
-    <cellStyle name="Обычный 6 7 3" xfId="857" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
-    <cellStyle name="Обычный 6 7 4" xfId="858" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
-    <cellStyle name="Обычный 6 7 5" xfId="859" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
-    <cellStyle name="Обычный 6 8" xfId="860" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
-    <cellStyle name="Обычный 6 9" xfId="861" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
-    <cellStyle name="Обычный 7" xfId="862" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
-    <cellStyle name="Обычный 7 10" xfId="863" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
-    <cellStyle name="Обычный 7 11" xfId="864" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
-    <cellStyle name="Обычный 7 2" xfId="866" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
-    <cellStyle name="Обычный 7 2 2" xfId="868" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
-    <cellStyle name="Обычный 7 2 2 2" xfId="869" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2" xfId="870" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 2" xfId="873" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 3" xfId="876" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 4" xfId="878" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 2 5" xfId="879" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 3" xfId="880" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 4" xfId="881" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 5" xfId="882" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
-    <cellStyle name="Обычный 7 2 2 2 6" xfId="883" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
-    <cellStyle name="Обычный 7 2 2 3" xfId="885" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 2" xfId="887" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 3" xfId="889" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 4" xfId="891" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
-    <cellStyle name="Обычный 7 2 2 3 5" xfId="893" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
-    <cellStyle name="Обычный 7 2 2 4" xfId="895" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
-    <cellStyle name="Обычный 7 2 2 5" xfId="734" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
-    <cellStyle name="Обычный 7 2 2 6" xfId="789" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
-    <cellStyle name="Обычный 7 2 2 7" xfId="810" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
-    <cellStyle name="Обычный 7 2 3" xfId="896" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
-    <cellStyle name="Обычный 7 2 3 2" xfId="898" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 2" xfId="899" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 3" xfId="901" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 4" xfId="903" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
-    <cellStyle name="Обычный 7 2 3 2 5" xfId="905" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
-    <cellStyle name="Обычный 7 2 3 3" xfId="908" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
-    <cellStyle name="Обычный 7 2 3 4" xfId="910" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
-    <cellStyle name="Обычный 7 2 3 5" xfId="865" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
-    <cellStyle name="Обычный 7 2 3 6" xfId="912" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
-    <cellStyle name="Обычный 7 2 4" xfId="913" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
-    <cellStyle name="Обычный 7 2 4 2" xfId="915" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
-    <cellStyle name="Обычный 7 2 4 3" xfId="918" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
-    <cellStyle name="Обычный 7 2 4 4" xfId="919" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
-    <cellStyle name="Обычный 7 2 4 5" xfId="921" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
-    <cellStyle name="Обычный 7 2 5" xfId="922" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
-    <cellStyle name="Обычный 7 2 6" xfId="923" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
-    <cellStyle name="Обычный 7 2 7" xfId="924" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
-    <cellStyle name="Обычный 7 2 8" xfId="925" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
-    <cellStyle name="Обычный 7 3" xfId="911" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
-    <cellStyle name="Обычный 7 3 2" xfId="926" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
-    <cellStyle name="Обычный 7 3 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 2" xfId="928" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 3" xfId="872" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 4" xfId="875" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
-    <cellStyle name="Обычный 7 3 2 2 5" xfId="877" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
-    <cellStyle name="Обычный 7 3 2 3" xfId="66" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
-    <cellStyle name="Обычный 7 3 2 4" xfId="59" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
-    <cellStyle name="Обычный 7 3 2 5" xfId="47" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
-    <cellStyle name="Обычный 7 3 2 6" xfId="930" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
-    <cellStyle name="Обычный 7 3 3" xfId="931" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
-    <cellStyle name="Обычный 7 3 3 2" xfId="933" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
-    <cellStyle name="Обычный 7 3 3 3" xfId="935" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
-    <cellStyle name="Обычный 7 3 3 4" xfId="937" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
-    <cellStyle name="Обычный 7 3 3 5" xfId="939" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
-    <cellStyle name="Обычный 7 3 4" xfId="940" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
-    <cellStyle name="Обычный 7 3 5" xfId="941" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
-    <cellStyle name="Обычный 7 3 6" xfId="942" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
-    <cellStyle name="Обычный 7 3 7" xfId="943" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
-    <cellStyle name="Обычный 7 4" xfId="944" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
-    <cellStyle name="Обычный 7 4 2" xfId="945" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
-    <cellStyle name="Обычный 7 4 2 2" xfId="946" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
-    <cellStyle name="Обычный 7 4 2 3" xfId="947" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
-    <cellStyle name="Обычный 7 4 2 4" xfId="948" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
-    <cellStyle name="Обычный 7 4 2 5" xfId="949" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
-    <cellStyle name="Обычный 7 4 3" xfId="950" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
-    <cellStyle name="Обычный 7 4 4" xfId="951" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
-    <cellStyle name="Обычный 7 4 5" xfId="952" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
-    <cellStyle name="Обычный 7 4 6" xfId="953" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
-    <cellStyle name="Обычный 7 5" xfId="954" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
-    <cellStyle name="Обычный 7 5 2" xfId="955" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
-    <cellStyle name="Обычный 7 5 2 2" xfId="956" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
-    <cellStyle name="Обычный 7 5 2 3" xfId="957" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
-    <cellStyle name="Обычный 7 5 2 4" xfId="958" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
-    <cellStyle name="Обычный 7 5 2 5" xfId="959" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
-    <cellStyle name="Обычный 7 5 3" xfId="960" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
-    <cellStyle name="Обычный 7 5 4" xfId="961" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
-    <cellStyle name="Обычный 7 5 5" xfId="962" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
-    <cellStyle name="Обычный 7 5 6" xfId="963" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
-    <cellStyle name="Обычный 7 6" xfId="964" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
-    <cellStyle name="Обычный 7 6 2" xfId="965" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
-    <cellStyle name="Обычный 7 6 2 2" xfId="966" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
-    <cellStyle name="Обычный 7 6 2 3" xfId="968" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
-    <cellStyle name="Обычный 7 6 2 4" xfId="970" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
-    <cellStyle name="Обычный 7 6 2 5" xfId="971" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
-    <cellStyle name="Обычный 7 6 3" xfId="972" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
-    <cellStyle name="Обычный 7 6 4" xfId="973" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
-    <cellStyle name="Обычный 7 6 5" xfId="974" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
-    <cellStyle name="Обычный 7 6 6" xfId="343" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
-    <cellStyle name="Обычный 7 7" xfId="975" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
-    <cellStyle name="Обычный 7 7 2" xfId="976" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
-    <cellStyle name="Обычный 7 7 3" xfId="977" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
-    <cellStyle name="Обычный 7 7 4" xfId="978" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
-    <cellStyle name="Обычный 7 7 5" xfId="979" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
-    <cellStyle name="Обычный 7 8" xfId="980" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
-    <cellStyle name="Обычный 7 9" xfId="192" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
-    <cellStyle name="Обычный 8" xfId="981" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
-    <cellStyle name="Обычный 8 2" xfId="920" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
-    <cellStyle name="Обычный 9" xfId="982" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
-    <cellStyle name="Обычный 9 2" xfId="984" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
+    <cellStyle name="Обычный 10" xfId="279"/>
+    <cellStyle name="Обычный 10 2" xfId="281"/>
+    <cellStyle name="Обычный 11" xfId="282"/>
+    <cellStyle name="Обычный 11 2" xfId="286"/>
+    <cellStyle name="Обычный 12" xfId="287"/>
+    <cellStyle name="Обычный 12 2" xfId="291"/>
+    <cellStyle name="Обычный 13" xfId="293"/>
+    <cellStyle name="Обычный 13 2" xfId="69"/>
+    <cellStyle name="Обычный 14" xfId="295"/>
+    <cellStyle name="Обычный 14 2" xfId="131"/>
+    <cellStyle name="Обычный 15" xfId="298"/>
+    <cellStyle name="Обычный 15 2" xfId="165"/>
+    <cellStyle name="Обычный 16" xfId="301"/>
+    <cellStyle name="Обычный 16 2" xfId="302"/>
+    <cellStyle name="Обычный 17" xfId="303"/>
+    <cellStyle name="Обычный 17 2" xfId="305"/>
+    <cellStyle name="Обычный 18" xfId="306"/>
+    <cellStyle name="Обычный 18 2" xfId="309"/>
+    <cellStyle name="Обычный 19" xfId="19"/>
+    <cellStyle name="Обычный 2" xfId="4"/>
+    <cellStyle name="Обычный 2 10" xfId="310"/>
+    <cellStyle name="Обычный 2 10 2" xfId="182"/>
+    <cellStyle name="Обычный 2 11" xfId="311"/>
+    <cellStyle name="Обычный 2 12" xfId="37"/>
+    <cellStyle name="Обычный 2 12 2" xfId="234"/>
+    <cellStyle name="Обычный 2 12 3" xfId="312"/>
+    <cellStyle name="Обычный 2 13" xfId="225"/>
+    <cellStyle name="Обычный 2 13 2" xfId="258"/>
+    <cellStyle name="Обычный 2 14" xfId="227"/>
+    <cellStyle name="Обычный 2 14 2" xfId="314"/>
+    <cellStyle name="Обычный 2 15" xfId="229"/>
+    <cellStyle name="Обычный 2 15 2" xfId="317"/>
+    <cellStyle name="Обычный 2 16" xfId="319"/>
+    <cellStyle name="Обычный 2 16 2" xfId="322"/>
+    <cellStyle name="Обычный 2 17" xfId="325"/>
+    <cellStyle name="Обычный 2 17 2" xfId="329"/>
+    <cellStyle name="Обычный 2 18" xfId="333"/>
+    <cellStyle name="Обычный 2 18 2" xfId="57"/>
+    <cellStyle name="Обычный 2 19" xfId="338"/>
+    <cellStyle name="Обычный 2 19 2" xfId="342"/>
+    <cellStyle name="Обычный 2 19 3" xfId="346"/>
+    <cellStyle name="Обычный 2 2" xfId="348"/>
+    <cellStyle name="Обычный 2 2 10" xfId="353"/>
+    <cellStyle name="Обычный 2 2 10 2" xfId="356"/>
+    <cellStyle name="Обычный 2 2 10 3" xfId="359"/>
+    <cellStyle name="Обычный 2 2 10 4" xfId="362"/>
+    <cellStyle name="Обычный 2 2 11" xfId="93"/>
+    <cellStyle name="Обычный 2 2 2" xfId="365"/>
+    <cellStyle name="Обычный 2 2 2 2" xfId="366"/>
+    <cellStyle name="Обычный 2 2 2 2 2" xfId="367"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2" xfId="71"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2" xfId="369"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 2" xfId="292"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 3" xfId="294"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 4" xfId="297"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 2 5" xfId="300"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 3" xfId="371"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 4" xfId="372"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 5" xfId="373"/>
+    <cellStyle name="Обычный 2 2 2 2 2 2 6" xfId="374"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3" xfId="75"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 2" xfId="376"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 3" xfId="191"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 4" xfId="202"/>
+    <cellStyle name="Обычный 2 2 2 2 2 3 5" xfId="204"/>
+    <cellStyle name="Обычный 2 2 2 2 2 4" xfId="377"/>
+    <cellStyle name="Обычный 2 2 2 2 2 5" xfId="378"/>
+    <cellStyle name="Обычный 2 2 2 2 2 6" xfId="379"/>
+    <cellStyle name="Обычный 2 2 2 2 2 7" xfId="380"/>
+    <cellStyle name="Обычный 2 2 2 2 3" xfId="82"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2" xfId="42"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 2" xfId="381"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 3" xfId="382"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 4" xfId="383"/>
+    <cellStyle name="Обычный 2 2 2 2 3 2 5" xfId="384"/>
+    <cellStyle name="Обычный 2 2 2 2 3 3" xfId="385"/>
+    <cellStyle name="Обычный 2 2 2 2 3 4" xfId="386"/>
+    <cellStyle name="Обычный 2 2 2 2 3 5" xfId="387"/>
+    <cellStyle name="Обычный 2 2 2 2 3 6" xfId="388"/>
+    <cellStyle name="Обычный 2 2 2 2 4" xfId="87"/>
+    <cellStyle name="Обычный 2 2 2 2 4 2" xfId="390"/>
+    <cellStyle name="Обычный 2 2 2 2 4 3" xfId="392"/>
+    <cellStyle name="Обычный 2 2 2 2 4 4" xfId="394"/>
+    <cellStyle name="Обычный 2 2 2 2 4 5" xfId="102"/>
+    <cellStyle name="Обычный 2 2 2 2 5" xfId="107"/>
+    <cellStyle name="Обычный 2 2 2 2 6" xfId="111"/>
+    <cellStyle name="Обычный 2 2 2 2 7" xfId="398"/>
+    <cellStyle name="Обычный 2 2 2 2 8" xfId="402"/>
+    <cellStyle name="Обычный 2 2 2 3" xfId="403"/>
+    <cellStyle name="Обычный 2 2 2 3 2" xfId="404"/>
+    <cellStyle name="Обычный 2 2 3" xfId="407"/>
+    <cellStyle name="Обычный 2 2 3 2" xfId="408"/>
+    <cellStyle name="Обычный 2 2 4" xfId="241"/>
+    <cellStyle name="Обычный 2 2 4 2" xfId="243"/>
+    <cellStyle name="Обычный 2 2 4 2 2" xfId="409"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2" xfId="135"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 2" xfId="137"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 3" xfId="150"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 4" xfId="154"/>
+    <cellStyle name="Обычный 2 2 4 2 2 2 5" xfId="162"/>
+    <cellStyle name="Обычный 2 2 4 2 2 3" xfId="167"/>
+    <cellStyle name="Обычный 2 2 4 2 2 4" xfId="179"/>
+    <cellStyle name="Обычный 2 2 4 2 2 5" xfId="181"/>
+    <cellStyle name="Обычный 2 2 4 2 2 6" xfId="184"/>
+    <cellStyle name="Обычный 2 2 4 2 3" xfId="410"/>
+    <cellStyle name="Обычный 2 2 4 2 3 2" xfId="208"/>
+    <cellStyle name="Обычный 2 2 4 2 3 3" xfId="216"/>
+    <cellStyle name="Обычный 2 2 4 2 3 4" xfId="51"/>
+    <cellStyle name="Обычный 2 2 4 2 3 5" xfId="218"/>
+    <cellStyle name="Обычный 2 2 4 2 4" xfId="412"/>
+    <cellStyle name="Обычный 2 2 4 2 5" xfId="308"/>
+    <cellStyle name="Обычный 2 2 4 2 6" xfId="414"/>
+    <cellStyle name="Обычный 2 2 4 2 7" xfId="352"/>
+    <cellStyle name="Обычный 2 2 4 3" xfId="245"/>
+    <cellStyle name="Обычный 2 2 4 3 2" xfId="415"/>
+    <cellStyle name="Обычный 2 2 4 3 2 2" xfId="417"/>
+    <cellStyle name="Обычный 2 2 4 3 2 3" xfId="420"/>
+    <cellStyle name="Обычный 2 2 4 3 2 4" xfId="423"/>
+    <cellStyle name="Обычный 2 2 4 3 2 5" xfId="425"/>
+    <cellStyle name="Обычный 2 2 4 3 3" xfId="426"/>
+    <cellStyle name="Обычный 2 2 4 3 4" xfId="427"/>
+    <cellStyle name="Обычный 2 2 4 3 5" xfId="60"/>
+    <cellStyle name="Обычный 2 2 4 3 6" xfId="49"/>
+    <cellStyle name="Обычный 2 2 4 4" xfId="247"/>
+    <cellStyle name="Обычный 2 2 4 4 2" xfId="27"/>
+    <cellStyle name="Обычный 2 2 4 4 3" xfId="431"/>
+    <cellStyle name="Обычный 2 2 4 4 4" xfId="434"/>
+    <cellStyle name="Обычный 2 2 4 4 5" xfId="437"/>
+    <cellStyle name="Обычный 2 2 4 5" xfId="249"/>
+    <cellStyle name="Обычный 2 2 4 6" xfId="438"/>
+    <cellStyle name="Обычный 2 2 4 7" xfId="223"/>
+    <cellStyle name="Обычный 2 2 4 8" xfId="53"/>
+    <cellStyle name="Обычный 2 2 5" xfId="251"/>
+    <cellStyle name="Обычный 2 2 5 2" xfId="440"/>
+    <cellStyle name="Обычный 2 2 5 2 2" xfId="442"/>
+    <cellStyle name="Обычный 2 2 5 2 2 2" xfId="444"/>
+    <cellStyle name="Обычный 2 2 5 2 2 3" xfId="446"/>
+    <cellStyle name="Обычный 2 2 5 2 2 4" xfId="170"/>
+    <cellStyle name="Обычный 2 2 5 2 2 5" xfId="174"/>
+    <cellStyle name="Обычный 2 2 5 2 3" xfId="448"/>
+    <cellStyle name="Обычный 2 2 5 2 4" xfId="450"/>
+    <cellStyle name="Обычный 2 2 5 2 5" xfId="452"/>
+    <cellStyle name="Обычный 2 2 5 2 6" xfId="454"/>
+    <cellStyle name="Обычный 2 2 5 3" xfId="456"/>
+    <cellStyle name="Обычный 2 2 5 3 2" xfId="458"/>
+    <cellStyle name="Обычный 2 2 5 3 3" xfId="460"/>
+    <cellStyle name="Обычный 2 2 5 3 4" xfId="461"/>
+    <cellStyle name="Обычный 2 2 5 3 5" xfId="462"/>
+    <cellStyle name="Обычный 2 2 5 4" xfId="464"/>
+    <cellStyle name="Обычный 2 2 5 5" xfId="364"/>
+    <cellStyle name="Обычный 2 2 5 6" xfId="406"/>
+    <cellStyle name="Обычный 2 2 5 7" xfId="240"/>
+    <cellStyle name="Обычный 2 2 6" xfId="253"/>
+    <cellStyle name="Обычный 2 2 6 2" xfId="86"/>
+    <cellStyle name="Обычный 2 2 6 2 2" xfId="389"/>
+    <cellStyle name="Обычный 2 2 6 2 3" xfId="391"/>
+    <cellStyle name="Обычный 2 2 6 2 4" xfId="393"/>
+    <cellStyle name="Обычный 2 2 6 2 5" xfId="100"/>
+    <cellStyle name="Обычный 2 2 6 3" xfId="106"/>
+    <cellStyle name="Обычный 2 2 6 4" xfId="110"/>
+    <cellStyle name="Обычный 2 2 6 5" xfId="396"/>
+    <cellStyle name="Обычный 2 2 6 6" xfId="400"/>
+    <cellStyle name="Обычный 2 2 7" xfId="255"/>
+    <cellStyle name="Обычный 2 2 7 2" xfId="465"/>
+    <cellStyle name="Обычный 2 2 7 2 2" xfId="468"/>
+    <cellStyle name="Обычный 2 2 7 2 3" xfId="285"/>
+    <cellStyle name="Обычный 2 2 7 2 4" xfId="473"/>
+    <cellStyle name="Обычный 2 2 7 2 5" xfId="141"/>
+    <cellStyle name="Обычный 2 2 7 3" xfId="474"/>
+    <cellStyle name="Обычный 2 2 7 4" xfId="280"/>
+    <cellStyle name="Обычный 2 2 7 5" xfId="476"/>
+    <cellStyle name="Обычный 2 2 7 6" xfId="478"/>
+    <cellStyle name="Обычный 2 2 8" xfId="257"/>
+    <cellStyle name="Обычный 2 2 8 2" xfId="479"/>
+    <cellStyle name="Обычный 2 2 8 2 2" xfId="482"/>
+    <cellStyle name="Обычный 2 2 8 2 3" xfId="485"/>
+    <cellStyle name="Обычный 2 2 8 2 4" xfId="488"/>
+    <cellStyle name="Обычный 2 2 8 2 5" xfId="491"/>
+    <cellStyle name="Обычный 2 2 8 3" xfId="466"/>
+    <cellStyle name="Обычный 2 2 8 4" xfId="283"/>
+    <cellStyle name="Обычный 2 2 8 5" xfId="469"/>
+    <cellStyle name="Обычный 2 2 8 6" xfId="140"/>
+    <cellStyle name="Обычный 2 2 9" xfId="492"/>
+    <cellStyle name="Обычный 2 2 9 2" xfId="493"/>
+    <cellStyle name="Обычный 2 2 9 3" xfId="79"/>
+    <cellStyle name="Обычный 2 2 9 4" xfId="288"/>
+    <cellStyle name="Обычный 2 2 9 5" xfId="496"/>
+    <cellStyle name="Обычный 2 20" xfId="230"/>
+    <cellStyle name="Обычный 2 20 2" xfId="318"/>
+    <cellStyle name="Обычный 2 21" xfId="320"/>
+    <cellStyle name="Обычный 2 21 2" xfId="323"/>
+    <cellStyle name="Обычный 2 22" xfId="326"/>
+    <cellStyle name="Обычный 2 22 2" xfId="330"/>
+    <cellStyle name="Обычный 2 23" xfId="334"/>
+    <cellStyle name="Обычный 2 24" xfId="339"/>
+    <cellStyle name="Обычный 2 25" xfId="500"/>
+    <cellStyle name="Обычный 2 26" xfId="504"/>
+    <cellStyle name="Обычный 2 27" xfId="506"/>
+    <cellStyle name="Обычный 2 28" xfId="508"/>
+    <cellStyle name="Обычный 2 29" xfId="156"/>
+    <cellStyle name="Обычный 2 3" xfId="509"/>
+    <cellStyle name="Обычный 2 3 10" xfId="324"/>
+    <cellStyle name="Обычный 2 3 10 2" xfId="328"/>
+    <cellStyle name="Обычный 2 3 11" xfId="332"/>
+    <cellStyle name="Обычный 2 3 11 2" xfId="56"/>
+    <cellStyle name="Обычный 2 3 12" xfId="336"/>
+    <cellStyle name="Обычный 2 3 12 2" xfId="340"/>
+    <cellStyle name="Обычный 2 3 13" xfId="498"/>
+    <cellStyle name="Обычный 2 3 13 2" xfId="514"/>
+    <cellStyle name="Обычный 2 3 14" xfId="502"/>
+    <cellStyle name="Обычный 2 3 14 2" xfId="188"/>
+    <cellStyle name="Обычный 2 3 2" xfId="395"/>
+    <cellStyle name="Обычный 2 3 2 2" xfId="515"/>
+    <cellStyle name="Обычный 2 3 2 2 2" xfId="212"/>
+    <cellStyle name="Обычный 2 3 3" xfId="399"/>
+    <cellStyle name="Обычный 2 3 3 2" xfId="516"/>
+    <cellStyle name="Обычный 2 3 4" xfId="262"/>
+    <cellStyle name="Обычный 2 3 5" xfId="265"/>
+    <cellStyle name="Обычный 2 3 5 2" xfId="517"/>
+    <cellStyle name="Обычный 2 3 5 3" xfId="518"/>
+    <cellStyle name="Обычный 2 3 6" xfId="267"/>
+    <cellStyle name="Обычный 2 3 6 2" xfId="519"/>
+    <cellStyle name="Обычный 2 3 7" xfId="269"/>
+    <cellStyle name="Обычный 2 3 7 2" xfId="520"/>
+    <cellStyle name="Обычный 2 3 8" xfId="313"/>
+    <cellStyle name="Обычный 2 3 9" xfId="521"/>
+    <cellStyle name="Обычный 2 3 9 2" xfId="271"/>
+    <cellStyle name="Обычный 2 30" xfId="1655"/>
+    <cellStyle name="Обычный 2 4" xfId="1"/>
+    <cellStyle name="Обычный 2 4 2" xfId="475"/>
+    <cellStyle name="Обычный 2 4 2 2" xfId="129"/>
+    <cellStyle name="Обычный 2 4 3" xfId="477"/>
+    <cellStyle name="Обычный 2 4 4" xfId="522"/>
+    <cellStyle name="Обычный 2 5" xfId="523"/>
+    <cellStyle name="Обычный 2 5 2" xfId="472"/>
+    <cellStyle name="Обычный 2 5 3" xfId="139"/>
+    <cellStyle name="Обычный 2 5 3 2" xfId="214"/>
+    <cellStyle name="Обычный 2 5 4" xfId="144"/>
+    <cellStyle name="Обычный 2 6" xfId="524"/>
+    <cellStyle name="Обычный 2 6 2" xfId="495"/>
+    <cellStyle name="Обычный 2 6 3" xfId="525"/>
+    <cellStyle name="Обычный 2 6 3 2" xfId="526"/>
+    <cellStyle name="Обычный 2 7" xfId="55"/>
+    <cellStyle name="Обычный 2 7 2" xfId="73"/>
+    <cellStyle name="Обычный 2 7 3" xfId="347"/>
+    <cellStyle name="Обычный 2 8" xfId="527"/>
+    <cellStyle name="Обычный 2 8 2" xfId="133"/>
+    <cellStyle name="Обычный 2 9" xfId="528"/>
+    <cellStyle name="Обычный 2 9 2" xfId="529"/>
+    <cellStyle name="Обычный 20" xfId="18"/>
+    <cellStyle name="Обычный 21" xfId="1641"/>
+    <cellStyle name="Обычный 22" xfId="1650"/>
+    <cellStyle name="Обычный 23" xfId="1660"/>
+    <cellStyle name="Обычный 24" xfId="1661"/>
+    <cellStyle name="Обычный 3" xfId="17"/>
+    <cellStyle name="Обычный 3 2" xfId="531"/>
+    <cellStyle name="Обычный 3 2 2" xfId="532"/>
+    <cellStyle name="Обычный 3 2 2 2" xfId="484"/>
+    <cellStyle name="Обычный 3 2 2 3" xfId="487"/>
+    <cellStyle name="Обычный 3 2 2 4" xfId="489"/>
+    <cellStyle name="Обычный 3 2 2 5" xfId="533"/>
+    <cellStyle name="Обычный 3 2 3" xfId="534"/>
+    <cellStyle name="Обычный 3 2 4" xfId="535"/>
+    <cellStyle name="Обычный 3 2 5" xfId="536"/>
+    <cellStyle name="Обычный 3 2 6" xfId="537"/>
+    <cellStyle name="Обычный 3 3" xfId="538"/>
+    <cellStyle name="Обычный 3 3 2" xfId="539"/>
+    <cellStyle name="Обычный 3 4" xfId="540"/>
+    <cellStyle name="Обычный 3 4 2" xfId="542"/>
+    <cellStyle name="Обычный 3 5" xfId="543"/>
+    <cellStyle name="Обычный 3 5 2" xfId="486"/>
+    <cellStyle name="Обычный 3 6" xfId="160"/>
+    <cellStyle name="Обычный 3 7" xfId="1645"/>
+    <cellStyle name="Обычный 3 8" xfId="1656"/>
+    <cellStyle name="Обычный 4" xfId="164"/>
+    <cellStyle name="Обычный 4 10" xfId="1657"/>
+    <cellStyle name="Обычный 4 2" xfId="545"/>
+    <cellStyle name="Обычный 4 2 10" xfId="546"/>
+    <cellStyle name="Обычный 4 2 2" xfId="548"/>
+    <cellStyle name="Обычный 4 2 3" xfId="551"/>
+    <cellStyle name="Обычный 4 2 3 2" xfId="115"/>
+    <cellStyle name="Обычный 4 2 3 2 2" xfId="553"/>
+    <cellStyle name="Обычный 4 2 3 2 2 2" xfId="554"/>
+    <cellStyle name="Обычный 4 2 3 2 2 3" xfId="555"/>
+    <cellStyle name="Обычный 4 2 3 2 2 4" xfId="541"/>
+    <cellStyle name="Обычный 4 2 3 2 2 5" xfId="557"/>
+    <cellStyle name="Обычный 4 2 3 2 3" xfId="480"/>
+    <cellStyle name="Обычный 4 2 3 2 4" xfId="467"/>
+    <cellStyle name="Обычный 4 2 3 2 5" xfId="284"/>
+    <cellStyle name="Обычный 4 2 3 2 6" xfId="470"/>
+    <cellStyle name="Обычный 4 2 3 3" xfId="117"/>
+    <cellStyle name="Обычный 4 2 3 3 2" xfId="558"/>
+    <cellStyle name="Обычный 4 2 3 3 3" xfId="494"/>
+    <cellStyle name="Обычный 4 2 3 3 4" xfId="80"/>
+    <cellStyle name="Обычный 4 2 3 3 5" xfId="289"/>
+    <cellStyle name="Обычный 4 2 3 4" xfId="119"/>
+    <cellStyle name="Обычный 4 2 3 5" xfId="559"/>
+    <cellStyle name="Обычный 4 2 3 6" xfId="560"/>
+    <cellStyle name="Обычный 4 2 3 7" xfId="561"/>
+    <cellStyle name="Обычный 4 2 4" xfId="35"/>
+    <cellStyle name="Обычный 4 2 4 2" xfId="124"/>
+    <cellStyle name="Обычный 4 2 4 2 2" xfId="562"/>
+    <cellStyle name="Обычный 4 2 4 2 3" xfId="563"/>
+    <cellStyle name="Обычный 4 2 4 2 4" xfId="481"/>
+    <cellStyle name="Обычный 4 2 4 2 5" xfId="483"/>
+    <cellStyle name="Обычный 4 2 4 3" xfId="126"/>
+    <cellStyle name="Обычный 4 2 4 4" xfId="564"/>
+    <cellStyle name="Обычный 4 2 4 5" xfId="565"/>
+    <cellStyle name="Обычный 4 2 4 6" xfId="566"/>
+    <cellStyle name="Обычный 4 2 5" xfId="195"/>
+    <cellStyle name="Обычный 4 2 5 2" xfId="568"/>
+    <cellStyle name="Обычный 4 2 5 2 2" xfId="430"/>
+    <cellStyle name="Обычный 4 2 5 2 3" xfId="433"/>
+    <cellStyle name="Обычный 4 2 5 2 4" xfId="436"/>
+    <cellStyle name="Обычный 4 2 5 2 5" xfId="570"/>
+    <cellStyle name="Обычный 4 2 5 3" xfId="26"/>
+    <cellStyle name="Обычный 4 2 5 4" xfId="572"/>
+    <cellStyle name="Обычный 4 2 5 5" xfId="574"/>
+    <cellStyle name="Обычный 4 2 5 6" xfId="576"/>
+    <cellStyle name="Обычный 4 2 6" xfId="198"/>
+    <cellStyle name="Обычный 4 2 6 2" xfId="578"/>
+    <cellStyle name="Обычный 4 2 6 3" xfId="418"/>
+    <cellStyle name="Обычный 4 2 6 4" xfId="421"/>
+    <cellStyle name="Обычный 4 2 6 5" xfId="424"/>
+    <cellStyle name="Обычный 4 2 7" xfId="200"/>
+    <cellStyle name="Обычный 4 2 8" xfId="368"/>
+    <cellStyle name="Обычный 4 2 9" xfId="370"/>
+    <cellStyle name="Обычный 4 3" xfId="580"/>
+    <cellStyle name="Обычный 4 3 2" xfId="350"/>
+    <cellStyle name="Обычный 4 3 2 2" xfId="355"/>
+    <cellStyle name="Обычный 4 3 2 2 2" xfId="581"/>
+    <cellStyle name="Обычный 4 3 2 2 2 2" xfId="331"/>
+    <cellStyle name="Обычный 4 3 2 2 2 3" xfId="335"/>
+    <cellStyle name="Обычный 4 3 2 2 2 4" xfId="497"/>
+    <cellStyle name="Обычный 4 3 2 2 2 5" xfId="501"/>
+    <cellStyle name="Обычный 4 3 2 2 3" xfId="304"/>
+    <cellStyle name="Обычный 4 3 2 2 4" xfId="582"/>
+    <cellStyle name="Обычный 4 3 2 2 5" xfId="549"/>
+    <cellStyle name="Обычный 4 3 2 2 6" xfId="552"/>
+    <cellStyle name="Обычный 4 3 2 3" xfId="358"/>
+    <cellStyle name="Обычный 4 3 2 3 2" xfId="411"/>
+    <cellStyle name="Обычный 4 3 2 3 3" xfId="307"/>
+    <cellStyle name="Обычный 4 3 2 3 4" xfId="413"/>
+    <cellStyle name="Обычный 4 3 2 3 5" xfId="351"/>
+    <cellStyle name="Обычный 4 3 2 4" xfId="361"/>
+    <cellStyle name="Обычный 4 3 2 5" xfId="316"/>
+    <cellStyle name="Обычный 4 3 2 6" xfId="583"/>
+    <cellStyle name="Обычный 4 3 2 7" xfId="32"/>
+    <cellStyle name="Обычный 4 3 3" xfId="91"/>
+    <cellStyle name="Обычный 4 3 3 2" xfId="146"/>
+    <cellStyle name="Обычный 4 3 3 2 2" xfId="21"/>
+    <cellStyle name="Обычный 4 3 3 2 3" xfId="65"/>
+    <cellStyle name="Обычный 4 3 3 2 4" xfId="58"/>
+    <cellStyle name="Обычный 4 3 3 2 5" xfId="45"/>
+    <cellStyle name="Обычный 4 3 3 3" xfId="148"/>
+    <cellStyle name="Обычный 4 3 3 4" xfId="584"/>
+    <cellStyle name="Обычный 4 3 3 5" xfId="321"/>
+    <cellStyle name="Обычный 4 3 3 6" xfId="585"/>
+    <cellStyle name="Обычный 4 3 4" xfId="587"/>
+    <cellStyle name="Обычный 4 3 4 2" xfId="588"/>
+    <cellStyle name="Обычный 4 3 4 3" xfId="589"/>
+    <cellStyle name="Обычный 4 3 4 4" xfId="590"/>
+    <cellStyle name="Обычный 4 3 4 5" xfId="327"/>
+    <cellStyle name="Обычный 4 3 5" xfId="592"/>
+    <cellStyle name="Обычный 4 3 6" xfId="594"/>
+    <cellStyle name="Обычный 4 3 7" xfId="595"/>
+    <cellStyle name="Обычный 4 3 8" xfId="375"/>
+    <cellStyle name="Обычный 4 4" xfId="29"/>
+    <cellStyle name="Обычный 4 5" xfId="597"/>
+    <cellStyle name="Обычный 4 6" xfId="599"/>
+    <cellStyle name="Обычный 4 7" xfId="511"/>
+    <cellStyle name="Обычный 4 8" xfId="600"/>
+    <cellStyle name="Обычный 4 9" xfId="1646"/>
+    <cellStyle name="Обычный 4_Капекс_НВ_ 12.09.11" xfId="344"/>
+    <cellStyle name="Обычный 5" xfId="530"/>
+    <cellStyle name="Обычный 5 2" xfId="602"/>
+    <cellStyle name="Обычный 5 2 10" xfId="603"/>
+    <cellStyle name="Обычный 5 2 2" xfId="44"/>
+    <cellStyle name="Обычный 5 2 2 2" xfId="606"/>
+    <cellStyle name="Обычный 5 2 2 2 2" xfId="607"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2" xfId="608"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 2" xfId="101"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 3" xfId="609"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 4" xfId="610"/>
+    <cellStyle name="Обычный 5 2 2 2 2 2 5" xfId="611"/>
+    <cellStyle name="Обычный 5 2 2 2 2 3" xfId="612"/>
+    <cellStyle name="Обычный 5 2 2 2 2 4" xfId="613"/>
+    <cellStyle name="Обычный 5 2 2 2 2 5" xfId="614"/>
+    <cellStyle name="Обычный 5 2 2 2 2 6" xfId="615"/>
+    <cellStyle name="Обычный 5 2 2 2 3" xfId="616"/>
+    <cellStyle name="Обычный 5 2 2 2 3 2" xfId="617"/>
+    <cellStyle name="Обычный 5 2 2 2 3 3" xfId="618"/>
+    <cellStyle name="Обычный 5 2 2 2 3 4" xfId="155"/>
+    <cellStyle name="Обычный 5 2 2 2 3 5" xfId="159"/>
+    <cellStyle name="Обычный 5 2 2 2 4" xfId="619"/>
+    <cellStyle name="Обычный 5 2 2 2 5" xfId="620"/>
+    <cellStyle name="Обычный 5 2 2 2 6" xfId="621"/>
+    <cellStyle name="Обычный 5 2 2 2 7" xfId="622"/>
+    <cellStyle name="Обычный 5 2 2 3" xfId="625"/>
+    <cellStyle name="Обычный 5 2 2 3 2" xfId="627"/>
+    <cellStyle name="Обычный 5 2 2 3 2 2" xfId="628"/>
+    <cellStyle name="Обычный 5 2 2 3 2 3" xfId="629"/>
+    <cellStyle name="Обычный 5 2 2 3 2 4" xfId="630"/>
+    <cellStyle name="Обычный 5 2 2 3 2 5" xfId="631"/>
+    <cellStyle name="Обычный 5 2 2 3 3" xfId="633"/>
+    <cellStyle name="Обычный 5 2 2 3 4" xfId="635"/>
+    <cellStyle name="Обычный 5 2 2 3 5" xfId="637"/>
+    <cellStyle name="Обычный 5 2 2 3 6" xfId="639"/>
+    <cellStyle name="Обычный 5 2 2 4" xfId="642"/>
+    <cellStyle name="Обычный 5 2 2 4 2" xfId="643"/>
+    <cellStyle name="Обычный 5 2 2 4 3" xfId="644"/>
+    <cellStyle name="Обычный 5 2 2 4 4" xfId="646"/>
+    <cellStyle name="Обычный 5 2 2 4 5" xfId="648"/>
+    <cellStyle name="Обычный 5 2 2 5" xfId="650"/>
+    <cellStyle name="Обычный 5 2 2 6" xfId="652"/>
+    <cellStyle name="Обычный 5 2 2 7" xfId="653"/>
+    <cellStyle name="Обычный 5 2 2 8" xfId="654"/>
+    <cellStyle name="Обычный 5 2 3" xfId="656"/>
+    <cellStyle name="Обычный 5 2 3 2" xfId="658"/>
+    <cellStyle name="Обычный 5 2 3 2 2" xfId="659"/>
+    <cellStyle name="Обычный 5 2 3 2 2 2" xfId="660"/>
+    <cellStyle name="Обычный 5 2 3 2 2 3" xfId="661"/>
+    <cellStyle name="Обычный 5 2 3 2 2 4" xfId="662"/>
+    <cellStyle name="Обычный 5 2 3 2 2 5" xfId="663"/>
+    <cellStyle name="Обычный 5 2 3 2 3" xfId="664"/>
+    <cellStyle name="Обычный 5 2 3 2 4" xfId="665"/>
+    <cellStyle name="Обычный 5 2 3 2 5" xfId="666"/>
+    <cellStyle name="Обычный 5 2 3 2 6" xfId="667"/>
+    <cellStyle name="Обычный 5 2 3 3" xfId="669"/>
+    <cellStyle name="Обычный 5 2 3 3 2" xfId="670"/>
+    <cellStyle name="Обычный 5 2 3 3 3" xfId="671"/>
+    <cellStyle name="Обычный 5 2 3 3 4" xfId="672"/>
+    <cellStyle name="Обычный 5 2 3 3 5" xfId="673"/>
+    <cellStyle name="Обычный 5 2 3 4" xfId="675"/>
+    <cellStyle name="Обычный 5 2 3 5" xfId="677"/>
+    <cellStyle name="Обычный 5 2 3 6" xfId="678"/>
+    <cellStyle name="Обычный 5 2 3 7" xfId="679"/>
+    <cellStyle name="Обычный 5 2 4" xfId="681"/>
+    <cellStyle name="Обычный 5 2 4 2" xfId="683"/>
+    <cellStyle name="Обычный 5 2 4 2 2" xfId="684"/>
+    <cellStyle name="Обычный 5 2 4 2 3" xfId="685"/>
+    <cellStyle name="Обычный 5 2 4 2 4" xfId="686"/>
+    <cellStyle name="Обычный 5 2 4 2 5" xfId="687"/>
+    <cellStyle name="Обычный 5 2 4 3" xfId="689"/>
+    <cellStyle name="Обычный 5 2 4 4" xfId="691"/>
+    <cellStyle name="Обычный 5 2 4 5" xfId="692"/>
+    <cellStyle name="Обычный 5 2 4 6" xfId="694"/>
+    <cellStyle name="Обычный 5 2 5" xfId="696"/>
+    <cellStyle name="Обычный 5 2 5 2" xfId="697"/>
+    <cellStyle name="Обычный 5 2 5 2 2" xfId="698"/>
+    <cellStyle name="Обычный 5 2 5 2 3" xfId="699"/>
+    <cellStyle name="Обычный 5 2 5 2 4" xfId="700"/>
+    <cellStyle name="Обычный 5 2 5 2 5" xfId="701"/>
+    <cellStyle name="Обычный 5 2 5 3" xfId="702"/>
+    <cellStyle name="Обычный 5 2 5 4" xfId="703"/>
+    <cellStyle name="Обычный 5 2 5 5" xfId="704"/>
+    <cellStyle name="Обычный 5 2 5 6" xfId="705"/>
+    <cellStyle name="Обычный 5 2 6" xfId="706"/>
+    <cellStyle name="Обычный 5 2 6 2" xfId="707"/>
+    <cellStyle name="Обычный 5 2 6 3" xfId="708"/>
+    <cellStyle name="Обычный 5 2 6 4" xfId="709"/>
+    <cellStyle name="Обычный 5 2 6 5" xfId="710"/>
+    <cellStyle name="Обычный 5 2 7" xfId="711"/>
+    <cellStyle name="Обычный 5 2 8" xfId="712"/>
+    <cellStyle name="Обычный 5 2 9" xfId="713"/>
+    <cellStyle name="Обычный 5 3" xfId="715"/>
+    <cellStyle name="Обычный 5 3 2" xfId="716"/>
+    <cellStyle name="Обычный 5 4" xfId="718"/>
+    <cellStyle name="Обычный 5 4 2" xfId="719"/>
+    <cellStyle name="Обычный 5 5" xfId="721"/>
+    <cellStyle name="Обычный 5 5 2" xfId="722"/>
+    <cellStyle name="Обычный 5 6" xfId="725"/>
+    <cellStyle name="Обычный 5 6 2" xfId="726"/>
+    <cellStyle name="Обычный 5 7" xfId="728"/>
+    <cellStyle name="Обычный 5 7 2" xfId="729"/>
+    <cellStyle name="Обычный 6" xfId="3"/>
+    <cellStyle name="Обычный 6 10" xfId="731"/>
+    <cellStyle name="Обычный 6 11" xfId="732"/>
+    <cellStyle name="Обычный 6 12" xfId="730"/>
+    <cellStyle name="Обычный 6 2" xfId="735"/>
+    <cellStyle name="Обычный 6 2 2" xfId="737"/>
+    <cellStyle name="Обычный 6 2 2 2" xfId="739"/>
+    <cellStyle name="Обычный 6 2 2 2 2" xfId="740"/>
+    <cellStyle name="Обычный 6 2 2 2 2 2" xfId="741"/>
+    <cellStyle name="Обычный 6 2 2 2 2 3" xfId="742"/>
+    <cellStyle name="Обычный 6 2 2 2 2 4" xfId="743"/>
+    <cellStyle name="Обычный 6 2 2 2 2 5" xfId="744"/>
+    <cellStyle name="Обычный 6 2 2 2 3" xfId="746"/>
+    <cellStyle name="Обычный 6 2 2 2 4" xfId="747"/>
+    <cellStyle name="Обычный 6 2 2 2 5" xfId="748"/>
+    <cellStyle name="Обычный 6 2 2 2 6" xfId="749"/>
+    <cellStyle name="Обычный 6 2 2 3" xfId="751"/>
+    <cellStyle name="Обычный 6 2 2 3 2" xfId="752"/>
+    <cellStyle name="Обычный 6 2 2 3 3" xfId="754"/>
+    <cellStyle name="Обычный 6 2 2 3 4" xfId="755"/>
+    <cellStyle name="Обычный 6 2 2 3 5" xfId="756"/>
+    <cellStyle name="Обычный 6 2 2 4" xfId="757"/>
+    <cellStyle name="Обычный 6 2 2 5" xfId="758"/>
+    <cellStyle name="Обычный 6 2 2 6" xfId="759"/>
+    <cellStyle name="Обычный 6 2 2 7" xfId="760"/>
+    <cellStyle name="Обычный 6 2 3" xfId="762"/>
+    <cellStyle name="Обычный 6 2 3 2" xfId="764"/>
+    <cellStyle name="Обычный 6 2 3 2 2" xfId="765"/>
+    <cellStyle name="Обычный 6 2 3 2 3" xfId="766"/>
+    <cellStyle name="Обычный 6 2 3 2 4" xfId="767"/>
+    <cellStyle name="Обычный 6 2 3 2 5" xfId="768"/>
+    <cellStyle name="Обычный 6 2 3 3" xfId="769"/>
+    <cellStyle name="Обычный 6 2 3 4" xfId="770"/>
+    <cellStyle name="Обычный 6 2 3 5" xfId="771"/>
+    <cellStyle name="Обычный 6 2 3 6" xfId="772"/>
+    <cellStyle name="Обычный 6 2 4" xfId="775"/>
+    <cellStyle name="Обычный 6 2 4 2" xfId="776"/>
+    <cellStyle name="Обычный 6 2 4 3" xfId="777"/>
+    <cellStyle name="Обычный 6 2 4 4" xfId="778"/>
+    <cellStyle name="Обычный 6 2 4 5" xfId="779"/>
+    <cellStyle name="Обычный 6 2 5" xfId="782"/>
+    <cellStyle name="Обычный 6 2 6" xfId="784"/>
+    <cellStyle name="Обычный 6 2 7" xfId="786"/>
+    <cellStyle name="Обычный 6 2 8" xfId="787"/>
+    <cellStyle name="Обычный 6 3" xfId="790"/>
+    <cellStyle name="Обычный 6 3 2" xfId="791"/>
+    <cellStyle name="Обычный 6 3 2 2" xfId="792"/>
+    <cellStyle name="Обычный 6 3 2 2 2" xfId="793"/>
+    <cellStyle name="Обычный 6 3 2 2 3" xfId="794"/>
+    <cellStyle name="Обычный 6 3 2 2 4" xfId="795"/>
+    <cellStyle name="Обычный 6 3 2 2 5" xfId="796"/>
+    <cellStyle name="Обычный 6 3 2 3" xfId="797"/>
+    <cellStyle name="Обычный 6 3 2 4" xfId="798"/>
+    <cellStyle name="Обычный 6 3 2 5" xfId="799"/>
+    <cellStyle name="Обычный 6 3 2 6" xfId="471"/>
+    <cellStyle name="Обычный 6 3 3" xfId="800"/>
+    <cellStyle name="Обычный 6 3 3 2" xfId="801"/>
+    <cellStyle name="Обычный 6 3 3 3" xfId="802"/>
+    <cellStyle name="Обычный 6 3 3 4" xfId="803"/>
+    <cellStyle name="Обычный 6 3 3 5" xfId="804"/>
+    <cellStyle name="Обычный 6 3 4" xfId="805"/>
+    <cellStyle name="Обычный 6 3 5" xfId="806"/>
+    <cellStyle name="Обычный 6 3 6" xfId="807"/>
+    <cellStyle name="Обычный 6 3 7" xfId="808"/>
+    <cellStyle name="Обычный 6 4" xfId="811"/>
+    <cellStyle name="Обычный 6 4 2" xfId="812"/>
+    <cellStyle name="Обычный 6 4 2 2" xfId="813"/>
+    <cellStyle name="Обычный 6 4 2 3" xfId="814"/>
+    <cellStyle name="Обычный 6 4 2 4" xfId="815"/>
+    <cellStyle name="Обычный 6 4 2 5" xfId="816"/>
+    <cellStyle name="Обычный 6 4 3" xfId="817"/>
+    <cellStyle name="Обычный 6 4 4" xfId="818"/>
+    <cellStyle name="Обычный 6 4 5" xfId="819"/>
+    <cellStyle name="Обычный 6 4 6" xfId="820"/>
+    <cellStyle name="Обычный 6 5" xfId="822"/>
+    <cellStyle name="Обычный 6 5 2" xfId="825"/>
+    <cellStyle name="Обычный 6 5 2 2" xfId="828"/>
+    <cellStyle name="Обычный 6 5 2 3" xfId="830"/>
+    <cellStyle name="Обычный 6 5 2 4" xfId="832"/>
+    <cellStyle name="Обычный 6 5 2 5" xfId="834"/>
+    <cellStyle name="Обычный 6 5 3" xfId="24"/>
+    <cellStyle name="Обычный 6 5 4" xfId="837"/>
+    <cellStyle name="Обычный 6 5 5" xfId="840"/>
+    <cellStyle name="Обычный 6 5 6" xfId="843"/>
+    <cellStyle name="Обычный 6 6" xfId="845"/>
+    <cellStyle name="Обычный 6 6 2" xfId="846"/>
+    <cellStyle name="Обычный 6 6 2 2" xfId="847"/>
+    <cellStyle name="Обычный 6 6 2 3" xfId="848"/>
+    <cellStyle name="Обычный 6 6 2 4" xfId="849"/>
+    <cellStyle name="Обычный 6 6 2 5" xfId="850"/>
+    <cellStyle name="Обычный 6 6 3" xfId="851"/>
+    <cellStyle name="Обычный 6 6 4" xfId="852"/>
+    <cellStyle name="Обычный 6 6 5" xfId="853"/>
+    <cellStyle name="Обычный 6 6 6" xfId="854"/>
+    <cellStyle name="Обычный 6 7" xfId="855"/>
+    <cellStyle name="Обычный 6 7 2" xfId="856"/>
+    <cellStyle name="Обычный 6 7 3" xfId="857"/>
+    <cellStyle name="Обычный 6 7 4" xfId="858"/>
+    <cellStyle name="Обычный 6 7 5" xfId="859"/>
+    <cellStyle name="Обычный 6 8" xfId="860"/>
+    <cellStyle name="Обычный 6 9" xfId="861"/>
+    <cellStyle name="Обычный 7" xfId="862"/>
+    <cellStyle name="Обычный 7 10" xfId="863"/>
+    <cellStyle name="Обычный 7 11" xfId="864"/>
+    <cellStyle name="Обычный 7 2" xfId="866"/>
+    <cellStyle name="Обычный 7 2 2" xfId="868"/>
+    <cellStyle name="Обычный 7 2 2 2" xfId="869"/>
+    <cellStyle name="Обычный 7 2 2 2 2" xfId="870"/>
+    <cellStyle name="Обычный 7 2 2 2 2 2" xfId="873"/>
+    <cellStyle name="Обычный 7 2 2 2 2 3" xfId="876"/>
+    <cellStyle name="Обычный 7 2 2 2 2 4" xfId="878"/>
+    <cellStyle name="Обычный 7 2 2 2 2 5" xfId="879"/>
+    <cellStyle name="Обычный 7 2 2 2 3" xfId="880"/>
+    <cellStyle name="Обычный 7 2 2 2 4" xfId="881"/>
+    <cellStyle name="Обычный 7 2 2 2 5" xfId="882"/>
+    <cellStyle name="Обычный 7 2 2 2 6" xfId="883"/>
+    <cellStyle name="Обычный 7 2 2 3" xfId="885"/>
+    <cellStyle name="Обычный 7 2 2 3 2" xfId="887"/>
+    <cellStyle name="Обычный 7 2 2 3 3" xfId="889"/>
+    <cellStyle name="Обычный 7 2 2 3 4" xfId="891"/>
+    <cellStyle name="Обычный 7 2 2 3 5" xfId="893"/>
+    <cellStyle name="Обычный 7 2 2 4" xfId="895"/>
+    <cellStyle name="Обычный 7 2 2 5" xfId="734"/>
+    <cellStyle name="Обычный 7 2 2 6" xfId="789"/>
+    <cellStyle name="Обычный 7 2 2 7" xfId="810"/>
+    <cellStyle name="Обычный 7 2 3" xfId="896"/>
+    <cellStyle name="Обычный 7 2 3 2" xfId="898"/>
+    <cellStyle name="Обычный 7 2 3 2 2" xfId="899"/>
+    <cellStyle name="Обычный 7 2 3 2 3" xfId="901"/>
+    <cellStyle name="Обычный 7 2 3 2 4" xfId="903"/>
+    <cellStyle name="Обычный 7 2 3 2 5" xfId="905"/>
+    <cellStyle name="Обычный 7 2 3 3" xfId="908"/>
+    <cellStyle name="Обычный 7 2 3 4" xfId="910"/>
+    <cellStyle name="Обычный 7 2 3 5" xfId="865"/>
+    <cellStyle name="Обычный 7 2 3 6" xfId="912"/>
+    <cellStyle name="Обычный 7 2 4" xfId="913"/>
+    <cellStyle name="Обычный 7 2 4 2" xfId="915"/>
+    <cellStyle name="Обычный 7 2 4 3" xfId="918"/>
+    <cellStyle name="Обычный 7 2 4 4" xfId="919"/>
+    <cellStyle name="Обычный 7 2 4 5" xfId="921"/>
+    <cellStyle name="Обычный 7 2 5" xfId="922"/>
+    <cellStyle name="Обычный 7 2 6" xfId="923"/>
+    <cellStyle name="Обычный 7 2 7" xfId="924"/>
+    <cellStyle name="Обычный 7 2 8" xfId="925"/>
+    <cellStyle name="Обычный 7 3" xfId="911"/>
+    <cellStyle name="Обычный 7 3 2" xfId="926"/>
+    <cellStyle name="Обычный 7 3 2 2" xfId="20"/>
+    <cellStyle name="Обычный 7 3 2 2 2" xfId="928"/>
+    <cellStyle name="Обычный 7 3 2 2 3" xfId="872"/>
+    <cellStyle name="Обычный 7 3 2 2 4" xfId="875"/>
+    <cellStyle name="Обычный 7 3 2 2 5" xfId="877"/>
+    <cellStyle name="Обычный 7 3 2 3" xfId="66"/>
+    <cellStyle name="Обычный 7 3 2 4" xfId="59"/>
+    <cellStyle name="Обычный 7 3 2 5" xfId="47"/>
+    <cellStyle name="Обычный 7 3 2 6" xfId="930"/>
+    <cellStyle name="Обычный 7 3 3" xfId="931"/>
+    <cellStyle name="Обычный 7 3 3 2" xfId="933"/>
+    <cellStyle name="Обычный 7 3 3 3" xfId="935"/>
+    <cellStyle name="Обычный 7 3 3 4" xfId="937"/>
+    <cellStyle name="Обычный 7 3 3 5" xfId="939"/>
+    <cellStyle name="Обычный 7 3 4" xfId="940"/>
+    <cellStyle name="Обычный 7 3 5" xfId="941"/>
+    <cellStyle name="Обычный 7 3 6" xfId="942"/>
+    <cellStyle name="Обычный 7 3 7" xfId="943"/>
+    <cellStyle name="Обычный 7 4" xfId="944"/>
+    <cellStyle name="Обычный 7 4 2" xfId="945"/>
+    <cellStyle name="Обычный 7 4 2 2" xfId="946"/>
+    <cellStyle name="Обычный 7 4 2 3" xfId="947"/>
+    <cellStyle name="Обычный 7 4 2 4" xfId="948"/>
+    <cellStyle name="Обычный 7 4 2 5" xfId="949"/>
+    <cellStyle name="Обычный 7 4 3" xfId="950"/>
+    <cellStyle name="Обычный 7 4 4" xfId="951"/>
+    <cellStyle name="Обычный 7 4 5" xfId="952"/>
+    <cellStyle name="Обычный 7 4 6" xfId="953"/>
+    <cellStyle name="Обычный 7 5" xfId="954"/>
+    <cellStyle name="Обычный 7 5 2" xfId="955"/>
+    <cellStyle name="Обычный 7 5 2 2" xfId="956"/>
+    <cellStyle name="Обычный 7 5 2 3" xfId="957"/>
+    <cellStyle name="Обычный 7 5 2 4" xfId="958"/>
+    <cellStyle name="Обычный 7 5 2 5" xfId="959"/>
+    <cellStyle name="Обычный 7 5 3" xfId="960"/>
+    <cellStyle name="Обычный 7 5 4" xfId="961"/>
+    <cellStyle name="Обычный 7 5 5" xfId="962"/>
+    <cellStyle name="Обычный 7 5 6" xfId="963"/>
+    <cellStyle name="Обычный 7 6" xfId="964"/>
+    <cellStyle name="Обычный 7 6 2" xfId="965"/>
+    <cellStyle name="Обычный 7 6 2 2" xfId="966"/>
+    <cellStyle name="Обычный 7 6 2 3" xfId="968"/>
+    <cellStyle name="Обычный 7 6 2 4" xfId="970"/>
+    <cellStyle name="Обычный 7 6 2 5" xfId="971"/>
+    <cellStyle name="Обычный 7 6 3" xfId="972"/>
+    <cellStyle name="Обычный 7 6 4" xfId="973"/>
+    <cellStyle name="Обычный 7 6 5" xfId="974"/>
+    <cellStyle name="Обычный 7 6 6" xfId="343"/>
+    <cellStyle name="Обычный 7 7" xfId="975"/>
+    <cellStyle name="Обычный 7 7 2" xfId="976"/>
+    <cellStyle name="Обычный 7 7 3" xfId="977"/>
+    <cellStyle name="Обычный 7 7 4" xfId="978"/>
+    <cellStyle name="Обычный 7 7 5" xfId="979"/>
+    <cellStyle name="Обычный 7 8" xfId="980"/>
+    <cellStyle name="Обычный 7 9" xfId="192"/>
+    <cellStyle name="Обычный 8" xfId="981"/>
+    <cellStyle name="Обычный 8 2" xfId="920"/>
+    <cellStyle name="Обычный 9" xfId="982"/>
+    <cellStyle name="Обычный 9 2" xfId="984"/>
     <cellStyle name="Процентный" xfId="13" builtinId="5"/>
-    <cellStyle name="Стиль 1" xfId="693" xr:uid="{00000000-0005-0000-0000-000010030000}"/>
-    <cellStyle name="Стиль 1 2" xfId="985" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
-    <cellStyle name="Стиль 1 2 2" xfId="986" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
-    <cellStyle name="Стиль 1 3" xfId="987" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
-    <cellStyle name="Стиль 1 3 2" xfId="988" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
-    <cellStyle name="Стиль 1 4" xfId="989" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
-    <cellStyle name="Стиль 1 4 2" xfId="990" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
-    <cellStyle name="Стиль 1 5" xfId="991" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
-    <cellStyle name="Стиль 1 5 2" xfId="993" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
-    <cellStyle name="Финансовый 2" xfId="994" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
-    <cellStyle name="Финансовый 2 10" xfId="995" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
-    <cellStyle name="Финансовый 2 10 2" xfId="997" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
-    <cellStyle name="Финансовый 2 2" xfId="221" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
-    <cellStyle name="Финансовый 2 3" xfId="236" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
-    <cellStyle name="Финансовый 2 4" xfId="260" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
-    <cellStyle name="Финансовый 2 4 2" xfId="263" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
-    <cellStyle name="Финансовый 2 5" xfId="272" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
-    <cellStyle name="Финансовый 2 5 2" xfId="998" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
-    <cellStyle name="Финансовый 2 6" xfId="274" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
-    <cellStyle name="Финансовый 2 6 2" xfId="999" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
-    <cellStyle name="Финансовый 2 7" xfId="276" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
-    <cellStyle name="Финансовый 2 7 2" xfId="1001" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
-    <cellStyle name="Финансовый 2 8" xfId="1003" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
-    <cellStyle name="Финансовый 2 8 2" xfId="1005" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
-    <cellStyle name="Финансовый 2 9" xfId="1007" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
-    <cellStyle name="Финансовый 2 9 2" xfId="1009" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
-    <cellStyle name="Финансовый 3" xfId="33" xr:uid="{00000000-0005-0000-0000-00002A030000}"/>
-    <cellStyle name="Финансовый 4" xfId="1642" xr:uid="{00000000-0005-0000-0000-00002B030000}"/>
-    <cellStyle name="Финансовый 5" xfId="1651" xr:uid="{00000000-0005-0000-0000-00002C030000}"/>
-    <cellStyle name="千位分隔 10" xfId="1464" xr:uid="{00000000-0005-0000-0000-00002D030000}"/>
-    <cellStyle name="千位分隔 10 2" xfId="1465" xr:uid="{00000000-0005-0000-0000-00002E030000}"/>
-    <cellStyle name="千位分隔 10 2 2" xfId="1466" xr:uid="{00000000-0005-0000-0000-00002F030000}"/>
-    <cellStyle name="千位分隔 10 2 3" xfId="1467" xr:uid="{00000000-0005-0000-0000-000030030000}"/>
-    <cellStyle name="千位分隔 10 2 4" xfId="1468" xr:uid="{00000000-0005-0000-0000-000031030000}"/>
-    <cellStyle name="千位分隔 10 2 5" xfId="1469" xr:uid="{00000000-0005-0000-0000-000032030000}"/>
-    <cellStyle name="千位分隔 10 3" xfId="1470" xr:uid="{00000000-0005-0000-0000-000033030000}"/>
-    <cellStyle name="千位分隔 10 4" xfId="1471" xr:uid="{00000000-0005-0000-0000-000034030000}"/>
-    <cellStyle name="千位分隔 10 5" xfId="1472" xr:uid="{00000000-0005-0000-0000-000035030000}"/>
-    <cellStyle name="千位分隔 10 6" xfId="1473" xr:uid="{00000000-0005-0000-0000-000036030000}"/>
-    <cellStyle name="千位分隔 11" xfId="1474" xr:uid="{00000000-0005-0000-0000-000037030000}"/>
-    <cellStyle name="千位分隔 11 2" xfId="1475" xr:uid="{00000000-0005-0000-0000-000038030000}"/>
-    <cellStyle name="千位分隔 12" xfId="1476" xr:uid="{00000000-0005-0000-0000-000039030000}"/>
-    <cellStyle name="千位分隔 12 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00003A030000}"/>
-    <cellStyle name="千位分隔 12 2 2" xfId="1328" xr:uid="{00000000-0005-0000-0000-00003B030000}"/>
-    <cellStyle name="千位分隔 12 2 3" xfId="1477" xr:uid="{00000000-0005-0000-0000-00003C030000}"/>
-    <cellStyle name="千位分隔 12 2 4" xfId="1478" xr:uid="{00000000-0005-0000-0000-00003D030000}"/>
-    <cellStyle name="千位分隔 12 2 5" xfId="1479" xr:uid="{00000000-0005-0000-0000-00003E030000}"/>
-    <cellStyle name="千位分隔 12 3" xfId="929" xr:uid="{00000000-0005-0000-0000-00003F030000}"/>
-    <cellStyle name="千位分隔 12 4" xfId="1480" xr:uid="{00000000-0005-0000-0000-000040030000}"/>
-    <cellStyle name="千位分隔 12 5" xfId="1481" xr:uid="{00000000-0005-0000-0000-000041030000}"/>
-    <cellStyle name="千位分隔 12 6" xfId="1482" xr:uid="{00000000-0005-0000-0000-000042030000}"/>
-    <cellStyle name="千位分隔 13" xfId="14" xr:uid="{00000000-0005-0000-0000-000043030000}"/>
-    <cellStyle name="千位分隔 13 2" xfId="938" xr:uid="{00000000-0005-0000-0000-000044030000}"/>
-    <cellStyle name="千位分隔 13 2 2" xfId="1383" xr:uid="{00000000-0005-0000-0000-000045030000}"/>
-    <cellStyle name="千位分隔 13 2 3" xfId="1484" xr:uid="{00000000-0005-0000-0000-000046030000}"/>
-    <cellStyle name="千位分隔 13 2 4" xfId="1485" xr:uid="{00000000-0005-0000-0000-000047030000}"/>
-    <cellStyle name="千位分隔 13 2 5" xfId="1486" xr:uid="{00000000-0005-0000-0000-000048030000}"/>
-    <cellStyle name="千位分隔 13 3" xfId="1487" xr:uid="{00000000-0005-0000-0000-000049030000}"/>
-    <cellStyle name="千位分隔 13 4" xfId="1488" xr:uid="{00000000-0005-0000-0000-00004A030000}"/>
-    <cellStyle name="千位分隔 13 5" xfId="1489" xr:uid="{00000000-0005-0000-0000-00004B030000}"/>
-    <cellStyle name="千位分隔 13 6" xfId="1490" xr:uid="{00000000-0005-0000-0000-00004C030000}"/>
-    <cellStyle name="千位分隔 13 7" xfId="1483" xr:uid="{00000000-0005-0000-0000-00004D030000}"/>
-    <cellStyle name="千位分隔 14" xfId="1491" xr:uid="{00000000-0005-0000-0000-00004E030000}"/>
-    <cellStyle name="千位分隔 14 2" xfId="1492" xr:uid="{00000000-0005-0000-0000-00004F030000}"/>
-    <cellStyle name="千位分隔 14 2 2" xfId="1493" xr:uid="{00000000-0005-0000-0000-000050030000}"/>
-    <cellStyle name="千位分隔 14 2 3" xfId="1494" xr:uid="{00000000-0005-0000-0000-000051030000}"/>
-    <cellStyle name="千位分隔 14 2 4" xfId="1495" xr:uid="{00000000-0005-0000-0000-000052030000}"/>
-    <cellStyle name="千位分隔 14 2 5" xfId="1496" xr:uid="{00000000-0005-0000-0000-000053030000}"/>
-    <cellStyle name="千位分隔 14 3" xfId="1497" xr:uid="{00000000-0005-0000-0000-000054030000}"/>
-    <cellStyle name="千位分隔 14 4" xfId="1498" xr:uid="{00000000-0005-0000-0000-000055030000}"/>
-    <cellStyle name="千位分隔 14 5" xfId="1499" xr:uid="{00000000-0005-0000-0000-000056030000}"/>
-    <cellStyle name="千位分隔 14 6" xfId="1500" xr:uid="{00000000-0005-0000-0000-000057030000}"/>
-    <cellStyle name="千位分隔 15" xfId="9" xr:uid="{00000000-0005-0000-0000-000058030000}"/>
-    <cellStyle name="千位分隔 15 2" xfId="1503" xr:uid="{00000000-0005-0000-0000-000059030000}"/>
-    <cellStyle name="千位分隔 15 3" xfId="1504" xr:uid="{00000000-0005-0000-0000-00005A030000}"/>
-    <cellStyle name="千位分隔 15 4" xfId="1505" xr:uid="{00000000-0005-0000-0000-00005B030000}"/>
-    <cellStyle name="千位分隔 15 5" xfId="1506" xr:uid="{00000000-0005-0000-0000-00005C030000}"/>
-    <cellStyle name="千位分隔 15 6" xfId="1502" xr:uid="{00000000-0005-0000-0000-00005D030000}"/>
-    <cellStyle name="千位分隔 16" xfId="605" xr:uid="{00000000-0005-0000-0000-00005E030000}"/>
-    <cellStyle name="千位分隔 17" xfId="624" xr:uid="{00000000-0005-0000-0000-00005F030000}"/>
-    <cellStyle name="千位分隔 17 2" xfId="626" xr:uid="{00000000-0005-0000-0000-000060030000}"/>
-    <cellStyle name="千位分隔 17 3" xfId="632" xr:uid="{00000000-0005-0000-0000-000061030000}"/>
-    <cellStyle name="千位分隔 18" xfId="11" xr:uid="{00000000-0005-0000-0000-000062030000}"/>
-    <cellStyle name="千位分隔 18 2" xfId="641" xr:uid="{00000000-0005-0000-0000-000063030000}"/>
-    <cellStyle name="千位分隔 19" xfId="16" xr:uid="{00000000-0005-0000-0000-000064030000}"/>
-    <cellStyle name="千位分隔 2" xfId="296" xr:uid="{00000000-0005-0000-0000-000065030000}"/>
-    <cellStyle name="千位分隔 2 10" xfId="1507" xr:uid="{00000000-0005-0000-0000-000066030000}"/>
-    <cellStyle name="千位分隔 2 11" xfId="1508" xr:uid="{00000000-0005-0000-0000-000067030000}"/>
-    <cellStyle name="千位分隔 2 12" xfId="290" xr:uid="{00000000-0005-0000-0000-000068030000}"/>
-    <cellStyle name="千位分隔 2 2" xfId="1509" xr:uid="{00000000-0005-0000-0000-000069030000}"/>
-    <cellStyle name="千位分隔 2 2 2" xfId="1287" xr:uid="{00000000-0005-0000-0000-00006A030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2" xfId="1510" xr:uid="{00000000-0005-0000-0000-00006B030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2" xfId="1511" xr:uid="{00000000-0005-0000-0000-00006C030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 2" xfId="1512" xr:uid="{00000000-0005-0000-0000-00006D030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 3" xfId="1513" xr:uid="{00000000-0005-0000-0000-00006E030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 4" xfId="1514" xr:uid="{00000000-0005-0000-0000-00006F030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 2 5" xfId="1515" xr:uid="{00000000-0005-0000-0000-000070030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 3" xfId="1516" xr:uid="{00000000-0005-0000-0000-000071030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 4" xfId="1517" xr:uid="{00000000-0005-0000-0000-000072030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 5" xfId="1518" xr:uid="{00000000-0005-0000-0000-000073030000}"/>
-    <cellStyle name="千位分隔 2 2 2 2 6" xfId="1089" xr:uid="{00000000-0005-0000-0000-000074030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3" xfId="1519" xr:uid="{00000000-0005-0000-0000-000075030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 2" xfId="1520" xr:uid="{00000000-0005-0000-0000-000076030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 3" xfId="1521" xr:uid="{00000000-0005-0000-0000-000077030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 4" xfId="1522" xr:uid="{00000000-0005-0000-0000-000078030000}"/>
-    <cellStyle name="千位分隔 2 2 2 3 5" xfId="1523" xr:uid="{00000000-0005-0000-0000-000079030000}"/>
-    <cellStyle name="千位分隔 2 2 2 4" xfId="1524" xr:uid="{00000000-0005-0000-0000-00007A030000}"/>
-    <cellStyle name="千位分隔 2 2 2 5" xfId="1525" xr:uid="{00000000-0005-0000-0000-00007B030000}"/>
-    <cellStyle name="千位分隔 2 2 2 6" xfId="1526" xr:uid="{00000000-0005-0000-0000-00007C030000}"/>
-    <cellStyle name="千位分隔 2 2 2 7" xfId="1527" xr:uid="{00000000-0005-0000-0000-00007D030000}"/>
-    <cellStyle name="千位分隔 2 2 3" xfId="1528" xr:uid="{00000000-0005-0000-0000-00007E030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2" xfId="1529" xr:uid="{00000000-0005-0000-0000-00007F030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 2" xfId="1530" xr:uid="{00000000-0005-0000-0000-000080030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 3" xfId="1531" xr:uid="{00000000-0005-0000-0000-000081030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 4" xfId="1532" xr:uid="{00000000-0005-0000-0000-000082030000}"/>
-    <cellStyle name="千位分隔 2 2 3 2 5" xfId="1533" xr:uid="{00000000-0005-0000-0000-000083030000}"/>
-    <cellStyle name="千位分隔 2 2 3 3" xfId="1534" xr:uid="{00000000-0005-0000-0000-000084030000}"/>
-    <cellStyle name="千位分隔 2 2 3 4" xfId="1535" xr:uid="{00000000-0005-0000-0000-000085030000}"/>
-    <cellStyle name="千位分隔 2 2 3 5" xfId="1536" xr:uid="{00000000-0005-0000-0000-000086030000}"/>
-    <cellStyle name="千位分隔 2 2 3 6" xfId="1537" xr:uid="{00000000-0005-0000-0000-000087030000}"/>
-    <cellStyle name="千位分隔 2 2 4" xfId="992" xr:uid="{00000000-0005-0000-0000-000088030000}"/>
-    <cellStyle name="千位分隔 2 2 4 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000089030000}"/>
-    <cellStyle name="千位分隔 2 2 4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00008A030000}"/>
-    <cellStyle name="千位分隔 2 2 4 4" xfId="68" xr:uid="{00000000-0005-0000-0000-00008B030000}"/>
-    <cellStyle name="千位分隔 2 2 4 5" xfId="72" xr:uid="{00000000-0005-0000-0000-00008C030000}"/>
-    <cellStyle name="千位分隔 2 2 5" xfId="1203" xr:uid="{00000000-0005-0000-0000-00008D030000}"/>
-    <cellStyle name="千位分隔 2 2 6" xfId="1205" xr:uid="{00000000-0005-0000-0000-00008E030000}"/>
-    <cellStyle name="千位分隔 2 2 7" xfId="512" xr:uid="{00000000-0005-0000-0000-00008F030000}"/>
-    <cellStyle name="千位分隔 2 2 8" xfId="1207" xr:uid="{00000000-0005-0000-0000-000090030000}"/>
-    <cellStyle name="千位分隔 2 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000091030000}"/>
-    <cellStyle name="千位分隔 2 3 2" xfId="1300" xr:uid="{00000000-0005-0000-0000-000092030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2" xfId="1539" xr:uid="{00000000-0005-0000-0000-000093030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 2" xfId="724" xr:uid="{00000000-0005-0000-0000-000094030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 3" xfId="727" xr:uid="{00000000-0005-0000-0000-000095030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 4" xfId="1540" xr:uid="{00000000-0005-0000-0000-000096030000}"/>
-    <cellStyle name="千位分隔 2 3 2 2 5" xfId="1541" xr:uid="{00000000-0005-0000-0000-000097030000}"/>
-    <cellStyle name="千位分隔 2 3 2 3" xfId="1542" xr:uid="{00000000-0005-0000-0000-000098030000}"/>
-    <cellStyle name="千位分隔 2 3 2 4" xfId="1543" xr:uid="{00000000-0005-0000-0000-000099030000}"/>
-    <cellStyle name="千位分隔 2 3 2 5" xfId="1544" xr:uid="{00000000-0005-0000-0000-00009A030000}"/>
-    <cellStyle name="千位分隔 2 3 2 6" xfId="1545" xr:uid="{00000000-0005-0000-0000-00009B030000}"/>
-    <cellStyle name="千位分隔 2 3 3" xfId="1546" xr:uid="{00000000-0005-0000-0000-00009C030000}"/>
-    <cellStyle name="千位分隔 2 3 3 2" xfId="1547" xr:uid="{00000000-0005-0000-0000-00009D030000}"/>
-    <cellStyle name="千位分隔 2 3 3 3" xfId="1548" xr:uid="{00000000-0005-0000-0000-00009E030000}"/>
-    <cellStyle name="千位分隔 2 3 3 4" xfId="1549" xr:uid="{00000000-0005-0000-0000-00009F030000}"/>
-    <cellStyle name="千位分隔 2 3 3 5" xfId="1550" xr:uid="{00000000-0005-0000-0000-0000A0030000}"/>
-    <cellStyle name="千位分隔 2 3 4" xfId="1551" xr:uid="{00000000-0005-0000-0000-0000A1030000}"/>
-    <cellStyle name="千位分隔 2 3 5" xfId="1552" xr:uid="{00000000-0005-0000-0000-0000A2030000}"/>
-    <cellStyle name="千位分隔 2 3 6" xfId="1553" xr:uid="{00000000-0005-0000-0000-0000A3030000}"/>
-    <cellStyle name="千位分隔 2 3 7" xfId="187" xr:uid="{00000000-0005-0000-0000-0000A4030000}"/>
-    <cellStyle name="千位分隔 2 3 8" xfId="1538" xr:uid="{00000000-0005-0000-0000-0000A5030000}"/>
-    <cellStyle name="千位分隔 2 4" xfId="544" xr:uid="{00000000-0005-0000-0000-0000A6030000}"/>
-    <cellStyle name="千位分隔 2 4 2" xfId="547" xr:uid="{00000000-0005-0000-0000-0000A7030000}"/>
-    <cellStyle name="千位分隔 2 4 2 2" xfId="1554" xr:uid="{00000000-0005-0000-0000-0000A8030000}"/>
-    <cellStyle name="千位分隔 2 4 2 3" xfId="1555" xr:uid="{00000000-0005-0000-0000-0000A9030000}"/>
-    <cellStyle name="千位分隔 2 4 2 4" xfId="1556" xr:uid="{00000000-0005-0000-0000-0000AA030000}"/>
-    <cellStyle name="千位分隔 2 4 2 5" xfId="1557" xr:uid="{00000000-0005-0000-0000-0000AB030000}"/>
-    <cellStyle name="千位分隔 2 4 3" xfId="550" xr:uid="{00000000-0005-0000-0000-0000AC030000}"/>
-    <cellStyle name="千位分隔 2 4 4" xfId="34" xr:uid="{00000000-0005-0000-0000-0000AD030000}"/>
-    <cellStyle name="千位分隔 2 4 5" xfId="194" xr:uid="{00000000-0005-0000-0000-0000AE030000}"/>
-    <cellStyle name="千位分隔 2 4 6" xfId="197" xr:uid="{00000000-0005-0000-0000-0000AF030000}"/>
-    <cellStyle name="千位分隔 2 5" xfId="579" xr:uid="{00000000-0005-0000-0000-0000B0030000}"/>
-    <cellStyle name="千位分隔 2 5 2" xfId="349" xr:uid="{00000000-0005-0000-0000-0000B1030000}"/>
-    <cellStyle name="千位分隔 2 5 2 2" xfId="354" xr:uid="{00000000-0005-0000-0000-0000B2030000}"/>
-    <cellStyle name="千位分隔 2 5 2 3" xfId="357" xr:uid="{00000000-0005-0000-0000-0000B3030000}"/>
-    <cellStyle name="千位分隔 2 5 2 4" xfId="360" xr:uid="{00000000-0005-0000-0000-0000B4030000}"/>
-    <cellStyle name="千位分隔 2 5 2 5" xfId="315" xr:uid="{00000000-0005-0000-0000-0000B5030000}"/>
-    <cellStyle name="千位分隔 2 5 3" xfId="90" xr:uid="{00000000-0005-0000-0000-0000B6030000}"/>
-    <cellStyle name="千位分隔 2 5 4" xfId="586" xr:uid="{00000000-0005-0000-0000-0000B7030000}"/>
-    <cellStyle name="千位分隔 2 5 5" xfId="591" xr:uid="{00000000-0005-0000-0000-0000B8030000}"/>
-    <cellStyle name="千位分隔 2 5 6" xfId="593" xr:uid="{00000000-0005-0000-0000-0000B9030000}"/>
-    <cellStyle name="千位分隔 2 6" xfId="28" xr:uid="{00000000-0005-0000-0000-0000BA030000}"/>
-    <cellStyle name="千位分隔 2 6 2" xfId="1558" xr:uid="{00000000-0005-0000-0000-0000BB030000}"/>
-    <cellStyle name="千位分隔 2 6 2 2" xfId="1559" xr:uid="{00000000-0005-0000-0000-0000BC030000}"/>
-    <cellStyle name="千位分隔 2 6 2 3" xfId="1560" xr:uid="{00000000-0005-0000-0000-0000BD030000}"/>
-    <cellStyle name="千位分隔 2 6 2 4" xfId="1561" xr:uid="{00000000-0005-0000-0000-0000BE030000}"/>
-    <cellStyle name="千位分隔 2 6 2 5" xfId="1562" xr:uid="{00000000-0005-0000-0000-0000BF030000}"/>
-    <cellStyle name="千位分隔 2 6 3" xfId="1563" xr:uid="{00000000-0005-0000-0000-0000C0030000}"/>
-    <cellStyle name="千位分隔 2 6 4" xfId="1564" xr:uid="{00000000-0005-0000-0000-0000C1030000}"/>
-    <cellStyle name="千位分隔 2 6 5" xfId="1565" xr:uid="{00000000-0005-0000-0000-0000C2030000}"/>
-    <cellStyle name="千位分隔 2 6 6" xfId="1566" xr:uid="{00000000-0005-0000-0000-0000C3030000}"/>
-    <cellStyle name="千位分隔 2 7" xfId="596" xr:uid="{00000000-0005-0000-0000-0000C4030000}"/>
-    <cellStyle name="千位分隔 2 7 2" xfId="1567" xr:uid="{00000000-0005-0000-0000-0000C5030000}"/>
-    <cellStyle name="千位分隔 2 7 3" xfId="1568" xr:uid="{00000000-0005-0000-0000-0000C6030000}"/>
-    <cellStyle name="千位分隔 2 7 4" xfId="1569" xr:uid="{00000000-0005-0000-0000-0000C7030000}"/>
-    <cellStyle name="千位分隔 2 7 5" xfId="1570" xr:uid="{00000000-0005-0000-0000-0000C8030000}"/>
-    <cellStyle name="千位分隔 2 8" xfId="598" xr:uid="{00000000-0005-0000-0000-0000C9030000}"/>
-    <cellStyle name="千位分隔 2 8 2" xfId="1571" xr:uid="{00000000-0005-0000-0000-0000CA030000}"/>
-    <cellStyle name="千位分隔 2 8 3" xfId="1572" xr:uid="{00000000-0005-0000-0000-0000CB030000}"/>
-    <cellStyle name="千位分隔 2 8 4" xfId="996" xr:uid="{00000000-0005-0000-0000-0000CC030000}"/>
-    <cellStyle name="千位分隔 2 8 5" xfId="1573" xr:uid="{00000000-0005-0000-0000-0000CD030000}"/>
-    <cellStyle name="千位分隔 2 9" xfId="510" xr:uid="{00000000-0005-0000-0000-0000CE030000}"/>
-    <cellStyle name="千位分隔 2 9 2" xfId="1574" xr:uid="{00000000-0005-0000-0000-0000CF030000}"/>
-    <cellStyle name="千位分隔 2 9 3" xfId="1575" xr:uid="{00000000-0005-0000-0000-0000D0030000}"/>
-    <cellStyle name="千位分隔 2 9 4" xfId="1576" xr:uid="{00000000-0005-0000-0000-0000D1030000}"/>
-    <cellStyle name="千位分隔 20" xfId="15" xr:uid="{00000000-0005-0000-0000-0000D2030000}"/>
-    <cellStyle name="千位分隔 20 2" xfId="1501" xr:uid="{00000000-0005-0000-0000-0000D3030000}"/>
-    <cellStyle name="千位分隔 21" xfId="604" xr:uid="{00000000-0005-0000-0000-0000D4030000}"/>
-    <cellStyle name="千位分隔 22" xfId="623" xr:uid="{00000000-0005-0000-0000-0000D5030000}"/>
-    <cellStyle name="千位分隔 23" xfId="640" xr:uid="{00000000-0005-0000-0000-0000D6030000}"/>
-    <cellStyle name="千位分隔 24" xfId="649" xr:uid="{00000000-0005-0000-0000-0000D7030000}"/>
-    <cellStyle name="千位分隔 25" xfId="651" xr:uid="{00000000-0005-0000-0000-0000D8030000}"/>
-    <cellStyle name="千位分隔 3" xfId="299" xr:uid="{00000000-0005-0000-0000-0000D9030000}"/>
-    <cellStyle name="千位分隔 3 2" xfId="1577" xr:uid="{00000000-0005-0000-0000-0000DA030000}"/>
-    <cellStyle name="千位分隔 3 2 2" xfId="1578" xr:uid="{00000000-0005-0000-0000-0000DB030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2" xfId="900" xr:uid="{00000000-0005-0000-0000-0000DC030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 2" xfId="1579" xr:uid="{00000000-0005-0000-0000-0000DD030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 3" xfId="1580" xr:uid="{00000000-0005-0000-0000-0000DE030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 4" xfId="1581" xr:uid="{00000000-0005-0000-0000-0000DF030000}"/>
-    <cellStyle name="千位分隔 3 2 2 2 5" xfId="1582" xr:uid="{00000000-0005-0000-0000-0000E0030000}"/>
-    <cellStyle name="千位分隔 3 2 2 3" xfId="902" xr:uid="{00000000-0005-0000-0000-0000E1030000}"/>
-    <cellStyle name="千位分隔 3 2 2 4" xfId="904" xr:uid="{00000000-0005-0000-0000-0000E2030000}"/>
-    <cellStyle name="千位分隔 3 2 2 5" xfId="1583" xr:uid="{00000000-0005-0000-0000-0000E3030000}"/>
-    <cellStyle name="千位分隔 3 2 2 6" xfId="1584" xr:uid="{00000000-0005-0000-0000-0000E4030000}"/>
-    <cellStyle name="千位分隔 3 2 3" xfId="1585" xr:uid="{00000000-0005-0000-0000-0000E5030000}"/>
-    <cellStyle name="千位分隔 3 2 3 2" xfId="1586" xr:uid="{00000000-0005-0000-0000-0000E6030000}"/>
-    <cellStyle name="千位分隔 3 2 3 3" xfId="1587" xr:uid="{00000000-0005-0000-0000-0000E7030000}"/>
-    <cellStyle name="千位分隔 3 2 3 4" xfId="1588" xr:uid="{00000000-0005-0000-0000-0000E8030000}"/>
-    <cellStyle name="千位分隔 3 2 3 5" xfId="1589" xr:uid="{00000000-0005-0000-0000-0000E9030000}"/>
-    <cellStyle name="千位分隔 3 2 4" xfId="1590" xr:uid="{00000000-0005-0000-0000-0000EA030000}"/>
-    <cellStyle name="千位分隔 3 2 5" xfId="1591" xr:uid="{00000000-0005-0000-0000-0000EB030000}"/>
-    <cellStyle name="千位分隔 3 2 6" xfId="1592" xr:uid="{00000000-0005-0000-0000-0000EC030000}"/>
-    <cellStyle name="千位分隔 3 2 7" xfId="1593" xr:uid="{00000000-0005-0000-0000-0000ED030000}"/>
-    <cellStyle name="千位分隔 3 3" xfId="1594" xr:uid="{00000000-0005-0000-0000-0000EE030000}"/>
-    <cellStyle name="千位分隔 3 3 2" xfId="1595" xr:uid="{00000000-0005-0000-0000-0000EF030000}"/>
-    <cellStyle name="千位分隔 3 3 2 2" xfId="1596" xr:uid="{00000000-0005-0000-0000-0000F0030000}"/>
-    <cellStyle name="千位分隔 3 3 2 3" xfId="1597" xr:uid="{00000000-0005-0000-0000-0000F1030000}"/>
-    <cellStyle name="千位分隔 3 3 2 4" xfId="1598" xr:uid="{00000000-0005-0000-0000-0000F2030000}"/>
-    <cellStyle name="千位分隔 3 3 2 5" xfId="1599" xr:uid="{00000000-0005-0000-0000-0000F3030000}"/>
-    <cellStyle name="千位分隔 3 3 3" xfId="1600" xr:uid="{00000000-0005-0000-0000-0000F4030000}"/>
-    <cellStyle name="千位分隔 3 3 4" xfId="1601" xr:uid="{00000000-0005-0000-0000-0000F5030000}"/>
-    <cellStyle name="千位分隔 3 3 5" xfId="1602" xr:uid="{00000000-0005-0000-0000-0000F6030000}"/>
-    <cellStyle name="千位分隔 3 3 6" xfId="1603" xr:uid="{00000000-0005-0000-0000-0000F7030000}"/>
-    <cellStyle name="千位分隔 3 4" xfId="601" xr:uid="{00000000-0005-0000-0000-0000F8030000}"/>
-    <cellStyle name="千位分隔 3 4 2" xfId="43" xr:uid="{00000000-0005-0000-0000-0000F9030000}"/>
-    <cellStyle name="千位分隔 3 4 3" xfId="655" xr:uid="{00000000-0005-0000-0000-0000FA030000}"/>
-    <cellStyle name="千位分隔 3 4 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000FB030000}"/>
-    <cellStyle name="千位分隔 3 4 5" xfId="695" xr:uid="{00000000-0005-0000-0000-0000FC030000}"/>
-    <cellStyle name="千位分隔 3 5" xfId="714" xr:uid="{00000000-0005-0000-0000-0000FD030000}"/>
-    <cellStyle name="千位分隔 3 6" xfId="717" xr:uid="{00000000-0005-0000-0000-0000FE030000}"/>
-    <cellStyle name="千位分隔 3 7" xfId="720" xr:uid="{00000000-0005-0000-0000-0000FF030000}"/>
-    <cellStyle name="千位分隔 3 8" xfId="723" xr:uid="{00000000-0005-0000-0000-000000040000}"/>
-    <cellStyle name="千位分隔 4" xfId="1604" xr:uid="{00000000-0005-0000-0000-000001040000}"/>
-    <cellStyle name="千位分隔 4 2" xfId="884" xr:uid="{00000000-0005-0000-0000-000002040000}"/>
-    <cellStyle name="千位分隔 4 2 2" xfId="886" xr:uid="{00000000-0005-0000-0000-000003040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2" xfId="1389" xr:uid="{00000000-0005-0000-0000-000004040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 2" xfId="1605" xr:uid="{00000000-0005-0000-0000-000005040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 3" xfId="1606" xr:uid="{00000000-0005-0000-0000-000006040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 4" xfId="1607" xr:uid="{00000000-0005-0000-0000-000007040000}"/>
-    <cellStyle name="千位分隔 4 2 2 2 5" xfId="1608" xr:uid="{00000000-0005-0000-0000-000008040000}"/>
-    <cellStyle name="千位分隔 4 2 2 3" xfId="1392" xr:uid="{00000000-0005-0000-0000-000009040000}"/>
-    <cellStyle name="千位分隔 4 2 2 4" xfId="1609" xr:uid="{00000000-0005-0000-0000-00000A040000}"/>
-    <cellStyle name="千位分隔 4 2 2 5" xfId="1610" xr:uid="{00000000-0005-0000-0000-00000B040000}"/>
-    <cellStyle name="千位分隔 4 2 2 6" xfId="1611" xr:uid="{00000000-0005-0000-0000-00000C040000}"/>
-    <cellStyle name="千位分隔 4 2 3" xfId="888" xr:uid="{00000000-0005-0000-0000-00000D040000}"/>
-    <cellStyle name="千位分隔 4 2 3 2" xfId="1411" xr:uid="{00000000-0005-0000-0000-00000E040000}"/>
-    <cellStyle name="千位分隔 4 2 3 3" xfId="1612" xr:uid="{00000000-0005-0000-0000-00000F040000}"/>
-    <cellStyle name="千位分隔 4 2 3 4" xfId="1613" xr:uid="{00000000-0005-0000-0000-000010040000}"/>
-    <cellStyle name="千位分隔 4 2 3 5" xfId="1614" xr:uid="{00000000-0005-0000-0000-000011040000}"/>
-    <cellStyle name="千位分隔 4 2 4" xfId="890" xr:uid="{00000000-0005-0000-0000-000012040000}"/>
-    <cellStyle name="千位分隔 4 2 5" xfId="892" xr:uid="{00000000-0005-0000-0000-000013040000}"/>
-    <cellStyle name="千位分隔 4 2 6" xfId="1615" xr:uid="{00000000-0005-0000-0000-000014040000}"/>
-    <cellStyle name="千位分隔 4 2 7" xfId="1616" xr:uid="{00000000-0005-0000-0000-000015040000}"/>
-    <cellStyle name="千位分隔 4 3" xfId="894" xr:uid="{00000000-0005-0000-0000-000016040000}"/>
-    <cellStyle name="千位分隔 4 3 2" xfId="1617" xr:uid="{00000000-0005-0000-0000-000017040000}"/>
-    <cellStyle name="千位分隔 4 3 2 2" xfId="1435" xr:uid="{00000000-0005-0000-0000-000018040000}"/>
-    <cellStyle name="千位分隔 4 3 2 3" xfId="1437" xr:uid="{00000000-0005-0000-0000-000019040000}"/>
-    <cellStyle name="千位分隔 4 3 2 4" xfId="1618" xr:uid="{00000000-0005-0000-0000-00001A040000}"/>
-    <cellStyle name="千位分隔 4 3 2 5" xfId="1619" xr:uid="{00000000-0005-0000-0000-00001B040000}"/>
-    <cellStyle name="千位分隔 4 3 3" xfId="1620" xr:uid="{00000000-0005-0000-0000-00001C040000}"/>
-    <cellStyle name="千位分隔 4 3 4" xfId="1621" xr:uid="{00000000-0005-0000-0000-00001D040000}"/>
-    <cellStyle name="千位分隔 4 3 5" xfId="1622" xr:uid="{00000000-0005-0000-0000-00001E040000}"/>
-    <cellStyle name="千位分隔 4 3 6" xfId="1623" xr:uid="{00000000-0005-0000-0000-00001F040000}"/>
-    <cellStyle name="千位分隔 4 4" xfId="733" xr:uid="{00000000-0005-0000-0000-000020040000}"/>
-    <cellStyle name="千位分隔 4 4 2" xfId="736" xr:uid="{00000000-0005-0000-0000-000021040000}"/>
-    <cellStyle name="千位分隔 4 4 3" xfId="761" xr:uid="{00000000-0005-0000-0000-000022040000}"/>
-    <cellStyle name="千位分隔 4 4 4" xfId="773" xr:uid="{00000000-0005-0000-0000-000023040000}"/>
-    <cellStyle name="千位分隔 4 4 5" xfId="780" xr:uid="{00000000-0005-0000-0000-000024040000}"/>
-    <cellStyle name="千位分隔 4 5" xfId="788" xr:uid="{00000000-0005-0000-0000-000025040000}"/>
-    <cellStyle name="千位分隔 4 6" xfId="809" xr:uid="{00000000-0005-0000-0000-000026040000}"/>
-    <cellStyle name="千位分隔 4 7" xfId="821" xr:uid="{00000000-0005-0000-0000-000027040000}"/>
-    <cellStyle name="千位分隔 4 8" xfId="844" xr:uid="{00000000-0005-0000-0000-000028040000}"/>
-    <cellStyle name="千位分隔 5" xfId="1624" xr:uid="{00000000-0005-0000-0000-000029040000}"/>
-    <cellStyle name="千位分隔 5 2" xfId="906" xr:uid="{00000000-0005-0000-0000-00002A040000}"/>
-    <cellStyle name="千位分隔 6" xfId="1102" xr:uid="{00000000-0005-0000-0000-00002B040000}"/>
-    <cellStyle name="千位分隔 6 2" xfId="916" xr:uid="{00000000-0005-0000-0000-00002C040000}"/>
-    <cellStyle name="千位分隔 7" xfId="1625" xr:uid="{00000000-0005-0000-0000-00002D040000}"/>
-    <cellStyle name="千位分隔 7 2" xfId="1626" xr:uid="{00000000-0005-0000-0000-00002E040000}"/>
-    <cellStyle name="千位分隔 7 2 2" xfId="1627" xr:uid="{00000000-0005-0000-0000-00002F040000}"/>
-    <cellStyle name="千位分隔 7 2 2 2" xfId="1628" xr:uid="{00000000-0005-0000-0000-000030040000}"/>
-    <cellStyle name="千位分隔 7 2 2 3" xfId="1629" xr:uid="{00000000-0005-0000-0000-000031040000}"/>
-    <cellStyle name="千位分隔 7 2 2 4" xfId="1630" xr:uid="{00000000-0005-0000-0000-000032040000}"/>
-    <cellStyle name="千位分隔 7 2 2 5" xfId="1631" xr:uid="{00000000-0005-0000-0000-000033040000}"/>
-    <cellStyle name="千位分隔 7 2 3" xfId="657" xr:uid="{00000000-0005-0000-0000-000034040000}"/>
-    <cellStyle name="千位分隔 7 2 4" xfId="668" xr:uid="{00000000-0005-0000-0000-000035040000}"/>
-    <cellStyle name="千位分隔 7 2 5" xfId="674" xr:uid="{00000000-0005-0000-0000-000036040000}"/>
-    <cellStyle name="千位分隔 7 2 6" xfId="676" xr:uid="{00000000-0005-0000-0000-000037040000}"/>
-    <cellStyle name="千位分隔 7 3" xfId="1632" xr:uid="{00000000-0005-0000-0000-000038040000}"/>
-    <cellStyle name="千位分隔 7 3 2" xfId="1633" xr:uid="{00000000-0005-0000-0000-000039040000}"/>
-    <cellStyle name="千位分隔 7 3 3" xfId="682" xr:uid="{00000000-0005-0000-0000-00003A040000}"/>
-    <cellStyle name="千位分隔 7 3 4" xfId="688" xr:uid="{00000000-0005-0000-0000-00003B040000}"/>
-    <cellStyle name="千位分隔 7 3 5" xfId="690" xr:uid="{00000000-0005-0000-0000-00003C040000}"/>
-    <cellStyle name="千位分隔 7 4" xfId="983" xr:uid="{00000000-0005-0000-0000-00003D040000}"/>
-    <cellStyle name="千位分隔 7 5" xfId="1634" xr:uid="{00000000-0005-0000-0000-00003E040000}"/>
-    <cellStyle name="千位分隔 7 6" xfId="1635" xr:uid="{00000000-0005-0000-0000-00003F040000}"/>
-    <cellStyle name="千位分隔 7 7" xfId="1636" xr:uid="{00000000-0005-0000-0000-000040040000}"/>
-    <cellStyle name="千位分隔 8" xfId="1637" xr:uid="{00000000-0005-0000-0000-000041040000}"/>
-    <cellStyle name="千位分隔 8 2" xfId="1638" xr:uid="{00000000-0005-0000-0000-000042040000}"/>
-    <cellStyle name="千位分隔 8 3" xfId="1639" xr:uid="{00000000-0005-0000-0000-000043040000}"/>
-    <cellStyle name="千位分隔 9" xfId="1640" xr:uid="{00000000-0005-0000-0000-000044040000}"/>
-    <cellStyle name="常规 10" xfId="439" xr:uid="{00000000-0005-0000-0000-000045040000}"/>
-    <cellStyle name="常规 10 10" xfId="1010" xr:uid="{00000000-0005-0000-0000-000046040000}"/>
-    <cellStyle name="常规 10 11" xfId="1011" xr:uid="{00000000-0005-0000-0000-000047040000}"/>
-    <cellStyle name="常规 10 12" xfId="1654" xr:uid="{00000000-0005-0000-0000-000048040000}"/>
-    <cellStyle name="常规 10 2" xfId="441" xr:uid="{00000000-0005-0000-0000-000049040000}"/>
-    <cellStyle name="常规 10 2 2" xfId="443" xr:uid="{00000000-0005-0000-0000-00004A040000}"/>
-    <cellStyle name="常规 10 2 2 2" xfId="1012" xr:uid="{00000000-0005-0000-0000-00004B040000}"/>
-    <cellStyle name="常规 10 2 2 2 2" xfId="1013" xr:uid="{00000000-0005-0000-0000-00004C040000}"/>
-    <cellStyle name="常规 10 2 2 2 2 2" xfId="1014" xr:uid="{00000000-0005-0000-0000-00004D040000}"/>
-    <cellStyle name="常规 10 2 2 2 3" xfId="1015" xr:uid="{00000000-0005-0000-0000-00004E040000}"/>
-    <cellStyle name="常规 10 2 2 2 4" xfId="1016" xr:uid="{00000000-0005-0000-0000-00004F040000}"/>
-    <cellStyle name="常规 10 2 2 2 5" xfId="1017" xr:uid="{00000000-0005-0000-0000-000050040000}"/>
-    <cellStyle name="常规 10 2 2 2 6" xfId="1018" xr:uid="{00000000-0005-0000-0000-000051040000}"/>
-    <cellStyle name="常规 10 2 2 3" xfId="1019" xr:uid="{00000000-0005-0000-0000-000052040000}"/>
-    <cellStyle name="常规 10 2 2 3 2" xfId="1020" xr:uid="{00000000-0005-0000-0000-000053040000}"/>
-    <cellStyle name="常规 10 2 2 4" xfId="1021" xr:uid="{00000000-0005-0000-0000-000054040000}"/>
-    <cellStyle name="常规 10 2 2 5" xfId="1022" xr:uid="{00000000-0005-0000-0000-000055040000}"/>
-    <cellStyle name="常规 10 2 2 6" xfId="1023" xr:uid="{00000000-0005-0000-0000-000056040000}"/>
-    <cellStyle name="常规 10 2 3" xfId="445" xr:uid="{00000000-0005-0000-0000-000057040000}"/>
-    <cellStyle name="常规 10 2 3 2" xfId="556" xr:uid="{00000000-0005-0000-0000-000058040000}"/>
-    <cellStyle name="常规 10 2 3 2 2" xfId="1024" xr:uid="{00000000-0005-0000-0000-000059040000}"/>
-    <cellStyle name="常规 10 2 3 2 2 2" xfId="1025" xr:uid="{00000000-0005-0000-0000-00005A040000}"/>
-    <cellStyle name="常规 10 2 3 2 3" xfId="1026" xr:uid="{00000000-0005-0000-0000-00005B040000}"/>
-    <cellStyle name="常规 10 2 3 2 4" xfId="1027" xr:uid="{00000000-0005-0000-0000-00005C040000}"/>
-    <cellStyle name="常规 10 2 3 2 5" xfId="1028" xr:uid="{00000000-0005-0000-0000-00005D040000}"/>
-    <cellStyle name="常规 10 2 3 2 6" xfId="1029" xr:uid="{00000000-0005-0000-0000-00005E040000}"/>
-    <cellStyle name="常规 10 2 3 3" xfId="1030" xr:uid="{00000000-0005-0000-0000-00005F040000}"/>
-    <cellStyle name="常规 10 2 3 3 2" xfId="1031" xr:uid="{00000000-0005-0000-0000-000060040000}"/>
-    <cellStyle name="常规 10 2 3 4" xfId="1032" xr:uid="{00000000-0005-0000-0000-000061040000}"/>
-    <cellStyle name="常规 10 2 3 5" xfId="1033" xr:uid="{00000000-0005-0000-0000-000062040000}"/>
-    <cellStyle name="常规 10 2 3 6" xfId="1034" xr:uid="{00000000-0005-0000-0000-000063040000}"/>
-    <cellStyle name="常规 10 2 4" xfId="169" xr:uid="{00000000-0005-0000-0000-000064040000}"/>
-    <cellStyle name="常规 10 2 4 2" xfId="490" xr:uid="{00000000-0005-0000-0000-000065040000}"/>
-    <cellStyle name="常规 10 2 4 2 2" xfId="1035" xr:uid="{00000000-0005-0000-0000-000066040000}"/>
-    <cellStyle name="常规 10 2 4 2 2 2" xfId="459" xr:uid="{00000000-0005-0000-0000-000067040000}"/>
-    <cellStyle name="常规 10 2 4 2 3" xfId="1036" xr:uid="{00000000-0005-0000-0000-000068040000}"/>
-    <cellStyle name="常规 10 2 4 2 4" xfId="1037" xr:uid="{00000000-0005-0000-0000-000069040000}"/>
-    <cellStyle name="常规 10 2 4 2 5" xfId="1038" xr:uid="{00000000-0005-0000-0000-00006A040000}"/>
-    <cellStyle name="常规 10 2 4 3" xfId="1039" xr:uid="{00000000-0005-0000-0000-00006B040000}"/>
-    <cellStyle name="常规 10 2 4 3 2" xfId="1040" xr:uid="{00000000-0005-0000-0000-00006C040000}"/>
-    <cellStyle name="常规 10 2 4 3 2 2" xfId="1041" xr:uid="{00000000-0005-0000-0000-00006D040000}"/>
-    <cellStyle name="常规 10 2 4 3 3" xfId="1042" xr:uid="{00000000-0005-0000-0000-00006E040000}"/>
-    <cellStyle name="常规 10 2 4 3 4" xfId="1043" xr:uid="{00000000-0005-0000-0000-00006F040000}"/>
-    <cellStyle name="常规 10 2 4 3 5" xfId="1044" xr:uid="{00000000-0005-0000-0000-000070040000}"/>
-    <cellStyle name="常规 10 2 4 3 6" xfId="1046" xr:uid="{00000000-0005-0000-0000-000071040000}"/>
-    <cellStyle name="常规 10 2 4 4" xfId="1047" xr:uid="{00000000-0005-0000-0000-000072040000}"/>
-    <cellStyle name="常规 10 2 4 4 2" xfId="1048" xr:uid="{00000000-0005-0000-0000-000073040000}"/>
-    <cellStyle name="常规 10 2 4 5" xfId="1049" xr:uid="{00000000-0005-0000-0000-000074040000}"/>
-    <cellStyle name="常规 10 2 4 6" xfId="1050" xr:uid="{00000000-0005-0000-0000-000075040000}"/>
-    <cellStyle name="常规 10 2 4 7" xfId="1051" xr:uid="{00000000-0005-0000-0000-000076040000}"/>
-    <cellStyle name="常规 10 2 5" xfId="173" xr:uid="{00000000-0005-0000-0000-000077040000}"/>
-    <cellStyle name="常规 10 2 5 2" xfId="1052" xr:uid="{00000000-0005-0000-0000-000078040000}"/>
-    <cellStyle name="常规 10 2 5 2 2" xfId="1053" xr:uid="{00000000-0005-0000-0000-000079040000}"/>
-    <cellStyle name="常规 10 2 5 3" xfId="1054" xr:uid="{00000000-0005-0000-0000-00007A040000}"/>
-    <cellStyle name="常规 10 2 5 4" xfId="1055" xr:uid="{00000000-0005-0000-0000-00007B040000}"/>
-    <cellStyle name="常规 10 2 5 5" xfId="1056" xr:uid="{00000000-0005-0000-0000-00007C040000}"/>
-    <cellStyle name="常规 10 2 5 6" xfId="1057" xr:uid="{00000000-0005-0000-0000-00007D040000}"/>
-    <cellStyle name="常规 10 2 6" xfId="1058" xr:uid="{00000000-0005-0000-0000-00007E040000}"/>
-    <cellStyle name="常规 10 2 6 2" xfId="1059" xr:uid="{00000000-0005-0000-0000-00007F040000}"/>
-    <cellStyle name="常规 10 2 7" xfId="1060" xr:uid="{00000000-0005-0000-0000-000080040000}"/>
-    <cellStyle name="常规 10 2 8" xfId="1061" xr:uid="{00000000-0005-0000-0000-000081040000}"/>
-    <cellStyle name="常规 10 2 9" xfId="1062" xr:uid="{00000000-0005-0000-0000-000082040000}"/>
-    <cellStyle name="常规 10 3" xfId="447" xr:uid="{00000000-0005-0000-0000-000083040000}"/>
-    <cellStyle name="常规 10 3 2" xfId="1063" xr:uid="{00000000-0005-0000-0000-000084040000}"/>
-    <cellStyle name="常规 10 3 2 2" xfId="1064" xr:uid="{00000000-0005-0000-0000-000085040000}"/>
-    <cellStyle name="常规 10 3 2 2 2" xfId="1065" xr:uid="{00000000-0005-0000-0000-000086040000}"/>
-    <cellStyle name="常规 10 3 2 3" xfId="1066" xr:uid="{00000000-0005-0000-0000-000087040000}"/>
-    <cellStyle name="常规 10 3 2 4" xfId="1067" xr:uid="{00000000-0005-0000-0000-000088040000}"/>
-    <cellStyle name="常规 10 3 2 5" xfId="1068" xr:uid="{00000000-0005-0000-0000-000089040000}"/>
-    <cellStyle name="常规 10 3 3" xfId="1069" xr:uid="{00000000-0005-0000-0000-00008A040000}"/>
-    <cellStyle name="常规 10 3 3 2" xfId="1070" xr:uid="{00000000-0005-0000-0000-00008B040000}"/>
-    <cellStyle name="常规 10 3 3 2 2" xfId="1071" xr:uid="{00000000-0005-0000-0000-00008C040000}"/>
-    <cellStyle name="常规 10 3 3 3" xfId="1072" xr:uid="{00000000-0005-0000-0000-00008D040000}"/>
-    <cellStyle name="常规 10 3 3 4" xfId="1073" xr:uid="{00000000-0005-0000-0000-00008E040000}"/>
-    <cellStyle name="常规 10 3 3 5" xfId="1074" xr:uid="{00000000-0005-0000-0000-00008F040000}"/>
-    <cellStyle name="常规 10 3 3 6" xfId="1075" xr:uid="{00000000-0005-0000-0000-000090040000}"/>
-    <cellStyle name="常规 10 3 4" xfId="1076" xr:uid="{00000000-0005-0000-0000-000091040000}"/>
-    <cellStyle name="常规 10 3 4 2" xfId="1077" xr:uid="{00000000-0005-0000-0000-000092040000}"/>
-    <cellStyle name="常规 10 3 5" xfId="1078" xr:uid="{00000000-0005-0000-0000-000093040000}"/>
-    <cellStyle name="常规 10 3 6" xfId="1079" xr:uid="{00000000-0005-0000-0000-000094040000}"/>
-    <cellStyle name="常规 10 3 7" xfId="1080" xr:uid="{00000000-0005-0000-0000-000095040000}"/>
-    <cellStyle name="常规 10 4" xfId="449" xr:uid="{00000000-0005-0000-0000-000096040000}"/>
-    <cellStyle name="常规 10 4 2" xfId="1081" xr:uid="{00000000-0005-0000-0000-000097040000}"/>
-    <cellStyle name="常规 10 4 2 2" xfId="1082" xr:uid="{00000000-0005-0000-0000-000098040000}"/>
-    <cellStyle name="常规 10 4 2 2 2" xfId="1083" xr:uid="{00000000-0005-0000-0000-000099040000}"/>
-    <cellStyle name="常规 10 4 2 3" xfId="1084" xr:uid="{00000000-0005-0000-0000-00009A040000}"/>
-    <cellStyle name="常规 10 4 2 4" xfId="1085" xr:uid="{00000000-0005-0000-0000-00009B040000}"/>
-    <cellStyle name="常规 10 4 2 5" xfId="1086" xr:uid="{00000000-0005-0000-0000-00009C040000}"/>
-    <cellStyle name="常规 10 4 3" xfId="1087" xr:uid="{00000000-0005-0000-0000-00009D040000}"/>
-    <cellStyle name="常规 10 4 3 2" xfId="1088" xr:uid="{00000000-0005-0000-0000-00009E040000}"/>
-    <cellStyle name="常规 10 4 3 2 2" xfId="1090" xr:uid="{00000000-0005-0000-0000-00009F040000}"/>
-    <cellStyle name="常规 10 4 3 3" xfId="1091" xr:uid="{00000000-0005-0000-0000-0000A0040000}"/>
-    <cellStyle name="常规 10 4 3 4" xfId="1092" xr:uid="{00000000-0005-0000-0000-0000A1040000}"/>
-    <cellStyle name="常规 10 4 3 5" xfId="1093" xr:uid="{00000000-0005-0000-0000-0000A2040000}"/>
-    <cellStyle name="常规 10 4 3 6" xfId="1094" xr:uid="{00000000-0005-0000-0000-0000A3040000}"/>
-    <cellStyle name="常规 10 4 4" xfId="1095" xr:uid="{00000000-0005-0000-0000-0000A4040000}"/>
-    <cellStyle name="常规 10 4 4 2" xfId="1096" xr:uid="{00000000-0005-0000-0000-0000A5040000}"/>
-    <cellStyle name="常规 10 4 5" xfId="1097" xr:uid="{00000000-0005-0000-0000-0000A6040000}"/>
-    <cellStyle name="常规 10 4 6" xfId="1098" xr:uid="{00000000-0005-0000-0000-0000A7040000}"/>
-    <cellStyle name="常规 10 4 7" xfId="1099" xr:uid="{00000000-0005-0000-0000-0000A8040000}"/>
-    <cellStyle name="常规 10 5" xfId="451" xr:uid="{00000000-0005-0000-0000-0000A9040000}"/>
-    <cellStyle name="常规 10 5 2" xfId="1100" xr:uid="{00000000-0005-0000-0000-0000AA040000}"/>
-    <cellStyle name="常规 10 5 2 2" xfId="1101" xr:uid="{00000000-0005-0000-0000-0000AB040000}"/>
-    <cellStyle name="常规 10 5 2 2 2" xfId="1103" xr:uid="{00000000-0005-0000-0000-0000AC040000}"/>
-    <cellStyle name="常规 10 5 2 3" xfId="1104" xr:uid="{00000000-0005-0000-0000-0000AD040000}"/>
-    <cellStyle name="常规 10 5 2 4" xfId="1105" xr:uid="{00000000-0005-0000-0000-0000AE040000}"/>
-    <cellStyle name="常规 10 5 2 5" xfId="1106" xr:uid="{00000000-0005-0000-0000-0000AF040000}"/>
-    <cellStyle name="常规 10 5 3" xfId="1107" xr:uid="{00000000-0005-0000-0000-0000B0040000}"/>
-    <cellStyle name="常规 10 5 3 2" xfId="1108" xr:uid="{00000000-0005-0000-0000-0000B1040000}"/>
-    <cellStyle name="常规 10 5 3 2 2" xfId="1109" xr:uid="{00000000-0005-0000-0000-0000B2040000}"/>
-    <cellStyle name="常规 10 5 3 3" xfId="1110" xr:uid="{00000000-0005-0000-0000-0000B3040000}"/>
-    <cellStyle name="常规 10 5 3 4" xfId="1111" xr:uid="{00000000-0005-0000-0000-0000B4040000}"/>
-    <cellStyle name="常规 10 5 3 5" xfId="1112" xr:uid="{00000000-0005-0000-0000-0000B5040000}"/>
-    <cellStyle name="常规 10 5 3 6" xfId="1113" xr:uid="{00000000-0005-0000-0000-0000B6040000}"/>
-    <cellStyle name="常规 10 5 4" xfId="1114" xr:uid="{00000000-0005-0000-0000-0000B7040000}"/>
-    <cellStyle name="常规 10 5 4 2" xfId="1115" xr:uid="{00000000-0005-0000-0000-0000B8040000}"/>
-    <cellStyle name="常规 10 5 5" xfId="1116" xr:uid="{00000000-0005-0000-0000-0000B9040000}"/>
-    <cellStyle name="常规 10 5 6" xfId="1118" xr:uid="{00000000-0005-0000-0000-0000BA040000}"/>
-    <cellStyle name="常规 10 5 7" xfId="1120" xr:uid="{00000000-0005-0000-0000-0000BB040000}"/>
-    <cellStyle name="常规 10 6" xfId="453" xr:uid="{00000000-0005-0000-0000-0000BC040000}"/>
-    <cellStyle name="常规 10 6 2" xfId="1121" xr:uid="{00000000-0005-0000-0000-0000BD040000}"/>
-    <cellStyle name="常规 10 6 2 2" xfId="1122" xr:uid="{00000000-0005-0000-0000-0000BE040000}"/>
-    <cellStyle name="常规 10 6 3" xfId="1123" xr:uid="{00000000-0005-0000-0000-0000BF040000}"/>
-    <cellStyle name="常规 10 6 4" xfId="1124" xr:uid="{00000000-0005-0000-0000-0000C0040000}"/>
-    <cellStyle name="常规 10 6 5" xfId="1125" xr:uid="{00000000-0005-0000-0000-0000C1040000}"/>
-    <cellStyle name="常规 10 6 6" xfId="429" xr:uid="{00000000-0005-0000-0000-0000C2040000}"/>
-    <cellStyle name="常规 10 7" xfId="1126" xr:uid="{00000000-0005-0000-0000-0000C3040000}"/>
-    <cellStyle name="常规 10 7 2" xfId="1127" xr:uid="{00000000-0005-0000-0000-0000C4040000}"/>
-    <cellStyle name="常规 10 7 2 2" xfId="1128" xr:uid="{00000000-0005-0000-0000-0000C5040000}"/>
-    <cellStyle name="常规 10 7 3" xfId="1129" xr:uid="{00000000-0005-0000-0000-0000C6040000}"/>
-    <cellStyle name="常规 10 7 4" xfId="1130" xr:uid="{00000000-0005-0000-0000-0000C7040000}"/>
-    <cellStyle name="常规 10 7 5" xfId="1131" xr:uid="{00000000-0005-0000-0000-0000C8040000}"/>
-    <cellStyle name="常规 10 7 6" xfId="1133" xr:uid="{00000000-0005-0000-0000-0000C9040000}"/>
-    <cellStyle name="常规 10 8" xfId="1134" xr:uid="{00000000-0005-0000-0000-0000CA040000}"/>
-    <cellStyle name="常规 10 8 2" xfId="1135" xr:uid="{00000000-0005-0000-0000-0000CB040000}"/>
-    <cellStyle name="常规 10 8 3" xfId="1136" xr:uid="{00000000-0005-0000-0000-0000CC040000}"/>
-    <cellStyle name="常规 10 8 4" xfId="1137" xr:uid="{00000000-0005-0000-0000-0000CD040000}"/>
-    <cellStyle name="常规 10 8 5" xfId="1138" xr:uid="{00000000-0005-0000-0000-0000CE040000}"/>
-    <cellStyle name="常规 10 9" xfId="1139" xr:uid="{00000000-0005-0000-0000-0000CF040000}"/>
-    <cellStyle name="常规 11" xfId="455" xr:uid="{00000000-0005-0000-0000-0000D0040000}"/>
-    <cellStyle name="常规 11 2" xfId="457" xr:uid="{00000000-0005-0000-0000-0000D1040000}"/>
-    <cellStyle name="常规 11 3" xfId="1647" xr:uid="{00000000-0005-0000-0000-0000D2040000}"/>
-    <cellStyle name="常规 12" xfId="463" xr:uid="{00000000-0005-0000-0000-0000D3040000}"/>
-    <cellStyle name="常规 12 2" xfId="745" xr:uid="{00000000-0005-0000-0000-0000D4040000}"/>
-    <cellStyle name="常规 13" xfId="363" xr:uid="{00000000-0005-0000-0000-0000D5040000}"/>
-    <cellStyle name="常规 13 2" xfId="753" xr:uid="{00000000-0005-0000-0000-0000D6040000}"/>
-    <cellStyle name="常规 14" xfId="405" xr:uid="{00000000-0005-0000-0000-0000D7040000}"/>
-    <cellStyle name="常规 14 2" xfId="1140" xr:uid="{00000000-0005-0000-0000-0000D8040000}"/>
-    <cellStyle name="常规 15" xfId="5" xr:uid="{00000000-0005-0000-0000-0000D9040000}"/>
-    <cellStyle name="常规 15 2" xfId="1142" xr:uid="{00000000-0005-0000-0000-0000DA040000}"/>
-    <cellStyle name="常规 15 2 2" xfId="1143" xr:uid="{00000000-0005-0000-0000-0000DB040000}"/>
-    <cellStyle name="常规 15 2 2 2" xfId="1144" xr:uid="{00000000-0005-0000-0000-0000DC040000}"/>
-    <cellStyle name="常规 15 2 2 3" xfId="1145" xr:uid="{00000000-0005-0000-0000-0000DD040000}"/>
-    <cellStyle name="常规 15 2 2 4" xfId="1146" xr:uid="{00000000-0005-0000-0000-0000DE040000}"/>
-    <cellStyle name="常规 15 2 2 5" xfId="1147" xr:uid="{00000000-0005-0000-0000-0000DF040000}"/>
-    <cellStyle name="常规 15 2 3" xfId="1148" xr:uid="{00000000-0005-0000-0000-0000E0040000}"/>
-    <cellStyle name="常规 15 2 4" xfId="897" xr:uid="{00000000-0005-0000-0000-0000E1040000}"/>
-    <cellStyle name="常规 15 2 5" xfId="907" xr:uid="{00000000-0005-0000-0000-0000E2040000}"/>
-    <cellStyle name="常规 15 2 6" xfId="909" xr:uid="{00000000-0005-0000-0000-0000E3040000}"/>
-    <cellStyle name="常规 15 3" xfId="1151" xr:uid="{00000000-0005-0000-0000-0000E4040000}"/>
-    <cellStyle name="常规 15 3 2" xfId="1152" xr:uid="{00000000-0005-0000-0000-0000E5040000}"/>
-    <cellStyle name="常规 15 3 3" xfId="1153" xr:uid="{00000000-0005-0000-0000-0000E6040000}"/>
-    <cellStyle name="常规 15 3 4" xfId="914" xr:uid="{00000000-0005-0000-0000-0000E7040000}"/>
-    <cellStyle name="常规 15 3 5" xfId="917" xr:uid="{00000000-0005-0000-0000-0000E8040000}"/>
-    <cellStyle name="常规 15 4" xfId="1155" xr:uid="{00000000-0005-0000-0000-0000E9040000}"/>
-    <cellStyle name="常规 15 5" xfId="1157" xr:uid="{00000000-0005-0000-0000-0000EA040000}"/>
-    <cellStyle name="常规 15 6" xfId="1159" xr:uid="{00000000-0005-0000-0000-0000EB040000}"/>
-    <cellStyle name="常规 15 7" xfId="1160" xr:uid="{00000000-0005-0000-0000-0000EC040000}"/>
-    <cellStyle name="常规 15 8" xfId="239" xr:uid="{00000000-0005-0000-0000-0000ED040000}"/>
-    <cellStyle name="常规 16" xfId="1162" xr:uid="{00000000-0005-0000-0000-0000EE040000}"/>
-    <cellStyle name="常规 16 2" xfId="1164" xr:uid="{00000000-0005-0000-0000-0000EF040000}"/>
-    <cellStyle name="常规 16 2 2" xfId="1165" xr:uid="{00000000-0005-0000-0000-0000F0040000}"/>
-    <cellStyle name="常规 16 2 2 2" xfId="1167" xr:uid="{00000000-0005-0000-0000-0000F1040000}"/>
-    <cellStyle name="常规 16 2 2 3" xfId="1169" xr:uid="{00000000-0005-0000-0000-0000F2040000}"/>
-    <cellStyle name="常规 16 2 2 4" xfId="171" xr:uid="{00000000-0005-0000-0000-0000F3040000}"/>
-    <cellStyle name="常规 16 2 2 5" xfId="175" xr:uid="{00000000-0005-0000-0000-0000F4040000}"/>
-    <cellStyle name="常规 16 2 3" xfId="1170" xr:uid="{00000000-0005-0000-0000-0000F5040000}"/>
-    <cellStyle name="常规 16 2 4" xfId="932" xr:uid="{00000000-0005-0000-0000-0000F6040000}"/>
-    <cellStyle name="常规 16 2 5" xfId="934" xr:uid="{00000000-0005-0000-0000-0000F7040000}"/>
-    <cellStyle name="常规 16 2 6" xfId="936" xr:uid="{00000000-0005-0000-0000-0000F8040000}"/>
-    <cellStyle name="常规 16 3" xfId="1171" xr:uid="{00000000-0005-0000-0000-0000F9040000}"/>
-    <cellStyle name="常规 16 3 2" xfId="1172" xr:uid="{00000000-0005-0000-0000-0000FA040000}"/>
-    <cellStyle name="常规 16 3 3" xfId="1173" xr:uid="{00000000-0005-0000-0000-0000FB040000}"/>
-    <cellStyle name="常规 16 3 4" xfId="1174" xr:uid="{00000000-0005-0000-0000-0000FC040000}"/>
-    <cellStyle name="常规 16 3 5" xfId="1175" xr:uid="{00000000-0005-0000-0000-0000FD040000}"/>
-    <cellStyle name="常规 16 4" xfId="1176" xr:uid="{00000000-0005-0000-0000-0000FE040000}"/>
-    <cellStyle name="常规 16 5" xfId="1177" xr:uid="{00000000-0005-0000-0000-0000FF040000}"/>
-    <cellStyle name="常规 16 6" xfId="1178" xr:uid="{00000000-0005-0000-0000-000000050000}"/>
-    <cellStyle name="常规 16 7" xfId="1179" xr:uid="{00000000-0005-0000-0000-000001050000}"/>
-    <cellStyle name="常规 17" xfId="1181" xr:uid="{00000000-0005-0000-0000-000002050000}"/>
-    <cellStyle name="常规 17 2" xfId="1183" xr:uid="{00000000-0005-0000-0000-000003050000}"/>
-    <cellStyle name="常规 17 3" xfId="1185" xr:uid="{00000000-0005-0000-0000-000004050000}"/>
-    <cellStyle name="常规 18" xfId="1187" xr:uid="{00000000-0005-0000-0000-000005050000}"/>
-    <cellStyle name="常规 18 2" xfId="1189" xr:uid="{00000000-0005-0000-0000-000006050000}"/>
-    <cellStyle name="常规 18 3" xfId="1191" xr:uid="{00000000-0005-0000-0000-000007050000}"/>
-    <cellStyle name="常规 19" xfId="1193" xr:uid="{00000000-0005-0000-0000-000008050000}"/>
-    <cellStyle name="常规 19 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000009050000}"/>
-    <cellStyle name="常规 19 3" xfId="1195" xr:uid="{00000000-0005-0000-0000-00000A050000}"/>
-    <cellStyle name="常规 2" xfId="1196" xr:uid="{00000000-0005-0000-0000-00000B050000}"/>
-    <cellStyle name="常规 2 10" xfId="1658" xr:uid="{00000000-0005-0000-0000-00000C050000}"/>
-    <cellStyle name="常规 2 2" xfId="1197" xr:uid="{00000000-0005-0000-0000-00000D050000}"/>
-    <cellStyle name="常规 2 2 2" xfId="1198" xr:uid="{00000000-0005-0000-0000-00000E050000}"/>
-    <cellStyle name="常规 2 2 2 2" xfId="1117" xr:uid="{00000000-0005-0000-0000-00000F050000}"/>
-    <cellStyle name="常规 2 2 2 2 2" xfId="1199" xr:uid="{00000000-0005-0000-0000-000010050000}"/>
-    <cellStyle name="常规 2 2 2 2 3" xfId="1200" xr:uid="{00000000-0005-0000-0000-000011050000}"/>
-    <cellStyle name="常规 2 2 2 2 4" xfId="1201" xr:uid="{00000000-0005-0000-0000-000012050000}"/>
-    <cellStyle name="常规 2 2 2 2 5" xfId="1202" xr:uid="{00000000-0005-0000-0000-000013050000}"/>
-    <cellStyle name="常规 2 2 2 3" xfId="1119" xr:uid="{00000000-0005-0000-0000-000014050000}"/>
-    <cellStyle name="常规 2 2 2 4" xfId="61" xr:uid="{00000000-0005-0000-0000-000015050000}"/>
-    <cellStyle name="常规 2 2 2 5" xfId="50" xr:uid="{00000000-0005-0000-0000-000016050000}"/>
-    <cellStyle name="常规 2 2 2 6" xfId="63" xr:uid="{00000000-0005-0000-0000-000017050000}"/>
-    <cellStyle name="常规 2 2 3" xfId="567" xr:uid="{00000000-0005-0000-0000-000018050000}"/>
-    <cellStyle name="常规 2 2 3 2" xfId="428" xr:uid="{00000000-0005-0000-0000-000019050000}"/>
-    <cellStyle name="常规 2 2 3 2 2" xfId="1204" xr:uid="{00000000-0005-0000-0000-00001A050000}"/>
-    <cellStyle name="常规 2 2 3 2 3" xfId="1206" xr:uid="{00000000-0005-0000-0000-00001B050000}"/>
-    <cellStyle name="常规 2 2 3 2 4" xfId="513" xr:uid="{00000000-0005-0000-0000-00001C050000}"/>
-    <cellStyle name="常规 2 2 3 2 5" xfId="1208" xr:uid="{00000000-0005-0000-0000-00001D050000}"/>
-    <cellStyle name="常规 2 2 3 3" xfId="432" xr:uid="{00000000-0005-0000-0000-00001E050000}"/>
-    <cellStyle name="常规 2 2 3 4" xfId="435" xr:uid="{00000000-0005-0000-0000-00001F050000}"/>
-    <cellStyle name="常规 2 2 3 5" xfId="569" xr:uid="{00000000-0005-0000-0000-000020050000}"/>
-    <cellStyle name="常规 2 2 3 6" xfId="1209" xr:uid="{00000000-0005-0000-0000-000021050000}"/>
-    <cellStyle name="常规 2 2 4" xfId="25" xr:uid="{00000000-0005-0000-0000-000022050000}"/>
-    <cellStyle name="常规 2 2 4 2" xfId="1132" xr:uid="{00000000-0005-0000-0000-000023050000}"/>
-    <cellStyle name="常规 2 2 4 3" xfId="1210" xr:uid="{00000000-0005-0000-0000-000024050000}"/>
-    <cellStyle name="常规 2 2 4 4" xfId="1211" xr:uid="{00000000-0005-0000-0000-000025050000}"/>
-    <cellStyle name="常规 2 2 4 5" xfId="1212" xr:uid="{00000000-0005-0000-0000-000026050000}"/>
-    <cellStyle name="常规 2 2 5" xfId="571" xr:uid="{00000000-0005-0000-0000-000027050000}"/>
-    <cellStyle name="常规 2 2 6" xfId="573" xr:uid="{00000000-0005-0000-0000-000028050000}"/>
-    <cellStyle name="常规 2 2 7" xfId="575" xr:uid="{00000000-0005-0000-0000-000029050000}"/>
-    <cellStyle name="常规 2 2 8" xfId="1213" xr:uid="{00000000-0005-0000-0000-00002A050000}"/>
-    <cellStyle name="常规 2 3" xfId="1214" xr:uid="{00000000-0005-0000-0000-00002B050000}"/>
-    <cellStyle name="常规 2 3 2" xfId="1215" xr:uid="{00000000-0005-0000-0000-00002C050000}"/>
-    <cellStyle name="常规 2 3 2 2" xfId="1216" xr:uid="{00000000-0005-0000-0000-00002D050000}"/>
-    <cellStyle name="常规 2 3 2 3" xfId="1217" xr:uid="{00000000-0005-0000-0000-00002E050000}"/>
-    <cellStyle name="常规 2 3 2 4" xfId="1218" xr:uid="{00000000-0005-0000-0000-00002F050000}"/>
-    <cellStyle name="常规 2 3 2 5" xfId="1219" xr:uid="{00000000-0005-0000-0000-000030050000}"/>
-    <cellStyle name="常规 2 3 3" xfId="577" xr:uid="{00000000-0005-0000-0000-000031050000}"/>
-    <cellStyle name="常规 2 3 4" xfId="416" xr:uid="{00000000-0005-0000-0000-000032050000}"/>
-    <cellStyle name="常规 2 3 5" xfId="419" xr:uid="{00000000-0005-0000-0000-000033050000}"/>
-    <cellStyle name="常规 2 3 6" xfId="422" xr:uid="{00000000-0005-0000-0000-000034050000}"/>
-    <cellStyle name="常规 2 4" xfId="1220" xr:uid="{00000000-0005-0000-0000-000035050000}"/>
-    <cellStyle name="常规 2 4 2" xfId="1221" xr:uid="{00000000-0005-0000-0000-000036050000}"/>
-    <cellStyle name="常规 2 4 2 2" xfId="1222" xr:uid="{00000000-0005-0000-0000-000037050000}"/>
-    <cellStyle name="常规 2 4 2 3" xfId="1223" xr:uid="{00000000-0005-0000-0000-000038050000}"/>
-    <cellStyle name="常规 2 4 2 4" xfId="1224" xr:uid="{00000000-0005-0000-0000-000039050000}"/>
-    <cellStyle name="常规 2 4 2 5" xfId="1225" xr:uid="{00000000-0005-0000-0000-00003A050000}"/>
-    <cellStyle name="常规 2 4 3" xfId="1226" xr:uid="{00000000-0005-0000-0000-00003B050000}"/>
-    <cellStyle name="常规 2 4 4" xfId="1227" xr:uid="{00000000-0005-0000-0000-00003C050000}"/>
-    <cellStyle name="常规 2 4 5" xfId="1228" xr:uid="{00000000-0005-0000-0000-00003D050000}"/>
-    <cellStyle name="常规 2 4 6" xfId="1229" xr:uid="{00000000-0005-0000-0000-00003E050000}"/>
-    <cellStyle name="常规 2 5" xfId="1230" xr:uid="{00000000-0005-0000-0000-00003F050000}"/>
-    <cellStyle name="常规 2 5 2" xfId="1231" xr:uid="{00000000-0005-0000-0000-000040050000}"/>
-    <cellStyle name="常规 2 5 2 2" xfId="1232" xr:uid="{00000000-0005-0000-0000-000041050000}"/>
-    <cellStyle name="常规 2 5 2 3" xfId="1233" xr:uid="{00000000-0005-0000-0000-000042050000}"/>
-    <cellStyle name="常规 2 5 2 4" xfId="1234" xr:uid="{00000000-0005-0000-0000-000043050000}"/>
-    <cellStyle name="常规 2 5 2 5" xfId="1000" xr:uid="{00000000-0005-0000-0000-000044050000}"/>
-    <cellStyle name="常规 2 5 3" xfId="1235" xr:uid="{00000000-0005-0000-0000-000045050000}"/>
-    <cellStyle name="常规 2 5 4" xfId="1236" xr:uid="{00000000-0005-0000-0000-000046050000}"/>
-    <cellStyle name="常规 2 5 5" xfId="1237" xr:uid="{00000000-0005-0000-0000-000047050000}"/>
-    <cellStyle name="常规 2 5 6" xfId="1238" xr:uid="{00000000-0005-0000-0000-000048050000}"/>
-    <cellStyle name="常规 2 6" xfId="1239" xr:uid="{00000000-0005-0000-0000-000049050000}"/>
-    <cellStyle name="常规 2 6 2" xfId="1240" xr:uid="{00000000-0005-0000-0000-00004A050000}"/>
-    <cellStyle name="常规 2 6 3" xfId="1241" xr:uid="{00000000-0005-0000-0000-00004B050000}"/>
-    <cellStyle name="常规 2 6 4" xfId="1242" xr:uid="{00000000-0005-0000-0000-00004C050000}"/>
-    <cellStyle name="常规 2 6 5" xfId="1243" xr:uid="{00000000-0005-0000-0000-00004D050000}"/>
-    <cellStyle name="常规 2 7" xfId="1166" xr:uid="{00000000-0005-0000-0000-00004E050000}"/>
-    <cellStyle name="常规 2 7 2" xfId="1244" xr:uid="{00000000-0005-0000-0000-00004F050000}"/>
-    <cellStyle name="常规 2 7 3" xfId="1245" xr:uid="{00000000-0005-0000-0000-000050050000}"/>
-    <cellStyle name="常规 2 7 4" xfId="1246" xr:uid="{00000000-0005-0000-0000-000051050000}"/>
-    <cellStyle name="常规 2 8" xfId="1168" xr:uid="{00000000-0005-0000-0000-000052050000}"/>
-    <cellStyle name="常规 2 8 2" xfId="967" xr:uid="{00000000-0005-0000-0000-000053050000}"/>
-    <cellStyle name="常规 2 8 3" xfId="969" xr:uid="{00000000-0005-0000-0000-000054050000}"/>
-    <cellStyle name="常规 2 9" xfId="1648" xr:uid="{00000000-0005-0000-0000-000055050000}"/>
-    <cellStyle name="常规 20" xfId="238" xr:uid="{00000000-0005-0000-0000-000056050000}"/>
-    <cellStyle name="常规 20 2" xfId="1141" xr:uid="{00000000-0005-0000-0000-000057050000}"/>
-    <cellStyle name="常规 20 3" xfId="1150" xr:uid="{00000000-0005-0000-0000-000058050000}"/>
-    <cellStyle name="常规 21" xfId="1161" xr:uid="{00000000-0005-0000-0000-000059050000}"/>
-    <cellStyle name="常规 21 2" xfId="1163" xr:uid="{00000000-0005-0000-0000-00005A050000}"/>
-    <cellStyle name="常规 22" xfId="1180" xr:uid="{00000000-0005-0000-0000-00005B050000}"/>
-    <cellStyle name="常规 22 2" xfId="1182" xr:uid="{00000000-0005-0000-0000-00005C050000}"/>
-    <cellStyle name="常规 22 2 2" xfId="1247" xr:uid="{00000000-0005-0000-0000-00005D050000}"/>
-    <cellStyle name="常规 22 2 3" xfId="1248" xr:uid="{00000000-0005-0000-0000-00005E050000}"/>
-    <cellStyle name="常规 22 2 4" xfId="1249" xr:uid="{00000000-0005-0000-0000-00005F050000}"/>
-    <cellStyle name="常规 22 2 5" xfId="103" xr:uid="{00000000-0005-0000-0000-000060050000}"/>
-    <cellStyle name="常规 22 3" xfId="1184" xr:uid="{00000000-0005-0000-0000-000061050000}"/>
-    <cellStyle name="常规 22 4" xfId="1250" xr:uid="{00000000-0005-0000-0000-000062050000}"/>
-    <cellStyle name="常规 22 5" xfId="1251" xr:uid="{00000000-0005-0000-0000-000063050000}"/>
-    <cellStyle name="常规 22 6" xfId="1252" xr:uid="{00000000-0005-0000-0000-000064050000}"/>
-    <cellStyle name="常规 23" xfId="1186" xr:uid="{00000000-0005-0000-0000-000065050000}"/>
-    <cellStyle name="常规 23 2" xfId="1188" xr:uid="{00000000-0005-0000-0000-000066050000}"/>
-    <cellStyle name="常规 23 2 2" xfId="1253" xr:uid="{00000000-0005-0000-0000-000067050000}"/>
-    <cellStyle name="常规 23 2 3" xfId="1254" xr:uid="{00000000-0005-0000-0000-000068050000}"/>
-    <cellStyle name="常规 23 2 4" xfId="1255" xr:uid="{00000000-0005-0000-0000-000069050000}"/>
-    <cellStyle name="常规 23 2 5" xfId="142" xr:uid="{00000000-0005-0000-0000-00006A050000}"/>
-    <cellStyle name="常规 23 3" xfId="1190" xr:uid="{00000000-0005-0000-0000-00006B050000}"/>
-    <cellStyle name="常规 23 4" xfId="1256" xr:uid="{00000000-0005-0000-0000-00006C050000}"/>
-    <cellStyle name="常规 23 5" xfId="1257" xr:uid="{00000000-0005-0000-0000-00006D050000}"/>
-    <cellStyle name="常规 23 6" xfId="1258" xr:uid="{00000000-0005-0000-0000-00006E050000}"/>
-    <cellStyle name="常规 24" xfId="1192" xr:uid="{00000000-0005-0000-0000-00006F050000}"/>
-    <cellStyle name="常规 24 2" xfId="1194" xr:uid="{00000000-0005-0000-0000-000070050000}"/>
-    <cellStyle name="常规 25" xfId="1260" xr:uid="{00000000-0005-0000-0000-000071050000}"/>
-    <cellStyle name="常规 25 2" xfId="1261" xr:uid="{00000000-0005-0000-0000-000072050000}"/>
-    <cellStyle name="常规 26" xfId="1263" xr:uid="{00000000-0005-0000-0000-000073050000}"/>
-    <cellStyle name="常规 26 2" xfId="31" xr:uid="{00000000-0005-0000-0000-000074050000}"/>
-    <cellStyle name="常规 27" xfId="1265" xr:uid="{00000000-0005-0000-0000-000075050000}"/>
-    <cellStyle name="常规 27 2" xfId="1267" xr:uid="{00000000-0005-0000-0000-000076050000}"/>
-    <cellStyle name="常规 27 2 2" xfId="1268" xr:uid="{00000000-0005-0000-0000-000077050000}"/>
-    <cellStyle name="常规 27 2 3" xfId="1269" xr:uid="{00000000-0005-0000-0000-000078050000}"/>
-    <cellStyle name="常规 27 2 4" xfId="1270" xr:uid="{00000000-0005-0000-0000-000079050000}"/>
-    <cellStyle name="常规 27 2 5" xfId="1271" xr:uid="{00000000-0005-0000-0000-00007A050000}"/>
-    <cellStyle name="常规 27 3" xfId="1273" xr:uid="{00000000-0005-0000-0000-00007B050000}"/>
-    <cellStyle name="常规 27 4" xfId="1275" xr:uid="{00000000-0005-0000-0000-00007C050000}"/>
-    <cellStyle name="常规 27 5" xfId="1277" xr:uid="{00000000-0005-0000-0000-00007D050000}"/>
-    <cellStyle name="常规 27 6" xfId="1278" xr:uid="{00000000-0005-0000-0000-00007E050000}"/>
-    <cellStyle name="常规 28" xfId="1280" xr:uid="{00000000-0005-0000-0000-00007F050000}"/>
-    <cellStyle name="常规 28 2" xfId="153" xr:uid="{00000000-0005-0000-0000-000080050000}"/>
-    <cellStyle name="常规 28 2 2" xfId="1281" xr:uid="{00000000-0005-0000-0000-000081050000}"/>
-    <cellStyle name="常规 28 2 3" xfId="1282" xr:uid="{00000000-0005-0000-0000-000082050000}"/>
-    <cellStyle name="常规 28 2 4" xfId="1283" xr:uid="{00000000-0005-0000-0000-000083050000}"/>
-    <cellStyle name="常规 28 2 5" xfId="1284" xr:uid="{00000000-0005-0000-0000-000084050000}"/>
-    <cellStyle name="常规 28 3" xfId="161" xr:uid="{00000000-0005-0000-0000-000085050000}"/>
-    <cellStyle name="常规 28 4" xfId="1285" xr:uid="{00000000-0005-0000-0000-000086050000}"/>
-    <cellStyle name="常规 28 5" xfId="1286" xr:uid="{00000000-0005-0000-0000-000087050000}"/>
-    <cellStyle name="常规 28 6" xfId="1288" xr:uid="{00000000-0005-0000-0000-000088050000}"/>
-    <cellStyle name="常规 29" xfId="1290" xr:uid="{00000000-0005-0000-0000-000089050000}"/>
-    <cellStyle name="常规 29 2" xfId="1292" xr:uid="{00000000-0005-0000-0000-00008A050000}"/>
-    <cellStyle name="常规 29 2 2" xfId="1293" xr:uid="{00000000-0005-0000-0000-00008B050000}"/>
-    <cellStyle name="常规 29 2 3" xfId="1294" xr:uid="{00000000-0005-0000-0000-00008C050000}"/>
-    <cellStyle name="常规 29 2 4" xfId="1295" xr:uid="{00000000-0005-0000-0000-00008D050000}"/>
-    <cellStyle name="常规 29 2 5" xfId="1296" xr:uid="{00000000-0005-0000-0000-00008E050000}"/>
-    <cellStyle name="常规 29 3" xfId="1297" xr:uid="{00000000-0005-0000-0000-00008F050000}"/>
-    <cellStyle name="常规 29 4" xfId="1298" xr:uid="{00000000-0005-0000-0000-000090050000}"/>
-    <cellStyle name="常规 29 5" xfId="1299" xr:uid="{00000000-0005-0000-0000-000091050000}"/>
-    <cellStyle name="常规 29 6" xfId="1301" xr:uid="{00000000-0005-0000-0000-000092050000}"/>
-    <cellStyle name="常规 3" xfId="1302" xr:uid="{00000000-0005-0000-0000-000093050000}"/>
-    <cellStyle name="常规 3 10" xfId="1659" xr:uid="{00000000-0005-0000-0000-000094050000}"/>
-    <cellStyle name="常规 3 2" xfId="1002" xr:uid="{00000000-0005-0000-0000-000095050000}"/>
-    <cellStyle name="常规 3 2 2" xfId="1004" xr:uid="{00000000-0005-0000-0000-000096050000}"/>
-    <cellStyle name="常规 3 2 2 2" xfId="397" xr:uid="{00000000-0005-0000-0000-000097050000}"/>
-    <cellStyle name="常规 3 2 2 2 2" xfId="1303" xr:uid="{00000000-0005-0000-0000-000098050000}"/>
-    <cellStyle name="常规 3 2 2 2 3" xfId="1304" xr:uid="{00000000-0005-0000-0000-000099050000}"/>
-    <cellStyle name="常规 3 2 2 2 4" xfId="1305" xr:uid="{00000000-0005-0000-0000-00009A050000}"/>
-    <cellStyle name="常规 3 2 2 2 5" xfId="1306" xr:uid="{00000000-0005-0000-0000-00009B050000}"/>
-    <cellStyle name="常规 3 2 2 3" xfId="401" xr:uid="{00000000-0005-0000-0000-00009C050000}"/>
-    <cellStyle name="常规 3 2 2 4" xfId="1307" xr:uid="{00000000-0005-0000-0000-00009D050000}"/>
-    <cellStyle name="常规 3 2 2 5" xfId="1308" xr:uid="{00000000-0005-0000-0000-00009E050000}"/>
-    <cellStyle name="常规 3 2 2 6" xfId="1309" xr:uid="{00000000-0005-0000-0000-00009F050000}"/>
-    <cellStyle name="常规 3 2 3" xfId="1310" xr:uid="{00000000-0005-0000-0000-0000A0050000}"/>
-    <cellStyle name="常规 3 2 3 2" xfId="1311" xr:uid="{00000000-0005-0000-0000-0000A1050000}"/>
-    <cellStyle name="常规 3 2 3 3" xfId="1312" xr:uid="{00000000-0005-0000-0000-0000A2050000}"/>
-    <cellStyle name="常规 3 2 3 4" xfId="1313" xr:uid="{00000000-0005-0000-0000-0000A3050000}"/>
-    <cellStyle name="常规 3 2 3 5" xfId="867" xr:uid="{00000000-0005-0000-0000-0000A4050000}"/>
-    <cellStyle name="常规 3 2 4" xfId="1314" xr:uid="{00000000-0005-0000-0000-0000A5050000}"/>
-    <cellStyle name="常规 3 2 5" xfId="927" xr:uid="{00000000-0005-0000-0000-0000A6050000}"/>
-    <cellStyle name="常规 3 2 6" xfId="871" xr:uid="{00000000-0005-0000-0000-0000A7050000}"/>
-    <cellStyle name="常规 3 2 7" xfId="874" xr:uid="{00000000-0005-0000-0000-0000A8050000}"/>
-    <cellStyle name="常规 3 3" xfId="1006" xr:uid="{00000000-0005-0000-0000-0000A9050000}"/>
-    <cellStyle name="常规 3 3 2" xfId="1008" xr:uid="{00000000-0005-0000-0000-0000AA050000}"/>
-    <cellStyle name="常规 3 3 2 2" xfId="1315" xr:uid="{00000000-0005-0000-0000-0000AB050000}"/>
-    <cellStyle name="常规 3 3 2 3" xfId="1316" xr:uid="{00000000-0005-0000-0000-0000AC050000}"/>
-    <cellStyle name="常规 3 3 2 4" xfId="1317" xr:uid="{00000000-0005-0000-0000-0000AD050000}"/>
-    <cellStyle name="常规 3 3 2 5" xfId="1318" xr:uid="{00000000-0005-0000-0000-0000AE050000}"/>
-    <cellStyle name="常规 3 3 3" xfId="1319" xr:uid="{00000000-0005-0000-0000-0000AF050000}"/>
-    <cellStyle name="常规 3 3 4" xfId="1320" xr:uid="{00000000-0005-0000-0000-0000B0050000}"/>
-    <cellStyle name="常规 3 3 5" xfId="1321" xr:uid="{00000000-0005-0000-0000-0000B1050000}"/>
-    <cellStyle name="常规 3 3 6" xfId="1322" xr:uid="{00000000-0005-0000-0000-0000B2050000}"/>
-    <cellStyle name="常规 3 4" xfId="1323" xr:uid="{00000000-0005-0000-0000-0000B3050000}"/>
-    <cellStyle name="常规 3 5" xfId="1324" xr:uid="{00000000-0005-0000-0000-0000B4050000}"/>
-    <cellStyle name="常规 3 5 2" xfId="1325" xr:uid="{00000000-0005-0000-0000-0000B5050000}"/>
-    <cellStyle name="常规 3 5 3" xfId="1326" xr:uid="{00000000-0005-0000-0000-0000B6050000}"/>
-    <cellStyle name="常规 3 5 4" xfId="1327" xr:uid="{00000000-0005-0000-0000-0000B7050000}"/>
-    <cellStyle name="常规 3 5 5" xfId="1329" xr:uid="{00000000-0005-0000-0000-0000B8050000}"/>
-    <cellStyle name="常规 3 6" xfId="1330" xr:uid="{00000000-0005-0000-0000-0000B9050000}"/>
-    <cellStyle name="常规 3 6 2" xfId="1331" xr:uid="{00000000-0005-0000-0000-0000BA050000}"/>
-    <cellStyle name="常规 3 7" xfId="1332" xr:uid="{00000000-0005-0000-0000-0000BB050000}"/>
-    <cellStyle name="常规 3 7 2" xfId="92" xr:uid="{00000000-0005-0000-0000-0000BC050000}"/>
-    <cellStyle name="常规 3 7 3" xfId="1333" xr:uid="{00000000-0005-0000-0000-0000BD050000}"/>
-    <cellStyle name="常规 3 8" xfId="1334" xr:uid="{00000000-0005-0000-0000-0000BE050000}"/>
-    <cellStyle name="常规 3 9" xfId="1649" xr:uid="{00000000-0005-0000-0000-0000BF050000}"/>
-    <cellStyle name="常规 30" xfId="1259" xr:uid="{00000000-0005-0000-0000-0000C0050000}"/>
-    <cellStyle name="常规 31" xfId="1262" xr:uid="{00000000-0005-0000-0000-0000C1050000}"/>
-    <cellStyle name="常规 31 2" xfId="30" xr:uid="{00000000-0005-0000-0000-0000C2050000}"/>
-    <cellStyle name="常规 31 2 2" xfId="1335" xr:uid="{00000000-0005-0000-0000-0000C3050000}"/>
-    <cellStyle name="常规 31 2 3" xfId="1336" xr:uid="{00000000-0005-0000-0000-0000C4050000}"/>
-    <cellStyle name="常规 31 2 4" xfId="1337" xr:uid="{00000000-0005-0000-0000-0000C5050000}"/>
-    <cellStyle name="常规 31 2 5" xfId="1338" xr:uid="{00000000-0005-0000-0000-0000C6050000}"/>
-    <cellStyle name="常规 31 3" xfId="67" xr:uid="{00000000-0005-0000-0000-0000C7050000}"/>
-    <cellStyle name="常规 31 4" xfId="70" xr:uid="{00000000-0005-0000-0000-0000C8050000}"/>
-    <cellStyle name="常规 31 5" xfId="74" xr:uid="{00000000-0005-0000-0000-0000C9050000}"/>
-    <cellStyle name="常规 31 6" xfId="1339" xr:uid="{00000000-0005-0000-0000-0000CA050000}"/>
-    <cellStyle name="常规 32" xfId="1264" xr:uid="{00000000-0005-0000-0000-0000CB050000}"/>
-    <cellStyle name="常规 32 2" xfId="1266" xr:uid="{00000000-0005-0000-0000-0000CC050000}"/>
-    <cellStyle name="常规 32 3" xfId="1272" xr:uid="{00000000-0005-0000-0000-0000CD050000}"/>
-    <cellStyle name="常规 32 4" xfId="1274" xr:uid="{00000000-0005-0000-0000-0000CE050000}"/>
-    <cellStyle name="常规 32 5" xfId="1276" xr:uid="{00000000-0005-0000-0000-0000CF050000}"/>
-    <cellStyle name="常规 33" xfId="8" xr:uid="{00000000-0005-0000-0000-0000D0050000}"/>
-    <cellStyle name="常规 33 2" xfId="152" xr:uid="{00000000-0005-0000-0000-0000D1050000}"/>
-    <cellStyle name="常规 33 3" xfId="1279" xr:uid="{00000000-0005-0000-0000-0000D2050000}"/>
-    <cellStyle name="常规 34" xfId="1289" xr:uid="{00000000-0005-0000-0000-0000D3050000}"/>
-    <cellStyle name="常规 34 2" xfId="1291" xr:uid="{00000000-0005-0000-0000-0000D4050000}"/>
-    <cellStyle name="常规 35" xfId="12" xr:uid="{00000000-0005-0000-0000-0000D5050000}"/>
-    <cellStyle name="常规 35 2" xfId="1341" xr:uid="{00000000-0005-0000-0000-0000D6050000}"/>
-    <cellStyle name="常规 36" xfId="1343" xr:uid="{00000000-0005-0000-0000-0000D7050000}"/>
-    <cellStyle name="常规 36 2" xfId="1345" xr:uid="{00000000-0005-0000-0000-0000D8050000}"/>
-    <cellStyle name="常规 37" xfId="1347" xr:uid="{00000000-0005-0000-0000-0000D9050000}"/>
-    <cellStyle name="常规 37 2" xfId="1349" xr:uid="{00000000-0005-0000-0000-0000DA050000}"/>
-    <cellStyle name="常规 37 3" xfId="1350" xr:uid="{00000000-0005-0000-0000-0000DB050000}"/>
-    <cellStyle name="常规 38" xfId="824" xr:uid="{00000000-0005-0000-0000-0000DC050000}"/>
-    <cellStyle name="常规 38 2" xfId="827" xr:uid="{00000000-0005-0000-0000-0000DD050000}"/>
-    <cellStyle name="常规 38 3" xfId="829" xr:uid="{00000000-0005-0000-0000-0000DE050000}"/>
-    <cellStyle name="常规 38 4" xfId="831" xr:uid="{00000000-0005-0000-0000-0000DF050000}"/>
-    <cellStyle name="常规 38 5" xfId="833" xr:uid="{00000000-0005-0000-0000-0000E0050000}"/>
-    <cellStyle name="常规 39" xfId="23" xr:uid="{00000000-0005-0000-0000-0000E1050000}"/>
-    <cellStyle name="常规 39 2" xfId="1352" xr:uid="{00000000-0005-0000-0000-0000E2050000}"/>
-    <cellStyle name="常规 39 3" xfId="1353" xr:uid="{00000000-0005-0000-0000-0000E3050000}"/>
-    <cellStyle name="常规 39 4" xfId="1354" xr:uid="{00000000-0005-0000-0000-0000E4050000}"/>
-    <cellStyle name="常规 4" xfId="1355" xr:uid="{00000000-0005-0000-0000-0000E5050000}"/>
-    <cellStyle name="常规 4 2" xfId="1356" xr:uid="{00000000-0005-0000-0000-0000E6050000}"/>
-    <cellStyle name="常规 4 2 2" xfId="1358" xr:uid="{00000000-0005-0000-0000-0000E7050000}"/>
-    <cellStyle name="常规 4 2 2 2" xfId="1361" xr:uid="{00000000-0005-0000-0000-0000E8050000}"/>
-    <cellStyle name="常规 4 2 2 2 2" xfId="1363" xr:uid="{00000000-0005-0000-0000-0000E9050000}"/>
-    <cellStyle name="常规 4 2 2 2 3" xfId="1365" xr:uid="{00000000-0005-0000-0000-0000EA050000}"/>
-    <cellStyle name="常规 4 2 2 2 4" xfId="1367" xr:uid="{00000000-0005-0000-0000-0000EB050000}"/>
-    <cellStyle name="常规 4 2 2 2 5" xfId="1369" xr:uid="{00000000-0005-0000-0000-0000EC050000}"/>
-    <cellStyle name="常规 4 2 2 3" xfId="41" xr:uid="{00000000-0005-0000-0000-0000ED050000}"/>
-    <cellStyle name="常规 4 2 2 4" xfId="1372" xr:uid="{00000000-0005-0000-0000-0000EE050000}"/>
-    <cellStyle name="常规 4 2 2 5" xfId="1375" xr:uid="{00000000-0005-0000-0000-0000EF050000}"/>
-    <cellStyle name="常规 4 2 2 6" xfId="1377" xr:uid="{00000000-0005-0000-0000-0000F0050000}"/>
-    <cellStyle name="常规 4 2 3" xfId="1379" xr:uid="{00000000-0005-0000-0000-0000F1050000}"/>
-    <cellStyle name="常规 4 2 3 2" xfId="1380" xr:uid="{00000000-0005-0000-0000-0000F2050000}"/>
-    <cellStyle name="常规 4 2 3 3" xfId="1381" xr:uid="{00000000-0005-0000-0000-0000F3050000}"/>
-    <cellStyle name="常规 4 2 3 4" xfId="1382" xr:uid="{00000000-0005-0000-0000-0000F4050000}"/>
-    <cellStyle name="常规 4 2 3 5" xfId="1384" xr:uid="{00000000-0005-0000-0000-0000F5050000}"/>
-    <cellStyle name="常规 4 2 4" xfId="1386" xr:uid="{00000000-0005-0000-0000-0000F6050000}"/>
-    <cellStyle name="常规 4 2 5" xfId="1388" xr:uid="{00000000-0005-0000-0000-0000F7050000}"/>
-    <cellStyle name="常规 4 2 6" xfId="1391" xr:uid="{00000000-0005-0000-0000-0000F8050000}"/>
-    <cellStyle name="常规 4 2 7" xfId="1393" xr:uid="{00000000-0005-0000-0000-0000F9050000}"/>
-    <cellStyle name="常规 4 3" xfId="1394" xr:uid="{00000000-0005-0000-0000-0000FA050000}"/>
-    <cellStyle name="常规 4 3 2" xfId="1396" xr:uid="{00000000-0005-0000-0000-0000FB050000}"/>
-    <cellStyle name="常规 4 3 2 2" xfId="1398" xr:uid="{00000000-0005-0000-0000-0000FC050000}"/>
-    <cellStyle name="常规 4 3 2 3" xfId="1400" xr:uid="{00000000-0005-0000-0000-0000FD050000}"/>
-    <cellStyle name="常规 4 3 2 4" xfId="1402" xr:uid="{00000000-0005-0000-0000-0000FE050000}"/>
-    <cellStyle name="常规 4 3 2 5" xfId="1404" xr:uid="{00000000-0005-0000-0000-0000FF050000}"/>
-    <cellStyle name="常规 4 3 3" xfId="1406" xr:uid="{00000000-0005-0000-0000-000000060000}"/>
-    <cellStyle name="常规 4 3 4" xfId="1408" xr:uid="{00000000-0005-0000-0000-000001060000}"/>
-    <cellStyle name="常规 4 3 5" xfId="1410" xr:uid="{00000000-0005-0000-0000-000002060000}"/>
-    <cellStyle name="常规 4 3 6" xfId="1413" xr:uid="{00000000-0005-0000-0000-000003060000}"/>
-    <cellStyle name="常规 4 4" xfId="1357" xr:uid="{00000000-0005-0000-0000-000004060000}"/>
-    <cellStyle name="常规 4 4 2" xfId="1360" xr:uid="{00000000-0005-0000-0000-000005060000}"/>
-    <cellStyle name="常规 4 4 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000006060000}"/>
-    <cellStyle name="常规 4 4 4" xfId="1371" xr:uid="{00000000-0005-0000-0000-000007060000}"/>
-    <cellStyle name="常规 4 4 5" xfId="1374" xr:uid="{00000000-0005-0000-0000-000008060000}"/>
-    <cellStyle name="常规 4 5" xfId="1378" xr:uid="{00000000-0005-0000-0000-000009060000}"/>
-    <cellStyle name="常规 4 6" xfId="1385" xr:uid="{00000000-0005-0000-0000-00000A060000}"/>
-    <cellStyle name="常规 4 7" xfId="1387" xr:uid="{00000000-0005-0000-0000-00000B060000}"/>
-    <cellStyle name="常规 4 8" xfId="1390" xr:uid="{00000000-0005-0000-0000-00000C060000}"/>
-    <cellStyle name="常规 40" xfId="1340" xr:uid="{00000000-0005-0000-0000-00000D060000}"/>
-    <cellStyle name="常规 40 2" xfId="1414" xr:uid="{00000000-0005-0000-0000-00000E060000}"/>
-    <cellStyle name="常规 41" xfId="1342" xr:uid="{00000000-0005-0000-0000-00000F060000}"/>
-    <cellStyle name="常规 41 2" xfId="1344" xr:uid="{00000000-0005-0000-0000-000010060000}"/>
-    <cellStyle name="常规 42" xfId="1346" xr:uid="{00000000-0005-0000-0000-000011060000}"/>
-    <cellStyle name="常规 42 2" xfId="1348" xr:uid="{00000000-0005-0000-0000-000012060000}"/>
-    <cellStyle name="常规 43" xfId="823" xr:uid="{00000000-0005-0000-0000-000013060000}"/>
-    <cellStyle name="常规 43 2" xfId="826" xr:uid="{00000000-0005-0000-0000-000014060000}"/>
-    <cellStyle name="常规 44" xfId="22" xr:uid="{00000000-0005-0000-0000-000015060000}"/>
-    <cellStyle name="常规 44 2" xfId="1351" xr:uid="{00000000-0005-0000-0000-000016060000}"/>
-    <cellStyle name="常规 45" xfId="836" xr:uid="{00000000-0005-0000-0000-000017060000}"/>
-    <cellStyle name="常规 45 2" xfId="1415" xr:uid="{00000000-0005-0000-0000-000018060000}"/>
-    <cellStyle name="常规 46" xfId="839" xr:uid="{00000000-0005-0000-0000-000019060000}"/>
-    <cellStyle name="常规 47" xfId="842" xr:uid="{00000000-0005-0000-0000-00001A060000}"/>
-    <cellStyle name="常规 47 2" xfId="1416" xr:uid="{00000000-0005-0000-0000-00001B060000}"/>
-    <cellStyle name="常规 48" xfId="1418" xr:uid="{00000000-0005-0000-0000-00001C060000}"/>
-    <cellStyle name="常规 49" xfId="1420" xr:uid="{00000000-0005-0000-0000-00001D060000}"/>
-    <cellStyle name="常规 5" xfId="1421" xr:uid="{00000000-0005-0000-0000-00001E060000}"/>
-    <cellStyle name="常规 5 2" xfId="1422" xr:uid="{00000000-0005-0000-0000-00001F060000}"/>
-    <cellStyle name="常规 5 2 2" xfId="1423" xr:uid="{00000000-0005-0000-0000-000020060000}"/>
-    <cellStyle name="常规 5 2 2 2" xfId="1424" xr:uid="{00000000-0005-0000-0000-000021060000}"/>
-    <cellStyle name="常规 5 2 2 2 2" xfId="1149" xr:uid="{00000000-0005-0000-0000-000022060000}"/>
-    <cellStyle name="常规 5 2 2 2 3" xfId="1154" xr:uid="{00000000-0005-0000-0000-000023060000}"/>
-    <cellStyle name="常规 5 2 2 2 4" xfId="1156" xr:uid="{00000000-0005-0000-0000-000024060000}"/>
-    <cellStyle name="常规 5 2 2 2 5" xfId="1158" xr:uid="{00000000-0005-0000-0000-000025060000}"/>
-    <cellStyle name="常规 5 2 2 3" xfId="1425" xr:uid="{00000000-0005-0000-0000-000026060000}"/>
-    <cellStyle name="常规 5 2 2 4" xfId="1426" xr:uid="{00000000-0005-0000-0000-000027060000}"/>
-    <cellStyle name="常规 5 2 2 5" xfId="1427" xr:uid="{00000000-0005-0000-0000-000028060000}"/>
-    <cellStyle name="常规 5 2 2 6" xfId="1428" xr:uid="{00000000-0005-0000-0000-000029060000}"/>
-    <cellStyle name="常规 5 2 3" xfId="1429" xr:uid="{00000000-0005-0000-0000-00002A060000}"/>
-    <cellStyle name="常规 5 2 3 2" xfId="1045" xr:uid="{00000000-0005-0000-0000-00002B060000}"/>
-    <cellStyle name="常规 5 2 3 3" xfId="1430" xr:uid="{00000000-0005-0000-0000-00002C060000}"/>
-    <cellStyle name="常规 5 2 3 4" xfId="1431" xr:uid="{00000000-0005-0000-0000-00002D060000}"/>
-    <cellStyle name="常规 5 2 3 5" xfId="1432" xr:uid="{00000000-0005-0000-0000-00002E060000}"/>
-    <cellStyle name="常规 5 2 4" xfId="1433" xr:uid="{00000000-0005-0000-0000-00002F060000}"/>
-    <cellStyle name="常规 5 2 5" xfId="1434" xr:uid="{00000000-0005-0000-0000-000030060000}"/>
-    <cellStyle name="常规 5 2 6" xfId="1436" xr:uid="{00000000-0005-0000-0000-000031060000}"/>
-    <cellStyle name="常规 5 2 7" xfId="1438" xr:uid="{00000000-0005-0000-0000-000032060000}"/>
-    <cellStyle name="常规 5 3" xfId="1439" xr:uid="{00000000-0005-0000-0000-000033060000}"/>
-    <cellStyle name="常规 5 3 2" xfId="337" xr:uid="{00000000-0005-0000-0000-000034060000}"/>
-    <cellStyle name="常规 5 3 2 2" xfId="341" xr:uid="{00000000-0005-0000-0000-000035060000}"/>
-    <cellStyle name="常规 5 3 2 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000036060000}"/>
-    <cellStyle name="常规 5 3 2 4" xfId="1440" xr:uid="{00000000-0005-0000-0000-000037060000}"/>
-    <cellStyle name="常规 5 3 2 5" xfId="1441" xr:uid="{00000000-0005-0000-0000-000038060000}"/>
-    <cellStyle name="常规 5 3 3" xfId="499" xr:uid="{00000000-0005-0000-0000-000039060000}"/>
-    <cellStyle name="常规 5 3 4" xfId="503" xr:uid="{00000000-0005-0000-0000-00003A060000}"/>
-    <cellStyle name="常规 5 3 5" xfId="505" xr:uid="{00000000-0005-0000-0000-00003B060000}"/>
-    <cellStyle name="常规 5 3 6" xfId="507" xr:uid="{00000000-0005-0000-0000-00003C060000}"/>
-    <cellStyle name="常规 5 4" xfId="1395" xr:uid="{00000000-0005-0000-0000-00003D060000}"/>
-    <cellStyle name="常规 5 4 2" xfId="1397" xr:uid="{00000000-0005-0000-0000-00003E060000}"/>
-    <cellStyle name="常规 5 4 3" xfId="1399" xr:uid="{00000000-0005-0000-0000-00003F060000}"/>
-    <cellStyle name="常规 5 4 4" xfId="1401" xr:uid="{00000000-0005-0000-0000-000040060000}"/>
-    <cellStyle name="常规 5 4 5" xfId="1403" xr:uid="{00000000-0005-0000-0000-000041060000}"/>
-    <cellStyle name="常规 5 5" xfId="1405" xr:uid="{00000000-0005-0000-0000-000042060000}"/>
-    <cellStyle name="常规 5 6" xfId="1407" xr:uid="{00000000-0005-0000-0000-000043060000}"/>
-    <cellStyle name="常规 5 7" xfId="1409" xr:uid="{00000000-0005-0000-0000-000044060000}"/>
-    <cellStyle name="常规 5 8" xfId="1412" xr:uid="{00000000-0005-0000-0000-000045060000}"/>
-    <cellStyle name="常规 50" xfId="835" xr:uid="{00000000-0005-0000-0000-000046060000}"/>
-    <cellStyle name="常规 51" xfId="838" xr:uid="{00000000-0005-0000-0000-000047060000}"/>
-    <cellStyle name="常规 52" xfId="841" xr:uid="{00000000-0005-0000-0000-000048060000}"/>
-    <cellStyle name="常规 53" xfId="1417" xr:uid="{00000000-0005-0000-0000-000049060000}"/>
-    <cellStyle name="常规 54" xfId="1419" xr:uid="{00000000-0005-0000-0000-00004A060000}"/>
-    <cellStyle name="常规 55" xfId="85" xr:uid="{00000000-0005-0000-0000-00004B060000}"/>
-    <cellStyle name="常规 56" xfId="105" xr:uid="{00000000-0005-0000-0000-00004C060000}"/>
-    <cellStyle name="常规 57" xfId="109" xr:uid="{00000000-0005-0000-0000-00004D060000}"/>
-    <cellStyle name="常规 6" xfId="1442" xr:uid="{00000000-0005-0000-0000-00004E060000}"/>
-    <cellStyle name="常规 6 2" xfId="1443" xr:uid="{00000000-0005-0000-0000-00004F060000}"/>
-    <cellStyle name="常规 6 2 2" xfId="634" xr:uid="{00000000-0005-0000-0000-000050060000}"/>
-    <cellStyle name="常规 6 2 2 2" xfId="1444" xr:uid="{00000000-0005-0000-0000-000051060000}"/>
-    <cellStyle name="常规 6 2 2 2 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000052060000}"/>
-    <cellStyle name="常规 6 2 2 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-000053060000}"/>
-    <cellStyle name="常规 6 2 2 2 4" xfId="783" xr:uid="{00000000-0005-0000-0000-000054060000}"/>
-    <cellStyle name="常规 6 2 2 2 5" xfId="785" xr:uid="{00000000-0005-0000-0000-000055060000}"/>
-    <cellStyle name="常规 6 2 2 3" xfId="1445" xr:uid="{00000000-0005-0000-0000-000056060000}"/>
-    <cellStyle name="常规 6 2 2 4" xfId="1446" xr:uid="{00000000-0005-0000-0000-000057060000}"/>
-    <cellStyle name="常规 6 2 2 5" xfId="1447" xr:uid="{00000000-0005-0000-0000-000058060000}"/>
-    <cellStyle name="常规 6 2 2 6" xfId="1448" xr:uid="{00000000-0005-0000-0000-000059060000}"/>
-    <cellStyle name="常规 6 2 3" xfId="636" xr:uid="{00000000-0005-0000-0000-00005A060000}"/>
-    <cellStyle name="常规 6 2 3 2" xfId="1449" xr:uid="{00000000-0005-0000-0000-00005B060000}"/>
-    <cellStyle name="常规 6 2 3 3" xfId="1450" xr:uid="{00000000-0005-0000-0000-00005C060000}"/>
-    <cellStyle name="常规 6 2 3 4" xfId="1451" xr:uid="{00000000-0005-0000-0000-00005D060000}"/>
-    <cellStyle name="常规 6 2 3 5" xfId="1452" xr:uid="{00000000-0005-0000-0000-00005E060000}"/>
-    <cellStyle name="常规 6 2 4" xfId="638" xr:uid="{00000000-0005-0000-0000-00005F060000}"/>
-    <cellStyle name="常规 6 2 5" xfId="1453" xr:uid="{00000000-0005-0000-0000-000060060000}"/>
-    <cellStyle name="常规 6 2 6" xfId="738" xr:uid="{00000000-0005-0000-0000-000061060000}"/>
-    <cellStyle name="常规 6 2 7" xfId="750" xr:uid="{00000000-0005-0000-0000-000062060000}"/>
-    <cellStyle name="常规 6 3" xfId="1454" xr:uid="{00000000-0005-0000-0000-000063060000}"/>
-    <cellStyle name="常规 6 3 2" xfId="645" xr:uid="{00000000-0005-0000-0000-000064060000}"/>
-    <cellStyle name="常规 6 3 2 2" xfId="1455" xr:uid="{00000000-0005-0000-0000-000065060000}"/>
-    <cellStyle name="常规 6 3 2 3" xfId="1456" xr:uid="{00000000-0005-0000-0000-000066060000}"/>
-    <cellStyle name="常规 6 3 2 4" xfId="1457" xr:uid="{00000000-0005-0000-0000-000067060000}"/>
-    <cellStyle name="常规 6 3 2 5" xfId="1458" xr:uid="{00000000-0005-0000-0000-000068060000}"/>
-    <cellStyle name="常规 6 3 3" xfId="647" xr:uid="{00000000-0005-0000-0000-000069060000}"/>
-    <cellStyle name="常规 6 3 4" xfId="1459" xr:uid="{00000000-0005-0000-0000-00006A060000}"/>
-    <cellStyle name="常规 6 3 5" xfId="1460" xr:uid="{00000000-0005-0000-0000-00006B060000}"/>
-    <cellStyle name="常规 6 3 6" xfId="763" xr:uid="{00000000-0005-0000-0000-00006C060000}"/>
-    <cellStyle name="常规 6 4" xfId="1359" xr:uid="{00000000-0005-0000-0000-00006D060000}"/>
-    <cellStyle name="常规 6 4 2" xfId="1362" xr:uid="{00000000-0005-0000-0000-00006E060000}"/>
-    <cellStyle name="常规 6 4 3" xfId="1364" xr:uid="{00000000-0005-0000-0000-00006F060000}"/>
-    <cellStyle name="常规 6 4 4" xfId="1366" xr:uid="{00000000-0005-0000-0000-000070060000}"/>
-    <cellStyle name="常规 6 4 5" xfId="1368" xr:uid="{00000000-0005-0000-0000-000071060000}"/>
-    <cellStyle name="常规 6 5" xfId="39" xr:uid="{00000000-0005-0000-0000-000072060000}"/>
-    <cellStyle name="常规 6 6" xfId="1370" xr:uid="{00000000-0005-0000-0000-000073060000}"/>
-    <cellStyle name="常规 6 7" xfId="1373" xr:uid="{00000000-0005-0000-0000-000074060000}"/>
-    <cellStyle name="常规 6 8" xfId="1376" xr:uid="{00000000-0005-0000-0000-000075060000}"/>
-    <cellStyle name="常规 60" xfId="1643" xr:uid="{00000000-0005-0000-0000-000076060000}"/>
-    <cellStyle name="常规 60 2" xfId="1652" xr:uid="{00000000-0005-0000-0000-000077060000}"/>
-    <cellStyle name="常规 61" xfId="1644" xr:uid="{00000000-0005-0000-0000-000078060000}"/>
-    <cellStyle name="常规 61 2" xfId="1653" xr:uid="{00000000-0005-0000-0000-000079060000}"/>
-    <cellStyle name="常规 7" xfId="1461" xr:uid="{00000000-0005-0000-0000-00007A060000}"/>
-    <cellStyle name="常规 8" xfId="1462" xr:uid="{00000000-0005-0000-0000-00007B060000}"/>
-    <cellStyle name="常规 8 2" xfId="1463" xr:uid="{00000000-0005-0000-0000-00007C060000}"/>
-    <cellStyle name="常规 9" xfId="6" xr:uid="{00000000-0005-0000-0000-00007D060000}"/>
+    <cellStyle name="Стиль 1" xfId="693"/>
+    <cellStyle name="Стиль 1 2" xfId="985"/>
+    <cellStyle name="Стиль 1 2 2" xfId="986"/>
+    <cellStyle name="Стиль 1 3" xfId="987"/>
+    <cellStyle name="Стиль 1 3 2" xfId="988"/>
+    <cellStyle name="Стиль 1 4" xfId="989"/>
+    <cellStyle name="Стиль 1 4 2" xfId="990"/>
+    <cellStyle name="Стиль 1 5" xfId="991"/>
+    <cellStyle name="Стиль 1 5 2" xfId="993"/>
+    <cellStyle name="Финансовый 2" xfId="994"/>
+    <cellStyle name="Финансовый 2 10" xfId="995"/>
+    <cellStyle name="Финансовый 2 10 2" xfId="997"/>
+    <cellStyle name="Финансовый 2 2" xfId="221"/>
+    <cellStyle name="Финансовый 2 3" xfId="236"/>
+    <cellStyle name="Финансовый 2 4" xfId="260"/>
+    <cellStyle name="Финансовый 2 4 2" xfId="263"/>
+    <cellStyle name="Финансовый 2 5" xfId="272"/>
+    <cellStyle name="Финансовый 2 5 2" xfId="998"/>
+    <cellStyle name="Финансовый 2 6" xfId="274"/>
+    <cellStyle name="Финансовый 2 6 2" xfId="999"/>
+    <cellStyle name="Финансовый 2 7" xfId="276"/>
+    <cellStyle name="Финансовый 2 7 2" xfId="1001"/>
+    <cellStyle name="Финансовый 2 8" xfId="1003"/>
+    <cellStyle name="Финансовый 2 8 2" xfId="1005"/>
+    <cellStyle name="Финансовый 2 9" xfId="1007"/>
+    <cellStyle name="Финансовый 2 9 2" xfId="1009"/>
+    <cellStyle name="Финансовый 3" xfId="33"/>
+    <cellStyle name="Финансовый 4" xfId="1642"/>
+    <cellStyle name="Финансовый 5" xfId="1651"/>
+    <cellStyle name="千位分隔 10" xfId="1464"/>
+    <cellStyle name="千位分隔 10 2" xfId="1465"/>
+    <cellStyle name="千位分隔 10 2 2" xfId="1466"/>
+    <cellStyle name="千位分隔 10 2 3" xfId="1467"/>
+    <cellStyle name="千位分隔 10 2 4" xfId="1468"/>
+    <cellStyle name="千位分隔 10 2 5" xfId="1469"/>
+    <cellStyle name="千位分隔 10 3" xfId="1470"/>
+    <cellStyle name="千位分隔 10 4" xfId="1471"/>
+    <cellStyle name="千位分隔 10 5" xfId="1472"/>
+    <cellStyle name="千位分隔 10 6" xfId="1473"/>
+    <cellStyle name="千位分隔 11" xfId="1474"/>
+    <cellStyle name="千位分隔 11 2" xfId="1475"/>
+    <cellStyle name="千位分隔 12" xfId="1476"/>
+    <cellStyle name="千位分隔 12 2" xfId="46"/>
+    <cellStyle name="千位分隔 12 2 2" xfId="1328"/>
+    <cellStyle name="千位分隔 12 2 3" xfId="1477"/>
+    <cellStyle name="千位分隔 12 2 4" xfId="1478"/>
+    <cellStyle name="千位分隔 12 2 5" xfId="1479"/>
+    <cellStyle name="千位分隔 12 3" xfId="929"/>
+    <cellStyle name="千位分隔 12 4" xfId="1480"/>
+    <cellStyle name="千位分隔 12 5" xfId="1481"/>
+    <cellStyle name="千位分隔 12 6" xfId="1482"/>
+    <cellStyle name="千位分隔 13" xfId="14"/>
+    <cellStyle name="千位分隔 13 2" xfId="938"/>
+    <cellStyle name="千位分隔 13 2 2" xfId="1383"/>
+    <cellStyle name="千位分隔 13 2 3" xfId="1484"/>
+    <cellStyle name="千位分隔 13 2 4" xfId="1485"/>
+    <cellStyle name="千位分隔 13 2 5" xfId="1486"/>
+    <cellStyle name="千位分隔 13 3" xfId="1487"/>
+    <cellStyle name="千位分隔 13 4" xfId="1488"/>
+    <cellStyle name="千位分隔 13 5" xfId="1489"/>
+    <cellStyle name="千位分隔 13 6" xfId="1490"/>
+    <cellStyle name="千位分隔 13 7" xfId="1483"/>
+    <cellStyle name="千位分隔 14" xfId="1491"/>
+    <cellStyle name="千位分隔 14 2" xfId="1492"/>
+    <cellStyle name="千位分隔 14 2 2" xfId="1493"/>
+    <cellStyle name="千位分隔 14 2 3" xfId="1494"/>
+    <cellStyle name="千位分隔 14 2 4" xfId="1495"/>
+    <cellStyle name="千位分隔 14 2 5" xfId="1496"/>
+    <cellStyle name="千位分隔 14 3" xfId="1497"/>
+    <cellStyle name="千位分隔 14 4" xfId="1498"/>
+    <cellStyle name="千位分隔 14 5" xfId="1499"/>
+    <cellStyle name="千位分隔 14 6" xfId="1500"/>
+    <cellStyle name="千位分隔 15" xfId="9"/>
+    <cellStyle name="千位分隔 15 2" xfId="1503"/>
+    <cellStyle name="千位分隔 15 3" xfId="1504"/>
+    <cellStyle name="千位分隔 15 4" xfId="1505"/>
+    <cellStyle name="千位分隔 15 5" xfId="1506"/>
+    <cellStyle name="千位分隔 15 6" xfId="1502"/>
+    <cellStyle name="千位分隔 16" xfId="605"/>
+    <cellStyle name="千位分隔 17" xfId="624"/>
+    <cellStyle name="千位分隔 17 2" xfId="626"/>
+    <cellStyle name="千位分隔 17 3" xfId="632"/>
+    <cellStyle name="千位分隔 18" xfId="11"/>
+    <cellStyle name="千位分隔 18 2" xfId="641"/>
+    <cellStyle name="千位分隔 19" xfId="16"/>
+    <cellStyle name="千位分隔 2" xfId="296"/>
+    <cellStyle name="千位分隔 2 10" xfId="1507"/>
+    <cellStyle name="千位分隔 2 11" xfId="1508"/>
+    <cellStyle name="千位分隔 2 12" xfId="290"/>
+    <cellStyle name="千位分隔 2 2" xfId="1509"/>
+    <cellStyle name="千位分隔 2 2 2" xfId="1287"/>
+    <cellStyle name="千位分隔 2 2 2 2" xfId="1510"/>
+    <cellStyle name="千位分隔 2 2 2 2 2" xfId="1511"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 2" xfId="1512"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 3" xfId="1513"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 4" xfId="1514"/>
+    <cellStyle name="千位分隔 2 2 2 2 2 5" xfId="1515"/>
+    <cellStyle name="千位分隔 2 2 2 2 3" xfId="1516"/>
+    <cellStyle name="千位分隔 2 2 2 2 4" xfId="1517"/>
+    <cellStyle name="千位分隔 2 2 2 2 5" xfId="1518"/>
+    <cellStyle name="千位分隔 2 2 2 2 6" xfId="1089"/>
+    <cellStyle name="千位分隔 2 2 2 3" xfId="1519"/>
+    <cellStyle name="千位分隔 2 2 2 3 2" xfId="1520"/>
+    <cellStyle name="千位分隔 2 2 2 3 3" xfId="1521"/>
+    <cellStyle name="千位分隔 2 2 2 3 4" xfId="1522"/>
+    <cellStyle name="千位分隔 2 2 2 3 5" xfId="1523"/>
+    <cellStyle name="千位分隔 2 2 2 4" xfId="1524"/>
+    <cellStyle name="千位分隔 2 2 2 5" xfId="1525"/>
+    <cellStyle name="千位分隔 2 2 2 6" xfId="1526"/>
+    <cellStyle name="千位分隔 2 2 2 7" xfId="1527"/>
+    <cellStyle name="千位分隔 2 2 3" xfId="1528"/>
+    <cellStyle name="千位分隔 2 2 3 2" xfId="1529"/>
+    <cellStyle name="千位分隔 2 2 3 2 2" xfId="1530"/>
+    <cellStyle name="千位分隔 2 2 3 2 3" xfId="1531"/>
+    <cellStyle name="千位分隔 2 2 3 2 4" xfId="1532"/>
+    <cellStyle name="千位分隔 2 2 3 2 5" xfId="1533"/>
+    <cellStyle name="千位分隔 2 2 3 3" xfId="1534"/>
+    <cellStyle name="千位分隔 2 2 3 4" xfId="1535"/>
+    <cellStyle name="千位分隔 2 2 3 5" xfId="1536"/>
+    <cellStyle name="千位分隔 2 2 3 6" xfId="1537"/>
+    <cellStyle name="千位分隔 2 2 4" xfId="992"/>
+    <cellStyle name="千位分隔 2 2 4 2" xfId="62"/>
+    <cellStyle name="千位分隔 2 2 4 3" xfId="64"/>
+    <cellStyle name="千位分隔 2 2 4 4" xfId="68"/>
+    <cellStyle name="千位分隔 2 2 4 5" xfId="72"/>
+    <cellStyle name="千位分隔 2 2 5" xfId="1203"/>
+    <cellStyle name="千位分隔 2 2 6" xfId="1205"/>
+    <cellStyle name="千位分隔 2 2 7" xfId="512"/>
+    <cellStyle name="千位分隔 2 2 8" xfId="1207"/>
+    <cellStyle name="千位分隔 2 3" xfId="7"/>
+    <cellStyle name="千位分隔 2 3 2" xfId="1300"/>
+    <cellStyle name="千位分隔 2 3 2 2" xfId="1539"/>
+    <cellStyle name="千位分隔 2 3 2 2 2" xfId="724"/>
+    <cellStyle name="千位分隔 2 3 2 2 3" xfId="727"/>
+    <cellStyle name="千位分隔 2 3 2 2 4" xfId="1540"/>
+    <cellStyle name="千位分隔 2 3 2 2 5" xfId="1541"/>
+    <cellStyle name="千位分隔 2 3 2 3" xfId="1542"/>
+    <cellStyle name="千位分隔 2 3 2 4" xfId="1543"/>
+    <cellStyle name="千位分隔 2 3 2 5" xfId="1544"/>
+    <cellStyle name="千位分隔 2 3 2 6" xfId="1545"/>
+    <cellStyle name="千位分隔 2 3 3" xfId="1546"/>
+    <cellStyle name="千位分隔 2 3 3 2" xfId="1547"/>
+    <cellStyle name="千位分隔 2 3 3 3" xfId="1548"/>
+    <cellStyle name="千位分隔 2 3 3 4" xfId="1549"/>
+    <cellStyle name="千位分隔 2 3 3 5" xfId="1550"/>
+    <cellStyle name="千位分隔 2 3 4" xfId="1551"/>
+    <cellStyle name="千位分隔 2 3 5" xfId="1552"/>
+    <cellStyle name="千位分隔 2 3 6" xfId="1553"/>
+    <cellStyle name="千位分隔 2 3 7" xfId="187"/>
+    <cellStyle name="千位分隔 2 3 8" xfId="1538"/>
+    <cellStyle name="千位分隔 2 4" xfId="544"/>
+    <cellStyle name="千位分隔 2 4 2" xfId="547"/>
+    <cellStyle name="千位分隔 2 4 2 2" xfId="1554"/>
+    <cellStyle name="千位分隔 2 4 2 3" xfId="1555"/>
+    <cellStyle name="千位分隔 2 4 2 4" xfId="1556"/>
+    <cellStyle name="千位分隔 2 4 2 5" xfId="1557"/>
+    <cellStyle name="千位分隔 2 4 3" xfId="550"/>
+    <cellStyle name="千位分隔 2 4 4" xfId="34"/>
+    <cellStyle name="千位分隔 2 4 5" xfId="194"/>
+    <cellStyle name="千位分隔 2 4 6" xfId="197"/>
+    <cellStyle name="千位分隔 2 5" xfId="579"/>
+    <cellStyle name="千位分隔 2 5 2" xfId="349"/>
+    <cellStyle name="千位分隔 2 5 2 2" xfId="354"/>
+    <cellStyle name="千位分隔 2 5 2 3" xfId="357"/>
+    <cellStyle name="千位分隔 2 5 2 4" xfId="360"/>
+    <cellStyle name="千位分隔 2 5 2 5" xfId="315"/>
+    <cellStyle name="千位分隔 2 5 3" xfId="90"/>
+    <cellStyle name="千位分隔 2 5 4" xfId="586"/>
+    <cellStyle name="千位分隔 2 5 5" xfId="591"/>
+    <cellStyle name="千位分隔 2 5 6" xfId="593"/>
+    <cellStyle name="千位分隔 2 6" xfId="28"/>
+    <cellStyle name="千位分隔 2 6 2" xfId="1558"/>
+    <cellStyle name="千位分隔 2 6 2 2" xfId="1559"/>
+    <cellStyle name="千位分隔 2 6 2 3" xfId="1560"/>
+    <cellStyle name="千位分隔 2 6 2 4" xfId="1561"/>
+    <cellStyle name="千位分隔 2 6 2 5" xfId="1562"/>
+    <cellStyle name="千位分隔 2 6 3" xfId="1563"/>
+    <cellStyle name="千位分隔 2 6 4" xfId="1564"/>
+    <cellStyle name="千位分隔 2 6 5" xfId="1565"/>
+    <cellStyle name="千位分隔 2 6 6" xfId="1566"/>
+    <cellStyle name="千位分隔 2 7" xfId="596"/>
+    <cellStyle name="千位分隔 2 7 2" xfId="1567"/>
+    <cellStyle name="千位分隔 2 7 3" xfId="1568"/>
+    <cellStyle name="千位分隔 2 7 4" xfId="1569"/>
+    <cellStyle name="千位分隔 2 7 5" xfId="1570"/>
+    <cellStyle name="千位分隔 2 8" xfId="598"/>
+    <cellStyle name="千位分隔 2 8 2" xfId="1571"/>
+    <cellStyle name="千位分隔 2 8 3" xfId="1572"/>
+    <cellStyle name="千位分隔 2 8 4" xfId="996"/>
+    <cellStyle name="千位分隔 2 8 5" xfId="1573"/>
+    <cellStyle name="千位分隔 2 9" xfId="510"/>
+    <cellStyle name="千位分隔 2 9 2" xfId="1574"/>
+    <cellStyle name="千位分隔 2 9 3" xfId="1575"/>
+    <cellStyle name="千位分隔 2 9 4" xfId="1576"/>
+    <cellStyle name="千位分隔 20" xfId="15"/>
+    <cellStyle name="千位分隔 20 2" xfId="1501"/>
+    <cellStyle name="千位分隔 21" xfId="604"/>
+    <cellStyle name="千位分隔 22" xfId="623"/>
+    <cellStyle name="千位分隔 23" xfId="640"/>
+    <cellStyle name="千位分隔 24" xfId="649"/>
+    <cellStyle name="千位分隔 25" xfId="651"/>
+    <cellStyle name="千位分隔 3" xfId="299"/>
+    <cellStyle name="千位分隔 3 2" xfId="1577"/>
+    <cellStyle name="千位分隔 3 2 2" xfId="1578"/>
+    <cellStyle name="千位分隔 3 2 2 2" xfId="900"/>
+    <cellStyle name="千位分隔 3 2 2 2 2" xfId="1579"/>
+    <cellStyle name="千位分隔 3 2 2 2 3" xfId="1580"/>
+    <cellStyle name="千位分隔 3 2 2 2 4" xfId="1581"/>
+    <cellStyle name="千位分隔 3 2 2 2 5" xfId="1582"/>
+    <cellStyle name="千位分隔 3 2 2 3" xfId="902"/>
+    <cellStyle name="千位分隔 3 2 2 4" xfId="904"/>
+    <cellStyle name="千位分隔 3 2 2 5" xfId="1583"/>
+    <cellStyle name="千位分隔 3 2 2 6" xfId="1584"/>
+    <cellStyle name="千位分隔 3 2 3" xfId="1585"/>
+    <cellStyle name="千位分隔 3 2 3 2" xfId="1586"/>
+    <cellStyle name="千位分隔 3 2 3 3" xfId="1587"/>
+    <cellStyle name="千位分隔 3 2 3 4" xfId="1588"/>
+    <cellStyle name="千位分隔 3 2 3 5" xfId="1589"/>
+    <cellStyle name="千位分隔 3 2 4" xfId="1590"/>
+    <cellStyle name="千位分隔 3 2 5" xfId="1591"/>
+    <cellStyle name="千位分隔 3 2 6" xfId="1592"/>
+    <cellStyle name="千位分隔 3 2 7" xfId="1593"/>
+    <cellStyle name="千位分隔 3 3" xfId="1594"/>
+    <cellStyle name="千位分隔 3 3 2" xfId="1595"/>
+    <cellStyle name="千位分隔 3 3 2 2" xfId="1596"/>
+    <cellStyle name="千位分隔 3 3 2 3" xfId="1597"/>
+    <cellStyle name="千位分隔 3 3 2 4" xfId="1598"/>
+    <cellStyle name="千位分隔 3 3 2 5" xfId="1599"/>
+    <cellStyle name="千位分隔 3 3 3" xfId="1600"/>
+    <cellStyle name="千位分隔 3 3 4" xfId="1601"/>
+    <cellStyle name="千位分隔 3 3 5" xfId="1602"/>
+    <cellStyle name="千位分隔 3 3 6" xfId="1603"/>
+    <cellStyle name="千位分隔 3 4" xfId="601"/>
+    <cellStyle name="千位分隔 3 4 2" xfId="43"/>
+    <cellStyle name="千位分隔 3 4 3" xfId="655"/>
+    <cellStyle name="千位分隔 3 4 4" xfId="680"/>
+    <cellStyle name="千位分隔 3 4 5" xfId="695"/>
+    <cellStyle name="千位分隔 3 5" xfId="714"/>
+    <cellStyle name="千位分隔 3 6" xfId="717"/>
+    <cellStyle name="千位分隔 3 7" xfId="720"/>
+    <cellStyle name="千位分隔 3 8" xfId="723"/>
+    <cellStyle name="千位分隔 4" xfId="1604"/>
+    <cellStyle name="千位分隔 4 2" xfId="884"/>
+    <cellStyle name="千位分隔 4 2 2" xfId="886"/>
+    <cellStyle name="千位分隔 4 2 2 2" xfId="1389"/>
+    <cellStyle name="千位分隔 4 2 2 2 2" xfId="1605"/>
+    <cellStyle name="千位分隔 4 2 2 2 3" xfId="1606"/>
+    <cellStyle name="千位分隔 4 2 2 2 4" xfId="1607"/>
+    <cellStyle name="千位分隔 4 2 2 2 5" xfId="1608"/>
+    <cellStyle name="千位分隔 4 2 2 3" xfId="1392"/>
+    <cellStyle name="千位分隔 4 2 2 4" xfId="1609"/>
+    <cellStyle name="千位分隔 4 2 2 5" xfId="1610"/>
+    <cellStyle name="千位分隔 4 2 2 6" xfId="1611"/>
+    <cellStyle name="千位分隔 4 2 3" xfId="888"/>
+    <cellStyle name="千位分隔 4 2 3 2" xfId="1411"/>
+    <cellStyle name="千位分隔 4 2 3 3" xfId="1612"/>
+    <cellStyle name="千位分隔 4 2 3 4" xfId="1613"/>
+    <cellStyle name="千位分隔 4 2 3 5" xfId="1614"/>
+    <cellStyle name="千位分隔 4 2 4" xfId="890"/>
+    <cellStyle name="千位分隔 4 2 5" xfId="892"/>
+    <cellStyle name="千位分隔 4 2 6" xfId="1615"/>
+    <cellStyle name="千位分隔 4 2 7" xfId="1616"/>
+    <cellStyle name="千位分隔 4 3" xfId="894"/>
+    <cellStyle name="千位分隔 4 3 2" xfId="1617"/>
+    <cellStyle name="千位分隔 4 3 2 2" xfId="1435"/>
+    <cellStyle name="千位分隔 4 3 2 3" xfId="1437"/>
+    <cellStyle name="千位分隔 4 3 2 4" xfId="1618"/>
+    <cellStyle name="千位分隔 4 3 2 5" xfId="1619"/>
+    <cellStyle name="千位分隔 4 3 3" xfId="1620"/>
+    <cellStyle name="千位分隔 4 3 4" xfId="1621"/>
+    <cellStyle name="千位分隔 4 3 5" xfId="1622"/>
+    <cellStyle name="千位分隔 4 3 6" xfId="1623"/>
+    <cellStyle name="千位分隔 4 4" xfId="733"/>
+    <cellStyle name="千位分隔 4 4 2" xfId="736"/>
+    <cellStyle name="千位分隔 4 4 3" xfId="761"/>
+    <cellStyle name="千位分隔 4 4 4" xfId="773"/>
+    <cellStyle name="千位分隔 4 4 5" xfId="780"/>
+    <cellStyle name="千位分隔 4 5" xfId="788"/>
+    <cellStyle name="千位分隔 4 6" xfId="809"/>
+    <cellStyle name="千位分隔 4 7" xfId="821"/>
+    <cellStyle name="千位分隔 4 8" xfId="844"/>
+    <cellStyle name="千位分隔 5" xfId="1624"/>
+    <cellStyle name="千位分隔 5 2" xfId="906"/>
+    <cellStyle name="千位分隔 6" xfId="1102"/>
+    <cellStyle name="千位分隔 6 2" xfId="916"/>
+    <cellStyle name="千位分隔 7" xfId="1625"/>
+    <cellStyle name="千位分隔 7 2" xfId="1626"/>
+    <cellStyle name="千位分隔 7 2 2" xfId="1627"/>
+    <cellStyle name="千位分隔 7 2 2 2" xfId="1628"/>
+    <cellStyle name="千位分隔 7 2 2 3" xfId="1629"/>
+    <cellStyle name="千位分隔 7 2 2 4" xfId="1630"/>
+    <cellStyle name="千位分隔 7 2 2 5" xfId="1631"/>
+    <cellStyle name="千位分隔 7 2 3" xfId="657"/>
+    <cellStyle name="千位分隔 7 2 4" xfId="668"/>
+    <cellStyle name="千位分隔 7 2 5" xfId="674"/>
+    <cellStyle name="千位分隔 7 2 6" xfId="676"/>
+    <cellStyle name="千位分隔 7 3" xfId="1632"/>
+    <cellStyle name="千位分隔 7 3 2" xfId="1633"/>
+    <cellStyle name="千位分隔 7 3 3" xfId="682"/>
+    <cellStyle name="千位分隔 7 3 4" xfId="688"/>
+    <cellStyle name="千位分隔 7 3 5" xfId="690"/>
+    <cellStyle name="千位分隔 7 4" xfId="983"/>
+    <cellStyle name="千位分隔 7 5" xfId="1634"/>
+    <cellStyle name="千位分隔 7 6" xfId="1635"/>
+    <cellStyle name="千位分隔 7 7" xfId="1636"/>
+    <cellStyle name="千位分隔 8" xfId="1637"/>
+    <cellStyle name="千位分隔 8 2" xfId="1638"/>
+    <cellStyle name="千位分隔 8 3" xfId="1639"/>
+    <cellStyle name="千位分隔 9" xfId="1640"/>
+    <cellStyle name="常规 10" xfId="439"/>
+    <cellStyle name="常规 10 10" xfId="1010"/>
+    <cellStyle name="常规 10 11" xfId="1011"/>
+    <cellStyle name="常规 10 12" xfId="1654"/>
+    <cellStyle name="常规 10 2" xfId="441"/>
+    <cellStyle name="常规 10 2 2" xfId="443"/>
+    <cellStyle name="常规 10 2 2 2" xfId="1012"/>
+    <cellStyle name="常规 10 2 2 2 2" xfId="1013"/>
+    <cellStyle name="常规 10 2 2 2 2 2" xfId="1014"/>
+    <cellStyle name="常规 10 2 2 2 3" xfId="1015"/>
+    <cellStyle name="常规 10 2 2 2 4" xfId="1016"/>
+    <cellStyle name="常规 10 2 2 2 5" xfId="1017"/>
+    <cellStyle name="常规 10 2 2 2 6" xfId="1018"/>
+    <cellStyle name="常规 10 2 2 3" xfId="1019"/>
+    <cellStyle name="常规 10 2 2 3 2" xfId="1020"/>
+    <cellStyle name="常规 10 2 2 4" xfId="1021"/>
+    <cellStyle name="常规 10 2 2 5" xfId="1022"/>
+    <cellStyle name="常规 10 2 2 6" xfId="1023"/>
+    <cellStyle name="常规 10 2 3" xfId="445"/>
+    <cellStyle name="常规 10 2 3 2" xfId="556"/>
+    <cellStyle name="常规 10 2 3 2 2" xfId="1024"/>
+    <cellStyle name="常规 10 2 3 2 2 2" xfId="1025"/>
+    <cellStyle name="常规 10 2 3 2 3" xfId="1026"/>
+    <cellStyle name="常规 10 2 3 2 4" xfId="1027"/>
+    <cellStyle name="常规 10 2 3 2 5" xfId="1028"/>
+    <cellStyle name="常规 10 2 3 2 6" xfId="1029"/>
+    <cellStyle name="常规 10 2 3 3" xfId="1030"/>
+    <cellStyle name="常规 10 2 3 3 2" xfId="1031"/>
+    <cellStyle name="常规 10 2 3 4" xfId="1032"/>
+    <cellStyle name="常规 10 2 3 5" xfId="1033"/>
+    <cellStyle name="常规 10 2 3 6" xfId="1034"/>
+    <cellStyle name="常规 10 2 4" xfId="169"/>
+    <cellStyle name="常规 10 2 4 2" xfId="490"/>
+    <cellStyle name="常规 10 2 4 2 2" xfId="1035"/>
+    <cellStyle name="常规 10 2 4 2 2 2" xfId="459"/>
+    <cellStyle name="常规 10 2 4 2 3" xfId="1036"/>
+    <cellStyle name="常规 10 2 4 2 4" xfId="1037"/>
+    <cellStyle name="常规 10 2 4 2 5" xfId="1038"/>
+    <cellStyle name="常规 10 2 4 3" xfId="1039"/>
+    <cellStyle name="常规 10 2 4 3 2" xfId="1040"/>
+    <cellStyle name="常规 10 2 4 3 2 2" xfId="1041"/>
+    <cellStyle name="常规 10 2 4 3 3" xfId="1042"/>
+    <cellStyle name="常规 10 2 4 3 4" xfId="1043"/>
+    <cellStyle name="常规 10 2 4 3 5" xfId="1044"/>
+    <cellStyle name="常规 10 2 4 3 6" xfId="1046"/>
+    <cellStyle name="常规 10 2 4 4" xfId="1047"/>
+    <cellStyle name="常规 10 2 4 4 2" xfId="1048"/>
+    <cellStyle name="常规 10 2 4 5" xfId="1049"/>
+    <cellStyle name="常规 10 2 4 6" xfId="1050"/>
+    <cellStyle name="常规 10 2 4 7" xfId="1051"/>
+    <cellStyle name="常规 10 2 5" xfId="173"/>
+    <cellStyle name="常规 10 2 5 2" xfId="1052"/>
+    <cellStyle name="常规 10 2 5 2 2" xfId="1053"/>
+    <cellStyle name="常规 10 2 5 3" xfId="1054"/>
+    <cellStyle name="常规 10 2 5 4" xfId="1055"/>
+    <cellStyle name="常规 10 2 5 5" xfId="1056"/>
+    <cellStyle name="常规 10 2 5 6" xfId="1057"/>
+    <cellStyle name="常规 10 2 6" xfId="1058"/>
+    <cellStyle name="常规 10 2 6 2" xfId="1059"/>
+    <cellStyle name="常规 10 2 7" xfId="1060"/>
+    <cellStyle name="常规 10 2 8" xfId="1061"/>
+    <cellStyle name="常规 10 2 9" xfId="1062"/>
+    <cellStyle name="常规 10 3" xfId="447"/>
+    <cellStyle name="常规 10 3 2" xfId="1063"/>
+    <cellStyle name="常规 10 3 2 2" xfId="1064"/>
+    <cellStyle name="常规 10 3 2 2 2" xfId="1065"/>
+    <cellStyle name="常规 10 3 2 3" xfId="1066"/>
+    <cellStyle name="常规 10 3 2 4" xfId="1067"/>
+    <cellStyle name="常规 10 3 2 5" xfId="1068"/>
+    <cellStyle name="常规 10 3 3" xfId="1069"/>
+    <cellStyle name="常规 10 3 3 2" xfId="1070"/>
+    <cellStyle name="常规 10 3 3 2 2" xfId="1071"/>
+    <cellStyle name="常规 10 3 3 3" xfId="1072"/>
+    <cellStyle name="常规 10 3 3 4" xfId="1073"/>
+    <cellStyle name="常规 10 3 3 5" xfId="1074"/>
+    <cellStyle name="常规 10 3 3 6" xfId="1075"/>
+    <cellStyle name="常规 10 3 4" xfId="1076"/>
+    <cellStyle name="常规 10 3 4 2" xfId="1077"/>
+    <cellStyle name="常规 10 3 5" xfId="1078"/>
+    <cellStyle name="常规 10 3 6" xfId="1079"/>
+    <cellStyle name="常规 10 3 7" xfId="1080"/>
+    <cellStyle name="常规 10 4" xfId="449"/>
+    <cellStyle name="常规 10 4 2" xfId="1081"/>
+    <cellStyle name="常规 10 4 2 2" xfId="1082"/>
+    <cellStyle name="常规 10 4 2 2 2" xfId="1083"/>
+    <cellStyle name="常规 10 4 2 3" xfId="1084"/>
+    <cellStyle name="常规 10 4 2 4" xfId="1085"/>
+    <cellStyle name="常规 10 4 2 5" xfId="1086"/>
+    <cellStyle name="常规 10 4 3" xfId="1087"/>
+    <cellStyle name="常规 10 4 3 2" xfId="1088"/>
+    <cellStyle name="常规 10 4 3 2 2" xfId="1090"/>
+    <cellStyle name="常规 10 4 3 3" xfId="1091"/>
+    <cellStyle name="常规 10 4 3 4" xfId="1092"/>
+    <cellStyle name="常规 10 4 3 5" xfId="1093"/>
+    <cellStyle name="常规 10 4 3 6" xfId="1094"/>
+    <cellStyle name="常规 10 4 4" xfId="1095"/>
+    <cellStyle name="常规 10 4 4 2" xfId="1096"/>
+    <cellStyle name="常规 10 4 5" xfId="1097"/>
+    <cellStyle name="常规 10 4 6" xfId="1098"/>
+    <cellStyle name="常规 10 4 7" xfId="1099"/>
+    <cellStyle name="常规 10 5" xfId="451"/>
+    <cellStyle name="常规 10 5 2" xfId="1100"/>
+    <cellStyle name="常规 10 5 2 2" xfId="1101"/>
+    <cellStyle name="常规 10 5 2 2 2" xfId="1103"/>
+    <cellStyle name="常规 10 5 2 3" xfId="1104"/>
+    <cellStyle name="常规 10 5 2 4" xfId="1105"/>
+    <cellStyle name="常规 10 5 2 5" xfId="1106"/>
+    <cellStyle name="常规 10 5 3" xfId="1107"/>
+    <cellStyle name="常规 10 5 3 2" xfId="1108"/>
+    <cellStyle name="常规 10 5 3 2 2" xfId="1109"/>
+    <cellStyle name="常规 10 5 3 3" xfId="1110"/>
+    <cellStyle name="常规 10 5 3 4" xfId="1111"/>
+    <cellStyle name="常规 10 5 3 5" xfId="1112"/>
+    <cellStyle name="常规 10 5 3 6" xfId="1113"/>
+    <cellStyle name="常规 10 5 4" xfId="1114"/>
+    <cellStyle name="常规 10 5 4 2" xfId="1115"/>
+    <cellStyle name="常规 10 5 5" xfId="1116"/>
+    <cellStyle name="常规 10 5 6" xfId="1118"/>
+    <cellStyle name="常规 10 5 7" xfId="1120"/>
+    <cellStyle name="常规 10 6" xfId="453"/>
+    <cellStyle name="常规 10 6 2" xfId="1121"/>
+    <cellStyle name="常规 10 6 2 2" xfId="1122"/>
+    <cellStyle name="常规 10 6 3" xfId="1123"/>
+    <cellStyle name="常规 10 6 4" xfId="1124"/>
+    <cellStyle name="常规 10 6 5" xfId="1125"/>
+    <cellStyle name="常规 10 6 6" xfId="429"/>
+    <cellStyle name="常规 10 7" xfId="1126"/>
+    <cellStyle name="常规 10 7 2" xfId="1127"/>
+    <cellStyle name="常规 10 7 2 2" xfId="1128"/>
+    <cellStyle name="常规 10 7 3" xfId="1129"/>
+    <cellStyle name="常规 10 7 4" xfId="1130"/>
+    <cellStyle name="常规 10 7 5" xfId="1131"/>
+    <cellStyle name="常规 10 7 6" xfId="1133"/>
+    <cellStyle name="常规 10 8" xfId="1134"/>
+    <cellStyle name="常规 10 8 2" xfId="1135"/>
+    <cellStyle name="常规 10 8 3" xfId="1136"/>
+    <cellStyle name="常规 10 8 4" xfId="1137"/>
+    <cellStyle name="常规 10 8 5" xfId="1138"/>
+    <cellStyle name="常规 10 9" xfId="1139"/>
+    <cellStyle name="常规 11" xfId="455"/>
+    <cellStyle name="常规 11 2" xfId="457"/>
+    <cellStyle name="常规 11 3" xfId="1647"/>
+    <cellStyle name="常规 12" xfId="463"/>
+    <cellStyle name="常规 12 2" xfId="745"/>
+    <cellStyle name="常规 13" xfId="363"/>
+    <cellStyle name="常规 13 2" xfId="753"/>
+    <cellStyle name="常规 14" xfId="405"/>
+    <cellStyle name="常规 14 2" xfId="1140"/>
+    <cellStyle name="常规 15" xfId="5"/>
+    <cellStyle name="常规 15 2" xfId="1142"/>
+    <cellStyle name="常规 15 2 2" xfId="1143"/>
+    <cellStyle name="常规 15 2 2 2" xfId="1144"/>
+    <cellStyle name="常规 15 2 2 3" xfId="1145"/>
+    <cellStyle name="常规 15 2 2 4" xfId="1146"/>
+    <cellStyle name="常规 15 2 2 5" xfId="1147"/>
+    <cellStyle name="常规 15 2 3" xfId="1148"/>
+    <cellStyle name="常规 15 2 4" xfId="897"/>
+    <cellStyle name="常规 15 2 5" xfId="907"/>
+    <cellStyle name="常规 15 2 6" xfId="909"/>
+    <cellStyle name="常规 15 3" xfId="1151"/>
+    <cellStyle name="常规 15 3 2" xfId="1152"/>
+    <cellStyle name="常规 15 3 3" xfId="1153"/>
+    <cellStyle name="常规 15 3 4" xfId="914"/>
+    <cellStyle name="常规 15 3 5" xfId="917"/>
+    <cellStyle name="常规 15 4" xfId="1155"/>
+    <cellStyle name="常规 15 5" xfId="1157"/>
+    <cellStyle name="常规 15 6" xfId="1159"/>
+    <cellStyle name="常规 15 7" xfId="1160"/>
+    <cellStyle name="常规 15 8" xfId="239"/>
+    <cellStyle name="常规 16" xfId="1162"/>
+    <cellStyle name="常规 16 2" xfId="1164"/>
+    <cellStyle name="常规 16 2 2" xfId="1165"/>
+    <cellStyle name="常规 16 2 2 2" xfId="1167"/>
+    <cellStyle name="常规 16 2 2 3" xfId="1169"/>
+    <cellStyle name="常规 16 2 2 4" xfId="171"/>
+    <cellStyle name="常规 16 2 2 5" xfId="175"/>
+    <cellStyle name="常规 16 2 3" xfId="1170"/>
+    <cellStyle name="常规 16 2 4" xfId="932"/>
+    <cellStyle name="常规 16 2 5" xfId="934"/>
+    <cellStyle name="常规 16 2 6" xfId="936"/>
+    <cellStyle name="常规 16 3" xfId="1171"/>
+    <cellStyle name="常规 16 3 2" xfId="1172"/>
+    <cellStyle name="常规 16 3 3" xfId="1173"/>
+    <cellStyle name="常规 16 3 4" xfId="1174"/>
+    <cellStyle name="常规 16 3 5" xfId="1175"/>
+    <cellStyle name="常规 16 4" xfId="1176"/>
+    <cellStyle name="常规 16 5" xfId="1177"/>
+    <cellStyle name="常规 16 6" xfId="1178"/>
+    <cellStyle name="常规 16 7" xfId="1179"/>
+    <cellStyle name="常规 17" xfId="1181"/>
+    <cellStyle name="常规 17 2" xfId="1183"/>
+    <cellStyle name="常规 17 3" xfId="1185"/>
+    <cellStyle name="常规 18" xfId="1187"/>
+    <cellStyle name="常规 18 2" xfId="1189"/>
+    <cellStyle name="常规 18 3" xfId="1191"/>
+    <cellStyle name="常规 19" xfId="1193"/>
+    <cellStyle name="常规 19 2" xfId="10"/>
+    <cellStyle name="常规 19 3" xfId="1195"/>
+    <cellStyle name="常规 2" xfId="1196"/>
+    <cellStyle name="常规 2 10" xfId="1658"/>
+    <cellStyle name="常规 2 2" xfId="1197"/>
+    <cellStyle name="常规 2 2 2" xfId="1198"/>
+    <cellStyle name="常规 2 2 2 2" xfId="1117"/>
+    <cellStyle name="常规 2 2 2 2 2" xfId="1199"/>
+    <cellStyle name="常规 2 2 2 2 3" xfId="1200"/>
+    <cellStyle name="常规 2 2 2 2 4" xfId="1201"/>
+    <cellStyle name="常规 2 2 2 2 5" xfId="1202"/>
+    <cellStyle name="常规 2 2 2 3" xfId="1119"/>
+    <cellStyle name="常规 2 2 2 4" xfId="61"/>
+    <cellStyle name="常规 2 2 2 5" xfId="50"/>
+    <cellStyle name="常规 2 2 2 6" xfId="63"/>
+    <cellStyle name="常规 2 2 3" xfId="567"/>
+    <cellStyle name="常规 2 2 3 2" xfId="428"/>
+    <cellStyle name="常规 2 2 3 2 2" xfId="1204"/>
+    <cellStyle name="常规 2 2 3 2 3" xfId="1206"/>
+    <cellStyle name="常规 2 2 3 2 4" xfId="513"/>
+    <cellStyle name="常规 2 2 3 2 5" xfId="1208"/>
+    <cellStyle name="常规 2 2 3 3" xfId="432"/>
+    <cellStyle name="常规 2 2 3 4" xfId="435"/>
+    <cellStyle name="常规 2 2 3 5" xfId="569"/>
+    <cellStyle name="常规 2 2 3 6" xfId="1209"/>
+    <cellStyle name="常规 2 2 4" xfId="25"/>
+    <cellStyle name="常规 2 2 4 2" xfId="1132"/>
+    <cellStyle name="常规 2 2 4 3" xfId="1210"/>
+    <cellStyle name="常规 2 2 4 4" xfId="1211"/>
+    <cellStyle name="常规 2 2 4 5" xfId="1212"/>
+    <cellStyle name="常规 2 2 5" xfId="571"/>
+    <cellStyle name="常规 2 2 6" xfId="573"/>
+    <cellStyle name="常规 2 2 7" xfId="575"/>
+    <cellStyle name="常规 2 2 8" xfId="1213"/>
+    <cellStyle name="常规 2 3" xfId="1214"/>
+    <cellStyle name="常规 2 3 2" xfId="1215"/>
+    <cellStyle name="常规 2 3 2 2" xfId="1216"/>
+    <cellStyle name="常规 2 3 2 3" xfId="1217"/>
+    <cellStyle name="常规 2 3 2 4" xfId="1218"/>
+    <cellStyle name="常规 2 3 2 5" xfId="1219"/>
+    <cellStyle name="常规 2 3 3" xfId="577"/>
+    <cellStyle name="常规 2 3 4" xfId="416"/>
+    <cellStyle name="常规 2 3 5" xfId="419"/>
+    <cellStyle name="常规 2 3 6" xfId="422"/>
+    <cellStyle name="常规 2 4" xfId="1220"/>
+    <cellStyle name="常规 2 4 2" xfId="1221"/>
+    <cellStyle name="常规 2 4 2 2" xfId="1222"/>
+    <cellStyle name="常规 2 4 2 3" xfId="1223"/>
+    <cellStyle name="常规 2 4 2 4" xfId="1224"/>
+    <cellStyle name="常规 2 4 2 5" xfId="1225"/>
+    <cellStyle name="常规 2 4 3" xfId="1226"/>
+    <cellStyle name="常规 2 4 4" xfId="1227"/>
+    <cellStyle name="常规 2 4 5" xfId="1228"/>
+    <cellStyle name="常规 2 4 6" xfId="1229"/>
+    <cellStyle name="常规 2 5" xfId="1230"/>
+    <cellStyle name="常规 2 5 2" xfId="1231"/>
+    <cellStyle name="常规 2 5 2 2" xfId="1232"/>
+    <cellStyle name="常规 2 5 2 3" xfId="1233"/>
+    <cellStyle name="常规 2 5 2 4" xfId="1234"/>
+    <cellStyle name="常规 2 5 2 5" xfId="1000"/>
+    <cellStyle name="常规 2 5 3" xfId="1235"/>
+    <cellStyle name="常规 2 5 4" xfId="1236"/>
+    <cellStyle name="常规 2 5 5" xfId="1237"/>
+    <cellStyle name="常规 2 5 6" xfId="1238"/>
+    <cellStyle name="常规 2 6" xfId="1239"/>
+    <cellStyle name="常规 2 6 2" xfId="1240"/>
+    <cellStyle name="常规 2 6 3" xfId="1241"/>
+    <cellStyle name="常规 2 6 4" xfId="1242"/>
+    <cellStyle name="常规 2 6 5" xfId="1243"/>
+    <cellStyle name="常规 2 7" xfId="1166"/>
+    <cellStyle name="常规 2 7 2" xfId="1244"/>
+    <cellStyle name="常规 2 7 3" xfId="1245"/>
+    <cellStyle name="常规 2 7 4" xfId="1246"/>
+    <cellStyle name="常规 2 8" xfId="1168"/>
+    <cellStyle name="常规 2 8 2" xfId="967"/>
+    <cellStyle name="常规 2 8 3" xfId="969"/>
+    <cellStyle name="常规 2 9" xfId="1648"/>
+    <cellStyle name="常规 20" xfId="238"/>
+    <cellStyle name="常规 20 2" xfId="1141"/>
+    <cellStyle name="常规 20 3" xfId="1150"/>
+    <cellStyle name="常规 21" xfId="1161"/>
+    <cellStyle name="常规 21 2" xfId="1163"/>
+    <cellStyle name="常规 22" xfId="1180"/>
+    <cellStyle name="常规 22 2" xfId="1182"/>
+    <cellStyle name="常规 22 2 2" xfId="1247"/>
+    <cellStyle name="常规 22 2 3" xfId="1248"/>
+    <cellStyle name="常规 22 2 4" xfId="1249"/>
+    <cellStyle name="常规 22 2 5" xfId="103"/>
+    <cellStyle name="常规 22 3" xfId="1184"/>
+    <cellStyle name="常规 22 4" xfId="1250"/>
+    <cellStyle name="常规 22 5" xfId="1251"/>
+    <cellStyle name="常规 22 6" xfId="1252"/>
+    <cellStyle name="常规 23" xfId="1186"/>
+    <cellStyle name="常规 23 2" xfId="1188"/>
+    <cellStyle name="常规 23 2 2" xfId="1253"/>
+    <cellStyle name="常规 23 2 3" xfId="1254"/>
+    <cellStyle name="常规 23 2 4" xfId="1255"/>
+    <cellStyle name="常规 23 2 5" xfId="142"/>
+    <cellStyle name="常规 23 3" xfId="1190"/>
+    <cellStyle name="常规 23 4" xfId="1256"/>
+    <cellStyle name="常规 23 5" xfId="1257"/>
+    <cellStyle name="常规 23 6" xfId="1258"/>
+    <cellStyle name="常规 24" xfId="1192"/>
+    <cellStyle name="常规 24 2" xfId="1194"/>
+    <cellStyle name="常规 25" xfId="1260"/>
+    <cellStyle name="常规 25 2" xfId="1261"/>
+    <cellStyle name="常规 26" xfId="1263"/>
+    <cellStyle name="常规 26 2" xfId="31"/>
+    <cellStyle name="常规 27" xfId="1265"/>
+    <cellStyle name="常规 27 2" xfId="1267"/>
+    <cellStyle name="常规 27 2 2" xfId="1268"/>
+    <cellStyle name="常规 27 2 3" xfId="1269"/>
+    <cellStyle name="常规 27 2 4" xfId="1270"/>
+    <cellStyle name="常规 27 2 5" xfId="1271"/>
+    <cellStyle name="常规 27 3" xfId="1273"/>
+    <cellStyle name="常规 27 4" xfId="1275"/>
+    <cellStyle name="常规 27 5" xfId="1277"/>
+    <cellStyle name="常规 27 6" xfId="1278"/>
+    <cellStyle name="常规 28" xfId="1280"/>
+    <cellStyle name="常规 28 2" xfId="153"/>
+    <cellStyle name="常规 28 2 2" xfId="1281"/>
+    <cellStyle name="常规 28 2 3" xfId="1282"/>
+    <cellStyle name="常规 28 2 4" xfId="1283"/>
+    <cellStyle name="常规 28 2 5" xfId="1284"/>
+    <cellStyle name="常规 28 3" xfId="161"/>
+    <cellStyle name="常规 28 4" xfId="1285"/>
+    <cellStyle name="常规 28 5" xfId="1286"/>
+    <cellStyle name="常规 28 6" xfId="1288"/>
+    <cellStyle name="常规 29" xfId="1290"/>
+    <cellStyle name="常规 29 2" xfId="1292"/>
+    <cellStyle name="常规 29 2 2" xfId="1293"/>
+    <cellStyle name="常规 29 2 3" xfId="1294"/>
+    <cellStyle name="常规 29 2 4" xfId="1295"/>
+    <cellStyle name="常规 29 2 5" xfId="1296"/>
+    <cellStyle name="常规 29 3" xfId="1297"/>
+    <cellStyle name="常规 29 4" xfId="1298"/>
+    <cellStyle name="常规 29 5" xfId="1299"/>
+    <cellStyle name="常规 29 6" xfId="1301"/>
+    <cellStyle name="常规 3" xfId="1302"/>
+    <cellStyle name="常规 3 10" xfId="1659"/>
+    <cellStyle name="常规 3 2" xfId="1002"/>
+    <cellStyle name="常规 3 2 2" xfId="1004"/>
+    <cellStyle name="常规 3 2 2 2" xfId="397"/>
+    <cellStyle name="常规 3 2 2 2 2" xfId="1303"/>
+    <cellStyle name="常规 3 2 2 2 3" xfId="1304"/>
+    <cellStyle name="常规 3 2 2 2 4" xfId="1305"/>
+    <cellStyle name="常规 3 2 2 2 5" xfId="1306"/>
+    <cellStyle name="常规 3 2 2 3" xfId="401"/>
+    <cellStyle name="常规 3 2 2 4" xfId="1307"/>
+    <cellStyle name="常规 3 2 2 5" xfId="1308"/>
+    <cellStyle name="常规 3 2 2 6" xfId="1309"/>
+    <cellStyle name="常规 3 2 3" xfId="1310"/>
+    <cellStyle name="常规 3 2 3 2" xfId="1311"/>
+    <cellStyle name="常规 3 2 3 3" xfId="1312"/>
+    <cellStyle name="常规 3 2 3 4" xfId="1313"/>
+    <cellStyle name="常规 3 2 3 5" xfId="867"/>
+    <cellStyle name="常规 3 2 4" xfId="1314"/>
+    <cellStyle name="常规 3 2 5" xfId="927"/>
+    <cellStyle name="常规 3 2 6" xfId="871"/>
+    <cellStyle name="常规 3 2 7" xfId="874"/>
+    <cellStyle name="常规 3 3" xfId="1006"/>
+    <cellStyle name="常规 3 3 2" xfId="1008"/>
+    <cellStyle name="常规 3 3 2 2" xfId="1315"/>
+    <cellStyle name="常规 3 3 2 3" xfId="1316"/>
+    <cellStyle name="常规 3 3 2 4" xfId="1317"/>
+    <cellStyle name="常规 3 3 2 5" xfId="1318"/>
+    <cellStyle name="常规 3 3 3" xfId="1319"/>
+    <cellStyle name="常规 3 3 4" xfId="1320"/>
+    <cellStyle name="常规 3 3 5" xfId="1321"/>
+    <cellStyle name="常规 3 3 6" xfId="1322"/>
+    <cellStyle name="常规 3 4" xfId="1323"/>
+    <cellStyle name="常规 3 5" xfId="1324"/>
+    <cellStyle name="常规 3 5 2" xfId="1325"/>
+    <cellStyle name="常规 3 5 3" xfId="1326"/>
+    <cellStyle name="常规 3 5 4" xfId="1327"/>
+    <cellStyle name="常规 3 5 5" xfId="1329"/>
+    <cellStyle name="常规 3 6" xfId="1330"/>
+    <cellStyle name="常规 3 6 2" xfId="1331"/>
+    <cellStyle name="常规 3 7" xfId="1332"/>
+    <cellStyle name="常规 3 7 2" xfId="92"/>
+    <cellStyle name="常规 3 7 3" xfId="1333"/>
+    <cellStyle name="常规 3 8" xfId="1334"/>
+    <cellStyle name="常规 3 9" xfId="1649"/>
+    <cellStyle name="常规 30" xfId="1259"/>
+    <cellStyle name="常规 31" xfId="1262"/>
+    <cellStyle name="常规 31 2" xfId="30"/>
+    <cellStyle name="常规 31 2 2" xfId="1335"/>
+    <cellStyle name="常规 31 2 3" xfId="1336"/>
+    <cellStyle name="常规 31 2 4" xfId="1337"/>
+    <cellStyle name="常规 31 2 5" xfId="1338"/>
+    <cellStyle name="常规 31 3" xfId="67"/>
+    <cellStyle name="常规 31 4" xfId="70"/>
+    <cellStyle name="常规 31 5" xfId="74"/>
+    <cellStyle name="常规 31 6" xfId="1339"/>
+    <cellStyle name="常规 32" xfId="1264"/>
+    <cellStyle name="常规 32 2" xfId="1266"/>
+    <cellStyle name="常规 32 3" xfId="1272"/>
+    <cellStyle name="常规 32 4" xfId="1274"/>
+    <cellStyle name="常规 32 5" xfId="1276"/>
+    <cellStyle name="常规 33" xfId="8"/>
+    <cellStyle name="常规 33 2" xfId="152"/>
+    <cellStyle name="常规 33 3" xfId="1279"/>
+    <cellStyle name="常规 34" xfId="1289"/>
+    <cellStyle name="常规 34 2" xfId="1291"/>
+    <cellStyle name="常规 35" xfId="12"/>
+    <cellStyle name="常规 35 2" xfId="1341"/>
+    <cellStyle name="常规 36" xfId="1343"/>
+    <cellStyle name="常规 36 2" xfId="1345"/>
+    <cellStyle name="常规 37" xfId="1347"/>
+    <cellStyle name="常规 37 2" xfId="1349"/>
+    <cellStyle name="常规 37 3" xfId="1350"/>
+    <cellStyle name="常规 38" xfId="824"/>
+    <cellStyle name="常规 38 2" xfId="827"/>
+    <cellStyle name="常规 38 3" xfId="829"/>
+    <cellStyle name="常规 38 4" xfId="831"/>
+    <cellStyle name="常规 38 5" xfId="833"/>
+    <cellStyle name="常规 39" xfId="23"/>
+    <cellStyle name="常规 39 2" xfId="1352"/>
+    <cellStyle name="常规 39 3" xfId="1353"/>
+    <cellStyle name="常规 39 4" xfId="1354"/>
+    <cellStyle name="常规 4" xfId="1355"/>
+    <cellStyle name="常规 4 2" xfId="1356"/>
+    <cellStyle name="常规 4 2 2" xfId="1358"/>
+    <cellStyle name="常规 4 2 2 2" xfId="1361"/>
+    <cellStyle name="常规 4 2 2 2 2" xfId="1363"/>
+    <cellStyle name="常规 4 2 2 2 3" xfId="1365"/>
+    <cellStyle name="常规 4 2 2 2 4" xfId="1367"/>
+    <cellStyle name="常规 4 2 2 2 5" xfId="1369"/>
+    <cellStyle name="常规 4 2 2 3" xfId="41"/>
+    <cellStyle name="常规 4 2 2 4" xfId="1372"/>
+    <cellStyle name="常规 4 2 2 5" xfId="1375"/>
+    <cellStyle name="常规 4 2 2 6" xfId="1377"/>
+    <cellStyle name="常规 4 2 3" xfId="1379"/>
+    <cellStyle name="常规 4 2 3 2" xfId="1380"/>
+    <cellStyle name="常规 4 2 3 3" xfId="1381"/>
+    <cellStyle name="常规 4 2 3 4" xfId="1382"/>
+    <cellStyle name="常规 4 2 3 5" xfId="1384"/>
+    <cellStyle name="常规 4 2 4" xfId="1386"/>
+    <cellStyle name="常规 4 2 5" xfId="1388"/>
+    <cellStyle name="常规 4 2 6" xfId="1391"/>
+    <cellStyle name="常规 4 2 7" xfId="1393"/>
+    <cellStyle name="常规 4 3" xfId="1394"/>
+    <cellStyle name="常规 4 3 2" xfId="1396"/>
+    <cellStyle name="常规 4 3 2 2" xfId="1398"/>
+    <cellStyle name="常规 4 3 2 3" xfId="1400"/>
+    <cellStyle name="常规 4 3 2 4" xfId="1402"/>
+    <cellStyle name="常规 4 3 2 5" xfId="1404"/>
+    <cellStyle name="常规 4 3 3" xfId="1406"/>
+    <cellStyle name="常规 4 3 4" xfId="1408"/>
+    <cellStyle name="常规 4 3 5" xfId="1410"/>
+    <cellStyle name="常规 4 3 6" xfId="1413"/>
+    <cellStyle name="常规 4 4" xfId="1357"/>
+    <cellStyle name="常规 4 4 2" xfId="1360"/>
+    <cellStyle name="常规 4 4 3" xfId="40"/>
+    <cellStyle name="常规 4 4 4" xfId="1371"/>
+    <cellStyle name="常规 4 4 5" xfId="1374"/>
+    <cellStyle name="常规 4 5" xfId="1378"/>
+    <cellStyle name="常规 4 6" xfId="1385"/>
+    <cellStyle name="常规 4 7" xfId="1387"/>
+    <cellStyle name="常规 4 8" xfId="1390"/>
+    <cellStyle name="常规 40" xfId="1340"/>
+    <cellStyle name="常规 40 2" xfId="1414"/>
+    <cellStyle name="常规 41" xfId="1342"/>
+    <cellStyle name="常规 41 2" xfId="1344"/>
+    <cellStyle name="常规 42" xfId="1346"/>
+    <cellStyle name="常规 42 2" xfId="1348"/>
+    <cellStyle name="常规 43" xfId="823"/>
+    <cellStyle name="常规 43 2" xfId="826"/>
+    <cellStyle name="常规 44" xfId="22"/>
+    <cellStyle name="常规 44 2" xfId="1351"/>
+    <cellStyle name="常规 45" xfId="836"/>
+    <cellStyle name="常规 45 2" xfId="1415"/>
+    <cellStyle name="常规 46" xfId="839"/>
+    <cellStyle name="常规 47" xfId="842"/>
+    <cellStyle name="常规 47 2" xfId="1416"/>
+    <cellStyle name="常规 48" xfId="1418"/>
+    <cellStyle name="常规 49" xfId="1420"/>
+    <cellStyle name="常规 5" xfId="1421"/>
+    <cellStyle name="常规 5 2" xfId="1422"/>
+    <cellStyle name="常规 5 2 2" xfId="1423"/>
+    <cellStyle name="常规 5 2 2 2" xfId="1424"/>
+    <cellStyle name="常规 5 2 2 2 2" xfId="1149"/>
+    <cellStyle name="常规 5 2 2 2 3" xfId="1154"/>
+    <cellStyle name="常规 5 2 2 2 4" xfId="1156"/>
+    <cellStyle name="常规 5 2 2 2 5" xfId="1158"/>
+    <cellStyle name="常规 5 2 2 3" xfId="1425"/>
+    <cellStyle name="常规 5 2 2 4" xfId="1426"/>
+    <cellStyle name="常规 5 2 2 5" xfId="1427"/>
+    <cellStyle name="常规 5 2 2 6" xfId="1428"/>
+    <cellStyle name="常规 5 2 3" xfId="1429"/>
+    <cellStyle name="常规 5 2 3 2" xfId="1045"/>
+    <cellStyle name="常规 5 2 3 3" xfId="1430"/>
+    <cellStyle name="常规 5 2 3 4" xfId="1431"/>
+    <cellStyle name="常规 5 2 3 5" xfId="1432"/>
+    <cellStyle name="常规 5 2 4" xfId="1433"/>
+    <cellStyle name="常规 5 2 5" xfId="1434"/>
+    <cellStyle name="常规 5 2 6" xfId="1436"/>
+    <cellStyle name="常规 5 2 7" xfId="1438"/>
+    <cellStyle name="常规 5 3" xfId="1439"/>
+    <cellStyle name="常规 5 3 2" xfId="337"/>
+    <cellStyle name="常规 5 3 2 2" xfId="341"/>
+    <cellStyle name="常规 5 3 2 3" xfId="345"/>
+    <cellStyle name="常规 5 3 2 4" xfId="1440"/>
+    <cellStyle name="常规 5 3 2 5" xfId="1441"/>
+    <cellStyle name="常规 5 3 3" xfId="499"/>
+    <cellStyle name="常规 5 3 4" xfId="503"/>
+    <cellStyle name="常规 5 3 5" xfId="505"/>
+    <cellStyle name="常规 5 3 6" xfId="507"/>
+    <cellStyle name="常规 5 4" xfId="1395"/>
+    <cellStyle name="常规 5 4 2" xfId="1397"/>
+    <cellStyle name="常规 5 4 3" xfId="1399"/>
+    <cellStyle name="常规 5 4 4" xfId="1401"/>
+    <cellStyle name="常规 5 4 5" xfId="1403"/>
+    <cellStyle name="常规 5 5" xfId="1405"/>
+    <cellStyle name="常规 5 6" xfId="1407"/>
+    <cellStyle name="常规 5 7" xfId="1409"/>
+    <cellStyle name="常规 5 8" xfId="1412"/>
+    <cellStyle name="常规 50" xfId="835"/>
+    <cellStyle name="常规 51" xfId="838"/>
+    <cellStyle name="常规 52" xfId="841"/>
+    <cellStyle name="常规 53" xfId="1417"/>
+    <cellStyle name="常规 54" xfId="1419"/>
+    <cellStyle name="常规 55" xfId="85"/>
+    <cellStyle name="常规 56" xfId="105"/>
+    <cellStyle name="常规 57" xfId="109"/>
+    <cellStyle name="常规 6" xfId="1442"/>
+    <cellStyle name="常规 6 2" xfId="1443"/>
+    <cellStyle name="常规 6 2 2" xfId="634"/>
+    <cellStyle name="常规 6 2 2 2" xfId="1444"/>
+    <cellStyle name="常规 6 2 2 2 2" xfId="774"/>
+    <cellStyle name="常规 6 2 2 2 3" xfId="781"/>
+    <cellStyle name="常规 6 2 2 2 4" xfId="783"/>
+    <cellStyle name="常规 6 2 2 2 5" xfId="785"/>
+    <cellStyle name="常规 6 2 2 3" xfId="1445"/>
+    <cellStyle name="常规 6 2 2 4" xfId="1446"/>
+    <cellStyle name="常规 6 2 2 5" xfId="1447"/>
+    <cellStyle name="常规 6 2 2 6" xfId="1448"/>
+    <cellStyle name="常规 6 2 3" xfId="636"/>
+    <cellStyle name="常规 6 2 3 2" xfId="1449"/>
+    <cellStyle name="常规 6 2 3 3" xfId="1450"/>
+    <cellStyle name="常规 6 2 3 4" xfId="1451"/>
+    <cellStyle name="常规 6 2 3 5" xfId="1452"/>
+    <cellStyle name="常规 6 2 4" xfId="638"/>
+    <cellStyle name="常规 6 2 5" xfId="1453"/>
+    <cellStyle name="常规 6 2 6" xfId="738"/>
+    <cellStyle name="常规 6 2 7" xfId="750"/>
+    <cellStyle name="常规 6 3" xfId="1454"/>
+    <cellStyle name="常规 6 3 2" xfId="645"/>
+    <cellStyle name="常规 6 3 2 2" xfId="1455"/>
+    <cellStyle name="常规 6 3 2 3" xfId="1456"/>
+    <cellStyle name="常规 6 3 2 4" xfId="1457"/>
+    <cellStyle name="常规 6 3 2 5" xfId="1458"/>
+    <cellStyle name="常规 6 3 3" xfId="647"/>
+    <cellStyle name="常规 6 3 4" xfId="1459"/>
+    <cellStyle name="常规 6 3 5" xfId="1460"/>
+    <cellStyle name="常规 6 3 6" xfId="763"/>
+    <cellStyle name="常规 6 4" xfId="1359"/>
+    <cellStyle name="常规 6 4 2" xfId="1362"/>
+    <cellStyle name="常规 6 4 3" xfId="1364"/>
+    <cellStyle name="常规 6 4 4" xfId="1366"/>
+    <cellStyle name="常规 6 4 5" xfId="1368"/>
+    <cellStyle name="常规 6 5" xfId="39"/>
+    <cellStyle name="常规 6 6" xfId="1370"/>
+    <cellStyle name="常规 6 7" xfId="1373"/>
+    <cellStyle name="常规 6 8" xfId="1376"/>
+    <cellStyle name="常规 60" xfId="1643"/>
+    <cellStyle name="常规 60 2" xfId="1652"/>
+    <cellStyle name="常规 61" xfId="1644"/>
+    <cellStyle name="常规 61 2" xfId="1653"/>
+    <cellStyle name="常规 7" xfId="1461"/>
+    <cellStyle name="常规 8" xfId="1462"/>
+    <cellStyle name="常规 8 2" xfId="1463"/>
+    <cellStyle name="常规 9" xfId="6"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -5313,9 +5312,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5353,9 +5352,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5390,7 +5389,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5425,7 +5424,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5598,7 +5597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
@@ -6193,7 +6192,7 @@
         <v>27</v>
       </c>
       <c r="I12" s="146" t="e">
-        <f>I11*1.2</f>
+        <f>I11*1.22</f>
         <v>#VALUE!</v>
       </c>
       <c r="J12" s="81"/>
@@ -6725,7 +6724,7 @@
       <c r="G25" s="114"/>
       <c r="H25" s="115"/>
       <c r="I25" s="156" t="e">
-        <f>I24/120*20</f>
+        <f>I24/122*22</f>
         <v>#VALUE!</v>
       </c>
       <c r="J25"/>
@@ -11752,7 +11751,7 @@
       <c r="AZ522"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:AC10">
+  <sortState ref="B9:AC10">
     <sortCondition ref="B9"/>
   </sortState>
   <mergeCells count="2">
@@ -11765,10 +11764,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
       <formula1>$D$43:$D$44</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37">
       <formula1>$C$43:$C$44</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates_docs/template.xlsx
+++ b/templates_docs/template.xlsx
@@ -16,7 +16,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$36</definedName>
-    <definedName name="Длина_сделки">расчет!$K$15</definedName>
   </definedNames>
   <calcPr calcId="162913" fullPrecision="0"/>
   <extLst>
@@ -318,7 +317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="23">
+  <numFmts count="22">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-415]General"/>
@@ -341,7 +340,6 @@
     <numFmt numFmtId="181" formatCode="#,##0.00\ &quot;₽&quot;;[Red]#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="182" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
     <numFmt numFmtId="183" formatCode="_ [$¥-804]* #,##0.00_ ;_ [$¥-804]* \-#,##0.00_ ;_ [$¥-804]* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="184" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -629,7 +627,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -651,12 +649,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3130,7 +3122,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3214,12 +3206,6 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3240,12 +3226,6 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3305,9 +3285,6 @@
     <xf numFmtId="9" fontId="32" fillId="3" borderId="14" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="32" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3408,9 +3385,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="32" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3576,7 +3550,7 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="37" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="37" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="37" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5613,14 +5587,14 @@
     <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34" style="147" customWidth="1"/>
+    <col min="9" max="9" width="34" style="141" customWidth="1"/>
     <col min="10" max="11" width="20.6640625" style="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="16.1640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="28.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.1640625" style="96" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" style="96" customWidth="1"/>
+    <col min="16" max="16" width="11.1640625" style="90" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" style="90" customWidth="1"/>
     <col min="18" max="18" width="16.6640625" style="8" customWidth="1"/>
     <col min="19" max="19" width="15.6640625" style="8" customWidth="1"/>
     <col min="20" max="20" width="16.1640625" style="8" customWidth="1"/>
@@ -5637,23 +5611,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="168" t="s">
+      <c r="B1" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="170"/>
-      <c r="AD1" s="167"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="163"/>
+      <c r="L1" s="163"/>
+      <c r="M1" s="163"/>
+      <c r="N1" s="163"/>
+      <c r="O1" s="164"/>
+      <c r="AD1" s="161"/>
       <c r="AU1"/>
       <c r="AV1"/>
       <c r="AW1"/>
@@ -5670,14 +5644,14 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="140"/>
+      <c r="I2" s="134"/>
       <c r="J2" s="6"/>
-      <c r="V2" s="133"/>
-      <c r="W2" s="133"/>
-      <c r="X2" s="133"/>
-      <c r="Y2" s="133"/>
-      <c r="Z2" s="133"/>
-      <c r="AD2" s="167"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AD2" s="161"/>
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
@@ -5696,7 +5670,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="140"/>
+      <c r="I3" s="134"/>
       <c r="J3" s="5"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5705,12 +5679,12 @@
       <c r="O3" s="5"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
-      <c r="V3" s="133"/>
-      <c r="W3" s="133"/>
-      <c r="X3" s="133"/>
-      <c r="Y3" s="133"/>
-      <c r="Z3" s="133"/>
-      <c r="AD3" s="167"/>
+      <c r="V3" s="127"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="127"/>
+      <c r="Y3" s="127"/>
+      <c r="Z3" s="127"/>
+      <c r="AD3" s="161"/>
       <c r="AU3"/>
       <c r="AV3"/>
       <c r="AW3"/>
@@ -5729,25 +5703,28 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="140"/>
+      <c r="I4" s="134"/>
       <c r="J4" s="5"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="171"/>
-      <c r="Q4" s="172"/>
-      <c r="R4" s="172"/>
-      <c r="S4" s="172"/>
-      <c r="T4" s="172"/>
-      <c r="U4" s="173"/>
-      <c r="V4" s="133"/>
-      <c r="W4" s="133"/>
-      <c r="X4" s="133"/>
-      <c r="Y4" s="133"/>
-      <c r="Z4" s="133"/>
-      <c r="AD4" s="167"/>
+      <c r="P4" s="165"/>
+      <c r="Q4" s="166"/>
+      <c r="R4" s="166"/>
+      <c r="S4" s="166"/>
+      <c r="T4" s="166"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="127"/>
+      <c r="W4" s="127"/>
+      <c r="X4" s="127"/>
+      <c r="Y4" s="127"/>
+      <c r="Z4" s="127"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
       <c r="AU4"/>
       <c r="AV4"/>
       <c r="AW4"/>
@@ -5767,7 +5744,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="141"/>
+      <c r="I5" s="135"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -5780,12 +5757,15 @@
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
-      <c r="V5" s="133"/>
-      <c r="W5" s="133"/>
-      <c r="X5" s="133"/>
-      <c r="Y5" s="133"/>
-      <c r="Z5" s="133"/>
-      <c r="AD5" s="167"/>
+      <c r="V5" s="127"/>
+      <c r="W5" s="127"/>
+      <c r="X5" s="127"/>
+      <c r="Y5" s="127"/>
+      <c r="Z5" s="127"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
       <c r="AU5"/>
       <c r="AV5"/>
       <c r="AW5"/>
@@ -5795,28 +5775,31 @@
     </row>
     <row r="6" spans="1:52" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="136"/>
+      <c r="C6" s="130"/>
       <c r="D6" s="18"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
-      <c r="I6" s="142"/>
+      <c r="I6" s="136"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
-      <c r="V6" s="134"/>
-      <c r="W6" s="134"/>
-      <c r="X6" s="134"/>
-      <c r="Y6" s="134"/>
-      <c r="Z6" s="134"/>
-      <c r="AD6" s="167"/>
+      <c r="V6" s="128"/>
+      <c r="W6" s="128"/>
+      <c r="X6" s="128"/>
+      <c r="Y6" s="128"/>
+      <c r="Z6" s="128"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6"/>
@@ -5826,36 +5809,39 @@
     </row>
     <row r="7" spans="1:52" ht="15" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="143"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="131" t="s">
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="131"/>
-      <c r="T7" s="131"/>
-      <c r="U7" s="131"/>
-      <c r="V7" s="131"/>
-      <c r="W7" s="131"/>
-      <c r="X7" s="131"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="132"/>
-      <c r="AD7" s="167"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="125"/>
+      <c r="R7" s="125"/>
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="125"/>
+      <c r="X7" s="125"/>
+      <c r="Y7" s="125"/>
+      <c r="Z7" s="126"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
       <c r="AU7"/>
       <c r="AV7"/>
       <c r="AW7"/>
@@ -5886,7 +5872,7 @@
       <c r="H8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="144" t="s">
+      <c r="I8" s="138" t="s">
         <v>26</v>
       </c>
       <c r="J8" s="26" t="s">
@@ -5931,17 +5917,17 @@
       <c r="W8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="X8" s="137" t="s">
+      <c r="X8" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="Y8" s="138"/>
+      <c r="Y8" s="132"/>
       <c r="Z8" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="30"/>
-      <c r="AD8" s="167"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
       <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8"/>
@@ -5949,73 +5935,73 @@
       <c r="AY8"/>
       <c r="AZ8"/>
     </row>
-    <row r="9" spans="1:52" s="40" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A9" s="31"/>
-      <c r="B9" s="135">
+    <row r="9" spans="1:52" s="36" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A9" s="29"/>
+      <c r="B9" s="129">
         <v>1</v>
       </c>
-      <c r="C9" s="135"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124">
+      <c r="C9" s="129"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118">
         <v>2</v>
       </c>
-      <c r="G9" s="124">
+      <c r="G9" s="118">
         <v>3</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="31">
         <v>4</v>
       </c>
-      <c r="I9" s="145">
+      <c r="I9" s="139">
         <v>5</v>
       </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="33">
+      <c r="J9" s="32"/>
+      <c r="K9" s="31">
         <v>6</v>
       </c>
-      <c r="L9" s="35">
+      <c r="L9" s="33">
         <v>7</v>
       </c>
-      <c r="M9" s="33">
+      <c r="M9" s="31">
         <v>8</v>
       </c>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33">
+      <c r="N9" s="31"/>
+      <c r="O9" s="31">
         <v>9</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="31">
         <v>10</v>
       </c>
-      <c r="Q9" s="36">
+      <c r="Q9" s="34">
         <v>11</v>
       </c>
-      <c r="R9" s="36">
+      <c r="R9" s="34">
         <v>12</v>
       </c>
-      <c r="S9" s="36">
+      <c r="S9" s="34">
         <v>13</v>
       </c>
-      <c r="T9" s="36">
+      <c r="T9" s="34">
         <v>14</v>
       </c>
-      <c r="U9" s="37">
+      <c r="U9" s="35">
         <v>15</v>
       </c>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37">
+      <c r="V9" s="35"/>
+      <c r="W9" s="35">
         <v>16</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="35">
         <v>17</v>
       </c>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37">
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35">
         <v>19</v>
       </c>
-      <c r="AA9" s="38"/>
-      <c r="AB9" s="38"/>
-      <c r="AC9" s="39"/>
-      <c r="AD9" s="167"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
       <c r="AU9"/>
       <c r="AV9"/>
       <c r="AW9"/>
@@ -6023,95 +6009,95 @@
       <c r="AY9"/>
       <c r="AZ9"/>
     </row>
-    <row r="10" spans="1:52" s="60" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A10" s="41"/>
-      <c r="B10" s="42">
+    <row r="10" spans="1:52" s="55" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A10" s="37"/>
+      <c r="B10" s="38">
         <v>1</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="166"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="45" t="s">
+      <c r="D10" s="160"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="160" t="s">
+      <c r="G10" s="154" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="146"/>
-      <c r="I10" s="146" t="e">
+      <c r="H10" s="140"/>
+      <c r="I10" s="140" t="e">
         <f>G10*H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="47" t="e">
+      <c r="J10" s="43" t="e">
         <f>I10*14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K10" s="48" t="s">
+      <c r="K10" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="49" t="str">
+      <c r="L10" s="45" t="str">
         <f>G10</f>
         <v>{{ quantity }}</v>
       </c>
-      <c r="M10" s="50" t="s">
+      <c r="M10" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="N10" s="51" t="e">
+      <c r="N10" s="47" t="e">
         <f>M10/P10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O10" s="52" t="e">
+      <c r="O10" s="48" t="e">
         <f>M10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P10" s="161" t="s">
+      <c r="P10" s="155" t="s">
         <v>81</v>
       </c>
-      <c r="Q10" s="53" t="e">
+      <c r="Q10" s="49" t="e">
         <f>P10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R10" s="54" t="e">
+      <c r="R10" s="50" t="e">
         <f>$U$14/$Q$11*P10/12*0.3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S10" s="54" t="e">
+      <c r="S10" s="50" t="e">
         <f>R10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="T10" s="54" t="e">
+      <c r="T10" s="50" t="e">
         <f>$U$14/$Q$11*P10/12*0.7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U10" s="54" t="e">
+      <c r="U10" s="50" t="e">
         <f>T10*L10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V10" s="55" t="e">
+      <c r="V10" s="51" t="e">
         <f>H10/P10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W10" s="51" t="e">
+      <c r="W10" s="47" t="e">
         <f>N10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X10" s="56" t="s">
+      <c r="X10" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="Y10" s="57" t="e">
+      <c r="Y10" s="53" t="e">
         <f>L10*(M10+R10)*X10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z10" s="58" t="e">
+      <c r="Z10" s="54" t="e">
         <f>(I10-O10-S10-U10-Y10-AA10-AC10-AB10)/I10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA10" s="59"/>
-      <c r="AB10" s="59"/>
-      <c r="AC10" s="59"/>
-      <c r="AD10" s="167"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
       <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
@@ -6119,60 +6105,60 @@
       <c r="AY10"/>
       <c r="AZ10"/>
     </row>
-    <row r="11" spans="1:52" s="60" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="41"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="146" t="e">
+    <row r="11" spans="1:52" s="55" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="37"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="140" t="e">
         <f>SUM(I10:I10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="65"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="67"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="46" t="e">
+      <c r="J11" s="60"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="42" t="e">
         <f>SUM(O10:O10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="71" t="e">
+      <c r="P11" s="65"/>
+      <c r="Q11" s="66" t="e">
         <f>SUM(Q10:Q10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R11" s="72"/>
-      <c r="S11" s="46" t="e">
+      <c r="R11" s="67"/>
+      <c r="S11" s="42" t="e">
         <f>SUM(S10:S10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="T11" s="73"/>
-      <c r="U11" s="73" t="e">
+      <c r="T11" s="68"/>
+      <c r="U11" s="68" t="e">
         <f>SUM(U10:U10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V11" s="74"/>
-      <c r="W11" s="75"/>
-      <c r="X11" s="76" t="e">
+      <c r="V11" s="69"/>
+      <c r="W11" s="70"/>
+      <c r="X11" s="71" t="e">
         <f>AVERAGE(X10:X10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y11" s="46" t="e">
+      <c r="Y11" s="42" t="e">
         <f>SUM(Y10:Y10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z11" s="77" t="e">
+      <c r="Z11" s="72" t="e">
         <f>(I11-O11-S11-U11-Y11-AA11-AC11-AB11)/I11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA11" s="59"/>
-      <c r="AB11" s="59"/>
-      <c r="AC11" s="59"/>
-      <c r="AD11" s="167"/>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
       <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11"/>
@@ -6180,40 +6166,42 @@
       <c r="AY11"/>
       <c r="AZ11"/>
     </row>
-    <row r="12" spans="1:52" s="60" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="41"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="64" t="s">
+    <row r="12" spans="1:52" s="55" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="37"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="146" t="e">
+      <c r="I12" s="140" t="e">
         <f>I11*1.22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="81"/>
+      <c r="J12" s="76"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="84"/>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="87"/>
-      <c r="S12" s="88"/>
-      <c r="T12" s="89"/>
-      <c r="U12" s="90"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="75"/>
-      <c r="X12" s="91"/>
-      <c r="Y12" s="92"/>
-      <c r="Z12" s="93"/>
-      <c r="AC12" s="94"/>
-      <c r="AD12" s="167"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="78"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="83"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="85"/>
+      <c r="V12" s="69"/>
+      <c r="W12" s="70"/>
+      <c r="X12" s="86"/>
+      <c r="Y12" s="87"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
       <c r="AU12"/>
       <c r="AV12"/>
       <c r="AW12"/>
@@ -6222,21 +6210,21 @@
       <c r="AZ12"/>
     </row>
     <row r="13" spans="1:52" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="125" t="s">
+      <c r="B13" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="126"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="147"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="141"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="90"/>
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13"/>
@@ -6249,7 +6237,9 @@
       <c r="Y13"/>
       <c r="Z13"/>
       <c r="AA13"/>
-      <c r="AD13" s="167"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
       <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13"/>
@@ -6258,33 +6248,33 @@
       <c r="AZ13"/>
     </row>
     <row r="14" spans="1:52" ht="14.1" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="148"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="142"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-      <c r="O14" s="107"/>
+      <c r="O14" s="101"/>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14"/>
-      <c r="T14" s="163" t="s">
+      <c r="T14" s="157" t="s">
         <v>83</v>
       </c>
-      <c r="U14" s="162" t="s">
+      <c r="U14" s="156" t="s">
         <v>82</v>
       </c>
       <c r="V14"/>
@@ -6293,7 +6283,9 @@
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
-      <c r="AD14" s="167"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
       <c r="AU14"/>
       <c r="AV14"/>
       <c r="AW14"/>
@@ -6302,29 +6294,29 @@
       <c r="AZ14"/>
     </row>
     <row r="15" spans="1:52" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="103" t="s">
+      <c r="B15" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="149">
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="143">
         <v>150</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="96">
+      <c r="K15" s="90">
         <f>I15+I16</f>
         <v>180</v>
       </c>
-      <c r="L15" s="96"/>
+      <c r="L15" s="90"/>
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15"/>
@@ -6337,7 +6329,9 @@
       <c r="Y15"/>
       <c r="Z15"/>
       <c r="AA15"/>
-      <c r="AD15" s="167"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
       <c r="AU15"/>
       <c r="AV15"/>
       <c r="AW15"/>
@@ -6345,29 +6339,29 @@
       <c r="AY15"/>
       <c r="AZ15"/>
     </row>
-    <row r="16" spans="1:52" s="40" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A16" s="95" t="s">
+    <row r="16" spans="1:52" s="36" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A16" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="150">
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="144">
         <v>30</v>
       </c>
-      <c r="J16" s="108"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
       <c r="N16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O16" s="109" t="e">
+      <c r="O16" s="103" t="e">
         <f>I11*14</f>
         <v>#VALUE!</v>
       </c>
@@ -6383,7 +6377,9 @@
       <c r="Y16"/>
       <c r="Z16"/>
       <c r="AA16"/>
-      <c r="AD16" s="167"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
       <c r="AU16"/>
       <c r="AV16"/>
       <c r="AW16"/>
@@ -6392,26 +6388,26 @@
       <c r="AZ16"/>
     </row>
     <row r="17" spans="1:52" ht="14.1" customHeight="1">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="113" t="s">
+      <c r="B17" s="107" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="151"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
       <c r="N17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O17" s="109" t="e">
+      <c r="O17" s="103" t="e">
         <f>I12*14</f>
         <v>#VALUE!</v>
       </c>
@@ -6427,7 +6423,9 @@
       <c r="Y17"/>
       <c r="Z17"/>
       <c r="AA17"/>
-      <c r="AD17" s="167"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
       <c r="AU17"/>
       <c r="AV17"/>
       <c r="AW17"/>
@@ -6436,22 +6434,22 @@
       <c r="AZ17"/>
     </row>
     <row r="18" spans="1:52" ht="14.1" customHeight="1">
-      <c r="A18" s="95" t="s">
+      <c r="A18" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18"/>
@@ -6464,7 +6462,9 @@
       <c r="Y18"/>
       <c r="Z18"/>
       <c r="AA18"/>
-      <c r="AD18" s="167"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18"/>
@@ -6473,25 +6473,25 @@
       <c r="AZ18"/>
     </row>
     <row r="19" spans="1:52" ht="18.75" customHeight="1">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="153" t="e">
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="147" t="e">
         <f>I11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="112"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
       <c r="M19" s="8"/>
       <c r="P19"/>
       <c r="Q19"/>
@@ -6505,7 +6505,9 @@
       <c r="Y19"/>
       <c r="Z19"/>
       <c r="AA19"/>
-      <c r="AD19" s="167"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
       <c r="AU19"/>
       <c r="AV19"/>
       <c r="AW19"/>
@@ -6514,17 +6516,17 @@
       <c r="AZ19"/>
     </row>
     <row r="20" spans="1:52" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="113"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="114"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="153"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="147"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
@@ -6543,7 +6545,9 @@
       <c r="Y20"/>
       <c r="Z20"/>
       <c r="AA20"/>
-      <c r="AD20" s="167"/>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
       <c r="AU20"/>
       <c r="AV20"/>
       <c r="AW20"/>
@@ -6552,17 +6556,17 @@
       <c r="AZ20"/>
     </row>
     <row r="21" spans="1:52" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A21" s="95" t="s">
+      <c r="A21" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="113"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="153"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="147"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
@@ -6581,7 +6585,9 @@
       <c r="Y21"/>
       <c r="Z21"/>
       <c r="AA21"/>
-      <c r="AD21" s="167"/>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
       <c r="AU21"/>
       <c r="AV21"/>
       <c r="AW21"/>
@@ -6590,24 +6596,24 @@
       <c r="AZ21"/>
     </row>
     <row r="22" spans="1:52" s="1" customFormat="1" ht="11.1" customHeight="1">
-      <c r="A22" s="95" t="s">
+      <c r="A22" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="113"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="114"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="153"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="108"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="147"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
-      <c r="M22" s="164" t="s">
+      <c r="M22" s="158" t="s">
         <v>85</v>
       </c>
-      <c r="N22" s="165"/>
+      <c r="N22" s="159"/>
       <c r="O22"/>
       <c r="P22"/>
       <c r="Q22"/>
@@ -6621,7 +6627,9 @@
       <c r="Y22"/>
       <c r="Z22"/>
       <c r="AA22"/>
-      <c r="AD22" s="167"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
       <c r="AU22"/>
       <c r="AV22"/>
       <c r="AW22"/>
@@ -6629,20 +6637,20 @@
       <c r="AY22"/>
       <c r="AZ22"/>
     </row>
-    <row r="23" spans="1:52" s="100" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="97" t="s">
+    <row r="23" spans="1:52" s="94" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="116"/>
-      <c r="D23" s="114"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="114"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="154"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="108"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="148"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
@@ -6659,7 +6667,9 @@
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23"/>
-      <c r="AD23" s="167"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
       <c r="AU23"/>
       <c r="AV23"/>
       <c r="AW23"/>
@@ -6667,28 +6677,28 @@
       <c r="AY23"/>
       <c r="AZ23"/>
     </row>
-    <row r="24" spans="1:52" s="98" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="101"/>
-      <c r="B24" s="113" t="s">
+    <row r="24" spans="1:52" s="92" customFormat="1" ht="15" customHeight="1">
+      <c r="A24" s="95"/>
+      <c r="B24" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="114"/>
-      <c r="D24" s="114"/>
-      <c r="E24" s="114"/>
-      <c r="F24" s="114"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="155" t="e">
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="149" t="e">
         <f>I12</f>
         <v>#VALUE!</v>
       </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
-      <c r="M24" s="164" t="s">
+      <c r="M24" s="158" t="s">
         <v>86</v>
       </c>
-      <c r="N24" s="165" t="s">
+      <c r="N24" s="159" t="s">
         <v>87</v>
       </c>
       <c r="O24"/>
@@ -6704,7 +6714,9 @@
       <c r="Y24"/>
       <c r="Z24"/>
       <c r="AA24"/>
-      <c r="AD24" s="167"/>
+      <c r="AB24"/>
+      <c r="AC24"/>
+      <c r="AD24"/>
       <c r="AU24"/>
       <c r="AV24"/>
       <c r="AW24"/>
@@ -6712,26 +6724,26 @@
       <c r="AY24"/>
       <c r="AZ24"/>
     </row>
-    <row r="25" spans="1:52" s="60" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="113" t="s">
+    <row r="25" spans="1:52" s="55" customFormat="1" ht="15" customHeight="1">
+      <c r="A25" s="37"/>
+      <c r="B25" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="114"/>
-      <c r="D25" s="114"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="114"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="115"/>
-      <c r="I25" s="156" t="e">
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="150" t="e">
         <f>I24/122*22</f>
         <v>#VALUE!</v>
       </c>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
-      <c r="M25" s="100"/>
-      <c r="N25" s="100"/>
+      <c r="M25" s="94"/>
+      <c r="N25" s="94"/>
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25"/>
@@ -6745,7 +6757,7 @@
       <c r="Y25"/>
       <c r="Z25"/>
       <c r="AA25"/>
-      <c r="AD25" s="167"/>
+      <c r="AD25" s="161"/>
       <c r="AU25"/>
       <c r="AV25"/>
       <c r="AW25"/>
@@ -6753,28 +6765,28 @@
       <c r="AY25"/>
       <c r="AZ25"/>
     </row>
-    <row r="26" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="113" t="s">
+    <row r="26" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="96"/>
+      <c r="B26" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="114"/>
-      <c r="D26" s="114"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="114"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="115"/>
-      <c r="I26" s="156" t="e">
+      <c r="C26" s="108"/>
+      <c r="D26" s="108"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="150" t="e">
         <f>I24-I25</f>
         <v>#VALUE!</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26"/>
-      <c r="M26" s="164" t="s">
+      <c r="M26" s="158" t="s">
         <v>88</v>
       </c>
-      <c r="N26" s="165" t="s">
+      <c r="N26" s="159" t="s">
         <v>89</v>
       </c>
       <c r="O26"/>
@@ -6790,7 +6802,7 @@
       <c r="Y26"/>
       <c r="Z26"/>
       <c r="AA26"/>
-      <c r="AD26" s="167"/>
+      <c r="AD26" s="161"/>
       <c r="AU26"/>
       <c r="AV26"/>
       <c r="AW26"/>
@@ -6798,18 +6810,18 @@
       <c r="AY26"/>
       <c r="AZ26"/>
     </row>
-    <row r="27" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="113" t="s">
+    <row r="27" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="96"/>
+      <c r="B27" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="114"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="156" t="e">
+      <c r="C27" s="108"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="150" t="e">
         <f>SUM(I28:I37)</f>
         <v>#VALUE!</v>
       </c>
@@ -6831,7 +6843,7 @@
       <c r="Y27"/>
       <c r="Z27"/>
       <c r="AA27"/>
-      <c r="AD27" s="167"/>
+      <c r="AD27" s="161"/>
       <c r="AU27"/>
       <c r="AV27"/>
       <c r="AW27"/>
@@ -6839,18 +6851,18 @@
       <c r="AY27"/>
       <c r="AZ27"/>
     </row>
-    <row r="28" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="113" t="s">
+    <row r="28" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="96"/>
+      <c r="B28" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="156" t="e">
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="150" t="e">
         <f>O11</f>
         <v>#VALUE!</v>
       </c>
@@ -6872,7 +6884,7 @@
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28"/>
-      <c r="AD28" s="167"/>
+      <c r="AD28" s="161"/>
       <c r="AU28"/>
       <c r="AV28"/>
       <c r="AW28"/>
@@ -6880,20 +6892,20 @@
       <c r="AY28"/>
       <c r="AZ28"/>
     </row>
-    <row r="29" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="121" t="s">
+    <row r="29" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="96"/>
+      <c r="B29" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="122"/>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="118" t="s">
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="116"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="157" t="e">
+      <c r="I29" s="151" t="e">
         <f>IF(H29=D43,I28*3.2%,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -6915,7 +6927,7 @@
       <c r="Y29"/>
       <c r="Z29"/>
       <c r="AA29"/>
-      <c r="AD29" s="167"/>
+      <c r="AD29" s="161"/>
       <c r="AU29"/>
       <c r="AV29"/>
       <c r="AW29"/>
@@ -6923,18 +6935,18 @@
       <c r="AY29"/>
       <c r="AZ29"/>
     </row>
-    <row r="30" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="113" t="s">
+    <row r="30" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="96"/>
+      <c r="B30" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="115"/>
-      <c r="I30" s="156">
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="150">
         <f>AA11</f>
         <v>0</v>
       </c>
@@ -6956,7 +6968,7 @@
       <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
-      <c r="AD30" s="167"/>
+      <c r="AD30" s="161"/>
       <c r="AU30"/>
       <c r="AV30"/>
       <c r="AW30"/>
@@ -6964,18 +6976,18 @@
       <c r="AY30"/>
       <c r="AZ30"/>
     </row>
-    <row r="31" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="120" t="s">
+    <row r="31" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="96"/>
+      <c r="B31" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="114"/>
-      <c r="D31" s="114"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="114"/>
-      <c r="G31" s="114"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="156">
+      <c r="C31" s="108"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="150">
         <f>AB11</f>
         <v>0</v>
       </c>
@@ -6997,11 +7009,11 @@
       <c r="Y31"/>
       <c r="Z31"/>
       <c r="AA31"/>
-      <c r="AB31" s="99"/>
-      <c r="AC31" s="99"/>
-      <c r="AD31" s="167"/>
-      <c r="AE31" s="99"/>
-      <c r="AF31" s="99"/>
+      <c r="AB31" s="93"/>
+      <c r="AC31" s="93"/>
+      <c r="AD31" s="161"/>
+      <c r="AE31" s="93"/>
+      <c r="AF31" s="93"/>
       <c r="AU31"/>
       <c r="AV31"/>
       <c r="AW31"/>
@@ -7009,18 +7021,18 @@
       <c r="AY31"/>
       <c r="AZ31"/>
     </row>
-    <row r="32" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A32" s="102"/>
-      <c r="B32" s="120" t="s">
+    <row r="32" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="96"/>
+      <c r="B32" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="114"/>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="115"/>
-      <c r="I32" s="156">
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="150">
         <f>AC11</f>
         <v>0</v>
       </c>
@@ -7042,11 +7054,11 @@
       <c r="Y32"/>
       <c r="Z32"/>
       <c r="AA32"/>
-      <c r="AB32" s="99"/>
-      <c r="AC32" s="99"/>
-      <c r="AD32" s="167"/>
-      <c r="AE32" s="99"/>
-      <c r="AF32" s="99"/>
+      <c r="AB32" s="93"/>
+      <c r="AC32" s="93"/>
+      <c r="AD32" s="161"/>
+      <c r="AE32" s="93"/>
+      <c r="AF32" s="93"/>
       <c r="AU32"/>
       <c r="AV32"/>
       <c r="AW32"/>
@@ -7054,21 +7066,21 @@
       <c r="AY32"/>
       <c r="AZ32"/>
     </row>
-    <row r="33" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A33" s="102"/>
-      <c r="B33" s="121" t="s">
+    <row r="33" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="96"/>
+      <c r="B33" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="122"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="122"/>
-      <c r="G33" s="119"/>
-      <c r="H33" s="118" t="s">
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="116"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="I33" s="157">
-        <f>IF(H33="ДА",I28*16%/365*Длина_сделки,0)</f>
+      <c r="I33" s="151">
+        <f>IF(H33="ДА",I28*16%/365*K15,0)</f>
         <v>0</v>
       </c>
       <c r="J33"/>
@@ -7089,11 +7101,11 @@
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
-      <c r="AB33" s="99"/>
-      <c r="AC33" s="99"/>
-      <c r="AD33" s="167"/>
-      <c r="AE33" s="99"/>
-      <c r="AF33" s="99"/>
+      <c r="AB33" s="93"/>
+      <c r="AC33" s="93"/>
+      <c r="AD33" s="161"/>
+      <c r="AE33" s="93"/>
+      <c r="AF33" s="93"/>
       <c r="AU33"/>
       <c r="AV33"/>
       <c r="AW33"/>
@@ -7101,18 +7113,18 @@
       <c r="AY33"/>
       <c r="AZ33"/>
     </row>
-    <row r="34" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A34" s="102"/>
-      <c r="B34" s="120" t="s">
+    <row r="34" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A34" s="96"/>
+      <c r="B34" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="114"/>
-      <c r="D34" s="114"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="114"/>
-      <c r="G34" s="114"/>
-      <c r="H34" s="115"/>
-      <c r="I34" s="156">
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="150">
         <f>AA11</f>
         <v>0</v>
       </c>
@@ -7134,12 +7146,12 @@
       <c r="Y34"/>
       <c r="Z34"/>
       <c r="AA34"/>
-      <c r="AB34" s="99"/>
-      <c r="AC34" s="99"/>
-      <c r="AD34" s="167"/>
-      <c r="AE34" s="99"/>
-      <c r="AF34" s="99"/>
-      <c r="AG34" s="99"/>
+      <c r="AB34" s="93"/>
+      <c r="AC34" s="93"/>
+      <c r="AD34" s="161"/>
+      <c r="AE34" s="93"/>
+      <c r="AF34" s="93"/>
+      <c r="AG34" s="93"/>
       <c r="AU34"/>
       <c r="AV34"/>
       <c r="AW34"/>
@@ -7147,18 +7159,18 @@
       <c r="AY34"/>
       <c r="AZ34"/>
     </row>
-    <row r="35" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="102"/>
-      <c r="B35" s="120" t="s">
+    <row r="35" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A35" s="96"/>
+      <c r="B35" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="115"/>
-      <c r="I35" s="156">
+      <c r="C35" s="108"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="150">
         <f>AB11</f>
         <v>0</v>
       </c>
@@ -7180,12 +7192,12 @@
       <c r="Y35"/>
       <c r="Z35"/>
       <c r="AA35"/>
-      <c r="AB35" s="99"/>
-      <c r="AC35" s="99"/>
-      <c r="AD35" s="167"/>
-      <c r="AE35" s="99"/>
-      <c r="AF35" s="99"/>
-      <c r="AG35" s="99"/>
+      <c r="AB35" s="93"/>
+      <c r="AC35" s="93"/>
+      <c r="AD35" s="161"/>
+      <c r="AE35" s="93"/>
+      <c r="AF35" s="93"/>
+      <c r="AG35" s="93"/>
       <c r="AU35"/>
       <c r="AV35"/>
       <c r="AW35"/>
@@ -7193,18 +7205,18 @@
       <c r="AY35"/>
       <c r="AZ35"/>
     </row>
-    <row r="36" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A36" s="102"/>
-      <c r="B36" s="120" t="s">
+    <row r="36" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A36" s="96"/>
+      <c r="B36" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="114"/>
-      <c r="D36" s="114"/>
-      <c r="E36" s="114"/>
-      <c r="F36" s="114"/>
-      <c r="G36" s="114"/>
-      <c r="H36" s="115"/>
-      <c r="I36" s="156">
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="150">
         <f>AC11</f>
         <v>0</v>
       </c>
@@ -7226,12 +7238,12 @@
       <c r="Y36"/>
       <c r="Z36"/>
       <c r="AA36"/>
-      <c r="AB36" s="99"/>
-      <c r="AC36" s="99"/>
-      <c r="AD36" s="167"/>
-      <c r="AE36" s="99"/>
-      <c r="AF36" s="99"/>
-      <c r="AG36" s="99"/>
+      <c r="AB36" s="93"/>
+      <c r="AC36" s="93"/>
+      <c r="AD36" s="161"/>
+      <c r="AE36" s="93"/>
+      <c r="AF36" s="93"/>
+      <c r="AG36" s="93"/>
       <c r="AU36"/>
       <c r="AV36"/>
       <c r="AW36"/>
@@ -7239,20 +7251,20 @@
       <c r="AY36"/>
       <c r="AZ36"/>
     </row>
-    <row r="37" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A37" s="102"/>
-      <c r="B37" s="121" t="s">
+    <row r="37" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A37" s="96"/>
+      <c r="B37" s="115" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="122"/>
-      <c r="D37" s="122"/>
-      <c r="E37" s="122"/>
-      <c r="F37" s="122"/>
-      <c r="G37" s="119"/>
-      <c r="H37" s="118" t="s">
+      <c r="C37" s="116"/>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="116"/>
+      <c r="G37" s="113"/>
+      <c r="H37" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="I37" s="157">
+      <c r="I37" s="151">
         <f>IF(H37="ДА",I24*3%/365*(I15+I16),0)</f>
         <v>0</v>
       </c>
@@ -7274,12 +7286,12 @@
       <c r="Y37"/>
       <c r="Z37"/>
       <c r="AA37"/>
-      <c r="AB37" s="99"/>
-      <c r="AC37" s="99"/>
-      <c r="AD37" s="167"/>
-      <c r="AE37" s="99"/>
-      <c r="AF37" s="99"/>
-      <c r="AG37" s="99"/>
+      <c r="AB37" s="93"/>
+      <c r="AC37" s="93"/>
+      <c r="AD37" s="161"/>
+      <c r="AE37" s="93"/>
+      <c r="AF37" s="93"/>
+      <c r="AG37" s="93"/>
       <c r="AU37"/>
       <c r="AV37"/>
       <c r="AW37"/>
@@ -7287,18 +7299,18 @@
       <c r="AY37"/>
       <c r="AZ37"/>
     </row>
-    <row r="38" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A38" s="102"/>
-      <c r="B38" s="120" t="s">
+    <row r="38" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A38" s="96"/>
+      <c r="B38" s="114" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="114"/>
-      <c r="D38" s="114"/>
-      <c r="E38" s="114"/>
-      <c r="F38" s="114"/>
-      <c r="G38" s="114"/>
-      <c r="H38" s="115"/>
-      <c r="I38" s="156" t="e">
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="150" t="e">
         <f>I26-I27</f>
         <v>#VALUE!</v>
       </c>
@@ -7320,12 +7332,12 @@
       <c r="Y38"/>
       <c r="Z38"/>
       <c r="AA38"/>
-      <c r="AB38" s="99"/>
-      <c r="AC38" s="99"/>
-      <c r="AD38" s="167"/>
-      <c r="AE38" s="99"/>
-      <c r="AF38" s="99"/>
-      <c r="AG38" s="99"/>
+      <c r="AB38" s="93"/>
+      <c r="AC38" s="93"/>
+      <c r="AD38" s="161"/>
+      <c r="AE38" s="93"/>
+      <c r="AF38" s="93"/>
+      <c r="AG38" s="93"/>
       <c r="AU38"/>
       <c r="AV38"/>
       <c r="AW38"/>
@@ -7333,18 +7345,18 @@
       <c r="AY38"/>
       <c r="AZ38"/>
     </row>
-    <row r="39" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A39" s="102"/>
-      <c r="B39" s="120" t="s">
+    <row r="39" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A39" s="96"/>
+      <c r="B39" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="114"/>
-      <c r="D39" s="114"/>
-      <c r="E39" s="114"/>
-      <c r="F39" s="114"/>
-      <c r="G39" s="114"/>
-      <c r="H39" s="115"/>
-      <c r="I39" s="156"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="108"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="150"/>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39"/>
@@ -7363,12 +7375,12 @@
       <c r="Y39"/>
       <c r="Z39"/>
       <c r="AA39"/>
-      <c r="AB39" s="99"/>
-      <c r="AC39" s="99"/>
-      <c r="AD39" s="167"/>
-      <c r="AE39" s="99"/>
-      <c r="AF39" s="99"/>
-      <c r="AG39" s="99"/>
+      <c r="AB39" s="93"/>
+      <c r="AC39" s="93"/>
+      <c r="AD39" s="161"/>
+      <c r="AE39" s="93"/>
+      <c r="AF39" s="93"/>
+      <c r="AG39" s="93"/>
       <c r="AU39"/>
       <c r="AV39"/>
       <c r="AW39"/>
@@ -7376,18 +7388,18 @@
       <c r="AY39"/>
       <c r="AZ39"/>
     </row>
-    <row r="40" spans="1:52" s="96" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="102"/>
-      <c r="B40" s="120" t="s">
+    <row r="40" spans="1:52" s="90" customFormat="1" ht="15" customHeight="1">
+      <c r="A40" s="96"/>
+      <c r="B40" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="114"/>
-      <c r="D40" s="114"/>
-      <c r="E40" s="114"/>
-      <c r="F40" s="114"/>
-      <c r="G40" s="114"/>
-      <c r="H40" s="115"/>
-      <c r="I40" s="158" t="e">
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108"/>
+      <c r="H40" s="109"/>
+      <c r="I40" s="152" t="e">
         <f>I38/I26</f>
         <v>#VALUE!</v>
       </c>
@@ -7409,12 +7421,12 @@
       <c r="Y40"/>
       <c r="Z40"/>
       <c r="AA40"/>
-      <c r="AB40" s="99"/>
-      <c r="AC40" s="99"/>
-      <c r="AD40" s="167"/>
-      <c r="AE40" s="99"/>
-      <c r="AF40" s="99"/>
-      <c r="AG40" s="99"/>
+      <c r="AB40" s="93"/>
+      <c r="AC40" s="93"/>
+      <c r="AD40" s="161"/>
+      <c r="AE40" s="93"/>
+      <c r="AF40" s="93"/>
+      <c r="AG40" s="93"/>
       <c r="AU40"/>
       <c r="AV40"/>
       <c r="AW40"/>
@@ -7422,7 +7434,7 @@
       <c r="AY40"/>
       <c r="AZ40"/>
     </row>
-    <row r="41" spans="1:52" s="96" customFormat="1" ht="12" customHeight="1">
+    <row r="41" spans="1:52" s="90" customFormat="1" ht="12" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41"/>
       <c r="C41"/>
@@ -7431,7 +7443,7 @@
       <c r="F41"/>
       <c r="G41"/>
       <c r="H41"/>
-      <c r="I41" s="159"/>
+      <c r="I41" s="153"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
@@ -7452,7 +7464,7 @@
       <c r="AA41"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-      <c r="AD41" s="167"/>
+      <c r="AD41" s="161"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
@@ -7471,7 +7483,7 @@
       <c r="F42"/>
       <c r="G42"/>
       <c r="H42"/>
-      <c r="I42" s="159"/>
+      <c r="I42" s="153"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42"/>
@@ -7492,7 +7504,7 @@
       <c r="AA42"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="167"/>
+      <c r="AD42" s="161"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
@@ -7514,7 +7526,7 @@
       <c r="F43"/>
       <c r="G43"/>
       <c r="H43"/>
-      <c r="I43" s="159"/>
+      <c r="I43" s="153"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
@@ -7535,7 +7547,7 @@
       <c r="AA43"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="167"/>
+      <c r="AD43" s="161"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
@@ -7557,7 +7569,7 @@
       <c r="F44"/>
       <c r="G44"/>
       <c r="H44"/>
-      <c r="I44" s="159"/>
+      <c r="I44" s="153"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
@@ -7576,7 +7588,7 @@
       <c r="Y44"/>
       <c r="Z44"/>
       <c r="AA44"/>
-      <c r="AD44" s="167"/>
+      <c r="AD44" s="161"/>
       <c r="AU44"/>
       <c r="AV44"/>
       <c r="AW44"/>
@@ -7592,7 +7604,7 @@
       <c r="F45"/>
       <c r="G45"/>
       <c r="H45"/>
-      <c r="I45" s="159"/>
+      <c r="I45" s="153"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45"/>
@@ -7611,7 +7623,7 @@
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AD45" s="167"/>
+      <c r="AD45" s="161"/>
       <c r="AU45"/>
       <c r="AV45"/>
       <c r="AW45"/>
@@ -7627,7 +7639,7 @@
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46"/>
-      <c r="I46" s="159"/>
+      <c r="I46" s="153"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46"/>
@@ -7646,7 +7658,7 @@
       <c r="Y46"/>
       <c r="Z46"/>
       <c r="AA46"/>
-      <c r="AD46" s="167"/>
+      <c r="AD46" s="161"/>
       <c r="AU46"/>
       <c r="AV46"/>
       <c r="AW46"/>
@@ -7662,7 +7674,7 @@
       <c r="F47"/>
       <c r="G47"/>
       <c r="H47"/>
-      <c r="I47" s="159"/>
+      <c r="I47" s="153"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47"/>
@@ -7681,7 +7693,7 @@
       <c r="Y47"/>
       <c r="Z47"/>
       <c r="AA47"/>
-      <c r="AD47" s="167"/>
+      <c r="AD47" s="161"/>
       <c r="AU47"/>
       <c r="AV47"/>
       <c r="AW47"/>
@@ -7690,7 +7702,7 @@
       <c r="AZ47"/>
     </row>
     <row r="48" spans="1:52" ht="11.45" customHeight="1">
-      <c r="AD48" s="167"/>
+      <c r="AD48" s="161"/>
       <c r="AU48"/>
       <c r="AV48"/>
       <c r="AW48"/>
@@ -7700,12 +7712,12 @@
     </row>
     <row r="49" spans="9:49" ht="11.45" customHeight="1">
       <c r="I49" s="1"/>
-      <c r="M49" s="96"/>
-      <c r="N49" s="96"/>
+      <c r="M49" s="90"/>
+      <c r="N49" s="90"/>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
       <c r="Q49" s="8"/>
-      <c r="AA49" s="167"/>
+      <c r="AA49" s="161"/>
       <c r="AR49"/>
       <c r="AS49"/>
       <c r="AT49"/>
@@ -7715,12 +7727,12 @@
     </row>
     <row r="50" spans="9:49" ht="11.45" customHeight="1">
       <c r="I50" s="1"/>
-      <c r="M50" s="96"/>
-      <c r="N50" s="96"/>
+      <c r="M50" s="90"/>
+      <c r="N50" s="90"/>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
-      <c r="AA50" s="167"/>
+      <c r="AA50" s="161"/>
       <c r="AR50"/>
       <c r="AS50"/>
       <c r="AT50"/>
@@ -7730,12 +7742,12 @@
     </row>
     <row r="51" spans="9:49" ht="11.45" customHeight="1">
       <c r="I51" s="1"/>
-      <c r="M51" s="96"/>
-      <c r="N51" s="96"/>
+      <c r="M51" s="90"/>
+      <c r="N51" s="90"/>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
       <c r="Q51" s="8"/>
-      <c r="AA51" s="167"/>
+      <c r="AA51" s="161"/>
       <c r="AR51"/>
       <c r="AS51"/>
       <c r="AT51"/>
@@ -7745,12 +7757,12 @@
     </row>
     <row r="52" spans="9:49" ht="11.45" customHeight="1">
       <c r="I52" s="1"/>
-      <c r="M52" s="96"/>
-      <c r="N52" s="96"/>
+      <c r="M52" s="90"/>
+      <c r="N52" s="90"/>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
       <c r="Q52" s="8"/>
-      <c r="AA52" s="167"/>
+      <c r="AA52" s="161"/>
       <c r="AR52"/>
       <c r="AS52"/>
       <c r="AT52"/>
@@ -7760,12 +7772,12 @@
     </row>
     <row r="53" spans="9:49" ht="11.45" customHeight="1">
       <c r="I53" s="1"/>
-      <c r="M53" s="96"/>
-      <c r="N53" s="96"/>
+      <c r="M53" s="90"/>
+      <c r="N53" s="90"/>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
       <c r="Q53" s="8"/>
-      <c r="AA53" s="167"/>
+      <c r="AA53" s="161"/>
       <c r="AR53"/>
       <c r="AS53"/>
       <c r="AT53"/>
@@ -7775,12 +7787,12 @@
     </row>
     <row r="54" spans="9:49" ht="11.45" customHeight="1">
       <c r="I54" s="1"/>
-      <c r="M54" s="96"/>
-      <c r="N54" s="96"/>
+      <c r="M54" s="90"/>
+      <c r="N54" s="90"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
-      <c r="AA54" s="167"/>
+      <c r="AA54" s="161"/>
       <c r="AR54"/>
       <c r="AS54"/>
       <c r="AT54"/>
@@ -7790,12 +7802,12 @@
     </row>
     <row r="55" spans="9:49" ht="11.45" customHeight="1">
       <c r="I55" s="1"/>
-      <c r="M55" s="96"/>
-      <c r="N55" s="96"/>
+      <c r="M55" s="90"/>
+      <c r="N55" s="90"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
-      <c r="AA55" s="167"/>
+      <c r="AA55" s="161"/>
       <c r="AR55"/>
       <c r="AS55"/>
       <c r="AT55"/>
@@ -7805,12 +7817,12 @@
     </row>
     <row r="56" spans="9:49" ht="11.45" customHeight="1">
       <c r="I56" s="1"/>
-      <c r="M56" s="96"/>
-      <c r="N56" s="96"/>
+      <c r="M56" s="90"/>
+      <c r="N56" s="90"/>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
-      <c r="AA56" s="167"/>
+      <c r="AA56" s="161"/>
       <c r="AR56"/>
       <c r="AS56"/>
       <c r="AT56"/>
@@ -7820,12 +7832,12 @@
     </row>
     <row r="57" spans="9:49" ht="11.45" customHeight="1">
       <c r="I57" s="1"/>
-      <c r="M57" s="96"/>
-      <c r="N57" s="96"/>
+      <c r="M57" s="90"/>
+      <c r="N57" s="90"/>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
-      <c r="AA57" s="167"/>
+      <c r="AA57" s="161"/>
       <c r="AR57"/>
       <c r="AS57"/>
       <c r="AT57"/>
@@ -7835,12 +7847,12 @@
     </row>
     <row r="58" spans="9:49" ht="11.45" customHeight="1">
       <c r="I58" s="1"/>
-      <c r="M58" s="96"/>
-      <c r="N58" s="96"/>
+      <c r="M58" s="90"/>
+      <c r="N58" s="90"/>
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
-      <c r="AA58" s="167"/>
+      <c r="AA58" s="161"/>
       <c r="AR58"/>
       <c r="AS58"/>
       <c r="AT58"/>
@@ -7850,12 +7862,12 @@
     </row>
     <row r="59" spans="9:49" ht="11.45" customHeight="1">
       <c r="I59" s="1"/>
-      <c r="M59" s="96"/>
-      <c r="N59" s="96"/>
+      <c r="M59" s="90"/>
+      <c r="N59" s="90"/>
       <c r="O59" s="8"/>
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
-      <c r="AA59" s="167"/>
+      <c r="AA59" s="161"/>
       <c r="AR59"/>
       <c r="AS59"/>
       <c r="AT59"/>
@@ -7865,12 +7877,12 @@
     </row>
     <row r="60" spans="9:49" ht="11.45" customHeight="1">
       <c r="I60" s="1"/>
-      <c r="M60" s="96"/>
-      <c r="N60" s="96"/>
+      <c r="M60" s="90"/>
+      <c r="N60" s="90"/>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="AA60" s="167"/>
+      <c r="AA60" s="161"/>
       <c r="AR60"/>
       <c r="AS60"/>
       <c r="AT60"/>
@@ -7880,12 +7892,12 @@
     </row>
     <row r="61" spans="9:49" ht="11.45" customHeight="1">
       <c r="I61" s="1"/>
-      <c r="M61" s="96"/>
-      <c r="N61" s="96"/>
+      <c r="M61" s="90"/>
+      <c r="N61" s="90"/>
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="AA61" s="167"/>
+      <c r="AA61" s="161"/>
       <c r="AR61"/>
       <c r="AS61"/>
       <c r="AT61"/>
@@ -7895,12 +7907,12 @@
     </row>
     <row r="62" spans="9:49" ht="11.45" customHeight="1">
       <c r="I62" s="1"/>
-      <c r="M62" s="96"/>
-      <c r="N62" s="96"/>
+      <c r="M62" s="90"/>
+      <c r="N62" s="90"/>
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="AA62" s="167"/>
+      <c r="AA62" s="161"/>
       <c r="AR62"/>
       <c r="AS62"/>
       <c r="AT62"/>
@@ -7910,12 +7922,12 @@
     </row>
     <row r="63" spans="9:49" ht="11.45" customHeight="1">
       <c r="I63" s="1"/>
-      <c r="M63" s="96"/>
-      <c r="N63" s="96"/>
+      <c r="M63" s="90"/>
+      <c r="N63" s="90"/>
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="AA63" s="167"/>
+      <c r="AA63" s="161"/>
       <c r="AR63"/>
       <c r="AS63"/>
       <c r="AT63"/>
@@ -7925,12 +7937,12 @@
     </row>
     <row r="64" spans="9:49" ht="11.45" customHeight="1">
       <c r="I64" s="1"/>
-      <c r="M64" s="96"/>
-      <c r="N64" s="96"/>
+      <c r="M64" s="90"/>
+      <c r="N64" s="90"/>
       <c r="O64" s="8"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
-      <c r="AA64" s="167"/>
+      <c r="AA64" s="161"/>
       <c r="AR64"/>
       <c r="AS64"/>
       <c r="AT64"/>
@@ -7940,12 +7952,12 @@
     </row>
     <row r="65" spans="9:52" ht="11.45" customHeight="1">
       <c r="I65" s="1"/>
-      <c r="M65" s="96"/>
-      <c r="N65" s="96"/>
+      <c r="M65" s="90"/>
+      <c r="N65" s="90"/>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
-      <c r="AA65" s="167"/>
+      <c r="AA65" s="161"/>
       <c r="AR65"/>
       <c r="AS65"/>
       <c r="AT65"/>
@@ -7955,12 +7967,12 @@
     </row>
     <row r="66" spans="9:52" ht="11.45" customHeight="1">
       <c r="I66" s="1"/>
-      <c r="M66" s="96"/>
-      <c r="N66" s="96"/>
+      <c r="M66" s="90"/>
+      <c r="N66" s="90"/>
       <c r="O66" s="8"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
-      <c r="AA66" s="167"/>
+      <c r="AA66" s="161"/>
       <c r="AR66"/>
       <c r="AS66"/>
       <c r="AT66"/>
@@ -7969,7 +7981,7 @@
       <c r="AW66"/>
     </row>
     <row r="67" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD67" s="167"/>
+      <c r="AD67" s="161"/>
       <c r="AU67"/>
       <c r="AV67"/>
       <c r="AW67"/>
@@ -7978,7 +7990,7 @@
       <c r="AZ67"/>
     </row>
     <row r="68" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD68" s="167"/>
+      <c r="AD68" s="161"/>
       <c r="AU68"/>
       <c r="AV68"/>
       <c r="AW68"/>
@@ -7987,7 +7999,7 @@
       <c r="AZ68"/>
     </row>
     <row r="69" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD69" s="167"/>
+      <c r="AD69" s="161"/>
       <c r="AU69"/>
       <c r="AV69"/>
       <c r="AW69"/>
@@ -7996,7 +8008,7 @@
       <c r="AZ69"/>
     </row>
     <row r="70" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD70" s="167"/>
+      <c r="AD70" s="161"/>
       <c r="AU70"/>
       <c r="AV70"/>
       <c r="AW70"/>
@@ -8005,7 +8017,7 @@
       <c r="AZ70"/>
     </row>
     <row r="71" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD71" s="167"/>
+      <c r="AD71" s="161"/>
       <c r="AU71"/>
       <c r="AV71"/>
       <c r="AW71"/>
@@ -8014,7 +8026,7 @@
       <c r="AZ71"/>
     </row>
     <row r="72" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD72" s="167"/>
+      <c r="AD72" s="161"/>
       <c r="AU72"/>
       <c r="AV72"/>
       <c r="AW72"/>
@@ -8023,7 +8035,7 @@
       <c r="AZ72"/>
     </row>
     <row r="73" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD73" s="167"/>
+      <c r="AD73" s="161"/>
       <c r="AU73"/>
       <c r="AV73"/>
       <c r="AW73"/>
@@ -8032,7 +8044,7 @@
       <c r="AZ73"/>
     </row>
     <row r="74" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD74" s="167"/>
+      <c r="AD74" s="161"/>
       <c r="AU74"/>
       <c r="AV74"/>
       <c r="AW74"/>
@@ -8041,7 +8053,7 @@
       <c r="AZ74"/>
     </row>
     <row r="75" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD75" s="167"/>
+      <c r="AD75" s="161"/>
       <c r="AU75"/>
       <c r="AV75"/>
       <c r="AW75"/>
@@ -8050,7 +8062,7 @@
       <c r="AZ75"/>
     </row>
     <row r="76" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD76" s="167"/>
+      <c r="AD76" s="161"/>
       <c r="AU76"/>
       <c r="AV76"/>
       <c r="AW76"/>
@@ -8059,7 +8071,7 @@
       <c r="AZ76"/>
     </row>
     <row r="77" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD77" s="167"/>
+      <c r="AD77" s="161"/>
       <c r="AU77"/>
       <c r="AV77"/>
       <c r="AW77"/>
@@ -8068,7 +8080,7 @@
       <c r="AZ77"/>
     </row>
     <row r="78" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD78" s="167"/>
+      <c r="AD78" s="161"/>
       <c r="AU78"/>
       <c r="AV78"/>
       <c r="AW78"/>
@@ -8077,7 +8089,7 @@
       <c r="AZ78"/>
     </row>
     <row r="79" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD79" s="167"/>
+      <c r="AD79" s="161"/>
       <c r="AU79"/>
       <c r="AV79"/>
       <c r="AW79"/>
@@ -8086,7 +8098,7 @@
       <c r="AZ79"/>
     </row>
     <row r="80" spans="9:52" ht="11.45" customHeight="1">
-      <c r="AD80" s="167"/>
+      <c r="AD80" s="161"/>
       <c r="AU80"/>
       <c r="AV80"/>
       <c r="AW80"/>
@@ -8095,7 +8107,7 @@
       <c r="AZ80"/>
     </row>
     <row r="81" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD81" s="167"/>
+      <c r="AD81" s="161"/>
       <c r="AU81"/>
       <c r="AV81"/>
       <c r="AW81"/>
@@ -8104,7 +8116,7 @@
       <c r="AZ81"/>
     </row>
     <row r="82" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD82" s="167"/>
+      <c r="AD82" s="161"/>
       <c r="AU82"/>
       <c r="AV82"/>
       <c r="AW82"/>
@@ -8113,7 +8125,7 @@
       <c r="AZ82"/>
     </row>
     <row r="83" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD83" s="167"/>
+      <c r="AD83" s="161"/>
       <c r="AU83"/>
       <c r="AV83"/>
       <c r="AW83"/>
@@ -8122,7 +8134,7 @@
       <c r="AZ83"/>
     </row>
     <row r="84" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD84" s="167"/>
+      <c r="AD84" s="161"/>
       <c r="AU84"/>
       <c r="AV84"/>
       <c r="AW84"/>
@@ -8131,7 +8143,7 @@
       <c r="AZ84"/>
     </row>
     <row r="85" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD85" s="167"/>
+      <c r="AD85" s="161"/>
       <c r="AU85"/>
       <c r="AV85"/>
       <c r="AW85"/>
@@ -8140,7 +8152,7 @@
       <c r="AZ85"/>
     </row>
     <row r="86" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD86" s="167"/>
+      <c r="AD86" s="161"/>
       <c r="AU86"/>
       <c r="AV86"/>
       <c r="AW86"/>
@@ -8149,7 +8161,7 @@
       <c r="AZ86"/>
     </row>
     <row r="87" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD87" s="167"/>
+      <c r="AD87" s="161"/>
       <c r="AU87"/>
       <c r="AV87"/>
       <c r="AW87"/>
@@ -8158,7 +8170,7 @@
       <c r="AZ87"/>
     </row>
     <row r="88" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD88" s="167"/>
+      <c r="AD88" s="161"/>
       <c r="AU88"/>
       <c r="AV88"/>
       <c r="AW88"/>
@@ -8167,7 +8179,7 @@
       <c r="AZ88"/>
     </row>
     <row r="89" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD89" s="167"/>
+      <c r="AD89" s="161"/>
       <c r="AU89"/>
       <c r="AV89"/>
       <c r="AW89"/>
@@ -8176,7 +8188,7 @@
       <c r="AZ89"/>
     </row>
     <row r="90" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD90" s="167"/>
+      <c r="AD90" s="161"/>
       <c r="AU90"/>
       <c r="AV90"/>
       <c r="AW90"/>
@@ -8185,7 +8197,7 @@
       <c r="AZ90"/>
     </row>
     <row r="91" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD91" s="167"/>
+      <c r="AD91" s="161"/>
       <c r="AU91"/>
       <c r="AV91"/>
       <c r="AW91"/>
@@ -8194,7 +8206,7 @@
       <c r="AZ91"/>
     </row>
     <row r="92" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD92" s="167"/>
+      <c r="AD92" s="161"/>
       <c r="AU92"/>
       <c r="AV92"/>
       <c r="AW92"/>
@@ -8203,7 +8215,7 @@
       <c r="AZ92"/>
     </row>
     <row r="93" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD93" s="167"/>
+      <c r="AD93" s="161"/>
       <c r="AU93"/>
       <c r="AV93"/>
       <c r="AW93"/>
@@ -8212,7 +8224,7 @@
       <c r="AZ93"/>
     </row>
     <row r="94" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD94" s="167"/>
+      <c r="AD94" s="161"/>
       <c r="AU94"/>
       <c r="AV94"/>
       <c r="AW94"/>
@@ -8221,7 +8233,7 @@
       <c r="AZ94"/>
     </row>
     <row r="95" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD95" s="167"/>
+      <c r="AD95" s="161"/>
       <c r="AU95"/>
       <c r="AV95"/>
       <c r="AW95"/>
@@ -8230,7 +8242,7 @@
       <c r="AZ95"/>
     </row>
     <row r="96" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD96" s="167"/>
+      <c r="AD96" s="161"/>
       <c r="AU96"/>
       <c r="AV96"/>
       <c r="AW96"/>
@@ -8239,7 +8251,7 @@
       <c r="AZ96"/>
     </row>
     <row r="97" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD97" s="167"/>
+      <c r="AD97" s="161"/>
       <c r="AU97"/>
       <c r="AV97"/>
       <c r="AW97"/>
@@ -8248,7 +8260,7 @@
       <c r="AZ97"/>
     </row>
     <row r="98" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD98" s="167"/>
+      <c r="AD98" s="161"/>
       <c r="AU98"/>
       <c r="AV98"/>
       <c r="AW98"/>
@@ -8257,7 +8269,7 @@
       <c r="AZ98"/>
     </row>
     <row r="99" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD99" s="167"/>
+      <c r="AD99" s="161"/>
       <c r="AU99"/>
       <c r="AV99"/>
       <c r="AW99"/>
@@ -8266,7 +8278,7 @@
       <c r="AZ99"/>
     </row>
     <row r="100" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD100" s="167"/>
+      <c r="AD100" s="161"/>
       <c r="AU100"/>
       <c r="AV100"/>
       <c r="AW100"/>
@@ -8275,7 +8287,7 @@
       <c r="AZ100"/>
     </row>
     <row r="101" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD101" s="167"/>
+      <c r="AD101" s="161"/>
       <c r="AU101"/>
       <c r="AV101"/>
       <c r="AW101"/>
@@ -8284,7 +8296,7 @@
       <c r="AZ101"/>
     </row>
     <row r="102" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD102" s="167"/>
+      <c r="AD102" s="161"/>
       <c r="AU102"/>
       <c r="AV102"/>
       <c r="AW102"/>
@@ -8293,7 +8305,7 @@
       <c r="AZ102"/>
     </row>
     <row r="103" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD103" s="167"/>
+      <c r="AD103" s="161"/>
       <c r="AU103"/>
       <c r="AV103"/>
       <c r="AW103"/>
@@ -8302,7 +8314,7 @@
       <c r="AZ103"/>
     </row>
     <row r="104" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD104" s="167"/>
+      <c r="AD104" s="161"/>
       <c r="AU104"/>
       <c r="AV104"/>
       <c r="AW104"/>
@@ -8311,7 +8323,7 @@
       <c r="AZ104"/>
     </row>
     <row r="105" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD105" s="167"/>
+      <c r="AD105" s="161"/>
       <c r="AU105"/>
       <c r="AV105"/>
       <c r="AW105"/>
@@ -8320,7 +8332,7 @@
       <c r="AZ105"/>
     </row>
     <row r="106" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD106" s="167"/>
+      <c r="AD106" s="161"/>
       <c r="AU106"/>
       <c r="AV106"/>
       <c r="AW106"/>
@@ -8329,7 +8341,7 @@
       <c r="AZ106"/>
     </row>
     <row r="107" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD107" s="167"/>
+      <c r="AD107" s="161"/>
       <c r="AU107"/>
       <c r="AV107"/>
       <c r="AW107"/>
@@ -8338,7 +8350,7 @@
       <c r="AZ107"/>
     </row>
     <row r="108" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD108" s="167"/>
+      <c r="AD108" s="161"/>
       <c r="AU108"/>
       <c r="AV108"/>
       <c r="AW108"/>
@@ -8347,7 +8359,7 @@
       <c r="AZ108"/>
     </row>
     <row r="109" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD109" s="167"/>
+      <c r="AD109" s="161"/>
       <c r="AU109"/>
       <c r="AV109"/>
       <c r="AW109"/>
@@ -8356,7 +8368,7 @@
       <c r="AZ109"/>
     </row>
     <row r="110" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD110" s="167"/>
+      <c r="AD110" s="161"/>
       <c r="AU110"/>
       <c r="AV110"/>
       <c r="AW110"/>
@@ -8365,7 +8377,7 @@
       <c r="AZ110"/>
     </row>
     <row r="111" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD111" s="167"/>
+      <c r="AD111" s="161"/>
       <c r="AU111"/>
       <c r="AV111"/>
       <c r="AW111"/>
@@ -8374,7 +8386,7 @@
       <c r="AZ111"/>
     </row>
     <row r="112" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD112" s="167"/>
+      <c r="AD112" s="161"/>
       <c r="AU112"/>
       <c r="AV112"/>
       <c r="AW112"/>
@@ -8383,7 +8395,7 @@
       <c r="AZ112"/>
     </row>
     <row r="113" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD113" s="167"/>
+      <c r="AD113" s="161"/>
       <c r="AU113"/>
       <c r="AV113"/>
       <c r="AW113"/>
@@ -8392,7 +8404,7 @@
       <c r="AZ113"/>
     </row>
     <row r="114" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD114" s="167"/>
+      <c r="AD114" s="161"/>
       <c r="AU114"/>
       <c r="AV114"/>
       <c r="AW114"/>
@@ -8401,7 +8413,7 @@
       <c r="AZ114"/>
     </row>
     <row r="115" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD115" s="167"/>
+      <c r="AD115" s="161"/>
       <c r="AU115"/>
       <c r="AV115"/>
       <c r="AW115"/>
@@ -8410,7 +8422,7 @@
       <c r="AZ115"/>
     </row>
     <row r="116" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD116" s="167"/>
+      <c r="AD116" s="161"/>
       <c r="AU116"/>
       <c r="AV116"/>
       <c r="AW116"/>
@@ -8419,7 +8431,7 @@
       <c r="AZ116"/>
     </row>
     <row r="117" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD117" s="167"/>
+      <c r="AD117" s="161"/>
       <c r="AU117"/>
       <c r="AV117"/>
       <c r="AW117"/>
@@ -8428,7 +8440,7 @@
       <c r="AZ117"/>
     </row>
     <row r="118" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD118" s="167"/>
+      <c r="AD118" s="161"/>
       <c r="AU118"/>
       <c r="AV118"/>
       <c r="AW118"/>
@@ -8437,7 +8449,7 @@
       <c r="AZ118"/>
     </row>
     <row r="119" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD119" s="167"/>
+      <c r="AD119" s="161"/>
       <c r="AU119"/>
       <c r="AV119"/>
       <c r="AW119"/>
@@ -8446,7 +8458,7 @@
       <c r="AZ119"/>
     </row>
     <row r="120" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD120" s="167"/>
+      <c r="AD120" s="161"/>
       <c r="AU120"/>
       <c r="AV120"/>
       <c r="AW120"/>
@@ -8455,7 +8467,7 @@
       <c r="AZ120"/>
     </row>
     <row r="121" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD121" s="167"/>
+      <c r="AD121" s="161"/>
       <c r="AU121"/>
       <c r="AV121"/>
       <c r="AW121"/>
@@ -8464,7 +8476,7 @@
       <c r="AZ121"/>
     </row>
     <row r="122" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD122" s="167"/>
+      <c r="AD122" s="161"/>
       <c r="AU122"/>
       <c r="AV122"/>
       <c r="AW122"/>
@@ -8473,7 +8485,7 @@
       <c r="AZ122"/>
     </row>
     <row r="123" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD123" s="167"/>
+      <c r="AD123" s="161"/>
       <c r="AU123"/>
       <c r="AV123"/>
       <c r="AW123"/>
@@ -8482,7 +8494,7 @@
       <c r="AZ123"/>
     </row>
     <row r="124" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD124" s="167"/>
+      <c r="AD124" s="161"/>
       <c r="AU124"/>
       <c r="AV124"/>
       <c r="AW124"/>
@@ -8491,7 +8503,7 @@
       <c r="AZ124"/>
     </row>
     <row r="125" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD125" s="167"/>
+      <c r="AD125" s="161"/>
       <c r="AU125"/>
       <c r="AV125"/>
       <c r="AW125"/>
@@ -8500,7 +8512,7 @@
       <c r="AZ125"/>
     </row>
     <row r="126" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD126" s="167"/>
+      <c r="AD126" s="161"/>
       <c r="AU126"/>
       <c r="AV126"/>
       <c r="AW126"/>
@@ -8509,7 +8521,7 @@
       <c r="AZ126"/>
     </row>
     <row r="127" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD127" s="167"/>
+      <c r="AD127" s="161"/>
       <c r="AU127"/>
       <c r="AV127"/>
       <c r="AW127"/>
@@ -8518,7 +8530,7 @@
       <c r="AZ127"/>
     </row>
     <row r="128" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD128" s="167"/>
+      <c r="AD128" s="161"/>
       <c r="AU128"/>
       <c r="AV128"/>
       <c r="AW128"/>
@@ -8527,7 +8539,7 @@
       <c r="AZ128"/>
     </row>
     <row r="129" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD129" s="167"/>
+      <c r="AD129" s="161"/>
       <c r="AU129"/>
       <c r="AV129"/>
       <c r="AW129"/>
@@ -8536,7 +8548,7 @@
       <c r="AZ129"/>
     </row>
     <row r="130" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD130" s="167"/>
+      <c r="AD130" s="161"/>
       <c r="AU130"/>
       <c r="AV130"/>
       <c r="AW130"/>
@@ -8545,7 +8557,7 @@
       <c r="AZ130"/>
     </row>
     <row r="131" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD131" s="167"/>
+      <c r="AD131" s="161"/>
       <c r="AU131"/>
       <c r="AV131"/>
       <c r="AW131"/>
@@ -8554,7 +8566,7 @@
       <c r="AZ131"/>
     </row>
     <row r="132" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD132" s="167"/>
+      <c r="AD132" s="161"/>
       <c r="AU132"/>
       <c r="AV132"/>
       <c r="AW132"/>
@@ -8563,7 +8575,7 @@
       <c r="AZ132"/>
     </row>
     <row r="133" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD133" s="167"/>
+      <c r="AD133" s="161"/>
       <c r="AU133"/>
       <c r="AV133"/>
       <c r="AW133"/>
@@ -8572,7 +8584,7 @@
       <c r="AZ133"/>
     </row>
     <row r="134" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD134" s="167"/>
+      <c r="AD134" s="161"/>
       <c r="AU134"/>
       <c r="AV134"/>
       <c r="AW134"/>
@@ -8581,7 +8593,7 @@
       <c r="AZ134"/>
     </row>
     <row r="135" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD135" s="167"/>
+      <c r="AD135" s="161"/>
       <c r="AU135"/>
       <c r="AV135"/>
       <c r="AW135"/>
@@ -8590,7 +8602,7 @@
       <c r="AZ135"/>
     </row>
     <row r="136" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD136" s="167"/>
+      <c r="AD136" s="161"/>
       <c r="AU136"/>
       <c r="AV136"/>
       <c r="AW136"/>
@@ -8599,7 +8611,7 @@
       <c r="AZ136"/>
     </row>
     <row r="137" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD137" s="167"/>
+      <c r="AD137" s="161"/>
       <c r="AU137"/>
       <c r="AV137"/>
       <c r="AW137"/>
@@ -8608,7 +8620,7 @@
       <c r="AZ137"/>
     </row>
     <row r="138" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD138" s="167"/>
+      <c r="AD138" s="161"/>
       <c r="AU138"/>
       <c r="AV138"/>
       <c r="AW138"/>
@@ -8617,7 +8629,7 @@
       <c r="AZ138"/>
     </row>
     <row r="139" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD139" s="167"/>
+      <c r="AD139" s="161"/>
       <c r="AU139"/>
       <c r="AV139"/>
       <c r="AW139"/>
@@ -8626,7 +8638,7 @@
       <c r="AZ139"/>
     </row>
     <row r="140" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD140" s="167"/>
+      <c r="AD140" s="161"/>
       <c r="AU140"/>
       <c r="AV140"/>
       <c r="AW140"/>
@@ -8635,7 +8647,7 @@
       <c r="AZ140"/>
     </row>
     <row r="141" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD141" s="167"/>
+      <c r="AD141" s="161"/>
       <c r="AU141"/>
       <c r="AV141"/>
       <c r="AW141"/>
@@ -8644,7 +8656,7 @@
       <c r="AZ141"/>
     </row>
     <row r="142" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD142" s="167"/>
+      <c r="AD142" s="161"/>
       <c r="AU142"/>
       <c r="AV142"/>
       <c r="AW142"/>
@@ -8653,7 +8665,7 @@
       <c r="AZ142"/>
     </row>
     <row r="143" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD143" s="167"/>
+      <c r="AD143" s="161"/>
       <c r="AU143"/>
       <c r="AV143"/>
       <c r="AW143"/>
@@ -8662,7 +8674,7 @@
       <c r="AZ143"/>
     </row>
     <row r="144" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD144" s="167"/>
+      <c r="AD144" s="161"/>
       <c r="AU144"/>
       <c r="AV144"/>
       <c r="AW144"/>
@@ -8671,7 +8683,7 @@
       <c r="AZ144"/>
     </row>
     <row r="145" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD145" s="167"/>
+      <c r="AD145" s="161"/>
       <c r="AU145"/>
       <c r="AV145"/>
       <c r="AW145"/>
@@ -8680,7 +8692,7 @@
       <c r="AZ145"/>
     </row>
     <row r="146" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD146" s="167"/>
+      <c r="AD146" s="161"/>
       <c r="AU146"/>
       <c r="AV146"/>
       <c r="AW146"/>
@@ -8689,7 +8701,7 @@
       <c r="AZ146"/>
     </row>
     <row r="147" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD147" s="167"/>
+      <c r="AD147" s="161"/>
       <c r="AU147"/>
       <c r="AV147"/>
       <c r="AW147"/>
@@ -8698,7 +8710,7 @@
       <c r="AZ147"/>
     </row>
     <row r="148" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD148" s="167"/>
+      <c r="AD148" s="161"/>
       <c r="AU148"/>
       <c r="AV148"/>
       <c r="AW148"/>
@@ -8707,7 +8719,7 @@
       <c r="AZ148"/>
     </row>
     <row r="149" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD149" s="167"/>
+      <c r="AD149" s="161"/>
       <c r="AU149"/>
       <c r="AV149"/>
       <c r="AW149"/>
@@ -8716,7 +8728,7 @@
       <c r="AZ149"/>
     </row>
     <row r="150" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD150" s="167"/>
+      <c r="AD150" s="161"/>
       <c r="AU150"/>
       <c r="AV150"/>
       <c r="AW150"/>
@@ -8725,7 +8737,7 @@
       <c r="AZ150"/>
     </row>
     <row r="151" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD151" s="167"/>
+      <c r="AD151" s="161"/>
       <c r="AU151"/>
       <c r="AV151"/>
       <c r="AW151"/>
@@ -8734,7 +8746,7 @@
       <c r="AZ151"/>
     </row>
     <row r="152" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD152" s="167"/>
+      <c r="AD152" s="161"/>
       <c r="AU152"/>
       <c r="AV152"/>
       <c r="AW152"/>
@@ -8743,7 +8755,7 @@
       <c r="AZ152"/>
     </row>
     <row r="153" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD153" s="167"/>
+      <c r="AD153" s="161"/>
       <c r="AU153"/>
       <c r="AV153"/>
       <c r="AW153"/>
@@ -8752,7 +8764,7 @@
       <c r="AZ153"/>
     </row>
     <row r="154" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD154" s="167"/>
+      <c r="AD154" s="161"/>
       <c r="AU154"/>
       <c r="AV154"/>
       <c r="AW154"/>
@@ -8761,7 +8773,7 @@
       <c r="AZ154"/>
     </row>
     <row r="155" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD155" s="167"/>
+      <c r="AD155" s="161"/>
       <c r="AU155"/>
       <c r="AV155"/>
       <c r="AW155"/>
@@ -8770,7 +8782,7 @@
       <c r="AZ155"/>
     </row>
     <row r="156" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD156" s="167"/>
+      <c r="AD156" s="161"/>
       <c r="AU156"/>
       <c r="AV156"/>
       <c r="AW156"/>
@@ -8779,7 +8791,7 @@
       <c r="AZ156"/>
     </row>
     <row r="157" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD157" s="167"/>
+      <c r="AD157" s="161"/>
       <c r="AU157"/>
       <c r="AV157"/>
       <c r="AW157"/>
@@ -8788,7 +8800,7 @@
       <c r="AZ157"/>
     </row>
     <row r="158" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD158" s="167"/>
+      <c r="AD158" s="161"/>
       <c r="AU158"/>
       <c r="AV158"/>
       <c r="AW158"/>
@@ -8797,7 +8809,7 @@
       <c r="AZ158"/>
     </row>
     <row r="159" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD159" s="167"/>
+      <c r="AD159" s="161"/>
       <c r="AU159"/>
       <c r="AV159"/>
       <c r="AW159"/>
@@ -8806,7 +8818,7 @@
       <c r="AZ159"/>
     </row>
     <row r="160" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD160" s="167"/>
+      <c r="AD160" s="161"/>
       <c r="AU160"/>
       <c r="AV160"/>
       <c r="AW160"/>
@@ -8815,7 +8827,7 @@
       <c r="AZ160"/>
     </row>
     <row r="161" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD161" s="167"/>
+      <c r="AD161" s="161"/>
       <c r="AU161"/>
       <c r="AV161"/>
       <c r="AW161"/>
@@ -8824,7 +8836,7 @@
       <c r="AZ161"/>
     </row>
     <row r="162" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD162" s="167"/>
+      <c r="AD162" s="161"/>
       <c r="AU162"/>
       <c r="AV162"/>
       <c r="AW162"/>
@@ -8833,7 +8845,7 @@
       <c r="AZ162"/>
     </row>
     <row r="163" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD163" s="167"/>
+      <c r="AD163" s="161"/>
       <c r="AU163"/>
       <c r="AV163"/>
       <c r="AW163"/>
@@ -8842,7 +8854,7 @@
       <c r="AZ163"/>
     </row>
     <row r="164" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD164" s="167"/>
+      <c r="AD164" s="161"/>
       <c r="AU164"/>
       <c r="AV164"/>
       <c r="AW164"/>
@@ -8851,7 +8863,7 @@
       <c r="AZ164"/>
     </row>
     <row r="165" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD165" s="167"/>
+      <c r="AD165" s="161"/>
       <c r="AU165"/>
       <c r="AV165"/>
       <c r="AW165"/>
@@ -8860,7 +8872,7 @@
       <c r="AZ165"/>
     </row>
     <row r="166" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD166" s="167"/>
+      <c r="AD166" s="161"/>
       <c r="AU166"/>
       <c r="AV166"/>
       <c r="AW166"/>
@@ -8869,7 +8881,7 @@
       <c r="AZ166"/>
     </row>
     <row r="167" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD167" s="167"/>
+      <c r="AD167" s="161"/>
       <c r="AU167"/>
       <c r="AV167"/>
       <c r="AW167"/>
@@ -8878,7 +8890,7 @@
       <c r="AZ167"/>
     </row>
     <row r="168" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD168" s="167"/>
+      <c r="AD168" s="161"/>
       <c r="AU168"/>
       <c r="AV168"/>
       <c r="AW168"/>
@@ -8887,7 +8899,7 @@
       <c r="AZ168"/>
     </row>
     <row r="169" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD169" s="167"/>
+      <c r="AD169" s="161"/>
       <c r="AU169"/>
       <c r="AV169"/>
       <c r="AW169"/>
@@ -8896,7 +8908,7 @@
       <c r="AZ169"/>
     </row>
     <row r="170" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD170" s="167"/>
+      <c r="AD170" s="161"/>
       <c r="AU170"/>
       <c r="AV170"/>
       <c r="AW170"/>
@@ -8905,7 +8917,7 @@
       <c r="AZ170"/>
     </row>
     <row r="171" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD171" s="167"/>
+      <c r="AD171" s="161"/>
       <c r="AU171"/>
       <c r="AV171"/>
       <c r="AW171"/>
@@ -8914,7 +8926,7 @@
       <c r="AZ171"/>
     </row>
     <row r="172" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD172" s="167"/>
+      <c r="AD172" s="161"/>
       <c r="AU172"/>
       <c r="AV172"/>
       <c r="AW172"/>
@@ -8923,7 +8935,7 @@
       <c r="AZ172"/>
     </row>
     <row r="173" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD173" s="167"/>
+      <c r="AD173" s="161"/>
       <c r="AU173"/>
       <c r="AV173"/>
       <c r="AW173"/>
@@ -8932,7 +8944,7 @@
       <c r="AZ173"/>
     </row>
     <row r="174" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD174" s="167"/>
+      <c r="AD174" s="161"/>
       <c r="AU174"/>
       <c r="AV174"/>
       <c r="AW174"/>
@@ -8941,7 +8953,7 @@
       <c r="AZ174"/>
     </row>
     <row r="175" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD175" s="167"/>
+      <c r="AD175" s="161"/>
       <c r="AU175"/>
       <c r="AV175"/>
       <c r="AW175"/>
@@ -8950,7 +8962,7 @@
       <c r="AZ175"/>
     </row>
     <row r="176" spans="30:52" ht="11.45" customHeight="1">
-      <c r="AD176" s="167"/>
+      <c r="AD176" s="161"/>
       <c r="AU176"/>
       <c r="AV176"/>
       <c r="AW176"/>
@@ -8959,7 +8971,7 @@
       <c r="AZ176"/>
   